--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-15T19:11:07+00:00</t>
+    <t>2026-01-16T14:21:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-16T14:21:16+00:00</t>
+    <t>2026-01-19T10:22:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8035" uniqueCount="788">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="8035" uniqueCount="787">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-20T10:13:19+00:00</t>
+    <t>2026-01-21T17:03:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1590,7 +1590,7 @@
     <t>MedicationRequest.identifier</t>
   </si>
   <si>
-    <t>Geplante-Abgabe-ID (früher eMed-ID), bildet 'Rezept-Klammer' bei mehreren gleichzeitig ausgestellten geplanten Abgaben.</t>
+    <t>MedicationRequest identifier = {eMed-ID}_{locally assigned ID}  Setzt sich zusammen aus groupIdentifier (Rezept-Klammer) und individueller Identifikation der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -1657,7 +1657,7 @@
     <t>MedicationRequest.category</t>
   </si>
   <si>
-    <t>Art der Medikamentenanforderung (z.B. ambulante oder stationäre Einnahme oder Verabreichung)</t>
+    <t>Kategorie damit geplante Abgabe von Medikationsplaneintrag unterschieden werden kann</t>
   </si>
   <si>
     <t>Indicates the type of medication request (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -2026,7 +2026,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t>Grund für die Verordnung des Arzneimittels. Annahme: Keine Verwendung in der geplanten Abgabe, reasonReference ausreichend.</t>
+    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz (evtl. Invariante).</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -2046,9 +2046,6 @@
   <si>
     <t xml:space="preserve">Reference(Condition|4.0.1|Observation|4.0.1)
 </t>
-  </si>
-  <si>
-    <t>Grund für die Verordnung des Arzneimittels (Referenz). Verwendung erst, wenn e-Diagnose referenzierbar ist.</t>
   </si>
   <si>
     <t>Condition or observation that supports why the medication was ordered.</t>
@@ -3293,7 +3290,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
     </row>
     <row r="91">
@@ -3301,7 +3298,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>755</v>
+        <v>754</v>
       </c>
     </row>
     <row r="92">
@@ -3317,7 +3314,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>756</v>
+        <v>755</v>
       </c>
     </row>
     <row r="94">
@@ -3325,7 +3322,7 @@
         <v>10</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
     </row>
     <row r="95">
@@ -3387,7 +3384,7 @@
         <v>24</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
     </row>
     <row r="103">
@@ -15656,7 +15653,7 @@
         <v>77</v>
       </c>
       <c r="H117" t="s" s="2">
-        <v>77</v>
+        <v>78</v>
       </c>
       <c r="I117" t="s" s="2">
         <v>23</v>
@@ -16488,7 +16485,7 @@
         <v>84</v>
       </c>
       <c r="H125" t="s" s="2">
-        <v>84</v>
+        <v>78</v>
       </c>
       <c r="I125" t="s" s="2">
         <v>23</v>
@@ -17123,7 +17120,7 @@
         <v>84</v>
       </c>
       <c r="I131" t="s" s="2">
-        <v>85</v>
+        <v>23</v>
       </c>
       <c r="J131" t="s" s="2">
         <v>23</v>
@@ -18496,13 +18493,13 @@
         <v>652</v>
       </c>
       <c r="M144" t="s" s="2">
+        <v>646</v>
+      </c>
+      <c r="N144" t="s" s="2">
         <v>653</v>
       </c>
-      <c r="N144" t="s" s="2">
+      <c r="O144" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="O144" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="P144" s="2"/>
       <c r="Q144" t="s" s="2">
@@ -18572,10 +18569,10 @@
         <v>485</v>
       </c>
       <c r="B145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D145" s="2"/>
       <c r="E145" t="s" s="2">
@@ -18598,13 +18595,13 @@
         <v>85</v>
       </c>
       <c r="L145" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="M145" t="s" s="2">
         <v>542</v>
       </c>
       <c r="N145" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="O145" s="2"/>
       <c r="P145" s="2"/>
@@ -18655,7 +18652,7 @@
         <v>23</v>
       </c>
       <c r="AG145" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AH145" t="s" s="2">
         <v>77</v>
@@ -18675,10 +18672,10 @@
         <v>485</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C146" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D146" s="2"/>
       <c r="E146" t="s" s="2">
@@ -18707,7 +18704,7 @@
         <v>542</v>
       </c>
       <c r="N146" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O146" s="2"/>
       <c r="P146" s="2"/>
@@ -18758,7 +18755,7 @@
         <v>23</v>
       </c>
       <c r="AG146" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AH146" t="s" s="2">
         <v>77</v>
@@ -18778,10 +18775,10 @@
         <v>485</v>
       </c>
       <c r="B147" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C147" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D147" s="2"/>
       <c r="E147" t="s" s="2">
@@ -18804,13 +18801,13 @@
         <v>85</v>
       </c>
       <c r="L147" t="s" s="2">
+        <v>661</v>
+      </c>
+      <c r="M147" t="s" s="2">
         <v>662</v>
       </c>
-      <c r="M147" t="s" s="2">
+      <c r="N147" t="s" s="2">
         <v>663</v>
-      </c>
-      <c r="N147" t="s" s="2">
-        <v>664</v>
       </c>
       <c r="O147" s="2"/>
       <c r="P147" s="2"/>
@@ -18861,7 +18858,7 @@
         <v>23</v>
       </c>
       <c r="AG147" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AH147" t="s" s="2">
         <v>77</v>
@@ -18881,10 +18878,10 @@
         <v>485</v>
       </c>
       <c r="B148" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C148" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D148" s="2"/>
       <c r="E148" t="s" s="2">
@@ -18892,13 +18889,13 @@
       </c>
       <c r="F148" s="2"/>
       <c r="G148" t="s" s="2">
-        <v>77</v>
+        <v>84</v>
       </c>
       <c r="H148" t="s" s="2">
         <v>84</v>
       </c>
       <c r="I148" t="s" s="2">
-        <v>23</v>
+        <v>85</v>
       </c>
       <c r="J148" t="s" s="2">
         <v>23</v>
@@ -18910,14 +18907,14 @@
         <v>140</v>
       </c>
       <c r="M148" t="s" s="2">
+        <v>665</v>
+      </c>
+      <c r="N148" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="N148" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="O148" s="2"/>
       <c r="P148" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q148" t="s" s="2">
         <v>23</v>
@@ -18966,7 +18963,7 @@
         <v>23</v>
       </c>
       <c r="AG148" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AH148" t="s" s="2">
         <v>77</v>
@@ -18986,10 +18983,10 @@
         <v>485</v>
       </c>
       <c r="B149" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C149" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D149" s="2"/>
       <c r="E149" t="s" s="2">
@@ -19015,13 +19012,13 @@
         <v>164</v>
       </c>
       <c r="M149" t="s" s="2">
+        <v>669</v>
+      </c>
+      <c r="N149" t="s" s="2">
         <v>670</v>
       </c>
-      <c r="N149" t="s" s="2">
+      <c r="O149" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="O149" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="P149" s="2"/>
       <c r="Q149" t="s" s="2">
@@ -19050,11 +19047,11 @@
         <v>169</v>
       </c>
       <c r="Z149" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AA149" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="AA149" t="s" s="2">
-        <v>674</v>
-      </c>
       <c r="AB149" t="s" s="2">
         <v>23</v>
       </c>
@@ -19071,7 +19068,7 @@
         <v>23</v>
       </c>
       <c r="AG149" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AH149" t="s" s="2">
         <v>77</v>
@@ -19091,10 +19088,10 @@
         <v>485</v>
       </c>
       <c r="B150" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C150" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D150" s="2"/>
       <c r="E150" t="s" s="2">
@@ -19117,13 +19114,13 @@
         <v>23</v>
       </c>
       <c r="L150" t="s" s="2">
+        <v>675</v>
+      </c>
+      <c r="M150" t="s" s="2">
         <v>676</v>
       </c>
-      <c r="M150" t="s" s="2">
+      <c r="N150" t="s" s="2">
         <v>677</v>
-      </c>
-      <c r="N150" t="s" s="2">
-        <v>678</v>
       </c>
       <c r="O150" s="2"/>
       <c r="P150" s="2"/>
@@ -19174,7 +19171,7 @@
         <v>23</v>
       </c>
       <c r="AG150" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AH150" t="s" s="2">
         <v>77</v>
@@ -19194,10 +19191,10 @@
         <v>485</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D151" s="2"/>
       <c r="E151" t="s" s="2">
@@ -19223,10 +19220,10 @@
         <v>203</v>
       </c>
       <c r="M151" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N151" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="N151" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O151" s="2"/>
       <c r="P151" s="2"/>
@@ -19277,7 +19274,7 @@
         <v>23</v>
       </c>
       <c r="AG151" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AH151" t="s" s="2">
         <v>77</v>
@@ -19297,10 +19294,10 @@
         <v>485</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C152" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D152" s="2"/>
       <c r="E152" t="s" s="2">
@@ -19326,13 +19323,13 @@
         <v>447</v>
       </c>
       <c r="M152" t="s" s="2">
-        <v>683</v>
+        <v>682</v>
       </c>
       <c r="N152" t="s" s="2">
         <v>449</v>
       </c>
       <c r="O152" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P152" s="2"/>
       <c r="Q152" t="s" s="2">
@@ -19382,7 +19379,7 @@
         <v>23</v>
       </c>
       <c r="AG152" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AH152" t="s" s="2">
         <v>77</v>
@@ -19402,10 +19399,10 @@
         <v>485</v>
       </c>
       <c r="B153" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C153" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D153" s="2"/>
       <c r="E153" t="s" s="2">
@@ -19431,10 +19428,10 @@
         <v>207</v>
       </c>
       <c r="M153" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N153" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N153" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="O153" s="2"/>
       <c r="P153" s="2"/>
@@ -19485,7 +19482,7 @@
         <v>23</v>
       </c>
       <c r="AG153" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AH153" t="s" s="2">
         <v>77</v>
@@ -19505,10 +19502,10 @@
         <v>485</v>
       </c>
       <c r="B154" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C154" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D154" s="2"/>
       <c r="E154" t="s" s="2">
@@ -19608,10 +19605,10 @@
         <v>485</v>
       </c>
       <c r="B155" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C155" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D155" s="2"/>
       <c r="E155" t="s" s="2">
@@ -19713,10 +19710,10 @@
         <v>485</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C156" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D156" s="2"/>
       <c r="E156" t="s" s="2">
@@ -19820,10 +19817,10 @@
         <v>485</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C157" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D157" s="2"/>
       <c r="E157" t="s" s="2">
@@ -19849,13 +19846,13 @@
         <v>207</v>
       </c>
       <c r="M157" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N157" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N157" t="s" s="2">
+      <c r="O157" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O157" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P157" s="2"/>
       <c r="Q157" t="s" s="2">
@@ -19905,7 +19902,7 @@
         <v>23</v>
       </c>
       <c r="AG157" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AH157" t="s" s="2">
         <v>77</v>
@@ -19925,10 +19922,10 @@
         <v>485</v>
       </c>
       <c r="B158" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C158" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D158" s="2"/>
       <c r="E158" t="s" s="2">
@@ -20028,10 +20025,10 @@
         <v>485</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C159" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D159" s="2"/>
       <c r="E159" t="s" s="2">
@@ -20133,10 +20130,10 @@
         <v>485</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C160" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D160" s="2"/>
       <c r="E160" t="s" s="2">
@@ -20240,10 +20237,10 @@
         <v>485</v>
       </c>
       <c r="B161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D161" s="2"/>
       <c r="E161" t="s" s="2">
@@ -20269,10 +20266,10 @@
         <v>424</v>
       </c>
       <c r="M161" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N161" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="N161" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="O161" s="2"/>
       <c r="P161" s="2"/>
@@ -20323,7 +20320,7 @@
         <v>23</v>
       </c>
       <c r="AG161" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AH161" t="s" s="2">
         <v>77</v>
@@ -20343,10 +20340,10 @@
         <v>485</v>
       </c>
       <c r="B162" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C162" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D162" s="2"/>
       <c r="E162" t="s" s="2">
@@ -20369,13 +20366,13 @@
         <v>23</v>
       </c>
       <c r="L162" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M162" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M162" t="s" s="2">
+      <c r="N162" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="N162" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="O162" s="2"/>
       <c r="P162" s="2"/>
@@ -20426,7 +20423,7 @@
         <v>23</v>
       </c>
       <c r="AG162" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AH162" t="s" s="2">
         <v>77</v>
@@ -20446,10 +20443,10 @@
         <v>485</v>
       </c>
       <c r="B163" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C163" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D163" s="2"/>
       <c r="E163" t="s" s="2">
@@ -20472,13 +20469,13 @@
         <v>23</v>
       </c>
       <c r="L163" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M163" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N163" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="N163" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="O163" s="2"/>
       <c r="P163" s="2"/>
@@ -20529,7 +20526,7 @@
         <v>23</v>
       </c>
       <c r="AG163" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AH163" t="s" s="2">
         <v>77</v>
@@ -20549,10 +20546,10 @@
         <v>485</v>
       </c>
       <c r="B164" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C164" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D164" s="2"/>
       <c r="E164" t="s" s="2">
@@ -20575,19 +20572,19 @@
         <v>23</v>
       </c>
       <c r="L164" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M164" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M164" t="s" s="2">
+      <c r="N164" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="N164" t="s" s="2">
+      <c r="O164" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="O164" t="s" s="2">
+      <c r="P164" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="P164" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="Q164" t="s" s="2">
         <v>23</v>
@@ -20636,7 +20633,7 @@
         <v>23</v>
       </c>
       <c r="AG164" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AH164" t="s" s="2">
         <v>77</v>
@@ -20656,10 +20653,10 @@
         <v>485</v>
       </c>
       <c r="B165" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C165" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D165" s="2"/>
       <c r="E165" t="s" s="2">
@@ -20682,16 +20679,16 @@
         <v>23</v>
       </c>
       <c r="L165" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M165" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M165" t="s" s="2">
+      <c r="N165" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="N165" t="s" s="2">
+      <c r="O165" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="O165" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="P165" s="2"/>
       <c r="Q165" t="s" s="2">
@@ -20741,7 +20738,7 @@
         <v>23</v>
       </c>
       <c r="AG165" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AH165" t="s" s="2">
         <v>77</v>
@@ -20761,10 +20758,10 @@
         <v>485</v>
       </c>
       <c r="B166" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C166" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D166" s="2"/>
       <c r="E166" t="s" s="2">
@@ -20790,10 +20787,10 @@
         <v>424</v>
       </c>
       <c r="M166" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N166" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="N166" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="O166" s="2"/>
       <c r="P166" s="2"/>
@@ -20844,7 +20841,7 @@
         <v>23</v>
       </c>
       <c r="AG166" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AH166" t="s" s="2">
         <v>77</v>
@@ -20864,10 +20861,10 @@
         <v>485</v>
       </c>
       <c r="B167" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C167" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D167" s="2"/>
       <c r="E167" t="s" s="2">
@@ -20890,16 +20887,16 @@
         <v>23</v>
       </c>
       <c r="L167" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M167" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N167" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="N167" t="s" s="2">
+      <c r="O167" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="O167" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="P167" s="2"/>
       <c r="Q167" t="s" s="2">
@@ -20949,7 +20946,7 @@
         <v>23</v>
       </c>
       <c r="AG167" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AH167" t="s" s="2">
         <v>77</v>
@@ -20969,10 +20966,10 @@
         <v>485</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C168" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D168" s="2"/>
       <c r="E168" t="s" s="2">
@@ -20998,10 +20995,10 @@
         <v>289</v>
       </c>
       <c r="M168" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N168" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="N168" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="O168" s="2"/>
       <c r="P168" s="2"/>
@@ -21052,7 +21049,7 @@
         <v>23</v>
       </c>
       <c r="AG168" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AH168" t="s" s="2">
         <v>77</v>
@@ -21072,10 +21069,10 @@
         <v>485</v>
       </c>
       <c r="B169" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C169" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D169" s="2"/>
       <c r="E169" t="s" s="2">
@@ -21101,10 +21098,10 @@
         <v>207</v>
       </c>
       <c r="M169" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="N169" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="N169" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="O169" s="2"/>
       <c r="P169" s="2"/>
@@ -21155,7 +21152,7 @@
         <v>23</v>
       </c>
       <c r="AG169" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AH169" t="s" s="2">
         <v>77</v>
@@ -21175,10 +21172,10 @@
         <v>485</v>
       </c>
       <c r="B170" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C170" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D170" s="2"/>
       <c r="E170" t="s" s="2">
@@ -21278,10 +21275,10 @@
         <v>485</v>
       </c>
       <c r="B171" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C171" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D171" s="2"/>
       <c r="E171" t="s" s="2">
@@ -21383,10 +21380,10 @@
         <v>485</v>
       </c>
       <c r="B172" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C172" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D172" s="2"/>
       <c r="E172" t="s" s="2">
@@ -21490,10 +21487,10 @@
         <v>485</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C173" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D173" s="2"/>
       <c r="E173" t="s" s="2">
@@ -21516,16 +21513,16 @@
         <v>23</v>
       </c>
       <c r="L173" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M173" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="M173" t="s" s="2">
+      <c r="N173" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="N173" t="s" s="2">
+      <c r="O173" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="O173" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="P173" s="2"/>
       <c r="Q173" t="s" s="2">
@@ -21554,7 +21551,7 @@
         <v>169</v>
       </c>
       <c r="Z173" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AA173" t="s" s="2">
         <v>464</v>
@@ -21575,7 +21572,7 @@
         <v>23</v>
       </c>
       <c r="AG173" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AH173" t="s" s="2">
         <v>84</v>
@@ -21595,10 +21592,10 @@
         <v>485</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C174" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D174" s="2"/>
       <c r="E174" t="s" s="2">
@@ -21624,10 +21621,10 @@
         <v>164</v>
       </c>
       <c r="M174" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="N174" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="N174" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="O174" s="2"/>
       <c r="P174" s="2"/>
@@ -21678,7 +21675,7 @@
         <v>23</v>
       </c>
       <c r="AG174" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AH174" t="s" s="2">
         <v>77</v>
@@ -21698,10 +21695,10 @@
         <v>485</v>
       </c>
       <c r="B175" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C175" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D175" s="2"/>
       <c r="E175" t="s" s="2">
@@ -21727,10 +21724,10 @@
         <v>415</v>
       </c>
       <c r="M175" t="s" s="2">
+        <v>744</v>
+      </c>
+      <c r="N175" t="s" s="2">
         <v>745</v>
-      </c>
-      <c r="N175" t="s" s="2">
-        <v>746</v>
       </c>
       <c r="O175" s="2"/>
       <c r="P175" s="2"/>
@@ -21781,7 +21778,7 @@
         <v>23</v>
       </c>
       <c r="AG175" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AH175" t="s" s="2">
         <v>77</v>
@@ -21801,10 +21798,10 @@
         <v>485</v>
       </c>
       <c r="B176" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C176" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D176" s="2"/>
       <c r="E176" t="s" s="2">
@@ -21830,10 +21827,10 @@
         <v>476</v>
       </c>
       <c r="M176" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="N176" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="N176" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="O176" t="s" s="2">
         <v>479</v>
@@ -21886,7 +21883,7 @@
         <v>23</v>
       </c>
       <c r="AG176" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AH176" t="s" s="2">
         <v>77</v>
@@ -21906,10 +21903,10 @@
         <v>485</v>
       </c>
       <c r="B177" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C177" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D177" s="2"/>
       <c r="E177" t="s" s="2">
@@ -21935,13 +21932,13 @@
         <v>481</v>
       </c>
       <c r="M177" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="N177" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="N177" t="s" s="2">
+      <c r="O177" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="O177" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="P177" s="2"/>
       <c r="Q177" t="s" s="2">
@@ -21991,7 +21988,7 @@
         <v>23</v>
       </c>
       <c r="AG177" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AH177" t="s" s="2">
         <v>77</v>
@@ -22008,7 +22005,7 @@
     </row>
     <row r="178">
       <c r="A178" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B178" t="s" s="2">
         <v>490</v>
@@ -22040,7 +22037,7 @@
         <v>79</v>
       </c>
       <c r="M178" t="s" s="2">
-        <v>759</v>
+        <v>758</v>
       </c>
       <c r="N178" t="s" s="2">
         <v>494</v>
@@ -22111,7 +22108,7 @@
     </row>
     <row r="179">
       <c r="A179" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B179" t="s" s="2">
         <v>496</v>
@@ -22216,7 +22213,7 @@
     </row>
     <row r="180">
       <c r="A180" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B180" t="s" s="2">
         <v>497</v>
@@ -22319,7 +22316,7 @@
     </row>
     <row r="181">
       <c r="A181" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B181" t="s" s="2">
         <v>498</v>
@@ -22424,7 +22421,7 @@
     </row>
     <row r="182">
       <c r="A182" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B182" t="s" s="2">
         <v>499</v>
@@ -22529,7 +22526,7 @@
     </row>
     <row r="183">
       <c r="A183" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B183" t="s" s="2">
         <v>500</v>
@@ -22634,7 +22631,7 @@
     </row>
     <row r="184">
       <c r="A184" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B184" t="s" s="2">
         <v>501</v>
@@ -22739,7 +22736,7 @@
     </row>
     <row r="185">
       <c r="A185" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B185" t="s" s="2">
         <v>502</v>
@@ -22844,7 +22841,7 @@
     </row>
     <row r="186">
       <c r="A186" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B186" t="s" s="2">
         <v>503</v>
@@ -22951,7 +22948,7 @@
     </row>
     <row r="187">
       <c r="A187" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B187" t="s" s="2">
         <v>504</v>
@@ -22983,7 +22980,7 @@
         <v>140</v>
       </c>
       <c r="M187" t="s" s="2">
-        <v>760</v>
+        <v>759</v>
       </c>
       <c r="N187" t="s" s="2">
         <v>506</v>
@@ -23056,7 +23053,7 @@
     </row>
     <row r="188">
       <c r="A188" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B188" t="s" s="2">
         <v>507</v>
@@ -23088,7 +23085,7 @@
         <v>104</v>
       </c>
       <c r="M188" t="s" s="2">
-        <v>761</v>
+        <v>760</v>
       </c>
       <c r="N188" t="s" s="2">
         <v>509</v>
@@ -23161,7 +23158,7 @@
     </row>
     <row r="189">
       <c r="A189" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B189" t="s" s="2">
         <v>512</v>
@@ -23193,7 +23190,7 @@
         <v>164</v>
       </c>
       <c r="M189" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="N189" t="s" s="2">
         <v>514</v>
@@ -23266,7 +23263,7 @@
     </row>
     <row r="190">
       <c r="A190" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B190" t="s" s="2">
         <v>518</v>
@@ -23298,7 +23295,7 @@
         <v>104</v>
       </c>
       <c r="M190" t="s" s="2">
-        <v>763</v>
+        <v>762</v>
       </c>
       <c r="N190" t="s" s="2">
         <v>520</v>
@@ -23371,7 +23368,7 @@
     </row>
     <row r="191">
       <c r="A191" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B191" t="s" s="2">
         <v>525</v>
@@ -23403,7 +23400,7 @@
         <v>164</v>
       </c>
       <c r="M191" t="s" s="2">
-        <v>764</v>
+        <v>763</v>
       </c>
       <c r="N191" t="s" s="2">
         <v>527</v>
@@ -23476,7 +23473,7 @@
     </row>
     <row r="192">
       <c r="A192" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B192" t="s" s="2">
         <v>531</v>
@@ -23508,7 +23505,7 @@
         <v>104</v>
       </c>
       <c r="M192" t="s" s="2">
-        <v>765</v>
+        <v>764</v>
       </c>
       <c r="N192" t="s" s="2">
         <v>533</v>
@@ -23579,7 +23576,7 @@
     </row>
     <row r="193">
       <c r="A193" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B193" t="s" s="2">
         <v>536</v>
@@ -23611,7 +23608,7 @@
         <v>232</v>
       </c>
       <c r="M193" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="N193" t="s" s="2">
         <v>538</v>
@@ -23684,7 +23681,7 @@
     </row>
     <row r="194">
       <c r="A194" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B194" t="s" s="2">
         <v>540</v>
@@ -23716,7 +23713,7 @@
         <v>541</v>
       </c>
       <c r="M194" t="s" s="2">
-        <v>767</v>
+        <v>766</v>
       </c>
       <c r="N194" t="s" s="2">
         <v>543</v>
@@ -23787,7 +23784,7 @@
     </row>
     <row r="195">
       <c r="A195" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B195" t="s" s="2">
         <v>544</v>
@@ -23892,7 +23889,7 @@
     </row>
     <row r="196">
       <c r="A196" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B196" t="s" s="2">
         <v>618</v>
@@ -23924,7 +23921,7 @@
         <v>383</v>
       </c>
       <c r="M196" t="s" s="2">
-        <v>768</v>
+        <v>767</v>
       </c>
       <c r="N196" t="s" s="2">
         <v>621</v>
@@ -23997,7 +23994,7 @@
     </row>
     <row r="197">
       <c r="A197" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B197" t="s" s="2">
         <v>623</v>
@@ -24029,7 +24026,7 @@
         <v>179</v>
       </c>
       <c r="M197" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="N197" t="s" s="2">
         <v>624</v>
@@ -24102,7 +24099,7 @@
     </row>
     <row r="198">
       <c r="A198" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B198" t="s" s="2">
         <v>626</v>
@@ -24134,7 +24131,7 @@
         <v>244</v>
       </c>
       <c r="M198" t="s" s="2">
-        <v>770</v>
+        <v>769</v>
       </c>
       <c r="N198" t="s" s="2">
         <v>627</v>
@@ -24205,7 +24202,7 @@
     </row>
     <row r="199">
       <c r="A199" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B199" t="s" s="2">
         <v>628</v>
@@ -24237,7 +24234,7 @@
         <v>183</v>
       </c>
       <c r="M199" t="s" s="2">
-        <v>771</v>
+        <v>770</v>
       </c>
       <c r="N199" t="s" s="2">
         <v>630</v>
@@ -24308,7 +24305,7 @@
     </row>
     <row r="200">
       <c r="A200" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B200" t="s" s="2">
         <v>631</v>
@@ -24337,10 +24334,10 @@
         <v>85</v>
       </c>
       <c r="L200" t="s" s="2">
+        <v>771</v>
+      </c>
+      <c r="M200" t="s" s="2">
         <v>772</v>
-      </c>
-      <c r="M200" t="s" s="2">
-        <v>773</v>
       </c>
       <c r="N200" t="s" s="2">
         <v>634</v>
@@ -24411,7 +24408,7 @@
     </row>
     <row r="201">
       <c r="A201" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B201" t="s" s="2">
         <v>635</v>
@@ -24443,7 +24440,7 @@
         <v>636</v>
       </c>
       <c r="M201" t="s" s="2">
-        <v>774</v>
+        <v>773</v>
       </c>
       <c r="N201" t="s" s="2">
         <v>637</v>
@@ -24514,7 +24511,7 @@
     </row>
     <row r="202">
       <c r="A202" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B202" t="s" s="2">
         <v>638</v>
@@ -24546,7 +24543,7 @@
         <v>164</v>
       </c>
       <c r="M202" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="N202" t="s" s="2">
         <v>639</v>
@@ -24619,7 +24616,7 @@
     </row>
     <row r="203">
       <c r="A203" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B203" t="s" s="2">
         <v>643</v>
@@ -24651,7 +24648,7 @@
         <v>471</v>
       </c>
       <c r="M203" t="s" s="2">
-        <v>776</v>
+        <v>775</v>
       </c>
       <c r="N203" t="s" s="2">
         <v>644</v>
@@ -24722,7 +24719,7 @@
     </row>
     <row r="204">
       <c r="A204" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B204" t="s" s="2">
         <v>645</v>
@@ -24754,7 +24751,7 @@
         <v>164</v>
       </c>
       <c r="M204" t="s" s="2">
-        <v>777</v>
+        <v>776</v>
       </c>
       <c r="N204" t="s" s="2">
         <v>647</v>
@@ -24827,7 +24824,7 @@
     </row>
     <row r="205">
       <c r="A205" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B205" t="s" s="2">
         <v>651</v>
@@ -24859,13 +24856,13 @@
         <v>652</v>
       </c>
       <c r="M205" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="N205" t="s" s="2">
+        <v>653</v>
+      </c>
+      <c r="O205" t="s" s="2">
         <v>654</v>
-      </c>
-      <c r="O205" t="s" s="2">
-        <v>655</v>
       </c>
       <c r="P205" s="2"/>
       <c r="Q205" t="s" s="2">
@@ -24932,13 +24929,13 @@
     </row>
     <row r="206">
       <c r="A206" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B206" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C206" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D206" s="2"/>
       <c r="E206" t="s" s="2">
@@ -24961,13 +24958,13 @@
         <v>85</v>
       </c>
       <c r="L206" t="s" s="2">
+        <v>656</v>
+      </c>
+      <c r="M206" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="N206" t="s" s="2">
         <v>657</v>
-      </c>
-      <c r="M206" t="s" s="2">
-        <v>779</v>
-      </c>
-      <c r="N206" t="s" s="2">
-        <v>658</v>
       </c>
       <c r="O206" s="2"/>
       <c r="P206" s="2"/>
@@ -25018,7 +25015,7 @@
         <v>23</v>
       </c>
       <c r="AG206" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="AH206" t="s" s="2">
         <v>77</v>
@@ -25035,13 +25032,13 @@
     </row>
     <row r="207">
       <c r="A207" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B207" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C207" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D207" s="2"/>
       <c r="E207" t="s" s="2">
@@ -25067,10 +25064,10 @@
         <v>98</v>
       </c>
       <c r="M207" t="s" s="2">
-        <v>780</v>
+        <v>779</v>
       </c>
       <c r="N207" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="O207" s="2"/>
       <c r="P207" s="2"/>
@@ -25121,7 +25118,7 @@
         <v>23</v>
       </c>
       <c r="AG207" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="AH207" t="s" s="2">
         <v>77</v>
@@ -25138,13 +25135,13 @@
     </row>
     <row r="208">
       <c r="A208" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B208" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C208" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D208" s="2"/>
       <c r="E208" t="s" s="2">
@@ -25167,13 +25164,13 @@
         <v>85</v>
       </c>
       <c r="L208" t="s" s="2">
+        <v>780</v>
+      </c>
+      <c r="M208" t="s" s="2">
         <v>781</v>
       </c>
-      <c r="M208" t="s" s="2">
-        <v>782</v>
-      </c>
       <c r="N208" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="O208" s="2"/>
       <c r="P208" s="2"/>
@@ -25224,7 +25221,7 @@
         <v>23</v>
       </c>
       <c r="AG208" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="AH208" t="s" s="2">
         <v>77</v>
@@ -25241,13 +25238,13 @@
     </row>
     <row r="209">
       <c r="A209" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B209" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="C209" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="D209" s="2"/>
       <c r="E209" t="s" s="2">
@@ -25273,14 +25270,14 @@
         <v>140</v>
       </c>
       <c r="M209" t="s" s="2">
-        <v>783</v>
+        <v>782</v>
       </c>
       <c r="N209" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="O209" s="2"/>
       <c r="P209" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="Q209" t="s" s="2">
         <v>23</v>
@@ -25329,7 +25326,7 @@
         <v>23</v>
       </c>
       <c r="AG209" t="s" s="2">
-        <v>665</v>
+        <v>664</v>
       </c>
       <c r="AH209" t="s" s="2">
         <v>77</v>
@@ -25346,13 +25343,13 @@
     </row>
     <row r="210">
       <c r="A210" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B210" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="C210" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="D210" s="2"/>
       <c r="E210" t="s" s="2">
@@ -25378,13 +25375,13 @@
         <v>164</v>
       </c>
       <c r="M210" t="s" s="2">
-        <v>784</v>
+        <v>783</v>
       </c>
       <c r="N210" t="s" s="2">
+        <v>670</v>
+      </c>
+      <c r="O210" t="s" s="2">
         <v>671</v>
-      </c>
-      <c r="O210" t="s" s="2">
-        <v>672</v>
       </c>
       <c r="P210" s="2"/>
       <c r="Q210" t="s" s="2">
@@ -25413,11 +25410,11 @@
         <v>169</v>
       </c>
       <c r="Z210" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="AA210" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="AA210" t="s" s="2">
-        <v>674</v>
-      </c>
       <c r="AB210" t="s" s="2">
         <v>23</v>
       </c>
@@ -25434,7 +25431,7 @@
         <v>23</v>
       </c>
       <c r="AG210" t="s" s="2">
-        <v>669</v>
+        <v>668</v>
       </c>
       <c r="AH210" t="s" s="2">
         <v>77</v>
@@ -25451,13 +25448,13 @@
     </row>
     <row r="211">
       <c r="A211" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B211" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="C211" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="D211" s="2"/>
       <c r="E211" t="s" s="2">
@@ -25480,13 +25477,13 @@
         <v>23</v>
       </c>
       <c r="L211" t="s" s="2">
-        <v>676</v>
+        <v>675</v>
       </c>
       <c r="M211" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="N211" t="s" s="2">
-        <v>678</v>
+        <v>677</v>
       </c>
       <c r="O211" s="2"/>
       <c r="P211" s="2"/>
@@ -25537,7 +25534,7 @@
         <v>23</v>
       </c>
       <c r="AG211" t="s" s="2">
-        <v>675</v>
+        <v>674</v>
       </c>
       <c r="AH211" t="s" s="2">
         <v>77</v>
@@ -25554,13 +25551,13 @@
     </row>
     <row r="212">
       <c r="A212" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="C212" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="D212" s="2"/>
       <c r="E212" t="s" s="2">
@@ -25586,10 +25583,10 @@
         <v>203</v>
       </c>
       <c r="M212" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="N212" t="s" s="2">
         <v>680</v>
-      </c>
-      <c r="N212" t="s" s="2">
-        <v>681</v>
       </c>
       <c r="O212" s="2"/>
       <c r="P212" s="2"/>
@@ -25640,7 +25637,7 @@
         <v>23</v>
       </c>
       <c r="AG212" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="AH212" t="s" s="2">
         <v>77</v>
@@ -25657,13 +25654,13 @@
     </row>
     <row r="213">
       <c r="A213" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B213" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="C213" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="D213" s="2"/>
       <c r="E213" t="s" s="2">
@@ -25689,13 +25686,13 @@
         <v>447</v>
       </c>
       <c r="M213" t="s" s="2">
-        <v>786</v>
+        <v>785</v>
       </c>
       <c r="N213" t="s" s="2">
         <v>449</v>
       </c>
       <c r="O213" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="P213" s="2"/>
       <c r="Q213" t="s" s="2">
@@ -25745,7 +25742,7 @@
         <v>23</v>
       </c>
       <c r="AG213" t="s" s="2">
-        <v>682</v>
+        <v>681</v>
       </c>
       <c r="AH213" t="s" s="2">
         <v>77</v>
@@ -25762,13 +25759,13 @@
     </row>
     <row r="214">
       <c r="A214" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B214" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="C214" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="D214" s="2"/>
       <c r="E214" t="s" s="2">
@@ -25794,10 +25791,10 @@
         <v>207</v>
       </c>
       <c r="M214" t="s" s="2">
+        <v>685</v>
+      </c>
+      <c r="N214" t="s" s="2">
         <v>686</v>
-      </c>
-      <c r="N214" t="s" s="2">
-        <v>687</v>
       </c>
       <c r="O214" s="2"/>
       <c r="P214" s="2"/>
@@ -25848,7 +25845,7 @@
         <v>23</v>
       </c>
       <c r="AG214" t="s" s="2">
-        <v>685</v>
+        <v>684</v>
       </c>
       <c r="AH214" t="s" s="2">
         <v>77</v>
@@ -25865,13 +25862,13 @@
     </row>
     <row r="215">
       <c r="A215" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B215" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="C215" t="s" s="2">
-        <v>688</v>
+        <v>687</v>
       </c>
       <c r="D215" s="2"/>
       <c r="E215" t="s" s="2">
@@ -25968,13 +25965,13 @@
     </row>
     <row r="216">
       <c r="A216" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B216" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C216" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D216" s="2"/>
       <c r="E216" t="s" s="2">
@@ -26073,13 +26070,13 @@
     </row>
     <row r="217">
       <c r="A217" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="C217" t="s" s="2">
-        <v>690</v>
+        <v>689</v>
       </c>
       <c r="D217" s="2"/>
       <c r="E217" t="s" s="2">
@@ -26180,13 +26177,13 @@
     </row>
     <row r="218">
       <c r="A218" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="C218" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="D218" s="2"/>
       <c r="E218" t="s" s="2">
@@ -26212,13 +26209,13 @@
         <v>207</v>
       </c>
       <c r="M218" t="s" s="2">
+        <v>691</v>
+      </c>
+      <c r="N218" t="s" s="2">
         <v>692</v>
       </c>
-      <c r="N218" t="s" s="2">
+      <c r="O218" t="s" s="2">
         <v>693</v>
-      </c>
-      <c r="O218" t="s" s="2">
-        <v>694</v>
       </c>
       <c r="P218" s="2"/>
       <c r="Q218" t="s" s="2">
@@ -26268,7 +26265,7 @@
         <v>23</v>
       </c>
       <c r="AG218" t="s" s="2">
-        <v>691</v>
+        <v>690</v>
       </c>
       <c r="AH218" t="s" s="2">
         <v>77</v>
@@ -26285,13 +26282,13 @@
     </row>
     <row r="219">
       <c r="A219" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B219" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C219" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D219" s="2"/>
       <c r="E219" t="s" s="2">
@@ -26388,13 +26385,13 @@
     </row>
     <row r="220">
       <c r="A220" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B220" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="C220" t="s" s="2">
-        <v>696</v>
+        <v>695</v>
       </c>
       <c r="D220" s="2"/>
       <c r="E220" t="s" s="2">
@@ -26493,13 +26490,13 @@
     </row>
     <row r="221">
       <c r="A221" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B221" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="C221" t="s" s="2">
-        <v>697</v>
+        <v>696</v>
       </c>
       <c r="D221" s="2"/>
       <c r="E221" t="s" s="2">
@@ -26600,13 +26597,13 @@
     </row>
     <row r="222">
       <c r="A222" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B222" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="C222" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="D222" s="2"/>
       <c r="E222" t="s" s="2">
@@ -26632,10 +26629,10 @@
         <v>424</v>
       </c>
       <c r="M222" t="s" s="2">
+        <v>698</v>
+      </c>
+      <c r="N222" t="s" s="2">
         <v>699</v>
-      </c>
-      <c r="N222" t="s" s="2">
-        <v>700</v>
       </c>
       <c r="O222" s="2"/>
       <c r="P222" s="2"/>
@@ -26686,7 +26683,7 @@
         <v>23</v>
       </c>
       <c r="AG222" t="s" s="2">
-        <v>698</v>
+        <v>697</v>
       </c>
       <c r="AH222" t="s" s="2">
         <v>77</v>
@@ -26703,13 +26700,13 @@
     </row>
     <row r="223">
       <c r="A223" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B223" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="C223" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="D223" s="2"/>
       <c r="E223" t="s" s="2">
@@ -26732,13 +26729,13 @@
         <v>23</v>
       </c>
       <c r="L223" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="M223" t="s" s="2">
         <v>702</v>
       </c>
-      <c r="M223" t="s" s="2">
+      <c r="N223" t="s" s="2">
         <v>703</v>
-      </c>
-      <c r="N223" t="s" s="2">
-        <v>704</v>
       </c>
       <c r="O223" s="2"/>
       <c r="P223" s="2"/>
@@ -26789,7 +26786,7 @@
         <v>23</v>
       </c>
       <c r="AG223" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AH223" t="s" s="2">
         <v>77</v>
@@ -26806,13 +26803,13 @@
     </row>
     <row r="224">
       <c r="A224" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B224" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="C224" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="D224" s="2"/>
       <c r="E224" t="s" s="2">
@@ -26835,13 +26832,13 @@
         <v>23</v>
       </c>
       <c r="L224" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M224" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="N224" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="N224" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="O224" s="2"/>
       <c r="P224" s="2"/>
@@ -26892,7 +26889,7 @@
         <v>23</v>
       </c>
       <c r="AG224" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AH224" t="s" s="2">
         <v>77</v>
@@ -26909,13 +26906,13 @@
     </row>
     <row r="225">
       <c r="A225" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B225" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="C225" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="D225" s="2"/>
       <c r="E225" t="s" s="2">
@@ -26938,19 +26935,19 @@
         <v>23</v>
       </c>
       <c r="L225" t="s" s="2">
+        <v>708</v>
+      </c>
+      <c r="M225" t="s" s="2">
         <v>709</v>
       </c>
-      <c r="M225" t="s" s="2">
+      <c r="N225" t="s" s="2">
         <v>710</v>
       </c>
-      <c r="N225" t="s" s="2">
+      <c r="O225" t="s" s="2">
         <v>711</v>
       </c>
-      <c r="O225" t="s" s="2">
+      <c r="P225" t="s" s="2">
         <v>712</v>
-      </c>
-      <c r="P225" t="s" s="2">
-        <v>713</v>
       </c>
       <c r="Q225" t="s" s="2">
         <v>23</v>
@@ -26999,7 +26996,7 @@
         <v>23</v>
       </c>
       <c r="AG225" t="s" s="2">
-        <v>708</v>
+        <v>707</v>
       </c>
       <c r="AH225" t="s" s="2">
         <v>77</v>
@@ -27016,13 +27013,13 @@
     </row>
     <row r="226">
       <c r="A226" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -27045,16 +27042,16 @@
         <v>23</v>
       </c>
       <c r="L226" t="s" s="2">
+        <v>714</v>
+      </c>
+      <c r="M226" t="s" s="2">
         <v>715</v>
       </c>
-      <c r="M226" t="s" s="2">
+      <c r="N226" t="s" s="2">
         <v>716</v>
       </c>
-      <c r="N226" t="s" s="2">
+      <c r="O226" t="s" s="2">
         <v>717</v>
-      </c>
-      <c r="O226" t="s" s="2">
-        <v>718</v>
       </c>
       <c r="P226" s="2"/>
       <c r="Q226" t="s" s="2">
@@ -27104,7 +27101,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>714</v>
+        <v>713</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>77</v>
@@ -27121,13 +27118,13 @@
     </row>
     <row r="227">
       <c r="A227" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -27153,10 +27150,10 @@
         <v>424</v>
       </c>
       <c r="M227" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N227" t="s" s="2">
         <v>720</v>
-      </c>
-      <c r="N227" t="s" s="2">
-        <v>721</v>
       </c>
       <c r="O227" s="2"/>
       <c r="P227" s="2"/>
@@ -27207,7 +27204,7 @@
         <v>23</v>
       </c>
       <c r="AG227" t="s" s="2">
-        <v>719</v>
+        <v>718</v>
       </c>
       <c r="AH227" t="s" s="2">
         <v>77</v>
@@ -27224,13 +27221,13 @@
     </row>
     <row r="228">
       <c r="A228" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -27253,16 +27250,16 @@
         <v>23</v>
       </c>
       <c r="L228" t="s" s="2">
-        <v>702</v>
+        <v>701</v>
       </c>
       <c r="M228" t="s" s="2">
+        <v>722</v>
+      </c>
+      <c r="N228" t="s" s="2">
         <v>723</v>
       </c>
-      <c r="N228" t="s" s="2">
+      <c r="O228" t="s" s="2">
         <v>724</v>
-      </c>
-      <c r="O228" t="s" s="2">
-        <v>725</v>
       </c>
       <c r="P228" s="2"/>
       <c r="Q228" t="s" s="2">
@@ -27312,7 +27309,7 @@
         <v>23</v>
       </c>
       <c r="AG228" t="s" s="2">
-        <v>722</v>
+        <v>721</v>
       </c>
       <c r="AH228" t="s" s="2">
         <v>77</v>
@@ -27329,13 +27326,13 @@
     </row>
     <row r="229">
       <c r="A229" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -27361,10 +27358,10 @@
         <v>289</v>
       </c>
       <c r="M229" t="s" s="2">
+        <v>726</v>
+      </c>
+      <c r="N229" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="N229" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="O229" s="2"/>
       <c r="P229" s="2"/>
@@ -27415,7 +27412,7 @@
         <v>23</v>
       </c>
       <c r="AG229" t="s" s="2">
-        <v>726</v>
+        <v>725</v>
       </c>
       <c r="AH229" t="s" s="2">
         <v>77</v>
@@ -27432,13 +27429,13 @@
     </row>
     <row r="230">
       <c r="A230" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -27464,10 +27461,10 @@
         <v>207</v>
       </c>
       <c r="M230" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="N230" t="s" s="2">
         <v>730</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>731</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" s="2"/>
@@ -27518,7 +27515,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>77</v>
@@ -27535,13 +27532,13 @@
     </row>
     <row r="231">
       <c r="A231" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>732</v>
+        <v>731</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -27638,13 +27635,13 @@
     </row>
     <row r="232">
       <c r="A232" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -27743,13 +27740,13 @@
     </row>
     <row r="233">
       <c r="A233" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -27850,13 +27847,13 @@
     </row>
     <row r="234">
       <c r="A234" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -27879,16 +27876,16 @@
         <v>23</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>735</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>736</v>
       </c>
-      <c r="M234" t="s" s="2">
+      <c r="N234" t="s" s="2">
         <v>737</v>
       </c>
-      <c r="N234" t="s" s="2">
+      <c r="O234" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="O234" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="P234" s="2"/>
       <c r="Q234" t="s" s="2">
@@ -27917,7 +27914,7 @@
         <v>169</v>
       </c>
       <c r="Z234" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="AA234" t="s" s="2">
         <v>464</v>
@@ -27938,7 +27935,7 @@
         <v>23</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>735</v>
+        <v>734</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>84</v>
@@ -27955,13 +27952,13 @@
     </row>
     <row r="235">
       <c r="A235" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -27987,10 +27984,10 @@
         <v>164</v>
       </c>
       <c r="M235" t="s" s="2">
+        <v>741</v>
+      </c>
+      <c r="N235" t="s" s="2">
         <v>742</v>
-      </c>
-      <c r="N235" t="s" s="2">
-        <v>743</v>
       </c>
       <c r="O235" s="2"/>
       <c r="P235" s="2"/>
@@ -28041,7 +28038,7 @@
         <v>23</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>77</v>
@@ -28058,13 +28055,13 @@
     </row>
     <row r="236">
       <c r="A236" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B236" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="C236" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="D236" s="2"/>
       <c r="E236" t="s" s="2">
@@ -28090,10 +28087,10 @@
         <v>415</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>787</v>
+        <v>786</v>
       </c>
       <c r="N236" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="O236" s="2"/>
       <c r="P236" s="2"/>
@@ -28144,7 +28141,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>744</v>
+        <v>743</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>77</v>
@@ -28161,13 +28158,13 @@
     </row>
     <row r="237">
       <c r="A237" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B237" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="C237" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="D237" s="2"/>
       <c r="E237" t="s" s="2">
@@ -28193,10 +28190,10 @@
         <v>476</v>
       </c>
       <c r="M237" t="s" s="2">
+        <v>747</v>
+      </c>
+      <c r="N237" t="s" s="2">
         <v>748</v>
-      </c>
-      <c r="N237" t="s" s="2">
-        <v>749</v>
       </c>
       <c r="O237" t="s" s="2">
         <v>479</v>
@@ -28249,7 +28246,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>747</v>
+        <v>746</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>77</v>
@@ -28266,13 +28263,13 @@
     </row>
     <row r="238">
       <c r="A238" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -28298,13 +28295,13 @@
         <v>481</v>
       </c>
       <c r="M238" t="s" s="2">
+        <v>750</v>
+      </c>
+      <c r="N238" t="s" s="2">
         <v>751</v>
       </c>
-      <c r="N238" t="s" s="2">
+      <c r="O238" t="s" s="2">
         <v>752</v>
-      </c>
-      <c r="O238" t="s" s="2">
-        <v>753</v>
       </c>
       <c r="P238" s="2"/>
       <c r="Q238" t="s" s="2">
@@ -28354,7 +28351,7 @@
         <v>23</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>77</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-21T17:03:29+00:00</t>
+    <t>2026-01-22T09:24:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T09:24:15+00:00</t>
+    <t>2026-01-22T12:59:21+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-22T12:59:21+00:00</t>
+    <t>2026-01-22T14:02:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-01-28T19:29:09+00:00</t>
+    <t>2026-01-29T08:16:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-12T16:23:56+00:00</t>
+    <t>2026-02-16T10:10:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17629" uniqueCount="1172">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="17627" uniqueCount="1173">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-16T10:10:16+00:00</t>
+    <t>2026-02-16T15:59:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2167,6 +2167,9 @@
     <t>Medication.text</t>
   </si>
   <si>
+    <t>TODO: Freitext für magistrale Anwendungen oder Abbildung in Substance.description?</t>
+  </si>
+  <si>
     <t>Medication.contained</t>
   </si>
   <si>
@@ -2331,7 +2334,8 @@
 </t>
   </si>
   <si>
-    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; prüfen ob Einschränkung auf österr. Organisation</t>
+    <t>Der Hersteller des Arzneimittels. Keine Verwendung im Kontext Planeintrag. 
+TODO: Prüfen, ob im Kontext durchgeführte Abgabe und magistraler Zubereitung erforderlich; HL7ATCoreOrganization schränkt auf Organisationen gemäß GDA-Index ein.</t>
   </si>
   <si>
     <t>Describes the details of the manufacturer of the medication product.  This is not intended to represent the distributor of a medication product.</t>
@@ -2374,7 +2378,7 @@
   <si>
     <t>Wirkstoffe. Wenn PZN vorhanden 0..0, da Anreicherung aus ASP-Liste durch Fachanwendung.
 Gemäß AG: Einschränkung auf CodeableConcept, TODO: prüfen, wie Freitext bei magistraler Zubereitung abgebildet wird:
-In diesem Fall müsste in einer Substance-Ressource die description (string) befüllt werden.</t>
+Evtl. in einer Substance-Ressource in der description (string).</t>
   </si>
   <si>
     <t>Identifies a particular constituent of interest in the product.</t>
@@ -2719,16 +2723,14 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe (im Standardfall active oder complete): active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown -&gt; entfernen: draft, unknown</t>
+    <t>Status der geplanten Abgabe (im Standardfall active oder complete): 
+ (req) active | on-hold | cancelled | completed | entered-in-error | stopped  (entfernt: draft | unknown); TODO: Fachlich zu prüfen.</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
-    <t>A coded concept specifying the state of the prescribing event. Describes the lifecycle of the prescription.</t>
-  </si>
-  <si>
-    <t>http://hl7.org/fhir/ValueSet/medicationrequest-status|4.0.1</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>
   </si>
   <si>
     <t>MedicationRequest.statusReason</t>
@@ -3389,20 +3391,19 @@
 - Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Client.</t>
   </si>
   <si>
-    <t xml:space="preserve">Status des Medikationsplaneintrags. TODO: Einschränken auf active, complete, on hold; 
-(req) active | on-hold | cancelled | completed | entered-in-error | stopped | draft | unknown 
-TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (z.B. Allergie).
+    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie).
 Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann.
-</t>
+(entfernt: cancelled, entered-in-error, draft, unknown)</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
   </si>
   <si>
     <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.
-TODO: Verwendung prüfen im Zusammenhang mit status.</t>
-  </si>
-  <si>
-    <t>TODO: Begründung, warum hier immer "order" anzugeben ist:
-Der Medikationsplaneintrag ist eine Handlungsermächtigung. Dieser wurde von einem:r Arzt:Ärztin erstellt und ermächtigt (auch andere Ärzte) zur Ausstellung einer geplanten Abgabe
-basierend auf diesen Eintrag.
+TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
+  </si>
+  <si>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order".
 (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. 
 https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
@@ -4781,7 +4782,7 @@
         <v>2</v>
       </c>
       <c r="B112" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
     </row>
     <row r="113">
@@ -4789,7 +4790,7 @@
         <v>4</v>
       </c>
       <c r="B113" t="s" s="2">
-        <v>813</v>
+        <v>814</v>
       </c>
     </row>
     <row r="114">
@@ -4805,7 +4806,7 @@
         <v>8</v>
       </c>
       <c r="B115" t="s" s="2">
-        <v>814</v>
+        <v>815</v>
       </c>
     </row>
     <row r="116">
@@ -4813,7 +4814,7 @@
         <v>10</v>
       </c>
       <c r="B116" t="s" s="2">
-        <v>815</v>
+        <v>816</v>
       </c>
     </row>
     <row r="117">
@@ -4875,7 +4876,7 @@
         <v>24</v>
       </c>
       <c r="B124" t="s" s="2">
-        <v>816</v>
+        <v>817</v>
       </c>
     </row>
     <row r="125">
@@ -4911,7 +4912,7 @@
         <v>32</v>
       </c>
       <c r="B129" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="130">
@@ -4919,7 +4920,7 @@
         <v>34</v>
       </c>
       <c r="B130" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="131">
@@ -5081,7 +5082,7 @@
         <v>32</v>
       </c>
       <c r="B151" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
     </row>
     <row r="152">
@@ -5089,7 +5090,7 @@
         <v>34</v>
       </c>
       <c r="B152" t="s" s="2">
-        <v>818</v>
+        <v>819</v>
       </c>
     </row>
     <row r="153">
@@ -5121,7 +5122,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
     </row>
     <row r="157">
@@ -5129,7 +5130,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
     </row>
     <row r="158">
@@ -5145,7 +5146,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
     </row>
     <row r="160">
@@ -5153,7 +5154,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
     </row>
     <row r="161">
@@ -5215,7 +5216,7 @@
         <v>24</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
     </row>
     <row r="169">
@@ -5251,7 +5252,7 @@
         <v>32</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
     </row>
     <row r="174">
@@ -5259,7 +5260,7 @@
         <v>34</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
     </row>
     <row r="175">
@@ -37804,7 +37805,7 @@
         <v>83</v>
       </c>
       <c r="I312" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J312" t="s" s="2">
         <v>23</v>
@@ -37816,7 +37817,7 @@
         <v>358</v>
       </c>
       <c r="M312" t="s" s="2">
-        <v>359</v>
+        <v>678</v>
       </c>
       <c r="N312" t="s" s="2">
         <v>360</v>
@@ -37892,10 +37893,10 @@
         <v>663</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>678</v>
+        <v>679</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -37997,10 +37998,10 @@
         <v>663</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>679</v>
+        <v>680</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -38102,10 +38103,10 @@
         <v>663</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>680</v>
+        <v>681</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -38209,10 +38210,10 @@
         <v>663</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -38238,13 +38239,13 @@
         <v>112</v>
       </c>
       <c r="M316" t="s" s="2">
-        <v>682</v>
+        <v>683</v>
       </c>
       <c r="N316" t="s" s="2">
-        <v>683</v>
+        <v>684</v>
       </c>
       <c r="O316" t="s" s="2">
-        <v>684</v>
+        <v>685</v>
       </c>
       <c r="P316" s="2"/>
       <c r="Q316" t="s" s="2">
@@ -38294,7 +38295,7 @@
         <v>23</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>681</v>
+        <v>682</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>76</v>
@@ -38314,10 +38315,10 @@
         <v>663</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -38343,13 +38344,13 @@
         <v>398</v>
       </c>
       <c r="M317" t="s" s="2">
-        <v>686</v>
+        <v>687</v>
       </c>
       <c r="N317" t="s" s="2">
-        <v>687</v>
+        <v>688</v>
       </c>
       <c r="O317" t="s" s="2">
-        <v>688</v>
+        <v>689</v>
       </c>
       <c r="P317" s="2"/>
       <c r="Q317" t="s" s="2">
@@ -38397,7 +38398,7 @@
         <v>23</v>
       </c>
       <c r="AG317" t="s" s="2">
-        <v>685</v>
+        <v>686</v>
       </c>
       <c r="AH317" t="s" s="2">
         <v>76</v>
@@ -38417,10 +38418,10 @@
         <v>663</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>689</v>
+        <v>690</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -38520,10 +38521,10 @@
         <v>663</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>690</v>
+        <v>691</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -38625,10 +38626,10 @@
         <v>663</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>691</v>
+        <v>692</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -38732,10 +38733,10 @@
         <v>663</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>692</v>
+        <v>693</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -38835,10 +38836,10 @@
         <v>663</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>693</v>
+        <v>694</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -38940,10 +38941,10 @@
         <v>663</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>694</v>
+        <v>695</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -38969,16 +38970,16 @@
         <v>97</v>
       </c>
       <c r="M323" t="s" s="2">
-        <v>695</v>
+        <v>696</v>
       </c>
       <c r="N323" t="s" s="2">
-        <v>696</v>
+        <v>697</v>
       </c>
       <c r="O323" t="s" s="2">
-        <v>697</v>
+        <v>698</v>
       </c>
       <c r="P323" t="s" s="2">
-        <v>698</v>
+        <v>699</v>
       </c>
       <c r="Q323" t="s" s="2">
         <v>23</v>
@@ -39027,7 +39028,7 @@
         <v>23</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>699</v>
+        <v>700</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>76</v>
@@ -39047,10 +39048,10 @@
         <v>663</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>700</v>
+        <v>701</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -39076,13 +39077,13 @@
         <v>141</v>
       </c>
       <c r="M324" t="s" s="2">
-        <v>701</v>
+        <v>702</v>
       </c>
       <c r="N324" t="s" s="2">
-        <v>702</v>
+        <v>703</v>
       </c>
       <c r="O324" t="s" s="2">
-        <v>703</v>
+        <v>704</v>
       </c>
       <c r="P324" s="2"/>
       <c r="Q324" t="s" s="2">
@@ -39132,7 +39133,7 @@
         <v>23</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>704</v>
+        <v>705</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>76</v>
@@ -39152,10 +39153,10 @@
         <v>663</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>705</v>
+        <v>706</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -39181,14 +39182,14 @@
         <v>103</v>
       </c>
       <c r="M325" t="s" s="2">
-        <v>706</v>
+        <v>707</v>
       </c>
       <c r="N325" t="s" s="2">
-        <v>707</v>
+        <v>708</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" t="s" s="2">
-        <v>708</v>
+        <v>709</v>
       </c>
       <c r="Q325" t="s" s="2">
         <v>23</v>
@@ -39237,7 +39238,7 @@
         <v>23</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>709</v>
+        <v>710</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>76</v>
@@ -39257,10 +39258,10 @@
         <v>663</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>710</v>
+        <v>711</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -39286,14 +39287,14 @@
         <v>141</v>
       </c>
       <c r="M326" t="s" s="2">
-        <v>711</v>
+        <v>712</v>
       </c>
       <c r="N326" t="s" s="2">
-        <v>712</v>
+        <v>713</v>
       </c>
       <c r="O326" s="2"/>
       <c r="P326" t="s" s="2">
-        <v>713</v>
+        <v>714</v>
       </c>
       <c r="Q326" t="s" s="2">
         <v>23</v>
@@ -39342,7 +39343,7 @@
         <v>23</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>714</v>
+        <v>715</v>
       </c>
       <c r="AH326" t="s" s="2">
         <v>76</v>
@@ -39362,10 +39363,10 @@
         <v>663</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>715</v>
+        <v>716</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -39391,16 +39392,16 @@
         <v>456</v>
       </c>
       <c r="M327" t="s" s="2">
-        <v>716</v>
+        <v>717</v>
       </c>
       <c r="N327" t="s" s="2">
-        <v>717</v>
+        <v>718</v>
       </c>
       <c r="O327" t="s" s="2">
-        <v>718</v>
+        <v>719</v>
       </c>
       <c r="P327" t="s" s="2">
-        <v>719</v>
+        <v>720</v>
       </c>
       <c r="Q327" t="s" s="2">
         <v>23</v>
@@ -39449,7 +39450,7 @@
         <v>23</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>720</v>
+        <v>721</v>
       </c>
       <c r="AH327" t="s" s="2">
         <v>76</v>
@@ -39469,10 +39470,10 @@
         <v>663</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>721</v>
+        <v>722</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -39576,10 +39577,10 @@
         <v>663</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -39605,13 +39606,13 @@
         <v>103</v>
       </c>
       <c r="M329" t="s" s="2">
-        <v>723</v>
+        <v>724</v>
       </c>
       <c r="N329" t="s" s="2">
-        <v>724</v>
+        <v>725</v>
       </c>
       <c r="O329" t="s" s="2">
-        <v>725</v>
+        <v>726</v>
       </c>
       <c r="P329" s="2"/>
       <c r="Q329" t="s" s="2">
@@ -39640,10 +39641,10 @@
         <v>121</v>
       </c>
       <c r="Z329" t="s" s="2">
-        <v>726</v>
+        <v>727</v>
       </c>
       <c r="AA329" t="s" s="2">
-        <v>727</v>
+        <v>728</v>
       </c>
       <c r="AB329" t="s" s="2">
         <v>23</v>
@@ -39661,7 +39662,7 @@
         <v>23</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>722</v>
+        <v>723</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>76</v>
@@ -39681,10 +39682,10 @@
         <v>663</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -39707,13 +39708,13 @@
         <v>84</v>
       </c>
       <c r="L330" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M330" t="s" s="2">
-        <v>730</v>
+        <v>731</v>
       </c>
       <c r="N330" t="s" s="2">
-        <v>731</v>
+        <v>732</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
@@ -39764,7 +39765,7 @@
         <v>23</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>728</v>
+        <v>729</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>76</v>
@@ -39784,10 +39785,10 @@
         <v>663</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -39813,13 +39814,13 @@
         <v>398</v>
       </c>
       <c r="M331" t="s" s="2">
-        <v>733</v>
+        <v>734</v>
       </c>
       <c r="N331" t="s" s="2">
-        <v>734</v>
+        <v>735</v>
       </c>
       <c r="O331" t="s" s="2">
-        <v>735</v>
+        <v>736</v>
       </c>
       <c r="P331" s="2"/>
       <c r="Q331" t="s" s="2">
@@ -39849,7 +39850,7 @@
       </c>
       <c r="Z331" s="2"/>
       <c r="AA331" t="s" s="2">
-        <v>736</v>
+        <v>737</v>
       </c>
       <c r="AB331" t="s" s="2">
         <v>23</v>
@@ -39867,7 +39868,7 @@
         <v>23</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>732</v>
+        <v>733</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>76</v>
@@ -39887,10 +39888,10 @@
         <v>663</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -39913,13 +39914,13 @@
         <v>84</v>
       </c>
       <c r="L332" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M332" t="s" s="2">
-        <v>739</v>
+        <v>740</v>
       </c>
       <c r="N332" t="s" s="2">
-        <v>740</v>
+        <v>741</v>
       </c>
       <c r="O332" s="2"/>
       <c r="P332" s="2"/>
@@ -39970,7 +39971,7 @@
         <v>23</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>737</v>
+        <v>738</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>76</v>
@@ -39990,10 +39991,10 @@
         <v>663</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -40019,13 +40020,13 @@
         <v>136</v>
       </c>
       <c r="M333" t="s" s="2">
-        <v>742</v>
+        <v>743</v>
       </c>
       <c r="N333" t="s" s="2">
-        <v>743</v>
+        <v>744</v>
       </c>
       <c r="O333" t="s" s="2">
-        <v>744</v>
+        <v>745</v>
       </c>
       <c r="P333" s="2"/>
       <c r="Q333" t="s" s="2">
@@ -40075,7 +40076,7 @@
         <v>23</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>741</v>
+        <v>742</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>76</v>
@@ -40095,10 +40096,10 @@
         <v>663</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>745</v>
+        <v>746</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -40198,10 +40199,10 @@
         <v>663</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>746</v>
+        <v>747</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -40303,10 +40304,10 @@
         <v>663</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>747</v>
+        <v>748</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -40410,10 +40411,10 @@
         <v>663</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -40436,17 +40437,17 @@
         <v>23</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>749</v>
+        <v>750</v>
       </c>
       <c r="M337" t="s" s="2">
-        <v>750</v>
+        <v>751</v>
       </c>
       <c r="N337" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O337" s="2"/>
       <c r="P337" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Q337" t="s" s="2">
         <v>23</v>
@@ -40493,7 +40494,7 @@
         <v>169</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>83</v>
@@ -40513,13 +40514,13 @@
         <v>663</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>753</v>
+        <v>754</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D338" t="s" s="2">
-        <v>754</v>
+        <v>755</v>
       </c>
       <c r="E338" t="s" s="2">
         <v>23</v>
@@ -40544,14 +40545,14 @@
         <v>398</v>
       </c>
       <c r="M338" t="s" s="2">
-        <v>755</v>
+        <v>756</v>
       </c>
       <c r="N338" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O338" s="2"/>
       <c r="P338" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Q338" t="s" s="2">
         <v>23</v>
@@ -40600,7 +40601,7 @@
         <v>23</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>83</v>
@@ -40620,13 +40621,13 @@
         <v>663</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>756</v>
+        <v>757</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="D339" t="s" s="2">
-        <v>757</v>
+        <v>758</v>
       </c>
       <c r="E339" t="s" s="2">
         <v>23</v>
@@ -40648,17 +40649,17 @@
         <v>23</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>758</v>
+        <v>759</v>
       </c>
       <c r="M339" t="s" s="2">
-        <v>759</v>
+        <v>760</v>
       </c>
       <c r="N339" t="s" s="2">
-        <v>751</v>
+        <v>752</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" t="s" s="2">
-        <v>752</v>
+        <v>753</v>
       </c>
       <c r="Q339" t="s" s="2">
         <v>23</v>
@@ -40707,7 +40708,7 @@
         <v>23</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>748</v>
+        <v>749</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>83</v>
@@ -40727,10 +40728,10 @@
         <v>663</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>760</v>
+        <v>761</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>761</v>
+        <v>762</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -40830,10 +40831,10 @@
         <v>663</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>762</v>
+        <v>763</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>763</v>
+        <v>764</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -40935,10 +40936,10 @@
         <v>663</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>764</v>
+        <v>765</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>765</v>
+        <v>766</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -40964,13 +40965,13 @@
         <v>141</v>
       </c>
       <c r="M342" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N342" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O342" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P342" s="2"/>
       <c r="Q342" t="s" s="2">
@@ -41020,7 +41021,7 @@
         <v>23</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>76</v>
@@ -41029,10 +41030,10 @@
         <v>83</v>
       </c>
       <c r="AJ342" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AK342" t="s" s="2">
-        <v>771</v>
+        <v>772</v>
       </c>
     </row>
     <row r="343">
@@ -41040,10 +41041,10 @@
         <v>663</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>772</v>
+        <v>773</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>773</v>
+        <v>774</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -41069,13 +41070,13 @@
         <v>97</v>
       </c>
       <c r="M343" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N343" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O343" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P343" s="2"/>
       <c r="Q343" t="s" s="2">
@@ -41101,13 +41102,13 @@
         <v>23</v>
       </c>
       <c r="Y343" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Z343" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AA343" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AB343" t="s" s="2">
         <v>23</v>
@@ -41125,7 +41126,7 @@
         <v>23</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>76</v>
@@ -41145,10 +41146,10 @@
         <v>663</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>781</v>
+        <v>782</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>782</v>
+        <v>783</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -41174,13 +41175,13 @@
         <v>112</v>
       </c>
       <c r="M344" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N344" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O344" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P344" s="2"/>
       <c r="Q344" t="s" s="2">
@@ -41230,7 +41231,7 @@
         <v>23</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>76</v>
@@ -41250,10 +41251,10 @@
         <v>663</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>787</v>
+        <v>788</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>788</v>
+        <v>789</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -41279,13 +41280,13 @@
         <v>141</v>
       </c>
       <c r="M345" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N345" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O345" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P345" s="2"/>
       <c r="Q345" t="s" s="2">
@@ -41335,7 +41336,7 @@
         <v>23</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>76</v>
@@ -41355,10 +41356,10 @@
         <v>663</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -41384,14 +41385,14 @@
         <v>456</v>
       </c>
       <c r="M346" t="s" s="2">
-        <v>794</v>
+        <v>795</v>
       </c>
       <c r="N346" t="s" s="2">
-        <v>795</v>
+        <v>796</v>
       </c>
       <c r="O346" s="2"/>
       <c r="P346" t="s" s="2">
-        <v>796</v>
+        <v>797</v>
       </c>
       <c r="Q346" t="s" s="2">
         <v>23</v>
@@ -41440,7 +41441,7 @@
         <v>23</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>793</v>
+        <v>794</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>76</v>
@@ -41460,10 +41461,10 @@
         <v>663</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -41486,13 +41487,13 @@
         <v>23</v>
       </c>
       <c r="L347" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M347" t="s" s="2">
-        <v>798</v>
+        <v>799</v>
       </c>
       <c r="N347" t="s" s="2">
-        <v>799</v>
+        <v>800</v>
       </c>
       <c r="O347" s="2"/>
       <c r="P347" s="2"/>
@@ -41543,7 +41544,7 @@
         <v>23</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>797</v>
+        <v>798</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>76</v>
@@ -41563,10 +41564,10 @@
         <v>663</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -41592,10 +41593,10 @@
         <v>136</v>
       </c>
       <c r="M348" t="s" s="2">
-        <v>801</v>
+        <v>802</v>
       </c>
       <c r="N348" t="s" s="2">
-        <v>802</v>
+        <v>803</v>
       </c>
       <c r="O348" s="2"/>
       <c r="P348" s="2"/>
@@ -41646,7 +41647,7 @@
         <v>23</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>800</v>
+        <v>801</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>76</v>
@@ -41666,10 +41667,10 @@
         <v>663</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>803</v>
+        <v>804</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -41769,10 +41770,10 @@
         <v>663</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>804</v>
+        <v>805</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -41874,10 +41875,10 @@
         <v>663</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>805</v>
+        <v>806</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -41981,10 +41982,10 @@
         <v>663</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -42010,10 +42011,10 @@
         <v>141</v>
       </c>
       <c r="M352" t="s" s="2">
-        <v>807</v>
+        <v>808</v>
       </c>
       <c r="N352" t="s" s="2">
-        <v>808</v>
+        <v>809</v>
       </c>
       <c r="O352" s="2"/>
       <c r="P352" s="2"/>
@@ -42064,7 +42065,7 @@
         <v>23</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>806</v>
+        <v>807</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>76</v>
@@ -42084,10 +42085,10 @@
         <v>663</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -42113,10 +42114,10 @@
         <v>418</v>
       </c>
       <c r="M353" t="s" s="2">
-        <v>810</v>
+        <v>811</v>
       </c>
       <c r="N353" t="s" s="2">
-        <v>811</v>
+        <v>812</v>
       </c>
       <c r="O353" s="2"/>
       <c r="P353" s="2"/>
@@ -42167,7 +42168,7 @@
         <v>23</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>809</v>
+        <v>810</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>76</v>
@@ -42184,13 +42185,13 @@
     </row>
     <row r="354">
       <c r="A354" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -42216,7 +42217,7 @@
         <v>78</v>
       </c>
       <c r="M354" t="s" s="2">
-        <v>819</v>
+        <v>820</v>
       </c>
       <c r="N354" t="s" s="2">
         <v>303</v>
@@ -42270,7 +42271,7 @@
         <v>23</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>76</v>
@@ -42287,13 +42288,13 @@
     </row>
     <row r="355">
       <c r="A355" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -42392,13 +42393,13 @@
     </row>
     <row r="356">
       <c r="A356" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -42495,13 +42496,13 @@
     </row>
     <row r="357">
       <c r="A357" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -42600,13 +42601,13 @@
     </row>
     <row r="358">
       <c r="A358" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -42705,13 +42706,13 @@
     </row>
     <row r="359">
       <c r="A359" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -42810,13 +42811,13 @@
     </row>
     <row r="360">
       <c r="A360" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -42915,13 +42916,13 @@
     </row>
     <row r="361">
       <c r="A361" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -42947,10 +42948,10 @@
         <v>147</v>
       </c>
       <c r="M361" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N361" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O361" s="2"/>
       <c r="P361" s="2"/>
@@ -43016,16 +43017,16 @@
     </row>
     <row r="362">
       <c r="A362" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D362" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E362" t="s" s="2">
         <v>23</v>
@@ -43047,13 +43048,13 @@
         <v>23</v>
       </c>
       <c r="L362" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="M362" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="N362" t="s" s="2">
-        <v>833</v>
+        <v>834</v>
       </c>
       <c r="O362" s="2"/>
       <c r="P362" s="2"/>
@@ -43113,7 +43114,7 @@
         <v>77</v>
       </c>
       <c r="AJ362" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK362" t="s" s="2">
         <v>152</v>
@@ -43121,16 +43122,16 @@
     </row>
     <row r="363">
       <c r="A363" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D363" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E363" t="s" s="2">
         <v>23</v>
@@ -43152,13 +43153,13 @@
         <v>23</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M363" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N363" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O363" s="2"/>
       <c r="P363" s="2"/>
@@ -43218,7 +43219,7 @@
         <v>77</v>
       </c>
       <c r="AJ363" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK363" t="s" s="2">
         <v>152</v>
@@ -43226,16 +43227,16 @@
     </row>
     <row r="364">
       <c r="A364" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D364" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E364" t="s" s="2">
         <v>23</v>
@@ -43257,13 +43258,13 @@
         <v>23</v>
       </c>
       <c r="L364" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M364" t="s" s="2">
-        <v>843</v>
+        <v>844</v>
       </c>
       <c r="N364" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O364" s="2"/>
       <c r="P364" s="2"/>
@@ -43323,7 +43324,7 @@
         <v>77</v>
       </c>
       <c r="AJ364" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK364" t="s" s="2">
         <v>152</v>
@@ -43331,13 +43332,13 @@
     </row>
     <row r="365">
       <c r="A365" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -43438,13 +43439,13 @@
     </row>
     <row r="366">
       <c r="A366" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -43470,10 +43471,10 @@
         <v>112</v>
       </c>
       <c r="M366" t="s" s="2">
-        <v>847</v>
+        <v>848</v>
       </c>
       <c r="N366" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="O366" t="s" s="2">
         <v>499</v>
@@ -43526,7 +43527,7 @@
         <v>23</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>76</v>
@@ -43543,13 +43544,13 @@
     </row>
     <row r="367">
       <c r="A367" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -43563,7 +43564,7 @@
         <v>83</v>
       </c>
       <c r="I367" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J367" t="s" s="2">
         <v>84</v>
@@ -43575,10 +43576,10 @@
         <v>103</v>
       </c>
       <c r="M367" t="s" s="2">
-        <v>850</v>
+        <v>851</v>
       </c>
       <c r="N367" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="O367" t="s" s="2">
         <v>382</v>
@@ -43609,9 +43610,7 @@
       <c r="Y367" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="Z367" t="s" s="2">
-        <v>852</v>
-      </c>
+      <c r="Z367" s="2"/>
       <c r="AA367" t="s" s="2">
         <v>853</v>
       </c>
@@ -43631,7 +43630,7 @@
         <v>23</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>83</v>
@@ -43648,7 +43647,7 @@
     </row>
     <row r="368">
       <c r="A368" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B368" t="s" s="2">
         <v>854</v>
@@ -43753,7 +43752,7 @@
     </row>
     <row r="369">
       <c r="A369" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B369" t="s" s="2">
         <v>860</v>
@@ -43858,7 +43857,7 @@
     </row>
     <row r="370">
       <c r="A370" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B370" t="s" s="2">
         <v>867</v>
@@ -43963,7 +43962,7 @@
     </row>
     <row r="371">
       <c r="A371" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B371" t="s" s="2">
         <v>874</v>
@@ -44066,7 +44065,7 @@
     </row>
     <row r="372">
       <c r="A372" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B372" t="s" s="2">
         <v>879</v>
@@ -44171,7 +44170,7 @@
     </row>
     <row r="373">
       <c r="A373" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B373" t="s" s="2">
         <v>883</v>
@@ -44274,7 +44273,7 @@
     </row>
     <row r="374">
       <c r="A374" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B374" t="s" s="2">
         <v>887</v>
@@ -44377,7 +44376,7 @@
     </row>
     <row r="375">
       <c r="A375" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B375" t="s" s="2">
         <v>892</v>
@@ -44482,7 +44481,7 @@
     </row>
     <row r="376">
       <c r="A376" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B376" t="s" s="2">
         <v>893</v>
@@ -44585,7 +44584,7 @@
     </row>
     <row r="377">
       <c r="A377" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B377" t="s" s="2">
         <v>895</v>
@@ -44690,7 +44689,7 @@
     </row>
     <row r="378">
       <c r="A378" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B378" t="s" s="2">
         <v>897</v>
@@ -44797,7 +44796,7 @@
     </row>
     <row r="379">
       <c r="A379" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B379" t="s" s="2">
         <v>899</v>
@@ -44904,7 +44903,7 @@
     </row>
     <row r="380">
       <c r="A380" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B380" t="s" s="2">
         <v>901</v>
@@ -45011,7 +45010,7 @@
     </row>
     <row r="381">
       <c r="A381" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B381" t="s" s="2">
         <v>905</v>
@@ -45116,7 +45115,7 @@
     </row>
     <row r="382">
       <c r="A382" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B382" t="s" s="2">
         <v>909</v>
@@ -45221,7 +45220,7 @@
     </row>
     <row r="383">
       <c r="A383" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B383" t="s" s="2">
         <v>912</v>
@@ -45324,7 +45323,7 @@
     </row>
     <row r="384">
       <c r="A384" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B384" t="s" s="2">
         <v>914</v>
@@ -45427,7 +45426,7 @@
     </row>
     <row r="385">
       <c r="A385" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B385" t="s" s="2">
         <v>917</v>
@@ -45530,7 +45529,7 @@
     </row>
     <row r="386">
       <c r="A386" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B386" t="s" s="2">
         <v>920</v>
@@ -45633,7 +45632,7 @@
     </row>
     <row r="387">
       <c r="A387" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B387" t="s" s="2">
         <v>923</v>
@@ -45738,7 +45737,7 @@
     </row>
     <row r="388">
       <c r="A388" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B388" t="s" s="2">
         <v>928</v>
@@ -45841,7 +45840,7 @@
     </row>
     <row r="389">
       <c r="A389" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B389" t="s" s="2">
         <v>931</v>
@@ -45946,7 +45945,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>937</v>
@@ -46049,7 +46048,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>938</v>
@@ -46154,7 +46153,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>939</v>
@@ -46261,7 +46260,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>940</v>
@@ -46368,7 +46367,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>941</v>
@@ -46473,7 +46472,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>945</v>
@@ -46576,7 +46575,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>949</v>
@@ -46679,7 +46678,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>952</v>
@@ -46782,7 +46781,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>955</v>
@@ -46887,7 +46886,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>959</v>
@@ -46992,7 +46991,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>965</v>
@@ -47095,7 +47094,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>968</v>
@@ -47198,7 +47197,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>971</v>
@@ -47303,7 +47302,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>974</v>
@@ -47406,7 +47405,7 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B404" t="s" s="2">
         <v>977</v>
@@ -47509,7 +47508,7 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B405" t="s" s="2">
         <v>978</v>
@@ -47614,7 +47613,7 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B406" t="s" s="2">
         <v>979</v>
@@ -47721,7 +47720,7 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B407" t="s" s="2">
         <v>980</v>
@@ -47826,7 +47825,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>984</v>
@@ -47929,7 +47928,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>985</v>
@@ -48034,7 +48033,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>986</v>
@@ -48141,7 +48140,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>987</v>
@@ -48244,7 +48243,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>990</v>
@@ -48347,7 +48346,7 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B413" t="s" s="2">
         <v>994</v>
@@ -48450,7 +48449,7 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B414" t="s" s="2">
         <v>997</v>
@@ -48557,7 +48556,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>1003</v>
@@ -48662,7 +48661,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>1007</v>
@@ -48765,7 +48764,7 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B417" t="s" s="2">
         <v>1010</v>
@@ -48870,7 +48869,7 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B418" t="s" s="2">
         <v>1014</v>
@@ -48899,7 +48898,7 @@
         <v>23</v>
       </c>
       <c r="L418" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M418" t="s" s="2">
         <v>1015</v>
@@ -48973,7 +48972,7 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B419" t="s" s="2">
         <v>1017</v>
@@ -49076,7 +49075,7 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B420" t="s" s="2">
         <v>1020</v>
@@ -49179,7 +49178,7 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B421" t="s" s="2">
         <v>1021</v>
@@ -49284,7 +49283,7 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B422" t="s" s="2">
         <v>1022</v>
@@ -49391,7 +49390,7 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B423" t="s" s="2">
         <v>1023</v>
@@ -49496,7 +49495,7 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B424" t="s" s="2">
         <v>1029</v>
@@ -49599,7 +49598,7 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B425" t="s" s="2">
         <v>1032</v>
@@ -49702,7 +49701,7 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B426" t="s" s="2">
         <v>1035</v>
@@ -49807,7 +49806,7 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>812</v>
+        <v>813</v>
       </c>
       <c r="B427" t="s" s="2">
         <v>1038</v>
@@ -49915,10 +49914,10 @@
         <v>1042</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -49998,7 +49997,7 @@
         <v>23</v>
       </c>
       <c r="AG428" t="s" s="2">
-        <v>817</v>
+        <v>818</v>
       </c>
       <c r="AH428" t="s" s="2">
         <v>76</v>
@@ -50018,10 +50017,10 @@
         <v>1042</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>820</v>
+        <v>821</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -50123,10 +50122,10 @@
         <v>1042</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>821</v>
+        <v>822</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -50226,10 +50225,10 @@
         <v>1042</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>822</v>
+        <v>823</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -50331,10 +50330,10 @@
         <v>1042</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>823</v>
+        <v>824</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -50436,10 +50435,10 @@
         <v>1042</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>824</v>
+        <v>825</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -50541,10 +50540,10 @@
         <v>1042</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -50647,7 +50646,7 @@
         <v>1047</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D435" t="s" s="2">
         <v>1048</v>
@@ -50754,7 +50753,7 @@
         <v>1050</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>825</v>
+        <v>826</v>
       </c>
       <c r="D436" t="s" s="2">
         <v>1051</v>
@@ -50858,10 +50857,10 @@
         <v>1042</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -50887,10 +50886,10 @@
         <v>147</v>
       </c>
       <c r="M437" t="s" s="2">
-        <v>827</v>
+        <v>828</v>
       </c>
       <c r="N437" t="s" s="2">
-        <v>828</v>
+        <v>829</v>
       </c>
       <c r="O437" s="2"/>
       <c r="P437" s="2"/>
@@ -50959,13 +50958,13 @@
         <v>1042</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>829</v>
+        <v>830</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D438" t="s" s="2">
-        <v>830</v>
+        <v>831</v>
       </c>
       <c r="E438" t="s" s="2">
         <v>23</v>
@@ -50987,10 +50986,10 @@
         <v>23</v>
       </c>
       <c r="L438" t="s" s="2">
-        <v>831</v>
+        <v>832</v>
       </c>
       <c r="M438" t="s" s="2">
-        <v>832</v>
+        <v>833</v>
       </c>
       <c r="N438" t="s" s="2">
         <v>1055</v>
@@ -51053,7 +51052,7 @@
         <v>77</v>
       </c>
       <c r="AJ438" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK438" t="s" s="2">
         <v>152</v>
@@ -51064,13 +51063,13 @@
         <v>1042</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>835</v>
+        <v>836</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D439" t="s" s="2">
-        <v>836</v>
+        <v>837</v>
       </c>
       <c r="E439" t="s" s="2">
         <v>23</v>
@@ -51092,13 +51091,13 @@
         <v>23</v>
       </c>
       <c r="L439" t="s" s="2">
-        <v>837</v>
+        <v>838</v>
       </c>
       <c r="M439" t="s" s="2">
-        <v>838</v>
+        <v>839</v>
       </c>
       <c r="N439" t="s" s="2">
-        <v>839</v>
+        <v>840</v>
       </c>
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
@@ -51158,7 +51157,7 @@
         <v>77</v>
       </c>
       <c r="AJ439" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK439" t="s" s="2">
         <v>152</v>
@@ -51169,13 +51168,13 @@
         <v>1042</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>840</v>
+        <v>841</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>826</v>
+        <v>827</v>
       </c>
       <c r="D440" t="s" s="2">
-        <v>841</v>
+        <v>842</v>
       </c>
       <c r="E440" t="s" s="2">
         <v>23</v>
@@ -51197,13 +51196,13 @@
         <v>23</v>
       </c>
       <c r="L440" t="s" s="2">
-        <v>842</v>
+        <v>843</v>
       </c>
       <c r="M440" t="s" s="2">
         <v>1056</v>
       </c>
       <c r="N440" t="s" s="2">
-        <v>844</v>
+        <v>845</v>
       </c>
       <c r="O440" s="2"/>
       <c r="P440" s="2"/>
@@ -51263,7 +51262,7 @@
         <v>77</v>
       </c>
       <c r="AJ440" t="s" s="2">
-        <v>834</v>
+        <v>835</v>
       </c>
       <c r="AK440" t="s" s="2">
         <v>152</v>
@@ -51274,10 +51273,10 @@
         <v>1042</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>845</v>
+        <v>846</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -51381,10 +51380,10 @@
         <v>1042</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -51392,13 +51391,13 @@
       </c>
       <c r="F442" s="2"/>
       <c r="G442" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H442" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I442" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J442" t="s" s="2">
         <v>23</v>
@@ -51413,7 +51412,7 @@
         <v>1057</v>
       </c>
       <c r="N442" t="s" s="2">
-        <v>848</v>
+        <v>849</v>
       </c>
       <c r="O442" t="s" s="2">
         <v>499</v>
@@ -51466,7 +51465,7 @@
         <v>23</v>
       </c>
       <c r="AG442" t="s" s="2">
-        <v>846</v>
+        <v>847</v>
       </c>
       <c r="AH442" t="s" s="2">
         <v>76</v>
@@ -51486,10 +51485,10 @@
         <v>1042</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -51518,7 +51517,7 @@
         <v>1058</v>
       </c>
       <c r="N443" t="s" s="2">
-        <v>851</v>
+        <v>852</v>
       </c>
       <c r="O443" t="s" s="2">
         <v>382</v>
@@ -51549,11 +51548,9 @@
       <c r="Y443" t="s" s="2">
         <v>121</v>
       </c>
-      <c r="Z443" t="s" s="2">
-        <v>852</v>
-      </c>
+      <c r="Z443" s="2"/>
       <c r="AA443" t="s" s="2">
-        <v>853</v>
+        <v>1059</v>
       </c>
       <c r="AB443" t="s" s="2">
         <v>23</v>
@@ -51571,7 +51568,7 @@
         <v>23</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>849</v>
+        <v>850</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>83</v>
@@ -51620,7 +51617,7 @@
         <v>398</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="N444" t="s" s="2">
         <v>856</v>
@@ -51725,7 +51722,7 @@
         <v>103</v>
       </c>
       <c r="M445" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="N445" t="s" s="2">
         <v>862</v>
@@ -51830,7 +51827,7 @@
         <v>398</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="N446" t="s" s="2">
         <v>869</v>
@@ -51847,7 +51844,7 @@
         <v>23</v>
       </c>
       <c r="T446" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="U446" t="s" s="2">
         <v>23</v>
@@ -51935,7 +51932,7 @@
         <v>103</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="N447" t="s" s="2">
         <v>876</v>
@@ -52038,7 +52035,7 @@
         <v>456</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N448" t="s" s="2">
         <v>881</v>
@@ -52143,7 +52140,7 @@
         <v>884</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="N449" t="s" s="2">
         <v>886</v>
@@ -52215,13 +52212,13 @@
         <v>1042</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C450" t="s" s="2">
         <v>883</v>
       </c>
       <c r="D450" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="E450" t="s" s="2">
         <v>23</v>
@@ -52246,7 +52243,7 @@
         <v>456</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="N450" t="s" s="2">
         <v>886</v>
@@ -52320,13 +52317,13 @@
         <v>1042</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C451" t="s" s="2">
         <v>883</v>
       </c>
       <c r="D451" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="E451" t="s" s="2">
         <v>23</v>
@@ -52348,10 +52345,10 @@
         <v>84</v>
       </c>
       <c r="L451" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="M451" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="N451" t="s" s="2">
         <v>886</v>
@@ -52454,7 +52451,7 @@
         <v>903</v>
       </c>
       <c r="M452" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="N452" t="s" s="2">
         <v>889</v>
@@ -52738,10 +52735,10 @@
         <v>1042</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -52767,13 +52764,13 @@
         <v>141</v>
       </c>
       <c r="M455" t="s" s="2">
-        <v>766</v>
+        <v>767</v>
       </c>
       <c r="N455" t="s" s="2">
-        <v>767</v>
+        <v>768</v>
       </c>
       <c r="O455" t="s" s="2">
-        <v>768</v>
+        <v>769</v>
       </c>
       <c r="P455" s="2"/>
       <c r="Q455" t="s" s="2">
@@ -52823,7 +52820,7 @@
         <v>23</v>
       </c>
       <c r="AG455" t="s" s="2">
-        <v>769</v>
+        <v>770</v>
       </c>
       <c r="AH455" t="s" s="2">
         <v>76</v>
@@ -52832,10 +52829,10 @@
         <v>83</v>
       </c>
       <c r="AJ455" t="s" s="2">
-        <v>770</v>
+        <v>771</v>
       </c>
       <c r="AK455" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
     </row>
     <row r="456">
@@ -52843,10 +52840,10 @@
         <v>1042</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -52872,13 +52869,13 @@
         <v>97</v>
       </c>
       <c r="M456" t="s" s="2">
-        <v>774</v>
+        <v>775</v>
       </c>
       <c r="N456" t="s" s="2">
-        <v>775</v>
+        <v>776</v>
       </c>
       <c r="O456" t="s" s="2">
-        <v>776</v>
+        <v>777</v>
       </c>
       <c r="P456" s="2"/>
       <c r="Q456" t="s" s="2">
@@ -52904,13 +52901,13 @@
         <v>23</v>
       </c>
       <c r="Y456" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Z456" t="s" s="2">
-        <v>778</v>
+        <v>779</v>
       </c>
       <c r="AA456" t="s" s="2">
-        <v>779</v>
+        <v>780</v>
       </c>
       <c r="AB456" t="s" s="2">
         <v>23</v>
@@ -52928,7 +52925,7 @@
         <v>23</v>
       </c>
       <c r="AG456" t="s" s="2">
-        <v>780</v>
+        <v>781</v>
       </c>
       <c r="AH456" t="s" s="2">
         <v>76</v>
@@ -52948,10 +52945,10 @@
         <v>1042</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -52977,13 +52974,13 @@
         <v>112</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>783</v>
+        <v>784</v>
       </c>
       <c r="N457" t="s" s="2">
-        <v>784</v>
+        <v>785</v>
       </c>
       <c r="O457" t="s" s="2">
-        <v>785</v>
+        <v>786</v>
       </c>
       <c r="P457" s="2"/>
       <c r="Q457" t="s" s="2">
@@ -53033,7 +53030,7 @@
         <v>23</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>786</v>
+        <v>787</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>76</v>
@@ -53053,10 +53050,10 @@
         <v>1042</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -53082,13 +53079,13 @@
         <v>141</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>789</v>
+        <v>790</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>790</v>
+        <v>791</v>
       </c>
       <c r="O458" t="s" s="2">
-        <v>791</v>
+        <v>792</v>
       </c>
       <c r="P458" s="2"/>
       <c r="Q458" t="s" s="2">
@@ -53138,7 +53135,7 @@
         <v>23</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>792</v>
+        <v>793</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>76</v>
@@ -53187,7 +53184,7 @@
         <v>408</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="N459" t="s" s="2">
         <v>907</v>
@@ -53292,7 +53289,7 @@
         <v>414</v>
       </c>
       <c r="M460" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N460" t="s" s="2">
         <v>910</v>
@@ -53397,7 +53394,7 @@
         <v>570</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="N461" t="s" s="2">
         <v>913</v>
@@ -53500,7 +53497,7 @@
         <v>418</v>
       </c>
       <c r="M462" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="N462" t="s" s="2">
         <v>916</v>
@@ -53603,7 +53600,7 @@
         <v>586</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="N463" t="s" s="2">
         <v>919</v>
@@ -53706,7 +53703,7 @@
         <v>921</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="N464" t="s" s="2">
         <v>922</v>
@@ -53809,7 +53806,7 @@
         <v>398</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="N465" t="s" s="2">
         <v>924</v>
@@ -53914,7 +53911,7 @@
         <v>929</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="N466" t="s" s="2">
         <v>930</v>
@@ -54017,7 +54014,7 @@
         <v>398</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N467" t="s" s="2">
         <v>933</v>
@@ -54122,7 +54119,7 @@
         <v>942</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="N468" t="s" s="2">
         <v>943</v>
@@ -54227,7 +54224,7 @@
         <v>946</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="N469" t="s" s="2">
         <v>948</v>
@@ -54330,7 +54327,7 @@
         <v>97</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="N470" t="s" s="2">
         <v>951</v>
@@ -54430,10 +54427,10 @@
         <v>84</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="N471" t="s" s="2">
         <v>954</v>
@@ -54536,7 +54533,7 @@
         <v>112</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="N472" t="s" s="2">
         <v>957</v>
@@ -54641,7 +54638,7 @@
         <v>398</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>961</v>
@@ -54746,7 +54743,7 @@
         <v>966</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="N474" t="s" s="2">
         <v>967</v>
@@ -54849,7 +54846,7 @@
         <v>438</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="N475" t="s" s="2">
         <v>970</v>
@@ -54952,7 +54949,7 @@
         <v>626</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="N476" t="s" s="2">
         <v>628</v>
@@ -55057,7 +55054,7 @@
         <v>136</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N477" t="s" s="2">
         <v>976</v>
@@ -56311,7 +56308,7 @@
         <v>130</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="N489" t="s" s="2">
         <v>1005</v>
@@ -56621,7 +56618,7 @@
         <v>23</v>
       </c>
       <c r="L492" t="s" s="2">
-        <v>729</v>
+        <v>730</v>
       </c>
       <c r="M492" t="s" s="2">
         <v>1015</v>
@@ -56727,7 +56724,7 @@
         <v>136</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="N493" t="s" s="2">
         <v>1019</v>
@@ -57353,7 +57350,7 @@
         <v>594</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="N499" t="s" s="2">
         <v>1034</v>
@@ -57456,7 +57453,7 @@
         <v>654</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="N500" t="s" s="2">
         <v>1037</v>
@@ -57561,7 +57558,7 @@
         <v>659</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N501" t="s" s="2">
         <v>1040</v>
@@ -57634,13 +57631,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -57720,7 +57717,7 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>76</v>
@@ -57737,13 +57734,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -57842,13 +57839,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -57945,13 +57942,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58050,13 +58047,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -58155,13 +58152,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -58260,13 +58257,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -58365,13 +58362,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -58470,13 +58467,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -58577,13 +58574,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -58609,13 +58606,13 @@
         <v>112</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
@@ -58665,7 +58662,7 @@
         <v>23</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -58682,13 +58679,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -58714,10 +58711,10 @@
         <v>103</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -58747,10 +58744,10 @@
         <v>121</v>
       </c>
       <c r="Z512" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AA512" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AB512" t="s" s="2">
         <v>23</v>
@@ -58768,7 +58765,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -58785,13 +58782,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -58817,13 +58814,13 @@
         <v>398</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -58849,13 +58846,13 @@
         <v>23</v>
       </c>
       <c r="Y513" t="s" s="2">
-        <v>777</v>
+        <v>778</v>
       </c>
       <c r="Z513" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AA513" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="AB513" t="s" s="2">
         <v>23</v>
@@ -58873,7 +58870,7 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
@@ -58890,13 +58887,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -58922,13 +58919,13 @@
         <v>398</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
@@ -58957,10 +58954,10 @@
         <v>404</v>
       </c>
       <c r="Z514" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AA514" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="AB514" t="s" s="2">
         <v>23</v>
@@ -58978,7 +58975,7 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>83</v>
@@ -58995,13 +58992,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59027,10 +59024,10 @@
         <v>141</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="O515" s="2"/>
       <c r="P515" s="2"/>
@@ -59081,7 +59078,7 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>76</v>
@@ -59098,13 +59095,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -59130,10 +59127,10 @@
         <v>136</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="O516" s="2"/>
       <c r="P516" s="2"/>
@@ -59141,7 +59138,7 @@
         <v>23</v>
       </c>
       <c r="R516" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="S516" t="s" s="2">
         <v>23</v>
@@ -59186,7 +59183,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -59203,13 +59200,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -59306,13 +59303,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -59411,13 +59408,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -59518,13 +59515,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -59550,10 +59547,10 @@
         <v>112</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -59604,7 +59601,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -59621,13 +59618,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -59653,10 +59650,10 @@
         <v>418</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -59707,7 +59704,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -59724,13 +59721,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -59756,10 +59753,10 @@
         <v>603</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" s="2"/>
@@ -59810,7 +59807,7 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
@@ -59827,13 +59824,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -59859,10 +59856,10 @@
         <v>136</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -59913,7 +59910,7 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
@@ -59930,13 +59927,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60033,13 +60030,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -60138,13 +60135,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -60245,13 +60242,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -60274,13 +60271,13 @@
         <v>84</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>738</v>
+        <v>739</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -60331,7 +60328,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -60348,13 +60345,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -60377,13 +60374,13 @@
         <v>84</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -60413,10 +60410,10 @@
         <v>404</v>
       </c>
       <c r="Z528" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="AA528" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="AB528" t="s" s="2">
         <v>23</v>
@@ -60434,7 +60431,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>83</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19855" uniqueCount="1442">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19855" uniqueCount="1441">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-23T17:25:44+00:00</t>
+    <t>2026-02-26T16:36:39+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>**Beschreibung:** Das Bundle vom Typ Collection bestehend aus: 
+    <t>Das Bundle vom Typ Collection bestehend aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus) 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
@@ -1078,7 +1078,7 @@
     <t>ELGA e-Med Medikationsplan Transaction Bundle</t>
   </si>
   <si>
-    <t>**Beschreibung:** Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus) 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
@@ -1107,13 +1107,10 @@
     <t>ELGA e-Med Dosage</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dosage</t>
+    <t>Dosage</t>
   </si>
   <si>
     <t>complex-type</t>
-  </si>
-  <si>
-    <t>Dosage</t>
   </si>
   <si>
     <t>http://hl7.org/fhir/StructureDefinition/Dosage</t>
@@ -1642,7 +1639,7 @@
     <t>ELGA e-Med Medikationsplan</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
+    <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
 Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
 Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).
 TODO: Invariante, dass überall in der List der gleiche Patient enthalten sein muss</t>
@@ -1887,13 +1884,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device)
 </t>
   </si>
   <si>
     <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen.</t>
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>
@@ -2067,7 +2064,7 @@
     <t>ELGA e-Med Durchgeführte Abgabe</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
+    <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
 Sofern eine zugehörige geplante Abgabe vorliegt, können Abweichungen hinsichtlich der Dosierung oder einer möglichen
 Substitution des Medikaments in der durchgeführten Abgabe dokumentiert werden.</t>
   </si>
@@ -2579,6 +2576,10 @@
     <t>MedicationDispense.substitution.responsibleParty</t>
   </si>
   <si>
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole)
+</t>
+  </si>
+  <si>
     <t>Für die Subistution Verantwortlicher.</t>
   </si>
   <si>
@@ -2634,7 +2635,7 @@
     <t>ELGA e-Med Medikation</t>
   </si>
   <si>
-    <t xml:space="preserve">**Beschreibung:** Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
+    <t xml:space="preserve">Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe. Aktuell nur geprüft im Kontext Planeintrag.
 Unterschieden werden folgende Fälle:
 1. Arzneimittel besitzt eine PZN und wird über diese identifiziert, die weiteren Informationen werden durch die Fachanwendung angereichert.
     a. Identifikation nur über PZN: eine Befüllung jener Felder, die über die ASP-Liste angereichert werden können, durch den GDA wird technisch verhindert (Invariante oder eigene Medication Ressource).
@@ -3115,7 +3116,7 @@
     <t>ELGA e-Med Geplante Abgabe</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
+    <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
 Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
@@ -3890,7 +3891,7 @@
     <t>ELGA e-Med Planeintrag</t>
   </si>
   <si>
-    <t>**Beschreibung:** Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
+    <t>Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Er enthält genau ein Arzneimittel und dessen Dosierung.
 Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
   </si>
@@ -4044,7 +4045,7 @@
     <t>ELGA e-Med Substanz</t>
   </si>
   <si>
-    <t>**Beschreibung:** Dokumentation der Substanz eines Inhaltsstoffes eines Arzneimittels, sofern es nicht kodiert vorliegt.</t>
+    <t>Dokumentation der Substanz eines Inhaltsstoffes eines Arzneimittels, sofern es nicht kodiert vorliegt.</t>
   </si>
   <si>
     <t>Substance</t>
@@ -4247,9 +4248,6 @@
   </si>
   <si>
     <t>ELGA e-Med Timing</t>
-  </si>
-  <si>
-    <t>**Beschreibung:** ELGA e-Med Timing</t>
   </si>
   <si>
     <t>Timing</t>
@@ -5201,7 +5199,7 @@
         <v>32</v>
       </c>
       <c r="B63" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
     </row>
     <row r="64">
@@ -5209,7 +5207,7 @@
         <v>34</v>
       </c>
       <c r="B64" t="s" s="2">
-        <v>351</v>
+        <v>350</v>
       </c>
     </row>
     <row r="65">
@@ -5241,7 +5239,7 @@
         <v>2</v>
       </c>
       <c r="B68" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
     </row>
     <row r="69">
@@ -5249,7 +5247,7 @@
         <v>4</v>
       </c>
       <c r="B69" t="s" s="2">
-        <v>517</v>
+        <v>516</v>
       </c>
     </row>
     <row r="70">
@@ -5265,7 +5263,7 @@
         <v>8</v>
       </c>
       <c r="B71" t="s" s="2">
-        <v>518</v>
+        <v>517</v>
       </c>
     </row>
     <row r="72">
@@ -5273,7 +5271,7 @@
         <v>10</v>
       </c>
       <c r="B72" t="s" s="2">
-        <v>519</v>
+        <v>518</v>
       </c>
     </row>
     <row r="73">
@@ -5335,7 +5333,7 @@
         <v>24</v>
       </c>
       <c r="B80" t="s" s="2">
-        <v>520</v>
+        <v>519</v>
       </c>
     </row>
     <row r="81">
@@ -5371,7 +5369,7 @@
         <v>32</v>
       </c>
       <c r="B85" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
     </row>
     <row r="86">
@@ -5379,7 +5377,7 @@
         <v>34</v>
       </c>
       <c r="B86" t="s" s="2">
-        <v>522</v>
+        <v>521</v>
       </c>
     </row>
     <row r="87">
@@ -5411,7 +5409,7 @@
         <v>2</v>
       </c>
       <c r="B90" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
     </row>
     <row r="91">
@@ -5419,7 +5417,7 @@
         <v>4</v>
       </c>
       <c r="B91" t="s" s="2">
-        <v>647</v>
+        <v>646</v>
       </c>
     </row>
     <row r="92">
@@ -5435,7 +5433,7 @@
         <v>8</v>
       </c>
       <c r="B93" t="s" s="2">
-        <v>648</v>
+        <v>647</v>
       </c>
     </row>
     <row r="94">
@@ -5443,7 +5441,7 @@
         <v>10</v>
       </c>
       <c r="B94" t="s" s="2">
-        <v>649</v>
+        <v>648</v>
       </c>
     </row>
     <row r="95">
@@ -5505,7 +5503,7 @@
         <v>24</v>
       </c>
       <c r="B102" t="s" s="2">
-        <v>650</v>
+        <v>649</v>
       </c>
     </row>
     <row r="103">
@@ -5541,7 +5539,7 @@
         <v>32</v>
       </c>
       <c r="B107" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
     </row>
     <row r="108">
@@ -5549,7 +5547,7 @@
         <v>34</v>
       </c>
       <c r="B108" t="s" s="2">
-        <v>652</v>
+        <v>651</v>
       </c>
     </row>
     <row r="109">
@@ -6355,7 +6353,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1334</v>
+        <v>1333</v>
       </c>
     </row>
     <row r="213">
@@ -6391,7 +6389,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1335</v>
+        <v>1334</v>
       </c>
     </row>
     <row r="218">
@@ -6399,7 +6397,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1336</v>
+        <v>1335</v>
       </c>
     </row>
     <row r="219">
@@ -29939,10 +29937,10 @@
         <v>344</v>
       </c>
       <c r="B226" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="C226" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="D226" s="2"/>
       <c r="E226" t="s" s="2">
@@ -29968,10 +29966,10 @@
         <v>78</v>
       </c>
       <c r="M226" t="s" s="2">
+        <v>351</v>
+      </c>
+      <c r="N226" t="s" s="2">
         <v>352</v>
-      </c>
-      <c r="N226" t="s" s="2">
-        <v>353</v>
       </c>
       <c r="O226" s="2"/>
       <c r="P226" s="2"/>
@@ -30022,7 +30020,7 @@
         <v>23</v>
       </c>
       <c r="AG226" t="s" s="2">
-        <v>350</v>
+        <v>348</v>
       </c>
       <c r="AH226" t="s" s="2">
         <v>76</v>
@@ -30042,10 +30040,10 @@
         <v>344</v>
       </c>
       <c r="B227" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="C227" t="s" s="2">
-        <v>354</v>
+        <v>353</v>
       </c>
       <c r="D227" s="2"/>
       <c r="E227" t="s" s="2">
@@ -30145,10 +30143,10 @@
         <v>344</v>
       </c>
       <c r="B228" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="C228" t="s" s="2">
-        <v>355</v>
+        <v>354</v>
       </c>
       <c r="D228" s="2"/>
       <c r="E228" t="s" s="2">
@@ -30218,16 +30216,16 @@
         <v>23</v>
       </c>
       <c r="AC228" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD228" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD228" t="s" s="2">
+      <c r="AE228" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF228" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE228" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF228" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG228" t="s" s="2">
         <v>151</v>
@@ -30250,10 +30248,10 @@
         <v>344</v>
       </c>
       <c r="B229" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="C229" t="s" s="2">
-        <v>359</v>
+        <v>358</v>
       </c>
       <c r="D229" s="2"/>
       <c r="E229" t="s" s="2">
@@ -30357,10 +30355,10 @@
         <v>344</v>
       </c>
       <c r="B230" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="C230" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="D230" s="2"/>
       <c r="E230" t="s" s="2">
@@ -30383,17 +30381,17 @@
         <v>84</v>
       </c>
       <c r="L230" t="s" s="2">
+        <v>360</v>
+      </c>
+      <c r="M230" t="s" s="2">
         <v>361</v>
       </c>
-      <c r="M230" t="s" s="2">
+      <c r="N230" t="s" s="2">
         <v>362</v>
-      </c>
-      <c r="N230" t="s" s="2">
-        <v>363</v>
       </c>
       <c r="O230" s="2"/>
       <c r="P230" t="s" s="2">
-        <v>364</v>
+        <v>363</v>
       </c>
       <c r="Q230" t="s" s="2">
         <v>23</v>
@@ -30442,7 +30440,7 @@
         <v>23</v>
       </c>
       <c r="AG230" t="s" s="2">
-        <v>360</v>
+        <v>359</v>
       </c>
       <c r="AH230" t="s" s="2">
         <v>76</v>
@@ -30462,10 +30460,10 @@
         <v>344</v>
       </c>
       <c r="B231" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="C231" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="D231" s="2"/>
       <c r="E231" t="s" s="2">
@@ -30491,14 +30489,14 @@
         <v>141</v>
       </c>
       <c r="M231" t="s" s="2">
+        <v>365</v>
+      </c>
+      <c r="N231" t="s" s="2">
         <v>366</v>
-      </c>
-      <c r="N231" t="s" s="2">
-        <v>367</v>
       </c>
       <c r="O231" s="2"/>
       <c r="P231" t="s" s="2">
-        <v>368</v>
+        <v>367</v>
       </c>
       <c r="Q231" t="s" s="2">
         <v>23</v>
@@ -30547,7 +30545,7 @@
         <v>23</v>
       </c>
       <c r="AG231" t="s" s="2">
-        <v>365</v>
+        <v>364</v>
       </c>
       <c r="AH231" t="s" s="2">
         <v>76</v>
@@ -30567,10 +30565,10 @@
         <v>344</v>
       </c>
       <c r="B232" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="C232" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="D232" s="2"/>
       <c r="E232" t="s" s="2">
@@ -30593,19 +30591,19 @@
         <v>84</v>
       </c>
       <c r="L232" t="s" s="2">
+        <v>369</v>
+      </c>
+      <c r="M232" t="s" s="2">
         <v>370</v>
       </c>
-      <c r="M232" t="s" s="2">
+      <c r="N232" t="s" s="2">
         <v>371</v>
       </c>
-      <c r="N232" t="s" s="2">
+      <c r="O232" t="s" s="2">
         <v>372</v>
       </c>
-      <c r="O232" t="s" s="2">
+      <c r="P232" t="s" s="2">
         <v>373</v>
-      </c>
-      <c r="P232" t="s" s="2">
-        <v>374</v>
       </c>
       <c r="Q232" t="s" s="2">
         <v>23</v>
@@ -30630,14 +30628,14 @@
         <v>23</v>
       </c>
       <c r="Y232" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z232" t="s" s="2">
         <v>375</v>
       </c>
-      <c r="Z232" t="s" s="2">
+      <c r="AA232" t="s" s="2">
         <v>376</v>
       </c>
-      <c r="AA232" t="s" s="2">
-        <v>377</v>
-      </c>
       <c r="AB232" t="s" s="2">
         <v>23</v>
       </c>
@@ -30654,7 +30652,7 @@
         <v>23</v>
       </c>
       <c r="AG232" t="s" s="2">
-        <v>369</v>
+        <v>368</v>
       </c>
       <c r="AH232" t="s" s="2">
         <v>76</v>
@@ -30674,10 +30672,10 @@
         <v>344</v>
       </c>
       <c r="B233" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="C233" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="D233" s="2"/>
       <c r="E233" t="s" s="2">
@@ -30703,10 +30701,10 @@
         <v>141</v>
       </c>
       <c r="M233" t="s" s="2">
+        <v>378</v>
+      </c>
+      <c r="N233" t="s" s="2">
         <v>379</v>
-      </c>
-      <c r="N233" t="s" s="2">
-        <v>380</v>
       </c>
       <c r="O233" s="2"/>
       <c r="P233" s="2"/>
@@ -30757,7 +30755,7 @@
         <v>23</v>
       </c>
       <c r="AG233" t="s" s="2">
-        <v>378</v>
+        <v>377</v>
       </c>
       <c r="AH233" t="s" s="2">
         <v>76</v>
@@ -30777,10 +30775,10 @@
         <v>344</v>
       </c>
       <c r="B234" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="C234" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="D234" s="2"/>
       <c r="E234" t="s" s="2">
@@ -30803,19 +30801,19 @@
         <v>84</v>
       </c>
       <c r="L234" t="s" s="2">
+        <v>381</v>
+      </c>
+      <c r="M234" t="s" s="2">
         <v>382</v>
       </c>
-      <c r="M234" t="s" s="2">
+      <c r="N234" t="s" s="2">
         <v>383</v>
       </c>
-      <c r="N234" t="s" s="2">
+      <c r="O234" t="s" s="2">
         <v>384</v>
       </c>
-      <c r="O234" t="s" s="2">
+      <c r="P234" t="s" s="2">
         <v>385</v>
-      </c>
-      <c r="P234" t="s" s="2">
-        <v>386</v>
       </c>
       <c r="Q234" t="s" s="2">
         <v>23</v>
@@ -30864,7 +30862,7 @@
         <v>23</v>
       </c>
       <c r="AG234" t="s" s="2">
-        <v>381</v>
+        <v>380</v>
       </c>
       <c r="AH234" t="s" s="2">
         <v>76</v>
@@ -30884,10 +30882,10 @@
         <v>344</v>
       </c>
       <c r="B235" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="C235" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="D235" s="2"/>
       <c r="E235" t="s" s="2">
@@ -30910,16 +30908,16 @@
         <v>84</v>
       </c>
       <c r="L235" t="s" s="2">
+        <v>387</v>
+      </c>
+      <c r="M235" t="s" s="2">
         <v>388</v>
       </c>
-      <c r="M235" t="s" s="2">
+      <c r="N235" t="s" s="2">
         <v>389</v>
       </c>
-      <c r="N235" t="s" s="2">
+      <c r="O235" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O235" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P235" s="2"/>
       <c r="Q235" t="s" s="2">
@@ -30945,19 +30943,19 @@
         <v>23</v>
       </c>
       <c r="Y235" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z235" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA235" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AA235" t="s" s="2">
+      <c r="AB235" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC235" t="s" s="2">
         <v>393</v>
-      </c>
-      <c r="AB235" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC235" t="s" s="2">
-        <v>394</v>
       </c>
       <c r="AD235" s="2"/>
       <c r="AE235" t="s" s="2">
@@ -30967,7 +30965,7 @@
         <v>169</v>
       </c>
       <c r="AG235" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AH235" t="s" s="2">
         <v>76</v>
@@ -30987,13 +30985,13 @@
         <v>344</v>
       </c>
       <c r="B236" t="s" s="2">
+        <v>394</v>
+      </c>
+      <c r="C236" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D236" t="s" s="2">
         <v>395</v>
-      </c>
-      <c r="C236" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="D236" t="s" s="2">
-        <v>396</v>
       </c>
       <c r="E236" t="s" s="2">
         <v>23</v>
@@ -31015,16 +31013,16 @@
         <v>84</v>
       </c>
       <c r="L236" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M236" t="s" s="2">
-        <v>397</v>
+        <v>396</v>
       </c>
       <c r="N236" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O236" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O236" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P236" s="2"/>
       <c r="Q236" t="s" s="2">
@@ -31074,7 +31072,7 @@
         <v>23</v>
       </c>
       <c r="AG236" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AH236" t="s" s="2">
         <v>76</v>
@@ -31094,13 +31092,13 @@
         <v>344</v>
       </c>
       <c r="B237" t="s" s="2">
+        <v>397</v>
+      </c>
+      <c r="C237" t="s" s="2">
+        <v>386</v>
+      </c>
+      <c r="D237" t="s" s="2">
         <v>398</v>
-      </c>
-      <c r="C237" t="s" s="2">
-        <v>387</v>
-      </c>
-      <c r="D237" t="s" s="2">
-        <v>399</v>
       </c>
       <c r="E237" t="s" s="2">
         <v>23</v>
@@ -31122,16 +31120,16 @@
         <v>84</v>
       </c>
       <c r="L237" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M237" t="s" s="2">
-        <v>400</v>
+        <v>399</v>
       </c>
       <c r="N237" t="s" s="2">
+        <v>389</v>
+      </c>
+      <c r="O237" t="s" s="2">
         <v>390</v>
-      </c>
-      <c r="O237" t="s" s="2">
-        <v>391</v>
       </c>
       <c r="P237" s="2"/>
       <c r="Q237" t="s" s="2">
@@ -31157,14 +31155,14 @@
         <v>23</v>
       </c>
       <c r="Y237" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z237" t="s" s="2">
+        <v>391</v>
+      </c>
+      <c r="AA237" t="s" s="2">
         <v>392</v>
       </c>
-      <c r="AA237" t="s" s="2">
-        <v>393</v>
-      </c>
       <c r="AB237" t="s" s="2">
         <v>23</v>
       </c>
@@ -31181,7 +31179,7 @@
         <v>23</v>
       </c>
       <c r="AG237" t="s" s="2">
-        <v>387</v>
+        <v>386</v>
       </c>
       <c r="AH237" t="s" s="2">
         <v>76</v>
@@ -31201,10 +31199,10 @@
         <v>344</v>
       </c>
       <c r="B238" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="C238" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="D238" s="2"/>
       <c r="E238" t="s" s="2">
@@ -31227,19 +31225,19 @@
         <v>84</v>
       </c>
       <c r="L238" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M238" t="s" s="2">
+        <v>401</v>
+      </c>
+      <c r="N238" t="s" s="2">
         <v>402</v>
       </c>
-      <c r="N238" t="s" s="2">
+      <c r="O238" t="s" s="2">
         <v>403</v>
       </c>
-      <c r="O238" t="s" s="2">
+      <c r="P238" t="s" s="2">
         <v>404</v>
-      </c>
-      <c r="P238" t="s" s="2">
-        <v>405</v>
       </c>
       <c r="Q238" t="s" s="2">
         <v>23</v>
@@ -31264,14 +31262,14 @@
         <v>23</v>
       </c>
       <c r="Y238" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z238" t="s" s="2">
+        <v>405</v>
+      </c>
+      <c r="AA238" t="s" s="2">
         <v>406</v>
       </c>
-      <c r="AA238" t="s" s="2">
-        <v>407</v>
-      </c>
       <c r="AB238" t="s" s="2">
         <v>23</v>
       </c>
@@ -31288,7 +31286,7 @@
         <v>23</v>
       </c>
       <c r="AG238" t="s" s="2">
-        <v>401</v>
+        <v>400</v>
       </c>
       <c r="AH238" t="s" s="2">
         <v>76</v>
@@ -31308,10 +31306,10 @@
         <v>344</v>
       </c>
       <c r="B239" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="C239" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="D239" s="2"/>
       <c r="E239" t="s" s="2">
@@ -31334,17 +31332,17 @@
         <v>84</v>
       </c>
       <c r="L239" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M239" t="s" s="2">
+        <v>408</v>
+      </c>
+      <c r="N239" t="s" s="2">
         <v>409</v>
-      </c>
-      <c r="N239" t="s" s="2">
-        <v>410</v>
       </c>
       <c r="O239" s="2"/>
       <c r="P239" t="s" s="2">
-        <v>411</v>
+        <v>410</v>
       </c>
       <c r="Q239" t="s" s="2">
         <v>23</v>
@@ -31373,7 +31371,7 @@
       </c>
       <c r="Z239" s="2"/>
       <c r="AA239" t="s" s="2">
-        <v>412</v>
+        <v>411</v>
       </c>
       <c r="AB239" t="s" s="2">
         <v>23</v>
@@ -31391,7 +31389,7 @@
         <v>23</v>
       </c>
       <c r="AG239" t="s" s="2">
-        <v>408</v>
+        <v>407</v>
       </c>
       <c r="AH239" t="s" s="2">
         <v>76</v>
@@ -31411,10 +31409,10 @@
         <v>344</v>
       </c>
       <c r="B240" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="C240" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="D240" s="2"/>
       <c r="E240" t="s" s="2">
@@ -31437,19 +31435,19 @@
         <v>84</v>
       </c>
       <c r="L240" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M240" t="s" s="2">
+        <v>413</v>
+      </c>
+      <c r="N240" t="s" s="2">
         <v>414</v>
       </c>
-      <c r="N240" t="s" s="2">
+      <c r="O240" t="s" s="2">
         <v>415</v>
       </c>
-      <c r="O240" t="s" s="2">
+      <c r="P240" t="s" s="2">
         <v>416</v>
-      </c>
-      <c r="P240" t="s" s="2">
-        <v>417</v>
       </c>
       <c r="Q240" t="s" s="2">
         <v>23</v>
@@ -31474,14 +31472,14 @@
         <v>23</v>
       </c>
       <c r="Y240" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z240" t="s" s="2">
+        <v>417</v>
+      </c>
+      <c r="AA240" t="s" s="2">
         <v>418</v>
       </c>
-      <c r="AA240" t="s" s="2">
-        <v>419</v>
-      </c>
       <c r="AB240" t="s" s="2">
         <v>23</v>
       </c>
@@ -31498,7 +31496,7 @@
         <v>23</v>
       </c>
       <c r="AG240" t="s" s="2">
-        <v>413</v>
+        <v>412</v>
       </c>
       <c r="AH240" t="s" s="2">
         <v>76</v>
@@ -31518,10 +31516,10 @@
         <v>344</v>
       </c>
       <c r="B241" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="C241" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="D241" s="2"/>
       <c r="E241" t="s" s="2">
@@ -31544,13 +31542,13 @@
         <v>84</v>
       </c>
       <c r="L241" t="s" s="2">
+        <v>420</v>
+      </c>
+      <c r="M241" t="s" s="2">
         <v>421</v>
       </c>
-      <c r="M241" t="s" s="2">
+      <c r="N241" t="s" s="2">
         <v>422</v>
-      </c>
-      <c r="N241" t="s" s="2">
-        <v>423</v>
       </c>
       <c r="O241" s="2"/>
       <c r="P241" s="2"/>
@@ -31601,7 +31599,7 @@
         <v>23</v>
       </c>
       <c r="AG241" t="s" s="2">
-        <v>420</v>
+        <v>419</v>
       </c>
       <c r="AH241" t="s" s="2">
         <v>76</v>
@@ -31621,10 +31619,10 @@
         <v>344</v>
       </c>
       <c r="B242" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="C242" t="s" s="2">
-        <v>424</v>
+        <v>423</v>
       </c>
       <c r="D242" s="2"/>
       <c r="E242" t="s" s="2">
@@ -31724,10 +31722,10 @@
         <v>344</v>
       </c>
       <c r="B243" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="C243" t="s" s="2">
-        <v>425</v>
+        <v>424</v>
       </c>
       <c r="D243" s="2"/>
       <c r="E243" t="s" s="2">
@@ -31797,16 +31795,16 @@
         <v>23</v>
       </c>
       <c r="AC243" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD243" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD243" t="s" s="2">
+      <c r="AE243" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF243" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE243" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF243" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG243" t="s" s="2">
         <v>151</v>
@@ -31829,10 +31827,10 @@
         <v>344</v>
       </c>
       <c r="B244" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="C244" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="D244" s="2"/>
       <c r="E244" t="s" s="2">
@@ -31855,17 +31853,17 @@
         <v>84</v>
       </c>
       <c r="L244" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M244" t="s" s="2">
+        <v>426</v>
+      </c>
+      <c r="N244" t="s" s="2">
         <v>427</v>
-      </c>
-      <c r="N244" t="s" s="2">
-        <v>428</v>
       </c>
       <c r="O244" s="2"/>
       <c r="P244" t="s" s="2">
-        <v>429</v>
+        <v>428</v>
       </c>
       <c r="Q244" t="s" s="2">
         <v>23</v>
@@ -31890,14 +31888,14 @@
         <v>23</v>
       </c>
       <c r="Y244" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z244" t="s" s="2">
+        <v>429</v>
+      </c>
+      <c r="AA244" t="s" s="2">
         <v>430</v>
       </c>
-      <c r="AA244" t="s" s="2">
-        <v>431</v>
-      </c>
       <c r="AB244" t="s" s="2">
         <v>23</v>
       </c>
@@ -31914,7 +31912,7 @@
         <v>23</v>
       </c>
       <c r="AG244" t="s" s="2">
-        <v>426</v>
+        <v>425</v>
       </c>
       <c r="AH244" t="s" s="2">
         <v>76</v>
@@ -31934,10 +31932,10 @@
         <v>344</v>
       </c>
       <c r="B245" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="C245" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="D245" s="2"/>
       <c r="E245" t="s" s="2">
@@ -31960,19 +31958,19 @@
         <v>84</v>
       </c>
       <c r="L245" t="s" s="2">
+        <v>432</v>
+      </c>
+      <c r="M245" t="s" s="2">
         <v>433</v>
       </c>
-      <c r="M245" t="s" s="2">
+      <c r="N245" t="s" s="2">
         <v>434</v>
       </c>
-      <c r="N245" t="s" s="2">
+      <c r="O245" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="O245" t="s" s="2">
+      <c r="P245" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="P245" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="Q245" t="s" s="2">
         <v>23</v>
@@ -32009,7 +32007,7 @@
         <v>23</v>
       </c>
       <c r="AC245" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD245" s="2"/>
       <c r="AE245" t="s" s="2">
@@ -32019,7 +32017,7 @@
         <v>169</v>
       </c>
       <c r="AG245" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH245" t="s" s="2">
         <v>76</v>
@@ -32039,13 +32037,13 @@
         <v>344</v>
       </c>
       <c r="B246" t="s" s="2">
+        <v>437</v>
+      </c>
+      <c r="C246" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="D246" t="s" s="2">
         <v>438</v>
-      </c>
-      <c r="C246" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="D246" t="s" s="2">
-        <v>439</v>
       </c>
       <c r="E246" t="s" s="2">
         <v>23</v>
@@ -32067,19 +32065,19 @@
         <v>84</v>
       </c>
       <c r="L246" t="s" s="2">
+        <v>439</v>
+      </c>
+      <c r="M246" t="s" s="2">
         <v>440</v>
       </c>
-      <c r="M246" t="s" s="2">
-        <v>441</v>
-      </c>
       <c r="N246" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O246" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="O246" t="s" s="2">
+      <c r="P246" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="P246" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="Q246" t="s" s="2">
         <v>23</v>
@@ -32128,7 +32126,7 @@
         <v>23</v>
       </c>
       <c r="AG246" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH246" t="s" s="2">
         <v>76</v>
@@ -32148,13 +32146,13 @@
         <v>344</v>
       </c>
       <c r="B247" t="s" s="2">
+        <v>441</v>
+      </c>
+      <c r="C247" t="s" s="2">
+        <v>431</v>
+      </c>
+      <c r="D247" t="s" s="2">
         <v>442</v>
-      </c>
-      <c r="C247" t="s" s="2">
-        <v>432</v>
-      </c>
-      <c r="D247" t="s" s="2">
-        <v>443</v>
       </c>
       <c r="E247" t="s" s="2">
         <v>23</v>
@@ -32176,19 +32174,19 @@
         <v>84</v>
       </c>
       <c r="L247" t="s" s="2">
+        <v>443</v>
+      </c>
+      <c r="M247" t="s" s="2">
         <v>444</v>
       </c>
-      <c r="M247" t="s" s="2">
-        <v>445</v>
-      </c>
       <c r="N247" t="s" s="2">
+        <v>434</v>
+      </c>
+      <c r="O247" t="s" s="2">
         <v>435</v>
       </c>
-      <c r="O247" t="s" s="2">
+      <c r="P247" t="s" s="2">
         <v>436</v>
-      </c>
-      <c r="P247" t="s" s="2">
-        <v>437</v>
       </c>
       <c r="Q247" t="s" s="2">
         <v>23</v>
@@ -32237,7 +32235,7 @@
         <v>23</v>
       </c>
       <c r="AG247" t="s" s="2">
-        <v>432</v>
+        <v>431</v>
       </c>
       <c r="AH247" t="s" s="2">
         <v>76</v>
@@ -32257,10 +32255,10 @@
         <v>344</v>
       </c>
       <c r="B248" t="s" s="2">
+        <v>445</v>
+      </c>
+      <c r="C248" t="s" s="2">
         <v>446</v>
-      </c>
-      <c r="C248" t="s" s="2">
-        <v>447</v>
       </c>
       <c r="D248" s="2"/>
       <c r="E248" t="s" s="2">
@@ -32360,10 +32358,10 @@
         <v>344</v>
       </c>
       <c r="B249" t="s" s="2">
+        <v>447</v>
+      </c>
+      <c r="C249" t="s" s="2">
         <v>448</v>
-      </c>
-      <c r="C249" t="s" s="2">
-        <v>449</v>
       </c>
       <c r="D249" s="2"/>
       <c r="E249" t="s" s="2">
@@ -32433,16 +32431,16 @@
         <v>23</v>
       </c>
       <c r="AC249" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD249" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD249" t="s" s="2">
+      <c r="AE249" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF249" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE249" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF249" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG249" t="s" s="2">
         <v>151</v>
@@ -32465,10 +32463,10 @@
         <v>344</v>
       </c>
       <c r="B250" t="s" s="2">
+        <v>449</v>
+      </c>
+      <c r="C250" t="s" s="2">
         <v>450</v>
-      </c>
-      <c r="C250" t="s" s="2">
-        <v>451</v>
       </c>
       <c r="D250" s="2"/>
       <c r="E250" t="s" s="2">
@@ -32494,16 +32492,16 @@
         <v>199</v>
       </c>
       <c r="M250" t="s" s="2">
+        <v>451</v>
+      </c>
+      <c r="N250" t="s" s="2">
         <v>452</v>
       </c>
-      <c r="N250" t="s" s="2">
+      <c r="O250" t="s" s="2">
         <v>453</v>
       </c>
-      <c r="O250" t="s" s="2">
+      <c r="P250" t="s" s="2">
         <v>454</v>
-      </c>
-      <c r="P250" t="s" s="2">
-        <v>455</v>
       </c>
       <c r="Q250" t="s" s="2">
         <v>23</v>
@@ -32552,7 +32550,7 @@
         <v>23</v>
       </c>
       <c r="AG250" t="s" s="2">
-        <v>456</v>
+        <v>455</v>
       </c>
       <c r="AH250" t="s" s="2">
         <v>76</v>
@@ -32572,10 +32570,10 @@
         <v>344</v>
       </c>
       <c r="B251" t="s" s="2">
+        <v>456</v>
+      </c>
+      <c r="C251" t="s" s="2">
         <v>457</v>
-      </c>
-      <c r="C251" t="s" s="2">
-        <v>458</v>
       </c>
       <c r="D251" s="2"/>
       <c r="E251" t="s" s="2">
@@ -32601,20 +32599,20 @@
         <v>103</v>
       </c>
       <c r="M251" t="s" s="2">
+        <v>458</v>
+      </c>
+      <c r="N251" t="s" s="2">
         <v>459</v>
-      </c>
-      <c r="N251" t="s" s="2">
-        <v>460</v>
       </c>
       <c r="O251" s="2"/>
       <c r="P251" t="s" s="2">
+        <v>460</v>
+      </c>
+      <c r="Q251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R251" t="s" s="2">
         <v>461</v>
-      </c>
-      <c r="Q251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R251" t="s" s="2">
-        <v>462</v>
       </c>
       <c r="S251" t="s" s="2">
         <v>23</v>
@@ -32638,28 +32636,28 @@
         <v>121</v>
       </c>
       <c r="Z251" t="s" s="2">
+        <v>462</v>
+      </c>
+      <c r="AA251" t="s" s="2">
         <v>463</v>
       </c>
-      <c r="AA251" t="s" s="2">
+      <c r="AB251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF251" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG251" t="s" s="2">
         <v>464</v>
-      </c>
-      <c r="AB251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF251" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG251" t="s" s="2">
-        <v>465</v>
       </c>
       <c r="AH251" t="s" s="2">
         <v>76</v>
@@ -32679,10 +32677,10 @@
         <v>344</v>
       </c>
       <c r="B252" t="s" s="2">
+        <v>465</v>
+      </c>
+      <c r="C252" t="s" s="2">
         <v>466</v>
-      </c>
-      <c r="C252" t="s" s="2">
-        <v>467</v>
       </c>
       <c r="D252" s="2"/>
       <c r="E252" t="s" s="2">
@@ -32708,14 +32706,14 @@
         <v>141</v>
       </c>
       <c r="M252" t="s" s="2">
+        <v>467</v>
+      </c>
+      <c r="N252" t="s" s="2">
         <v>468</v>
-      </c>
-      <c r="N252" t="s" s="2">
-        <v>469</v>
       </c>
       <c r="O252" s="2"/>
       <c r="P252" t="s" s="2">
-        <v>470</v>
+        <v>469</v>
       </c>
       <c r="Q252" t="s" s="2">
         <v>23</v>
@@ -32744,25 +32742,25 @@
       </c>
       <c r="Z252" s="2"/>
       <c r="AA252" t="s" s="2">
+        <v>470</v>
+      </c>
+      <c r="AB252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF252" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG252" t="s" s="2">
         <v>471</v>
-      </c>
-      <c r="AB252" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC252" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD252" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE252" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF252" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG252" t="s" s="2">
-        <v>472</v>
       </c>
       <c r="AH252" t="s" s="2">
         <v>76</v>
@@ -32782,10 +32780,10 @@
         <v>344</v>
       </c>
       <c r="B253" t="s" s="2">
+        <v>472</v>
+      </c>
+      <c r="C253" t="s" s="2">
         <v>473</v>
-      </c>
-      <c r="C253" t="s" s="2">
-        <v>474</v>
       </c>
       <c r="D253" s="2"/>
       <c r="E253" t="s" s="2">
@@ -32811,14 +32809,14 @@
         <v>97</v>
       </c>
       <c r="M253" t="s" s="2">
+        <v>474</v>
+      </c>
+      <c r="N253" t="s" s="2">
         <v>475</v>
-      </c>
-      <c r="N253" t="s" s="2">
-        <v>476</v>
       </c>
       <c r="O253" s="2"/>
       <c r="P253" t="s" s="2">
-        <v>477</v>
+        <v>476</v>
       </c>
       <c r="Q253" t="s" s="2">
         <v>23</v>
@@ -32867,16 +32865,16 @@
         <v>23</v>
       </c>
       <c r="AG253" t="s" s="2">
+        <v>477</v>
+      </c>
+      <c r="AH253" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI253" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ253" t="s" s="2">
         <v>478</v>
-      </c>
-      <c r="AH253" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI253" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ253" t="s" s="2">
-        <v>479</v>
       </c>
       <c r="AK253" t="s" s="2">
         <v>95</v>
@@ -32887,10 +32885,10 @@
         <v>344</v>
       </c>
       <c r="B254" t="s" s="2">
+        <v>479</v>
+      </c>
+      <c r="C254" t="s" s="2">
         <v>480</v>
-      </c>
-      <c r="C254" t="s" s="2">
-        <v>481</v>
       </c>
       <c r="D254" s="2"/>
       <c r="E254" t="s" s="2">
@@ -32916,16 +32914,16 @@
         <v>103</v>
       </c>
       <c r="M254" t="s" s="2">
+        <v>481</v>
+      </c>
+      <c r="N254" t="s" s="2">
         <v>482</v>
       </c>
-      <c r="N254" t="s" s="2">
+      <c r="O254" t="s" s="2">
         <v>483</v>
       </c>
-      <c r="O254" t="s" s="2">
+      <c r="P254" t="s" s="2">
         <v>484</v>
-      </c>
-      <c r="P254" t="s" s="2">
-        <v>485</v>
       </c>
       <c r="Q254" t="s" s="2">
         <v>23</v>
@@ -32974,7 +32972,7 @@
         <v>23</v>
       </c>
       <c r="AG254" t="s" s="2">
-        <v>486</v>
+        <v>485</v>
       </c>
       <c r="AH254" t="s" s="2">
         <v>76</v>
@@ -32994,10 +32992,10 @@
         <v>344</v>
       </c>
       <c r="B255" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="C255" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="D255" s="2"/>
       <c r="E255" t="s" s="2">
@@ -33020,19 +33018,19 @@
         <v>84</v>
       </c>
       <c r="L255" t="s" s="2">
+        <v>487</v>
+      </c>
+      <c r="M255" t="s" s="2">
         <v>488</v>
       </c>
-      <c r="M255" t="s" s="2">
+      <c r="N255" t="s" s="2">
         <v>489</v>
       </c>
-      <c r="N255" t="s" s="2">
+      <c r="O255" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O255" t="s" s="2">
+      <c r="P255" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P255" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="Q255" t="s" s="2">
         <v>23</v>
@@ -33069,7 +33067,7 @@
         <v>23</v>
       </c>
       <c r="AC255" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD255" s="2"/>
       <c r="AE255" t="s" s="2">
@@ -33079,7 +33077,7 @@
         <v>169</v>
       </c>
       <c r="AG255" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH255" t="s" s="2">
         <v>76</v>
@@ -33099,13 +33097,13 @@
         <v>344</v>
       </c>
       <c r="B256" t="s" s="2">
+        <v>492</v>
+      </c>
+      <c r="C256" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D256" t="s" s="2">
         <v>493</v>
-      </c>
-      <c r="C256" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="D256" t="s" s="2">
-        <v>494</v>
       </c>
       <c r="E256" t="s" s="2">
         <v>23</v>
@@ -33127,19 +33125,19 @@
         <v>84</v>
       </c>
       <c r="L256" t="s" s="2">
+        <v>494</v>
+      </c>
+      <c r="M256" t="s" s="2">
         <v>495</v>
       </c>
-      <c r="M256" t="s" s="2">
-        <v>496</v>
-      </c>
       <c r="N256" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O256" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O256" t="s" s="2">
+      <c r="P256" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P256" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="Q256" t="s" s="2">
         <v>23</v>
@@ -33188,7 +33186,7 @@
         <v>23</v>
       </c>
       <c r="AG256" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH256" t="s" s="2">
         <v>76</v>
@@ -33208,13 +33206,13 @@
         <v>344</v>
       </c>
       <c r="B257" t="s" s="2">
+        <v>496</v>
+      </c>
+      <c r="C257" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D257" t="s" s="2">
         <v>497</v>
-      </c>
-      <c r="C257" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="D257" t="s" s="2">
-        <v>498</v>
       </c>
       <c r="E257" t="s" s="2">
         <v>23</v>
@@ -33236,19 +33234,19 @@
         <v>84</v>
       </c>
       <c r="L257" t="s" s="2">
-        <v>440</v>
+        <v>439</v>
       </c>
       <c r="M257" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N257" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O257" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O257" t="s" s="2">
+      <c r="P257" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P257" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="Q257" t="s" s="2">
         <v>23</v>
@@ -33297,7 +33295,7 @@
         <v>23</v>
       </c>
       <c r="AG257" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH257" t="s" s="2">
         <v>76</v>
@@ -33317,13 +33315,13 @@
         <v>344</v>
       </c>
       <c r="B258" t="s" s="2">
+        <v>498</v>
+      </c>
+      <c r="C258" t="s" s="2">
+        <v>486</v>
+      </c>
+      <c r="D258" t="s" s="2">
         <v>499</v>
-      </c>
-      <c r="C258" t="s" s="2">
-        <v>487</v>
-      </c>
-      <c r="D258" t="s" s="2">
-        <v>500</v>
       </c>
       <c r="E258" t="s" s="2">
         <v>23</v>
@@ -33345,19 +33343,19 @@
         <v>84</v>
       </c>
       <c r="L258" t="s" s="2">
-        <v>444</v>
+        <v>443</v>
       </c>
       <c r="M258" t="s" s="2">
-        <v>496</v>
+        <v>495</v>
       </c>
       <c r="N258" t="s" s="2">
+        <v>489</v>
+      </c>
+      <c r="O258" t="s" s="2">
         <v>490</v>
       </c>
-      <c r="O258" t="s" s="2">
+      <c r="P258" t="s" s="2">
         <v>491</v>
-      </c>
-      <c r="P258" t="s" s="2">
-        <v>492</v>
       </c>
       <c r="Q258" t="s" s="2">
         <v>23</v>
@@ -33406,7 +33404,7 @@
         <v>23</v>
       </c>
       <c r="AG258" t="s" s="2">
-        <v>487</v>
+        <v>486</v>
       </c>
       <c r="AH258" t="s" s="2">
         <v>76</v>
@@ -33426,10 +33424,10 @@
         <v>344</v>
       </c>
       <c r="B259" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="C259" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="D259" s="2"/>
       <c r="E259" t="s" s="2">
@@ -33452,19 +33450,19 @@
         <v>84</v>
       </c>
       <c r="L259" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M259" t="s" s="2">
+        <v>501</v>
+      </c>
+      <c r="N259" t="s" s="2">
         <v>502</v>
       </c>
-      <c r="N259" t="s" s="2">
+      <c r="O259" t="s" s="2">
         <v>503</v>
       </c>
-      <c r="O259" t="s" s="2">
+      <c r="P259" t="s" s="2">
         <v>504</v>
-      </c>
-      <c r="P259" t="s" s="2">
-        <v>505</v>
       </c>
       <c r="Q259" t="s" s="2">
         <v>23</v>
@@ -33513,7 +33511,7 @@
         <v>23</v>
       </c>
       <c r="AG259" t="s" s="2">
-        <v>501</v>
+        <v>500</v>
       </c>
       <c r="AH259" t="s" s="2">
         <v>76</v>
@@ -33533,10 +33531,10 @@
         <v>344</v>
       </c>
       <c r="B260" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="C260" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="D260" s="2"/>
       <c r="E260" t="s" s="2">
@@ -33559,19 +33557,19 @@
         <v>84</v>
       </c>
       <c r="L260" t="s" s="2">
+        <v>506</v>
+      </c>
+      <c r="M260" t="s" s="2">
         <v>507</v>
       </c>
-      <c r="M260" t="s" s="2">
+      <c r="N260" t="s" s="2">
         <v>508</v>
       </c>
-      <c r="N260" t="s" s="2">
+      <c r="O260" t="s" s="2">
         <v>509</v>
       </c>
-      <c r="O260" t="s" s="2">
+      <c r="P260" t="s" s="2">
         <v>510</v>
-      </c>
-      <c r="P260" t="s" s="2">
-        <v>511</v>
       </c>
       <c r="Q260" t="s" s="2">
         <v>23</v>
@@ -33620,7 +33618,7 @@
         <v>23</v>
       </c>
       <c r="AG260" t="s" s="2">
-        <v>506</v>
+        <v>505</v>
       </c>
       <c r="AH260" t="s" s="2">
         <v>76</v>
@@ -33640,10 +33638,10 @@
         <v>344</v>
       </c>
       <c r="B261" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="C261" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="D261" s="2"/>
       <c r="E261" t="s" s="2">
@@ -33666,17 +33664,17 @@
         <v>84</v>
       </c>
       <c r="L261" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M261" t="s" s="2">
+        <v>512</v>
+      </c>
+      <c r="N261" t="s" s="2">
         <v>513</v>
-      </c>
-      <c r="N261" t="s" s="2">
-        <v>514</v>
       </c>
       <c r="O261" s="2"/>
       <c r="P261" t="s" s="2">
-        <v>515</v>
+        <v>514</v>
       </c>
       <c r="Q261" t="s" s="2">
         <v>23</v>
@@ -33725,7 +33723,7 @@
         <v>23</v>
       </c>
       <c r="AG261" t="s" s="2">
-        <v>512</v>
+        <v>511</v>
       </c>
       <c r="AH261" t="s" s="2">
         <v>76</v>
@@ -33742,13 +33740,13 @@
     </row>
     <row r="262">
       <c r="A262" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B262" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="C262" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="D262" s="2"/>
       <c r="E262" t="s" s="2">
@@ -33828,7 +33826,7 @@
         <v>23</v>
       </c>
       <c r="AG262" t="s" s="2">
-        <v>521</v>
+        <v>520</v>
       </c>
       <c r="AH262" t="s" s="2">
         <v>76</v>
@@ -33840,18 +33838,18 @@
         <v>23</v>
       </c>
       <c r="AK262" t="s" s="2">
-        <v>523</v>
+        <v>522</v>
       </c>
     </row>
     <row r="263">
       <c r="A263" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B263" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="C263" t="s" s="2">
-        <v>524</v>
+        <v>523</v>
       </c>
       <c r="D263" s="2"/>
       <c r="E263" t="s" s="2">
@@ -33950,13 +33948,13 @@
     </row>
     <row r="264">
       <c r="A264" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B264" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="C264" t="s" s="2">
-        <v>525</v>
+        <v>524</v>
       </c>
       <c r="D264" s="2"/>
       <c r="E264" t="s" s="2">
@@ -34053,13 +34051,13 @@
     </row>
     <row r="265">
       <c r="A265" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B265" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="C265" t="s" s="2">
-        <v>526</v>
+        <v>525</v>
       </c>
       <c r="D265" s="2"/>
       <c r="E265" t="s" s="2">
@@ -34158,13 +34156,13 @@
     </row>
     <row r="266">
       <c r="A266" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B266" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="C266" t="s" s="2">
-        <v>527</v>
+        <v>526</v>
       </c>
       <c r="D266" s="2"/>
       <c r="E266" t="s" s="2">
@@ -34263,17 +34261,17 @@
     </row>
     <row r="267">
       <c r="A267" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B267" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="C267" t="s" s="2">
-        <v>528</v>
+        <v>527</v>
       </c>
       <c r="D267" s="2"/>
       <c r="E267" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F267" s="2"/>
       <c r="G267" t="s" s="2">
@@ -34292,16 +34290,16 @@
         <v>23</v>
       </c>
       <c r="L267" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M267" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M267" t="s" s="2">
+      <c r="N267" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N267" t="s" s="2">
+      <c r="O267" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O267" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P267" s="2"/>
       <c r="Q267" t="s" s="2">
@@ -34351,7 +34349,7 @@
         <v>23</v>
       </c>
       <c r="AG267" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH267" t="s" s="2">
         <v>76</v>
@@ -34368,17 +34366,17 @@
     </row>
     <row r="268">
       <c r="A268" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B268" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="C268" t="s" s="2">
-        <v>535</v>
+        <v>534</v>
       </c>
       <c r="D268" s="2"/>
       <c r="E268" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F268" s="2"/>
       <c r="G268" t="s" s="2">
@@ -34400,13 +34398,13 @@
         <v>182</v>
       </c>
       <c r="M268" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N268" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N268" t="s" s="2">
+      <c r="O268" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O268" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P268" s="2"/>
       <c r="Q268" t="s" s="2">
@@ -34456,7 +34454,7 @@
         <v>23</v>
       </c>
       <c r="AG268" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH268" t="s" s="2">
         <v>76</v>
@@ -34473,13 +34471,13 @@
     </row>
     <row r="269">
       <c r="A269" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B269" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="C269" t="s" s="2">
-        <v>541</v>
+        <v>540</v>
       </c>
       <c r="D269" s="2"/>
       <c r="E269" t="s" s="2">
@@ -34508,7 +34506,7 @@
         <v>148</v>
       </c>
       <c r="N269" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="O269" t="s" s="2">
         <v>150</v>
@@ -34561,7 +34559,7 @@
         <v>23</v>
       </c>
       <c r="AG269" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH269" t="s" s="2">
         <v>76</v>
@@ -34578,13 +34576,13 @@
     </row>
     <row r="270">
       <c r="A270" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B270" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="C270" t="s" s="2">
-        <v>544</v>
+        <v>543</v>
       </c>
       <c r="D270" s="2"/>
       <c r="E270" t="s" s="2">
@@ -34610,10 +34608,10 @@
         <v>147</v>
       </c>
       <c r="M270" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N270" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N270" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O270" t="s" s="2">
         <v>150</v>
@@ -34668,7 +34666,7 @@
         <v>23</v>
       </c>
       <c r="AG270" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH270" t="s" s="2">
         <v>76</v>
@@ -34685,13 +34683,13 @@
     </row>
     <row r="271">
       <c r="A271" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B271" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="C271" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="D271" s="2"/>
       <c r="E271" t="s" s="2">
@@ -34717,10 +34715,10 @@
         <v>112</v>
       </c>
       <c r="M271" t="s" s="2">
+        <v>548</v>
+      </c>
+      <c r="N271" t="s" s="2">
         <v>549</v>
-      </c>
-      <c r="N271" t="s" s="2">
-        <v>550</v>
       </c>
       <c r="O271" s="2"/>
       <c r="P271" s="2"/>
@@ -34771,7 +34769,7 @@
         <v>23</v>
       </c>
       <c r="AG271" t="s" s="2">
-        <v>548</v>
+        <v>547</v>
       </c>
       <c r="AH271" t="s" s="2">
         <v>76</v>
@@ -34788,13 +34786,13 @@
     </row>
     <row r="272">
       <c r="A272" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B272" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="C272" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="D272" s="2"/>
       <c r="E272" t="s" s="2">
@@ -34820,13 +34818,13 @@
         <v>103</v>
       </c>
       <c r="M272" t="s" s="2">
+        <v>551</v>
+      </c>
+      <c r="N272" t="s" s="2">
         <v>552</v>
       </c>
-      <c r="N272" t="s" s="2">
+      <c r="O272" t="s" s="2">
         <v>553</v>
-      </c>
-      <c r="O272" t="s" s="2">
-        <v>554</v>
       </c>
       <c r="P272" s="2"/>
       <c r="Q272" t="s" s="2">
@@ -34855,11 +34853,11 @@
         <v>121</v>
       </c>
       <c r="Z272" t="s" s="2">
+        <v>554</v>
+      </c>
+      <c r="AA272" t="s" s="2">
         <v>555</v>
       </c>
-      <c r="AA272" t="s" s="2">
-        <v>556</v>
-      </c>
       <c r="AB272" t="s" s="2">
         <v>23</v>
       </c>
@@ -34876,7 +34874,7 @@
         <v>23</v>
       </c>
       <c r="AG272" t="s" s="2">
-        <v>551</v>
+        <v>550</v>
       </c>
       <c r="AH272" t="s" s="2">
         <v>83</v>
@@ -34893,13 +34891,13 @@
     </row>
     <row r="273">
       <c r="A273" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B273" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="C273" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="D273" s="2"/>
       <c r="E273" t="s" s="2">
@@ -34925,16 +34923,16 @@
         <v>103</v>
       </c>
       <c r="M273" t="s" s="2">
+        <v>557</v>
+      </c>
+      <c r="N273" t="s" s="2">
         <v>558</v>
       </c>
-      <c r="N273" t="s" s="2">
+      <c r="O273" t="s" s="2">
         <v>559</v>
       </c>
-      <c r="O273" t="s" s="2">
+      <c r="P273" t="s" s="2">
         <v>560</v>
-      </c>
-      <c r="P273" t="s" s="2">
-        <v>561</v>
       </c>
       <c r="Q273" t="s" s="2">
         <v>23</v>
@@ -34962,11 +34960,11 @@
         <v>121</v>
       </c>
       <c r="Z273" t="s" s="2">
+        <v>561</v>
+      </c>
+      <c r="AA273" t="s" s="2">
         <v>562</v>
       </c>
-      <c r="AA273" t="s" s="2">
-        <v>563</v>
-      </c>
       <c r="AB273" t="s" s="2">
         <v>23</v>
       </c>
@@ -34983,7 +34981,7 @@
         <v>23</v>
       </c>
       <c r="AG273" t="s" s="2">
-        <v>557</v>
+        <v>556</v>
       </c>
       <c r="AH273" t="s" s="2">
         <v>83</v>
@@ -35000,13 +34998,13 @@
     </row>
     <row r="274">
       <c r="A274" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B274" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="C274" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="D274" s="2"/>
       <c r="E274" t="s" s="2">
@@ -35032,14 +35030,14 @@
         <v>141</v>
       </c>
       <c r="M274" t="s" s="2">
+        <v>564</v>
+      </c>
+      <c r="N274" t="s" s="2">
         <v>565</v>
-      </c>
-      <c r="N274" t="s" s="2">
-        <v>566</v>
       </c>
       <c r="O274" s="2"/>
       <c r="P274" t="s" s="2">
-        <v>567</v>
+        <v>566</v>
       </c>
       <c r="Q274" t="s" s="2">
         <v>23</v>
@@ -35052,7 +35050,7 @@
         <v>23</v>
       </c>
       <c r="U274" t="s" s="2">
-        <v>568</v>
+        <v>567</v>
       </c>
       <c r="V274" t="s" s="2">
         <v>23</v>
@@ -35088,7 +35086,7 @@
         <v>23</v>
       </c>
       <c r="AG274" t="s" s="2">
-        <v>564</v>
+        <v>563</v>
       </c>
       <c r="AH274" t="s" s="2">
         <v>76</v>
@@ -35105,13 +35103,13 @@
     </row>
     <row r="275">
       <c r="A275" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B275" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="C275" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="D275" s="2"/>
       <c r="E275" t="s" s="2">
@@ -35134,19 +35132,19 @@
         <v>84</v>
       </c>
       <c r="L275" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M275" t="s" s="2">
+        <v>569</v>
+      </c>
+      <c r="N275" t="s" s="2">
         <v>570</v>
       </c>
-      <c r="N275" t="s" s="2">
+      <c r="O275" t="s" s="2">
         <v>571</v>
       </c>
-      <c r="O275" t="s" s="2">
+      <c r="P275" t="s" s="2">
         <v>572</v>
-      </c>
-      <c r="P275" t="s" s="2">
-        <v>573</v>
       </c>
       <c r="Q275" t="s" s="2">
         <v>23</v>
@@ -35156,29 +35154,29 @@
         <v>23</v>
       </c>
       <c r="T275" t="s" s="2">
+        <v>573</v>
+      </c>
+      <c r="U275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X275" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y275" t="s" s="2">
+        <v>374</v>
+      </c>
+      <c r="Z275" t="s" s="2">
         <v>574</v>
       </c>
-      <c r="U275" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V275" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W275" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X275" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y275" t="s" s="2">
-        <v>375</v>
-      </c>
-      <c r="Z275" t="s" s="2">
+      <c r="AA275" t="s" s="2">
         <v>575</v>
       </c>
-      <c r="AA275" t="s" s="2">
-        <v>576</v>
-      </c>
       <c r="AB275" t="s" s="2">
         <v>23</v>
       </c>
@@ -35195,7 +35193,7 @@
         <v>23</v>
       </c>
       <c r="AG275" t="s" s="2">
-        <v>569</v>
+        <v>568</v>
       </c>
       <c r="AH275" t="s" s="2">
         <v>76</v>
@@ -35212,13 +35210,13 @@
     </row>
     <row r="276">
       <c r="A276" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B276" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="C276" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="D276" s="2"/>
       <c r="E276" t="s" s="2">
@@ -35241,19 +35239,19 @@
         <v>84</v>
       </c>
       <c r="L276" t="s" s="2">
+        <v>577</v>
+      </c>
+      <c r="M276" t="s" s="2">
         <v>578</v>
       </c>
-      <c r="M276" t="s" s="2">
+      <c r="N276" t="s" s="2">
         <v>579</v>
       </c>
-      <c r="N276" t="s" s="2">
+      <c r="O276" t="s" s="2">
         <v>580</v>
       </c>
-      <c r="O276" t="s" s="2">
+      <c r="P276" t="s" s="2">
         <v>581</v>
-      </c>
-      <c r="P276" t="s" s="2">
-        <v>582</v>
       </c>
       <c r="Q276" t="s" s="2">
         <v>23</v>
@@ -35302,7 +35300,7 @@
         <v>23</v>
       </c>
       <c r="AG276" t="s" s="2">
-        <v>577</v>
+        <v>576</v>
       </c>
       <c r="AH276" t="s" s="2">
         <v>76</v>
@@ -35319,13 +35317,13 @@
     </row>
     <row r="277">
       <c r="A277" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B277" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="C277" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="D277" s="2"/>
       <c r="E277" t="s" s="2">
@@ -35348,13 +35346,13 @@
         <v>23</v>
       </c>
       <c r="L277" t="s" s="2">
+        <v>583</v>
+      </c>
+      <c r="M277" t="s" s="2">
         <v>584</v>
       </c>
-      <c r="M277" t="s" s="2">
+      <c r="N277" t="s" s="2">
         <v>585</v>
-      </c>
-      <c r="N277" t="s" s="2">
-        <v>586</v>
       </c>
       <c r="O277" s="2"/>
       <c r="P277" s="2"/>
@@ -35405,7 +35403,7 @@
         <v>23</v>
       </c>
       <c r="AG277" t="s" s="2">
-        <v>583</v>
+        <v>582</v>
       </c>
       <c r="AH277" t="s" s="2">
         <v>76</v>
@@ -35422,13 +35420,13 @@
     </row>
     <row r="278">
       <c r="A278" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B278" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="C278" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="D278" s="2"/>
       <c r="E278" t="s" s="2">
@@ -35451,19 +35449,19 @@
         <v>84</v>
       </c>
       <c r="L278" t="s" s="2">
+        <v>587</v>
+      </c>
+      <c r="M278" t="s" s="2">
         <v>588</v>
       </c>
-      <c r="M278" t="s" s="2">
+      <c r="N278" t="s" s="2">
         <v>589</v>
       </c>
-      <c r="N278" t="s" s="2">
+      <c r="O278" t="s" s="2">
         <v>590</v>
       </c>
-      <c r="O278" t="s" s="2">
+      <c r="P278" t="s" s="2">
         <v>591</v>
-      </c>
-      <c r="P278" t="s" s="2">
-        <v>592</v>
       </c>
       <c r="Q278" t="s" s="2">
         <v>23</v>
@@ -35512,7 +35510,7 @@
         <v>23</v>
       </c>
       <c r="AG278" t="s" s="2">
-        <v>587</v>
+        <v>586</v>
       </c>
       <c r="AH278" t="s" s="2">
         <v>76</v>
@@ -35529,17 +35527,17 @@
     </row>
     <row r="279">
       <c r="A279" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B279" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="C279" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="D279" s="2"/>
       <c r="E279" t="s" s="2">
-        <v>594</v>
+        <v>593</v>
       </c>
       <c r="F279" s="2"/>
       <c r="G279" t="s" s="2">
@@ -35558,19 +35556,19 @@
         <v>84</v>
       </c>
       <c r="L279" t="s" s="2">
+        <v>594</v>
+      </c>
+      <c r="M279" t="s" s="2">
         <v>595</v>
       </c>
-      <c r="M279" t="s" s="2">
+      <c r="N279" t="s" s="2">
         <v>596</v>
       </c>
-      <c r="N279" t="s" s="2">
+      <c r="O279" t="s" s="2">
         <v>597</v>
       </c>
-      <c r="O279" t="s" s="2">
+      <c r="P279" t="s" s="2">
         <v>598</v>
-      </c>
-      <c r="P279" t="s" s="2">
-        <v>599</v>
       </c>
       <c r="Q279" t="s" s="2">
         <v>23</v>
@@ -35619,7 +35617,7 @@
         <v>23</v>
       </c>
       <c r="AG279" t="s" s="2">
-        <v>593</v>
+        <v>592</v>
       </c>
       <c r="AH279" t="s" s="2">
         <v>76</v>
@@ -35636,13 +35634,13 @@
     </row>
     <row r="280">
       <c r="A280" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B280" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="C280" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="D280" s="2"/>
       <c r="E280" t="s" s="2">
@@ -35665,19 +35663,19 @@
         <v>23</v>
       </c>
       <c r="L280" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M280" t="s" s="2">
+        <v>600</v>
+      </c>
+      <c r="N280" t="s" s="2">
         <v>601</v>
       </c>
-      <c r="N280" t="s" s="2">
+      <c r="O280" t="s" s="2">
         <v>602</v>
       </c>
-      <c r="O280" t="s" s="2">
+      <c r="P280" t="s" s="2">
         <v>603</v>
-      </c>
-      <c r="P280" t="s" s="2">
-        <v>604</v>
       </c>
       <c r="Q280" t="s" s="2">
         <v>23</v>
@@ -35687,7 +35685,7 @@
         <v>23</v>
       </c>
       <c r="T280" t="s" s="2">
-        <v>605</v>
+        <v>604</v>
       </c>
       <c r="U280" t="s" s="2">
         <v>23</v>
@@ -35706,7 +35704,7 @@
       </c>
       <c r="Z280" s="2"/>
       <c r="AA280" t="s" s="2">
-        <v>606</v>
+        <v>605</v>
       </c>
       <c r="AB280" t="s" s="2">
         <v>23</v>
@@ -35724,7 +35722,7 @@
         <v>23</v>
       </c>
       <c r="AG280" t="s" s="2">
-        <v>600</v>
+        <v>599</v>
       </c>
       <c r="AH280" t="s" s="2">
         <v>76</v>
@@ -35741,13 +35739,13 @@
     </row>
     <row r="281">
       <c r="A281" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B281" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="C281" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="D281" s="2"/>
       <c r="E281" t="s" s="2">
@@ -35770,13 +35768,13 @@
         <v>23</v>
       </c>
       <c r="L281" t="s" s="2">
+        <v>607</v>
+      </c>
+      <c r="M281" t="s" s="2">
         <v>608</v>
       </c>
-      <c r="M281" t="s" s="2">
+      <c r="N281" t="s" s="2">
         <v>609</v>
-      </c>
-      <c r="N281" t="s" s="2">
-        <v>610</v>
       </c>
       <c r="O281" s="2"/>
       <c r="P281" s="2"/>
@@ -35827,7 +35825,7 @@
         <v>23</v>
       </c>
       <c r="AG281" t="s" s="2">
-        <v>607</v>
+        <v>606</v>
       </c>
       <c r="AH281" t="s" s="2">
         <v>76</v>
@@ -35844,13 +35842,13 @@
     </row>
     <row r="282">
       <c r="A282" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B282" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="C282" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="D282" s="2"/>
       <c r="E282" t="s" s="2">
@@ -35876,13 +35874,13 @@
         <v>136</v>
       </c>
       <c r="M282" t="s" s="2">
+        <v>611</v>
+      </c>
+      <c r="N282" t="s" s="2">
         <v>612</v>
       </c>
-      <c r="N282" t="s" s="2">
+      <c r="O282" t="s" s="2">
         <v>613</v>
-      </c>
-      <c r="O282" t="s" s="2">
-        <v>614</v>
       </c>
       <c r="P282" s="2"/>
       <c r="Q282" t="s" s="2">
@@ -35932,7 +35930,7 @@
         <v>23</v>
       </c>
       <c r="AG282" t="s" s="2">
-        <v>611</v>
+        <v>610</v>
       </c>
       <c r="AH282" t="s" s="2">
         <v>76</v>
@@ -35941,7 +35939,7 @@
         <v>77</v>
       </c>
       <c r="AJ282" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AK282" t="s" s="2">
         <v>95</v>
@@ -35949,13 +35947,13 @@
     </row>
     <row r="283">
       <c r="A283" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B283" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="C283" t="s" s="2">
-        <v>616</v>
+        <v>615</v>
       </c>
       <c r="D283" s="2"/>
       <c r="E283" t="s" s="2">
@@ -36052,13 +36050,13 @@
     </row>
     <row r="284">
       <c r="A284" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B284" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="C284" t="s" s="2">
-        <v>617</v>
+        <v>616</v>
       </c>
       <c r="D284" s="2"/>
       <c r="E284" t="s" s="2">
@@ -36157,13 +36155,13 @@
     </row>
     <row r="285">
       <c r="A285" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B285" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="C285" t="s" s="2">
-        <v>618</v>
+        <v>617</v>
       </c>
       <c r="D285" s="2"/>
       <c r="E285" t="s" s="2">
@@ -36264,13 +36262,13 @@
     </row>
     <row r="286">
       <c r="A286" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B286" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="C286" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="D286" s="2"/>
       <c r="E286" t="s" s="2">
@@ -36293,19 +36291,19 @@
         <v>23</v>
       </c>
       <c r="L286" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M286" t="s" s="2">
+        <v>619</v>
+      </c>
+      <c r="N286" t="s" s="2">
         <v>620</v>
       </c>
-      <c r="N286" t="s" s="2">
+      <c r="O286" t="s" s="2">
         <v>621</v>
       </c>
-      <c r="O286" t="s" s="2">
+      <c r="P286" t="s" s="2">
         <v>622</v>
-      </c>
-      <c r="P286" t="s" s="2">
-        <v>623</v>
       </c>
       <c r="Q286" t="s" s="2">
         <v>23</v>
@@ -36334,7 +36332,7 @@
       </c>
       <c r="Z286" s="2"/>
       <c r="AA286" t="s" s="2">
-        <v>624</v>
+        <v>623</v>
       </c>
       <c r="AB286" t="s" s="2">
         <v>23</v>
@@ -36352,7 +36350,7 @@
         <v>23</v>
       </c>
       <c r="AG286" t="s" s="2">
-        <v>619</v>
+        <v>618</v>
       </c>
       <c r="AH286" t="s" s="2">
         <v>76</v>
@@ -36369,13 +36367,13 @@
     </row>
     <row r="287">
       <c r="A287" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B287" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="C287" t="s" s="2">
-        <v>625</v>
+        <v>624</v>
       </c>
       <c r="D287" s="2"/>
       <c r="E287" t="s" s="2">
@@ -36398,79 +36396,79 @@
         <v>23</v>
       </c>
       <c r="L287" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M287" t="s" s="2">
+        <v>625</v>
+      </c>
+      <c r="N287" t="s" s="2">
         <v>626</v>
       </c>
-      <c r="N287" t="s" s="2">
+      <c r="O287" t="s" s="2">
         <v>627</v>
       </c>
-      <c r="O287" t="s" s="2">
+      <c r="P287" t="s" s="2">
         <v>628</v>
       </c>
-      <c r="P287" t="s" s="2">
+      <c r="Q287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R287" t="s" s="2">
         <v>629</v>
       </c>
-      <c r="Q287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R287" t="s" s="2">
+      <c r="S287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF287" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG287" t="s" s="2">
+        <v>624</v>
+      </c>
+      <c r="AH287" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI287" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ287" t="s" s="2">
         <v>630</v>
-      </c>
-      <c r="S287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF287" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG287" t="s" s="2">
-        <v>625</v>
-      </c>
-      <c r="AH287" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI287" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ287" t="s" s="2">
-        <v>631</v>
       </c>
       <c r="AK287" t="s" s="2">
         <v>95</v>
@@ -36478,13 +36476,13 @@
     </row>
     <row r="288">
       <c r="A288" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B288" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="C288" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="D288" s="2"/>
       <c r="E288" t="s" s="2">
@@ -36507,17 +36505,17 @@
         <v>23</v>
       </c>
       <c r="L288" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M288" t="s" s="2">
+        <v>632</v>
+      </c>
+      <c r="N288" t="s" s="2">
         <v>633</v>
-      </c>
-      <c r="N288" t="s" s="2">
-        <v>634</v>
       </c>
       <c r="O288" s="2"/>
       <c r="P288" t="s" s="2">
-        <v>635</v>
+        <v>634</v>
       </c>
       <c r="Q288" t="s" s="2">
         <v>23</v>
@@ -36566,7 +36564,7 @@
         <v>23</v>
       </c>
       <c r="AG288" t="s" s="2">
-        <v>632</v>
+        <v>631</v>
       </c>
       <c r="AH288" t="s" s="2">
         <v>76</v>
@@ -36583,13 +36581,13 @@
     </row>
     <row r="289">
       <c r="A289" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B289" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="C289" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="D289" s="2"/>
       <c r="E289" t="s" s="2">
@@ -36612,13 +36610,13 @@
         <v>23</v>
       </c>
       <c r="L289" t="s" s="2">
+        <v>636</v>
+      </c>
+      <c r="M289" t="s" s="2">
         <v>637</v>
       </c>
-      <c r="M289" t="s" s="2">
+      <c r="N289" t="s" s="2">
         <v>638</v>
-      </c>
-      <c r="N289" t="s" s="2">
-        <v>639</v>
       </c>
       <c r="O289" s="2"/>
       <c r="P289" s="2"/>
@@ -36669,7 +36667,7 @@
         <v>23</v>
       </c>
       <c r="AG289" t="s" s="2">
-        <v>636</v>
+        <v>635</v>
       </c>
       <c r="AH289" t="s" s="2">
         <v>83</v>
@@ -36686,13 +36684,13 @@
     </row>
     <row r="290">
       <c r="A290" t="s" s="2">
-        <v>516</v>
+        <v>515</v>
       </c>
       <c r="B290" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="C290" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="D290" s="2"/>
       <c r="E290" t="s" s="2">
@@ -36715,19 +36713,19 @@
         <v>23</v>
       </c>
       <c r="L290" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M290" t="s" s="2">
+        <v>640</v>
+      </c>
+      <c r="N290" t="s" s="2">
         <v>641</v>
       </c>
-      <c r="N290" t="s" s="2">
+      <c r="O290" t="s" s="2">
         <v>642</v>
       </c>
-      <c r="O290" t="s" s="2">
+      <c r="P290" t="s" s="2">
         <v>643</v>
-      </c>
-      <c r="P290" t="s" s="2">
-        <v>644</v>
       </c>
       <c r="Q290" t="s" s="2">
         <v>23</v>
@@ -36756,7 +36754,7 @@
       </c>
       <c r="Z290" s="2"/>
       <c r="AA290" t="s" s="2">
-        <v>645</v>
+        <v>644</v>
       </c>
       <c r="AB290" t="s" s="2">
         <v>23</v>
@@ -36774,7 +36772,7 @@
         <v>23</v>
       </c>
       <c r="AG290" t="s" s="2">
-        <v>640</v>
+        <v>639</v>
       </c>
       <c r="AH290" t="s" s="2">
         <v>76</v>
@@ -36783,7 +36781,7 @@
         <v>83</v>
       </c>
       <c r="AJ290" t="s" s="2">
-        <v>615</v>
+        <v>614</v>
       </c>
       <c r="AK290" t="s" s="2">
         <v>95</v>
@@ -36791,13 +36789,13 @@
     </row>
     <row r="291">
       <c r="A291" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B291" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="C291" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="D291" s="2"/>
       <c r="E291" t="s" s="2">
@@ -36823,10 +36821,10 @@
         <v>78</v>
       </c>
       <c r="M291" t="s" s="2">
+        <v>652</v>
+      </c>
+      <c r="N291" t="s" s="2">
         <v>653</v>
-      </c>
-      <c r="N291" t="s" s="2">
-        <v>654</v>
       </c>
       <c r="O291" s="2"/>
       <c r="P291" s="2"/>
@@ -36877,7 +36875,7 @@
         <v>23</v>
       </c>
       <c r="AG291" t="s" s="2">
-        <v>651</v>
+        <v>650</v>
       </c>
       <c r="AH291" t="s" s="2">
         <v>76</v>
@@ -36889,18 +36887,18 @@
         <v>23</v>
       </c>
       <c r="AK291" t="s" s="2">
-        <v>655</v>
+        <v>654</v>
       </c>
     </row>
     <row r="292">
       <c r="A292" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B292" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="C292" t="s" s="2">
-        <v>656</v>
+        <v>655</v>
       </c>
       <c r="D292" s="2"/>
       <c r="E292" t="s" s="2">
@@ -36999,13 +36997,13 @@
     </row>
     <row r="293">
       <c r="A293" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B293" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="C293" t="s" s="2">
-        <v>657</v>
+        <v>656</v>
       </c>
       <c r="D293" s="2"/>
       <c r="E293" t="s" s="2">
@@ -37102,13 +37100,13 @@
     </row>
     <row r="294">
       <c r="A294" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B294" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="C294" t="s" s="2">
-        <v>658</v>
+        <v>657</v>
       </c>
       <c r="D294" s="2"/>
       <c r="E294" t="s" s="2">
@@ -37207,13 +37205,13 @@
     </row>
     <row r="295">
       <c r="A295" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B295" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="C295" t="s" s="2">
-        <v>659</v>
+        <v>658</v>
       </c>
       <c r="D295" s="2"/>
       <c r="E295" t="s" s="2">
@@ -37312,17 +37310,17 @@
     </row>
     <row r="296">
       <c r="A296" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B296" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="C296" t="s" s="2">
-        <v>660</v>
+        <v>659</v>
       </c>
       <c r="D296" s="2"/>
       <c r="E296" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F296" s="2"/>
       <c r="G296" t="s" s="2">
@@ -37341,16 +37339,16 @@
         <v>23</v>
       </c>
       <c r="L296" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M296" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M296" t="s" s="2">
+      <c r="N296" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N296" t="s" s="2">
+      <c r="O296" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O296" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P296" s="2"/>
       <c r="Q296" t="s" s="2">
@@ -37400,7 +37398,7 @@
         <v>23</v>
       </c>
       <c r="AG296" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH296" t="s" s="2">
         <v>76</v>
@@ -37417,17 +37415,17 @@
     </row>
     <row r="297">
       <c r="A297" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B297" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="C297" t="s" s="2">
-        <v>661</v>
+        <v>660</v>
       </c>
       <c r="D297" s="2"/>
       <c r="E297" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F297" s="2"/>
       <c r="G297" t="s" s="2">
@@ -37449,13 +37447,13 @@
         <v>182</v>
       </c>
       <c r="M297" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N297" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N297" t="s" s="2">
+      <c r="O297" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O297" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P297" s="2"/>
       <c r="Q297" t="s" s="2">
@@ -37505,7 +37503,7 @@
         <v>23</v>
       </c>
       <c r="AG297" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH297" t="s" s="2">
         <v>76</v>
@@ -37522,13 +37520,13 @@
     </row>
     <row r="298">
       <c r="A298" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B298" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="C298" t="s" s="2">
-        <v>662</v>
+        <v>661</v>
       </c>
       <c r="D298" s="2"/>
       <c r="E298" t="s" s="2">
@@ -37557,7 +37555,7 @@
         <v>148</v>
       </c>
       <c r="N298" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="O298" t="s" s="2">
         <v>150</v>
@@ -37610,7 +37608,7 @@
         <v>23</v>
       </c>
       <c r="AG298" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH298" t="s" s="2">
         <v>76</v>
@@ -37627,13 +37625,13 @@
     </row>
     <row r="299">
       <c r="A299" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B299" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="C299" t="s" s="2">
-        <v>663</v>
+        <v>662</v>
       </c>
       <c r="D299" s="2"/>
       <c r="E299" t="s" s="2">
@@ -37659,10 +37657,10 @@
         <v>147</v>
       </c>
       <c r="M299" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N299" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N299" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O299" t="s" s="2">
         <v>150</v>
@@ -37717,7 +37715,7 @@
         <v>23</v>
       </c>
       <c r="AG299" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH299" t="s" s="2">
         <v>76</v>
@@ -37734,13 +37732,13 @@
     </row>
     <row r="300">
       <c r="A300" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B300" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="C300" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="D300" s="2"/>
       <c r="E300" t="s" s="2">
@@ -37766,13 +37764,13 @@
         <v>112</v>
       </c>
       <c r="M300" t="s" s="2">
+        <v>664</v>
+      </c>
+      <c r="N300" t="s" s="2">
         <v>665</v>
       </c>
-      <c r="N300" t="s" s="2">
+      <c r="O300" t="s" s="2">
         <v>666</v>
-      </c>
-      <c r="O300" t="s" s="2">
-        <v>667</v>
       </c>
       <c r="P300" s="2"/>
       <c r="Q300" t="s" s="2">
@@ -37822,7 +37820,7 @@
         <v>23</v>
       </c>
       <c r="AG300" t="s" s="2">
-        <v>664</v>
+        <v>663</v>
       </c>
       <c r="AH300" t="s" s="2">
         <v>76</v>
@@ -37839,13 +37837,13 @@
     </row>
     <row r="301">
       <c r="A301" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B301" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="C301" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="D301" s="2"/>
       <c r="E301" t="s" s="2">
@@ -37868,13 +37866,13 @@
         <v>23</v>
       </c>
       <c r="L301" t="s" s="2">
+        <v>668</v>
+      </c>
+      <c r="M301" t="s" s="2">
         <v>669</v>
       </c>
-      <c r="M301" t="s" s="2">
+      <c r="N301" t="s" s="2">
         <v>670</v>
-      </c>
-      <c r="N301" t="s" s="2">
-        <v>671</v>
       </c>
       <c r="O301" s="2"/>
       <c r="P301" s="2"/>
@@ -37925,7 +37923,7 @@
         <v>23</v>
       </c>
       <c r="AG301" t="s" s="2">
-        <v>668</v>
+        <v>667</v>
       </c>
       <c r="AH301" t="s" s="2">
         <v>76</v>
@@ -37942,13 +37940,13 @@
     </row>
     <row r="302">
       <c r="A302" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B302" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="C302" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="D302" s="2"/>
       <c r="E302" t="s" s="2">
@@ -37974,13 +37972,13 @@
         <v>103</v>
       </c>
       <c r="M302" t="s" s="2">
+        <v>672</v>
+      </c>
+      <c r="N302" t="s" s="2">
         <v>673</v>
       </c>
-      <c r="N302" t="s" s="2">
-        <v>674</v>
-      </c>
       <c r="O302" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P302" s="2"/>
       <c r="Q302" t="s" s="2">
@@ -38009,11 +38007,11 @@
         <v>121</v>
       </c>
       <c r="Z302" t="s" s="2">
+        <v>674</v>
+      </c>
+      <c r="AA302" t="s" s="2">
         <v>675</v>
       </c>
-      <c r="AA302" t="s" s="2">
-        <v>676</v>
-      </c>
       <c r="AB302" t="s" s="2">
         <v>23</v>
       </c>
@@ -38030,7 +38028,7 @@
         <v>23</v>
       </c>
       <c r="AG302" t="s" s="2">
-        <v>672</v>
+        <v>671</v>
       </c>
       <c r="AH302" t="s" s="2">
         <v>83</v>
@@ -38047,13 +38045,13 @@
     </row>
     <row r="303">
       <c r="A303" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B303" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="C303" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="D303" s="2"/>
       <c r="E303" t="s" s="2">
@@ -38076,13 +38074,13 @@
         <v>23</v>
       </c>
       <c r="L303" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M303" t="s" s="2">
+        <v>677</v>
+      </c>
+      <c r="N303" t="s" s="2">
         <v>678</v>
-      </c>
-      <c r="N303" t="s" s="2">
-        <v>679</v>
       </c>
       <c r="O303" s="2"/>
       <c r="P303" s="2"/>
@@ -38109,19 +38107,19 @@
         <v>23</v>
       </c>
       <c r="Y303" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z303" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AA303" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AA303" t="s" s="2">
-        <v>681</v>
-      </c>
       <c r="AB303" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC303" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD303" s="2"/>
       <c r="AE303" t="s" s="2">
@@ -38131,7 +38129,7 @@
         <v>169</v>
       </c>
       <c r="AG303" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AH303" t="s" s="2">
         <v>76</v>
@@ -38148,16 +38146,16 @@
     </row>
     <row r="304">
       <c r="A304" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B304" t="s" s="2">
+        <v>681</v>
+      </c>
+      <c r="C304" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="D304" t="s" s="2">
         <v>682</v>
-      </c>
-      <c r="C304" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="D304" t="s" s="2">
-        <v>683</v>
       </c>
       <c r="E304" t="s" s="2">
         <v>23</v>
@@ -38179,13 +38177,13 @@
         <v>23</v>
       </c>
       <c r="L304" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M304" t="s" s="2">
-        <v>684</v>
+        <v>683</v>
       </c>
       <c r="N304" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="O304" s="2"/>
       <c r="P304" s="2"/>
@@ -38212,14 +38210,14 @@
         <v>23</v>
       </c>
       <c r="Y304" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z304" t="s" s="2">
+        <v>679</v>
+      </c>
+      <c r="AA304" t="s" s="2">
         <v>680</v>
       </c>
-      <c r="AA304" t="s" s="2">
-        <v>681</v>
-      </c>
       <c r="AB304" t="s" s="2">
         <v>23</v>
       </c>
@@ -38236,7 +38234,7 @@
         <v>23</v>
       </c>
       <c r="AG304" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AH304" t="s" s="2">
         <v>76</v>
@@ -38253,16 +38251,16 @@
     </row>
     <row r="305">
       <c r="A305" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B305" t="s" s="2">
+        <v>684</v>
+      </c>
+      <c r="C305" t="s" s="2">
+        <v>676</v>
+      </c>
+      <c r="D305" t="s" s="2">
         <v>685</v>
-      </c>
-      <c r="C305" t="s" s="2">
-        <v>677</v>
-      </c>
-      <c r="D305" t="s" s="2">
-        <v>686</v>
       </c>
       <c r="E305" t="s" s="2">
         <v>23</v>
@@ -38284,13 +38282,13 @@
         <v>23</v>
       </c>
       <c r="L305" t="s" s="2">
+        <v>686</v>
+      </c>
+      <c r="M305" t="s" s="2">
         <v>687</v>
       </c>
-      <c r="M305" t="s" s="2">
-        <v>688</v>
-      </c>
       <c r="N305" t="s" s="2">
-        <v>679</v>
+        <v>678</v>
       </c>
       <c r="O305" s="2"/>
       <c r="P305" s="2"/>
@@ -38341,7 +38339,7 @@
         <v>23</v>
       </c>
       <c r="AG305" t="s" s="2">
-        <v>677</v>
+        <v>676</v>
       </c>
       <c r="AH305" t="s" s="2">
         <v>76</v>
@@ -38358,13 +38356,13 @@
     </row>
     <row r="306">
       <c r="A306" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B306" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="C306" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="D306" s="2"/>
       <c r="E306" t="s" s="2">
@@ -38387,16 +38385,16 @@
         <v>23</v>
       </c>
       <c r="L306" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M306" t="s" s="2">
+        <v>689</v>
+      </c>
+      <c r="N306" t="s" s="2">
         <v>690</v>
       </c>
-      <c r="N306" t="s" s="2">
+      <c r="O306" t="s" s="2">
         <v>691</v>
-      </c>
-      <c r="O306" t="s" s="2">
-        <v>692</v>
       </c>
       <c r="P306" s="2"/>
       <c r="Q306" t="s" s="2">
@@ -38425,11 +38423,11 @@
         <v>107</v>
       </c>
       <c r="Z306" t="s" s="2">
+        <v>692</v>
+      </c>
+      <c r="AA306" t="s" s="2">
         <v>693</v>
       </c>
-      <c r="AA306" t="s" s="2">
-        <v>694</v>
-      </c>
       <c r="AB306" t="s" s="2">
         <v>23</v>
       </c>
@@ -38446,7 +38444,7 @@
         <v>23</v>
       </c>
       <c r="AG306" t="s" s="2">
-        <v>689</v>
+        <v>688</v>
       </c>
       <c r="AH306" t="s" s="2">
         <v>76</v>
@@ -38463,13 +38461,13 @@
     </row>
     <row r="307">
       <c r="A307" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B307" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="C307" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="D307" s="2"/>
       <c r="E307" t="s" s="2">
@@ -38492,16 +38490,16 @@
         <v>84</v>
       </c>
       <c r="L307" t="s" s="2">
+        <v>695</v>
+      </c>
+      <c r="M307" t="s" s="2">
         <v>696</v>
       </c>
-      <c r="M307" t="s" s="2">
+      <c r="N307" t="s" s="2">
         <v>697</v>
       </c>
-      <c r="N307" t="s" s="2">
+      <c r="O307" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="O307" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="P307" s="2"/>
       <c r="Q307" t="s" s="2">
@@ -38527,29 +38525,29 @@
         <v>23</v>
       </c>
       <c r="Y307" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z307" t="s" s="2">
+        <v>699</v>
+      </c>
+      <c r="AA307" t="s" s="2">
         <v>700</v>
       </c>
-      <c r="AA307" t="s" s="2">
-        <v>701</v>
-      </c>
       <c r="AB307" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC307" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD307" s="2"/>
       <c r="AE307" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF307" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG307" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH307" t="s" s="2">
         <v>83</v>
@@ -38566,16 +38564,16 @@
     </row>
     <row r="308">
       <c r="A308" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B308" t="s" s="2">
+        <v>701</v>
+      </c>
+      <c r="C308" t="s" s="2">
+        <v>694</v>
+      </c>
+      <c r="D308" t="s" s="2">
         <v>702</v>
-      </c>
-      <c r="C308" t="s" s="2">
-        <v>695</v>
-      </c>
-      <c r="D308" t="s" s="2">
-        <v>703</v>
       </c>
       <c r="E308" t="s" s="2">
         <v>23</v>
@@ -38597,16 +38595,16 @@
         <v>84</v>
       </c>
       <c r="L308" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M308" t="s" s="2">
-        <v>704</v>
+        <v>703</v>
       </c>
       <c r="N308" t="s" s="2">
+        <v>697</v>
+      </c>
+      <c r="O308" t="s" s="2">
         <v>698</v>
-      </c>
-      <c r="O308" t="s" s="2">
-        <v>699</v>
       </c>
       <c r="P308" s="2"/>
       <c r="Q308" t="s" s="2">
@@ -38636,7 +38634,7 @@
       </c>
       <c r="Z308" s="2"/>
       <c r="AA308" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AB308" t="s" s="2">
         <v>23</v>
@@ -38654,7 +38652,7 @@
         <v>23</v>
       </c>
       <c r="AG308" t="s" s="2">
-        <v>695</v>
+        <v>694</v>
       </c>
       <c r="AH308" t="s" s="2">
         <v>83</v>
@@ -38671,13 +38669,13 @@
     </row>
     <row r="309">
       <c r="A309" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B309" t="s" s="2">
+        <v>705</v>
+      </c>
+      <c r="C309" t="s" s="2">
         <v>706</v>
-      </c>
-      <c r="C309" t="s" s="2">
-        <v>707</v>
       </c>
       <c r="D309" s="2"/>
       <c r="E309" t="s" s="2">
@@ -38774,13 +38772,13 @@
     </row>
     <row r="310">
       <c r="A310" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B310" t="s" s="2">
+        <v>707</v>
+      </c>
+      <c r="C310" t="s" s="2">
         <v>708</v>
-      </c>
-      <c r="C310" t="s" s="2">
-        <v>709</v>
       </c>
       <c r="D310" s="2"/>
       <c r="E310" t="s" s="2">
@@ -38850,16 +38848,16 @@
         <v>23</v>
       </c>
       <c r="AC310" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD310" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD310" t="s" s="2">
+      <c r="AE310" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF310" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE310" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF310" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG310" t="s" s="2">
         <v>151</v>
@@ -38879,13 +38877,13 @@
     </row>
     <row r="311">
       <c r="A311" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B311" t="s" s="2">
+        <v>709</v>
+      </c>
+      <c r="C311" t="s" s="2">
         <v>710</v>
-      </c>
-      <c r="C311" t="s" s="2">
-        <v>711</v>
       </c>
       <c r="D311" s="2"/>
       <c r="E311" t="s" s="2">
@@ -38908,19 +38906,19 @@
         <v>84</v>
       </c>
       <c r="L311" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M311" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M311" t="s" s="2">
+      <c r="N311" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="N311" t="s" s="2">
+      <c r="O311" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="O311" t="s" s="2">
+      <c r="P311" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="P311" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="Q311" t="s" s="2">
         <v>23</v>
@@ -38969,7 +38967,7 @@
         <v>23</v>
       </c>
       <c r="AG311" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AH311" t="s" s="2">
         <v>76</v>
@@ -38986,13 +38984,13 @@
     </row>
     <row r="312">
       <c r="A312" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B312" t="s" s="2">
+        <v>717</v>
+      </c>
+      <c r="C312" t="s" s="2">
         <v>718</v>
-      </c>
-      <c r="C312" t="s" s="2">
-        <v>719</v>
       </c>
       <c r="D312" s="2"/>
       <c r="E312" t="s" s="2">
@@ -39018,16 +39016,16 @@
         <v>141</v>
       </c>
       <c r="M312" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N312" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="N312" t="s" s="2">
+      <c r="O312" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="O312" t="s" s="2">
+      <c r="P312" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="P312" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="Q312" t="s" s="2">
         <v>23</v>
@@ -39076,7 +39074,7 @@
         <v>23</v>
       </c>
       <c r="AG312" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AH312" t="s" s="2">
         <v>76</v>
@@ -39093,13 +39091,13 @@
     </row>
     <row r="313">
       <c r="A313" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B313" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="C313" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="D313" s="2"/>
       <c r="E313" t="s" s="2">
@@ -39122,16 +39120,16 @@
         <v>84</v>
       </c>
       <c r="L313" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M313" t="s" s="2">
+        <v>725</v>
+      </c>
+      <c r="N313" t="s" s="2">
         <v>726</v>
       </c>
-      <c r="N313" t="s" s="2">
+      <c r="O313" t="s" s="2">
         <v>727</v>
-      </c>
-      <c r="O313" t="s" s="2">
-        <v>728</v>
       </c>
       <c r="P313" s="2"/>
       <c r="Q313" t="s" s="2">
@@ -39181,7 +39179,7 @@
         <v>23</v>
       </c>
       <c r="AG313" t="s" s="2">
-        <v>725</v>
+        <v>724</v>
       </c>
       <c r="AH313" t="s" s="2">
         <v>76</v>
@@ -39198,13 +39196,13 @@
     </row>
     <row r="314">
       <c r="A314" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B314" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="C314" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="D314" s="2"/>
       <c r="E314" t="s" s="2">
@@ -39227,13 +39225,13 @@
         <v>23</v>
       </c>
       <c r="L314" t="s" s="2">
+        <v>729</v>
+      </c>
+      <c r="M314" t="s" s="2">
         <v>730</v>
       </c>
-      <c r="M314" t="s" s="2">
+      <c r="N314" t="s" s="2">
         <v>731</v>
-      </c>
-      <c r="N314" t="s" s="2">
-        <v>732</v>
       </c>
       <c r="O314" s="2"/>
       <c r="P314" s="2"/>
@@ -39284,7 +39282,7 @@
         <v>23</v>
       </c>
       <c r="AG314" t="s" s="2">
-        <v>729</v>
+        <v>728</v>
       </c>
       <c r="AH314" t="s" s="2">
         <v>76</v>
@@ -39301,13 +39299,13 @@
     </row>
     <row r="315">
       <c r="A315" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B315" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="C315" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="D315" s="2"/>
       <c r="E315" t="s" s="2">
@@ -39330,13 +39328,13 @@
         <v>23</v>
       </c>
       <c r="L315" t="s" s="2">
+        <v>733</v>
+      </c>
+      <c r="M315" t="s" s="2">
         <v>734</v>
       </c>
-      <c r="M315" t="s" s="2">
+      <c r="N315" t="s" s="2">
         <v>735</v>
-      </c>
-      <c r="N315" t="s" s="2">
-        <v>736</v>
       </c>
       <c r="O315" s="2"/>
       <c r="P315" s="2"/>
@@ -39387,7 +39385,7 @@
         <v>23</v>
       </c>
       <c r="AG315" t="s" s="2">
-        <v>733</v>
+        <v>732</v>
       </c>
       <c r="AH315" t="s" s="2">
         <v>76</v>
@@ -39404,13 +39402,13 @@
     </row>
     <row r="316">
       <c r="A316" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B316" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="C316" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="D316" s="2"/>
       <c r="E316" t="s" s="2">
@@ -39436,10 +39434,10 @@
         <v>136</v>
       </c>
       <c r="M316" t="s" s="2">
+        <v>737</v>
+      </c>
+      <c r="N316" t="s" s="2">
         <v>738</v>
-      </c>
-      <c r="N316" t="s" s="2">
-        <v>739</v>
       </c>
       <c r="O316" s="2"/>
       <c r="P316" s="2"/>
@@ -39490,7 +39488,7 @@
         <v>23</v>
       </c>
       <c r="AG316" t="s" s="2">
-        <v>737</v>
+        <v>736</v>
       </c>
       <c r="AH316" t="s" s="2">
         <v>76</v>
@@ -39507,13 +39505,13 @@
     </row>
     <row r="317">
       <c r="A317" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B317" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="C317" t="s" s="2">
-        <v>740</v>
+        <v>739</v>
       </c>
       <c r="D317" s="2"/>
       <c r="E317" t="s" s="2">
@@ -39610,13 +39608,13 @@
     </row>
     <row r="318">
       <c r="A318" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B318" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="C318" t="s" s="2">
-        <v>741</v>
+        <v>740</v>
       </c>
       <c r="D318" s="2"/>
       <c r="E318" t="s" s="2">
@@ -39715,13 +39713,13 @@
     </row>
     <row r="319">
       <c r="A319" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B319" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="C319" t="s" s="2">
-        <v>742</v>
+        <v>741</v>
       </c>
       <c r="D319" s="2"/>
       <c r="E319" t="s" s="2">
@@ -39822,13 +39820,13 @@
     </row>
     <row r="320">
       <c r="A320" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B320" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="C320" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="D320" s="2"/>
       <c r="E320" t="s" s="2">
@@ -39851,17 +39849,17 @@
         <v>23</v>
       </c>
       <c r="L320" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M320" t="s" s="2">
+        <v>743</v>
+      </c>
+      <c r="N320" t="s" s="2">
         <v>744</v>
-      </c>
-      <c r="N320" t="s" s="2">
-        <v>745</v>
       </c>
       <c r="O320" s="2"/>
       <c r="P320" t="s" s="2">
-        <v>746</v>
+        <v>745</v>
       </c>
       <c r="Q320" t="s" s="2">
         <v>23</v>
@@ -39886,14 +39884,14 @@
         <v>23</v>
       </c>
       <c r="Y320" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z320" t="s" s="2">
+        <v>746</v>
+      </c>
+      <c r="AA320" t="s" s="2">
         <v>747</v>
       </c>
-      <c r="AA320" t="s" s="2">
-        <v>748</v>
-      </c>
       <c r="AB320" t="s" s="2">
         <v>23</v>
       </c>
@@ -39910,7 +39908,7 @@
         <v>23</v>
       </c>
       <c r="AG320" t="s" s="2">
-        <v>743</v>
+        <v>742</v>
       </c>
       <c r="AH320" t="s" s="2">
         <v>76</v>
@@ -39927,13 +39925,13 @@
     </row>
     <row r="321">
       <c r="A321" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B321" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="C321" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="D321" s="2"/>
       <c r="E321" t="s" s="2">
@@ -39956,13 +39954,13 @@
         <v>23</v>
       </c>
       <c r="L321" t="s" s="2">
+        <v>749</v>
+      </c>
+      <c r="M321" t="s" s="2">
         <v>750</v>
       </c>
-      <c r="M321" t="s" s="2">
+      <c r="N321" t="s" s="2">
         <v>751</v>
-      </c>
-      <c r="N321" t="s" s="2">
-        <v>752</v>
       </c>
       <c r="O321" s="2"/>
       <c r="P321" s="2"/>
@@ -40013,7 +40011,7 @@
         <v>23</v>
       </c>
       <c r="AG321" t="s" s="2">
-        <v>749</v>
+        <v>748</v>
       </c>
       <c r="AH321" t="s" s="2">
         <v>83</v>
@@ -40030,13 +40028,13 @@
     </row>
     <row r="322">
       <c r="A322" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B322" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="C322" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="D322" s="2"/>
       <c r="E322" t="s" s="2">
@@ -40059,13 +40057,13 @@
         <v>23</v>
       </c>
       <c r="L322" t="s" s="2">
+        <v>753</v>
+      </c>
+      <c r="M322" t="s" s="2">
         <v>754</v>
       </c>
-      <c r="M322" t="s" s="2">
+      <c r="N322" t="s" s="2">
         <v>755</v>
-      </c>
-      <c r="N322" t="s" s="2">
-        <v>756</v>
       </c>
       <c r="O322" s="2"/>
       <c r="P322" s="2"/>
@@ -40116,7 +40114,7 @@
         <v>23</v>
       </c>
       <c r="AG322" t="s" s="2">
-        <v>753</v>
+        <v>752</v>
       </c>
       <c r="AH322" t="s" s="2">
         <v>76</v>
@@ -40133,13 +40131,13 @@
     </row>
     <row r="323">
       <c r="A323" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B323" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="C323" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="D323" s="2"/>
       <c r="E323" t="s" s="2">
@@ -40162,16 +40160,16 @@
         <v>23</v>
       </c>
       <c r="L323" t="s" s="2">
+        <v>757</v>
+      </c>
+      <c r="M323" t="s" s="2">
         <v>758</v>
       </c>
-      <c r="M323" t="s" s="2">
+      <c r="N323" t="s" s="2">
         <v>759</v>
       </c>
-      <c r="N323" t="s" s="2">
+      <c r="O323" t="s" s="2">
         <v>760</v>
-      </c>
-      <c r="O323" t="s" s="2">
-        <v>761</v>
       </c>
       <c r="P323" s="2"/>
       <c r="Q323" t="s" s="2">
@@ -40221,7 +40219,7 @@
         <v>23</v>
       </c>
       <c r="AG323" t="s" s="2">
-        <v>757</v>
+        <v>756</v>
       </c>
       <c r="AH323" t="s" s="2">
         <v>76</v>
@@ -40238,13 +40236,13 @@
     </row>
     <row r="324">
       <c r="A324" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B324" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="C324" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="D324" s="2"/>
       <c r="E324" t="s" s="2">
@@ -40267,13 +40265,13 @@
         <v>23</v>
       </c>
       <c r="L324" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M324" t="s" s="2">
+        <v>762</v>
+      </c>
+      <c r="N324" t="s" s="2">
         <v>763</v>
-      </c>
-      <c r="N324" t="s" s="2">
-        <v>764</v>
       </c>
       <c r="O324" s="2"/>
       <c r="P324" s="2"/>
@@ -40300,14 +40298,14 @@
         <v>23</v>
       </c>
       <c r="Y324" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z324" t="s" s="2">
+        <v>763</v>
+      </c>
+      <c r="AA324" t="s" s="2">
         <v>764</v>
       </c>
-      <c r="AA324" t="s" s="2">
-        <v>765</v>
-      </c>
       <c r="AB324" t="s" s="2">
         <v>23</v>
       </c>
@@ -40324,7 +40322,7 @@
         <v>23</v>
       </c>
       <c r="AG324" t="s" s="2">
-        <v>762</v>
+        <v>761</v>
       </c>
       <c r="AH324" t="s" s="2">
         <v>76</v>
@@ -40341,13 +40339,13 @@
     </row>
     <row r="325">
       <c r="A325" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B325" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="C325" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="D325" s="2"/>
       <c r="E325" t="s" s="2">
@@ -40370,13 +40368,13 @@
         <v>23</v>
       </c>
       <c r="L325" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M325" t="s" s="2">
+        <v>766</v>
+      </c>
+      <c r="N325" t="s" s="2">
         <v>767</v>
-      </c>
-      <c r="N325" t="s" s="2">
-        <v>768</v>
       </c>
       <c r="O325" s="2"/>
       <c r="P325" s="2"/>
@@ -40427,7 +40425,7 @@
         <v>23</v>
       </c>
       <c r="AG325" t="s" s="2">
-        <v>766</v>
+        <v>765</v>
       </c>
       <c r="AH325" t="s" s="2">
         <v>76</v>
@@ -40444,13 +40442,13 @@
     </row>
     <row r="326">
       <c r="A326" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B326" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="C326" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="D326" s="2"/>
       <c r="E326" t="s" s="2">
@@ -40473,13 +40471,13 @@
         <v>23</v>
       </c>
       <c r="L326" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M326" t="s" s="2">
+        <v>769</v>
+      </c>
+      <c r="N326" t="s" s="2">
         <v>770</v>
-      </c>
-      <c r="N326" t="s" s="2">
-        <v>771</v>
       </c>
       <c r="O326" s="2"/>
       <c r="P326" s="2"/>
@@ -40530,7 +40528,7 @@
         <v>23</v>
       </c>
       <c r="AG326" t="s" s="2">
-        <v>769</v>
+        <v>768</v>
       </c>
       <c r="AH326" t="s" s="2">
         <v>76</v>
@@ -40547,13 +40545,13 @@
     </row>
     <row r="327">
       <c r="A327" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B327" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="C327" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="D327" s="2"/>
       <c r="E327" t="s" s="2">
@@ -40576,13 +40574,13 @@
         <v>84</v>
       </c>
       <c r="L327" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M327" t="s" s="2">
+        <v>772</v>
+      </c>
+      <c r="N327" t="s" s="2">
         <v>773</v>
-      </c>
-      <c r="N327" t="s" s="2">
-        <v>774</v>
       </c>
       <c r="O327" s="2"/>
       <c r="P327" s="2"/>
@@ -40633,7 +40631,7 @@
         <v>23</v>
       </c>
       <c r="AG327" t="s" s="2">
-        <v>772</v>
+        <v>771</v>
       </c>
       <c r="AH327" t="s" s="2">
         <v>76</v>
@@ -40650,13 +40648,13 @@
     </row>
     <row r="328">
       <c r="A328" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B328" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="C328" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="D328" s="2"/>
       <c r="E328" t="s" s="2">
@@ -40679,13 +40677,13 @@
         <v>23</v>
       </c>
       <c r="L328" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M328" t="s" s="2">
+        <v>775</v>
+      </c>
+      <c r="N328" t="s" s="2">
         <v>776</v>
-      </c>
-      <c r="N328" t="s" s="2">
-        <v>777</v>
       </c>
       <c r="O328" s="2"/>
       <c r="P328" s="2"/>
@@ -40736,7 +40734,7 @@
         <v>23</v>
       </c>
       <c r="AG328" t="s" s="2">
-        <v>775</v>
+        <v>774</v>
       </c>
       <c r="AH328" t="s" s="2">
         <v>76</v>
@@ -40753,13 +40751,13 @@
     </row>
     <row r="329">
       <c r="A329" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B329" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="C329" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="D329" s="2"/>
       <c r="E329" t="s" s="2">
@@ -40782,13 +40780,13 @@
         <v>23</v>
       </c>
       <c r="L329" t="s" s="2">
-        <v>754</v>
+        <v>753</v>
       </c>
       <c r="M329" t="s" s="2">
+        <v>778</v>
+      </c>
+      <c r="N329" t="s" s="2">
         <v>779</v>
-      </c>
-      <c r="N329" t="s" s="2">
-        <v>780</v>
       </c>
       <c r="O329" s="2"/>
       <c r="P329" s="2"/>
@@ -40839,7 +40837,7 @@
         <v>23</v>
       </c>
       <c r="AG329" t="s" s="2">
-        <v>778</v>
+        <v>777</v>
       </c>
       <c r="AH329" t="s" s="2">
         <v>76</v>
@@ -40856,13 +40854,13 @@
     </row>
     <row r="330">
       <c r="A330" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B330" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="C330" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="D330" s="2"/>
       <c r="E330" t="s" s="2">
@@ -40885,13 +40883,13 @@
         <v>23</v>
       </c>
       <c r="L330" t="s" s="2">
+        <v>781</v>
+      </c>
+      <c r="M330" t="s" s="2">
         <v>782</v>
       </c>
-      <c r="M330" t="s" s="2">
+      <c r="N330" t="s" s="2">
         <v>783</v>
-      </c>
-      <c r="N330" t="s" s="2">
-        <v>784</v>
       </c>
       <c r="O330" s="2"/>
       <c r="P330" s="2"/>
@@ -40942,7 +40940,7 @@
         <v>23</v>
       </c>
       <c r="AG330" t="s" s="2">
-        <v>781</v>
+        <v>780</v>
       </c>
       <c r="AH330" t="s" s="2">
         <v>76</v>
@@ -40959,13 +40957,13 @@
     </row>
     <row r="331">
       <c r="A331" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B331" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="C331" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="D331" s="2"/>
       <c r="E331" t="s" s="2">
@@ -40988,13 +40986,13 @@
         <v>23</v>
       </c>
       <c r="L331" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M331" t="s" s="2">
+        <v>785</v>
+      </c>
+      <c r="N331" t="s" s="2">
         <v>786</v>
-      </c>
-      <c r="N331" t="s" s="2">
-        <v>787</v>
       </c>
       <c r="O331" s="2"/>
       <c r="P331" s="2"/>
@@ -41045,7 +41043,7 @@
         <v>23</v>
       </c>
       <c r="AG331" t="s" s="2">
-        <v>785</v>
+        <v>784</v>
       </c>
       <c r="AH331" t="s" s="2">
         <v>76</v>
@@ -41062,13 +41060,13 @@
     </row>
     <row r="332">
       <c r="A332" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B332" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="C332" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="D332" s="2"/>
       <c r="E332" t="s" s="2">
@@ -41091,16 +41089,16 @@
         <v>23</v>
       </c>
       <c r="L332" t="s" s="2">
+        <v>788</v>
+      </c>
+      <c r="M332" t="s" s="2">
         <v>789</v>
       </c>
-      <c r="M332" t="s" s="2">
+      <c r="N332" t="s" s="2">
         <v>790</v>
       </c>
-      <c r="N332" t="s" s="2">
+      <c r="O332" t="s" s="2">
         <v>791</v>
-      </c>
-      <c r="O332" t="s" s="2">
-        <v>792</v>
       </c>
       <c r="P332" s="2"/>
       <c r="Q332" t="s" s="2">
@@ -41150,7 +41148,7 @@
         <v>23</v>
       </c>
       <c r="AG332" t="s" s="2">
-        <v>788</v>
+        <v>787</v>
       </c>
       <c r="AH332" t="s" s="2">
         <v>76</v>
@@ -41167,13 +41165,13 @@
     </row>
     <row r="333">
       <c r="A333" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B333" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="C333" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="D333" s="2"/>
       <c r="E333" t="s" s="2">
@@ -41199,10 +41197,10 @@
         <v>136</v>
       </c>
       <c r="M333" t="s" s="2">
+        <v>793</v>
+      </c>
+      <c r="N333" t="s" s="2">
         <v>794</v>
-      </c>
-      <c r="N333" t="s" s="2">
-        <v>795</v>
       </c>
       <c r="O333" s="2"/>
       <c r="P333" s="2"/>
@@ -41253,7 +41251,7 @@
         <v>23</v>
       </c>
       <c r="AG333" t="s" s="2">
-        <v>793</v>
+        <v>792</v>
       </c>
       <c r="AH333" t="s" s="2">
         <v>76</v>
@@ -41270,13 +41268,13 @@
     </row>
     <row r="334">
       <c r="A334" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B334" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="C334" t="s" s="2">
-        <v>796</v>
+        <v>795</v>
       </c>
       <c r="D334" s="2"/>
       <c r="E334" t="s" s="2">
@@ -41373,13 +41371,13 @@
     </row>
     <row r="335">
       <c r="A335" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B335" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="C335" t="s" s="2">
-        <v>797</v>
+        <v>796</v>
       </c>
       <c r="D335" s="2"/>
       <c r="E335" t="s" s="2">
@@ -41478,13 +41476,13 @@
     </row>
     <row r="336">
       <c r="A336" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B336" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="C336" t="s" s="2">
-        <v>798</v>
+        <v>797</v>
       </c>
       <c r="D336" s="2"/>
       <c r="E336" t="s" s="2">
@@ -41585,13 +41583,13 @@
     </row>
     <row r="337">
       <c r="A337" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B337" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="C337" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="D337" s="2"/>
       <c r="E337" t="s" s="2">
@@ -41614,13 +41612,13 @@
         <v>23</v>
       </c>
       <c r="L337" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M337" t="s" s="2">
+        <v>799</v>
+      </c>
+      <c r="N337" t="s" s="2">
         <v>800</v>
-      </c>
-      <c r="N337" t="s" s="2">
-        <v>801</v>
       </c>
       <c r="O337" s="2"/>
       <c r="P337" s="2"/>
@@ -41671,7 +41669,7 @@
         <v>23</v>
       </c>
       <c r="AG337" t="s" s="2">
-        <v>799</v>
+        <v>798</v>
       </c>
       <c r="AH337" t="s" s="2">
         <v>83</v>
@@ -41688,13 +41686,13 @@
     </row>
     <row r="338">
       <c r="A338" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B338" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="C338" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="D338" s="2"/>
       <c r="E338" t="s" s="2">
@@ -41717,13 +41715,13 @@
         <v>23</v>
       </c>
       <c r="L338" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M338" t="s" s="2">
+        <v>802</v>
+      </c>
+      <c r="N338" t="s" s="2">
         <v>803</v>
-      </c>
-      <c r="N338" t="s" s="2">
-        <v>804</v>
       </c>
       <c r="O338" s="2"/>
       <c r="P338" s="2"/>
@@ -41750,14 +41748,14 @@
         <v>23</v>
       </c>
       <c r="Y338" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z338" t="s" s="2">
+        <v>804</v>
+      </c>
+      <c r="AA338" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="AA338" t="s" s="2">
-        <v>806</v>
-      </c>
       <c r="AB338" t="s" s="2">
         <v>23</v>
       </c>
@@ -41774,7 +41772,7 @@
         <v>23</v>
       </c>
       <c r="AG338" t="s" s="2">
-        <v>802</v>
+        <v>801</v>
       </c>
       <c r="AH338" t="s" s="2">
         <v>76</v>
@@ -41791,13 +41789,13 @@
     </row>
     <row r="339">
       <c r="A339" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B339" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="C339" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="D339" s="2"/>
       <c r="E339" t="s" s="2">
@@ -41820,13 +41818,13 @@
         <v>23</v>
       </c>
       <c r="L339" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M339" t="s" s="2">
+        <v>807</v>
+      </c>
+      <c r="N339" t="s" s="2">
         <v>808</v>
-      </c>
-      <c r="N339" t="s" s="2">
-        <v>809</v>
       </c>
       <c r="O339" s="2"/>
       <c r="P339" s="2"/>
@@ -41853,14 +41851,14 @@
         <v>23</v>
       </c>
       <c r="Y339" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z339" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AA339" t="s" s="2">
         <v>810</v>
       </c>
-      <c r="AA339" t="s" s="2">
-        <v>811</v>
-      </c>
       <c r="AB339" t="s" s="2">
         <v>23</v>
       </c>
@@ -41877,7 +41875,7 @@
         <v>23</v>
       </c>
       <c r="AG339" t="s" s="2">
-        <v>807</v>
+        <v>806</v>
       </c>
       <c r="AH339" t="s" s="2">
         <v>76</v>
@@ -41894,13 +41892,13 @@
     </row>
     <row r="340">
       <c r="A340" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B340" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C340" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D340" s="2"/>
       <c r="E340" t="s" s="2">
@@ -41923,7 +41921,7 @@
         <v>23</v>
       </c>
       <c r="L340" t="s" s="2">
-        <v>595</v>
+        <v>812</v>
       </c>
       <c r="M340" t="s" s="2">
         <v>813</v>
@@ -41980,7 +41978,7 @@
         <v>23</v>
       </c>
       <c r="AG340" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AH340" t="s" s="2">
         <v>76</v>
@@ -41997,7 +41995,7 @@
     </row>
     <row r="341">
       <c r="A341" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B341" t="s" s="2">
         <v>815</v>
@@ -42102,7 +42100,7 @@
     </row>
     <row r="342">
       <c r="A342" t="s" s="2">
-        <v>646</v>
+        <v>645</v>
       </c>
       <c r="B342" t="s" s="2">
         <v>821</v>
@@ -42738,7 +42736,7 @@
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F348" s="2"/>
       <c r="G348" t="s" s="2">
@@ -42757,16 +42755,16 @@
         <v>23</v>
       </c>
       <c r="L348" t="s" s="2">
-        <v>530</v>
+        <v>529</v>
       </c>
       <c r="M348" t="s" s="2">
         <v>841</v>
       </c>
       <c r="N348" t="s" s="2">
+        <v>531</v>
+      </c>
+      <c r="O348" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O348" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P348" s="2"/>
       <c r="Q348" t="s" s="2">
@@ -42816,7 +42814,7 @@
         <v>23</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>76</v>
@@ -42843,7 +42841,7 @@
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F349" s="2"/>
       <c r="G349" t="s" s="2">
@@ -42865,13 +42863,13 @@
         <v>182</v>
       </c>
       <c r="M349" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N349" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N349" t="s" s="2">
+      <c r="O349" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O349" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P349" s="2"/>
       <c r="Q349" t="s" s="2">
@@ -42921,7 +42919,7 @@
         <v>23</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>76</v>
@@ -42973,7 +42971,7 @@
         <v>148</v>
       </c>
       <c r="N350" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="O350" t="s" s="2">
         <v>150</v>
@@ -43026,7 +43024,7 @@
         <v>23</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>76</v>
@@ -43075,10 +43073,10 @@
         <v>147</v>
       </c>
       <c r="M351" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N351" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N351" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O351" t="s" s="2">
         <v>150</v>
@@ -43133,7 +43131,7 @@
         <v>23</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>76</v>
@@ -43284,7 +43282,7 @@
         <v>84</v>
       </c>
       <c r="L353" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M353" t="s" s="2">
         <v>850</v>
@@ -43323,7 +43321,7 @@
       </c>
       <c r="Z353" s="2"/>
       <c r="AA353" t="s" s="2">
-        <v>705</v>
+        <v>704</v>
       </c>
       <c r="AB353" t="s" s="2">
         <v>23</v>
@@ -43537,16 +43535,16 @@
         <v>23</v>
       </c>
       <c r="AC355" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD355" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD355" t="s" s="2">
+      <c r="AE355" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF355" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE355" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF355" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG355" t="s" s="2">
         <v>151</v>
@@ -43595,19 +43593,19 @@
         <v>84</v>
       </c>
       <c r="L356" t="s" s="2">
+        <v>711</v>
+      </c>
+      <c r="M356" t="s" s="2">
         <v>712</v>
       </c>
-      <c r="M356" t="s" s="2">
+      <c r="N356" t="s" s="2">
         <v>713</v>
       </c>
-      <c r="N356" t="s" s="2">
+      <c r="O356" t="s" s="2">
         <v>714</v>
       </c>
-      <c r="O356" t="s" s="2">
+      <c r="P356" t="s" s="2">
         <v>715</v>
-      </c>
-      <c r="P356" t="s" s="2">
-        <v>716</v>
       </c>
       <c r="Q356" t="s" s="2">
         <v>23</v>
@@ -43656,7 +43654,7 @@
         <v>23</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>717</v>
+        <v>716</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>76</v>
@@ -43852,16 +43850,16 @@
         <v>23</v>
       </c>
       <c r="AC358" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD358" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD358" t="s" s="2">
+      <c r="AE358" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF358" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE358" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF358" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG358" t="s" s="2">
         <v>151</v>
@@ -44332,7 +44330,7 @@
         <v>84</v>
       </c>
       <c r="L363" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M363" t="s" s="2">
         <v>880</v>
@@ -44442,16 +44440,16 @@
         <v>141</v>
       </c>
       <c r="M364" t="s" s="2">
+        <v>719</v>
+      </c>
+      <c r="N364" t="s" s="2">
         <v>720</v>
       </c>
-      <c r="N364" t="s" s="2">
+      <c r="O364" t="s" s="2">
         <v>721</v>
       </c>
-      <c r="O364" t="s" s="2">
+      <c r="P364" t="s" s="2">
         <v>722</v>
-      </c>
-      <c r="P364" t="s" s="2">
-        <v>723</v>
       </c>
       <c r="Q364" t="s" s="2">
         <v>23</v>
@@ -44500,7 +44498,7 @@
         <v>23</v>
       </c>
       <c r="AG364" t="s" s="2">
-        <v>724</v>
+        <v>723</v>
       </c>
       <c r="AH364" t="s" s="2">
         <v>76</v>
@@ -44754,7 +44752,7 @@
         <v>23</v>
       </c>
       <c r="L367" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M367" t="s" s="2">
         <v>897</v>
@@ -44793,7 +44791,7 @@
       </c>
       <c r="Z367" s="2"/>
       <c r="AA367" t="s" s="2">
-        <v>471</v>
+        <v>470</v>
       </c>
       <c r="AB367" t="s" s="2">
         <v>23</v>
@@ -44857,7 +44855,7 @@
         <v>84</v>
       </c>
       <c r="L368" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M368" t="s" s="2">
         <v>901</v>
@@ -45427,7 +45425,7 @@
         <v>23</v>
       </c>
       <c r="AC373" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD373" s="2"/>
       <c r="AE373" t="s" s="2">
@@ -45485,7 +45483,7 @@
         <v>23</v>
       </c>
       <c r="L374" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M374" t="s" s="2">
         <v>917</v>
@@ -45847,16 +45845,16 @@
         <v>23</v>
       </c>
       <c r="AC377" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD377" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD377" t="s" s="2">
+      <c r="AE377" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF377" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE377" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF377" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG377" t="s" s="2">
         <v>151</v>
@@ -46325,7 +46323,7 @@
         <v>23</v>
       </c>
       <c r="L382" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M382" t="s" s="2">
         <v>956</v>
@@ -46430,7 +46428,7 @@
         <v>23</v>
       </c>
       <c r="L383" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M383" t="s" s="2">
         <v>960</v>
@@ -47054,7 +47052,7 @@
         <v>23</v>
       </c>
       <c r="L389" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M389" t="s" s="2">
         <v>972</v>
@@ -47659,7 +47657,7 @@
       </c>
       <c r="D395" s="2"/>
       <c r="E395" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F395" s="2"/>
       <c r="G395" t="s" s="2">
@@ -47678,16 +47676,16 @@
         <v>23</v>
       </c>
       <c r="L395" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M395" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M395" t="s" s="2">
+      <c r="N395" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N395" t="s" s="2">
+      <c r="O395" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O395" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P395" s="2"/>
       <c r="Q395" t="s" s="2">
@@ -47737,7 +47735,7 @@
         <v>23</v>
       </c>
       <c r="AG395" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH395" t="s" s="2">
         <v>76</v>
@@ -47764,7 +47762,7 @@
       </c>
       <c r="D396" s="2"/>
       <c r="E396" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F396" s="2"/>
       <c r="G396" t="s" s="2">
@@ -47786,13 +47784,13 @@
         <v>182</v>
       </c>
       <c r="M396" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N396" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N396" t="s" s="2">
+      <c r="O396" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O396" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P396" s="2"/>
       <c r="Q396" t="s" s="2">
@@ -47830,17 +47828,17 @@
         <v>23</v>
       </c>
       <c r="AC396" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD396" s="2"/>
       <c r="AE396" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF396" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG396" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH396" t="s" s="2">
         <v>76</v>
@@ -47897,7 +47895,7 @@
         <v>834</v>
       </c>
       <c r="O397" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P397" s="2"/>
       <c r="Q397" t="s" s="2">
@@ -47947,7 +47945,7 @@
         <v>23</v>
       </c>
       <c r="AG397" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH397" t="s" s="2">
         <v>76</v>
@@ -48004,7 +48002,7 @@
         <v>995</v>
       </c>
       <c r="O398" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P398" s="2"/>
       <c r="Q398" t="s" s="2">
@@ -48054,7 +48052,7 @@
         <v>23</v>
       </c>
       <c r="AG398" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH398" t="s" s="2">
         <v>76</v>
@@ -48145,17 +48143,17 @@
         <v>23</v>
       </c>
       <c r="AC399" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD399" s="2"/>
       <c r="AE399" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF399" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG399" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH399" t="s" s="2">
         <v>76</v>
@@ -48260,7 +48258,7 @@
         <v>23</v>
       </c>
       <c r="AG400" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH400" t="s" s="2">
         <v>76</v>
@@ -48365,7 +48363,7 @@
         <v>23</v>
       </c>
       <c r="AG401" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH401" t="s" s="2">
         <v>76</v>
@@ -48470,7 +48468,7 @@
         <v>23</v>
       </c>
       <c r="AG402" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH402" t="s" s="2">
         <v>76</v>
@@ -48519,10 +48517,10 @@
         <v>147</v>
       </c>
       <c r="M403" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N403" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N403" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O403" t="s" s="2">
         <v>150</v>
@@ -48577,7 +48575,7 @@
         <v>23</v>
       </c>
       <c r="AG403" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH403" t="s" s="2">
         <v>76</v>
@@ -48632,7 +48630,7 @@
         <v>1018</v>
       </c>
       <c r="O404" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P404" s="2"/>
       <c r="Q404" t="s" s="2">
@@ -48737,7 +48735,7 @@
         <v>1021</v>
       </c>
       <c r="O405" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P405" s="2"/>
       <c r="Q405" t="s" s="2">
@@ -48831,7 +48829,7 @@
         <v>23</v>
       </c>
       <c r="L406" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M406" t="s" s="2">
         <v>1024</v>
@@ -48866,7 +48864,7 @@
         <v>23</v>
       </c>
       <c r="Y406" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z406" t="s" s="2">
         <v>1027</v>
@@ -49041,7 +49039,7 @@
         <v>23</v>
       </c>
       <c r="L408" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M408" t="s" s="2">
         <v>1037</v>
@@ -49076,7 +49074,7 @@
         <v>23</v>
       </c>
       <c r="Y408" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z408" t="s" s="2">
         <v>1041</v>
@@ -49249,7 +49247,7 @@
         <v>84</v>
       </c>
       <c r="L410" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M410" t="s" s="2">
         <v>1049</v>
@@ -49492,19 +49490,19 @@
         <v>23</v>
       </c>
       <c r="Y412" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z412" t="s" s="2">
         <v>1061</v>
       </c>
       <c r="AA412" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AB412" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC412" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD412" s="2"/>
       <c r="AE412" t="s" s="2">
@@ -49817,16 +49815,16 @@
         <v>23</v>
       </c>
       <c r="AC415" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD415" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD415" t="s" s="2">
+      <c r="AE415" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF415" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE415" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF415" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG415" t="s" s="2">
         <v>151</v>
@@ -50295,7 +50293,7 @@
         <v>84</v>
       </c>
       <c r="L420" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M420" t="s" s="2">
         <v>1080</v>
@@ -50400,7 +50398,7 @@
         <v>23</v>
       </c>
       <c r="L421" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M421" t="s" s="2">
         <v>1084</v>
@@ -50505,7 +50503,7 @@
         <v>23</v>
       </c>
       <c r="L422" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M422" t="s" s="2">
         <v>1088</v>
@@ -50608,7 +50606,7 @@
         <v>84</v>
       </c>
       <c r="L423" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M423" t="s" s="2">
         <v>1091</v>
@@ -50711,7 +50709,7 @@
         <v>84</v>
       </c>
       <c r="L424" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M424" t="s" s="2">
         <v>1094</v>
@@ -50917,7 +50915,7 @@
         <v>84</v>
       </c>
       <c r="L426" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M426" t="s" s="2">
         <v>1054</v>
@@ -50952,7 +50950,7 @@
         <v>23</v>
       </c>
       <c r="Y426" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z426" t="s" s="2">
         <v>1102</v>
@@ -51125,7 +51123,7 @@
         <v>23</v>
       </c>
       <c r="L428" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M428" t="s" s="2">
         <v>1108</v>
@@ -51160,7 +51158,7 @@
         <v>23</v>
       </c>
       <c r="Y428" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z428" t="s" s="2">
         <v>1111</v>
@@ -51541,7 +51539,7 @@
         <v>84</v>
       </c>
       <c r="L432" t="s" s="2">
-        <v>637</v>
+        <v>636</v>
       </c>
       <c r="M432" t="s" s="2">
         <v>1126</v>
@@ -51749,7 +51747,7 @@
         <v>23</v>
       </c>
       <c r="L434" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M434" t="s" s="2">
         <v>1133</v>
@@ -51784,7 +51782,7 @@
         <v>23</v>
       </c>
       <c r="Y434" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z434" t="s" s="2">
         <v>1136</v>
@@ -51957,7 +51955,7 @@
         <v>23</v>
       </c>
       <c r="L436" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M436" t="s" s="2">
         <v>1142</v>
@@ -52066,7 +52064,7 @@
         <v>1146</v>
       </c>
       <c r="N437" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O437" t="s" s="2">
         <v>1147</v>
@@ -53003,7 +53001,7 @@
         <v>23</v>
       </c>
       <c r="L446" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M446" t="s" s="2">
         <v>1162</v>
@@ -53524,7 +53522,7 @@
         <v>23</v>
       </c>
       <c r="L451" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M451" t="s" s="2">
         <v>1182</v>
@@ -54288,13 +54286,13 @@
         <v>23</v>
       </c>
       <c r="Y458" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z458" t="s" s="2">
         <v>1202</v>
       </c>
       <c r="AA458" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AB458" t="s" s="2">
         <v>23</v>
@@ -54358,7 +54356,7 @@
         <v>23</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M459" t="s" s="2">
         <v>1204</v>
@@ -54391,13 +54389,13 @@
         <v>23</v>
       </c>
       <c r="Y459" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z459" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AA459" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="AA459" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="AB459" t="s" s="2">
         <v>23</v>
@@ -54461,7 +54459,7 @@
         <v>23</v>
       </c>
       <c r="L460" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="M460" t="s" s="2">
         <v>1207</v>
@@ -55276,7 +55274,7 @@
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F468" s="2"/>
       <c r="G468" t="s" s="2">
@@ -55295,16 +55293,16 @@
         <v>23</v>
       </c>
       <c r="L468" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M468" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M468" t="s" s="2">
+      <c r="N468" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N468" t="s" s="2">
+      <c r="O468" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O468" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P468" s="2"/>
       <c r="Q468" t="s" s="2">
@@ -55354,7 +55352,7 @@
         <v>23</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>76</v>
@@ -55381,7 +55379,7 @@
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F469" s="2"/>
       <c r="G469" t="s" s="2">
@@ -55403,13 +55401,13 @@
         <v>182</v>
       </c>
       <c r="M469" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N469" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N469" t="s" s="2">
+      <c r="O469" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O469" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P469" s="2"/>
       <c r="Q469" t="s" s="2">
@@ -55447,17 +55445,17 @@
         <v>23</v>
       </c>
       <c r="AC469" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD469" s="2"/>
       <c r="AE469" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF469" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>76</v>
@@ -55514,7 +55512,7 @@
         <v>834</v>
       </c>
       <c r="O470" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P470" s="2"/>
       <c r="Q470" t="s" s="2">
@@ -55564,7 +55562,7 @@
         <v>23</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -55621,7 +55619,7 @@
         <v>995</v>
       </c>
       <c r="O471" t="s" s="2">
-        <v>539</v>
+        <v>538</v>
       </c>
       <c r="P471" s="2"/>
       <c r="Q471" t="s" s="2">
@@ -55671,7 +55669,7 @@
         <v>23</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>76</v>
@@ -55762,17 +55760,17 @@
         <v>23</v>
       </c>
       <c r="AC472" t="s" s="2">
-        <v>356</v>
+        <v>355</v>
       </c>
       <c r="AD472" s="2"/>
       <c r="AE472" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF472" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>76</v>
@@ -55877,7 +55875,7 @@
         <v>23</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55982,7 +55980,7 @@
         <v>23</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -56087,7 +56085,7 @@
         <v>23</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -56136,10 +56134,10 @@
         <v>147</v>
       </c>
       <c r="M476" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N476" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N476" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O476" t="s" s="2">
         <v>150</v>
@@ -56194,7 +56192,7 @@
         <v>23</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>76</v>
@@ -56249,7 +56247,7 @@
         <v>1018</v>
       </c>
       <c r="O477" t="s" s="2">
-        <v>667</v>
+        <v>666</v>
       </c>
       <c r="P477" s="2"/>
       <c r="Q477" t="s" s="2">
@@ -56354,7 +56352,7 @@
         <v>1021</v>
       </c>
       <c r="O478" t="s" s="2">
-        <v>554</v>
+        <v>553</v>
       </c>
       <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
@@ -56448,7 +56446,7 @@
         <v>23</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M479" t="s" s="2">
         <v>1224</v>
@@ -56483,7 +56481,7 @@
         <v>23</v>
       </c>
       <c r="Y479" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z479" t="s" s="2">
         <v>1027</v>
@@ -56658,7 +56656,7 @@
         <v>23</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M481" t="s" s="2">
         <v>1226</v>
@@ -56693,7 +56691,7 @@
         <v>23</v>
       </c>
       <c r="Y481" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z481" t="s" s="2">
         <v>1041</v>
@@ -56866,7 +56864,7 @@
         <v>84</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M483" t="s" s="2">
         <v>1229</v>
@@ -57016,7 +57014,7 @@
         <v>23</v>
       </c>
       <c r="AC484" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD484" s="2"/>
       <c r="AE484" t="s" s="2">
@@ -57179,7 +57177,7 @@
         <v>84</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>388</v>
+        <v>387</v>
       </c>
       <c r="M486" t="s" s="2">
         <v>1237</v>
@@ -57317,19 +57315,19 @@
         <v>23</v>
       </c>
       <c r="Y487" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z487" t="s" s="2">
         <v>1061</v>
       </c>
       <c r="AA487" t="s" s="2">
-        <v>701</v>
+        <v>700</v>
       </c>
       <c r="AB487" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC487" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD487" s="2"/>
       <c r="AE487" t="s" s="2">
@@ -57642,16 +57640,16 @@
         <v>23</v>
       </c>
       <c r="AC490" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD490" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD490" t="s" s="2">
+      <c r="AE490" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF490" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE490" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF490" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG490" t="s" s="2">
         <v>151</v>
@@ -58120,7 +58118,7 @@
         <v>84</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>578</v>
+        <v>577</v>
       </c>
       <c r="M495" t="s" s="2">
         <v>1239</v>
@@ -58225,7 +58223,7 @@
         <v>23</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>584</v>
+        <v>583</v>
       </c>
       <c r="M496" t="s" s="2">
         <v>1240</v>
@@ -58330,7 +58328,7 @@
         <v>23</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>734</v>
+        <v>733</v>
       </c>
       <c r="M497" t="s" s="2">
         <v>1241</v>
@@ -58433,7 +58431,7 @@
         <v>84</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M498" t="s" s="2">
         <v>1242</v>
@@ -58536,7 +58534,7 @@
         <v>84</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>750</v>
+        <v>749</v>
       </c>
       <c r="M499" t="s" s="2">
         <v>1243</v>
@@ -58742,7 +58740,7 @@
         <v>84</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M501" t="s" s="2">
         <v>1245</v>
@@ -58777,7 +58775,7 @@
         <v>23</v>
       </c>
       <c r="Y501" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z501" t="s" s="2">
         <v>1102</v>
@@ -58950,7 +58948,7 @@
         <v>23</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M503" t="s" s="2">
         <v>1247</v>
@@ -58985,7 +58983,7 @@
         <v>23</v>
       </c>
       <c r="Y503" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z503" t="s" s="2">
         <v>1111</v>
@@ -59574,7 +59572,7 @@
         <v>23</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M509" t="s" s="2">
         <v>1253</v>
@@ -59609,7 +59607,7 @@
         <v>23</v>
       </c>
       <c r="Y509" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z509" t="s" s="2">
         <v>1136</v>
@@ -59782,7 +59780,7 @@
         <v>23</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>608</v>
+        <v>607</v>
       </c>
       <c r="M511" t="s" s="2">
         <v>1255</v>
@@ -59891,7 +59889,7 @@
         <v>1146</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>791</v>
+        <v>790</v>
       </c>
       <c r="O512" t="s" s="2">
         <v>1147</v>
@@ -60828,7 +60826,7 @@
         <v>23</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M521" t="s" s="2">
         <v>1162</v>
@@ -61349,7 +61347,7 @@
         <v>23</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M526" t="s" s="2">
         <v>1182</v>
@@ -62113,13 +62111,13 @@
         <v>23</v>
       </c>
       <c r="Y533" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z533" t="s" s="2">
         <v>1202</v>
       </c>
       <c r="AA533" t="s" s="2">
-        <v>806</v>
+        <v>805</v>
       </c>
       <c r="AB533" t="s" s="2">
         <v>23</v>
@@ -62183,7 +62181,7 @@
         <v>23</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M534" t="s" s="2">
         <v>1204</v>
@@ -62216,13 +62214,13 @@
         <v>23</v>
       </c>
       <c r="Y534" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z534" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="AA534" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="AA534" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="AB534" t="s" s="2">
         <v>23</v>
@@ -62286,7 +62284,7 @@
         <v>23</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>758</v>
+        <v>757</v>
       </c>
       <c r="M535" t="s" s="2">
         <v>1259</v>
@@ -63101,7 +63099,7 @@
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
-        <v>529</v>
+        <v>528</v>
       </c>
       <c r="F543" s="2"/>
       <c r="G543" t="s" s="2">
@@ -63120,16 +63118,16 @@
         <v>23</v>
       </c>
       <c r="L543" t="s" s="2">
+        <v>529</v>
+      </c>
+      <c r="M543" t="s" s="2">
         <v>530</v>
       </c>
-      <c r="M543" t="s" s="2">
+      <c r="N543" t="s" s="2">
         <v>531</v>
       </c>
-      <c r="N543" t="s" s="2">
+      <c r="O543" t="s" s="2">
         <v>532</v>
-      </c>
-      <c r="O543" t="s" s="2">
-        <v>533</v>
       </c>
       <c r="P543" s="2"/>
       <c r="Q543" t="s" s="2">
@@ -63179,7 +63177,7 @@
         <v>23</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>534</v>
+        <v>533</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -63206,7 +63204,7 @@
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
-        <v>536</v>
+        <v>535</v>
       </c>
       <c r="F544" s="2"/>
       <c r="G544" t="s" s="2">
@@ -63228,13 +63226,13 @@
         <v>182</v>
       </c>
       <c r="M544" t="s" s="2">
+        <v>536</v>
+      </c>
+      <c r="N544" t="s" s="2">
         <v>537</v>
       </c>
-      <c r="N544" t="s" s="2">
+      <c r="O544" t="s" s="2">
         <v>538</v>
-      </c>
-      <c r="O544" t="s" s="2">
-        <v>539</v>
       </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
@@ -63284,7 +63282,7 @@
         <v>23</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>540</v>
+        <v>539</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
@@ -63336,7 +63334,7 @@
         <v>148</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>542</v>
+        <v>541</v>
       </c>
       <c r="O545" t="s" s="2">
         <v>150</v>
@@ -63389,7 +63387,7 @@
         <v>23</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>543</v>
+        <v>542</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63438,10 +63436,10 @@
         <v>147</v>
       </c>
       <c r="M546" t="s" s="2">
+        <v>544</v>
+      </c>
+      <c r="N546" t="s" s="2">
         <v>545</v>
-      </c>
-      <c r="N546" t="s" s="2">
-        <v>546</v>
       </c>
       <c r="O546" t="s" s="2">
         <v>150</v>
@@ -63496,7 +63494,7 @@
         <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>547</v>
+        <v>546</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -63750,7 +63748,7 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M549" t="s" s="2">
         <v>1286</v>
@@ -63855,7 +63853,7 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M550" t="s" s="2">
         <v>1292</v>
@@ -63890,7 +63888,7 @@
         <v>23</v>
       </c>
       <c r="Y550" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z550" t="s" s="2">
         <v>1295</v>
@@ -64586,7 +64584,7 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M557" t="s" s="2">
         <v>1311</v>
@@ -64689,7 +64687,7 @@
         <v>84</v>
       </c>
       <c r="L558" t="s" s="2">
-        <v>507</v>
+        <v>506</v>
       </c>
       <c r="M558" t="s" s="2">
         <v>1314</v>
@@ -65210,7 +65208,7 @@
         <v>84</v>
       </c>
       <c r="L563" t="s" s="2">
-        <v>495</v>
+        <v>494</v>
       </c>
       <c r="M563" t="s" s="2">
         <v>1323</v>
@@ -65346,7 +65344,7 @@
         <v>23</v>
       </c>
       <c r="Y564" t="s" s="2">
-        <v>375</v>
+        <v>374</v>
       </c>
       <c r="Z564" t="s" s="2">
         <v>1329</v>
@@ -65390,10 +65388,10 @@
         <v>1330</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65419,13 +65417,13 @@
         <v>78</v>
       </c>
       <c r="M565" t="s" s="2">
+        <v>1336</v>
+      </c>
+      <c r="N565" t="s" s="2">
         <v>1337</v>
       </c>
-      <c r="N565" t="s" s="2">
+      <c r="O565" t="s" s="2">
         <v>1338</v>
-      </c>
-      <c r="O565" t="s" s="2">
-        <v>1339</v>
       </c>
       <c r="P565" s="2"/>
       <c r="Q565" t="s" s="2">
@@ -65475,7 +65473,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1335</v>
+        <v>1334</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -65495,10 +65493,10 @@
         <v>1330</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1340</v>
+        <v>1339</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -65598,10 +65596,10 @@
         <v>1330</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -65671,16 +65669,16 @@
         <v>23</v>
       </c>
       <c r="AC567" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD567" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD567" t="s" s="2">
+      <c r="AE567" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF567" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE567" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF567" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG567" t="s" s="2">
         <v>151</v>
@@ -65703,10 +65701,10 @@
         <v>1330</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65810,10 +65808,10 @@
         <v>1330</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -65836,17 +65834,17 @@
         <v>84</v>
       </c>
       <c r="L569" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M569" t="s" s="2">
+        <v>1343</v>
+      </c>
+      <c r="N569" t="s" s="2">
         <v>1344</v>
-      </c>
-      <c r="N569" t="s" s="2">
-        <v>1345</v>
       </c>
       <c r="O569" s="2"/>
       <c r="P569" t="s" s="2">
-        <v>1346</v>
+        <v>1345</v>
       </c>
       <c r="Q569" t="s" s="2">
         <v>23</v>
@@ -65895,7 +65893,7 @@
         <v>23</v>
       </c>
       <c r="AG569" t="s" s="2">
-        <v>1343</v>
+        <v>1342</v>
       </c>
       <c r="AH569" t="s" s="2">
         <v>76</v>
@@ -65915,10 +65913,10 @@
         <v>1330</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -65941,17 +65939,17 @@
         <v>84</v>
       </c>
       <c r="L570" t="s" s="2">
-        <v>421</v>
+        <v>420</v>
       </c>
       <c r="M570" t="s" s="2">
+        <v>1347</v>
+      </c>
+      <c r="N570" t="s" s="2">
         <v>1348</v>
-      </c>
-      <c r="N570" t="s" s="2">
-        <v>1349</v>
       </c>
       <c r="O570" s="2"/>
       <c r="P570" t="s" s="2">
-        <v>1350</v>
+        <v>1349</v>
       </c>
       <c r="Q570" t="s" s="2">
         <v>23</v>
@@ -66000,7 +65998,7 @@
         <v>23</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>
@@ -66012,7 +66010,7 @@
         <v>23</v>
       </c>
       <c r="AK570" t="s" s="2">
-        <v>1351</v>
+        <v>1350</v>
       </c>
     </row>
     <row r="571">
@@ -66020,10 +66018,10 @@
         <v>1330</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -66123,10 +66121,10 @@
         <v>1330</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -66196,16 +66194,16 @@
         <v>23</v>
       </c>
       <c r="AC572" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD572" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD572" t="s" s="2">
+      <c r="AE572" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF572" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE572" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF572" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG572" t="s" s="2">
         <v>151</v>
@@ -66228,10 +66226,10 @@
         <v>1330</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -66254,13 +66252,13 @@
         <v>84</v>
       </c>
       <c r="L573" t="s" s="2">
+        <v>1354</v>
+      </c>
+      <c r="M573" t="s" s="2">
         <v>1355</v>
       </c>
-      <c r="M573" t="s" s="2">
+      <c r="N573" t="s" s="2">
         <v>1356</v>
-      </c>
-      <c r="N573" t="s" s="2">
-        <v>1357</v>
       </c>
       <c r="O573" s="2"/>
       <c r="P573" s="2"/>
@@ -66299,17 +66297,17 @@
         <v>23</v>
       </c>
       <c r="AC573" t="s" s="2">
-        <v>394</v>
+        <v>393</v>
       </c>
       <c r="AD573" s="2"/>
       <c r="AE573" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF573" t="s" s="2">
-        <v>358</v>
+        <v>357</v>
       </c>
       <c r="AG573" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="AH573" t="s" s="2">
         <v>76</v>
@@ -66329,13 +66327,13 @@
         <v>1330</v>
       </c>
       <c r="B574" t="s" s="2">
+        <v>1357</v>
+      </c>
+      <c r="C574" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="D574" t="s" s="2">
         <v>1358</v>
-      </c>
-      <c r="C574" t="s" s="2">
-        <v>1354</v>
-      </c>
-      <c r="D574" t="s" s="2">
-        <v>1359</v>
       </c>
       <c r="E574" t="s" s="2">
         <v>23</v>
@@ -66360,10 +66358,10 @@
         <v>1172</v>
       </c>
       <c r="M574" t="s" s="2">
+        <v>1355</v>
+      </c>
+      <c r="N574" t="s" s="2">
         <v>1356</v>
-      </c>
-      <c r="N574" t="s" s="2">
-        <v>1357</v>
       </c>
       <c r="O574" s="2"/>
       <c r="P574" s="2"/>
@@ -66414,7 +66412,7 @@
         <v>23</v>
       </c>
       <c r="AG574" t="s" s="2">
-        <v>1354</v>
+        <v>1353</v>
       </c>
       <c r="AH574" t="s" s="2">
         <v>76</v>
@@ -66434,10 +66432,10 @@
         <v>1330</v>
       </c>
       <c r="B575" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="C575" t="s" s="2">
         <v>1360</v>
-      </c>
-      <c r="C575" t="s" s="2">
-        <v>1361</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -66537,10 +66535,10 @@
         <v>1330</v>
       </c>
       <c r="B576" t="s" s="2">
+        <v>1361</v>
+      </c>
+      <c r="C576" t="s" s="2">
         <v>1362</v>
-      </c>
-      <c r="C576" t="s" s="2">
-        <v>1363</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
@@ -66610,16 +66608,16 @@
         <v>23</v>
       </c>
       <c r="AC576" t="s" s="2">
+        <v>355</v>
+      </c>
+      <c r="AD576" t="s" s="2">
         <v>356</v>
       </c>
-      <c r="AD576" t="s" s="2">
+      <c r="AE576" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF576" t="s" s="2">
         <v>357</v>
-      </c>
-      <c r="AE576" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF576" t="s" s="2">
-        <v>358</v>
       </c>
       <c r="AG576" t="s" s="2">
         <v>151</v>
@@ -66642,10 +66640,10 @@
         <v>1330</v>
       </c>
       <c r="B577" t="s" s="2">
+        <v>1363</v>
+      </c>
+      <c r="C577" t="s" s="2">
         <v>1364</v>
-      </c>
-      <c r="C577" t="s" s="2">
-        <v>1365</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
@@ -66668,16 +66666,16 @@
         <v>84</v>
       </c>
       <c r="L577" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M577" t="s" s="2">
+        <v>1365</v>
+      </c>
+      <c r="N577" t="s" s="2">
         <v>1366</v>
       </c>
-      <c r="N577" t="s" s="2">
+      <c r="O577" t="s" s="2">
         <v>1367</v>
-      </c>
-      <c r="O577" t="s" s="2">
-        <v>1368</v>
       </c>
       <c r="P577" s="2"/>
       <c r="Q577" t="s" s="2">
@@ -66727,16 +66725,16 @@
         <v>23</v>
       </c>
       <c r="AG577" t="s" s="2">
+        <v>1368</v>
+      </c>
+      <c r="AH577" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI577" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ577" t="s" s="2">
         <v>1369</v>
-      </c>
-      <c r="AH577" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI577" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ577" t="s" s="2">
-        <v>1370</v>
       </c>
       <c r="AK577" t="s" s="2">
         <v>95</v>
@@ -66747,10 +66745,10 @@
         <v>1330</v>
       </c>
       <c r="B578" t="s" s="2">
+        <v>1370</v>
+      </c>
+      <c r="C578" t="s" s="2">
         <v>1371</v>
-      </c>
-      <c r="C578" t="s" s="2">
-        <v>1372</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
@@ -66773,69 +66771,69 @@
         <v>84</v>
       </c>
       <c r="L578" t="s" s="2">
-        <v>588</v>
+        <v>587</v>
       </c>
       <c r="M578" t="s" s="2">
+        <v>1372</v>
+      </c>
+      <c r="N578" t="s" s="2">
         <v>1373</v>
       </c>
-      <c r="N578" t="s" s="2">
+      <c r="O578" t="s" s="2">
         <v>1374</v>
-      </c>
-      <c r="O578" t="s" s="2">
-        <v>1375</v>
       </c>
       <c r="P578" s="2"/>
       <c r="Q578" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R578" t="s" s="2">
+        <v>1375</v>
+      </c>
+      <c r="S578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF578" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG578" t="s" s="2">
         <v>1376</v>
       </c>
-      <c r="S578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF578" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG578" t="s" s="2">
-        <v>1377</v>
-      </c>
       <c r="AH578" t="s" s="2">
         <v>76</v>
       </c>
@@ -66843,7 +66841,7 @@
         <v>83</v>
       </c>
       <c r="AJ578" t="s" s="2">
-        <v>1370</v>
+        <v>1369</v>
       </c>
       <c r="AK578" t="s" s="2">
         <v>95</v>
@@ -66854,10 +66852,10 @@
         <v>1330</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -66880,19 +66878,19 @@
         <v>84</v>
       </c>
       <c r="L579" t="s" s="2">
+        <v>1378</v>
+      </c>
+      <c r="M579" t="s" s="2">
         <v>1379</v>
       </c>
-      <c r="M579" t="s" s="2">
+      <c r="N579" t="s" s="2">
         <v>1380</v>
       </c>
-      <c r="N579" t="s" s="2">
+      <c r="O579" t="s" s="2">
         <v>1381</v>
       </c>
-      <c r="O579" t="s" s="2">
+      <c r="P579" t="s" s="2">
         <v>1382</v>
-      </c>
-      <c r="P579" t="s" s="2">
-        <v>1383</v>
       </c>
       <c r="Q579" t="s" s="2">
         <v>23</v>
@@ -66941,7 +66939,7 @@
         <v>23</v>
       </c>
       <c r="AG579" t="s" s="2">
-        <v>1378</v>
+        <v>1377</v>
       </c>
       <c r="AH579" t="s" s="2">
         <v>76</v>
@@ -66961,10 +66959,10 @@
         <v>1330</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -66987,13 +66985,13 @@
         <v>84</v>
       </c>
       <c r="L580" t="s" s="2">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="M580" t="s" s="2">
+        <v>1384</v>
+      </c>
+      <c r="N580" t="s" s="2">
         <v>1385</v>
-      </c>
-      <c r="N580" t="s" s="2">
-        <v>1386</v>
       </c>
       <c r="O580" s="2"/>
       <c r="P580" s="2"/>
@@ -67044,7 +67042,7 @@
         <v>23</v>
       </c>
       <c r="AG580" t="s" s="2">
-        <v>1384</v>
+        <v>1383</v>
       </c>
       <c r="AH580" t="s" s="2">
         <v>76</v>
@@ -67064,10 +67062,10 @@
         <v>1330</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="D581" s="2"/>
       <c r="E581" t="s" s="2">
@@ -67093,16 +67091,16 @@
         <v>199</v>
       </c>
       <c r="M581" t="s" s="2">
+        <v>1387</v>
+      </c>
+      <c r="N581" t="s" s="2">
         <v>1388</v>
       </c>
-      <c r="N581" t="s" s="2">
+      <c r="O581" t="s" s="2">
         <v>1389</v>
       </c>
-      <c r="O581" t="s" s="2">
+      <c r="P581" t="s" s="2">
         <v>1390</v>
-      </c>
-      <c r="P581" t="s" s="2">
-        <v>1391</v>
       </c>
       <c r="Q581" t="s" s="2">
         <v>23</v>
@@ -67151,7 +67149,7 @@
         <v>23</v>
       </c>
       <c r="AG581" t="s" s="2">
-        <v>1387</v>
+        <v>1386</v>
       </c>
       <c r="AH581" t="s" s="2">
         <v>76</v>
@@ -67171,10 +67169,10 @@
         <v>1330</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="D582" s="2"/>
       <c r="E582" t="s" s="2">
@@ -67200,16 +67198,16 @@
         <v>199</v>
       </c>
       <c r="M582" t="s" s="2">
+        <v>1392</v>
+      </c>
+      <c r="N582" t="s" s="2">
         <v>1393</v>
       </c>
-      <c r="N582" t="s" s="2">
-        <v>1394</v>
-      </c>
       <c r="O582" t="s" s="2">
+        <v>1389</v>
+      </c>
+      <c r="P582" t="s" s="2">
         <v>1390</v>
-      </c>
-      <c r="P582" t="s" s="2">
-        <v>1391</v>
       </c>
       <c r="Q582" t="s" s="2">
         <v>23</v>
@@ -67258,7 +67256,7 @@
         <v>23</v>
       </c>
       <c r="AG582" t="s" s="2">
-        <v>1392</v>
+        <v>1391</v>
       </c>
       <c r="AH582" t="s" s="2">
         <v>76</v>
@@ -67278,10 +67276,10 @@
         <v>1330</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="D583" s="2"/>
       <c r="E583" t="s" s="2">
@@ -67307,10 +67305,10 @@
         <v>103</v>
       </c>
       <c r="M583" t="s" s="2">
+        <v>1395</v>
+      </c>
+      <c r="N583" t="s" s="2">
         <v>1396</v>
-      </c>
-      <c r="N583" t="s" s="2">
-        <v>1397</v>
       </c>
       <c r="O583" s="2"/>
       <c r="P583" s="2"/>
@@ -67340,11 +67338,11 @@
         <v>121</v>
       </c>
       <c r="Z583" t="s" s="2">
+        <v>1397</v>
+      </c>
+      <c r="AA583" t="s" s="2">
         <v>1398</v>
       </c>
-      <c r="AA583" t="s" s="2">
-        <v>1399</v>
-      </c>
       <c r="AB583" t="s" s="2">
         <v>23</v>
       </c>
@@ -67361,7 +67359,7 @@
         <v>23</v>
       </c>
       <c r="AG583" t="s" s="2">
-        <v>1395</v>
+        <v>1394</v>
       </c>
       <c r="AH583" t="s" s="2">
         <v>76</v>
@@ -67381,10 +67379,10 @@
         <v>1330</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" t="s" s="2">
@@ -67407,13 +67405,13 @@
         <v>84</v>
       </c>
       <c r="L584" t="s" s="2">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="M584" t="s" s="2">
+        <v>1400</v>
+      </c>
+      <c r="N584" t="s" s="2">
         <v>1401</v>
-      </c>
-      <c r="N584" t="s" s="2">
-        <v>1402</v>
       </c>
       <c r="O584" s="2"/>
       <c r="P584" s="2"/>
@@ -67421,7 +67419,7 @@
         <v>23</v>
       </c>
       <c r="R584" t="s" s="2">
-        <v>1403</v>
+        <v>1402</v>
       </c>
       <c r="S584" t="s" s="2">
         <v>23</v>
@@ -67466,7 +67464,7 @@
         <v>23</v>
       </c>
       <c r="AG584" t="s" s="2">
-        <v>1400</v>
+        <v>1399</v>
       </c>
       <c r="AH584" t="s" s="2">
         <v>76</v>
@@ -67486,10 +67484,10 @@
         <v>1330</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -67512,13 +67510,13 @@
         <v>84</v>
       </c>
       <c r="L585" t="s" s="2">
-        <v>1379</v>
+        <v>1378</v>
       </c>
       <c r="M585" t="s" s="2">
+        <v>1404</v>
+      </c>
+      <c r="N585" t="s" s="2">
         <v>1405</v>
-      </c>
-      <c r="N585" t="s" s="2">
-        <v>1406</v>
       </c>
       <c r="O585" s="2"/>
       <c r="P585" s="2"/>
@@ -67569,7 +67567,7 @@
         <v>23</v>
       </c>
       <c r="AG585" t="s" s="2">
-        <v>1404</v>
+        <v>1403</v>
       </c>
       <c r="AH585" t="s" s="2">
         <v>76</v>
@@ -67589,10 +67587,10 @@
         <v>1330</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -67618,10 +67616,10 @@
         <v>199</v>
       </c>
       <c r="M586" t="s" s="2">
+        <v>1407</v>
+      </c>
+      <c r="N586" t="s" s="2">
         <v>1408</v>
-      </c>
-      <c r="N586" t="s" s="2">
-        <v>1409</v>
       </c>
       <c r="O586" s="2"/>
       <c r="P586" s="2"/>
@@ -67672,7 +67670,7 @@
         <v>23</v>
       </c>
       <c r="AG586" t="s" s="2">
-        <v>1407</v>
+        <v>1406</v>
       </c>
       <c r="AH586" t="s" s="2">
         <v>76</v>
@@ -67692,10 +67690,10 @@
         <v>1330</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
@@ -67721,10 +67719,10 @@
         <v>199</v>
       </c>
       <c r="M587" t="s" s="2">
+        <v>1410</v>
+      </c>
+      <c r="N587" t="s" s="2">
         <v>1411</v>
-      </c>
-      <c r="N587" t="s" s="2">
-        <v>1412</v>
       </c>
       <c r="O587" s="2"/>
       <c r="P587" s="2"/>
@@ -67775,7 +67773,7 @@
         <v>23</v>
       </c>
       <c r="AG587" t="s" s="2">
-        <v>1410</v>
+        <v>1409</v>
       </c>
       <c r="AH587" t="s" s="2">
         <v>76</v>
@@ -67795,10 +67793,10 @@
         <v>1330</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -67824,10 +67822,10 @@
         <v>103</v>
       </c>
       <c r="M588" t="s" s="2">
+        <v>1413</v>
+      </c>
+      <c r="N588" t="s" s="2">
         <v>1414</v>
-      </c>
-      <c r="N588" t="s" s="2">
-        <v>1415</v>
       </c>
       <c r="O588" s="2"/>
       <c r="P588" s="2"/>
@@ -67858,7 +67856,7 @@
       </c>
       <c r="Z588" s="2"/>
       <c r="AA588" t="s" s="2">
-        <v>1416</v>
+        <v>1415</v>
       </c>
       <c r="AB588" t="s" s="2">
         <v>23</v>
@@ -67876,7 +67874,7 @@
         <v>23</v>
       </c>
       <c r="AG588" t="s" s="2">
-        <v>1413</v>
+        <v>1412</v>
       </c>
       <c r="AH588" t="s" s="2">
         <v>76</v>
@@ -67896,10 +67894,10 @@
         <v>1330</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -67925,13 +67923,13 @@
         <v>103</v>
       </c>
       <c r="M589" t="s" s="2">
+        <v>1417</v>
+      </c>
+      <c r="N589" t="s" s="2">
         <v>1418</v>
       </c>
-      <c r="N589" t="s" s="2">
+      <c r="O589" t="s" s="2">
         <v>1419</v>
-      </c>
-      <c r="O589" t="s" s="2">
-        <v>1420</v>
       </c>
       <c r="P589" s="2"/>
       <c r="Q589" t="s" s="2">
@@ -67961,7 +67959,7 @@
       </c>
       <c r="Z589" s="2"/>
       <c r="AA589" t="s" s="2">
-        <v>1421</v>
+        <v>1420</v>
       </c>
       <c r="AB589" t="s" s="2">
         <v>23</v>
@@ -67979,7 +67977,7 @@
         <v>23</v>
       </c>
       <c r="AG589" t="s" s="2">
-        <v>1417</v>
+        <v>1416</v>
       </c>
       <c r="AH589" t="s" s="2">
         <v>76</v>
@@ -67999,10 +67997,10 @@
         <v>1330</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" t="s" s="2">
@@ -68025,16 +68023,16 @@
         <v>84</v>
       </c>
       <c r="L590" t="s" s="2">
+        <v>1422</v>
+      </c>
+      <c r="M590" t="s" s="2">
         <v>1423</v>
       </c>
-      <c r="M590" t="s" s="2">
+      <c r="N590" t="s" s="2">
         <v>1424</v>
       </c>
-      <c r="N590" t="s" s="2">
+      <c r="O590" t="s" s="2">
         <v>1425</v>
-      </c>
-      <c r="O590" t="s" s="2">
-        <v>1426</v>
       </c>
       <c r="P590" s="2"/>
       <c r="Q590" t="s" s="2">
@@ -68084,7 +68082,7 @@
         <v>23</v>
       </c>
       <c r="AG590" t="s" s="2">
-        <v>1422</v>
+        <v>1421</v>
       </c>
       <c r="AH590" t="s" s="2">
         <v>76</v>
@@ -68104,10 +68102,10 @@
         <v>1330</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -68133,16 +68131,16 @@
         <v>103</v>
       </c>
       <c r="M591" t="s" s="2">
+        <v>1427</v>
+      </c>
+      <c r="N591" t="s" s="2">
         <v>1428</v>
       </c>
-      <c r="N591" t="s" s="2">
+      <c r="O591" t="s" s="2">
         <v>1429</v>
       </c>
-      <c r="O591" t="s" s="2">
+      <c r="P591" t="s" s="2">
         <v>1430</v>
-      </c>
-      <c r="P591" t="s" s="2">
-        <v>1431</v>
       </c>
       <c r="Q591" t="s" s="2">
         <v>23</v>
@@ -68171,7 +68169,7 @@
       </c>
       <c r="Z591" s="2"/>
       <c r="AA591" t="s" s="2">
-        <v>1432</v>
+        <v>1431</v>
       </c>
       <c r="AB591" t="s" s="2">
         <v>23</v>
@@ -68189,7 +68187,7 @@
         <v>23</v>
       </c>
       <c r="AG591" t="s" s="2">
-        <v>1427</v>
+        <v>1426</v>
       </c>
       <c r="AH591" t="s" s="2">
         <v>76</v>
@@ -68209,10 +68207,10 @@
         <v>1330</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" t="s" s="2">
@@ -68238,10 +68236,10 @@
         <v>130</v>
       </c>
       <c r="M592" t="s" s="2">
+        <v>1433</v>
+      </c>
+      <c r="N592" t="s" s="2">
         <v>1434</v>
-      </c>
-      <c r="N592" t="s" s="2">
-        <v>1435</v>
       </c>
       <c r="O592" s="2"/>
       <c r="P592" s="2"/>
@@ -68292,7 +68290,7 @@
         <v>23</v>
       </c>
       <c r="AG592" t="s" s="2">
-        <v>1433</v>
+        <v>1432</v>
       </c>
       <c r="AH592" t="s" s="2">
         <v>76</v>
@@ -68312,10 +68310,10 @@
         <v>1330</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
@@ -68338,16 +68336,16 @@
         <v>84</v>
       </c>
       <c r="L593" t="s" s="2">
-        <v>370</v>
+        <v>369</v>
       </c>
       <c r="M593" t="s" s="2">
+        <v>1436</v>
+      </c>
+      <c r="N593" t="s" s="2">
         <v>1437</v>
       </c>
-      <c r="N593" t="s" s="2">
+      <c r="O593" t="s" s="2">
         <v>1438</v>
-      </c>
-      <c r="O593" t="s" s="2">
-        <v>1439</v>
       </c>
       <c r="P593" s="2"/>
       <c r="Q593" t="s" s="2">
@@ -68376,11 +68374,11 @@
         <v>107</v>
       </c>
       <c r="Z593" t="s" s="2">
+        <v>1439</v>
+      </c>
+      <c r="AA593" t="s" s="2">
         <v>1440</v>
       </c>
-      <c r="AA593" t="s" s="2">
-        <v>1441</v>
-      </c>
       <c r="AB593" t="s" s="2">
         <v>23</v>
       </c>
@@ -68397,7 +68395,7 @@
         <v>23</v>
       </c>
       <c r="AG593" t="s" s="2">
-        <v>1436</v>
+        <v>1435</v>
       </c>
       <c r="AH593" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-02-26T16:36:39+00:00</t>
+    <t>2026-03-03T08:59:33+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1884,13 +1884,13 @@
 </t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device)
+    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|Device|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
 </t>
   </si>
   <si>
     <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
-des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung.</t>
+des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur zur Änderung der Reihenfolge der Planeinträge oder nachdem er Einträge gelöscht hat.</t>
   </si>
   <si>
     <t>The entity responsible for deciding what the contents of the list were. Where the list was created by a human, this is the same as the author of the list.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T08:59:33+00:00</t>
+    <t>2026-03-03T14:03:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1072,7 +1072,7 @@
     <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-emed-bundle-tx-medikationsplan</t>
   </si>
   <si>
-    <t>AtEmedBundleMedikationsplanTx</t>
+    <t>AtEmedBundleTxMedikationsplan</t>
   </si>
   <si>
     <t>ELGA e-Med Medikationsplan Transaction Bundle</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-03T14:03:22+00:00</t>
+    <t>2026-03-05T12:55:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T12:55:37+00:00</t>
+    <t>2026-03-05T13:31:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-05T13:31:59+00:00</t>
+    <t>2026-03-06T12:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3323,6 +3323,7 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="2"/&gt;
+    &lt;display value="Geplante Abgabe"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -3925,6 +3926,7 @@
   &lt;coding&gt;
     &lt;system value="https://fhir.hl7.at/elga/emed/r4/CodeSystem/MedicationRequestCategoryCS"/&gt;
     &lt;code value="1"/&gt;
+    &lt;display value="Medikationsplaneintrag"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-06T14:18:10+00:00</t>
+    <t>2026-03-09T08:14:04+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T08:14:04+00:00</t>
+    <t>2026-03-09T10:03:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T10:03:26+00:00</t>
+    <t>2026-03-09T11:27:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-09T11:27:52+00:00</t>
+    <t>2026-03-10T08:28:41+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20088" uniqueCount="1454">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="20088" uniqueCount="1455">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T08:28:41+00:00</t>
+    <t>2026-03-10T11:00:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2112,7 +2112,7 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Externer Identifier.</t>
+    <t>Durchgeführte-Abgabe-ID ? Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -2128,7 +2128,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis. Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Auslösendes Ereignis. Referenz auf Procedure-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -3118,7 +3118,7 @@
   <si>
     <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
 Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
-Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), die auch im e-Rezept mitgeführt wird.
+Als groupIdentifier dient die Geplante-Abgabe-ID, die auch im e-Rezept mitgeführt wird.
 Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
@@ -3242,9 +3242,7 @@
     <t>MedicationRequest.identifier</t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID = {groupIdentifier}_{Medikationsplaneintrag-ID}.
-Setzt sich zusammen aus: groupIdentifier (Rezept-Klammer) und Medikationsplaneintrag-ID.
-Wenn mehrere Medikamente gleichzeitig verordnet wurden, haben sie den gleichen groupIdentifier, aber unterschiedliche Medikationsplaneintrag-IDs.</t>
+    <t>Gepante-Abgabe-ID ? Verwendung prüfen.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -3450,8 +3448,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t>Patient, für den die geplante Abgabe ausgestellt werden soll, der über den 
-Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
+    <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -3495,8 +3492,8 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist.
-Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
+    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
+(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -3541,7 +3538,7 @@
   </si>
   <si>
     <t>Grund für die Verordnung des Arzneimittels. 
-Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
+Entweder Code oder Referenz (TODO: Evtl. Invariante). Verwendung in geplanter Abgabe prüfen.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -3579,8 +3576,8 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, die von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The URL pointing to a protocol, guideline, orderset, or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -3589,8 +3586,8 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, die von diesem 
-Medikationsplaneintrag ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The URL pointing to an externally maintained protocol, guideline, orderset or other definition that is adhered to in whole or in part by this MedicationRequest.</t>
@@ -3608,8 +3605,8 @@
     <t>MedicationRequest.groupIdentifier</t>
   </si>
   <si>
-    <t>Als groupIdentifier dient die Geplante-Abgabe-ID (früher eMED-ID), 
-die auch im e-Rezept mitgeführt wird. Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
+    <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
+Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
 wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
@@ -3663,7 +3660,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
+    <t>Angabe der Dosierinformationen. TODO: Dosiervarianten.</t>
   </si>
   <si>
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
@@ -3833,7 +3830,7 @@
     <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
 Erläutert die Absicht des verschreibenden Arztes. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. 
 Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. 
-TODO: Eher keine Verwendung in der geplanten Abgabe.</t>
+TODO: Verwendung in der geplanten Abgabe prüfen.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -4029,7 +4026,7 @@
     <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Vermutlich nicht möglich, da keine versionsspezifischen Referenzen verwendet werden.</t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
+    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
   </si>
   <si>
     <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
@@ -4039,6 +4036,9 @@
   </si>
   <si>
     <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error Informationen.</t>
+  </si>
+  <si>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
   </si>
   <si>
     <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan. Keine Verwendung im Medikationsplaneintrag.</t>
@@ -6130,7 +6130,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
     </row>
     <row r="179">
@@ -6138,7 +6138,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="180">
@@ -6154,7 +6154,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="182">
@@ -6162,7 +6162,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="183">
@@ -6224,7 +6224,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="191">
@@ -6260,7 +6260,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="196">
@@ -6268,7 +6268,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="197">
@@ -6300,7 +6300,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
     </row>
     <row r="201">
@@ -6308,7 +6308,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
     </row>
     <row r="202">
@@ -6324,7 +6324,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
     </row>
     <row r="204">
@@ -6332,7 +6332,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="205">
@@ -6394,7 +6394,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
     </row>
     <row r="213">
@@ -6430,7 +6430,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
     </row>
     <row r="218">
@@ -6438,7 +6438,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
     </row>
     <row r="219">
@@ -60666,7 +60666,7 @@
         <v>1145</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1146</v>
+        <v>1264</v>
       </c>
       <c r="N519" t="s" s="2">
         <v>790</v>
@@ -60771,7 +60771,7 @@
         <v>136</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="N520" t="s" s="2">
         <v>1150</v>
@@ -61609,7 +61609,7 @@
         <v>506</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="N528" t="s" s="2">
         <v>1163</v>
@@ -61815,7 +61815,7 @@
         <v>1165</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="N530" t="s" s="2">
         <v>1170</v>
@@ -61918,7 +61918,7 @@
         <v>1172</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N531" t="s" s="2">
         <v>1174</v>
@@ -62025,7 +62025,7 @@
         <v>130</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="N532" t="s" s="2">
         <v>1179</v>
@@ -62130,7 +62130,7 @@
         <v>506</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="N533" t="s" s="2">
         <v>1183</v>
@@ -62338,7 +62338,7 @@
         <v>893</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N535" t="s" s="2">
         <v>1199</v>
@@ -62441,7 +62441,7 @@
         <v>136</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="N536" t="s" s="2">
         <v>1202</v>
@@ -63067,7 +63067,7 @@
         <v>757</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="N542" t="s" s="2">
         <v>1217</v>
@@ -63170,7 +63170,7 @@
         <v>817</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N543" t="s" s="2">
         <v>1220</v>
@@ -63275,7 +63275,7 @@
         <v>822</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="N544" t="s" s="2">
         <v>1223</v>
@@ -63348,13 +63348,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63434,7 +63434,7 @@
         <v>23</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63451,13 +63451,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63556,13 +63556,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63659,13 +63659,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63764,13 +63764,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63869,13 +63869,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63974,13 +63974,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -64079,13 +64079,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -64184,13 +64184,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -64291,13 +64291,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -64323,13 +64323,13 @@
         <v>112</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="O554" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
@@ -64379,7 +64379,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64396,13 +64396,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64428,10 +64428,10 @@
         <v>103</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64461,10 +64461,10 @@
         <v>121</v>
       </c>
       <c r="Z555" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="AA555" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="AB555" t="s" s="2">
         <v>23</v>
@@ -64482,7 +64482,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64499,13 +64499,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64531,13 +64531,13 @@
         <v>369</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="O556" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P556" s="2"/>
       <c r="Q556" t="s" s="2">
@@ -64566,10 +64566,10 @@
         <v>939</v>
       </c>
       <c r="Z556" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="AA556" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="AB556" t="s" s="2">
         <v>23</v>
@@ -64587,7 +64587,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64604,13 +64604,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64636,13 +64636,13 @@
         <v>369</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="O557" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="P557" s="2"/>
       <c r="Q557" t="s" s="2">
@@ -64671,10 +64671,10 @@
         <v>374</v>
       </c>
       <c r="Z557" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="AA557" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AB557" t="s" s="2">
         <v>23</v>
@@ -64692,7 +64692,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>83</v>
@@ -64709,13 +64709,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64741,10 +64741,10 @@
         <v>141</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
@@ -64795,7 +64795,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64812,13 +64812,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64844,10 +64844,10 @@
         <v>136</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
@@ -64855,7 +64855,7 @@
         <v>23</v>
       </c>
       <c r="R559" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="S559" t="s" s="2">
         <v>23</v>
@@ -64900,7 +64900,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64917,13 +64917,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -65020,13 +65020,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -65125,13 +65125,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -65232,13 +65232,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -65264,10 +65264,10 @@
         <v>112</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" s="2"/>
@@ -65318,7 +65318,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65335,13 +65335,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65367,10 +65367,10 @@
         <v>587</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="O564" s="2"/>
       <c r="P564" s="2"/>
@@ -65421,7 +65421,7 @@
         <v>23</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -65438,13 +65438,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65470,10 +65470,10 @@
         <v>506</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -65524,7 +65524,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -65541,13 +65541,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -65573,10 +65573,10 @@
         <v>136</v>
       </c>
       <c r="M566" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="N566" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="O566" s="2"/>
       <c r="P566" s="2"/>
@@ -65627,7 +65627,7 @@
         <v>23</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>76</v>
@@ -65644,13 +65644,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -65747,13 +65747,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65852,13 +65852,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -65959,13 +65959,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -65991,10 +65991,10 @@
         <v>494</v>
       </c>
       <c r="M570" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="N570" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="O570" s="2"/>
       <c r="P570" s="2"/>
@@ -66045,7 +66045,7 @@
         <v>23</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>
@@ -66062,13 +66062,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -66091,13 +66091,13 @@
         <v>84</v>
       </c>
       <c r="L571" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="M571" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="N571" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="O571" s="2"/>
       <c r="P571" s="2"/>
@@ -66127,10 +66127,10 @@
         <v>374</v>
       </c>
       <c r="Z571" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="AA571" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AB571" t="s" s="2">
         <v>23</v>
@@ -66148,7 +66148,7 @@
         <v>23</v>
       </c>
       <c r="AG571" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="AH571" t="s" s="2">
         <v>83</v>
@@ -66165,13 +66165,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -66197,13 +66197,13 @@
         <v>78</v>
       </c>
       <c r="M572" t="s" s="2">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="N572" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="O572" t="s" s="2">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="P572" s="2"/>
       <c r="Q572" t="s" s="2">
@@ -66253,7 +66253,7 @@
         <v>23</v>
       </c>
       <c r="AG572" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="AH572" t="s" s="2">
         <v>76</v>
@@ -66270,13 +66270,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -66373,13 +66373,13 @@
     </row>
     <row r="574">
       <c r="A574" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B574" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C574" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D574" s="2"/>
       <c r="E574" t="s" s="2">
@@ -66478,13 +66478,13 @@
     </row>
     <row r="575">
       <c r="A575" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B575" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="C575" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="D575" s="2"/>
       <c r="E575" t="s" s="2">
@@ -66585,13 +66585,13 @@
     </row>
     <row r="576">
       <c r="A576" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B576" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C576" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D576" s="2"/>
       <c r="E576" t="s" s="2">
@@ -66617,14 +66617,14 @@
         <v>587</v>
       </c>
       <c r="M576" t="s" s="2">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="N576" t="s" s="2">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="O576" s="2"/>
       <c r="P576" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="Q576" t="s" s="2">
         <v>23</v>
@@ -66673,7 +66673,7 @@
         <v>23</v>
       </c>
       <c r="AG576" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="AH576" t="s" s="2">
         <v>76</v>
@@ -66690,13 +66690,13 @@
     </row>
     <row r="577">
       <c r="A577" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B577" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C577" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D577" s="2"/>
       <c r="E577" t="s" s="2">
@@ -66722,14 +66722,14 @@
         <v>420</v>
       </c>
       <c r="M577" t="s" s="2">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="N577" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="O577" s="2"/>
       <c r="P577" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="Q577" t="s" s="2">
         <v>23</v>
@@ -66778,7 +66778,7 @@
         <v>23</v>
       </c>
       <c r="AG577" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="AH577" t="s" s="2">
         <v>76</v>
@@ -66790,18 +66790,18 @@
         <v>23</v>
       </c>
       <c r="AK577" t="s" s="2">
-        <v>1363</v>
+        <v>1364</v>
       </c>
     </row>
     <row r="578">
       <c r="A578" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B578" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="C578" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="D578" s="2"/>
       <c r="E578" t="s" s="2">
@@ -66898,13 +66898,13 @@
     </row>
     <row r="579">
       <c r="A579" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B579" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C579" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D579" s="2"/>
       <c r="E579" t="s" s="2">
@@ -67003,13 +67003,13 @@
     </row>
     <row r="580">
       <c r="A580" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B580" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="C580" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D580" s="2"/>
       <c r="E580" t="s" s="2">
@@ -67032,13 +67032,13 @@
         <v>84</v>
       </c>
       <c r="L580" t="s" s="2">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="M580" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N580" t="s" s="2">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="O580" s="2"/>
       <c r="P580" s="2"/>
@@ -67087,7 +67087,7 @@
         <v>357</v>
       </c>
       <c r="AG580" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="AH580" t="s" s="2">
         <v>76</v>
@@ -67104,16 +67104,16 @@
     </row>
     <row r="581">
       <c r="A581" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B581" t="s" s="2">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="C581" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="D581" t="s" s="2">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="E581" t="s" s="2">
         <v>23</v>
@@ -67138,10 +67138,10 @@
         <v>1172</v>
       </c>
       <c r="M581" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="N581" t="s" s="2">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="O581" s="2"/>
       <c r="P581" s="2"/>
@@ -67192,7 +67192,7 @@
         <v>23</v>
       </c>
       <c r="AG581" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="AH581" t="s" s="2">
         <v>76</v>
@@ -67209,13 +67209,13 @@
     </row>
     <row r="582">
       <c r="A582" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B582" t="s" s="2">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C582" t="s" s="2">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="D582" s="2"/>
       <c r="E582" t="s" s="2">
@@ -67312,13 +67312,13 @@
     </row>
     <row r="583">
       <c r="A583" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B583" t="s" s="2">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="C583" t="s" s="2">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="D583" s="2"/>
       <c r="E583" t="s" s="2">
@@ -67417,13 +67417,13 @@
     </row>
     <row r="584">
       <c r="A584" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B584" t="s" s="2">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="C584" t="s" s="2">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D584" s="2"/>
       <c r="E584" t="s" s="2">
@@ -67449,13 +67449,13 @@
         <v>587</v>
       </c>
       <c r="M584" t="s" s="2">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="N584" t="s" s="2">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="O584" t="s" s="2">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="P584" s="2"/>
       <c r="Q584" t="s" s="2">
@@ -67505,7 +67505,7 @@
         <v>23</v>
       </c>
       <c r="AG584" t="s" s="2">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="AH584" t="s" s="2">
         <v>76</v>
@@ -67514,7 +67514,7 @@
         <v>83</v>
       </c>
       <c r="AJ584" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="AK584" t="s" s="2">
         <v>95</v>
@@ -67522,13 +67522,13 @@
     </row>
     <row r="585">
       <c r="A585" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B585" t="s" s="2">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="C585" t="s" s="2">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="D585" s="2"/>
       <c r="E585" t="s" s="2">
@@ -67554,20 +67554,20 @@
         <v>587</v>
       </c>
       <c r="M585" t="s" s="2">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="N585" t="s" s="2">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="O585" t="s" s="2">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="P585" s="2"/>
       <c r="Q585" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R585" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="S585" t="s" s="2">
         <v>23</v>
@@ -67612,7 +67612,7 @@
         <v>23</v>
       </c>
       <c r="AG585" t="s" s="2">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="AH585" t="s" s="2">
         <v>76</v>
@@ -67621,7 +67621,7 @@
         <v>83</v>
       </c>
       <c r="AJ585" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="AK585" t="s" s="2">
         <v>95</v>
@@ -67629,13 +67629,13 @@
     </row>
     <row r="586">
       <c r="A586" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B586" t="s" s="2">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="C586" t="s" s="2">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="D586" s="2"/>
       <c r="E586" t="s" s="2">
@@ -67658,19 +67658,19 @@
         <v>84</v>
       </c>
       <c r="L586" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M586" t="s" s="2">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="N586" t="s" s="2">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="O586" t="s" s="2">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="P586" t="s" s="2">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="Q586" t="s" s="2">
         <v>23</v>
@@ -67719,7 +67719,7 @@
         <v>23</v>
       </c>
       <c r="AG586" t="s" s="2">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="AH586" t="s" s="2">
         <v>76</v>
@@ -67736,13 +67736,13 @@
     </row>
     <row r="587">
       <c r="A587" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B587" t="s" s="2">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="C587" t="s" s="2">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="D587" s="2"/>
       <c r="E587" t="s" s="2">
@@ -67765,13 +67765,13 @@
         <v>84</v>
       </c>
       <c r="L587" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M587" t="s" s="2">
-        <v>1397</v>
+        <v>1398</v>
       </c>
       <c r="N587" t="s" s="2">
-        <v>1398</v>
+        <v>1399</v>
       </c>
       <c r="O587" s="2"/>
       <c r="P587" s="2"/>
@@ -67822,7 +67822,7 @@
         <v>23</v>
       </c>
       <c r="AG587" t="s" s="2">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="AH587" t="s" s="2">
         <v>76</v>
@@ -67839,13 +67839,13 @@
     </row>
     <row r="588">
       <c r="A588" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B588" t="s" s="2">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="C588" t="s" s="2">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="D588" s="2"/>
       <c r="E588" t="s" s="2">
@@ -67871,16 +67871,16 @@
         <v>199</v>
       </c>
       <c r="M588" t="s" s="2">
-        <v>1400</v>
+        <v>1401</v>
       </c>
       <c r="N588" t="s" s="2">
-        <v>1401</v>
+        <v>1402</v>
       </c>
       <c r="O588" t="s" s="2">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="P588" t="s" s="2">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="Q588" t="s" s="2">
         <v>23</v>
@@ -67929,7 +67929,7 @@
         <v>23</v>
       </c>
       <c r="AG588" t="s" s="2">
-        <v>1399</v>
+        <v>1400</v>
       </c>
       <c r="AH588" t="s" s="2">
         <v>76</v>
@@ -67946,13 +67946,13 @@
     </row>
     <row r="589">
       <c r="A589" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B589" t="s" s="2">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="C589" t="s" s="2">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="D589" s="2"/>
       <c r="E589" t="s" s="2">
@@ -67978,16 +67978,16 @@
         <v>199</v>
       </c>
       <c r="M589" t="s" s="2">
-        <v>1405</v>
+        <v>1406</v>
       </c>
       <c r="N589" t="s" s="2">
-        <v>1406</v>
+        <v>1407</v>
       </c>
       <c r="O589" t="s" s="2">
-        <v>1402</v>
+        <v>1403</v>
       </c>
       <c r="P589" t="s" s="2">
-        <v>1403</v>
+        <v>1404</v>
       </c>
       <c r="Q589" t="s" s="2">
         <v>23</v>
@@ -68036,7 +68036,7 @@
         <v>23</v>
       </c>
       <c r="AG589" t="s" s="2">
-        <v>1404</v>
+        <v>1405</v>
       </c>
       <c r="AH589" t="s" s="2">
         <v>76</v>
@@ -68053,13 +68053,13 @@
     </row>
     <row r="590">
       <c r="A590" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B590" t="s" s="2">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="C590" t="s" s="2">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="D590" s="2"/>
       <c r="E590" t="s" s="2">
@@ -68085,10 +68085,10 @@
         <v>103</v>
       </c>
       <c r="M590" t="s" s="2">
-        <v>1408</v>
+        <v>1409</v>
       </c>
       <c r="N590" t="s" s="2">
-        <v>1409</v>
+        <v>1410</v>
       </c>
       <c r="O590" s="2"/>
       <c r="P590" s="2"/>
@@ -68118,10 +68118,10 @@
         <v>121</v>
       </c>
       <c r="Z590" t="s" s="2">
-        <v>1410</v>
+        <v>1411</v>
       </c>
       <c r="AA590" t="s" s="2">
-        <v>1411</v>
+        <v>1412</v>
       </c>
       <c r="AB590" t="s" s="2">
         <v>23</v>
@@ -68139,7 +68139,7 @@
         <v>23</v>
       </c>
       <c r="AG590" t="s" s="2">
-        <v>1407</v>
+        <v>1408</v>
       </c>
       <c r="AH590" t="s" s="2">
         <v>76</v>
@@ -68156,13 +68156,13 @@
     </row>
     <row r="591">
       <c r="A591" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B591" t="s" s="2">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="C591" t="s" s="2">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="D591" s="2"/>
       <c r="E591" t="s" s="2">
@@ -68185,13 +68185,13 @@
         <v>84</v>
       </c>
       <c r="L591" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M591" t="s" s="2">
-        <v>1413</v>
+        <v>1414</v>
       </c>
       <c r="N591" t="s" s="2">
-        <v>1414</v>
+        <v>1415</v>
       </c>
       <c r="O591" s="2"/>
       <c r="P591" s="2"/>
@@ -68199,7 +68199,7 @@
         <v>23</v>
       </c>
       <c r="R591" t="s" s="2">
-        <v>1415</v>
+        <v>1416</v>
       </c>
       <c r="S591" t="s" s="2">
         <v>23</v>
@@ -68244,7 +68244,7 @@
         <v>23</v>
       </c>
       <c r="AG591" t="s" s="2">
-        <v>1412</v>
+        <v>1413</v>
       </c>
       <c r="AH591" t="s" s="2">
         <v>76</v>
@@ -68261,13 +68261,13 @@
     </row>
     <row r="592">
       <c r="A592" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B592" t="s" s="2">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="C592" t="s" s="2">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="D592" s="2"/>
       <c r="E592" t="s" s="2">
@@ -68290,13 +68290,13 @@
         <v>84</v>
       </c>
       <c r="L592" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="M592" t="s" s="2">
-        <v>1417</v>
+        <v>1418</v>
       </c>
       <c r="N592" t="s" s="2">
-        <v>1418</v>
+        <v>1419</v>
       </c>
       <c r="O592" s="2"/>
       <c r="P592" s="2"/>
@@ -68347,7 +68347,7 @@
         <v>23</v>
       </c>
       <c r="AG592" t="s" s="2">
-        <v>1416</v>
+        <v>1417</v>
       </c>
       <c r="AH592" t="s" s="2">
         <v>76</v>
@@ -68364,13 +68364,13 @@
     </row>
     <row r="593">
       <c r="A593" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B593" t="s" s="2">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="C593" t="s" s="2">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="D593" s="2"/>
       <c r="E593" t="s" s="2">
@@ -68396,10 +68396,10 @@
         <v>199</v>
       </c>
       <c r="M593" t="s" s="2">
-        <v>1420</v>
+        <v>1421</v>
       </c>
       <c r="N593" t="s" s="2">
-        <v>1421</v>
+        <v>1422</v>
       </c>
       <c r="O593" s="2"/>
       <c r="P593" s="2"/>
@@ -68450,7 +68450,7 @@
         <v>23</v>
       </c>
       <c r="AG593" t="s" s="2">
-        <v>1419</v>
+        <v>1420</v>
       </c>
       <c r="AH593" t="s" s="2">
         <v>76</v>
@@ -68467,13 +68467,13 @@
     </row>
     <row r="594">
       <c r="A594" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B594" t="s" s="2">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="C594" t="s" s="2">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="D594" s="2"/>
       <c r="E594" t="s" s="2">
@@ -68499,10 +68499,10 @@
         <v>199</v>
       </c>
       <c r="M594" t="s" s="2">
-        <v>1423</v>
+        <v>1424</v>
       </c>
       <c r="N594" t="s" s="2">
-        <v>1424</v>
+        <v>1425</v>
       </c>
       <c r="O594" s="2"/>
       <c r="P594" s="2"/>
@@ -68553,7 +68553,7 @@
         <v>23</v>
       </c>
       <c r="AG594" t="s" s="2">
-        <v>1422</v>
+        <v>1423</v>
       </c>
       <c r="AH594" t="s" s="2">
         <v>76</v>
@@ -68570,13 +68570,13 @@
     </row>
     <row r="595">
       <c r="A595" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B595" t="s" s="2">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="C595" t="s" s="2">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="D595" s="2"/>
       <c r="E595" t="s" s="2">
@@ -68602,10 +68602,10 @@
         <v>103</v>
       </c>
       <c r="M595" t="s" s="2">
-        <v>1426</v>
+        <v>1427</v>
       </c>
       <c r="N595" t="s" s="2">
-        <v>1427</v>
+        <v>1428</v>
       </c>
       <c r="O595" s="2"/>
       <c r="P595" s="2"/>
@@ -68636,7 +68636,7 @@
       </c>
       <c r="Z595" s="2"/>
       <c r="AA595" t="s" s="2">
-        <v>1428</v>
+        <v>1429</v>
       </c>
       <c r="AB595" t="s" s="2">
         <v>23</v>
@@ -68654,7 +68654,7 @@
         <v>23</v>
       </c>
       <c r="AG595" t="s" s="2">
-        <v>1425</v>
+        <v>1426</v>
       </c>
       <c r="AH595" t="s" s="2">
         <v>76</v>
@@ -68671,13 +68671,13 @@
     </row>
     <row r="596">
       <c r="A596" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B596" t="s" s="2">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="C596" t="s" s="2">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="D596" s="2"/>
       <c r="E596" t="s" s="2">
@@ -68703,13 +68703,13 @@
         <v>103</v>
       </c>
       <c r="M596" t="s" s="2">
-        <v>1430</v>
+        <v>1431</v>
       </c>
       <c r="N596" t="s" s="2">
-        <v>1431</v>
+        <v>1432</v>
       </c>
       <c r="O596" t="s" s="2">
-        <v>1432</v>
+        <v>1433</v>
       </c>
       <c r="P596" s="2"/>
       <c r="Q596" t="s" s="2">
@@ -68739,7 +68739,7 @@
       </c>
       <c r="Z596" s="2"/>
       <c r="AA596" t="s" s="2">
-        <v>1433</v>
+        <v>1434</v>
       </c>
       <c r="AB596" t="s" s="2">
         <v>23</v>
@@ -68757,7 +68757,7 @@
         <v>23</v>
       </c>
       <c r="AG596" t="s" s="2">
-        <v>1429</v>
+        <v>1430</v>
       </c>
       <c r="AH596" t="s" s="2">
         <v>76</v>
@@ -68774,13 +68774,13 @@
     </row>
     <row r="597">
       <c r="A597" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B597" t="s" s="2">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="C597" t="s" s="2">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="D597" s="2"/>
       <c r="E597" t="s" s="2">
@@ -68803,16 +68803,16 @@
         <v>84</v>
       </c>
       <c r="L597" t="s" s="2">
-        <v>1435</v>
+        <v>1436</v>
       </c>
       <c r="M597" t="s" s="2">
-        <v>1436</v>
+        <v>1437</v>
       </c>
       <c r="N597" t="s" s="2">
-        <v>1437</v>
+        <v>1438</v>
       </c>
       <c r="O597" t="s" s="2">
-        <v>1438</v>
+        <v>1439</v>
       </c>
       <c r="P597" s="2"/>
       <c r="Q597" t="s" s="2">
@@ -68862,7 +68862,7 @@
         <v>23</v>
       </c>
       <c r="AG597" t="s" s="2">
-        <v>1434</v>
+        <v>1435</v>
       </c>
       <c r="AH597" t="s" s="2">
         <v>76</v>
@@ -68879,13 +68879,13 @@
     </row>
     <row r="598">
       <c r="A598" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B598" t="s" s="2">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="C598" t="s" s="2">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="D598" s="2"/>
       <c r="E598" t="s" s="2">
@@ -68911,16 +68911,16 @@
         <v>103</v>
       </c>
       <c r="M598" t="s" s="2">
-        <v>1440</v>
+        <v>1441</v>
       </c>
       <c r="N598" t="s" s="2">
-        <v>1441</v>
+        <v>1442</v>
       </c>
       <c r="O598" t="s" s="2">
-        <v>1442</v>
+        <v>1443</v>
       </c>
       <c r="P598" t="s" s="2">
-        <v>1443</v>
+        <v>1444</v>
       </c>
       <c r="Q598" t="s" s="2">
         <v>23</v>
@@ -68949,7 +68949,7 @@
       </c>
       <c r="Z598" s="2"/>
       <c r="AA598" t="s" s="2">
-        <v>1444</v>
+        <v>1445</v>
       </c>
       <c r="AB598" t="s" s="2">
         <v>23</v>
@@ -68967,7 +68967,7 @@
         <v>23</v>
       </c>
       <c r="AG598" t="s" s="2">
-        <v>1439</v>
+        <v>1440</v>
       </c>
       <c r="AH598" t="s" s="2">
         <v>76</v>
@@ -68984,13 +68984,13 @@
     </row>
     <row r="599">
       <c r="A599" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B599" t="s" s="2">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="C599" t="s" s="2">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="D599" s="2"/>
       <c r="E599" t="s" s="2">
@@ -69016,10 +69016,10 @@
         <v>130</v>
       </c>
       <c r="M599" t="s" s="2">
-        <v>1446</v>
+        <v>1447</v>
       </c>
       <c r="N599" t="s" s="2">
-        <v>1447</v>
+        <v>1448</v>
       </c>
       <c r="O599" s="2"/>
       <c r="P599" s="2"/>
@@ -69070,7 +69070,7 @@
         <v>23</v>
       </c>
       <c r="AG599" t="s" s="2">
-        <v>1445</v>
+        <v>1446</v>
       </c>
       <c r="AH599" t="s" s="2">
         <v>76</v>
@@ -69087,13 +69087,13 @@
     </row>
     <row r="600">
       <c r="A600" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="B600" t="s" s="2">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="C600" t="s" s="2">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="D600" s="2"/>
       <c r="E600" t="s" s="2">
@@ -69119,13 +69119,13 @@
         <v>369</v>
       </c>
       <c r="M600" t="s" s="2">
-        <v>1449</v>
+        <v>1450</v>
       </c>
       <c r="N600" t="s" s="2">
-        <v>1450</v>
+        <v>1451</v>
       </c>
       <c r="O600" t="s" s="2">
-        <v>1451</v>
+        <v>1452</v>
       </c>
       <c r="P600" s="2"/>
       <c r="Q600" t="s" s="2">
@@ -69154,10 +69154,10 @@
         <v>107</v>
       </c>
       <c r="Z600" t="s" s="2">
-        <v>1452</v>
+        <v>1453</v>
       </c>
       <c r="AA600" t="s" s="2">
-        <v>1453</v>
+        <v>1454</v>
       </c>
       <c r="AB600" t="s" s="2">
         <v>23</v>
@@ -69175,7 +69175,7 @@
         <v>23</v>
       </c>
       <c r="AG600" t="s" s="2">
-        <v>1448</v>
+        <v>1449</v>
       </c>
       <c r="AH600" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-10T11:00:19+00:00</t>
+    <t>2026-03-10T11:31:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2153,7 +2153,7 @@
     <t>MedicationDispense.statusReason[x]</t>
   </si>
   <si>
-    <t>Warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
+    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
   </si>
   <si>
     <t>Indicates the reason why a dispense was not performed.</t>
@@ -2184,7 +2184,7 @@
 </t>
   </si>
   <si>
-    <t>Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Referenz auf DetectedIssue-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
@@ -2300,7 +2300,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t>Österreichischer Patient für den die durchgeführte Abgabe ausgestellt wird.</t>
+    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -2379,7 +2379,9 @@
 </t>
   </si>
   <si>
-    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization; entfernen: Patient, Device, RelatedPerson</t>
+    <t>RefrenzReference auf Practitioner, PractitionerRole, Organization (entfernen: Patient, Device, RelatedPerson), 
+die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+auf die ELGA e-Medikation des Patienten zuzugreifen)</t>
   </si>
   <si>
     <t>The device, practitioner, etc. who performed the action.  It should be assumed that the actor is the dispenser of the medication.</t>
@@ -2405,7 +2407,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe.</t>
+    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -2501,10 +2503,7 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
-Wenn sich die Dosis oder Dosierungsrate über den gesamten Verabreichungszeitraum ändern soll 
-(z.B. bei verschreibungspflichtigen Medikamenten mit schrittweiser Dosierungsreduktion), 
-müssen mehrere Dosierungsanweisungen bereitgestellt werden, um die verschiedenen Dosen/Dosierungsraten zu vermitteln. 
+    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. TODO: Dosiervarianten.
 Der Apotheker überprüft die Medikamentenbestellung vor der Abgabe und aktualisiert die Dosierungsanweisung auf der Grundlage 
 des tatsächlich abgegebenen Produkts.</t>
   </si>
@@ -2519,7 +2518,8 @@
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
+    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. 
+Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
@@ -2597,7 +2597,7 @@
 </t>
   </si>
   <si>
-    <t>Referenenz auf DetectedIssue Ressource. Verwendung prüfen.</t>
+    <t>Referenenz auf DetectedIssue Ressource, daher keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. drug-drug interaction, duplicate therapy, dosage alert etc.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T13:50:58+00:00</t>
+    <t>2026-03-20T15:30:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2162,14 +2162,16 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe: &lt;br&gt;
-"completed": durchgeführte Abgabe ist abgeschlossen &lt;br&gt;
-"entered-in-error": durchgeführte Abgabe wird aufgrund falscher Eingabe storniert &lt;br&gt;
-"stopped": Abgabe wird nicht durchgeführt (Medikament wird abgesetzt) &lt;br&gt;
-http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1</t>
-  </si>
-  <si>
-    <t>A code specifying the state of the set of dispense events.</t>
+    <t>Status der durchgeführten Abgabe: completed | entered-in-error | stopped. Details siehe Definition.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">* **\"completed\"**: Die durchgeführte Abgabe ist abgeschlossen. 
+* **\"entered-in-error\"**: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.
+* **\"stopped\"**: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt). 
+http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
+TODO: zu prüfen: 
+* ob es einen Status in-progress / preparation geben soll, z.B. wenn Bestellvorgang gestartet wurde und der typ First Fill - Part Fill ist.
+* Technische Prüfungen bezüglich Abhängigkeiten von status, typ, Rezeptart? automatisch geprüft werden? Falls der Status vom Typ der geplanten Abgabe (Rezeptart) abhängig sein kann (z.B. in-progress bei Bestellung o.ä.), evtl Operation </t>
   </si>
   <si>
     <t>A coded concept specifying the state of the dispense event.</t>
@@ -2282,7 +2284,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -2309,7 +2311,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Verwendung in der durchgeführten Abgabe prüfen.</t>
+    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -2393,7 +2395,7 @@
     <t>MedicationDispense.quantity</t>
   </si>
   <si>
-    <t>Abgegebene Menge und Einheit.</t>
+    <t>Abgegebene Packungsanzahl.</t>
   </si>
   <si>
     <t>The amount of medication that has been dispensed. Includes unit of measure.</t>
@@ -2429,7 +2431,7 @@
     <t>MedicationDispense.destination</t>
   </si>
   <si>
-    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Verwendung prüfen.</t>
+    <t>Ort an den das Medikament geschickt wurde (Referenz auf Location Ressource). Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Identification of the facility/location where the medication was shipped to, as part of the dispense event.</t>
@@ -2438,11 +2440,11 @@
     <t>MedicationDispense.receiver</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner)
+    <t xml:space="preserve">Reference(Patient|4.0.1|Practitioner|4.0.1)
 </t>
   </si>
   <si>
-    <t>Person, die das Medikament abgeholt hat. Verwendung prüfen.</t>
+    <t>Person, die das Medikament abgeholt hat. Referenz auf Patient oder Practitioner. Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Identifies the person who picked up the medication.  This will usually be a patient or their caregiver, but some cases exist where it can be a healthcare professional.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19196" uniqueCount="1397">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19196" uniqueCount="1398">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-20T15:30:14+00:00</t>
+    <t>2026-03-24T10:00:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1640,8 +1640,7 @@
   <si>
     <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
 Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
-Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus (weitere Elemente sind noch zu klären).
-TODO: Invariante, dass überall in der List der gleiche Patient enthalten sein muss</t>
+Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
   </si>
   <si>
     <t>List</t>
@@ -2008,7 +2007,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme des Medikationsplaneintrags. Fachlich zu klären.</t>
+    <t>Datum der Aufnahme / Änderung des Medikationsplaneintrags. Fachlich zu klären.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -3750,20 +3749,29 @@
     <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
   </si>
   <si>
-    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen.
+    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen. Details zur Herstellung von Bezügen von geänderten Planeinträgen, siehe Definition.</t>
+  </si>
+  <si>
+    <t>Medikationsplaneintrag-ID.
 Evt. mit Zeitstempel (Planeintrag-ID_{Zeitstempel}) zur Herstellung eines Bezugs von geänderten Planeinträgen.
 Vorteil: 
 - Auch wenn sich die PZN ändert, aber logisch der gleiche Eintrag betroffen ist (z.B. Austausch eines Arzneimittels durch ein anderes mit weniger Wechselwirkung), kann ein Bezug hergestellt werden.
 - Wenn zur Vorversion des Eintrags bereits eine geplante Abgabe erstellt wurde, kann ein Bezug zum ursprünglichen Eintrag hergestellt werden.
 Nachteil: 
 - Falls Planeinträge mit komplett neuer Arznei überschrieben werden, entsteht dadurch ein verwirrender Bezug. 
-- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Client.</t>
-  </si>
-  <si>
-    <t>Status des Medikationsplaneintrags. VS Einschränkung auf active, complete, on-hold, stopped (?); TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Auch im Kontext mit statusReason, wo dieser Grund codiert angegeben werden kann (entfernt: cancelled, entered-in-error, draft, unknown)</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
+- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Ersteller des Eintrags.</t>
+  </si>
+  <si>
+    <t>Status des Medikationsplaneintrags. active | completed | on-hold | stopped. TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Details siehe Definition.</t>
+  </si>
+  <si>
+    <t>Status des Medikationsplaneintrags:
+* \"active\": aktive Therapie; soll aktuell vom Patienten eingenommen werden
+* \"completed\": Therapie regulär abgeschlossen
+* \"on-hold\": Therapie vorübergehend unterbrochen; Wiederaufnahme vorgesehen
+* \"stopped\": begonnen Therapie, aber vorzeitig und ohne regulären Abschluss beendet
+(nicht verwendet: cancelled, entered-in-error, draft, unknown)
+https://hl7.org/fhir/R4/valueset-medicationrequest-status.html</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
@@ -3861,7 +3869,7 @@
     <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe (z.B. saisonal). Verwendung im Medikationsplaneintrag prüfen (dosageInstruction), evtl. durch Dosierungsinformationen abgedeck.</t>
+    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal. Verwendung im Medikationsplaneintrag prüfen, evtl. durch Dosierungsinformationen abgedeckt.</t>
   </si>
   <si>
     <t>Keine Verwendung im Medikationsplaneintrag.</t>
@@ -5971,7 +5979,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
     </row>
     <row r="179">
@@ -5979,7 +5987,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
     </row>
     <row r="180">
@@ -5995,7 +6003,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
     </row>
     <row r="182">
@@ -6003,7 +6011,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
     </row>
     <row r="183">
@@ -6065,7 +6073,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
     </row>
     <row r="191">
@@ -6101,7 +6109,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
     </row>
     <row r="196">
@@ -6109,7 +6117,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
     </row>
     <row r="197">
@@ -6141,7 +6149,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
     </row>
     <row r="201">
@@ -6149,7 +6157,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
     </row>
     <row r="202">
@@ -6165,7 +6173,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
     </row>
     <row r="204">
@@ -6173,7 +6181,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="205">
@@ -6235,7 +6243,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
     </row>
     <row r="213">
@@ -6271,7 +6279,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
     </row>
     <row r="218">
@@ -6279,7 +6287,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
     </row>
     <row r="219">
@@ -54761,7 +54769,7 @@
         <v>1168</v>
       </c>
       <c r="N464" t="s" s="2">
-        <v>960</v>
+        <v>1169</v>
       </c>
       <c r="O464" t="s" s="2">
         <v>674</v>
@@ -54863,10 +54871,10 @@
         <v>103</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N465" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="O465" t="s" s="2">
         <v>553</v>
@@ -54899,7 +54907,7 @@
       </c>
       <c r="Z465" s="2"/>
       <c r="AA465" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="AB465" t="s" s="2">
         <v>23</v>
@@ -54966,7 +54974,7 @@
         <v>369</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N466" t="s" s="2">
         <v>967</v>
@@ -55071,7 +55079,7 @@
         <v>103</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N467" t="s" s="2">
         <v>973</v>
@@ -55193,7 +55201,7 @@
         <v>23</v>
       </c>
       <c r="T468" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="U468" t="s" s="2">
         <v>23</v>
@@ -55281,7 +55289,7 @@
         <v>103</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N469" t="s" s="2">
         <v>996</v>
@@ -55384,7 +55392,7 @@
         <v>387</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N470" t="s" s="2">
         <v>1001</v>
@@ -55489,7 +55497,7 @@
         <v>1004</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="N471" t="s" s="2">
         <v>1006</v>
@@ -55561,13 +55569,13 @@
         <v>1158</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="C472" t="s" s="2">
         <v>1003</v>
       </c>
       <c r="D472" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="E472" t="s" s="2">
         <v>23</v>
@@ -55589,10 +55597,10 @@
         <v>84</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="N472" t="s" s="2">
         <v>1006</v>
@@ -55666,13 +55674,13 @@
         <v>1158</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="C473" t="s" s="2">
         <v>1003</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="E473" t="s" s="2">
         <v>23</v>
@@ -55697,7 +55705,7 @@
         <v>387</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>1006</v>
@@ -55800,7 +55808,7 @@
         <v>703</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N474" t="s" s="2">
         <v>1009</v>
@@ -55905,7 +55913,7 @@
         <v>577</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="N475" t="s" s="2">
         <v>1013</v>
@@ -56010,7 +56018,7 @@
         <v>583</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
       <c r="N476" t="s" s="2">
         <v>1017</v>
@@ -56115,7 +56123,7 @@
         <v>716</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
       <c r="N477" t="s" s="2">
         <v>1021</v>
@@ -56218,7 +56226,7 @@
         <v>587</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
       <c r="N478" t="s" s="2">
         <v>1024</v>
@@ -56321,7 +56329,7 @@
         <v>732</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
       <c r="N479" t="s" s="2">
         <v>1027</v>
@@ -56424,7 +56432,7 @@
         <v>1029</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="N480" t="s" s="2">
         <v>1030</v>
@@ -56527,7 +56535,7 @@
         <v>369</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
       <c r="N481" t="s" s="2">
         <v>1032</v>
@@ -56632,7 +56640,7 @@
         <v>795</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N482" t="s" s="2">
         <v>1038</v>
@@ -56735,7 +56743,7 @@
         <v>369</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="N483" t="s" s="2">
         <v>1041</v>
@@ -56945,7 +56953,7 @@
         <v>1051</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="N485" t="s" s="2">
         <v>1053</v>
@@ -57048,7 +57056,7 @@
         <v>97</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="N486" t="s" s="2">
         <v>1056</v>
@@ -57148,10 +57156,10 @@
         <v>84</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="N487" t="s" s="2">
         <v>1059</v>
@@ -57254,7 +57262,7 @@
         <v>112</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="N488" t="s" s="2">
         <v>1062</v>
@@ -57359,7 +57367,7 @@
         <v>369</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="N489" t="s" s="2">
         <v>1066</v>
@@ -57464,7 +57472,7 @@
         <v>1071</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="N490" t="s" s="2">
         <v>1073</v>
@@ -57567,7 +57575,7 @@
         <v>607</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="N491" t="s" s="2">
         <v>1076</v>
@@ -57670,7 +57678,7 @@
         <v>1078</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="N492" t="s" s="2">
         <v>773</v>
@@ -57775,7 +57783,7 @@
         <v>136</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="N493" t="s" s="2">
         <v>1083</v>
@@ -58613,7 +58621,7 @@
         <v>506</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="N501" t="s" s="2">
         <v>1096</v>
@@ -58819,7 +58827,7 @@
         <v>1098</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="N503" t="s" s="2">
         <v>1103</v>
@@ -58922,10 +58930,10 @@
         <v>1105</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="O504" t="s" s="2">
         <v>1108</v>
@@ -59134,7 +59142,7 @@
         <v>506</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="N506" t="s" s="2">
         <v>1116</v>
@@ -59342,7 +59350,7 @@
         <v>888</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N508" t="s" s="2">
         <v>1132</v>
@@ -59445,7 +59453,7 @@
         <v>136</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="N509" t="s" s="2">
         <v>1135</v>
@@ -60071,7 +60079,7 @@
         <v>740</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N515" t="s" s="2">
         <v>1150</v>
@@ -60174,7 +60182,7 @@
         <v>800</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="N516" t="s" s="2">
         <v>1153</v>
@@ -60279,7 +60287,7 @@
         <v>805</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="N517" t="s" s="2">
         <v>1156</v>
@@ -60352,13 +60360,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60384,10 +60392,10 @@
         <v>78</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" s="2"/>
@@ -60438,7 +60446,7 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
@@ -60455,13 +60463,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60560,13 +60568,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60663,13 +60671,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60768,13 +60776,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60873,13 +60881,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60978,13 +60986,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -61083,13 +61091,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61188,13 +61196,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61295,13 +61303,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61327,13 +61335,13 @@
         <v>112</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="O527" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="P527" s="2"/>
       <c r="Q527" t="s" s="2">
@@ -61383,7 +61391,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61400,13 +61408,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61432,10 +61440,10 @@
         <v>103</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61465,10 +61473,10 @@
         <v>121</v>
       </c>
       <c r="Z528" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="AA528" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="AB528" t="s" s="2">
         <v>23</v>
@@ -61486,7 +61494,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61503,13 +61511,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61535,13 +61543,13 @@
         <v>369</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="O529" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="P529" s="2"/>
       <c r="Q529" t="s" s="2">
@@ -61567,13 +61575,13 @@
         <v>23</v>
       </c>
       <c r="Y529" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="Z529" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="AA529" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="AB529" t="s" s="2">
         <v>23</v>
@@ -61591,7 +61599,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61608,13 +61616,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61640,13 +61648,13 @@
         <v>369</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="O530" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="P530" s="2"/>
       <c r="Q530" t="s" s="2">
@@ -61675,10 +61683,10 @@
         <v>374</v>
       </c>
       <c r="Z530" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="AA530" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="AB530" t="s" s="2">
         <v>23</v>
@@ -61696,7 +61704,7 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>83</v>
@@ -61713,13 +61721,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61745,10 +61753,10 @@
         <v>141</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
@@ -61799,7 +61807,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61816,13 +61824,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61848,10 +61856,10 @@
         <v>136</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
       <c r="O532" s="2"/>
       <c r="P532" s="2"/>
@@ -61859,7 +61867,7 @@
         <v>23</v>
       </c>
       <c r="R532" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
       <c r="S532" t="s" s="2">
         <v>23</v>
@@ -61904,7 +61912,7 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
@@ -61921,13 +61929,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -62024,13 +62032,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -62129,13 +62137,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -62236,13 +62244,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62268,10 +62276,10 @@
         <v>112</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -62322,7 +62330,7 @@
         <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
@@ -62339,13 +62347,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62371,10 +62379,10 @@
         <v>587</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="O537" s="2"/>
       <c r="P537" s="2"/>
@@ -62425,7 +62433,7 @@
         <v>23</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62442,13 +62450,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62474,10 +62482,10 @@
         <v>506</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="O538" s="2"/>
       <c r="P538" s="2"/>
@@ -62528,7 +62536,7 @@
         <v>23</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
@@ -62545,13 +62553,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62577,10 +62585,10 @@
         <v>136</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" s="2"/>
@@ -62631,7 +62639,7 @@
         <v>23</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
@@ -62648,13 +62656,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62751,13 +62759,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62856,13 +62864,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62963,13 +62971,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62995,10 +63003,10 @@
         <v>494</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -63049,7 +63057,7 @@
         <v>23</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -63066,13 +63074,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -63095,13 +63103,13 @@
         <v>84</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="O544" s="2"/>
       <c r="P544" s="2"/>
@@ -63131,10 +63139,10 @@
         <v>374</v>
       </c>
       <c r="Z544" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="AA544" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="AB544" t="s" s="2">
         <v>23</v>
@@ -63152,7 +63160,7 @@
         <v>23</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>83</v>
@@ -63169,13 +63177,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63201,13 +63209,13 @@
         <v>78</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="O545" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="P545" s="2"/>
       <c r="Q545" t="s" s="2">
@@ -63257,7 +63265,7 @@
         <v>23</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63274,13 +63282,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63377,13 +63385,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63482,13 +63490,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63589,13 +63597,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63621,14 +63629,14 @@
         <v>587</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="O549" s="2"/>
       <c r="P549" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="Q549" t="s" s="2">
         <v>23</v>
@@ -63677,7 +63685,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63694,13 +63702,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63726,14 +63734,14 @@
         <v>420</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="O550" s="2"/>
       <c r="P550" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="Q550" t="s" s="2">
         <v>23</v>
@@ -63782,7 +63790,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63794,18 +63802,18 @@
         <v>23</v>
       </c>
       <c r="AK550" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63902,13 +63910,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -64007,13 +64015,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -64036,13 +64044,13 @@
         <v>84</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
@@ -64091,7 +64099,7 @@
         <v>357</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -64108,16 +64116,16 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="D554" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="E554" t="s" s="2">
         <v>23</v>
@@ -64142,10 +64150,10 @@
         <v>1105</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O554" s="2"/>
       <c r="P554" s="2"/>
@@ -64196,7 +64204,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64213,13 +64221,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64316,13 +64324,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64421,13 +64429,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64453,13 +64461,13 @@
         <v>587</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="O557" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="P557" s="2"/>
       <c r="Q557" t="s" s="2">
@@ -64509,7 +64517,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64518,7 +64526,7 @@
         <v>83</v>
       </c>
       <c r="AJ557" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="AK557" t="s" s="2">
         <v>95</v>
@@ -64526,13 +64534,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64558,20 +64566,20 @@
         <v>587</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="O558" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="P558" s="2"/>
       <c r="Q558" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R558" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="S558" t="s" s="2">
         <v>23</v>
@@ -64616,7 +64624,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64625,7 +64633,7 @@
         <v>83</v>
       </c>
       <c r="AJ558" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="AK558" t="s" s="2">
         <v>95</v>
@@ -64633,13 +64641,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64662,19 +64670,19 @@
         <v>84</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="O559" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="P559" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="Q559" t="s" s="2">
         <v>23</v>
@@ -64723,7 +64731,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64740,13 +64748,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64769,13 +64777,13 @@
         <v>84</v>
       </c>
       <c r="L560" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="O560" s="2"/>
       <c r="P560" s="2"/>
@@ -64826,7 +64834,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64843,13 +64851,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64875,16 +64883,16 @@
         <v>199</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="O561" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="P561" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="Q561" t="s" s="2">
         <v>23</v>
@@ -64933,7 +64941,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64950,13 +64958,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64982,16 +64990,16 @@
         <v>199</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="O562" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="P562" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="Q562" t="s" s="2">
         <v>23</v>
@@ -65040,7 +65048,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -65057,13 +65065,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -65089,10 +65097,10 @@
         <v>103</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" s="2"/>
@@ -65122,10 +65130,10 @@
         <v>121</v>
       </c>
       <c r="Z563" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="AA563" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="AB563" t="s" s="2">
         <v>23</v>
@@ -65143,7 +65151,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65160,13 +65168,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65189,13 +65197,13 @@
         <v>84</v>
       </c>
       <c r="L564" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="O564" s="2"/>
       <c r="P564" s="2"/>
@@ -65203,7 +65211,7 @@
         <v>23</v>
       </c>
       <c r="R564" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="S564" t="s" s="2">
         <v>23</v>
@@ -65248,7 +65256,7 @@
         <v>23</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -65265,13 +65273,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65294,13 +65302,13 @@
         <v>84</v>
       </c>
       <c r="L565" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -65351,7 +65359,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -65368,13 +65376,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -65400,10 +65408,10 @@
         <v>199</v>
       </c>
       <c r="M566" t="s" s="2">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="N566" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="O566" s="2"/>
       <c r="P566" s="2"/>
@@ -65454,7 +65462,7 @@
         <v>23</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>76</v>
@@ -65471,13 +65479,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -65503,10 +65511,10 @@
         <v>199</v>
       </c>
       <c r="M567" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="N567" t="s" s="2">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="O567" s="2"/>
       <c r="P567" s="2"/>
@@ -65557,7 +65565,7 @@
         <v>23</v>
       </c>
       <c r="AG567" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="AH567" t="s" s="2">
         <v>76</v>
@@ -65574,13 +65582,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65606,10 +65614,10 @@
         <v>103</v>
       </c>
       <c r="M568" t="s" s="2">
-        <v>1369</v>
+        <v>1370</v>
       </c>
       <c r="N568" t="s" s="2">
-        <v>1370</v>
+        <v>1371</v>
       </c>
       <c r="O568" s="2"/>
       <c r="P568" s="2"/>
@@ -65640,7 +65648,7 @@
       </c>
       <c r="Z568" s="2"/>
       <c r="AA568" t="s" s="2">
-        <v>1371</v>
+        <v>1372</v>
       </c>
       <c r="AB568" t="s" s="2">
         <v>23</v>
@@ -65658,7 +65666,7 @@
         <v>23</v>
       </c>
       <c r="AG568" t="s" s="2">
-        <v>1368</v>
+        <v>1369</v>
       </c>
       <c r="AH568" t="s" s="2">
         <v>76</v>
@@ -65675,13 +65683,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -65707,13 +65715,13 @@
         <v>103</v>
       </c>
       <c r="M569" t="s" s="2">
-        <v>1373</v>
+        <v>1374</v>
       </c>
       <c r="N569" t="s" s="2">
-        <v>1374</v>
+        <v>1375</v>
       </c>
       <c r="O569" t="s" s="2">
-        <v>1375</v>
+        <v>1376</v>
       </c>
       <c r="P569" s="2"/>
       <c r="Q569" t="s" s="2">
@@ -65743,7 +65751,7 @@
       </c>
       <c r="Z569" s="2"/>
       <c r="AA569" t="s" s="2">
-        <v>1376</v>
+        <v>1377</v>
       </c>
       <c r="AB569" t="s" s="2">
         <v>23</v>
@@ -65761,7 +65769,7 @@
         <v>23</v>
       </c>
       <c r="AG569" t="s" s="2">
-        <v>1372</v>
+        <v>1373</v>
       </c>
       <c r="AH569" t="s" s="2">
         <v>76</v>
@@ -65778,13 +65786,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -65807,16 +65815,16 @@
         <v>84</v>
       </c>
       <c r="L570" t="s" s="2">
-        <v>1378</v>
+        <v>1379</v>
       </c>
       <c r="M570" t="s" s="2">
-        <v>1379</v>
+        <v>1380</v>
       </c>
       <c r="N570" t="s" s="2">
-        <v>1380</v>
+        <v>1381</v>
       </c>
       <c r="O570" t="s" s="2">
-        <v>1381</v>
+        <v>1382</v>
       </c>
       <c r="P570" s="2"/>
       <c r="Q570" t="s" s="2">
@@ -65866,7 +65874,7 @@
         <v>23</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1377</v>
+        <v>1378</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>
@@ -65883,13 +65891,13 @@
     </row>
     <row r="571">
       <c r="A571" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B571" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="C571" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="D571" s="2"/>
       <c r="E571" t="s" s="2">
@@ -65915,16 +65923,16 @@
         <v>103</v>
       </c>
       <c r="M571" t="s" s="2">
-        <v>1383</v>
+        <v>1384</v>
       </c>
       <c r="N571" t="s" s="2">
-        <v>1384</v>
+        <v>1385</v>
       </c>
       <c r="O571" t="s" s="2">
-        <v>1385</v>
+        <v>1386</v>
       </c>
       <c r="P571" t="s" s="2">
-        <v>1386</v>
+        <v>1387</v>
       </c>
       <c r="Q571" t="s" s="2">
         <v>23</v>
@@ -65953,7 +65961,7 @@
       </c>
       <c r="Z571" s="2"/>
       <c r="AA571" t="s" s="2">
-        <v>1387</v>
+        <v>1388</v>
       </c>
       <c r="AB571" t="s" s="2">
         <v>23</v>
@@ -65971,7 +65979,7 @@
         <v>23</v>
       </c>
       <c r="AG571" t="s" s="2">
-        <v>1382</v>
+        <v>1383</v>
       </c>
       <c r="AH571" t="s" s="2">
         <v>76</v>
@@ -65988,13 +65996,13 @@
     </row>
     <row r="572">
       <c r="A572" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B572" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="C572" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="D572" s="2"/>
       <c r="E572" t="s" s="2">
@@ -66020,10 +66028,10 @@
         <v>130</v>
       </c>
       <c r="M572" t="s" s="2">
-        <v>1389</v>
+        <v>1390</v>
       </c>
       <c r="N572" t="s" s="2">
-        <v>1390</v>
+        <v>1391</v>
       </c>
       <c r="O572" s="2"/>
       <c r="P572" s="2"/>
@@ -66074,7 +66082,7 @@
         <v>23</v>
       </c>
       <c r="AG572" t="s" s="2">
-        <v>1388</v>
+        <v>1389</v>
       </c>
       <c r="AH572" t="s" s="2">
         <v>76</v>
@@ -66091,13 +66099,13 @@
     </row>
     <row r="573">
       <c r="A573" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="B573" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="C573" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="D573" s="2"/>
       <c r="E573" t="s" s="2">
@@ -66123,13 +66131,13 @@
         <v>369</v>
       </c>
       <c r="M573" t="s" s="2">
-        <v>1392</v>
+        <v>1393</v>
       </c>
       <c r="N573" t="s" s="2">
-        <v>1393</v>
+        <v>1394</v>
       </c>
       <c r="O573" t="s" s="2">
-        <v>1394</v>
+        <v>1395</v>
       </c>
       <c r="P573" s="2"/>
       <c r="Q573" t="s" s="2">
@@ -66158,10 +66166,10 @@
         <v>107</v>
       </c>
       <c r="Z573" t="s" s="2">
-        <v>1395</v>
+        <v>1396</v>
       </c>
       <c r="AA573" t="s" s="2">
-        <v>1396</v>
+        <v>1397</v>
       </c>
       <c r="AB573" t="s" s="2">
         <v>23</v>
@@ -66179,7 +66187,7 @@
         <v>23</v>
       </c>
       <c r="AG573" t="s" s="2">
-        <v>1391</v>
+        <v>1392</v>
       </c>
       <c r="AH573" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-24T15:12:36+00:00</t>
+    <t>2026-03-27T10:18:57+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2372,7 +2372,9 @@
 </t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
+    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.
+zu prüfen (gemäß CDA): 'Ohne Verordnungsbezug kann nur die Abgabe jener OTC-Präparate in der e-Medikation 
+gespeichert werden, die auch wechselwirkungsrelevant sind.'</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-27T10:18:57+00:00</t>
+    <t>2026-03-30T07:39:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T07:39:16+00:00</t>
+    <t>2026-03-30T10:13:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-03-30T10:13:35+00:00</t>
+    <t>2026-04-01T13:59:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-01T13:59:59+00:00</t>
+    <t>2026-04-02T15:01:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3101,7 +3101,7 @@
 * \"completed\": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) 
 * \"entered-in-error\": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) 
 * \"stopped\": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)
-(nicht verwendet: on-hold, stopped, cancelled, draft, unknown)</t>
+(nicht verwendet: on-hold, cancelled, draft, unknown)</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-02T15:01:02+00:00</t>
+    <t>2026-04-07T09:06:22+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T09:06:22+00:00</t>
+    <t>2026-04-07T15:41:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T15:41:53+00:00</t>
+    <t>2026-04-07T16:09:01+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-07T16:09:01+00:00</t>
+    <t>2026-04-08T18:33:44+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-08T18:33:44+00:00</t>
+    <t>2026-04-09T06:40:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T06:40:16+00:00</t>
+    <t>2026-04-09T18:30:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-09T18:30:31+00:00</t>
+    <t>2026-04-10T11:48:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-10T11:48:51+00:00</t>
+    <t>2026-04-13T14:44:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1639,7 +1639,7 @@
   </si>
   <si>
     <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
-Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle verordneten Arzneimittel und deren Dosierung abbilden.
+Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle geplanten Medikationen und deren Dosierung abbilden.
 Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
   </si>
   <si>
@@ -1732,7 +1732,7 @@
     <t>List.identifier</t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste / des Medikationsplans. Verwendung zu prüfen.</t>
+    <t>Logischer Identfier der Liste (des Medikationsplans) zur Schreibintegritätsprüfung.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -1741,9 +1741,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Verpflichtende Angabe: current | retired. https://hl7.org/fhir/R4/valueset-list-status.html
-TODO: retired nach Ableben des Patienten bis Ende der Aufbewahrungsfrist? automatisch gesetzt?
-entered-in-error nicht sinnvoll</t>
+    <t>Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -1761,8 +1759,7 @@
     <t>List.mode</t>
   </si>
   <si>
-    <t>Verpflichtende Angabe: working | snapshot | changes. https://hl7.org/fhir/R4/valueset-list-mode.html
-Der Medikationsplan ist ein laufend gepflegtes Dokument: working.</t>
+    <t>Der Medikationsplan ist ein laufend gepflegtes Dokument. Fixer Wert: working.</t>
   </si>
   <si>
     <t>How this list was prepared - whether it is a working list that is suitable for being maintained on an ongoing basis, or if it represents a snapshot of a list of items from another source, or whether it is a prepared list where items may be marked as added, modified or deleted.</t>
@@ -1786,7 +1783,7 @@
     <t>List.title</t>
   </si>
   <si>
-    <t>Titel der Liste. Verwendung zu prüfen.</t>
+    <t>Titel der Liste.</t>
   </si>
   <si>
     <t>A label for the list assigned by the author.</t>
@@ -1801,7 +1798,7 @@
     <t>List.code</t>
   </si>
   <si>
-    <t>Code, der den Typ der Liste beschreibt. https://hl7.org/fhir/R4/valueset-list-example-codes.html. Zu prüfen, ob/wie in Medikationsplan verwendet.</t>
+    <t>Code, der den Typ der Liste beschreibt.</t>
   </si>
   <si>
     <t>This code defines the purpose of the list - why it was created.</t>
@@ -1817,7 +1814,7 @@
   &lt;coding&gt;
     &lt;system value="http://snomed.info/sct"/&gt;
     &lt;code value="736378000"/&gt;
-    &lt;display value="Medication management plan (record artifact)"/&gt;
+    &lt;display value="Medikationsplan"/&gt;
   &lt;/coding&gt;
 &lt;/valueCodeableConcept&gt;</t>
   </si>
@@ -1835,7 +1832,7 @@
 </t>
   </si>
   <si>
-    <t>Patient, für den der Medikationsplan erstellt werden soll, der über den 
+    <t>Patient, für den der Medikationsplan dokumentiert wird, der über den 
 Zentralen Patientenindex identifizierbar und Teilnehmer von ELGA e-Medikation ist.</t>
   </si>
   <si>
@@ -1855,7 +1852,7 @@
 </t>
   </si>
   <si>
-    <t>Verwendung zu prüfen.</t>
+    <t>Behandlungskontext, in dem die Liste erstellt wurde.</t>
   </si>
   <si>
     <t>The encounter that is the context in which this list was created.</t>
@@ -1891,7 +1888,7 @@
 </t>
   </si>
   <si>
-    <t>Arzt oder Ärztin, die den Medikationsplans erstellt und für den Inhalt verantwortlich ist. 
+    <t>Arzt oder Ärztin, die den Medikationsplans erstellt hat und für den Inhalt verantwortlich ist. 
 Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation 
 des Patienten zuzugreifen. Device nur für initiale Erstellung durch die Fachanwendung. Patient nur zur Änderung der Reihenfolge der Planeinträge oder nachdem er Einträge gelöscht hat.</t>
   </si>
@@ -1973,16 +1970,10 @@
     <t>List.entry.flag</t>
   </si>
   <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: (example) Unchanged | Changed | Cancelled | Prescribed | Ceased | Suspended. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: 
-* \"Unchanged\": Medikationsplaneintrag bleibt unverändert bestehen
-* \"Changed\": Medikationsplaneintrag wird geändert
-* \"Cancelled\": Medikationsplaneintrag wird storniert
-* \"Prescribed\": Neuer Medikationsplaneintrag wurde hinzugefügt
-* \"Ceased\": Medikationsplaneintrag wird abgesetzt
-* \"Suspended\": Medikationsplaneintrag wird pausiert</t>
+    <t>Kennzeichnet die Art der Änderung des Medikationsplaneintrags: [New | Unchanged | Changed | Removed] Bedeutung: New: Neuer Planeintrag wird hinzugefügt | Unchanged: Bestehender Planeintrag wird beibehalten und zur Kenntnis genommen | Changed: Bestehender Planeintrag wird geändert | Removed: Bestehender Planeintrag wird entfernt</t>
+  </si>
+  <si>
+    <t>The flag allows the system constructing the list to indicate the role and significance of the item in the list.</t>
   </si>
   <si>
     <t>The flag can only be understood in the context of the List.code. If the flag means that the entry has actually been deleted from the list, the deleted element SHALL be true. Deleted can only be used if the List.mode is "changes".</t>
@@ -1991,7 +1982,7 @@
     <t>This field is present to support various clinical uses of lists, such as a discharge summary medication list, where flags specify whether the medication was added, modified, or deleted from the list.</t>
   </si>
   <si>
-    <t>http://hl7.org/fhir/ValueSet/list-item-flag</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEntryFlagVS</t>
   </si>
   <si>
     <t>List.entry.deleted</t>
@@ -2044,13 +2035,10 @@
     <t>List.emptyReason</t>
   </si>
   <si>
-    <t>Begründung, warum der Medikationsplan leer ist: notstarted |  nilknown. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Begründung, warum der Medikationsplan leer ist. Eingeschränkt auf: &lt;vbr&gt;
-    - notstarted: Intitalzustand &lt;br&gt;
-    - nilknown: Patient nimmt derzeit keine Medikamente ein
-https://hl7.org/fhir/R4/valueset-list-empty-reason.html</t>
+    <t>Begründung, warum der Medikationsplan leer ist. Mögliche Ausprägungen: [notstarted |  nilknown] Bedeutung: notstarted: Intitalzustand - noch nie befüllt | nilknown: Patient nimmt derzeit keine Medikamente ein</t>
+  </si>
+  <si>
+    <t>If the list is empty, why the list is empty.</t>
   </si>
   <si>
     <t>The various reasons for an empty list make a significant interpretation to its interpretation. Note that this code is for use when the entire list has been suppressed, and not for when individual items are omitted - implementers may consider using a text note or a flag on an entry in these cases.</t>
@@ -2059,7 +2047,7 @@
     <t>Allows capturing things like "none exist" or "not asked" which can be important for most lists.</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplanEmptyReasonVS</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/ElgaListEmptyReasonVS</t>
   </si>
   <si>
     <t>at-emed-md-durchgefuehrte-abgabe</t>
@@ -34843,10 +34831,10 @@
       </c>
       <c r="R273" s="2"/>
       <c r="S273" t="s" s="2">
-        <v>23</v>
+        <v>561</v>
       </c>
       <c r="T273" t="s" s="2">
-        <v>561</v>
+        <v>23</v>
       </c>
       <c r="U273" t="s" s="2">
         <v>23</v>
@@ -35055,10 +35043,10 @@
       </c>
       <c r="R275" s="2"/>
       <c r="S275" t="s" s="2">
-        <v>23</v>
+        <v>574</v>
       </c>
       <c r="T275" t="s" s="2">
-        <v>574</v>
+        <v>23</v>
       </c>
       <c r="U275" t="s" s="2">
         <v>23</v>
@@ -36288,7 +36276,7 @@
         <v>76</v>
       </c>
       <c r="H287" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I287" t="s" s="2">
         <v>84</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T15:27:52+00:00</t>
+    <t>2026-04-13T20:12:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1638,9 +1638,9 @@
     <t>ELGA e-Med Medikationsplan</t>
   </si>
   <si>
-    <t>Bildet den Medikationsplan eines ELGA-Teilnehmers ab ("List"-Ressource). 
-Die Liste beinhaltet Referenzen auf 0..* Medikationsplaneinträge (MedicationRequests), die alle geplanten Medikationen und deren Dosierung abbilden.
-Die Reihenfolge der Listenelemente kann duch den User festgelegt werden. Jedes Listenelement enthält einen Änderungsstatus.</t>
+    <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
+Diese enthält 0..* Einträge (List.entry), wobei jedes Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
+Die Reihenfolge der Einträge kann durch den GDA oder den Patienten festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>List</t>
@@ -1732,7 +1732,7 @@
     <t>List.identifier</t>
   </si>
   <si>
-    <t>Logischer Identfier der Liste (des Medikationsplans) zur Schreibintegritätsprüfung.</t>
+    <t>Logischer Identfier der Liste (des Medikationsplans) zur Integritätsprüfung beim Schreibvorgang.</t>
   </si>
   <si>
     <t>Identifier for the List assigned for business purposes outside the context of FHIR.</t>
@@ -1902,9 +1902,7 @@
     <t>List.orderedBy</t>
   </si>
   <si>
-    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben. Da nicht verpflichtend, könnte das Element auch 0..0 gesetzt werden.
-Evtl. Unterscheidung user und patient.
-Mögliche Codes: user | system | event-date | entry-date| priority | alphabetic | category | patient (TODO: nur user oder andere Reihenfolge ermöglichen?)</t>
+    <t>Die Reihenfolge der Einträge im Medikationsplan ist fachlich relevant und wird durch den Ersteller vorgegeben.</t>
   </si>
   <si>
     <t>What order applies to the items in the list.</t>
@@ -1933,7 +1931,7 @@
 </t>
   </si>
   <si>
-    <t>Freitextliche Anmerkungen zum Medikationsplan. TODO: prüfen, ob fachlich sinnvoll.</t>
+    <t>Freitextliche Anmerkungen zum Medikationsplan.</t>
   </si>
   <si>
     <t>Comments that apply to the overall list.</t>
@@ -1942,7 +1940,7 @@
     <t>List.entry</t>
   </si>
   <si>
-    <t>Entries in the list</t>
+    <t>Medikationsplaneinträge in der Liste</t>
   </si>
   <si>
     <t>Entries in this list.</t>
@@ -1985,7 +1983,8 @@
     <t>List.entry.deleted</t>
   </si>
   <si>
-    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde. Unklar, ob Löschen so abgebildet werden soll oder einfach der Eintrag nicht mehr enthalten ist.</t>
+    <t>Gibt an, ob der referenzierte Medikationsplaneintrag zur Entfernung markiert wurde.
+Keine Verwendung im Medikationsplan, da GDA für die Kennzeichnung von zur Entfernung freigegebenen Planeinträgen das Element entry.flag mit dem Wert "removed" verwenden und ELGA-Teilnehmer Einträge durch Entfernen aus der Liste löschen.</t>
   </si>
   <si>
     <t>True if this item is marked as deleted in the list.</t>
@@ -2007,7 +2006,7 @@
     <t>List.entry.date</t>
   </si>
   <si>
-    <t>Datum der Aufnahme / Änderung des Medikationsplaneintrags. Fachlich zu klären.</t>
+    <t>Datum der Aufnahme bzw. Änderung des Medikationsplaneintrags.</t>
   </si>
   <si>
     <t>When this item was added to the list.</t>
@@ -3727,9 +3726,9 @@
     <t>ELGA e-Med Planeintrag</t>
   </si>
   <si>
-    <t>Bildet einen Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
-Er enthält genau ein Arzneimittel und dessen Dosierung.
-Kann in weiterer Folge dazu dienen, eine geplante Abgabe zu erstellen. Verwendet R5 Backport Extensions.</t>
+    <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
+Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline), also innerhalb der Ressource, dokumentiert wird.
+Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>MedicationRequest.extension:offLabelUse</t>
@@ -3761,22 +3760,16 @@
 - Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Ersteller des Eintrags.</t>
   </si>
   <si>
-    <t>Status des Medikationsplaneintrags. active | completed | on-hold | stopped. TODO: Fachlich zu püfen, ob im Medikationsplan dokumentiert werden soll, dass und warum ein Medikament abgesetzt wurde (Status: stopped, z.B. bei Allergie). Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Status des Medikationsplaneintrags:
-* \"active\": aktive Therapie; soll aktuell vom Patienten eingenommen werden
-* \"completed\": Therapie regulär abgeschlossen
-* \"on-hold\": Therapie vorübergehend unterbrochen; Wiederaufnahme vorgesehen
-* \"stopped\": begonnen Therapie, aber vorzeitig und ohne regulären Abschluss beendet
-(nicht verwendet: cancelled, entered-in-error, draft, unknown)
-https://hl7.org/fhir/R4/valueset-medicationrequest-status.html</t>
+    <t>Status des Medikationsplaneintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
+  </si>
+  <si>
+    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. TODO: Verwendung fachlich zu prüfen im Zusammenhang mit Status.</t>
+    <t>Grund für den aktuellen Status des Medikationsplaneintrags: (ex) https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html.</t>
   </si>
   <si>
     <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
@@ -54956,7 +54949,7 @@
         <v>76</v>
       </c>
       <c r="H466" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I466" t="s" s="2">
         <v>23</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-13T20:12:42+00:00</t>
+    <t>2026-04-14T10:13:14+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -34579,7 +34579,7 @@
       </c>
       <c r="F271" s="2"/>
       <c r="G271" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H271" t="s" s="2">
         <v>83</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-17T19:15:07+00:00</t>
+    <t>2026-04-20T08:20:06+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19096" uniqueCount="1390">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="19096" uniqueCount="1388">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T16:24:35+00:00</t>
+    <t>2026-04-20T19:04:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1556,7 +1556,7 @@
 </t>
   </si>
   <si>
-    <t>Upper limit on medication per unit of time</t>
+    <t>Maximale Menge pro Zeiteinheit</t>
   </si>
   <si>
     <t>Upper limit on medication per unit of time.</t>
@@ -1575,7 +1575,7 @@
 </t>
   </si>
   <si>
-    <t>Upper limit on medication per administration</t>
+    <t>Maximal Menge pro Abgabe</t>
   </si>
   <si>
     <t>Upper limit on medication per administration.</t>
@@ -1590,7 +1590,7 @@
     <t>Dosage.maxDosePerLifetime</t>
   </si>
   <si>
-    <t>Upper limit on medication per lifetime of the patient</t>
+    <t>Maximale Lebenszeitdosis</t>
   </si>
   <si>
     <t>Upper limit on medication per lifetime of the patient.</t>
@@ -1714,7 +1714,7 @@
     <t>List.status</t>
   </si>
   <si>
-    <t>Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
+    <t>Status des Medikationsplans. Mögliche Ausprägungen: [current | retired] Bedeutung: current: default | retired: nach Ableben des Patienten bis Ende der Aufbewahrungsfrist</t>
   </si>
   <si>
     <t>Indicates the current state of this list.</t>
@@ -2109,7 +2109,7 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. TODO: Verwendung zu prüfen.</t>
+    <t>Durchgeführte-Abgabe-ID.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -2125,7 +2125,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis. Referenz auf Procedure-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -2134,16 +2134,10 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe: completed | entered-in-error | stopped. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t xml:space="preserve">* **\"completed\"**: Die durchgeführte Abgabe ist abgeschlossen. 
-* **\"entered-in-error\"**: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert.
-* **\"stopped\"**: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt). 
-http://hl7.org/fhir/ValueSet/medicationdispense-status|4.0.1
-TODO: zu prüfen: 
-* ob es einen Status in-progress / preparation geben soll, z.B. wenn Bestellvorgang gestartet wurde und der typ First Fill - Part Fill ist.
-* Technische Prüfungen bezüglich Abhängigkeiten von status, typ, Rezeptart? automatisch geprüft werden? Falls der Status vom Typ der geplanten Abgabe (Rezeptart) abhängig sein kann (z.B. in-progress bei Bestellung o.ä.), evtl Operation </t>
+    <t>Status der durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+  </si>
+  <si>
+    <t>A code specifying the state of the set of dispense events.</t>
   </si>
   <si>
     <t>A coded concept specifying the state of the dispense event.</t>
@@ -2155,7 +2149,7 @@
     <t>MedicationDispense.statusReason[x]</t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Allergie, Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
+    <t>Grund für den aktuellen Status, z.B. warum keine Abgabe erfolgte (zB. Produkt nicht verfügbar). Code oder Referenz (DetectedIssue)</t>
   </si>
   <si>
     <t>Indicates the reason why a dispense was not performed.</t>
@@ -2173,7 +2167,7 @@
     <t>statusReasonCodeableConcept</t>
   </si>
   <si>
-    <t>Bsp: https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
+    <t>Grund für den aktuellen Status als Code. (ex) https://hl7.org/fhir/R4/valueset-medicationdispense-status-reason.html</t>
   </si>
   <si>
     <t>MedicationDispense.statusReason[x]:statusReasonReference</t>
@@ -2186,13 +2180,13 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf DetectedIssue-Ressource, daher keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant), https://hl7.org/fhir/R4/valueset-medicationdispense-category.html. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -2283,7 +2277,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle: https://hl7.org/fhir/R4/valueset-medicationdispense-performer-function.html; Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -2306,7 +2300,7 @@
   </si>
   <si>
     <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
-die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+der/die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
 auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -2333,9 +2327,7 @@
 </t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.
-zu prüfen (gemäß CDA): 'Ohne Verordnungsbezug kann nur die Abgabe jener OTC-Präparate in der e-Medikation 
-gespeichert werden, die auch wechselwirkungsrelevant sind.'</t>
+    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -2347,17 +2339,7 @@
     <t>MedicationDispense.type</t>
   </si>
   <si>
-    <t xml:space="preserve">Mögliche Werte z.B. FFC (First-Fill Complete für vollständig erfüllte Bestellungen), FFP (First-Fill Part Fill für teilweise erfüllte Bestellungen), 
-Bsp: http://terminology.hl7.org/ValueSet/v3-ActPharmacySupplyType  //ffc, ffp, Refill - Part Fill, refill complete: evtl. selbst definieren
-// für leerabgabe: complete-ausprägung; emergency supply offen (OTC), complete
-Der Prozess des „Besorgers“ (wenn ein Arzneimittel nicht lagernd ist und bestellt werden muss) wird in der e-Medikation abgebildet. 
-Dabei wird das Rezept von der Apotheke eingelöst, und die Abgabe wird als Teilabgabe gekennzeichnet 
-(siehe Markierung FFP „First Fill, Part Fill“ oder RFP „Refill - Part Fill“). Die Verordnung wird nicht in den Status EINGELÖST versetzt und es können solange weitere Abgaben dispensiert werden, bis eine Abgabe mit der Markierung RFC „Refill - Complete“ gespeichert wird. Die Kennzeichnung zeigt, dass das Arzneimittel dem Patienten noch nicht ausgehändigt wurde. Die Kennzeichnung zeigt auch, ob alle Packungen einer Verordnung bzw. teilweise Packungen einer Verordnung bestellt werden. Solange eine Abgabe mit der Kennzeichnung „Besorger“ vorhanden ist, muss die Abgabe mit der eMED-ID abrufbar sein.
-"FFC": First Fill - Complete:  &lt;br&gt;
-"FFP": First Fill - Part Fill &lt;br&gt;  
-"RFP": Refill - Part Fill &lt;br&gt; 
-"RFC": Refill - Complete &lt;br&gt;
-</t>
+    <t>Art der Abgabe (z.B. für Teilabgaben). Mögliche Ausprägungen: [FFC | FFP | RFP | RFC | EM]. Bedeutung: FFC: First Fill - Complete | FFP: First Fill - Part Fill | RFP: Refill - Part Fill | RFC: Refill - Complete | EM: Emergency Supply.</t>
   </si>
   <si>
     <t>Indicates the type of dispensing event that is performed. For example, Trial Fill, Completion of Trial, Partial Fill, Emergency Fill, Samples, etc.</t>
@@ -2378,7 +2360,7 @@
     <t>MedicationDispense.daysSupply</t>
   </si>
   <si>
-    <t>Medikamentenmenge, ausgedrückt als zeitliche Menge</t>
+    <t>Tage, für die die abgegebene Menge ausreicht</t>
   </si>
   <si>
     <t>The amount of medication expressed as a timing amount.</t>
@@ -2387,7 +2369,7 @@
     <t>MedicationDispense.whenPrepared</t>
   </si>
   <si>
-    <t>Verpackungs- und Prüfdatum.</t>
+    <t>Zeitpunkt, zu dem das Produkt verpackt und geprüft wurde.</t>
   </si>
   <si>
     <t>The time when the dispensed product was packaged and reviewed.</t>
@@ -2440,9 +2422,8 @@
 </t>
   </si>
   <si>
-    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. TODO: Dosiervarianten.
-Der Apotheker überprüft die Medikamentenbestellung vor der Abgabe und aktualisiert die Dosierungsanweisung auf der Grundlage 
-des tatsächlich abgegebenen Produkts.</t>
+    <t>Gibt an, wie das Medikament vom Patienten einzunehmen ist. 
+Der Apotheker überprüft die Medikamentenverordnung vor der Abgabe und passt die Dosierungsanweisung gegebenenfalls auf Grundlage des tatsächlich abgegebenen Produkts an.</t>
   </si>
   <si>
     <t>Indicates how the medication is to be used by the patient.</t>
@@ -2455,8 +2436,7 @@
     <t>MedicationDispense.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht. 
-Wenn nichts angegeben ist, wurde keine Substitution vorgenommen.</t>
+    <t>Gibt an, ob im Rahmen der Abgabe eine Substitution vorgenommen wurde oder nicht.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution was made as part of the dispense.  In some cases, substitution will be expected but does not happen, in other cases substitution is not expected but does happen.  This block explains what substitution did or did not happen and why.  If nothing is specified, substitution was not done.</t>
@@ -2534,7 +2514,7 @@
 </t>
   </si>
   <si>
-    <t>Referenenz auf DetectedIssue Ressource, daher keine Verwendung in durchgeführter Abgabe.</t>
+    <t>Referenenz auf DetectedIssue Ressource. Keine Verwendung in durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Indicates an actual or potential clinical issue with or between one or more active or proposed clinical actions for a patient; e.g. drug-drug interaction, duplicate therapy, dosage alert etc.</t>
@@ -2551,7 +2531,7 @@
   </si>
   <si>
     <t>Bezeichnet eine Liste von Provenance-Ressourcen, die verschiedene relevante Versionen 
-dieser Ressource dokumentieren. Verwendung prüfen.</t>
+dieser Ressource dokumentieren.</t>
   </si>
   <si>
     <t>A summary of the events of interest that have occurred, such as when the dispense was verified.</t>
@@ -3032,7 +3012,7 @@
     <t>MedicationRequest.identifier</t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID. TODO: Verwendung noch zu prüfen, evtl. basedon mit logischem Identifier ausreichend.</t>
+    <t>Gepante-Abgabe-ID.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -3041,15 +3021,10 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe: active | completed | entered-in-error | stopped. Details siehe Definition.</t>
-  </si>
-  <si>
-    <t>Status der geplanten Abgabe:
-* \"active\": offene, geplante Abgabe 
-* \"completed\": implizit mittels Custom Operation gesetzt, nachdem alle Abgaben durchgeführt wurden (Rezept komplett eingelöst) (TODO: techn. prüfen) 
-* \"entered-in-error\": nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde (TODO: techn. prüfen?) 
-* \"stopped\": TODO: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)
-(nicht verwendet: on-hold, cancelled, draft, unknown)</t>
+    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, geplante Abgabe | completed: geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+  </si>
+  <si>
+    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/GeplanteAbgabeStatusVS</t>
@@ -3058,7 +3033,7 @@
     <t>MedicationRequest.statusReason</t>
   </si>
   <si>
-    <t>Grund für den aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Grund des aktuellen Status: https://hl7.org/fhir/R4/valueset-medicationrequest-status-reason.html. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Captures the reason for the current state of the MedicationRequest.</t>
@@ -3076,8 +3051,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die Geplante Abgabe stellt eine Anforderung und Ermächtigung 
-zum Handeln durch den Antragsteller dar, daher ist intent immer "order".</t>
+    <t>Die geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -3255,8 +3229,7 @@
   </si>
   <si>
     <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
-(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).
-TODO: HL7ATCore-Practitioner-Profile profilieren.</t>
+(eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
     <t>The individual, organization, or device that initiated the request and has responsibility for its activation.</t>
@@ -3269,6 +3242,9 @@
 </t>
   </si>
   <si>
+    <t>Durchführende Person. Keine Verwendung in der geplanten Abgabe.</t>
+  </si>
+  <si>
     <t>The specified desired performer of the medication treatment (e.g. the performer of the medication administration).</t>
   </si>
   <si>
@@ -3290,7 +3266,7 @@
     <t>MedicationRequest.recorder</t>
   </si>
   <si>
-    <t>Person der Dateineingabe. Gemäß Vorgaben im CDA keine Verwendung in der geplanten Abgabe. TODO: Abstimmung der Verwendung mit e-Diagnose.</t>
+    <t>Person der Dateineingabe. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The person who entered the order on behalf of another individual for example in the case of a verbal or a telephone order.</t>
@@ -3299,7 +3275,7 @@
     <t>MedicationRequest.reasonCode</t>
   </si>
   <si>
-    <t xml:space="preserve">Grund für die Verordnung des Arzneimittels als Code oder Referenz. Bis zur Verfügbarkeit von e-Diagnose keine Verwendung in geplanter Abgabe. </t>
+    <t>Grund für die Verordnung des Arzneimittels als Code oder Referenz. Bis zur Verfügbarkeit von e-Diagnose keine Verwendung in geplanter Abgabe.</t>
   </si>
   <si>
     <t>The reason or the indication for ordering or not ordering the medication.</t>
@@ -3337,7 +3313,7 @@
 </t>
   </si>
   <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+    <t>URL, die auf eine Richtlinie/Guideline verweist, die von dieser 
 geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -3347,7 +3323,7 @@
     <t>MedicationRequest.instantiatesUri</t>
   </si>
   <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von dieser 
+    <t>URL, die auf eine externe gepflegte Richtlinie/Guideline verweist, die von dieser 
 geplanten Abgabe ganz oder teilweise eingehalten wird. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
@@ -3357,9 +3333,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.
-TODO: zu prüfen: zusätzliche logische Referenz: reference.identifier 
-{Medikationsplaneintrag-ID}_{Medikationsplaneintrag-ID_Version}.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -3369,9 +3343,8 @@
   </si>
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
-Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, 
-wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').
-TODO: eMED-ID Wording ist evtl. aufgrund des Parallelbetriebs noch anzupassen</t>
+Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
+geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -3414,8 +3387,7 @@
     <t>MedicationRequest.note</t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikations zw. Arzt und Apotheke); die nicht die Dosierung betreffen. 
-TODO: prüfen was CDA derzeit zulässt; HL7 Consultation, ob Feld benötigt</t>
+    <t>Zusätzliche Informationen zur geplanten Abgabe (Kommunikation zwischen Arzt und Apotheke, die nicht die Dosierung betreffen).</t>
   </si>
   <si>
     <t>Extra information about the prescription that could not be conveyed by the other attributes.</t>
@@ -3428,7 +3400,7 @@
 </t>
   </si>
   <si>
-    <t>Angabe der Dosierinformationen. TODO: Dosiervarianten.</t>
+    <t>Angabe der Dosierinformationen.</t>
   </si>
   <si>
     <t>There are examples where a medication request may include the option of an oral dose or an Intravenous or Intramuscular dose.  For example, "Ondansetron 8mg orally or IV twice a day as needed for nausea" or "Compazine® (prochlorperazine) 5-10mg PO or 25mg PR bid prn nausea or vomiting".  In these cases, two medication requests would be created that could be grouped together.  The decision on which dose and route of administration to use is based on the patient's condition at the time the dose is needed.</t>
@@ -3511,14 +3483,13 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart (siehe Definition).</t>
-  </si>
-  <si>
-    <t>Anzahl der weiteren möglichen Einlösungen:
+    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart: Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
 * **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
 * **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
-* **Sustitutionsrzepet**: keine weitere Einlösung möglich (fixer Wert 0) 
-TODO: Techn. Prüfung: Wenn Kassenrezept oder Substitutionsrezept, dann 0. Verpflichtende Eingabe, wenn Privatrezept, max 6.</t>
+* **Sustitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
   </si>
   <si>
     <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
@@ -3542,7 +3513,7 @@
     <t>MedicationRequest.dispenseRequest.quantity</t>
   </si>
   <si>
-    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll. 
+    <t>Menge des Medikaments, die bei jeder Abgabe bereitgestellt werden soll.
 Da sich die Angaben zum Arzneimittel jeweils auf eine Packung der Arznei beziehen, MUSS die Anzahl der auszugebenden Packungen angegeben werden (mindestens 1). 
 Dies gilt für Arzneimittel mit PZN und magistralen Zubereitungen.</t>
   </si>
@@ -3711,23 +3682,10 @@
     <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
   </si>
   <si>
-    <t>Medikationsplaneintrag-ID. TODO: Verwendung einer logischen Medikationsplaneintrag-ID prüfen. Details zur Herstellung von Bezügen von geänderten Planeinträgen, siehe Definition.</t>
-  </si>
-  <si>
-    <t>Medikationsplaneintrag-ID.
-Evt. mit Zeitstempel (Planeintrag-ID_{Zeitstempel}) zur Herstellung eines Bezugs von geänderten Planeinträgen.
-Vorteil: 
-- Auch wenn sich die PZN ändert, aber logisch der gleiche Eintrag betroffen ist (z.B. Austausch eines Arzneimittels durch ein anderes mit weniger Wechselwirkung), kann ein Bezug hergestellt werden.
-- Wenn zur Vorversion des Eintrags bereits eine geplante Abgabe erstellt wurde, kann ein Bezug zum ursprünglichen Eintrag hergestellt werden.
-Nachteil: 
-- Falls Planeinträge mit komplett neuer Arznei überschrieben werden, entsteht dadurch ein verwirrender Bezug. 
-- Die Verantwortung, dass nur Einträge geändert werden, die keine komplett neue Medikation beinhalten, liegt beim Ersteller des Eintrags.</t>
+    <t>Medikationsplaneintrag-ID.</t>
   </si>
   <si>
     <t>Status des Medikationsplaneintrags. Mögliche Ausprägungen: [active | on-hold | completed | stopped | entered-in-error]. Bedeutung: active: Planeintrag einer aktiven Medikation, die eingenommen werden soll | on-hold: Planeintrag ist pausiert, die Therapie ist unterbrochen (Wiederaufnahme vorgesehen) | completed: Therapie gemäß Planeintrag wie geplant durchgeführt und abgeschlossen | stopped: Therapie gemäß Planeintrag vorzeitig gestoppt und abgeschlossen | entered-in-error: Fehlerhafter Planeintrag storniert und abgeschlossen.</t>
-  </si>
-  <si>
-    <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
   </si>
   <si>
     <t>https://fhir.hl7.at/elga/emed/r4/ValueSet/MedikationsplaneintragStatusVS</t>
@@ -3776,7 +3734,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE. TODO: Klären ob hier der GDA eindeutig identifiziert sein muss (im GDA-I vorhanden) oder analog zu e-Impfpass Freitext sein kann. Juristisch Verantwortlichkeit für Korrektheit des Eintrags zu klären.</t>
+    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.</t>
   </si>
   <si>
     <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>
@@ -3797,44 +3755,41 @@
     <t>Arzt oder Ärztin, die den Medikationsplaneintrag erstellt hat und für den Inhalt verantwortlich ist. Eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen.</t>
   </si>
   <si>
-    <t>Der gewünschte Ausführende der medikamentösen Behandlung (z.B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
-  </si>
-  <si>
-    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. Keine Verwendung im Planeintrag. TODO: evtl im Kontext Medikationsblatt zu prüfen.</t>
-  </si>
-  <si>
-    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat. TODO: Prüfen, ob eine juristische Verpflichtung zur Dokumentation der Schreibkraft besteht.</t>
-  </si>
-  <si>
-    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz (TODO: Evtl. Invariante). Erst wenn codierte Angabe möglich.</t>
-  </si>
-  <si>
-    <t>URL, die auf ein Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
-  </si>
-  <si>
-    <t>URL, die auf ein extern gepflegtes Protokoll (Richtlinie, Guideline) verweist, das von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Der gewünschte Ausführende der medikamentösen Behandlung (z.B. der Ausführende der Medikamentengabe). Keine Verwendung im Planeintrag.</t>
+  </si>
+  <si>
+    <t>Rollen: https://hl7.org/fhir/R4/valueset-performer-role.html. Keine Verwendung im Planeintrag.</t>
+  </si>
+  <si>
+    <t>Die Person, die den Medikationsplaneintrag im Auftrag eines GDA eingegeben hat.</t>
+  </si>
+  <si>
+    <t>Grund für die Verordnung des Arzneimittels. Entweder Code oder Referenz. Verwendung erst, wenn codierte Angabe möglich.</t>
+  </si>
+  <si>
+    <t>URL, die auf eine Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
+  </si>
+  <si>
+    <t>URL, die auf eine extern gepflegte Richtlinie/Guideline verweist, die von diesem Medikationsplaneintrag ganz oder teilweise eingehalten wird. Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t xml:space="preserve">Reference(CarePlan|4.0.1|MedicationRequest|4.0.1|ServiceRequest|4.0.1|ImmunizationRecommendation|4.0.1)
 </t>
   </si>
   <si>
-    <t>TODO: Verwendung im Medikationsplaneintrag zu prüfen. Vermutlich nicht möglich, da keine versionsspezifischen Referenzen verwendet werden.</t>
-  </si>
-  <si>
-    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant. Evtl ein Verweis auf erstellte Rezepte? Würde Extension erfordern, da Kardinalität nur 0..1 zulässig</t>
-  </si>
-  <si>
-    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal. Verwendung im Medikationsplaneintrag prüfen, evtl. durch Dosierungsinformationen abgedeckt.</t>
-  </si>
-  <si>
     <t>Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
-    <t>Zusätzliche Informationen zum Medikationsplaneintrag. TODO: fachlich prüfen, an welchen Stellen überall Freitext erforderlich sein soll/muss. Auch im Kontext zu entered-in-error Informationen.</t>
-  </si>
-  <si>
-    <t>Angabe der Dosierinformationen strukturiert oder als Freitext. TODO: Inhalte AtEmedDosage fachlich prüfen.</t>
+    <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant.</t>
+  </si>
+  <si>
+    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal.</t>
+  </si>
+  <si>
+    <t>Zusätzliche Informationen zum Medikationsplaneintrag.</t>
+  </si>
+  <si>
+    <t>Angabe der Dosierinformationen strukturiert oder als Freitext.</t>
   </si>
   <si>
     <t>Details zur geplanten Abgabe des Arzneimittels im Medikationsplan. Keine Verwendung im Medikationsplaneintrag.</t>
@@ -3858,13 +3813,13 @@
     <t>Intended dispenser</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden. Die Dokumentation über eine tatsächlich erfolgte Substitution erfolgt in der Dispense-Resource. TODO: Usecase fachlich zu prüfen. Es kann für den Patienten selbst oder das Pflegeheim eine wichtige Information sein, mit welchem Medikament das verordnete Medikament im Bedarfsfall ersetzen werden kann.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden.</t>
   </si>
   <si>
     <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen.</t>
   </si>
   <si>
-    <t>Klinisches Problem mit Maßnahme. Nur mittesl Referenz auf Ressouce DetectedIssue, Keine Verwendung im Medikationsplaneintrag.</t>
+    <t>Klinisches Problem mit Maßnahme (Referenz auf Ressouce DetectedIssue). Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. Keine Verwendung im Medikationsplaneintrag.</t>
@@ -4124,7 +4079,7 @@
     <t>Timing.event</t>
   </si>
   <si>
-    <t>Zeitpunkt der Einnahme: Mapping /effectiveTime[1]/@value</t>
+    <t>Zeitpunkt der Einnahme.</t>
   </si>
   <si>
     <t>Identifies specific times when the event occurs.</t>
@@ -4192,7 +4147,7 @@
     <t>Timing.repeat.bounds[x].start</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Start. Mapping /effectiveTime[1]/low</t>
+    <t>Zeitraum der Einnahme: Start.</t>
   </si>
   <si>
     <t>The start of the period. The boundary is inclusive.</t>
@@ -4214,7 +4169,7 @@
     <t>Timing.repeat.bounds[x].end</t>
   </si>
   <si>
-    <t>Zeitraum der Einnahme: Ende. Mapping /effectiveTime[1]/high</t>
+    <t>Zeitraum der Einnahme: Ende.</t>
   </si>
   <si>
     <t>The end of the period. If the end of the period is missing, it means no end was known or planned at the time the instance was created. The start may be in the past, and the end date in the future, which means that period is expected/planned to end at that time.</t>
@@ -4299,8 +4254,7 @@
     <t>Timing.repeat.frequency</t>
   </si>
   <si>
-    <t>Häufigkeit der Einnahme, z.B. 1 mal täglich.
-Periodic Frequency /effectiveTime[operator="A" and xsi:type="PIVL_TS"] …/@institutionSpecified …/period/@value …/period/@unit</t>
+    <t>Häufigkeit der Einnahme, z.B. 3 mal täglich.</t>
   </si>
   <si>
     <t>The number of times to repeat the action within the specified period. If frequencyMax is present, this element indicates the lower bound of the allowed range of the frequency.</t>
@@ -4321,7 +4275,7 @@
     <t>Timing.repeat.period</t>
   </si>
   <si>
-    <t>Intervall der Einnahme, z.B. alle 8 Stunden.</t>
+    <t>Intervall der Einnahme, z.B. alle 4 Stunden.</t>
   </si>
   <si>
     <t>Indicates the duration of time over which repetitions are to occur; e.g. to express "3 times per day", 3 would be the frequency and "1 day" would be the period. If periodMax is present, this element indicates the lower bound of the allowed range of the period length.</t>
@@ -5765,7 +5719,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
     </row>
     <row r="157">
@@ -5773,7 +5727,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
     </row>
     <row r="158">
@@ -5789,7 +5743,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
     </row>
     <row r="160">
@@ -5797,7 +5751,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
     </row>
     <row r="161">
@@ -5859,7 +5813,7 @@
         <v>24</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
     </row>
     <row r="169">
@@ -5935,7 +5889,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
     </row>
     <row r="179">
@@ -5943,7 +5897,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1209</v>
+        <v>1207</v>
       </c>
     </row>
     <row r="180">
@@ -5959,7 +5913,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1210</v>
+        <v>1208</v>
       </c>
     </row>
     <row r="182">
@@ -5967,7 +5921,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1211</v>
+        <v>1209</v>
       </c>
     </row>
     <row r="183">
@@ -6029,7 +5983,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1212</v>
+        <v>1210</v>
       </c>
     </row>
     <row r="191">
@@ -6065,7 +6019,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
     </row>
     <row r="196">
@@ -6073,7 +6027,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1214</v>
+        <v>1212</v>
       </c>
     </row>
     <row r="197">
@@ -6105,7 +6059,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="201">
@@ -6113,7 +6067,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1280</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="202">
@@ -6129,7 +6083,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1281</v>
+        <v>1279</v>
       </c>
     </row>
     <row r="204">
@@ -6137,7 +6091,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="205">
@@ -6199,7 +6153,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1282</v>
+        <v>1280</v>
       </c>
     </row>
     <row r="213">
@@ -6235,7 +6189,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
     </row>
     <row r="218">
@@ -6243,7 +6197,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1284</v>
+        <v>1282</v>
       </c>
     </row>
     <row r="219">
@@ -48448,10 +48402,10 @@
         <v>1021</v>
       </c>
       <c r="M404" t="s" s="2">
-        <v>997</v>
+        <v>1022</v>
       </c>
       <c r="N404" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O404" s="2"/>
       <c r="P404" s="2"/>
@@ -48522,10 +48476,10 @@
         <v>927</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -48554,10 +48508,10 @@
         <v>997</v>
       </c>
       <c r="N405" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O405" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="P405" s="2"/>
       <c r="Q405" t="s" s="2">
@@ -48586,10 +48540,10 @@
         <v>372</v>
       </c>
       <c r="Z405" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AA405" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AB405" t="s" s="2">
         <v>23</v>
@@ -48607,7 +48561,7 @@
         <v>23</v>
       </c>
       <c r="AG405" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AH405" t="s" s="2">
         <v>76</v>
@@ -48627,10 +48581,10 @@
         <v>927</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -48656,10 +48610,10 @@
         <v>787</v>
       </c>
       <c r="M406" t="s" s="2">
-        <v>1029</v>
+        <v>1030</v>
       </c>
       <c r="N406" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O406" s="2"/>
       <c r="P406" s="2"/>
@@ -48710,7 +48664,7 @@
         <v>23</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>76</v>
@@ -48730,10 +48684,10 @@
         <v>927</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -48759,13 +48713,13 @@
         <v>367</v>
       </c>
       <c r="M407" t="s" s="2">
-        <v>1032</v>
+        <v>1033</v>
       </c>
       <c r="N407" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O407" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P407" s="2"/>
       <c r="Q407" t="s" s="2">
@@ -48794,10 +48748,10 @@
         <v>372</v>
       </c>
       <c r="Z407" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AA407" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AB407" t="s" s="2">
         <v>23</v>
@@ -48815,7 +48769,7 @@
         <v>23</v>
       </c>
       <c r="AG407" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AH407" t="s" s="2">
         <v>76</v>
@@ -48835,10 +48789,10 @@
         <v>927</v>
       </c>
       <c r="B408" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C408" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D408" s="2"/>
       <c r="E408" t="s" s="2">
@@ -48861,16 +48815,16 @@
         <v>23</v>
       </c>
       <c r="L408" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N408" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O408" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P408" s="2"/>
       <c r="Q408" t="s" s="2">
@@ -48920,7 +48874,7 @@
         <v>23</v>
       </c>
       <c r="AG408" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH408" t="s" s="2">
         <v>76</v>
@@ -48940,10 +48894,10 @@
         <v>927</v>
       </c>
       <c r="B409" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C409" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D409" s="2"/>
       <c r="E409" t="s" s="2">
@@ -48966,13 +48920,13 @@
         <v>84</v>
       </c>
       <c r="L409" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M409" t="s" s="2">
-        <v>1044</v>
+        <v>1045</v>
       </c>
       <c r="N409" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="O409" s="2"/>
       <c r="P409" s="2"/>
@@ -49023,7 +48977,7 @@
         <v>23</v>
       </c>
       <c r="AG409" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AH409" t="s" s="2">
         <v>76</v>
@@ -49043,10 +48997,10 @@
         <v>927</v>
       </c>
       <c r="B410" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C410" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D410" s="2"/>
       <c r="E410" t="s" s="2">
@@ -49072,10 +49026,10 @@
         <v>97</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>1047</v>
+        <v>1048</v>
       </c>
       <c r="N410" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O410" s="2"/>
       <c r="P410" s="2"/>
@@ -49126,7 +49080,7 @@
         <v>23</v>
       </c>
       <c r="AG410" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AH410" t="s" s="2">
         <v>76</v>
@@ -49146,10 +49100,10 @@
         <v>927</v>
       </c>
       <c r="B411" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C411" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D411" s="2"/>
       <c r="E411" t="s" s="2">
@@ -49175,10 +49129,10 @@
         <v>627</v>
       </c>
       <c r="M411" t="s" s="2">
-        <v>1050</v>
+        <v>1051</v>
       </c>
       <c r="N411" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="O411" s="2"/>
       <c r="P411" s="2"/>
@@ -49229,7 +49183,7 @@
         <v>23</v>
       </c>
       <c r="AG411" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AH411" t="s" s="2">
         <v>76</v>
@@ -49249,10 +49203,10 @@
         <v>927</v>
       </c>
       <c r="B412" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C412" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D412" s="2"/>
       <c r="E412" t="s" s="2">
@@ -49278,14 +49232,14 @@
         <v>112</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>1053</v>
+        <v>1054</v>
       </c>
       <c r="N412" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="O412" s="2"/>
       <c r="P412" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="Q412" t="s" s="2">
         <v>23</v>
@@ -49334,7 +49288,7 @@
         <v>23</v>
       </c>
       <c r="AG412" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AH412" t="s" s="2">
         <v>76</v>
@@ -49354,10 +49308,10 @@
         <v>927</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C413" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D413" s="2"/>
       <c r="E413" t="s" s="2">
@@ -49383,13 +49337,13 @@
         <v>367</v>
       </c>
       <c r="M413" t="s" s="2">
-        <v>1057</v>
+        <v>1058</v>
       </c>
       <c r="N413" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="O413" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="P413" s="2"/>
       <c r="Q413" t="s" s="2">
@@ -49418,10 +49372,10 @@
         <v>372</v>
       </c>
       <c r="Z413" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="AA413" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AB413" t="s" s="2">
         <v>23</v>
@@ -49439,7 +49393,7 @@
         <v>23</v>
       </c>
       <c r="AG413" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AH413" t="s" s="2">
         <v>76</v>
@@ -49459,10 +49413,10 @@
         <v>927</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C414" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D414" s="2"/>
       <c r="E414" t="s" s="2">
@@ -49485,13 +49439,13 @@
         <v>23</v>
       </c>
       <c r="L414" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M414" t="s" s="2">
-        <v>1064</v>
+        <v>1065</v>
       </c>
       <c r="N414" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O414" s="2"/>
       <c r="P414" s="2"/>
@@ -49542,7 +49496,7 @@
         <v>23</v>
       </c>
       <c r="AG414" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AH414" t="s" s="2">
         <v>76</v>
@@ -49562,10 +49516,10 @@
         <v>927</v>
       </c>
       <c r="B415" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C415" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D415" s="2"/>
       <c r="E415" t="s" s="2">
@@ -49591,10 +49545,10 @@
         <v>598</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="N415" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="O415" s="2"/>
       <c r="P415" s="2"/>
@@ -49645,7 +49599,7 @@
         <v>23</v>
       </c>
       <c r="AG415" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AH415" t="s" s="2">
         <v>76</v>
@@ -49665,10 +49619,10 @@
         <v>927</v>
       </c>
       <c r="B416" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C416" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D416" s="2"/>
       <c r="E416" t="s" s="2">
@@ -49691,16 +49645,16 @@
         <v>23</v>
       </c>
       <c r="L416" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>1071</v>
+        <v>1072</v>
       </c>
       <c r="N416" t="s" s="2">
         <v>765</v>
       </c>
       <c r="O416" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="P416" s="2"/>
       <c r="Q416" t="s" s="2">
@@ -49750,7 +49704,7 @@
         <v>23</v>
       </c>
       <c r="AG416" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AH416" t="s" s="2">
         <v>76</v>
@@ -49770,10 +49724,10 @@
         <v>927</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -49799,10 +49753,10 @@
         <v>136</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1074</v>
+        <v>1075</v>
       </c>
       <c r="N417" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="O417" s="2"/>
       <c r="P417" s="2"/>
@@ -49853,7 +49807,7 @@
         <v>23</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -49873,10 +49827,10 @@
         <v>927</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -49976,10 +49930,10 @@
         <v>927</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -50081,10 +50035,10 @@
         <v>927</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -50188,10 +50142,10 @@
         <v>927</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -50217,13 +50171,13 @@
         <v>136</v>
       </c>
       <c r="M421" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N421" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="O421" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="P421" s="2"/>
       <c r="Q421" t="s" s="2">
@@ -50273,7 +50227,7 @@
         <v>23</v>
       </c>
       <c r="AG421" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AH421" t="s" s="2">
         <v>76</v>
@@ -50293,10 +50247,10 @@
         <v>927</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -50396,10 +50350,10 @@
         <v>927</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -50501,10 +50455,10 @@
         <v>927</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -50608,10 +50562,10 @@
         <v>927</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -50637,10 +50591,10 @@
         <v>497</v>
       </c>
       <c r="M425" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="N425" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O425" s="2"/>
       <c r="P425" s="2"/>
@@ -50691,7 +50645,7 @@
         <v>23</v>
       </c>
       <c r="AG425" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="AH425" t="s" s="2">
         <v>76</v>
@@ -50711,10 +50665,10 @@
         <v>927</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -50737,13 +50691,13 @@
         <v>23</v>
       </c>
       <c r="L426" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O426" s="2"/>
       <c r="P426" s="2"/>
@@ -50794,7 +50748,7 @@
         <v>23</v>
       </c>
       <c r="AG426" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AH426" t="s" s="2">
         <v>76</v>
@@ -50814,10 +50768,10 @@
         <v>927</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -50840,13 +50794,13 @@
         <v>23</v>
       </c>
       <c r="L427" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M427" t="s" s="2">
-        <v>1094</v>
+        <v>1095</v>
       </c>
       <c r="N427" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="O427" s="2"/>
       <c r="P427" s="2"/>
@@ -50897,7 +50851,7 @@
         <v>23</v>
       </c>
       <c r="AG427" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AH427" t="s" s="2">
         <v>76</v>
@@ -50917,10 +50871,10 @@
         <v>927</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -50943,19 +50897,19 @@
         <v>23</v>
       </c>
       <c r="L428" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="M428" t="s" s="2">
-        <v>1098</v>
+        <v>1099</v>
       </c>
       <c r="N428" t="s" s="2">
-        <v>1099</v>
+        <v>1100</v>
       </c>
       <c r="O428" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P428" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="Q428" t="s" s="2">
         <v>23</v>
@@ -51004,7 +50958,7 @@
         <v>23</v>
       </c>
       <c r="AG428" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AH428" t="s" s="2">
         <v>76</v>
@@ -51024,10 +50978,10 @@
         <v>927</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -51053,13 +51007,13 @@
         <v>130</v>
       </c>
       <c r="M429" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N429" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O429" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="P429" s="2"/>
       <c r="Q429" t="s" s="2">
@@ -51109,7 +51063,7 @@
         <v>23</v>
       </c>
       <c r="AG429" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AH429" t="s" s="2">
         <v>76</v>
@@ -51129,10 +51083,10 @@
         <v>927</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -51158,10 +51112,10 @@
         <v>497</v>
       </c>
       <c r="M430" t="s" s="2">
-        <v>1107</v>
+        <v>1108</v>
       </c>
       <c r="N430" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="O430" s="2"/>
       <c r="P430" s="2"/>
@@ -51212,7 +51166,7 @@
         <v>23</v>
       </c>
       <c r="AG430" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AH430" t="s" s="2">
         <v>76</v>
@@ -51232,10 +51186,10 @@
         <v>927</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -51258,16 +51212,16 @@
         <v>23</v>
       </c>
       <c r="L431" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M431" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N431" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O431" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="P431" s="2"/>
       <c r="Q431" t="s" s="2">
@@ -51317,7 +51271,7 @@
         <v>23</v>
       </c>
       <c r="AG431" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AH431" t="s" s="2">
         <v>76</v>
@@ -51337,10 +51291,10 @@
         <v>927</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>1113</v>
+        <v>1114</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -51440,10 +51394,10 @@
         <v>927</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>1114</v>
+        <v>1115</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -51545,10 +51499,10 @@
         <v>927</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>1115</v>
+        <v>1116</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -51574,7 +51528,7 @@
         <v>199</v>
       </c>
       <c r="M434" t="s" s="2">
-        <v>1116</v>
+        <v>1117</v>
       </c>
       <c r="N434" t="s" s="2">
         <v>450</v>
@@ -51652,10 +51606,10 @@
         <v>927</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>1117</v>
+        <v>1118</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -51684,7 +51638,7 @@
         <v>456</v>
       </c>
       <c r="N435" t="s" s="2">
-        <v>1118</v>
+        <v>1119</v>
       </c>
       <c r="O435" s="2"/>
       <c r="P435" t="s" s="2">
@@ -51759,10 +51713,10 @@
         <v>927</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>1119</v>
+        <v>1120</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -51864,10 +51818,10 @@
         <v>927</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>1120</v>
+        <v>1121</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -51969,10 +51923,10 @@
         <v>927</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>1121</v>
+        <v>1122</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -52076,10 +52030,10 @@
         <v>927</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -52105,10 +52059,10 @@
         <v>880</v>
       </c>
       <c r="M439" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="N439" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="O439" s="2"/>
       <c r="P439" s="2"/>
@@ -52159,7 +52113,7 @@
         <v>23</v>
       </c>
       <c r="AG439" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AH439" t="s" s="2">
         <v>76</v>
@@ -52179,10 +52133,10 @@
         <v>927</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -52208,10 +52162,10 @@
         <v>136</v>
       </c>
       <c r="M440" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="N440" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="O440" s="2"/>
       <c r="P440" s="2"/>
@@ -52262,7 +52216,7 @@
         <v>23</v>
       </c>
       <c r="AG440" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AH440" t="s" s="2">
         <v>76</v>
@@ -52282,10 +52236,10 @@
         <v>927</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -52385,10 +52339,10 @@
         <v>927</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -52490,10 +52444,10 @@
         <v>927</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -52597,10 +52551,10 @@
         <v>927</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
@@ -52623,16 +52577,16 @@
         <v>23</v>
       </c>
       <c r="L444" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="N444" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="O444" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="P444" s="2"/>
       <c r="Q444" t="s" s="2">
@@ -52661,7 +52615,7 @@
         <v>372</v>
       </c>
       <c r="Z444" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AA444" t="s" s="2">
         <v>780</v>
@@ -52682,7 +52636,7 @@
         <v>23</v>
       </c>
       <c r="AG444" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AH444" t="s" s="2">
         <v>83</v>
@@ -52702,10 +52656,10 @@
         <v>927</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -52731,10 +52685,10 @@
         <v>367</v>
       </c>
       <c r="M445" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N445" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="O445" s="2"/>
       <c r="P445" s="2"/>
@@ -52785,7 +52739,7 @@
         <v>23</v>
       </c>
       <c r="AG445" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AH445" t="s" s="2">
         <v>76</v>
@@ -52805,10 +52759,10 @@
         <v>927</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -52834,10 +52788,10 @@
         <v>732</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="N446" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="O446" s="2"/>
       <c r="P446" s="2"/>
@@ -52888,7 +52842,7 @@
         <v>23</v>
       </c>
       <c r="AG446" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="AH446" t="s" s="2">
         <v>76</v>
@@ -52908,10 +52862,10 @@
         <v>927</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -52937,10 +52891,10 @@
         <v>792</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="N447" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="O447" t="s" s="2">
         <v>795</v>
@@ -52993,7 +52947,7 @@
         <v>23</v>
       </c>
       <c r="AG447" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AH447" t="s" s="2">
         <v>76</v>
@@ -53013,10 +52967,10 @@
         <v>927</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -53042,13 +52996,13 @@
         <v>797</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="N448" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="O448" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="P448" s="2"/>
       <c r="Q448" t="s" s="2">
@@ -53098,7 +53052,7 @@
         <v>23</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>76</v>
@@ -53115,7 +53069,7 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B449" t="s" s="2">
         <v>932</v>
@@ -53218,7 +53172,7 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B450" t="s" s="2">
         <v>935</v>
@@ -53323,7 +53277,7 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B451" t="s" s="2">
         <v>936</v>
@@ -53426,7 +53380,7 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B452" t="s" s="2">
         <v>937</v>
@@ -53531,7 +53485,7 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B453" t="s" s="2">
         <v>938</v>
@@ -53636,7 +53590,7 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B454" t="s" s="2">
         <v>939</v>
@@ -53741,7 +53695,7 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B455" t="s" s="2">
         <v>940</v>
@@ -53846,7 +53800,7 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B456" t="s" s="2">
         <v>941</v>
@@ -53947,7 +53901,7 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B457" t="s" s="2">
         <v>942</v>
@@ -54054,7 +54008,7 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B458" t="s" s="2">
         <v>948</v>
@@ -54161,16 +54115,16 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="C459" t="s" s="2">
         <v>941</v>
       </c>
       <c r="D459" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="E459" t="s" s="2">
         <v>23</v>
@@ -54192,13 +54146,13 @@
         <v>23</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -54266,7 +54220,7 @@
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B460" t="s" s="2">
         <v>949</v>
@@ -54373,7 +54327,7 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B461" t="s" s="2">
         <v>950</v>
@@ -54405,10 +54359,10 @@
         <v>112</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N461" t="s" s="2">
-        <v>1161</v>
+        <v>952</v>
       </c>
       <c r="O461" t="s" s="2">
         <v>666</v>
@@ -54478,7 +54432,7 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B462" t="s" s="2">
         <v>953</v>
@@ -54513,7 +54467,7 @@
         <v>1162</v>
       </c>
       <c r="N462" t="s" s="2">
-        <v>1163</v>
+        <v>955</v>
       </c>
       <c r="O462" t="s" s="2">
         <v>544</v>
@@ -54546,7 +54500,7 @@
       </c>
       <c r="Z462" s="2"/>
       <c r="AA462" t="s" s="2">
-        <v>1164</v>
+        <v>1163</v>
       </c>
       <c r="AB462" t="s" s="2">
         <v>23</v>
@@ -54581,7 +54535,7 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B463" t="s" s="2">
         <v>957</v>
@@ -54613,7 +54567,7 @@
         <v>367</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1165</v>
+        <v>1164</v>
       </c>
       <c r="N463" t="s" s="2">
         <v>959</v>
@@ -54686,7 +54640,7 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B464" t="s" s="2">
         <v>963</v>
@@ -54718,7 +54672,7 @@
         <v>103</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="N464" t="s" s="2">
         <v>965</v>
@@ -54791,7 +54745,7 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B465" t="s" s="2">
         <v>970</v>
@@ -54840,7 +54794,7 @@
         <v>23</v>
       </c>
       <c r="T465" t="s" s="2">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="U465" t="s" s="2">
         <v>23</v>
@@ -54896,7 +54850,7 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B466" t="s" s="2">
         <v>986</v>
@@ -54928,7 +54882,7 @@
         <v>103</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1168</v>
+        <v>1167</v>
       </c>
       <c r="N466" t="s" s="2">
         <v>988</v>
@@ -54999,7 +54953,7 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B467" t="s" s="2">
         <v>991</v>
@@ -55031,7 +54985,7 @@
         <v>385</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1169</v>
+        <v>1168</v>
       </c>
       <c r="N467" t="s" s="2">
         <v>993</v>
@@ -55104,7 +55058,7 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B468" t="s" s="2">
         <v>995</v>
@@ -55136,7 +55090,7 @@
         <v>996</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="N468" t="s" s="2">
         <v>998</v>
@@ -55205,16 +55159,16 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1171</v>
+        <v>1170</v>
       </c>
       <c r="C469" t="s" s="2">
         <v>995</v>
       </c>
       <c r="D469" t="s" s="2">
-        <v>1172</v>
+        <v>1171</v>
       </c>
       <c r="E469" t="s" s="2">
         <v>23</v>
@@ -55236,10 +55190,10 @@
         <v>84</v>
       </c>
       <c r="L469" t="s" s="2">
+        <v>1172</v>
+      </c>
+      <c r="M469" t="s" s="2">
         <v>1173</v>
-      </c>
-      <c r="M469" t="s" s="2">
-        <v>1174</v>
       </c>
       <c r="N469" t="s" s="2">
         <v>998</v>
@@ -55310,16 +55264,16 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1175</v>
+        <v>1174</v>
       </c>
       <c r="C470" t="s" s="2">
         <v>995</v>
       </c>
       <c r="D470" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="E470" t="s" s="2">
         <v>23</v>
@@ -55344,7 +55298,7 @@
         <v>385</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1177</v>
+        <v>1176</v>
       </c>
       <c r="N470" t="s" s="2">
         <v>998</v>
@@ -55415,7 +55369,7 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B471" t="s" s="2">
         <v>999</v>
@@ -55447,7 +55401,7 @@
         <v>695</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1178</v>
+        <v>1177</v>
       </c>
       <c r="N471" t="s" s="2">
         <v>1001</v>
@@ -55520,7 +55474,7 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B472" t="s" s="2">
         <v>1003</v>
@@ -55552,7 +55506,7 @@
         <v>568</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1179</v>
+        <v>1178</v>
       </c>
       <c r="N472" t="s" s="2">
         <v>1005</v>
@@ -55625,7 +55579,7 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B473" t="s" s="2">
         <v>1007</v>
@@ -55657,7 +55611,7 @@
         <v>574</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>1009</v>
@@ -55730,7 +55684,7 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B474" t="s" s="2">
         <v>1011</v>
@@ -55762,7 +55716,7 @@
         <v>708</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
       <c r="N474" t="s" s="2">
         <v>1013</v>
@@ -55833,7 +55787,7 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B475" t="s" s="2">
         <v>1014</v>
@@ -55865,7 +55819,7 @@
         <v>578</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="N475" t="s" s="2">
         <v>1016</v>
@@ -55936,7 +55890,7 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B476" t="s" s="2">
         <v>1017</v>
@@ -55968,7 +55922,7 @@
         <v>724</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1183</v>
+        <v>1182</v>
       </c>
       <c r="N476" t="s" s="2">
         <v>1019</v>
@@ -56039,7 +55993,7 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B477" t="s" s="2">
         <v>1020</v>
@@ -56071,10 +56025,10 @@
         <v>1021</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1184</v>
+        <v>1183</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1022</v>
+        <v>1023</v>
       </c>
       <c r="O477" s="2"/>
       <c r="P477" s="2"/>
@@ -56142,13 +56096,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56174,13 +56128,13 @@
         <v>367</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1024</v>
+        <v>1025</v>
       </c>
       <c r="O478" t="s" s="2">
-        <v>1025</v>
+        <v>1026</v>
       </c>
       <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
@@ -56209,10 +56163,10 @@
         <v>372</v>
       </c>
       <c r="Z478" t="s" s="2">
-        <v>1026</v>
+        <v>1027</v>
       </c>
       <c r="AA478" t="s" s="2">
-        <v>1027</v>
+        <v>1028</v>
       </c>
       <c r="AB478" t="s" s="2">
         <v>23</v>
@@ -56230,7 +56184,7 @@
         <v>23</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1023</v>
+        <v>1024</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>76</v>
@@ -56247,13 +56201,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56279,10 +56233,10 @@
         <v>787</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>1030</v>
+        <v>1031</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -56333,7 +56287,7 @@
         <v>23</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1028</v>
+        <v>1029</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>76</v>
@@ -56350,13 +56304,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56382,13 +56336,13 @@
         <v>367</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1187</v>
+        <v>1186</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="O480" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="P480" s="2"/>
       <c r="Q480" t="s" s="2">
@@ -56417,10 +56371,10 @@
         <v>372</v>
       </c>
       <c r="Z480" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="AA480" t="s" s="2">
-        <v>1036</v>
+        <v>1037</v>
       </c>
       <c r="AB480" t="s" s="2">
         <v>23</v>
@@ -56438,7 +56392,7 @@
         <v>23</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1031</v>
+        <v>1032</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
@@ -56455,13 +56409,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56484,16 +56438,16 @@
         <v>23</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>1038</v>
+        <v>1039</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1039</v>
+        <v>1040</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="O481" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="P481" s="2"/>
       <c r="Q481" t="s" s="2">
@@ -56543,7 +56497,7 @@
         <v>23</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1037</v>
+        <v>1038</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
@@ -56560,13 +56514,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56589,13 +56543,13 @@
         <v>84</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>1043</v>
+        <v>1044</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1188</v>
+        <v>1187</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>1045</v>
+        <v>1046</v>
       </c>
       <c r="O482" s="2"/>
       <c r="P482" s="2"/>
@@ -56646,7 +56600,7 @@
         <v>23</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
@@ -56663,13 +56617,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56695,10 +56649,10 @@
         <v>97</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>1048</v>
+        <v>1049</v>
       </c>
       <c r="O483" s="2"/>
       <c r="P483" s="2"/>
@@ -56749,7 +56703,7 @@
         <v>23</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>1046</v>
+        <v>1047</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
@@ -56766,13 +56720,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -56795,13 +56749,13 @@
         <v>84</v>
       </c>
       <c r="L484" t="s" s="2">
+        <v>1189</v>
+      </c>
+      <c r="M484" t="s" s="2">
         <v>1190</v>
       </c>
-      <c r="M484" t="s" s="2">
-        <v>1191</v>
-      </c>
       <c r="N484" t="s" s="2">
-        <v>1051</v>
+        <v>1052</v>
       </c>
       <c r="O484" s="2"/>
       <c r="P484" s="2"/>
@@ -56852,7 +56806,7 @@
         <v>23</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1049</v>
+        <v>1050</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
@@ -56869,13 +56823,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -56901,14 +56855,14 @@
         <v>112</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>1054</v>
+        <v>1055</v>
       </c>
       <c r="O485" s="2"/>
       <c r="P485" t="s" s="2">
-        <v>1055</v>
+        <v>1056</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>23</v>
@@ -56957,7 +56911,7 @@
         <v>23</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>1052</v>
+        <v>1053</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>76</v>
@@ -56974,13 +56928,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -57006,13 +56960,13 @@
         <v>367</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>1058</v>
+        <v>1059</v>
       </c>
       <c r="O486" t="s" s="2">
-        <v>1059</v>
+        <v>1060</v>
       </c>
       <c r="P486" s="2"/>
       <c r="Q486" t="s" s="2">
@@ -57041,10 +56995,10 @@
         <v>372</v>
       </c>
       <c r="Z486" t="s" s="2">
-        <v>1060</v>
+        <v>1061</v>
       </c>
       <c r="AA486" t="s" s="2">
-        <v>1061</v>
+        <v>1062</v>
       </c>
       <c r="AB486" t="s" s="2">
         <v>23</v>
@@ -57062,7 +57016,7 @@
         <v>23</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1056</v>
+        <v>1057</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>76</v>
@@ -57079,13 +57033,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -57108,13 +57062,13 @@
         <v>23</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1194</v>
+        <v>1190</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="O487" s="2"/>
       <c r="P487" s="2"/>
@@ -57165,7 +57119,7 @@
         <v>23</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -57182,13 +57136,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -57214,10 +57168,10 @@
         <v>598</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>1195</v>
+        <v>1193</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>1068</v>
+        <v>1069</v>
       </c>
       <c r="O488" s="2"/>
       <c r="P488" s="2"/>
@@ -57268,7 +57222,7 @@
         <v>23</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
@@ -57285,13 +57239,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -57314,16 +57268,16 @@
         <v>23</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>1070</v>
+        <v>1071</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1196</v>
+        <v>1194</v>
       </c>
       <c r="N489" t="s" s="2">
         <v>765</v>
       </c>
       <c r="O489" t="s" s="2">
-        <v>1072</v>
+        <v>1073</v>
       </c>
       <c r="P489" s="2"/>
       <c r="Q489" t="s" s="2">
@@ -57373,7 +57327,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1069</v>
+        <v>1070</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57390,13 +57344,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -57422,10 +57376,10 @@
         <v>136</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1197</v>
+        <v>1195</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1075</v>
+        <v>1076</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -57476,7 +57430,7 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1073</v>
+        <v>1074</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -57493,13 +57447,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1076</v>
+        <v>1077</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57596,13 +57550,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1077</v>
+        <v>1078</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57701,13 +57655,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1078</v>
+        <v>1079</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57808,13 +57762,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57840,13 +57794,13 @@
         <v>136</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1080</v>
+        <v>1081</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1081</v>
+        <v>1082</v>
       </c>
       <c r="O494" t="s" s="2">
-        <v>1082</v>
+        <v>1083</v>
       </c>
       <c r="P494" s="2"/>
       <c r="Q494" t="s" s="2">
@@ -57896,7 +57850,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1079</v>
+        <v>1080</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -57913,13 +57867,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1083</v>
+        <v>1084</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -58016,13 +57970,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1084</v>
+        <v>1085</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -58121,13 +58075,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -58228,13 +58182,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58260,10 +58214,10 @@
         <v>497</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1198</v>
+        <v>1196</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>1088</v>
+        <v>1089</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -58314,7 +58268,7 @@
         <v>23</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -58331,13 +58285,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -58360,13 +58314,13 @@
         <v>23</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>1091</v>
+        <v>1092</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>1092</v>
+        <v>1093</v>
       </c>
       <c r="O499" s="2"/>
       <c r="P499" s="2"/>
@@ -58417,7 +58371,7 @@
         <v>23</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1089</v>
+        <v>1090</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
@@ -58434,13 +58388,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -58463,13 +58417,13 @@
         <v>23</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1199</v>
+        <v>1197</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>1095</v>
+        <v>1096</v>
       </c>
       <c r="O500" s="2"/>
       <c r="P500" s="2"/>
@@ -58520,7 +58474,7 @@
         <v>23</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>1093</v>
+        <v>1094</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
@@ -58537,13 +58491,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -58566,19 +58520,19 @@
         <v>23</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1200</v>
+        <v>1198</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1201</v>
+        <v>1199</v>
       </c>
       <c r="O501" t="s" s="2">
-        <v>1100</v>
+        <v>1101</v>
       </c>
       <c r="P501" t="s" s="2">
-        <v>1101</v>
+        <v>1102</v>
       </c>
       <c r="Q501" t="s" s="2">
         <v>23</v>
@@ -58627,7 +58581,7 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1096</v>
+        <v>1097</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>76</v>
@@ -58644,13 +58598,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58676,13 +58630,13 @@
         <v>130</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1103</v>
+        <v>1104</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1104</v>
+        <v>1105</v>
       </c>
       <c r="O502" t="s" s="2">
-        <v>1105</v>
+        <v>1106</v>
       </c>
       <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
@@ -58732,7 +58686,7 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1102</v>
+        <v>1103</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>76</v>
@@ -58749,13 +58703,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58781,10 +58735,10 @@
         <v>497</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1202</v>
+        <v>1200</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1108</v>
+        <v>1109</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -58835,7 +58789,7 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1106</v>
+        <v>1107</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
@@ -58852,13 +58806,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58881,16 +58835,16 @@
         <v>23</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1110</v>
+        <v>1111</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1111</v>
+        <v>1112</v>
       </c>
       <c r="O504" t="s" s="2">
-        <v>1112</v>
+        <v>1113</v>
       </c>
       <c r="P504" s="2"/>
       <c r="Q504" t="s" s="2">
@@ -58940,7 +58894,7 @@
         <v>23</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1109</v>
+        <v>1110</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -58957,13 +58911,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58989,10 +58943,10 @@
         <v>880</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1203</v>
+        <v>1201</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="O505" s="2"/>
       <c r="P505" s="2"/>
@@ -59043,7 +58997,7 @@
         <v>23</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1122</v>
+        <v>1123</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -59060,13 +59014,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -59092,10 +59046,10 @@
         <v>136</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="O506" s="2"/>
       <c r="P506" s="2"/>
@@ -59146,7 +59100,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59163,13 +59117,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59266,13 +59220,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59371,13 +59325,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59478,13 +59432,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59507,16 +59461,16 @@
         <v>23</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="O510" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="P510" s="2"/>
       <c r="Q510" t="s" s="2">
@@ -59545,7 +59499,7 @@
         <v>372</v>
       </c>
       <c r="Z510" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AA510" t="s" s="2">
         <v>780</v>
@@ -59566,7 +59520,7 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>83</v>
@@ -59583,13 +59537,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59615,10 +59569,10 @@
         <v>367</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="O511" s="2"/>
       <c r="P511" s="2"/>
@@ -59669,7 +59623,7 @@
         <v>23</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -59686,13 +59640,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59718,10 +59672,10 @@
         <v>732</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>1205</v>
+        <v>1203</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="O512" s="2"/>
       <c r="P512" s="2"/>
@@ -59772,7 +59726,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -59789,13 +59743,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59821,10 +59775,10 @@
         <v>792</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>1206</v>
+        <v>1204</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="O513" t="s" s="2">
         <v>795</v>
@@ -59877,7 +59831,7 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
@@ -59894,13 +59848,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59926,13 +59880,13 @@
         <v>797</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>1207</v>
+        <v>1205</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
@@ -59982,7 +59936,7 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>76</v>
@@ -59999,13 +59953,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -60031,10 +59985,10 @@
         <v>78</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="O515" s="2"/>
       <c r="P515" s="2"/>
@@ -60085,7 +60039,7 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>1213</v>
+        <v>1211</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>76</v>
@@ -60102,13 +60056,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -60207,13 +60161,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1218</v>
+        <v>1216</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60310,13 +60264,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1219</v>
+        <v>1217</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60415,13 +60369,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60520,13 +60474,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1221</v>
+        <v>1219</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60625,13 +60579,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1222</v>
+        <v>1220</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60730,13 +60684,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1223</v>
+        <v>1221</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60835,13 +60789,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1224</v>
+        <v>1222</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60942,13 +60896,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60974,13 +60928,13 @@
         <v>112</v>
       </c>
       <c r="M524" t="s" s="2">
+        <v>1224</v>
+      </c>
+      <c r="N524" t="s" s="2">
+        <v>1225</v>
+      </c>
+      <c r="O524" t="s" s="2">
         <v>1226</v>
-      </c>
-      <c r="N524" t="s" s="2">
-        <v>1227</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>1228</v>
       </c>
       <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
@@ -61030,7 +60984,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -61047,13 +61001,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61079,10 +61033,10 @@
         <v>103</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="O525" s="2"/>
       <c r="P525" s="2"/>
@@ -61112,10 +61066,10 @@
         <v>121</v>
       </c>
       <c r="Z525" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="AA525" t="s" s="2">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="AB525" t="s" s="2">
         <v>23</v>
@@ -61133,7 +61087,7 @@
         <v>23</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
@@ -61150,13 +61104,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61182,13 +61136,13 @@
         <v>367</v>
       </c>
       <c r="M526" t="s" s="2">
+        <v>1232</v>
+      </c>
+      <c r="N526" t="s" s="2">
+        <v>1233</v>
+      </c>
+      <c r="O526" t="s" s="2">
         <v>1234</v>
-      </c>
-      <c r="N526" t="s" s="2">
-        <v>1235</v>
-      </c>
-      <c r="O526" t="s" s="2">
-        <v>1236</v>
       </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
@@ -61214,14 +61168,14 @@
         <v>23</v>
       </c>
       <c r="Y526" t="s" s="2">
+        <v>1235</v>
+      </c>
+      <c r="Z526" t="s" s="2">
+        <v>1236</v>
+      </c>
+      <c r="AA526" t="s" s="2">
         <v>1237</v>
       </c>
-      <c r="Z526" t="s" s="2">
-        <v>1238</v>
-      </c>
-      <c r="AA526" t="s" s="2">
-        <v>1239</v>
-      </c>
       <c r="AB526" t="s" s="2">
         <v>23</v>
       </c>
@@ -61238,7 +61192,7 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61255,13 +61209,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61287,13 +61241,13 @@
         <v>367</v>
       </c>
       <c r="M527" t="s" s="2">
+        <v>1239</v>
+      </c>
+      <c r="N527" t="s" s="2">
+        <v>1240</v>
+      </c>
+      <c r="O527" t="s" s="2">
         <v>1241</v>
-      </c>
-      <c r="N527" t="s" s="2">
-        <v>1242</v>
-      </c>
-      <c r="O527" t="s" s="2">
-        <v>1243</v>
       </c>
       <c r="P527" s="2"/>
       <c r="Q527" t="s" s="2">
@@ -61322,10 +61276,10 @@
         <v>372</v>
       </c>
       <c r="Z527" t="s" s="2">
-        <v>1244</v>
+        <v>1242</v>
       </c>
       <c r="AA527" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="AB527" t="s" s="2">
         <v>23</v>
@@ -61343,7 +61297,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>83</v>
@@ -61360,13 +61314,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61392,10 +61346,10 @@
         <v>141</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1247</v>
+        <v>1245</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1248</v>
+        <v>1246</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61446,7 +61400,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1246</v>
+        <v>1244</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61463,13 +61417,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61495,10 +61449,10 @@
         <v>136</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1250</v>
+        <v>1248</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1251</v>
+        <v>1249</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61506,7 +61460,7 @@
         <v>23</v>
       </c>
       <c r="R529" t="s" s="2">
-        <v>1252</v>
+        <v>1250</v>
       </c>
       <c r="S529" t="s" s="2">
         <v>23</v>
@@ -61551,7 +61505,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1249</v>
+        <v>1247</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61568,13 +61522,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1253</v>
+        <v>1251</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61671,13 +61625,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1254</v>
+        <v>1252</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61776,13 +61730,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1255</v>
+        <v>1253</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61883,13 +61837,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61915,10 +61869,10 @@
         <v>112</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1257</v>
+        <v>1255</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1258</v>
+        <v>1256</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -61969,7 +61923,7 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1256</v>
+        <v>1254</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>76</v>
@@ -61986,13 +61940,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -62018,10 +61972,10 @@
         <v>578</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>1260</v>
+        <v>1258</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>1261</v>
+        <v>1259</v>
       </c>
       <c r="O534" s="2"/>
       <c r="P534" s="2"/>
@@ -62072,7 +62026,7 @@
         <v>23</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1259</v>
+        <v>1257</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>76</v>
@@ -62089,13 +62043,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -62121,10 +62075,10 @@
         <v>497</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1263</v>
+        <v>1261</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1264</v>
+        <v>1262</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -62175,7 +62129,7 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1262</v>
+        <v>1260</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -62192,13 +62146,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62224,10 +62178,10 @@
         <v>136</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1266</v>
+        <v>1264</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1267</v>
+        <v>1265</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -62278,7 +62232,7 @@
         <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1265</v>
+        <v>1263</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
@@ -62295,13 +62249,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1268</v>
+        <v>1266</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62398,13 +62352,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1269</v>
+        <v>1267</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62503,13 +62457,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1270</v>
+        <v>1268</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62610,13 +62564,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62642,10 +62596,10 @@
         <v>491</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1272</v>
+        <v>1270</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1273</v>
+        <v>1271</v>
       </c>
       <c r="O540" s="2"/>
       <c r="P540" s="2"/>
@@ -62696,7 +62650,7 @@
         <v>23</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>76</v>
@@ -62713,13 +62667,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1208</v>
+        <v>1206</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62742,13 +62696,13 @@
         <v>84</v>
       </c>
       <c r="L541" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="M541" t="s" s="2">
+        <v>1274</v>
+      </c>
+      <c r="N541" t="s" s="2">
         <v>1275</v>
-      </c>
-      <c r="M541" t="s" s="2">
-        <v>1276</v>
-      </c>
-      <c r="N541" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="O541" s="2"/>
       <c r="P541" s="2"/>
@@ -62778,10 +62732,10 @@
         <v>372</v>
       </c>
       <c r="Z541" t="s" s="2">
-        <v>1278</v>
+        <v>1276</v>
       </c>
       <c r="AA541" t="s" s="2">
-        <v>1245</v>
+        <v>1243</v>
       </c>
       <c r="AB541" t="s" s="2">
         <v>23</v>
@@ -62799,7 +62753,7 @@
         <v>23</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1274</v>
+        <v>1272</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>83</v>
@@ -62816,13 +62770,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62848,13 +62802,13 @@
         <v>78</v>
       </c>
       <c r="M542" t="s" s="2">
+        <v>1283</v>
+      </c>
+      <c r="N542" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="O542" t="s" s="2">
         <v>1285</v>
-      </c>
-      <c r="N542" t="s" s="2">
-        <v>1286</v>
-      </c>
-      <c r="O542" t="s" s="2">
-        <v>1287</v>
       </c>
       <c r="P542" s="2"/>
       <c r="Q542" t="s" s="2">
@@ -62904,7 +62858,7 @@
         <v>23</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1283</v>
+        <v>1281</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
@@ -62921,13 +62875,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1288</v>
+        <v>1286</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -63024,13 +62978,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1289</v>
+        <v>1287</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -63129,13 +63083,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63236,13 +63190,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63268,14 +63222,14 @@
         <v>578</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>1292</v>
+        <v>1290</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>1293</v>
+        <v>1291</v>
       </c>
       <c r="O546" s="2"/>
       <c r="P546" t="s" s="2">
-        <v>1294</v>
+        <v>1292</v>
       </c>
       <c r="Q546" t="s" s="2">
         <v>23</v>
@@ -63324,7 +63278,7 @@
         <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -63341,13 +63295,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63373,14 +63327,14 @@
         <v>418</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>1296</v>
+        <v>1294</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="O547" s="2"/>
       <c r="P547" t="s" s="2">
-        <v>1298</v>
+        <v>1296</v>
       </c>
       <c r="Q547" t="s" s="2">
         <v>23</v>
@@ -63429,7 +63383,7 @@
         <v>23</v>
       </c>
       <c r="AG547" t="s" s="2">
-        <v>1295</v>
+        <v>1293</v>
       </c>
       <c r="AH547" t="s" s="2">
         <v>76</v>
@@ -63441,18 +63395,18 @@
         <v>23</v>
       </c>
       <c r="AK547" t="s" s="2">
-        <v>1299</v>
+        <v>1297</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1300</v>
+        <v>1298</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63549,13 +63503,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63654,13 +63608,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63683,13 +63637,13 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
+        <v>1301</v>
+      </c>
+      <c r="M550" t="s" s="2">
+        <v>1302</v>
+      </c>
+      <c r="N550" t="s" s="2">
         <v>1303</v>
-      </c>
-      <c r="M550" t="s" s="2">
-        <v>1304</v>
-      </c>
-      <c r="N550" t="s" s="2">
-        <v>1305</v>
       </c>
       <c r="O550" s="2"/>
       <c r="P550" s="2"/>
@@ -63738,7 +63692,7 @@
         <v>355</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63755,16 +63709,16 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="D551" t="s" s="2">
-        <v>1307</v>
+        <v>1305</v>
       </c>
       <c r="E551" t="s" s="2">
         <v>23</v>
@@ -63786,13 +63740,13 @@
         <v>84</v>
       </c>
       <c r="L551" t="s" s="2">
-        <v>1097</v>
+        <v>1098</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>1304</v>
+        <v>1302</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>1305</v>
+        <v>1303</v>
       </c>
       <c r="O551" s="2"/>
       <c r="P551" s="2"/>
@@ -63843,7 +63797,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1302</v>
+        <v>1300</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63860,13 +63814,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1308</v>
+        <v>1306</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63963,13 +63917,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1311</v>
+        <v>1309</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -64068,13 +64022,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1312</v>
+        <v>1310</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1313</v>
+        <v>1311</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -64100,13 +64054,13 @@
         <v>578</v>
       </c>
       <c r="M554" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="N554" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="O554" t="s" s="2">
         <v>1314</v>
-      </c>
-      <c r="N554" t="s" s="2">
-        <v>1315</v>
-      </c>
-      <c r="O554" t="s" s="2">
-        <v>1316</v>
       </c>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
@@ -64156,7 +64110,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1317</v>
+        <v>1315</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64165,7 +64119,7 @@
         <v>83</v>
       </c>
       <c r="AJ554" t="s" s="2">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="AK554" t="s" s="2">
         <v>95</v>
@@ -64173,13 +64127,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1319</v>
+        <v>1317</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1320</v>
+        <v>1318</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64205,20 +64159,20 @@
         <v>578</v>
       </c>
       <c r="M555" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="N555" t="s" s="2">
+        <v>1320</v>
+      </c>
+      <c r="O555" t="s" s="2">
         <v>1321</v>
-      </c>
-      <c r="N555" t="s" s="2">
-        <v>1322</v>
-      </c>
-      <c r="O555" t="s" s="2">
-        <v>1323</v>
       </c>
       <c r="P555" s="2"/>
       <c r="Q555" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R555" t="s" s="2">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="S555" t="s" s="2">
         <v>23</v>
@@ -64263,7 +64217,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64272,7 +64226,7 @@
         <v>83</v>
       </c>
       <c r="AJ555" t="s" s="2">
-        <v>1318</v>
+        <v>1316</v>
       </c>
       <c r="AK555" t="s" s="2">
         <v>95</v>
@@ -64280,13 +64234,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64309,19 +64263,19 @@
         <v>84</v>
       </c>
       <c r="L556" t="s" s="2">
+        <v>1325</v>
+      </c>
+      <c r="M556" t="s" s="2">
+        <v>1326</v>
+      </c>
+      <c r="N556" t="s" s="2">
         <v>1327</v>
       </c>
-      <c r="M556" t="s" s="2">
+      <c r="O556" t="s" s="2">
         <v>1328</v>
       </c>
-      <c r="N556" t="s" s="2">
+      <c r="P556" t="s" s="2">
         <v>1329</v>
-      </c>
-      <c r="O556" t="s" s="2">
-        <v>1330</v>
-      </c>
-      <c r="P556" t="s" s="2">
-        <v>1331</v>
       </c>
       <c r="Q556" t="s" s="2">
         <v>23</v>
@@ -64370,7 +64324,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64387,13 +64341,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64416,13 +64370,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1333</v>
+        <v>1331</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1334</v>
+        <v>1332</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64473,7 +64427,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1332</v>
+        <v>1330</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64490,13 +64444,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64522,16 +64476,16 @@
         <v>199</v>
       </c>
       <c r="M558" t="s" s="2">
+        <v>1334</v>
+      </c>
+      <c r="N558" t="s" s="2">
+        <v>1335</v>
+      </c>
+      <c r="O558" t="s" s="2">
         <v>1336</v>
       </c>
-      <c r="N558" t="s" s="2">
+      <c r="P558" t="s" s="2">
         <v>1337</v>
-      </c>
-      <c r="O558" t="s" s="2">
-        <v>1338</v>
-      </c>
-      <c r="P558" t="s" s="2">
-        <v>1339</v>
       </c>
       <c r="Q558" t="s" s="2">
         <v>23</v>
@@ -64580,7 +64534,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1335</v>
+        <v>1333</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64597,13 +64551,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64629,16 +64583,16 @@
         <v>199</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1342</v>
+        <v>1340</v>
       </c>
       <c r="O559" t="s" s="2">
-        <v>1338</v>
+        <v>1336</v>
       </c>
       <c r="P559" t="s" s="2">
-        <v>1339</v>
+        <v>1337</v>
       </c>
       <c r="Q559" t="s" s="2">
         <v>23</v>
@@ -64687,7 +64641,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1340</v>
+        <v>1338</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64704,13 +64658,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64736,10 +64690,10 @@
         <v>103</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1344</v>
+        <v>1342</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1345</v>
+        <v>1343</v>
       </c>
       <c r="O560" s="2"/>
       <c r="P560" s="2"/>
@@ -64769,10 +64723,10 @@
         <v>121</v>
       </c>
       <c r="Z560" t="s" s="2">
-        <v>1346</v>
+        <v>1344</v>
       </c>
       <c r="AA560" t="s" s="2">
-        <v>1347</v>
+        <v>1345</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64790,7 +64744,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1343</v>
+        <v>1341</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64807,13 +64761,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64836,13 +64790,13 @@
         <v>84</v>
       </c>
       <c r="L561" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1349</v>
+        <v>1347</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="O561" s="2"/>
       <c r="P561" s="2"/>
@@ -64850,7 +64804,7 @@
         <v>23</v>
       </c>
       <c r="R561" t="s" s="2">
-        <v>1351</v>
+        <v>1349</v>
       </c>
       <c r="S561" t="s" s="2">
         <v>23</v>
@@ -64895,7 +64849,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1348</v>
+        <v>1346</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64912,13 +64866,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64941,13 +64895,13 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1353</v>
+        <v>1351</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1354</v>
+        <v>1352</v>
       </c>
       <c r="O562" s="2"/>
       <c r="P562" s="2"/>
@@ -64998,7 +64952,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1352</v>
+        <v>1350</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -65015,13 +64969,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -65047,10 +65001,10 @@
         <v>199</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1356</v>
+        <v>1354</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1357</v>
+        <v>1355</v>
       </c>
       <c r="O563" s="2"/>
       <c r="P563" s="2"/>
@@ -65101,7 +65055,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65118,13 +65072,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65150,10 +65104,10 @@
         <v>199</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1359</v>
+        <v>1357</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1360</v>
+        <v>1358</v>
       </c>
       <c r="O564" s="2"/>
       <c r="P564" s="2"/>
@@ -65204,7 +65158,7 @@
         <v>23</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1358</v>
+        <v>1356</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -65221,13 +65175,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65253,10 +65207,10 @@
         <v>103</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1362</v>
+        <v>1360</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1363</v>
+        <v>1361</v>
       </c>
       <c r="O565" s="2"/>
       <c r="P565" s="2"/>
@@ -65287,7 +65241,7 @@
       </c>
       <c r="Z565" s="2"/>
       <c r="AA565" t="s" s="2">
-        <v>1364</v>
+        <v>1362</v>
       </c>
       <c r="AB565" t="s" s="2">
         <v>23</v>
@@ -65305,7 +65259,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1361</v>
+        <v>1359</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>
@@ -65322,13 +65276,13 @@
     </row>
     <row r="566">
       <c r="A566" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B566" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="C566" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="D566" s="2"/>
       <c r="E566" t="s" s="2">
@@ -65354,13 +65308,13 @@
         <v>103</v>
       </c>
       <c r="M566" t="s" s="2">
+        <v>1364</v>
+      </c>
+      <c r="N566" t="s" s="2">
+        <v>1365</v>
+      </c>
+      <c r="O566" t="s" s="2">
         <v>1366</v>
-      </c>
-      <c r="N566" t="s" s="2">
-        <v>1367</v>
-      </c>
-      <c r="O566" t="s" s="2">
-        <v>1368</v>
       </c>
       <c r="P566" s="2"/>
       <c r="Q566" t="s" s="2">
@@ -65390,7 +65344,7 @@
       </c>
       <c r="Z566" s="2"/>
       <c r="AA566" t="s" s="2">
-        <v>1369</v>
+        <v>1367</v>
       </c>
       <c r="AB566" t="s" s="2">
         <v>23</v>
@@ -65408,7 +65362,7 @@
         <v>23</v>
       </c>
       <c r="AG566" t="s" s="2">
-        <v>1365</v>
+        <v>1363</v>
       </c>
       <c r="AH566" t="s" s="2">
         <v>76</v>
@@ -65425,13 +65379,13 @@
     </row>
     <row r="567">
       <c r="A567" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B567" t="s" s="2">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="C567" t="s" s="2">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="D567" s="2"/>
       <c r="E567" t="s" s="2">
@@ -65454,16 +65408,16 @@
         <v>84</v>
       </c>
       <c r="L567" t="s" s="2">
+        <v>1369</v>
+      </c>
+      <c r="M567" t="s" s="2">
+        <v>1370</v>
+      </c>
+      <c r="N567" t="s" s="2">
         <v>1371</v>
       </c>
-      <c r="M567" t="s" s="2">
+      <c r="O567" t="s" s="2">
         <v>1372</v>
-      </c>
-      <c r="N567" t="s" s="2">
-        <v>1373</v>
-      </c>
-      <c r="O567" t="s" s="2">
-        <v>1374</v>
       </c>
       <c r="P567" s="2"/>
       <c r="Q567" t="s" s="2">
@@ -65513,7 +65467,7 @@
         <v>23</v>
       </c>
       <c r="AG567" t="s" s="2">
-        <v>1370</v>
+        <v>1368</v>
       </c>
       <c r="AH567" t="s" s="2">
         <v>76</v>
@@ -65530,13 +65484,13 @@
     </row>
     <row r="568">
       <c r="A568" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B568" t="s" s="2">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="C568" t="s" s="2">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="D568" s="2"/>
       <c r="E568" t="s" s="2">
@@ -65562,16 +65516,16 @@
         <v>103</v>
       </c>
       <c r="M568" t="s" s="2">
+        <v>1374</v>
+      </c>
+      <c r="N568" t="s" s="2">
+        <v>1375</v>
+      </c>
+      <c r="O568" t="s" s="2">
         <v>1376</v>
       </c>
-      <c r="N568" t="s" s="2">
+      <c r="P568" t="s" s="2">
         <v>1377</v>
-      </c>
-      <c r="O568" t="s" s="2">
-        <v>1378</v>
-      </c>
-      <c r="P568" t="s" s="2">
-        <v>1379</v>
       </c>
       <c r="Q568" t="s" s="2">
         <v>23</v>
@@ -65600,7 +65554,7 @@
       </c>
       <c r="Z568" s="2"/>
       <c r="AA568" t="s" s="2">
-        <v>1380</v>
+        <v>1378</v>
       </c>
       <c r="AB568" t="s" s="2">
         <v>23</v>
@@ -65618,7 +65572,7 @@
         <v>23</v>
       </c>
       <c r="AG568" t="s" s="2">
-        <v>1375</v>
+        <v>1373</v>
       </c>
       <c r="AH568" t="s" s="2">
         <v>76</v>
@@ -65635,13 +65589,13 @@
     </row>
     <row r="569">
       <c r="A569" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B569" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="C569" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="D569" s="2"/>
       <c r="E569" t="s" s="2">
@@ -65667,10 +65621,10 @@
         <v>130</v>
       </c>
       <c r="M569" t="s" s="2">
-        <v>1382</v>
+        <v>1380</v>
       </c>
       <c r="N569" t="s" s="2">
-        <v>1383</v>
+        <v>1381</v>
       </c>
       <c r="O569" s="2"/>
       <c r="P569" s="2"/>
@@ -65721,7 +65675,7 @@
         <v>23</v>
       </c>
       <c r="AG569" t="s" s="2">
-        <v>1381</v>
+        <v>1379</v>
       </c>
       <c r="AH569" t="s" s="2">
         <v>76</v>
@@ -65738,13 +65692,13 @@
     </row>
     <row r="570">
       <c r="A570" t="s" s="2">
-        <v>1279</v>
+        <v>1277</v>
       </c>
       <c r="B570" t="s" s="2">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="C570" t="s" s="2">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="D570" s="2"/>
       <c r="E570" t="s" s="2">
@@ -65770,13 +65724,13 @@
         <v>367</v>
       </c>
       <c r="M570" t="s" s="2">
+        <v>1383</v>
+      </c>
+      <c r="N570" t="s" s="2">
+        <v>1384</v>
+      </c>
+      <c r="O570" t="s" s="2">
         <v>1385</v>
-      </c>
-      <c r="N570" t="s" s="2">
-        <v>1386</v>
-      </c>
-      <c r="O570" t="s" s="2">
-        <v>1387</v>
       </c>
       <c r="P570" s="2"/>
       <c r="Q570" t="s" s="2">
@@ -65805,10 +65759,10 @@
         <v>107</v>
       </c>
       <c r="Z570" t="s" s="2">
-        <v>1388</v>
+        <v>1386</v>
       </c>
       <c r="AA570" t="s" s="2">
-        <v>1389</v>
+        <v>1387</v>
       </c>
       <c r="AB570" t="s" s="2">
         <v>23</v>
@@ -65826,7 +65780,7 @@
         <v>23</v>
       </c>
       <c r="AG570" t="s" s="2">
-        <v>1384</v>
+        <v>1382</v>
       </c>
       <c r="AH570" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-20T19:04:12+00:00</t>
+    <t>2026-04-21T08:44:51+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T08:44:51+00:00</t>
+    <t>2026-04-21T11:54:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T11:54:48+00:00</t>
+    <t>2026-04-21T14:09:10+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T14:09:10+00:00</t>
+    <t>2026-04-21T17:01:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-21T17:01:26+00:00</t>
+    <t>2026-04-22T08:49:17+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T08:49:17+00:00</t>
+    <t>2026-04-22T10:01:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2042,7 +2042,7 @@
     <t>http://hl7.org/fhir/StructureDefinition/MedicationDispense</t>
   </si>
   <si>
-    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zum Medikationsplan. Verwendet R5 Backport Extensions.</t>
+    <t>Durchgeführte Abgabe eines Arzneimittels mit oder ohne Bezug zur geplanten Abgabe. Verwendet R5 Backport Extensions.</t>
   </si>
   <si>
     <t>Indicates that a medication product is to be or has been dispensed for a named person/patient.  This includes a description of the medication product (supply) provided and the instructions for administering the medication.  The medication dispense is the result of a pharmacy system responding to a medication order.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-22T10:11:27+00:00</t>
+    <t>2026-04-28T11:58:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-04-30T15:16:21+00:00</t>
+    <t>2026-04-30T15:23:35+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18865" uniqueCount="1359">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18832" uniqueCount="1354">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-04T14:46:25+00:00</t>
+    <t>2026-05-08T13:20:53+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2865,7 +2865,7 @@
     <t>MedicationRequest.identifier</t>
   </si>
   <si>
-    <t>Gepante-Abgabe-ID.</t>
+    <t>Logischer Identifier. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this medication request that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -3425,8 +3425,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht.
-Erläutert die Absicht des verschreibenden Arztes. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -3517,22 +3516,6 @@
     <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
 Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
 Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.extension:offLabelUse</t>
-  </si>
-  <si>
-    <t>offLabelUse</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Extension {https://profiles.ihe.net/PHARM/MPD/StructureDefinition/ihe-ext-offLabel}
-</t>
-  </si>
-  <si>
-    <t>Weist darauf hin, dass der verschreibende Arzt das Medikament wissentlich für eine Indikation, Altersgruppe, Dosierung oder Verabreichungsform verschrieben hat, die nicht von den Aufsichtsbehörden zugelassen ist und in der Verschreibungsinformation für das Produkt nicht erwähnt wird.</t>
-  </si>
-  <si>
-    <t>Indicates that the prescriber has intentionally prescribed the medication in a manner not covered by the product authorization — such as for a different indication, age group, dosage, or route of administration.</t>
   </si>
   <si>
     <t>Medikationsplaneintrag-ID.</t>
@@ -3608,7 +3591,7 @@
     <t>Priorität des Medikationsplaneintrag: (req) routine | urgent | asap | stat. Keine Verwendung in Medikationsplaneintrag.</t>
   </si>
   <si>
-    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie). TODO: Fachlich zu prüfen, ob dieser Usecase existiert. Auch im Kontext mit status und statusReason zu betrachten. Evtl. erst in späterer Version</t>
+    <t>Gibt an, ob der Medikationsplaneintrag die Verordnung einer Medikation (und somit die Erstellung einer geplanten Abgabe) untersagt (z.B. bei Allergie).</t>
   </si>
   <si>
     <t>Reported rather than primary record</t>
@@ -3682,7 +3665,7 @@
     <t>Erst bei der geplanten Abgabe (Rezepterstellung) relevant.</t>
   </si>
   <si>
-    <t>Gesamtmuster der Medikamentengabe. continuous | acute | seasonal.</t>
+    <t>Gesamtmuster der Medikamentengabe. Mögliche Ausprägungen: [continuous | acute ]</t>
   </si>
   <si>
     <t>Zusätzliche Informationen zum Medikationsplaneintrag.</t>
@@ -3712,7 +3695,7 @@
     <t>Intended dispenser</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf oder nicht. Erläutert die Absicht des Arztes, der den Medikationsplaneintrag erstellt. Wenn nichts angegeben ist, kann eine Substitution vorgenommen werden.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der den Medikationsplaneintrag erstellt). Derzeit keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
     <t>Im Falle einer Änderung wird auf den ersetzten Medikationsplaneintrag verwiesen.</t>
@@ -5788,7 +5771,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
     </row>
     <row r="179">
@@ -5796,7 +5779,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1178</v>
+        <v>1173</v>
       </c>
     </row>
     <row r="180">
@@ -5812,7 +5795,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1179</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="182">
@@ -5820,7 +5803,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1180</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="183">
@@ -5882,7 +5865,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1181</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="191">
@@ -5918,7 +5901,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1182</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="196">
@@ -5926,7 +5909,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1183</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="197">
@@ -5958,7 +5941,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
     </row>
     <row r="201">
@@ -5966,7 +5949,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1249</v>
+        <v>1244</v>
       </c>
     </row>
     <row r="202">
@@ -5982,7 +5965,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1250</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="204">
@@ -5990,7 +5973,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1251</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="205">
@@ -6052,7 +6035,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1251</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="213">
@@ -6088,7 +6071,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1252</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="218">
@@ -6096,7 +6079,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1253</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="219">
@@ -6122,7 +6105,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK563"/>
+  <dimension ref="A1:AK562"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="29.828125" customWidth="true" bestFit="true"/>
@@ -52860,44 +52843,46 @@
         <v>1107</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>1112</v>
+        <v>905</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>897</v>
-      </c>
-      <c r="D448" t="s" s="2">
-        <v>1113</v>
-      </c>
+        <v>905</v>
+      </c>
+      <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F448" s="2"/>
       <c r="G448" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H448" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I448" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J448" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K448" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L448" t="s" s="2">
-        <v>1114</v>
+        <v>147</v>
       </c>
       <c r="M448" t="s" s="2">
-        <v>1115</v>
+        <v>535</v>
       </c>
       <c r="N448" t="s" s="2">
-        <v>1116</v>
-      </c>
-      <c r="O448" s="2"/>
-      <c r="P448" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O448" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P448" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q448" t="s" s="2">
         <v>23</v>
       </c>
@@ -52945,7 +52930,7 @@
         <v>23</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>76</v>
@@ -52954,7 +52939,7 @@
         <v>77</v>
       </c>
       <c r="AJ448" t="s" s="2">
-        <v>661</v>
+        <v>23</v>
       </c>
       <c r="AK448" t="s" s="2">
         <v>152</v>
@@ -52965,46 +52950,44 @@
         <v>1107</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>905</v>
+        <v>906</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F449" s="2"/>
       <c r="G449" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H449" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I449" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J449" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K449" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L449" t="s" s="2">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>535</v>
+        <v>1112</v>
       </c>
       <c r="N449" t="s" s="2">
-        <v>536</v>
+        <v>908</v>
       </c>
       <c r="O449" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P449" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>666</v>
+      </c>
+      <c r="P449" s="2"/>
       <c r="Q449" t="s" s="2">
         <v>23</v>
       </c>
@@ -53052,7 +53035,7 @@
         <v>23</v>
       </c>
       <c r="AG449" t="s" s="2">
-        <v>537</v>
+        <v>906</v>
       </c>
       <c r="AH449" t="s" s="2">
         <v>76</v>
@@ -53064,7 +53047,7 @@
         <v>23</v>
       </c>
       <c r="AK449" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="450">
@@ -53072,10 +53055,10 @@
         <v>1107</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -53089,25 +53072,25 @@
         <v>83</v>
       </c>
       <c r="I450" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J450" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K450" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L450" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>1117</v>
+        <v>1113</v>
       </c>
       <c r="N450" t="s" s="2">
-        <v>908</v>
+        <v>911</v>
       </c>
       <c r="O450" t="s" s="2">
-        <v>666</v>
+        <v>544</v>
       </c>
       <c r="P450" s="2"/>
       <c r="Q450" t="s" s="2">
@@ -53133,13 +53116,11 @@
         <v>23</v>
       </c>
       <c r="Y450" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z450" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z450" s="2"/>
       <c r="AA450" t="s" s="2">
-        <v>23</v>
+        <v>1114</v>
       </c>
       <c r="AB450" t="s" s="2">
         <v>23</v>
@@ -53157,13 +53138,13 @@
         <v>23</v>
       </c>
       <c r="AG450" t="s" s="2">
-        <v>906</v>
+        <v>909</v>
       </c>
       <c r="AH450" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI450" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ450" t="s" s="2">
         <v>23</v>
@@ -53177,10 +53158,10 @@
         <v>1107</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -53188,31 +53169,31 @@
       </c>
       <c r="F451" s="2"/>
       <c r="G451" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H451" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I451" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J451" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K451" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L451" t="s" s="2">
-        <v>103</v>
+        <v>367</v>
       </c>
       <c r="M451" t="s" s="2">
-        <v>1118</v>
+        <v>1115</v>
       </c>
       <c r="N451" t="s" s="2">
-        <v>911</v>
+        <v>915</v>
       </c>
       <c r="O451" t="s" s="2">
-        <v>544</v>
+        <v>916</v>
       </c>
       <c r="P451" s="2"/>
       <c r="Q451" t="s" s="2">
@@ -53238,11 +53219,13 @@
         <v>23</v>
       </c>
       <c r="Y451" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z451" s="2"/>
+        <v>372</v>
+      </c>
+      <c r="Z451" t="s" s="2">
+        <v>917</v>
+      </c>
       <c r="AA451" t="s" s="2">
-        <v>1119</v>
+        <v>918</v>
       </c>
       <c r="AB451" t="s" s="2">
         <v>23</v>
@@ -53260,10 +53243,10 @@
         <v>23</v>
       </c>
       <c r="AG451" t="s" s="2">
-        <v>909</v>
+        <v>913</v>
       </c>
       <c r="AH451" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI451" t="s" s="2">
         <v>83</v>
@@ -53280,10 +53263,10 @@
         <v>1107</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>913</v>
+        <v>1116</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>913</v>
+        <v>1116</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -53306,17 +53289,15 @@
         <v>23</v>
       </c>
       <c r="L452" t="s" s="2">
-        <v>367</v>
+        <v>141</v>
       </c>
       <c r="M452" t="s" s="2">
-        <v>1120</v>
+        <v>142</v>
       </c>
       <c r="N452" t="s" s="2">
-        <v>915</v>
-      </c>
-      <c r="O452" t="s" s="2">
-        <v>916</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O452" s="2"/>
       <c r="P452" s="2"/>
       <c r="Q452" t="s" s="2">
         <v>23</v>
@@ -53341,13 +53322,13 @@
         <v>23</v>
       </c>
       <c r="Y452" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z452" t="s" s="2">
-        <v>917</v>
+        <v>23</v>
       </c>
       <c r="AA452" t="s" s="2">
-        <v>918</v>
+        <v>23</v>
       </c>
       <c r="AB452" t="s" s="2">
         <v>23</v>
@@ -53365,7 +53346,7 @@
         <v>23</v>
       </c>
       <c r="AG452" t="s" s="2">
-        <v>913</v>
+        <v>144</v>
       </c>
       <c r="AH452" t="s" s="2">
         <v>76</v>
@@ -53377,7 +53358,7 @@
         <v>23</v>
       </c>
       <c r="AK452" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="453">
@@ -53385,21 +53366,21 @@
         <v>1107</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>1121</v>
+        <v>1117</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F453" s="2"/>
       <c r="G453" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H453" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I453" t="s" s="2">
         <v>23</v>
@@ -53411,15 +53392,17 @@
         <v>23</v>
       </c>
       <c r="L453" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M453" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N453" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O453" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O453" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P453" s="2"/>
       <c r="Q453" t="s" s="2">
         <v>23</v>
@@ -53456,31 +53439,31 @@
         <v>23</v>
       </c>
       <c r="AC453" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD453" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE453" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF453" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG453" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH453" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI453" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ453" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK453" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="454">
@@ -53488,21 +53471,21 @@
         <v>1107</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>1122</v>
+        <v>1118</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F454" s="2"/>
       <c r="G454" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H454" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I454" t="s" s="2">
         <v>23</v>
@@ -53511,21 +53494,23 @@
         <v>23</v>
       </c>
       <c r="K454" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L454" t="s" s="2">
-        <v>147</v>
+        <v>1119</v>
       </c>
       <c r="M454" t="s" s="2">
-        <v>148</v>
+        <v>1120</v>
       </c>
       <c r="N454" t="s" s="2">
-        <v>149</v>
+        <v>1121</v>
       </c>
       <c r="O454" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P454" s="2"/>
+        <v>1122</v>
+      </c>
+      <c r="P454" t="s" s="2">
+        <v>1123</v>
+      </c>
       <c r="Q454" t="s" s="2">
         <v>23</v>
       </c>
@@ -53561,19 +53546,19 @@
         <v>23</v>
       </c>
       <c r="AC454" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD454" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE454" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF454" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG454" t="s" s="2">
-        <v>151</v>
+        <v>1124</v>
       </c>
       <c r="AH454" t="s" s="2">
         <v>76</v>
@@ -53585,7 +53570,7 @@
         <v>23</v>
       </c>
       <c r="AK454" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="455">
@@ -53593,10 +53578,10 @@
         <v>1107</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -53607,10 +53592,10 @@
         <v>76</v>
       </c>
       <c r="H455" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I455" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J455" t="s" s="2">
         <v>23</v>
@@ -53619,19 +53604,19 @@
         <v>84</v>
       </c>
       <c r="L455" t="s" s="2">
-        <v>1124</v>
+        <v>141</v>
       </c>
       <c r="M455" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="N455" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="O455" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="P455" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="Q455" t="s" s="2">
         <v>23</v>
@@ -53680,13 +53665,13 @@
         <v>23</v>
       </c>
       <c r="AG455" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="AH455" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI455" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ455" t="s" s="2">
         <v>23</v>
@@ -53700,10 +53685,10 @@
         <v>1107</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1130</v>
+        <v>919</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1130</v>
+        <v>919</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -53711,7 +53696,7 @@
       </c>
       <c r="F456" s="2"/>
       <c r="G456" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H456" t="s" s="2">
         <v>83</v>
@@ -53720,26 +53705,24 @@
         <v>84</v>
       </c>
       <c r="J456" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K456" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L456" t="s" s="2">
-        <v>141</v>
+        <v>103</v>
       </c>
       <c r="M456" t="s" s="2">
         <v>1131</v>
       </c>
       <c r="N456" t="s" s="2">
-        <v>1132</v>
+        <v>921</v>
       </c>
       <c r="O456" t="s" s="2">
-        <v>1133</v>
-      </c>
-      <c r="P456" t="s" s="2">
-        <v>1134</v>
-      </c>
+        <v>922</v>
+      </c>
+      <c r="P456" s="2"/>
       <c r="Q456" t="s" s="2">
         <v>23</v>
       </c>
@@ -53748,7 +53731,7 @@
         <v>23</v>
       </c>
       <c r="T456" t="s" s="2">
-        <v>23</v>
+        <v>923</v>
       </c>
       <c r="U456" t="s" s="2">
         <v>23</v>
@@ -53763,13 +53746,13 @@
         <v>23</v>
       </c>
       <c r="Y456" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="Z456" t="s" s="2">
-        <v>23</v>
+        <v>924</v>
       </c>
       <c r="AA456" t="s" s="2">
-        <v>23</v>
+        <v>925</v>
       </c>
       <c r="AB456" t="s" s="2">
         <v>23</v>
@@ -53787,10 +53770,10 @@
         <v>23</v>
       </c>
       <c r="AG456" t="s" s="2">
-        <v>1135</v>
+        <v>919</v>
       </c>
       <c r="AH456" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI456" t="s" s="2">
         <v>83</v>
@@ -53807,10 +53790,10 @@
         <v>1107</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -53827,22 +53810,22 @@
         <v>84</v>
       </c>
       <c r="J457" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K457" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>103</v>
+        <v>367</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1136</v>
+        <v>936</v>
       </c>
       <c r="N457" t="s" s="2">
-        <v>921</v>
+        <v>929</v>
       </c>
       <c r="O457" t="s" s="2">
-        <v>922</v>
+        <v>930</v>
       </c>
       <c r="P457" s="2"/>
       <c r="Q457" t="s" s="2">
@@ -53853,7 +53836,7 @@
         <v>23</v>
       </c>
       <c r="T457" t="s" s="2">
-        <v>923</v>
+        <v>1132</v>
       </c>
       <c r="U457" t="s" s="2">
         <v>23</v>
@@ -53868,13 +53851,13 @@
         <v>23</v>
       </c>
       <c r="Y457" t="s" s="2">
-        <v>121</v>
+        <v>372</v>
       </c>
       <c r="Z457" t="s" s="2">
-        <v>924</v>
+        <v>931</v>
       </c>
       <c r="AA457" t="s" s="2">
-        <v>925</v>
+        <v>932</v>
       </c>
       <c r="AB457" t="s" s="2">
         <v>23</v>
@@ -53892,13 +53875,13 @@
         <v>23</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>919</v>
+        <v>926</v>
       </c>
       <c r="AH457" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI457" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ457" t="s" s="2">
         <v>23</v>
@@ -53912,10 +53895,10 @@
         <v>1107</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -53923,32 +53906,30 @@
       </c>
       <c r="F458" s="2"/>
       <c r="G458" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H458" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I458" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J458" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K458" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="J458" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K458" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="L458" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>936</v>
+        <v>1133</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>929</v>
-      </c>
-      <c r="O458" t="s" s="2">
-        <v>930</v>
-      </c>
+        <v>944</v>
+      </c>
+      <c r="O458" s="2"/>
       <c r="P458" s="2"/>
       <c r="Q458" t="s" s="2">
         <v>23</v>
@@ -53958,7 +53939,7 @@
         <v>23</v>
       </c>
       <c r="T458" t="s" s="2">
-        <v>1137</v>
+        <v>23</v>
       </c>
       <c r="U458" t="s" s="2">
         <v>23</v>
@@ -53973,13 +53954,13 @@
         <v>23</v>
       </c>
       <c r="Y458" t="s" s="2">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="Z458" t="s" s="2">
-        <v>931</v>
+        <v>945</v>
       </c>
       <c r="AA458" t="s" s="2">
-        <v>932</v>
+        <v>946</v>
       </c>
       <c r="AB458" t="s" s="2">
         <v>23</v>
@@ -53997,13 +53978,13 @@
         <v>23</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>926</v>
+        <v>942</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI458" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ458" t="s" s="2">
         <v>23</v>
@@ -54017,10 +53998,10 @@
         <v>1107</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -54037,21 +54018,23 @@
         <v>23</v>
       </c>
       <c r="J459" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K459" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L459" t="s" s="2">
-        <v>103</v>
+        <v>385</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1138</v>
+        <v>1134</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>944</v>
-      </c>
-      <c r="O459" s="2"/>
+        <v>949</v>
+      </c>
+      <c r="O459" t="s" s="2">
+        <v>950</v>
+      </c>
       <c r="P459" s="2"/>
       <c r="Q459" t="s" s="2">
         <v>23</v>
@@ -54076,13 +54059,13 @@
         <v>23</v>
       </c>
       <c r="Y459" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z459" t="s" s="2">
-        <v>945</v>
+        <v>23</v>
       </c>
       <c r="AA459" t="s" s="2">
-        <v>946</v>
+        <v>23</v>
       </c>
       <c r="AB459" t="s" s="2">
         <v>23</v>
@@ -54100,7 +54083,7 @@
         <v>23</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>942</v>
+        <v>947</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>76</v>
@@ -54120,10 +54103,10 @@
         <v>1107</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -54131,16 +54114,16 @@
       </c>
       <c r="F460" s="2"/>
       <c r="G460" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H460" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I460" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J460" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K460" t="s" s="2">
         <v>84</v>
@@ -54149,14 +54132,12 @@
         <v>385</v>
       </c>
       <c r="M460" t="s" s="2">
-        <v>1139</v>
+        <v>1135</v>
       </c>
       <c r="N460" t="s" s="2">
-        <v>949</v>
-      </c>
-      <c r="O460" t="s" s="2">
-        <v>950</v>
-      </c>
+        <v>954</v>
+      </c>
+      <c r="O460" s="2"/>
       <c r="P460" s="2"/>
       <c r="Q460" t="s" s="2">
         <v>23</v>
@@ -54193,19 +54174,17 @@
         <v>23</v>
       </c>
       <c r="AC460" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD460" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AD460" s="2"/>
       <c r="AE460" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF460" t="s" s="2">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="AG460" t="s" s="2">
-        <v>947</v>
+        <v>951</v>
       </c>
       <c r="AH460" t="s" s="2">
         <v>76</v>
@@ -54225,21 +54204,23 @@
         <v>1107</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>951</v>
+        <v>1136</v>
       </c>
       <c r="C461" t="s" s="2">
         <v>951</v>
       </c>
-      <c r="D461" s="2"/>
+      <c r="D461" t="s" s="2">
+        <v>1137</v>
+      </c>
       <c r="E461" t="s" s="2">
         <v>23</v>
       </c>
       <c r="F461" s="2"/>
       <c r="G461" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H461" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I461" t="s" s="2">
         <v>23</v>
@@ -54251,10 +54232,10 @@
         <v>84</v>
       </c>
       <c r="L461" t="s" s="2">
-        <v>385</v>
+        <v>1138</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="N461" t="s" s="2">
         <v>954</v>
@@ -54296,14 +54277,16 @@
         <v>23</v>
       </c>
       <c r="AC461" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AD461" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="AD461" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AE461" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF461" t="s" s="2">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="AG461" t="s" s="2">
         <v>951</v>
@@ -54326,13 +54309,13 @@
         <v>1107</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1141</v>
+        <v>1140</v>
       </c>
       <c r="C462" t="s" s="2">
         <v>951</v>
       </c>
       <c r="D462" t="s" s="2">
-        <v>1142</v>
+        <v>1141</v>
       </c>
       <c r="E462" t="s" s="2">
         <v>23</v>
@@ -54342,10 +54325,10 @@
         <v>76</v>
       </c>
       <c r="H462" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I462" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J462" t="s" s="2">
         <v>23</v>
@@ -54354,10 +54337,10 @@
         <v>84</v>
       </c>
       <c r="L462" t="s" s="2">
-        <v>1143</v>
+        <v>385</v>
       </c>
       <c r="M462" t="s" s="2">
-        <v>1144</v>
+        <v>1142</v>
       </c>
       <c r="N462" t="s" s="2">
         <v>954</v>
@@ -54431,20 +54414,18 @@
         <v>1107</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1145</v>
+        <v>955</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>951</v>
-      </c>
-      <c r="D463" t="s" s="2">
-        <v>1146</v>
-      </c>
+        <v>955</v>
+      </c>
+      <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
         <v>23</v>
       </c>
       <c r="F463" s="2"/>
       <c r="G463" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H463" t="s" s="2">
         <v>83</v>
@@ -54459,15 +54440,17 @@
         <v>84</v>
       </c>
       <c r="L463" t="s" s="2">
-        <v>385</v>
+        <v>695</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1147</v>
+        <v>1143</v>
       </c>
       <c r="N463" t="s" s="2">
-        <v>954</v>
-      </c>
-      <c r="O463" s="2"/>
+        <v>957</v>
+      </c>
+      <c r="O463" t="s" s="2">
+        <v>958</v>
+      </c>
       <c r="P463" s="2"/>
       <c r="Q463" t="s" s="2">
         <v>23</v>
@@ -54516,10 +54499,10 @@
         <v>23</v>
       </c>
       <c r="AG463" t="s" s="2">
-        <v>951</v>
+        <v>955</v>
       </c>
       <c r="AH463" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI463" t="s" s="2">
         <v>83</v>
@@ -54536,10 +54519,10 @@
         <v>1107</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -54562,16 +54545,16 @@
         <v>84</v>
       </c>
       <c r="L464" t="s" s="2">
-        <v>695</v>
+        <v>700</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1148</v>
+        <v>1144</v>
       </c>
       <c r="N464" t="s" s="2">
-        <v>957</v>
+        <v>961</v>
       </c>
       <c r="O464" t="s" s="2">
-        <v>958</v>
+        <v>962</v>
       </c>
       <c r="P464" s="2"/>
       <c r="Q464" t="s" s="2">
@@ -54621,7 +54604,7 @@
         <v>23</v>
       </c>
       <c r="AG464" t="s" s="2">
-        <v>955</v>
+        <v>959</v>
       </c>
       <c r="AH464" t="s" s="2">
         <v>83</v>
@@ -54641,10 +54624,10 @@
         <v>1107</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -54652,31 +54635,31 @@
       </c>
       <c r="F465" s="2"/>
       <c r="G465" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H465" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I465" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J465" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K465" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L465" t="s" s="2">
-        <v>700</v>
+        <v>574</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1149</v>
+        <v>1145</v>
       </c>
       <c r="N465" t="s" s="2">
-        <v>961</v>
+        <v>965</v>
       </c>
       <c r="O465" t="s" s="2">
-        <v>962</v>
+        <v>966</v>
       </c>
       <c r="P465" s="2"/>
       <c r="Q465" t="s" s="2">
@@ -54726,10 +54709,10 @@
         <v>23</v>
       </c>
       <c r="AG465" t="s" s="2">
-        <v>959</v>
+        <v>963</v>
       </c>
       <c r="AH465" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI465" t="s" s="2">
         <v>83</v>
@@ -54746,10 +54729,10 @@
         <v>1107</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -54772,17 +54755,15 @@
         <v>23</v>
       </c>
       <c r="L466" t="s" s="2">
-        <v>574</v>
+        <v>709</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1150</v>
+        <v>1146</v>
       </c>
       <c r="N466" t="s" s="2">
-        <v>965</v>
-      </c>
-      <c r="O466" t="s" s="2">
-        <v>966</v>
-      </c>
+        <v>969</v>
+      </c>
+      <c r="O466" s="2"/>
       <c r="P466" s="2"/>
       <c r="Q466" t="s" s="2">
         <v>23</v>
@@ -54831,13 +54812,13 @@
         <v>23</v>
       </c>
       <c r="AG466" t="s" s="2">
-        <v>963</v>
+        <v>967</v>
       </c>
       <c r="AH466" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI466" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ466" t="s" s="2">
         <v>23</v>
@@ -54851,10 +54832,10 @@
         <v>1107</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="D467" s="2"/>
       <c r="E467" t="s" s="2">
@@ -54862,28 +54843,28 @@
       </c>
       <c r="F467" s="2"/>
       <c r="G467" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H467" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I467" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J467" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K467" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L467" t="s" s="2">
-        <v>709</v>
+        <v>578</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1151</v>
+        <v>1147</v>
       </c>
       <c r="N467" t="s" s="2">
-        <v>969</v>
+        <v>972</v>
       </c>
       <c r="O467" s="2"/>
       <c r="P467" s="2"/>
@@ -54934,13 +54915,13 @@
         <v>23</v>
       </c>
       <c r="AG467" t="s" s="2">
-        <v>967</v>
+        <v>970</v>
       </c>
       <c r="AH467" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI467" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ467" t="s" s="2">
         <v>23</v>
@@ -54954,10 +54935,10 @@
         <v>1107</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -54980,13 +54961,13 @@
         <v>84</v>
       </c>
       <c r="L468" t="s" s="2">
-        <v>578</v>
+        <v>725</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1152</v>
+        <v>1148</v>
       </c>
       <c r="N468" t="s" s="2">
-        <v>972</v>
+        <v>975</v>
       </c>
       <c r="O468" s="2"/>
       <c r="P468" s="2"/>
@@ -55037,7 +55018,7 @@
         <v>23</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>970</v>
+        <v>973</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>76</v>
@@ -55057,10 +55038,10 @@
         <v>1107</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -55068,28 +55049,28 @@
       </c>
       <c r="F469" s="2"/>
       <c r="G469" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H469" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I469" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J469" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K469" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L469" t="s" s="2">
-        <v>725</v>
+        <v>977</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1153</v>
+        <v>1149</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>975</v>
+        <v>979</v>
       </c>
       <c r="O469" s="2"/>
       <c r="P469" s="2"/>
@@ -55140,7 +55121,7 @@
         <v>23</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>973</v>
+        <v>976</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>76</v>
@@ -55160,10 +55141,10 @@
         <v>1107</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -55183,18 +55164,20 @@
         <v>23</v>
       </c>
       <c r="K470" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>977</v>
+        <v>367</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1154</v>
+        <v>1150</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>979</v>
-      </c>
-      <c r="O470" s="2"/>
+        <v>981</v>
+      </c>
+      <c r="O470" t="s" s="2">
+        <v>982</v>
+      </c>
       <c r="P470" s="2"/>
       <c r="Q470" t="s" s="2">
         <v>23</v>
@@ -55219,13 +55202,13 @@
         <v>23</v>
       </c>
       <c r="Y470" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z470" t="s" s="2">
-        <v>23</v>
+        <v>983</v>
       </c>
       <c r="AA470" t="s" s="2">
-        <v>23</v>
+        <v>984</v>
       </c>
       <c r="AB470" t="s" s="2">
         <v>23</v>
@@ -55243,7 +55226,7 @@
         <v>23</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>976</v>
+        <v>980</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -55263,10 +55246,10 @@
         <v>1107</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55286,20 +55269,18 @@
         <v>23</v>
       </c>
       <c r="K471" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>367</v>
+        <v>788</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1155</v>
+        <v>1151</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>981</v>
-      </c>
-      <c r="O471" t="s" s="2">
-        <v>982</v>
-      </c>
+        <v>987</v>
+      </c>
+      <c r="O471" s="2"/>
       <c r="P471" s="2"/>
       <c r="Q471" t="s" s="2">
         <v>23</v>
@@ -55324,13 +55305,13 @@
         <v>23</v>
       </c>
       <c r="Y471" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z471" t="s" s="2">
-        <v>983</v>
+        <v>23</v>
       </c>
       <c r="AA471" t="s" s="2">
-        <v>984</v>
+        <v>23</v>
       </c>
       <c r="AB471" t="s" s="2">
         <v>23</v>
@@ -55348,7 +55329,7 @@
         <v>23</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>980</v>
+        <v>985</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>76</v>
@@ -55368,10 +55349,10 @@
         <v>1107</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -55394,15 +55375,17 @@
         <v>23</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>788</v>
+        <v>367</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1156</v>
+        <v>1152</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>987</v>
-      </c>
-      <c r="O472" s="2"/>
+        <v>990</v>
+      </c>
+      <c r="O472" t="s" s="2">
+        <v>991</v>
+      </c>
       <c r="P472" s="2"/>
       <c r="Q472" t="s" s="2">
         <v>23</v>
@@ -55427,13 +55410,13 @@
         <v>23</v>
       </c>
       <c r="Y472" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z472" t="s" s="2">
-        <v>23</v>
+        <v>992</v>
       </c>
       <c r="AA472" t="s" s="2">
-        <v>23</v>
+        <v>993</v>
       </c>
       <c r="AB472" t="s" s="2">
         <v>23</v>
@@ -55451,13 +55434,13 @@
         <v>23</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>985</v>
+        <v>988</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI472" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ472" t="s" s="2">
         <v>23</v>
@@ -55471,10 +55454,10 @@
         <v>1107</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
@@ -55497,16 +55480,16 @@
         <v>23</v>
       </c>
       <c r="L473" t="s" s="2">
-        <v>367</v>
+        <v>995</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1157</v>
+        <v>996</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>990</v>
+        <v>997</v>
       </c>
       <c r="O473" t="s" s="2">
-        <v>991</v>
+        <v>998</v>
       </c>
       <c r="P473" s="2"/>
       <c r="Q473" t="s" s="2">
@@ -55532,13 +55515,13 @@
         <v>23</v>
       </c>
       <c r="Y473" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z473" t="s" s="2">
-        <v>992</v>
+        <v>23</v>
       </c>
       <c r="AA473" t="s" s="2">
-        <v>993</v>
+        <v>23</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>23</v>
@@ -55556,7 +55539,7 @@
         <v>23</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>988</v>
+        <v>994</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55576,10 +55559,10 @@
         <v>1107</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="D474" s="2"/>
       <c r="E474" t="s" s="2">
@@ -55599,20 +55582,18 @@
         <v>23</v>
       </c>
       <c r="K474" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>995</v>
+        <v>1000</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>996</v>
+        <v>1153</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>997</v>
-      </c>
-      <c r="O474" t="s" s="2">
-        <v>998</v>
-      </c>
+        <v>1002</v>
+      </c>
+      <c r="O474" s="2"/>
       <c r="P474" s="2"/>
       <c r="Q474" t="s" s="2">
         <v>23</v>
@@ -55661,7 +55642,7 @@
         <v>23</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>994</v>
+        <v>999</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -55681,10 +55662,10 @@
         <v>1107</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -55707,13 +55688,13 @@
         <v>84</v>
       </c>
       <c r="L475" t="s" s="2">
-        <v>1000</v>
+        <v>97</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1158</v>
+        <v>1154</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1002</v>
+        <v>1005</v>
       </c>
       <c r="O475" s="2"/>
       <c r="P475" s="2"/>
@@ -55764,7 +55745,7 @@
         <v>23</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>999</v>
+        <v>1003</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -55784,10 +55765,10 @@
         <v>1107</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -55810,13 +55791,13 @@
         <v>84</v>
       </c>
       <c r="L476" t="s" s="2">
-        <v>97</v>
+        <v>1155</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1159</v>
+        <v>1156</v>
       </c>
       <c r="N476" t="s" s="2">
-        <v>1005</v>
+        <v>1008</v>
       </c>
       <c r="O476" s="2"/>
       <c r="P476" s="2"/>
@@ -55867,7 +55848,7 @@
         <v>23</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1003</v>
+        <v>1006</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>76</v>
@@ -55887,10 +55868,10 @@
         <v>1107</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -55913,16 +55894,18 @@
         <v>84</v>
       </c>
       <c r="L477" t="s" s="2">
-        <v>1160</v>
+        <v>112</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1161</v>
+        <v>1157</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1008</v>
+        <v>1011</v>
       </c>
       <c r="O477" s="2"/>
-      <c r="P477" s="2"/>
+      <c r="P477" t="s" s="2">
+        <v>1012</v>
+      </c>
       <c r="Q477" t="s" s="2">
         <v>23</v>
       </c>
@@ -55970,13 +55953,13 @@
         <v>23</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1006</v>
+        <v>1009</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI477" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ477" t="s" s="2">
         <v>23</v>
@@ -55990,10 +55973,10 @@
         <v>1107</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56004,30 +55987,30 @@
         <v>76</v>
       </c>
       <c r="H478" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I478" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J478" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K478" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>112</v>
+        <v>367</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1162</v>
+        <v>1158</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1011</v>
-      </c>
-      <c r="O478" s="2"/>
-      <c r="P478" t="s" s="2">
-        <v>1012</v>
-      </c>
+        <v>1015</v>
+      </c>
+      <c r="O478" t="s" s="2">
+        <v>1016</v>
+      </c>
+      <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
         <v>23</v>
       </c>
@@ -56051,13 +56034,13 @@
         <v>23</v>
       </c>
       <c r="Y478" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z478" t="s" s="2">
-        <v>23</v>
+        <v>1017</v>
       </c>
       <c r="AA478" t="s" s="2">
-        <v>23</v>
+        <v>1018</v>
       </c>
       <c r="AB478" t="s" s="2">
         <v>23</v>
@@ -56075,7 +56058,7 @@
         <v>23</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1009</v>
+        <v>1013</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>76</v>
@@ -56095,10 +56078,10 @@
         <v>1107</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56109,10 +56092,10 @@
         <v>76</v>
       </c>
       <c r="H479" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I479" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J479" t="s" s="2">
         <v>23</v>
@@ -56121,17 +56104,15 @@
         <v>23</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>367</v>
+        <v>1020</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1163</v>
+        <v>1156</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>1015</v>
-      </c>
-      <c r="O479" t="s" s="2">
-        <v>1016</v>
-      </c>
+        <v>1022</v>
+      </c>
+      <c r="O479" s="2"/>
       <c r="P479" s="2"/>
       <c r="Q479" t="s" s="2">
         <v>23</v>
@@ -56156,13 +56137,13 @@
         <v>23</v>
       </c>
       <c r="Y479" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z479" t="s" s="2">
-        <v>1017</v>
+        <v>23</v>
       </c>
       <c r="AA479" t="s" s="2">
-        <v>1018</v>
+        <v>23</v>
       </c>
       <c r="AB479" t="s" s="2">
         <v>23</v>
@@ -56180,13 +56161,13 @@
         <v>23</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1013</v>
+        <v>1019</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI479" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ479" t="s" s="2">
         <v>23</v>
@@ -56200,10 +56181,10 @@
         <v>1107</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56214,10 +56195,10 @@
         <v>76</v>
       </c>
       <c r="H480" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I480" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J480" t="s" s="2">
         <v>23</v>
@@ -56226,13 +56207,13 @@
         <v>23</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>1020</v>
+        <v>598</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1161</v>
+        <v>1159</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1022</v>
+        <v>1025</v>
       </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
@@ -56283,7 +56264,7 @@
         <v>23</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1019</v>
+        <v>1023</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
@@ -56303,10 +56284,10 @@
         <v>1107</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56314,7 +56295,7 @@
       </c>
       <c r="F481" s="2"/>
       <c r="G481" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H481" t="s" s="2">
         <v>77</v>
@@ -56329,15 +56310,17 @@
         <v>23</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>598</v>
+        <v>1027</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1164</v>
+        <v>1160</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>1025</v>
-      </c>
-      <c r="O481" s="2"/>
+        <v>766</v>
+      </c>
+      <c r="O481" t="s" s="2">
+        <v>1029</v>
+      </c>
       <c r="P481" s="2"/>
       <c r="Q481" t="s" s="2">
         <v>23</v>
@@ -56386,7 +56369,7 @@
         <v>23</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1023</v>
+        <v>1026</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
@@ -56406,10 +56389,10 @@
         <v>1107</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56417,13 +56400,13 @@
       </c>
       <c r="F482" s="2"/>
       <c r="G482" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H482" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I482" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J482" t="s" s="2">
         <v>23</v>
@@ -56432,17 +56415,15 @@
         <v>23</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>1027</v>
+        <v>136</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1165</v>
+        <v>1161</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>766</v>
-      </c>
-      <c r="O482" t="s" s="2">
-        <v>1029</v>
-      </c>
+        <v>1032</v>
+      </c>
+      <c r="O482" s="2"/>
       <c r="P482" s="2"/>
       <c r="Q482" t="s" s="2">
         <v>23</v>
@@ -56491,13 +56472,13 @@
         <v>23</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>1026</v>
+        <v>1030</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI482" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ482" t="s" s="2">
         <v>23</v>
@@ -56511,10 +56492,10 @@
         <v>1107</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1030</v>
+        <v>1033</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56525,7 +56506,7 @@
         <v>76</v>
       </c>
       <c r="H483" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I483" t="s" s="2">
         <v>23</v>
@@ -56537,13 +56518,13 @@
         <v>23</v>
       </c>
       <c r="L483" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1166</v>
+        <v>142</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>1032</v>
+        <v>143</v>
       </c>
       <c r="O483" s="2"/>
       <c r="P483" s="2"/>
@@ -56594,7 +56575,7 @@
         <v>23</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>1030</v>
+        <v>144</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
@@ -56606,7 +56587,7 @@
         <v>23</v>
       </c>
       <c r="AK483" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="484">
@@ -56614,21 +56595,21 @@
         <v>1107</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1033</v>
+        <v>1034</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F484" s="2"/>
       <c r="G484" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H484" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I484" t="s" s="2">
         <v>23</v>
@@ -56640,15 +56621,17 @@
         <v>23</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O484" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O484" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P484" s="2"/>
       <c r="Q484" t="s" s="2">
         <v>23</v>
@@ -56697,19 +56680,19 @@
         <v>23</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI484" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ484" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK484" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="485">
@@ -56717,14 +56700,14 @@
         <v>1107</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1034</v>
+        <v>1035</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F485" s="2"/>
       <c r="G485" t="s" s="2">
@@ -56737,24 +56720,26 @@
         <v>23</v>
       </c>
       <c r="J485" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K485" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L485" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O485" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P485" s="2"/>
+      <c r="P485" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q485" t="s" s="2">
         <v>23</v>
       </c>
@@ -56802,7 +56787,7 @@
         <v>23</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>76</v>
@@ -56822,46 +56807,44 @@
         <v>1107</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1035</v>
+        <v>1036</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F486" s="2"/>
       <c r="G486" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H486" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I486" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J486" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K486" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>155</v>
+        <v>1037</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>156</v>
+        <v>1038</v>
       </c>
       <c r="O486" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P486" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1039</v>
+      </c>
+      <c r="P486" s="2"/>
       <c r="Q486" t="s" s="2">
         <v>23</v>
       </c>
@@ -56909,19 +56892,19 @@
         <v>23</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>158</v>
+        <v>1036</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI486" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ486" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK486" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="487">
@@ -56929,10 +56912,10 @@
         <v>1107</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1036</v>
+        <v>1040</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56955,17 +56938,15 @@
         <v>23</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1037</v>
+        <v>142</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1038</v>
-      </c>
-      <c r="O487" t="s" s="2">
-        <v>1039</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O487" s="2"/>
       <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
         <v>23</v>
@@ -57014,7 +56995,7 @@
         <v>23</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1036</v>
+        <v>144</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -57026,7 +57007,7 @@
         <v>23</v>
       </c>
       <c r="AK487" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="488">
@@ -57034,21 +57015,21 @@
         <v>1107</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1040</v>
+        <v>1041</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F488" s="2"/>
       <c r="G488" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I488" t="s" s="2">
         <v>23</v>
@@ -57060,15 +57041,17 @@
         <v>23</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O488" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O488" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
         <v>23</v>
@@ -57117,19 +57100,19 @@
         <v>23</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK488" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="489">
@@ -57137,14 +57120,14 @@
         <v>1107</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1041</v>
+        <v>1042</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F489" s="2"/>
       <c r="G489" t="s" s="2">
@@ -57157,24 +57140,26 @@
         <v>23</v>
       </c>
       <c r="J489" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K489" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L489" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O489" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P489" s="2"/>
+      <c r="P489" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q489" t="s" s="2">
         <v>23</v>
       </c>
@@ -57222,7 +57207,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57242,46 +57227,42 @@
         <v>1107</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1042</v>
+        <v>1043</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F490" s="2"/>
       <c r="G490" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H490" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I490" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J490" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K490" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>147</v>
+        <v>497</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>155</v>
+        <v>1162</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O490" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P490" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1045</v>
+      </c>
+      <c r="O490" s="2"/>
+      <c r="P490" s="2"/>
       <c r="Q490" t="s" s="2">
         <v>23</v>
       </c>
@@ -57329,19 +57310,19 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>158</v>
+        <v>1043</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI490" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ490" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK490" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="491">
@@ -57349,10 +57330,10 @@
         <v>1107</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57375,13 +57356,13 @@
         <v>23</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>497</v>
+        <v>1047</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1167</v>
+        <v>1048</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1045</v>
+        <v>1049</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -57432,7 +57413,7 @@
         <v>23</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1043</v>
+        <v>1046</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
@@ -57452,10 +57433,10 @@
         <v>1107</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57481,10 +57462,10 @@
         <v>1047</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1048</v>
+        <v>1163</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1049</v>
+        <v>1052</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57535,7 +57516,7 @@
         <v>23</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1046</v>
+        <v>1050</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57555,10 +57536,10 @@
         <v>1107</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57581,16 +57562,20 @@
         <v>23</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>1047</v>
+        <v>1054</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1168</v>
+        <v>1164</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1052</v>
-      </c>
-      <c r="O493" s="2"/>
-      <c r="P493" s="2"/>
+        <v>1165</v>
+      </c>
+      <c r="O493" t="s" s="2">
+        <v>1057</v>
+      </c>
+      <c r="P493" t="s" s="2">
+        <v>1058</v>
+      </c>
       <c r="Q493" t="s" s="2">
         <v>23</v>
       </c>
@@ -57638,7 +57623,7 @@
         <v>23</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1050</v>
+        <v>1053</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -57658,10 +57643,10 @@
         <v>1107</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57684,20 +57669,18 @@
         <v>23</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1054</v>
+        <v>130</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1169</v>
+        <v>1060</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1170</v>
+        <v>1061</v>
       </c>
       <c r="O494" t="s" s="2">
-        <v>1057</v>
-      </c>
-      <c r="P494" t="s" s="2">
-        <v>1058</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="P494" s="2"/>
       <c r="Q494" t="s" s="2">
         <v>23</v>
       </c>
@@ -57745,7 +57728,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1053</v>
+        <v>1059</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -57765,10 +57748,10 @@
         <v>1107</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57791,17 +57774,15 @@
         <v>23</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>130</v>
+        <v>497</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1060</v>
+        <v>1166</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1061</v>
-      </c>
-      <c r="O495" t="s" s="2">
-        <v>1062</v>
-      </c>
+        <v>1065</v>
+      </c>
+      <c r="O495" s="2"/>
       <c r="P495" s="2"/>
       <c r="Q495" t="s" s="2">
         <v>23</v>
@@ -57850,7 +57831,7 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1059</v>
+        <v>1063</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
@@ -57870,10 +57851,10 @@
         <v>1107</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -57896,15 +57877,17 @@
         <v>23</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>497</v>
+        <v>1047</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1171</v>
+        <v>1067</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>1065</v>
-      </c>
-      <c r="O496" s="2"/>
+        <v>1068</v>
+      </c>
+      <c r="O496" t="s" s="2">
+        <v>1069</v>
+      </c>
       <c r="P496" s="2"/>
       <c r="Q496" t="s" s="2">
         <v>23</v>
@@ -57953,7 +57936,7 @@
         <v>23</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1063</v>
+        <v>1066</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -57973,10 +57956,10 @@
         <v>1107</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -57999,17 +57982,15 @@
         <v>23</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>1047</v>
+        <v>836</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1067</v>
+        <v>1167</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1068</v>
-      </c>
-      <c r="O497" t="s" s="2">
-        <v>1069</v>
-      </c>
+        <v>1081</v>
+      </c>
+      <c r="O497" s="2"/>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
         <v>23</v>
@@ -58058,7 +58039,7 @@
         <v>23</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1066</v>
+        <v>1079</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
@@ -58078,10 +58059,10 @@
         <v>1107</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58092,7 +58073,7 @@
         <v>76</v>
       </c>
       <c r="H498" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I498" t="s" s="2">
         <v>23</v>
@@ -58104,13 +58085,13 @@
         <v>23</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>836</v>
+        <v>136</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1172</v>
+        <v>1168</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>1081</v>
+        <v>1084</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -58161,7 +58142,7 @@
         <v>23</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1079</v>
+        <v>1082</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -58181,10 +58162,10 @@
         <v>1107</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1082</v>
+        <v>1085</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -58198,7 +58179,7 @@
         <v>83</v>
       </c>
       <c r="I499" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J499" t="s" s="2">
         <v>23</v>
@@ -58207,13 +58188,13 @@
         <v>23</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>1173</v>
+        <v>142</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>1084</v>
+        <v>143</v>
       </c>
       <c r="O499" s="2"/>
       <c r="P499" s="2"/>
@@ -58264,7 +58245,7 @@
         <v>23</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>1082</v>
+        <v>144</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
@@ -58276,7 +58257,7 @@
         <v>23</v>
       </c>
       <c r="AK499" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="500">
@@ -58284,21 +58265,21 @@
         <v>1107</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1085</v>
+        <v>1086</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H500" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I500" t="s" s="2">
         <v>23</v>
@@ -58310,15 +58291,17 @@
         <v>23</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O500" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O500" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
         <v>23</v>
@@ -58367,19 +58350,19 @@
         <v>23</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI500" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ500" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK500" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="501">
@@ -58387,14 +58370,14 @@
         <v>1107</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1086</v>
+        <v>1087</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
@@ -58407,24 +58390,26 @@
         <v>23</v>
       </c>
       <c r="J501" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L501" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O501" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P501" s="2"/>
+      <c r="P501" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q501" t="s" s="2">
         <v>23</v>
       </c>
@@ -58472,7 +58457,7 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>76</v>
@@ -58492,46 +58477,44 @@
         <v>1107</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1087</v>
+        <v>1088</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H502" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I502" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J502" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K502" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>147</v>
+        <v>1089</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>155</v>
+        <v>1090</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>156</v>
+        <v>1091</v>
       </c>
       <c r="O502" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P502" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1092</v>
+      </c>
+      <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
         <v>23</v>
       </c>
@@ -58555,13 +58538,13 @@
         <v>23</v>
       </c>
       <c r="Y502" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z502" t="s" s="2">
-        <v>23</v>
+        <v>1093</v>
       </c>
       <c r="AA502" t="s" s="2">
-        <v>23</v>
+        <v>781</v>
       </c>
       <c r="AB502" t="s" s="2">
         <v>23</v>
@@ -58579,19 +58562,19 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>158</v>
+        <v>1088</v>
       </c>
       <c r="AH502" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI502" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ502" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK502" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="503">
@@ -58599,10 +58582,10 @@
         <v>1107</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58610,7 +58593,7 @@
       </c>
       <c r="F503" s="2"/>
       <c r="G503" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H503" t="s" s="2">
         <v>83</v>
@@ -58625,17 +58608,15 @@
         <v>23</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>1089</v>
+        <v>367</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1090</v>
+        <v>1095</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1091</v>
-      </c>
-      <c r="O503" t="s" s="2">
-        <v>1092</v>
-      </c>
+        <v>1096</v>
+      </c>
+      <c r="O503" s="2"/>
       <c r="P503" s="2"/>
       <c r="Q503" t="s" s="2">
         <v>23</v>
@@ -58663,10 +58644,10 @@
         <v>372</v>
       </c>
       <c r="Z503" t="s" s="2">
-        <v>1093</v>
+        <v>785</v>
       </c>
       <c r="AA503" t="s" s="2">
-        <v>781</v>
+        <v>786</v>
       </c>
       <c r="AB503" t="s" s="2">
         <v>23</v>
@@ -58684,10 +58665,10 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1088</v>
+        <v>1094</v>
       </c>
       <c r="AH503" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI503" t="s" s="2">
         <v>83</v>
@@ -58704,10 +58685,10 @@
         <v>1107</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58721,7 +58702,7 @@
         <v>83</v>
       </c>
       <c r="I504" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J504" t="s" s="2">
         <v>23</v>
@@ -58730,13 +58711,13 @@
         <v>23</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>367</v>
+        <v>733</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1095</v>
+        <v>1169</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" s="2"/>
@@ -58763,13 +58744,13 @@
         <v>23</v>
       </c>
       <c r="Y504" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z504" t="s" s="2">
-        <v>785</v>
+        <v>23</v>
       </c>
       <c r="AA504" t="s" s="2">
-        <v>786</v>
+        <v>23</v>
       </c>
       <c r="AB504" t="s" s="2">
         <v>23</v>
@@ -58787,7 +58768,7 @@
         <v>23</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -58807,24 +58788,24 @@
         <v>1107</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
-        <v>23</v>
+        <v>792</v>
       </c>
       <c r="F505" s="2"/>
       <c r="G505" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H505" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I505" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J505" t="s" s="2">
         <v>23</v>
@@ -58833,15 +58814,17 @@
         <v>23</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>733</v>
+        <v>793</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1174</v>
+        <v>1170</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1099</v>
-      </c>
-      <c r="O505" s="2"/>
+        <v>1102</v>
+      </c>
+      <c r="O505" t="s" s="2">
+        <v>796</v>
+      </c>
       <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
         <v>23</v>
@@ -58890,13 +58873,13 @@
         <v>23</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI505" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ505" t="s" s="2">
         <v>23</v>
@@ -58910,14 +58893,14 @@
         <v>1107</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>792</v>
+        <v>23</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
@@ -58936,16 +58919,16 @@
         <v>23</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>793</v>
+        <v>798</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1175</v>
+        <v>1171</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1102</v>
+        <v>1105</v>
       </c>
       <c r="O506" t="s" s="2">
-        <v>796</v>
+        <v>1106</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -58995,7 +58978,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1100</v>
+        <v>1103</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59012,13 +58995,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1107</v>
+        <v>1172</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1103</v>
+        <v>1177</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1103</v>
+        <v>1177</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59029,7 +59012,7 @@
         <v>76</v>
       </c>
       <c r="H507" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I507" t="s" s="2">
         <v>23</v>
@@ -59041,17 +59024,15 @@
         <v>23</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>798</v>
+        <v>78</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1176</v>
+        <v>1179</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1105</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1106</v>
-      </c>
+        <v>1180</v>
+      </c>
+      <c r="O507" s="2"/>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
         <v>23</v>
@@ -59100,7 +59081,7 @@
         <v>23</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1103</v>
+        <v>1177</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59112,18 +59093,18 @@
         <v>23</v>
       </c>
       <c r="AK507" t="s" s="2">
-        <v>95</v>
+        <v>811</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1182</v>
+        <v>1181</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59134,7 +59115,7 @@
         <v>76</v>
       </c>
       <c r="H508" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I508" t="s" s="2">
         <v>23</v>
@@ -59143,18 +59124,20 @@
         <v>23</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>78</v>
+        <v>85</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1184</v>
+        <v>86</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>1185</v>
-      </c>
-      <c r="O508" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="O508" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
         <v>23</v>
@@ -59203,30 +59186,30 @@
         <v>23</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1182</v>
+        <v>89</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI508" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ508" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>811</v>
+        <v>23</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1186</v>
+        <v>1182</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59249,17 +59232,15 @@
         <v>84</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>85</v>
+        <v>91</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>86</v>
+        <v>92</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O509" t="s" s="2">
-        <v>88</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="O509" s="2"/>
       <c r="P509" s="2"/>
       <c r="Q509" t="s" s="2">
         <v>23</v>
@@ -59308,7 +59289,7 @@
         <v>23</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>89</v>
+        <v>94</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>76</v>
@@ -59320,18 +59301,18 @@
         <v>23</v>
       </c>
       <c r="AK509" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1187</v>
+        <v>1183</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59348,21 +59329,23 @@
         <v>23</v>
       </c>
       <c r="J510" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K510" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>91</v>
+        <v>97</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>92</v>
+        <v>98</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O510" s="2"/>
+        <v>99</v>
+      </c>
+      <c r="O510" t="s" s="2">
+        <v>100</v>
+      </c>
       <c r="P510" s="2"/>
       <c r="Q510" t="s" s="2">
         <v>23</v>
@@ -59411,7 +59394,7 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>94</v>
+        <v>101</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
@@ -59428,13 +59411,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1188</v>
+        <v>1184</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59451,22 +59434,22 @@
         <v>23</v>
       </c>
       <c r="J511" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K511" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>97</v>
+        <v>103</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>98</v>
+        <v>104</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>99</v>
+        <v>105</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>100</v>
+        <v>106</v>
       </c>
       <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
@@ -59492,13 +59475,13 @@
         <v>23</v>
       </c>
       <c r="Y511" t="s" s="2">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Z511" t="s" s="2">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="AA511" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="AB511" t="s" s="2">
         <v>23</v>
@@ -59516,7 +59499,7 @@
         <v>23</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>101</v>
+        <v>110</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -59533,17 +59516,17 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1189</v>
+        <v>1185</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
-        <v>23</v>
+        <v>519</v>
       </c>
       <c r="F512" s="2"/>
       <c r="G512" t="s" s="2">
@@ -59562,16 +59545,16 @@
         <v>23</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>103</v>
+        <v>520</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>104</v>
+        <v>521</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>105</v>
+        <v>522</v>
       </c>
       <c r="O512" t="s" s="2">
-        <v>106</v>
+        <v>523</v>
       </c>
       <c r="P512" s="2"/>
       <c r="Q512" t="s" s="2">
@@ -59597,13 +59580,13 @@
         <v>23</v>
       </c>
       <c r="Y512" t="s" s="2">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="Z512" t="s" s="2">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="AA512" t="s" s="2">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="AB512" t="s" s="2">
         <v>23</v>
@@ -59621,7 +59604,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>110</v>
+        <v>524</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -59638,24 +59621,24 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1190</v>
+        <v>1186</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
-        <v>519</v>
+        <v>526</v>
       </c>
       <c r="F513" s="2"/>
       <c r="G513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H513" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I513" t="s" s="2">
         <v>23</v>
@@ -59667,16 +59650,16 @@
         <v>23</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>520</v>
+        <v>182</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>521</v>
+        <v>527</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>522</v>
+        <v>528</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>523</v>
+        <v>529</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -59726,34 +59709,34 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>524</v>
+        <v>530</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI513" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ513" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK513" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1191</v>
+        <v>1187</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
-        <v>526</v>
+        <v>146</v>
       </c>
       <c r="F514" s="2"/>
       <c r="G514" t="s" s="2">
@@ -59772,16 +59755,16 @@
         <v>23</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>182</v>
+        <v>147</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>527</v>
+        <v>148</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>528</v>
+        <v>532</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>529</v>
+        <v>150</v>
       </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
@@ -59831,7 +59814,7 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>530</v>
+        <v>533</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>76</v>
@@ -59843,18 +59826,18 @@
         <v>23</v>
       </c>
       <c r="AK514" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1192</v>
+        <v>1188</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59871,7 +59854,7 @@
         <v>23</v>
       </c>
       <c r="J515" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K515" t="s" s="2">
         <v>23</v>
@@ -59880,15 +59863,17 @@
         <v>147</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>148</v>
+        <v>535</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>532</v>
+        <v>536</v>
       </c>
       <c r="O515" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P515" s="2"/>
+      <c r="P515" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q515" t="s" s="2">
         <v>23</v>
       </c>
@@ -59936,7 +59921,7 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>533</v>
+        <v>537</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>76</v>
@@ -59953,17 +59938,17 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1193</v>
+        <v>1189</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F516" s="2"/>
       <c r="G516" t="s" s="2">
@@ -59976,26 +59961,24 @@
         <v>23</v>
       </c>
       <c r="J516" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K516" t="s" s="2">
         <v>84</v>
       </c>
-      <c r="K516" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="L516" t="s" s="2">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>535</v>
+        <v>1190</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>536</v>
+        <v>1191</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P516" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1192</v>
+      </c>
+      <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
         <v>23</v>
       </c>
@@ -60043,7 +60026,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>537</v>
+        <v>1189</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -60055,18 +60038,18 @@
         <v>23</v>
       </c>
       <c r="AK516" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60077,29 +60060,27 @@
         <v>76</v>
       </c>
       <c r="H517" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I517" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J517" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K517" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>112</v>
+        <v>103</v>
       </c>
       <c r="M517" t="s" s="2">
+        <v>1194</v>
+      </c>
+      <c r="N517" t="s" s="2">
         <v>1195</v>
       </c>
-      <c r="N517" t="s" s="2">
-        <v>1196</v>
-      </c>
-      <c r="O517" t="s" s="2">
-        <v>1197</v>
-      </c>
+      <c r="O517" s="2"/>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
         <v>23</v>
@@ -60124,13 +60105,13 @@
         <v>23</v>
       </c>
       <c r="Y517" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="Z517" t="s" s="2">
-        <v>23</v>
+        <v>1195</v>
       </c>
       <c r="AA517" t="s" s="2">
-        <v>23</v>
+        <v>1196</v>
       </c>
       <c r="AB517" t="s" s="2">
         <v>23</v>
@@ -60148,13 +60129,13 @@
         <v>23</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI517" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ517" t="s" s="2">
         <v>23</v>
@@ -60165,13 +60146,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60182,27 +60163,29 @@
         <v>76</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J518" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K518" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>103</v>
+        <v>367</v>
       </c>
       <c r="M518" t="s" s="2">
+        <v>1198</v>
+      </c>
+      <c r="N518" t="s" s="2">
         <v>1199</v>
       </c>
-      <c r="N518" t="s" s="2">
+      <c r="O518" t="s" s="2">
         <v>1200</v>
       </c>
-      <c r="O518" s="2"/>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
         <v>23</v>
@@ -60227,13 +60210,13 @@
         <v>23</v>
       </c>
       <c r="Y518" t="s" s="2">
-        <v>121</v>
+        <v>1201</v>
       </c>
       <c r="Z518" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="AA518" t="s" s="2">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="AB518" t="s" s="2">
         <v>23</v>
@@ -60251,13 +60234,13 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1198</v>
+        <v>1197</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI518" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ518" t="s" s="2">
         <v>23</v>
@@ -60268,13 +60251,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60282,10 +60265,10 @@
       </c>
       <c r="F519" s="2"/>
       <c r="G519" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H519" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I519" t="s" s="2">
         <v>23</v>
@@ -60300,13 +60283,13 @@
         <v>367</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60332,13 +60315,13 @@
         <v>23</v>
       </c>
       <c r="Y519" t="s" s="2">
-        <v>1206</v>
+        <v>372</v>
       </c>
       <c r="Z519" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="AA519" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="AB519" t="s" s="2">
         <v>23</v>
@@ -60356,13 +60339,13 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="AH519" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI519" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ519" t="s" s="2">
         <v>23</v>
@@ -60373,13 +60356,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60387,7 +60370,7 @@
       </c>
       <c r="F520" s="2"/>
       <c r="G520" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H520" t="s" s="2">
         <v>83</v>
@@ -60402,17 +60385,15 @@
         <v>84</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>367</v>
+        <v>141</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1211</v>
-      </c>
-      <c r="O520" t="s" s="2">
         <v>1212</v>
       </c>
+      <c r="O520" s="2"/>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
         <v>23</v>
@@ -60437,13 +60418,13 @@
         <v>23</v>
       </c>
       <c r="Y520" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>1213</v>
+        <v>23</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>1214</v>
+        <v>23</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
@@ -60461,10 +60442,10 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="AH520" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI520" t="s" s="2">
         <v>83</v>
@@ -60478,13 +60459,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60495,7 +60476,7 @@
         <v>76</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I521" t="s" s="2">
         <v>23</v>
@@ -60507,20 +60488,22 @@
         <v>84</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1216</v>
+        <v>1214</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1217</v>
+        <v>1215</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R521" s="2"/>
+      <c r="R521" t="s" s="2">
+        <v>1216</v>
+      </c>
       <c r="S521" t="s" s="2">
         <v>23</v>
       </c>
@@ -60564,13 +60547,13 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1215</v>
+        <v>1213</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI521" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ521" t="s" s="2">
         <v>23</v>
@@ -60581,13 +60564,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60598,7 +60581,7 @@
         <v>76</v>
       </c>
       <c r="H522" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I522" t="s" s="2">
         <v>23</v>
@@ -60607,25 +60590,23 @@
         <v>23</v>
       </c>
       <c r="K522" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1219</v>
+        <v>142</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1220</v>
+        <v>143</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R522" t="s" s="2">
-        <v>1221</v>
-      </c>
+      <c r="R522" s="2"/>
       <c r="S522" t="s" s="2">
         <v>23</v>
       </c>
@@ -60669,41 +60650,41 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1218</v>
+        <v>144</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI522" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ522" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK522" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1222</v>
+        <v>1218</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F523" s="2"/>
       <c r="G523" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H523" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I523" t="s" s="2">
         <v>23</v>
@@ -60715,15 +60696,17 @@
         <v>23</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O523" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O523" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P523" s="2"/>
       <c r="Q523" t="s" s="2">
         <v>23</v>
@@ -60772,34 +60755,34 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI523" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ523" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK523" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1223</v>
+        <v>1219</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F524" s="2"/>
       <c r="G524" t="s" s="2">
@@ -60812,24 +60795,26 @@
         <v>23</v>
       </c>
       <c r="J524" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K524" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L524" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O524" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P524" s="2"/>
+      <c r="P524" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q524" t="s" s="2">
         <v>23</v>
       </c>
@@ -60877,7 +60862,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -60894,49 +60879,45 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1224</v>
+        <v>1220</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F525" s="2"/>
       <c r="G525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H525" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J525" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K525" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>147</v>
+        <v>112</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>155</v>
+        <v>1221</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O525" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P525" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1222</v>
+      </c>
+      <c r="O525" s="2"/>
+      <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
         <v>23</v>
       </c>
@@ -60984,30 +60965,30 @@
         <v>23</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>158</v>
+        <v>1220</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI525" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK525" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61030,13 +61011,13 @@
         <v>84</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>112</v>
+        <v>578</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1226</v>
+        <v>1224</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1227</v>
+        <v>1225</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" s="2"/>
@@ -61087,7 +61068,7 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1225</v>
+        <v>1223</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61104,13 +61085,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61133,13 +61114,13 @@
         <v>84</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>578</v>
+        <v>497</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1229</v>
+        <v>1227</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1230</v>
+        <v>1228</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -61190,7 +61171,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1228</v>
+        <v>1226</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61207,13 +61188,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61224,7 +61205,7 @@
         <v>76</v>
       </c>
       <c r="H528" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I528" t="s" s="2">
         <v>23</v>
@@ -61236,13 +61217,13 @@
         <v>84</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>497</v>
+        <v>136</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1232</v>
+        <v>1230</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1233</v>
+        <v>1231</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61293,13 +61274,13 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1231</v>
+        <v>1229</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI528" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ528" t="s" s="2">
         <v>23</v>
@@ -61310,13 +61291,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1234</v>
+        <v>1232</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61327,7 +61308,7 @@
         <v>76</v>
       </c>
       <c r="H529" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I529" t="s" s="2">
         <v>23</v>
@@ -61336,16 +61317,16 @@
         <v>23</v>
       </c>
       <c r="K529" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1235</v>
+        <v>142</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1236</v>
+        <v>143</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61396,41 +61377,41 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1234</v>
+        <v>144</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI529" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ529" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK529" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1237</v>
+        <v>1233</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F530" s="2"/>
       <c r="G530" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I530" t="s" s="2">
         <v>23</v>
@@ -61442,15 +61423,17 @@
         <v>23</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O530" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O530" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P530" s="2"/>
       <c r="Q530" t="s" s="2">
         <v>23</v>
@@ -61499,34 +61482,34 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ530" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK530" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1238</v>
+        <v>1234</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F531" s="2"/>
       <c r="G531" t="s" s="2">
@@ -61539,24 +61522,26 @@
         <v>23</v>
       </c>
       <c r="J531" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K531" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L531" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O531" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P531" s="2"/>
+      <c r="P531" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q531" t="s" s="2">
         <v>23</v>
       </c>
@@ -61604,7 +61589,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61621,49 +61606,45 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1239</v>
+        <v>1235</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F532" s="2"/>
       <c r="G532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J532" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K532" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>147</v>
+        <v>491</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>155</v>
+        <v>1236</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O532" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P532" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1237</v>
+      </c>
+      <c r="O532" s="2"/>
+      <c r="P532" s="2"/>
       <c r="Q532" t="s" s="2">
         <v>23</v>
       </c>
@@ -61711,30 +61692,30 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>158</v>
+        <v>1235</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI532" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1177</v>
+        <v>1172</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61742,7 +61723,7 @@
       </c>
       <c r="F533" s="2"/>
       <c r="G533" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H533" t="s" s="2">
         <v>83</v>
@@ -61757,13 +61738,13 @@
         <v>84</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>491</v>
+        <v>1239</v>
       </c>
       <c r="M533" t="s" s="2">
+        <v>1240</v>
+      </c>
+      <c r="N533" t="s" s="2">
         <v>1241</v>
-      </c>
-      <c r="N533" t="s" s="2">
-        <v>1242</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -61790,13 +61771,13 @@
         <v>23</v>
       </c>
       <c r="Y533" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z533" t="s" s="2">
-        <v>23</v>
+        <v>1242</v>
       </c>
       <c r="AA533" t="s" s="2">
-        <v>23</v>
+        <v>1209</v>
       </c>
       <c r="AB533" t="s" s="2">
         <v>23</v>
@@ -61814,10 +61795,10 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1240</v>
+        <v>1238</v>
       </c>
       <c r="AH533" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI533" t="s" s="2">
         <v>83</v>
@@ -61831,13 +61812,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1177</v>
+        <v>1243</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1243</v>
+        <v>1247</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61845,10 +61826,10 @@
       </c>
       <c r="F534" s="2"/>
       <c r="G534" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H534" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I534" t="s" s="2">
         <v>23</v>
@@ -61857,18 +61838,20 @@
         <v>23</v>
       </c>
       <c r="K534" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>1244</v>
+        <v>78</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>1245</v>
+        <v>1249</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>1246</v>
-      </c>
-      <c r="O534" s="2"/>
+        <v>1250</v>
+      </c>
+      <c r="O534" t="s" s="2">
+        <v>1251</v>
+      </c>
       <c r="P534" s="2"/>
       <c r="Q534" t="s" s="2">
         <v>23</v>
@@ -61893,37 +61876,37 @@
         <v>23</v>
       </c>
       <c r="Y534" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF534" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG534" t="s" s="2">
         <v>1247</v>
       </c>
-      <c r="AA534" t="s" s="2">
-        <v>1214</v>
-      </c>
-      <c r="AB534" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC534" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD534" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE534" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF534" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG534" t="s" s="2">
-        <v>1243</v>
-      </c>
       <c r="AH534" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI534" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ534" t="s" s="2">
         <v>23</v>
@@ -61934,7 +61917,7 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B535" t="s" s="2">
         <v>1252</v>
@@ -61951,7 +61934,7 @@
         <v>76</v>
       </c>
       <c r="H535" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I535" t="s" s="2">
         <v>23</v>
@@ -61963,17 +61946,15 @@
         <v>23</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>78</v>
+        <v>141</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1254</v>
+        <v>142</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1255</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>1256</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O535" s="2"/>
       <c r="P535" s="2"/>
       <c r="Q535" t="s" s="2">
         <v>23</v>
@@ -62022,41 +62003,41 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1252</v>
+        <v>144</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI535" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ535" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK535" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1257</v>
+        <v>1253</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F536" s="2"/>
       <c r="G536" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H536" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I536" t="s" s="2">
         <v>23</v>
@@ -62068,15 +62049,17 @@
         <v>23</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O536" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O536" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P536" s="2"/>
       <c r="Q536" t="s" s="2">
         <v>23</v>
@@ -62113,46 +62096,46 @@
         <v>23</v>
       </c>
       <c r="AC536" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD536" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE536" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF536" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI536" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ536" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK536" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1258</v>
+        <v>1254</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
-        <v>146</v>
+        <v>154</v>
       </c>
       <c r="F537" s="2"/>
       <c r="G537" t="s" s="2">
@@ -62165,24 +62148,26 @@
         <v>23</v>
       </c>
       <c r="J537" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K537" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L537" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>148</v>
+        <v>155</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>149</v>
+        <v>156</v>
       </c>
       <c r="O537" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P537" s="2"/>
+      <c r="P537" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q537" t="s" s="2">
         <v>23</v>
       </c>
@@ -62218,19 +62203,19 @@
         <v>23</v>
       </c>
       <c r="AC537" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD537" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE537" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF537" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>151</v>
+        <v>158</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62247,17 +62232,17 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1259</v>
+        <v>1255</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F538" s="2"/>
       <c r="G538" t="s" s="2">
@@ -62267,28 +62252,26 @@
         <v>77</v>
       </c>
       <c r="I538" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J538" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K538" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>147</v>
+        <v>578</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>155</v>
+        <v>1256</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O538" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1257</v>
+      </c>
+      <c r="O538" s="2"/>
       <c r="P538" t="s" s="2">
-        <v>157</v>
+        <v>1258</v>
       </c>
       <c r="Q538" t="s" s="2">
         <v>23</v>
@@ -62337,7 +62320,7 @@
         <v>23</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>158</v>
+        <v>1255</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
@@ -62349,18 +62332,18 @@
         <v>23</v>
       </c>
       <c r="AK538" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62371,7 +62354,7 @@
         <v>76</v>
       </c>
       <c r="H539" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I539" t="s" s="2">
         <v>84</v>
@@ -62383,17 +62366,17 @@
         <v>84</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>578</v>
+        <v>418</v>
       </c>
       <c r="M539" t="s" s="2">
+        <v>1260</v>
+      </c>
+      <c r="N539" t="s" s="2">
         <v>1261</v>
-      </c>
-      <c r="N539" t="s" s="2">
-        <v>1262</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>23</v>
@@ -62442,24 +62425,24 @@
         <v>23</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI539" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ539" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK539" t="s" s="2">
-        <v>95</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B540" t="s" s="2">
         <v>1264</v>
@@ -62479,27 +62462,25 @@
         <v>83</v>
       </c>
       <c r="I540" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J540" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K540" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>418</v>
+        <v>141</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1265</v>
+        <v>142</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1266</v>
+        <v>143</v>
       </c>
       <c r="O540" s="2"/>
-      <c r="P540" t="s" s="2">
-        <v>1267</v>
-      </c>
+      <c r="P540" s="2"/>
       <c r="Q540" t="s" s="2">
         <v>23</v>
       </c>
@@ -62547,7 +62528,7 @@
         <v>23</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1264</v>
+        <v>144</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>76</v>
@@ -62559,29 +62540,29 @@
         <v>23</v>
       </c>
       <c r="AK540" t="s" s="2">
-        <v>1268</v>
+        <v>23</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1269</v>
+        <v>1265</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F541" s="2"/>
       <c r="G541" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H541" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I541" t="s" s="2">
         <v>23</v>
@@ -62593,15 +62574,17 @@
         <v>23</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O541" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O541" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
         <v>23</v>
@@ -62638,53 +62621,53 @@
         <v>23</v>
       </c>
       <c r="AC541" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD541" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF541" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI541" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK541" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1270</v>
+        <v>1266</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F542" s="2"/>
       <c r="G542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H542" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I542" t="s" s="2">
         <v>23</v>
@@ -62693,20 +62676,18 @@
         <v>23</v>
       </c>
       <c r="K542" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>147</v>
+        <v>1267</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>148</v>
+        <v>1268</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O542" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1269</v>
+      </c>
+      <c r="O542" s="2"/>
       <c r="P542" s="2"/>
       <c r="Q542" t="s" s="2">
         <v>23</v>
@@ -62743,11 +62724,9 @@
         <v>23</v>
       </c>
       <c r="AC542" t="s" s="2">
-        <v>353</v>
-      </c>
-      <c r="AD542" t="s" s="2">
-        <v>354</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AD542" s="2"/>
       <c r="AE542" t="s" s="2">
         <v>23</v>
       </c>
@@ -62755,32 +62734,34 @@
         <v>355</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>151</v>
+        <v>1266</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI542" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ542" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK542" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B543" t="s" s="2">
+        <v>1270</v>
+      </c>
+      <c r="C543" t="s" s="2">
+        <v>1266</v>
+      </c>
+      <c r="D543" t="s" s="2">
         <v>1271</v>
       </c>
-      <c r="C543" t="s" s="2">
-        <v>1271</v>
-      </c>
-      <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
         <v>23</v>
       </c>
@@ -62801,13 +62782,13 @@
         <v>84</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>1272</v>
+        <v>1054</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1273</v>
+        <v>1268</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1274</v>
+        <v>1269</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -62846,17 +62827,19 @@
         <v>23</v>
       </c>
       <c r="AC543" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AD543" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="AD543" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AE543" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF543" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1271</v>
+        <v>1266</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -62873,17 +62856,15 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1275</v>
+        <v>1272</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1271</v>
-      </c>
-      <c r="D544" t="s" s="2">
-        <v>1276</v>
-      </c>
+        <v>1273</v>
+      </c>
+      <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
         <v>23</v>
       </c>
@@ -62901,16 +62882,16 @@
         <v>23</v>
       </c>
       <c r="K544" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>1054</v>
+        <v>141</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>1273</v>
+        <v>142</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>1274</v>
+        <v>143</v>
       </c>
       <c r="O544" s="2"/>
       <c r="P544" s="2"/>
@@ -62961,7 +62942,7 @@
         <v>23</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1271</v>
+        <v>144</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
@@ -62973,29 +62954,29 @@
         <v>23</v>
       </c>
       <c r="AK544" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1277</v>
+        <v>1274</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1278</v>
+        <v>1275</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F545" s="2"/>
       <c r="G545" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H545" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I545" t="s" s="2">
         <v>23</v>
@@ -63007,15 +62988,17 @@
         <v>23</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>141</v>
+        <v>147</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>142</v>
+        <v>148</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O545" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O545" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P545" s="2"/>
       <c r="Q545" t="s" s="2">
         <v>23</v>
@@ -63052,53 +63035,53 @@
         <v>23</v>
       </c>
       <c r="AC545" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD545" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE545" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF545" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>144</v>
+        <v>151</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI545" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ545" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK545" t="s" s="2">
-        <v>23</v>
+        <v>152</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1279</v>
+        <v>1276</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1280</v>
+        <v>1277</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F546" s="2"/>
       <c r="G546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H546" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I546" t="s" s="2">
         <v>23</v>
@@ -63107,19 +63090,19 @@
         <v>23</v>
       </c>
       <c r="K546" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L546" t="s" s="2">
-        <v>147</v>
+        <v>578</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>148</v>
+        <v>1278</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>149</v>
+        <v>1279</v>
       </c>
       <c r="O546" t="s" s="2">
-        <v>150</v>
+        <v>1280</v>
       </c>
       <c r="P546" s="2"/>
       <c r="Q546" t="s" s="2">
@@ -63157,42 +63140,42 @@
         <v>23</v>
       </c>
       <c r="AC546" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD546" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE546" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF546" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>151</v>
+        <v>1281</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI546" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ546" t="s" s="2">
-        <v>23</v>
+        <v>1282</v>
       </c>
       <c r="AK546" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63218,19 +63201,21 @@
         <v>578</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="O547" t="s" s="2">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="P547" s="2"/>
       <c r="Q547" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R547" s="2"/>
+      <c r="R547" t="s" s="2">
+        <v>1288</v>
+      </c>
       <c r="S547" t="s" s="2">
         <v>23</v>
       </c>
@@ -63274,7 +63259,7 @@
         <v>23</v>
       </c>
       <c r="AG547" t="s" s="2">
-        <v>1286</v>
+        <v>1289</v>
       </c>
       <c r="AH547" t="s" s="2">
         <v>76</v>
@@ -63283,7 +63268,7 @@
         <v>83</v>
       </c>
       <c r="AJ547" t="s" s="2">
-        <v>1287</v>
+        <v>1282</v>
       </c>
       <c r="AK547" t="s" s="2">
         <v>95</v>
@@ -63291,13 +63276,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63320,69 +63305,69 @@
         <v>84</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>578</v>
+        <v>1291</v>
       </c>
       <c r="M548" t="s" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N548" t="s" s="2">
+        <v>1293</v>
+      </c>
+      <c r="O548" t="s" s="2">
+        <v>1294</v>
+      </c>
+      <c r="P548" t="s" s="2">
+        <v>1295</v>
+      </c>
+      <c r="Q548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R548" s="2"/>
+      <c r="S548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG548" t="s" s="2">
         <v>1290</v>
       </c>
-      <c r="N548" t="s" s="2">
-        <v>1291</v>
-      </c>
-      <c r="O548" t="s" s="2">
-        <v>1292</v>
-      </c>
-      <c r="P548" s="2"/>
-      <c r="Q548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R548" t="s" s="2">
-        <v>1293</v>
-      </c>
-      <c r="S548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG548" t="s" s="2">
-        <v>1294</v>
-      </c>
       <c r="AH548" t="s" s="2">
         <v>76</v>
       </c>
@@ -63390,7 +63375,7 @@
         <v>83</v>
       </c>
       <c r="AJ548" t="s" s="2">
-        <v>1287</v>
+        <v>23</v>
       </c>
       <c r="AK548" t="s" s="2">
         <v>95</v>
@@ -63398,13 +63383,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63427,7 +63412,7 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="M549" t="s" s="2">
         <v>1297</v>
@@ -63435,12 +63420,8 @@
       <c r="N549" t="s" s="2">
         <v>1298</v>
       </c>
-      <c r="O549" t="s" s="2">
-        <v>1299</v>
-      </c>
-      <c r="P549" t="s" s="2">
-        <v>1300</v>
-      </c>
+      <c r="O549" s="2"/>
+      <c r="P549" s="2"/>
       <c r="Q549" t="s" s="2">
         <v>23</v>
       </c>
@@ -63488,7 +63469,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63505,13 +63486,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63534,16 +63515,20 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>1296</v>
+        <v>199</v>
       </c>
       <c r="M550" t="s" s="2">
+        <v>1300</v>
+      </c>
+      <c r="N550" t="s" s="2">
+        <v>1301</v>
+      </c>
+      <c r="O550" t="s" s="2">
         <v>1302</v>
       </c>
-      <c r="N550" t="s" s="2">
+      <c r="P550" t="s" s="2">
         <v>1303</v>
       </c>
-      <c r="O550" s="2"/>
-      <c r="P550" s="2"/>
       <c r="Q550" t="s" s="2">
         <v>23</v>
       </c>
@@ -63591,7 +63576,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1301</v>
+        <v>1299</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63608,7 +63593,7 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B551" t="s" s="2">
         <v>1304</v>
@@ -63646,10 +63631,10 @@
         <v>1306</v>
       </c>
       <c r="O551" t="s" s="2">
-        <v>1307</v>
+        <v>1302</v>
       </c>
       <c r="P551" t="s" s="2">
-        <v>1308</v>
+        <v>1303</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63715,13 +63700,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63744,20 +63729,16 @@
         <v>84</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>1310</v>
+        <v>1308</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1311</v>
-      </c>
-      <c r="O552" t="s" s="2">
-        <v>1307</v>
-      </c>
-      <c r="P552" t="s" s="2">
-        <v>1308</v>
-      </c>
+        <v>1309</v>
+      </c>
+      <c r="O552" s="2"/>
+      <c r="P552" s="2"/>
       <c r="Q552" t="s" s="2">
         <v>23</v>
       </c>
@@ -63781,13 +63762,13 @@
         <v>23</v>
       </c>
       <c r="Y552" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="Z552" t="s" s="2">
-        <v>23</v>
+        <v>1310</v>
       </c>
       <c r="AA552" t="s" s="2">
-        <v>23</v>
+        <v>1311</v>
       </c>
       <c r="AB552" t="s" s="2">
         <v>23</v>
@@ -63805,7 +63786,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1309</v>
+        <v>1307</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63822,7 +63803,7 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B553" t="s" s="2">
         <v>1312</v>
@@ -63851,7 +63832,7 @@
         <v>84</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>103</v>
+        <v>1291</v>
       </c>
       <c r="M553" t="s" s="2">
         <v>1313</v>
@@ -63864,7 +63845,9 @@
       <c r="Q553" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R553" s="2"/>
+      <c r="R553" t="s" s="2">
+        <v>1315</v>
+      </c>
       <c r="S553" t="s" s="2">
         <v>23</v>
       </c>
@@ -63884,13 +63867,13 @@
         <v>23</v>
       </c>
       <c r="Y553" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z553" t="s" s="2">
-        <v>1315</v>
+        <v>23</v>
       </c>
       <c r="AA553" t="s" s="2">
-        <v>1316</v>
+        <v>23</v>
       </c>
       <c r="AB553" t="s" s="2">
         <v>23</v>
@@ -63925,13 +63908,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63954,22 +63937,20 @@
         <v>84</v>
       </c>
       <c r="L554" t="s" s="2">
-        <v>1296</v>
+        <v>1291</v>
       </c>
       <c r="M554" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="N554" t="s" s="2">
         <v>1318</v>
-      </c>
-      <c r="N554" t="s" s="2">
-        <v>1319</v>
       </c>
       <c r="O554" s="2"/>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R554" t="s" s="2">
-        <v>1320</v>
-      </c>
+      <c r="R554" s="2"/>
       <c r="S554" t="s" s="2">
         <v>23</v>
       </c>
@@ -64013,7 +63994,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1317</v>
+        <v>1316</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64030,13 +64011,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64050,7 +64031,7 @@
         <v>83</v>
       </c>
       <c r="I555" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J555" t="s" s="2">
         <v>23</v>
@@ -64059,13 +64040,13 @@
         <v>84</v>
       </c>
       <c r="L555" t="s" s="2">
-        <v>1296</v>
+        <v>199</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1322</v>
+        <v>1320</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64116,7 +64097,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1321</v>
+        <v>1319</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64133,13 +64114,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64153,7 +64134,7 @@
         <v>83</v>
       </c>
       <c r="I556" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J556" t="s" s="2">
         <v>23</v>
@@ -64165,10 +64146,10 @@
         <v>199</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1326</v>
+        <v>1324</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64219,7 +64200,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64236,13 +64217,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64265,13 +64246,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>199</v>
+        <v>103</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1328</v>
+        <v>1326</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1329</v>
+        <v>1327</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64298,13 +64279,11 @@
         <v>23</v>
       </c>
       <c r="Y557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z557" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z557" s="2"/>
       <c r="AA557" t="s" s="2">
-        <v>23</v>
+        <v>1328</v>
       </c>
       <c r="AB557" t="s" s="2">
         <v>23</v>
@@ -64322,7 +64301,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1327</v>
+        <v>1325</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64339,13 +64318,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64356,7 +64335,7 @@
         <v>76</v>
       </c>
       <c r="H558" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I558" t="s" s="2">
         <v>23</v>
@@ -64371,12 +64350,14 @@
         <v>103</v>
       </c>
       <c r="M558" t="s" s="2">
+        <v>1330</v>
+      </c>
+      <c r="N558" t="s" s="2">
         <v>1331</v>
       </c>
-      <c r="N558" t="s" s="2">
+      <c r="O558" t="s" s="2">
         <v>1332</v>
       </c>
-      <c r="O558" s="2"/>
       <c r="P558" s="2"/>
       <c r="Q558" t="s" s="2">
         <v>23</v>
@@ -64423,13 +64404,13 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI558" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ558" t="s" s="2">
         <v>23</v>
@@ -64440,7 +64421,7 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>1334</v>
@@ -64469,16 +64450,16 @@
         <v>84</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>103</v>
+        <v>1335</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="O559" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="P559" s="2"/>
       <c r="Q559" t="s" s="2">
@@ -64504,11 +64485,13 @@
         <v>23</v>
       </c>
       <c r="Y559" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z559" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z559" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA559" t="s" s="2">
-        <v>1338</v>
+        <v>23</v>
       </c>
       <c r="AB559" t="s" s="2">
         <v>23</v>
@@ -64543,7 +64526,7 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B560" t="s" s="2">
         <v>1339</v>
@@ -64563,7 +64546,7 @@
         <v>77</v>
       </c>
       <c r="I560" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J560" t="s" s="2">
         <v>23</v>
@@ -64572,18 +64555,20 @@
         <v>84</v>
       </c>
       <c r="L560" t="s" s="2">
+        <v>103</v>
+      </c>
+      <c r="M560" t="s" s="2">
         <v>1340</v>
       </c>
-      <c r="M560" t="s" s="2">
+      <c r="N560" t="s" s="2">
         <v>1341</v>
       </c>
-      <c r="N560" t="s" s="2">
+      <c r="O560" t="s" s="2">
         <v>1342</v>
       </c>
-      <c r="O560" t="s" s="2">
+      <c r="P560" t="s" s="2">
         <v>1343</v>
       </c>
-      <c r="P560" s="2"/>
       <c r="Q560" t="s" s="2">
         <v>23</v>
       </c>
@@ -64607,13 +64592,11 @@
         <v>23</v>
       </c>
       <c r="Y560" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z560" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>23</v>
+        <v>1344</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64648,13 +64631,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64665,7 +64648,7 @@
         <v>76</v>
       </c>
       <c r="H561" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I561" t="s" s="2">
         <v>84</v>
@@ -64677,20 +64660,16 @@
         <v>84</v>
       </c>
       <c r="L561" t="s" s="2">
-        <v>103</v>
+        <v>130</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1346</v>
-      </c>
-      <c r="O561" t="s" s="2">
         <v>1347</v>
       </c>
-      <c r="P561" t="s" s="2">
-        <v>1348</v>
-      </c>
+      <c r="O561" s="2"/>
+      <c r="P561" s="2"/>
       <c r="Q561" t="s" s="2">
         <v>23</v>
       </c>
@@ -64714,11 +64693,13 @@
         <v>23</v>
       </c>
       <c r="Y561" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z561" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z561" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA561" t="s" s="2">
-        <v>1349</v>
+        <v>23</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64736,13 +64717,13 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI561" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ561" t="s" s="2">
         <v>23</v>
@@ -64753,13 +64734,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1248</v>
+        <v>1243</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64773,7 +64754,7 @@
         <v>83</v>
       </c>
       <c r="I562" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J562" t="s" s="2">
         <v>23</v>
@@ -64782,15 +64763,17 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>130</v>
+        <v>367</v>
       </c>
       <c r="M562" t="s" s="2">
+        <v>1349</v>
+      </c>
+      <c r="N562" t="s" s="2">
+        <v>1350</v>
+      </c>
+      <c r="O562" t="s" s="2">
         <v>1351</v>
       </c>
-      <c r="N562" t="s" s="2">
-        <v>1352</v>
-      </c>
-      <c r="O562" s="2"/>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
         <v>23</v>
@@ -64815,13 +64798,13 @@
         <v>23</v>
       </c>
       <c r="Y562" t="s" s="2">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Z562" t="s" s="2">
-        <v>23</v>
+        <v>1352</v>
       </c>
       <c r="AA562" t="s" s="2">
-        <v>23</v>
+        <v>1353</v>
       </c>
       <c r="AB562" t="s" s="2">
         <v>23</v>
@@ -64839,7 +64822,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1350</v>
+        <v>1348</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -64851,111 +64834,6 @@
         <v>23</v>
       </c>
       <c r="AK562" t="s" s="2">
-        <v>95</v>
-      </c>
-    </row>
-    <row r="563">
-      <c r="A563" t="s" s="2">
-        <v>1248</v>
-      </c>
-      <c r="B563" t="s" s="2">
-        <v>1353</v>
-      </c>
-      <c r="C563" t="s" s="2">
-        <v>1353</v>
-      </c>
-      <c r="D563" s="2"/>
-      <c r="E563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="F563" s="2"/>
-      <c r="G563" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="H563" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="I563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="J563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K563" t="s" s="2">
-        <v>84</v>
-      </c>
-      <c r="L563" t="s" s="2">
-        <v>367</v>
-      </c>
-      <c r="M563" t="s" s="2">
-        <v>1354</v>
-      </c>
-      <c r="N563" t="s" s="2">
-        <v>1355</v>
-      </c>
-      <c r="O563" t="s" s="2">
-        <v>1356</v>
-      </c>
-      <c r="P563" s="2"/>
-      <c r="Q563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R563" s="2"/>
-      <c r="S563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y563" t="s" s="2">
-        <v>107</v>
-      </c>
-      <c r="Z563" t="s" s="2">
-        <v>1357</v>
-      </c>
-      <c r="AA563" t="s" s="2">
-        <v>1358</v>
-      </c>
-      <c r="AB563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG563" t="s" s="2">
-        <v>1353</v>
-      </c>
-      <c r="AH563" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI563" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK563" t="s" s="2">
         <v>95</v>
       </c>
     </row>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18832" uniqueCount="1354">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18832" uniqueCount="1356">
   <si>
     <t>Property</t>
   </si>
@@ -24,13 +24,13 @@
     <t>ID</t>
   </si>
   <si>
-    <t>at-elga-emed-bundle-medikationsplan</t>
+    <t>at-elga-emed-bundle-medikationsplan-persistierung-tx</t>
   </si>
   <si>
     <t>URL</t>
   </si>
   <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-bundle-medikationsplan</t>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-bundle-medikationsplan-persistierung-tx</t>
   </si>
   <si>
     <t>Version</t>
@@ -42,13 +42,13 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AtEmedBundleMedikationsplan</t>
+    <t>AtElgaEmedBundleMedikationsplanTx</t>
   </si>
   <si>
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Collection Bundle Medikationsplan</t>
+    <t>AT ELGA e-Medikation Transaction Bundle Medikationsplan</t>
   </si>
   <si>
     <t>Status</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-11T15:21:25+00:00</t>
+    <t>2026-05-13T14:40:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,7 +90,7 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Collection bestehend aus: 
+    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
@@ -376,7 +376,7 @@
     <t>Bundle.type</t>
   </si>
   <si>
-    <t>Art des Bundles. Für Medikationspläne immer "collection".</t>
+    <t>Art des Bundles. Für schreibenden Zugriff immer Typ "transaction".</t>
   </si>
   <si>
     <t>Indicates the purpose of this bundle - how it is intended to be used.</t>
@@ -385,7 +385,7 @@
     <t>It's possible to use a bundle for other purposes (e.g. a document can be accepted as a transaction). This is primarily defined so that there can be specific rules for some of the bundle types.</t>
   </si>
   <si>
-    <t>collection</t>
+    <t>transaction</t>
   </si>
   <si>
     <t>required</t>
@@ -580,7 +580,7 @@
     <t>Bundle.entry.fullUrl</t>
   </si>
   <si>
-    <t>Eindeutige URL für den Eintrag im Bundle.</t>
+    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
   </si>
   <si>
     <t>The Absolute URL for the resource.  The fullUrl SHALL NOT disagree with the id in the resource - i.e. if the fullUrl is not a urn:uuid, the URL shall be version-independent URL consistent with the Resource.id. The fullUrl is a version independent reference to the resource. The fullUrl element SHALL have a value except that: 
@@ -1063,30 +1063,30 @@
     <t>A Signature holds an electronic representation of a signature and its supporting context in a FHIR accessible form. The signature may either be a cryptographic type (XML DigSig or a JWS), which is able to provide non-repudiation proof, or it may be a graphical image that represents a signature or a signature process. This element allows capturing signatures on documents, messages, transactions or even search responses, to support content-authentication, non-repudiation or other business cases. This is primarily relevant where the bundle may travel through multiple hops or via other mechanisms where HTTPS non-repudiation is insufficient.</t>
   </si>
   <si>
-    <t>at-elga-emed-bundle-tx-medikationsplan</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-bundle-tx-medikationsplan</t>
-  </si>
-  <si>
-    <t>AtElgaEmedBundleTxMedikationsplan</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Medikation Transaction Bundle Medikationsplan</t>
-  </si>
-  <si>
-    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+    <t>at-elga-emed-bundle-medikationsplan</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-bundle-medikationsplan</t>
+  </si>
+  <si>
+    <t>AtEmedBundleMedikationsplan</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Collection Bundle Medikationsplan</t>
+  </si>
+  <si>
+    <t>Das Bundle vom Typ Collection bestehend aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
 - 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
   </si>
   <si>
-    <t>Art des Bundles. Für schreibenden Zugriff immer Typ "transaction".</t>
-  </si>
-  <si>
-    <t>transaction</t>
-  </si>
-  <si>
-    <t xml:space="preserve">Eindeutige URL für den Eintrag im Bundle. </t>
+    <t>Art des Bundles. Für Medikationspläne immer "collection".</t>
+  </si>
+  <si>
+    <t>collection</t>
+  </si>
+  <si>
+    <t>Eindeutige URL für den Eintrag im Bundle.</t>
   </si>
   <si>
     <t>at-elga-emed-dosage-dosierung</t>
@@ -2023,7 +2023,7 @@
     <t>AtElgaEmedMedicationMedikation</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation medication Medikation</t>
+    <t>AT ELGA e-Medikation Medication Medikation</t>
   </si>
   <si>
     <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe.</t>
@@ -2864,28 +2864,32 @@
 </t>
   </si>
   <si>
-    <t>Die Anzahl der weiteren möglichen Einlösungen ist abhängig von der Rezeptart: Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
+    <t>Gültigkeitszeitraum einer geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
+  </si>
+  <si>
+    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.
+Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
+* **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
+* **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
+* **Substitutionsrezept**: Maximale Gültigkeitsdauer 12 Monate. Das validityPeriod.start darf maximal einen Monat in der Zukunft liegen, gültig bis das validityPeriod.end erreicht ist.</t>
+  </si>
+  <si>
+    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
+  </si>
+  <si>
+    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
+  </si>
+  <si>
+    <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
+  </si>
+  <si>
+    <t>Die Anzahl der weiteren möglichen Einlösungen (abhängig von Rezeptart): Kassenrezept: keine weitere Einlösung möglich (fixer Wert 0). Privatrezept: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden. Sustitutionsrezept: keine weitere Einlösung möglich (fixer Wert 0)</t>
   </si>
   <si>
     <t xml:space="preserve">Anzahl der weiteren möglichen Einlösungen:
 * **Kassenrezept**: keine weitere Einlösung möglich (fixer Wert 0)
 * **Privatrezept**: bis zu 6 Einlösungen, Anzahl der möglichen Einlösungen kann vom Arzt definiert werden
 * **Sustitutionsrezept**: keine weitere Einlösung möglich (fixer Wert 0) </t>
-  </si>
-  <si>
-    <t>It reflects the prescribers' perspective for the validity of the prescription. Dispenses must not be made against the prescription outside of this period. The lower-bound of the Dispensing Window signifies the earliest date that the prescription can be filled for the first time. If an upper-bound is not specified then the Prescription is open-ended or will default to a stale-date based on regulations.</t>
-  </si>
-  <si>
-    <t>Indicates when the Prescription becomes valid, and when it ceases to be a dispensable Prescription.</t>
-  </si>
-  <si>
-    <t>MedicationRequest.dispenseRequest.numberOfRepeatsAllowed</t>
-  </si>
-  <si>
-    <t>Number of refills authorized</t>
-  </si>
-  <si>
-    <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
   </si>
   <si>
     <t>If displaying "number of authorized fills", add 1 to this number.</t>
@@ -3243,6 +3247,12 @@
   </si>
   <si>
     <t>This indicates the validity period of a prescription (stale dating the Prescription).</t>
+  </si>
+  <si>
+    <t>Number of refills authorized</t>
+  </si>
+  <si>
+    <t>An integer indicating the number of times, in addition to the original dispense, (aka refills or repeats) that the patient can receive the prescribed medication. Usage Notes: This integer does not include the original order dispense. This means that if an order indicates dispense 30 tablets plus "3 repeats", then the order can be dispensed a total of 4 times and the patient can receive a total of 120 tablets.  A prescriber may explicitly say that zero refills are permitted after the initial dispense.</t>
   </si>
   <si>
     <t>Amount of medication to supply per dispense</t>
@@ -5601,7 +5611,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="157">
@@ -5609,7 +5619,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1030</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="158">
@@ -5625,7 +5635,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1031</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="160">
@@ -5633,7 +5643,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1032</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="161">
@@ -5695,7 +5705,7 @@
         <v>24</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>1033</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="169">
@@ -5731,7 +5741,7 @@
         <v>32</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="174">
@@ -5739,7 +5749,7 @@
         <v>34</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1035</v>
+        <v>1037</v>
       </c>
     </row>
     <row r="175">
@@ -5771,7 +5781,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
     </row>
     <row r="179">
@@ -5779,7 +5789,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1173</v>
+        <v>1175</v>
       </c>
     </row>
     <row r="180">
@@ -5795,7 +5805,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1174</v>
+        <v>1176</v>
       </c>
     </row>
     <row r="182">
@@ -5803,7 +5813,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1175</v>
+        <v>1177</v>
       </c>
     </row>
     <row r="183">
@@ -5865,7 +5875,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1176</v>
+        <v>1178</v>
       </c>
     </row>
     <row r="191">
@@ -5901,7 +5911,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="196">
@@ -5909,7 +5919,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1178</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="197">
@@ -5941,7 +5951,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
     </row>
     <row r="201">
@@ -5949,7 +5959,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1244</v>
+        <v>1246</v>
       </c>
     </row>
     <row r="202">
@@ -5965,7 +5975,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1245</v>
+        <v>1247</v>
       </c>
     </row>
     <row r="204">
@@ -5973,7 +5983,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="205">
@@ -6035,7 +6045,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1246</v>
+        <v>1248</v>
       </c>
     </row>
     <row r="213">
@@ -6071,7 +6081,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1247</v>
+        <v>1249</v>
       </c>
     </row>
     <row r="218">
@@ -6079,7 +6089,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1248</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="219">
@@ -52678,10 +52688,10 @@
         <v>130</v>
       </c>
       <c r="M446" t="s" s="2">
-        <v>909</v>
+        <v>1023</v>
       </c>
       <c r="N446" t="s" s="2">
-        <v>910</v>
+        <v>1024</v>
       </c>
       <c r="O446" t="s" s="2">
         <v>911</v>
@@ -52783,7 +52793,7 @@
         <v>497</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1023</v>
+        <v>1025</v>
       </c>
       <c r="N447" t="s" s="2">
         <v>914</v>
@@ -52991,7 +53001,7 @@
         <v>670</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>1024</v>
+        <v>1026</v>
       </c>
       <c r="N449" t="s" s="2">
         <v>930</v>
@@ -53094,7 +53104,7 @@
         <v>136</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>1025</v>
+        <v>1027</v>
       </c>
       <c r="N450" t="s" s="2">
         <v>933</v>
@@ -53720,7 +53730,7 @@
         <v>950</v>
       </c>
       <c r="M456" t="s" s="2">
-        <v>1026</v>
+        <v>1028</v>
       </c>
       <c r="N456" t="s" s="2">
         <v>952</v>
@@ -53823,7 +53833,7 @@
         <v>955</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1027</v>
+        <v>1029</v>
       </c>
       <c r="N457" t="s" s="2">
         <v>957</v>
@@ -53928,7 +53938,7 @@
         <v>960</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>1028</v>
+        <v>1030</v>
       </c>
       <c r="N458" t="s" s="2">
         <v>962</v>
@@ -54001,13 +54011,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -54033,10 +54043,10 @@
         <v>78</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1036</v>
+        <v>1038</v>
       </c>
       <c r="N459" t="s" s="2">
-        <v>1037</v>
+        <v>1039</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -54087,7 +54097,7 @@
         <v>23</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>1034</v>
+        <v>1036</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>76</v>
@@ -54099,18 +54109,18 @@
         <v>23</v>
       </c>
       <c r="AK459" t="s" s="2">
-        <v>1038</v>
+        <v>1040</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1039</v>
+        <v>1041</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -54209,13 +54219,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1040</v>
+        <v>1042</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -54312,13 +54322,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1041</v>
+        <v>1043</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -54417,13 +54427,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1042</v>
+        <v>1044</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -54522,13 +54532,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1043</v>
+        <v>1045</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -54627,13 +54637,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1044</v>
+        <v>1046</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -54732,13 +54742,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -54833,13 +54843,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1046</v>
+        <v>1048</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1045</v>
+        <v>1047</v>
       </c>
       <c r="D467" t="s" s="2">
         <v>742</v>
@@ -54940,13 +54950,13 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B468" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1047</v>
+        <v>1049</v>
       </c>
       <c r="D468" s="2"/>
       <c r="E468" t="s" s="2">
@@ -55047,13 +55057,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -55079,10 +55089,10 @@
         <v>112</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1049</v>
+        <v>1051</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>1050</v>
+        <v>1052</v>
       </c>
       <c r="O469" t="s" s="2">
         <v>751</v>
@@ -55135,7 +55145,7 @@
         <v>23</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>1048</v>
+        <v>1050</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>76</v>
@@ -55152,13 +55162,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -55181,13 +55191,13 @@
         <v>23</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>1052</v>
+        <v>1054</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1053</v>
+        <v>1055</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>1054</v>
+        <v>1056</v>
       </c>
       <c r="O470" s="2"/>
       <c r="P470" s="2"/>
@@ -55238,7 +55248,7 @@
         <v>23</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>1051</v>
+        <v>1053</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -55255,13 +55265,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55287,10 +55297,10 @@
         <v>103</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1056</v>
+        <v>1058</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="O471" t="s" s="2">
         <v>544</v>
@@ -55322,10 +55332,10 @@
         <v>121</v>
       </c>
       <c r="Z471" t="s" s="2">
-        <v>1058</v>
+        <v>1060</v>
       </c>
       <c r="AA471" t="s" s="2">
-        <v>1059</v>
+        <v>1061</v>
       </c>
       <c r="AB471" t="s" s="2">
         <v>23</v>
@@ -55343,7 +55353,7 @@
         <v>23</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>83</v>
@@ -55360,13 +55370,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -55392,10 +55402,10 @@
         <v>367</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1061</v>
+        <v>1063</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O472" s="2"/>
       <c r="P472" s="2"/>
@@ -55425,10 +55435,10 @@
         <v>372</v>
       </c>
       <c r="Z472" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AA472" t="s" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="AB472" t="s" s="2">
         <v>23</v>
@@ -55444,7 +55454,7 @@
         <v>169</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>76</v>
@@ -55461,16 +55471,16 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1065</v>
+        <v>1067</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D473" t="s" s="2">
-        <v>1066</v>
+        <v>1068</v>
       </c>
       <c r="E473" t="s" s="2">
         <v>23</v>
@@ -55495,10 +55505,10 @@
         <v>367</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1067</v>
+        <v>1069</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O473" s="2"/>
       <c r="P473" s="2"/>
@@ -55528,10 +55538,10 @@
         <v>372</v>
       </c>
       <c r="Z473" t="s" s="2">
-        <v>1063</v>
+        <v>1065</v>
       </c>
       <c r="AA473" t="s" s="2">
-        <v>1064</v>
+        <v>1066</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>23</v>
@@ -55549,7 +55559,7 @@
         <v>23</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55566,16 +55576,16 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1068</v>
+        <v>1070</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="D474" t="s" s="2">
-        <v>1069</v>
+        <v>1071</v>
       </c>
       <c r="E474" t="s" s="2">
         <v>23</v>
@@ -55597,13 +55607,13 @@
         <v>23</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>1070</v>
+        <v>1072</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1071</v>
+        <v>1073</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1062</v>
+        <v>1064</v>
       </c>
       <c r="O474" s="2"/>
       <c r="P474" s="2"/>
@@ -55654,7 +55664,7 @@
         <v>23</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1060</v>
+        <v>1062</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -55671,13 +55681,13 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="D475" s="2"/>
       <c r="E475" t="s" s="2">
@@ -55703,13 +55713,13 @@
         <v>367</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="O475" t="s" s="2">
-        <v>1075</v>
+        <v>1077</v>
       </c>
       <c r="P475" s="2"/>
       <c r="Q475" t="s" s="2">
@@ -55738,10 +55748,10 @@
         <v>107</v>
       </c>
       <c r="Z475" t="s" s="2">
-        <v>1076</v>
+        <v>1078</v>
       </c>
       <c r="AA475" t="s" s="2">
-        <v>1077</v>
+        <v>1079</v>
       </c>
       <c r="AB475" t="s" s="2">
         <v>23</v>
@@ -55759,7 +55769,7 @@
         <v>23</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1072</v>
+        <v>1074</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -55776,13 +55786,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -55808,13 +55818,13 @@
         <v>799</v>
       </c>
       <c r="M476" t="s" s="2">
-        <v>1079</v>
+        <v>1081</v>
       </c>
       <c r="N476" t="s" s="2">
-        <v>1080</v>
+        <v>1082</v>
       </c>
       <c r="O476" t="s" s="2">
-        <v>1081</v>
+        <v>1083</v>
       </c>
       <c r="P476" s="2"/>
       <c r="Q476" t="s" s="2">
@@ -55864,7 +55874,7 @@
         <v>23</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1078</v>
+        <v>1080</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>83</v>
@@ -55881,13 +55891,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -55913,13 +55923,13 @@
         <v>804</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1083</v>
+        <v>1085</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="O477" t="s" s="2">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="P477" s="2"/>
       <c r="Q477" t="s" s="2">
@@ -55969,7 +55979,7 @@
         <v>23</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1082</v>
+        <v>1084</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>76</v>
@@ -55986,13 +55996,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56015,13 +56025,13 @@
         <v>23</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1089</v>
+        <v>1091</v>
       </c>
       <c r="O478" s="2"/>
       <c r="P478" s="2"/>
@@ -56072,7 +56082,7 @@
         <v>23</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>76</v>
@@ -56089,13 +56099,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56121,10 +56131,10 @@
         <v>813</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1091</v>
+        <v>1093</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -56175,7 +56185,7 @@
         <v>23</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1090</v>
+        <v>1092</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>76</v>
@@ -56192,13 +56202,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56224,10 +56234,10 @@
         <v>136</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1094</v>
+        <v>1096</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1095</v>
+        <v>1097</v>
       </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
@@ -56278,7 +56288,7 @@
         <v>23</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1093</v>
+        <v>1095</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
@@ -56295,13 +56305,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1096</v>
+        <v>1098</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56398,13 +56408,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1097</v>
+        <v>1099</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56503,13 +56513,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1098</v>
+        <v>1100</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56610,13 +56620,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -56642,14 +56652,14 @@
         <v>367</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1100</v>
+        <v>1102</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>1101</v>
+        <v>1103</v>
       </c>
       <c r="O484" s="2"/>
       <c r="P484" t="s" s="2">
-        <v>1102</v>
+        <v>1104</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>23</v>
@@ -56677,10 +56687,10 @@
         <v>372</v>
       </c>
       <c r="Z484" t="s" s="2">
-        <v>1103</v>
+        <v>1105</v>
       </c>
       <c r="AA484" t="s" s="2">
-        <v>1104</v>
+        <v>1106</v>
       </c>
       <c r="AB484" t="s" s="2">
         <v>23</v>
@@ -56698,7 +56708,7 @@
         <v>23</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1099</v>
+        <v>1101</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
@@ -56715,13 +56725,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -56747,10 +56757,10 @@
         <v>820</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1106</v>
+        <v>1108</v>
       </c>
       <c r="N485" t="s" s="2">
-        <v>1107</v>
+        <v>1109</v>
       </c>
       <c r="O485" s="2"/>
       <c r="P485" s="2"/>
@@ -56801,7 +56811,7 @@
         <v>23</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>1105</v>
+        <v>1107</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>83</v>
@@ -56818,13 +56828,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -56847,13 +56857,13 @@
         <v>23</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>1110</v>
+        <v>1112</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>1111</v>
+        <v>1113</v>
       </c>
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
@@ -56904,7 +56914,7 @@
         <v>23</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1108</v>
+        <v>1110</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>76</v>
@@ -56921,13 +56931,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56953,13 +56963,13 @@
         <v>950</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="O487" t="s" s="2">
-        <v>1115</v>
+        <v>1117</v>
       </c>
       <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
@@ -57009,7 +57019,7 @@
         <v>23</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -57026,13 +57036,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1116</v>
+        <v>1118</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -57058,10 +57068,10 @@
         <v>367</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>1117</v>
+        <v>1119</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="O488" s="2"/>
       <c r="P488" s="2"/>
@@ -57091,28 +57101,28 @@
         <v>372</v>
       </c>
       <c r="Z488" t="s" s="2">
+        <v>1120</v>
+      </c>
+      <c r="AA488" t="s" s="2">
+        <v>1121</v>
+      </c>
+      <c r="AB488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG488" t="s" s="2">
         <v>1118</v>
-      </c>
-      <c r="AA488" t="s" s="2">
-        <v>1119</v>
-      </c>
-      <c r="AB488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG488" t="s" s="2">
-        <v>1116</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
@@ -57129,13 +57139,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -57161,10 +57171,10 @@
         <v>497</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1121</v>
+        <v>1123</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="O489" s="2"/>
       <c r="P489" s="2"/>
@@ -57215,7 +57225,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1120</v>
+        <v>1122</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57232,13 +57242,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -57264,10 +57274,10 @@
         <v>497</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1125</v>
+        <v>1127</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -57318,7 +57328,7 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -57335,13 +57345,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57367,10 +57377,10 @@
         <v>578</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1127</v>
+        <v>1129</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1128</v>
+        <v>1130</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -57421,7 +57431,7 @@
         <v>23</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1126</v>
+        <v>1128</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
@@ -57438,13 +57448,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57470,10 +57480,10 @@
         <v>578</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1130</v>
+        <v>1132</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1131</v>
+        <v>1133</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57524,7 +57534,7 @@
         <v>23</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1129</v>
+        <v>1131</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57541,13 +57551,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57570,13 +57580,13 @@
         <v>23</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>1109</v>
+        <v>1111</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1133</v>
+        <v>1135</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1134</v>
+        <v>1136</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
@@ -57627,7 +57637,7 @@
         <v>23</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1132</v>
+        <v>1134</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -57644,13 +57654,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57673,13 +57683,13 @@
         <v>23</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1136</v>
+        <v>1138</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1137</v>
+        <v>1139</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1138</v>
+        <v>1140</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
@@ -57730,7 +57740,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1135</v>
+        <v>1137</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -57747,13 +57757,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57779,10 +57789,10 @@
         <v>598</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
@@ -57833,7 +57843,7 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
@@ -57850,13 +57860,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -57879,16 +57889,16 @@
         <v>23</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>1143</v>
+        <v>1145</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1144</v>
+        <v>1146</v>
       </c>
       <c r="N496" t="s" s="2">
         <v>877</v>
       </c>
       <c r="O496" t="s" s="2">
-        <v>1145</v>
+        <v>1147</v>
       </c>
       <c r="P496" s="2"/>
       <c r="Q496" t="s" s="2">
@@ -57938,7 +57948,7 @@
         <v>23</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1142</v>
+        <v>1144</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -57955,13 +57965,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -57987,10 +57997,10 @@
         <v>136</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1147</v>
+        <v>1149</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="O497" s="2"/>
       <c r="P497" s="2"/>
@@ -58041,7 +58051,7 @@
         <v>23</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
@@ -58058,13 +58068,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1149</v>
+        <v>1151</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58161,13 +58171,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1150</v>
+        <v>1152</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -58266,13 +58276,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1151</v>
+        <v>1153</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -58373,13 +58383,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -58405,10 +58415,10 @@
         <v>385</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1153</v>
+        <v>1155</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1154</v>
+        <v>1156</v>
       </c>
       <c r="O501" s="2"/>
       <c r="P501" s="2"/>
@@ -58459,7 +58469,7 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1152</v>
+        <v>1154</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>83</v>
@@ -58476,13 +58486,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58508,10 +58518,10 @@
         <v>367</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1156</v>
+        <v>1158</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1157</v>
+        <v>1159</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -58541,7 +58551,7 @@
         <v>372</v>
       </c>
       <c r="Z502" t="s" s="2">
-        <v>1158</v>
+        <v>1160</v>
       </c>
       <c r="AA502" t="s" s="2">
         <v>943</v>
@@ -58562,7 +58572,7 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1155</v>
+        <v>1157</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>76</v>
@@ -58579,13 +58589,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58611,10 +58621,10 @@
         <v>367</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1160</v>
+        <v>1162</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -58665,7 +58675,7 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1159</v>
+        <v>1161</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
@@ -58682,13 +58692,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58714,10 +58724,10 @@
         <v>833</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1164</v>
+        <v>1166</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" s="2"/>
@@ -58768,7 +58778,7 @@
         <v>23</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -58785,13 +58795,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58817,10 +58827,10 @@
         <v>955</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1166</v>
+        <v>1168</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1167</v>
+        <v>1169</v>
       </c>
       <c r="O505" t="s" s="2">
         <v>958</v>
@@ -58873,7 +58883,7 @@
         <v>23</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1165</v>
+        <v>1167</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -58890,13 +58900,13 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1029</v>
+        <v>1031</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
@@ -58922,13 +58932,13 @@
         <v>960</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1169</v>
+        <v>1171</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1170</v>
+        <v>1172</v>
       </c>
       <c r="O506" t="s" s="2">
-        <v>1171</v>
+        <v>1173</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -58978,7 +58988,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1168</v>
+        <v>1170</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -58995,13 +59005,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59027,10 +59037,10 @@
         <v>78</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1179</v>
+        <v>1181</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1180</v>
+        <v>1182</v>
       </c>
       <c r="O507" s="2"/>
       <c r="P507" s="2"/>
@@ -59081,7 +59091,7 @@
         <v>23</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1177</v>
+        <v>1179</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59098,13 +59108,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1181</v>
+        <v>1183</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59203,13 +59213,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1182</v>
+        <v>1184</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59306,13 +59316,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59411,13 +59421,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1184</v>
+        <v>1186</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59516,13 +59526,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1185</v>
+        <v>1187</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59621,13 +59631,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1186</v>
+        <v>1188</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59726,13 +59736,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1187</v>
+        <v>1189</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59831,13 +59841,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1188</v>
+        <v>1190</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59938,13 +59948,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -59970,13 +59980,13 @@
         <v>112</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1190</v>
+        <v>1192</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>1191</v>
+        <v>1193</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>1192</v>
+        <v>1194</v>
       </c>
       <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
@@ -60026,7 +60036,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -60043,13 +60053,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1193</v>
+        <v>1195</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60075,10 +60085,10 @@
         <v>103</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1194</v>
+        <v>1196</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="O517" s="2"/>
       <c r="P517" s="2"/>
@@ -60108,28 +60118,28 @@
         <v>121</v>
       </c>
       <c r="Z517" t="s" s="2">
+        <v>1197</v>
+      </c>
+      <c r="AA517" t="s" s="2">
+        <v>1198</v>
+      </c>
+      <c r="AB517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG517" t="s" s="2">
         <v>1195</v>
-      </c>
-      <c r="AA517" t="s" s="2">
-        <v>1196</v>
-      </c>
-      <c r="AB517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG517" t="s" s="2">
-        <v>1193</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
@@ -60146,13 +60156,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60178,13 +60188,13 @@
         <v>367</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>1198</v>
+        <v>1200</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="O518" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
@@ -60210,13 +60220,13 @@
         <v>23</v>
       </c>
       <c r="Y518" t="s" s="2">
-        <v>1201</v>
+        <v>1203</v>
       </c>
       <c r="Z518" t="s" s="2">
-        <v>1202</v>
+        <v>1204</v>
       </c>
       <c r="AA518" t="s" s="2">
-        <v>1203</v>
+        <v>1205</v>
       </c>
       <c r="AB518" t="s" s="2">
         <v>23</v>
@@ -60234,7 +60244,7 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1197</v>
+        <v>1199</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
@@ -60251,13 +60261,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60283,13 +60293,13 @@
         <v>367</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1205</v>
+        <v>1207</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1206</v>
+        <v>1208</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>1207</v>
+        <v>1209</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60318,10 +60328,10 @@
         <v>372</v>
       </c>
       <c r="Z519" t="s" s="2">
-        <v>1208</v>
+        <v>1210</v>
       </c>
       <c r="AA519" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="AB519" t="s" s="2">
         <v>23</v>
@@ -60339,7 +60349,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1204</v>
+        <v>1206</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>83</v>
@@ -60356,13 +60366,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60388,10 +60398,10 @@
         <v>141</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1211</v>
+        <v>1213</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1212</v>
+        <v>1214</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -60442,7 +60452,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1210</v>
+        <v>1212</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -60459,13 +60469,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60491,10 +60501,10 @@
         <v>136</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1214</v>
+        <v>1216</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1215</v>
+        <v>1217</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -60502,7 +60512,7 @@
         <v>23</v>
       </c>
       <c r="R521" t="s" s="2">
-        <v>1216</v>
+        <v>1218</v>
       </c>
       <c r="S521" t="s" s="2">
         <v>23</v>
@@ -60547,7 +60557,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1213</v>
+        <v>1215</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -60564,13 +60574,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1217</v>
+        <v>1219</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60667,13 +60677,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1218</v>
+        <v>1220</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60772,13 +60782,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60879,13 +60889,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -60911,10 +60921,10 @@
         <v>112</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1221</v>
+        <v>1223</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>1222</v>
+        <v>1224</v>
       </c>
       <c r="O525" s="2"/>
       <c r="P525" s="2"/>
@@ -60965,7 +60975,7 @@
         <v>23</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1220</v>
+        <v>1222</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
@@ -60982,13 +60992,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61014,10 +61024,10 @@
         <v>578</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1224</v>
+        <v>1226</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" s="2"/>
@@ -61068,7 +61078,7 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1223</v>
+        <v>1225</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61085,13 +61095,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61117,10 +61127,10 @@
         <v>497</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1227</v>
+        <v>1229</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1228</v>
+        <v>1230</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -61171,7 +61181,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1226</v>
+        <v>1228</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61188,13 +61198,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61220,10 +61230,10 @@
         <v>136</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1230</v>
+        <v>1232</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1231</v>
+        <v>1233</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61274,7 +61284,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1229</v>
+        <v>1231</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61291,13 +61301,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1232</v>
+        <v>1234</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61394,13 +61404,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1233</v>
+        <v>1235</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61499,13 +61509,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1234</v>
+        <v>1236</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61606,13 +61616,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61638,10 +61648,10 @@
         <v>491</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1236</v>
+        <v>1238</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1237</v>
+        <v>1239</v>
       </c>
       <c r="O532" s="2"/>
       <c r="P532" s="2"/>
@@ -61692,7 +61702,7 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1235</v>
+        <v>1237</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
@@ -61709,13 +61719,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1172</v>
+        <v>1174</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61738,13 +61748,13 @@
         <v>84</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>1239</v>
+        <v>1241</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1240</v>
+        <v>1242</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1241</v>
+        <v>1243</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -61774,10 +61784,10 @@
         <v>372</v>
       </c>
       <c r="Z533" t="s" s="2">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="AA533" t="s" s="2">
-        <v>1209</v>
+        <v>1211</v>
       </c>
       <c r="AB533" t="s" s="2">
         <v>23</v>
@@ -61795,7 +61805,7 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1238</v>
+        <v>1240</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>83</v>
@@ -61812,13 +61822,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61844,13 +61854,13 @@
         <v>78</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>1249</v>
+        <v>1251</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>1250</v>
+        <v>1252</v>
       </c>
       <c r="O534" t="s" s="2">
-        <v>1251</v>
+        <v>1253</v>
       </c>
       <c r="P534" s="2"/>
       <c r="Q534" t="s" s="2">
@@ -61900,7 +61910,7 @@
         <v>23</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1247</v>
+        <v>1249</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>76</v>
@@ -61917,13 +61927,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1252</v>
+        <v>1254</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -62020,13 +62030,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1253</v>
+        <v>1255</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62125,13 +62135,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1254</v>
+        <v>1256</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62232,13 +62242,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62264,14 +62274,14 @@
         <v>578</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1256</v>
+        <v>1258</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1257</v>
+        <v>1259</v>
       </c>
       <c r="O538" s="2"/>
       <c r="P538" t="s" s="2">
-        <v>1258</v>
+        <v>1260</v>
       </c>
       <c r="Q538" t="s" s="2">
         <v>23</v>
@@ -62320,7 +62330,7 @@
         <v>23</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1255</v>
+        <v>1257</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
@@ -62337,13 +62347,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62369,14 +62379,14 @@
         <v>418</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1260</v>
+        <v>1262</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" t="s" s="2">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>23</v>
@@ -62425,7 +62435,7 @@
         <v>23</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1259</v>
+        <v>1261</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
@@ -62437,18 +62447,18 @@
         <v>23</v>
       </c>
       <c r="AK539" t="s" s="2">
-        <v>1263</v>
+        <v>1265</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62545,13 +62555,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1265</v>
+        <v>1267</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62650,13 +62660,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62679,13 +62689,13 @@
         <v>84</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>1267</v>
+        <v>1269</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="O542" s="2"/>
       <c r="P542" s="2"/>
@@ -62734,7 +62744,7 @@
         <v>355</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
@@ -62751,16 +62761,16 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1270</v>
+        <v>1272</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="D543" t="s" s="2">
-        <v>1271</v>
+        <v>1273</v>
       </c>
       <c r="E543" t="s" s="2">
         <v>23</v>
@@ -62785,10 +62795,10 @@
         <v>903</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1268</v>
+        <v>1270</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1269</v>
+        <v>1271</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -62839,7 +62849,7 @@
         <v>23</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -62856,13 +62866,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1273</v>
+        <v>1275</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -62959,13 +62969,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1274</v>
+        <v>1276</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1275</v>
+        <v>1277</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63064,13 +63074,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1276</v>
+        <v>1278</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63096,13 +63106,13 @@
         <v>578</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>1278</v>
+        <v>1280</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>1279</v>
+        <v>1281</v>
       </c>
       <c r="O546" t="s" s="2">
-        <v>1280</v>
+        <v>1282</v>
       </c>
       <c r="P546" s="2"/>
       <c r="Q546" t="s" s="2">
@@ -63152,7 +63162,7 @@
         <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1281</v>
+        <v>1283</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -63161,7 +63171,7 @@
         <v>83</v>
       </c>
       <c r="AJ546" t="s" s="2">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="AK546" t="s" s="2">
         <v>95</v>
@@ -63169,13 +63179,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1283</v>
+        <v>1285</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1284</v>
+        <v>1286</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63201,20 +63211,20 @@
         <v>578</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>1285</v>
+        <v>1287</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>1286</v>
+        <v>1288</v>
       </c>
       <c r="O547" t="s" s="2">
-        <v>1287</v>
+        <v>1289</v>
       </c>
       <c r="P547" s="2"/>
       <c r="Q547" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R547" t="s" s="2">
-        <v>1288</v>
+        <v>1290</v>
       </c>
       <c r="S547" t="s" s="2">
         <v>23</v>
@@ -63259,7 +63269,7 @@
         <v>23</v>
       </c>
       <c r="AG547" t="s" s="2">
-        <v>1289</v>
+        <v>1291</v>
       </c>
       <c r="AH547" t="s" s="2">
         <v>76</v>
@@ -63268,7 +63278,7 @@
         <v>83</v>
       </c>
       <c r="AJ547" t="s" s="2">
-        <v>1282</v>
+        <v>1284</v>
       </c>
       <c r="AK547" t="s" s="2">
         <v>95</v>
@@ -63276,13 +63286,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63305,19 +63315,19 @@
         <v>84</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M548" t="s" s="2">
-        <v>1292</v>
+        <v>1294</v>
       </c>
       <c r="N548" t="s" s="2">
-        <v>1293</v>
+        <v>1295</v>
       </c>
       <c r="O548" t="s" s="2">
-        <v>1294</v>
+        <v>1296</v>
       </c>
       <c r="P548" t="s" s="2">
-        <v>1295</v>
+        <v>1297</v>
       </c>
       <c r="Q548" t="s" s="2">
         <v>23</v>
@@ -63366,7 +63376,7 @@
         <v>23</v>
       </c>
       <c r="AG548" t="s" s="2">
-        <v>1290</v>
+        <v>1292</v>
       </c>
       <c r="AH548" t="s" s="2">
         <v>76</v>
@@ -63383,13 +63393,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63412,13 +63422,13 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1297</v>
+        <v>1299</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1298</v>
+        <v>1300</v>
       </c>
       <c r="O549" s="2"/>
       <c r="P549" s="2"/>
@@ -63469,7 +63479,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1296</v>
+        <v>1298</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63486,13 +63496,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63518,16 +63528,16 @@
         <v>199</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1300</v>
+        <v>1302</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1301</v>
+        <v>1303</v>
       </c>
       <c r="O550" t="s" s="2">
-        <v>1302</v>
+        <v>1304</v>
       </c>
       <c r="P550" t="s" s="2">
-        <v>1303</v>
+        <v>1305</v>
       </c>
       <c r="Q550" t="s" s="2">
         <v>23</v>
@@ -63576,7 +63586,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1299</v>
+        <v>1301</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63593,13 +63603,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63625,16 +63635,16 @@
         <v>199</v>
       </c>
       <c r="M551" t="s" s="2">
+        <v>1307</v>
+      </c>
+      <c r="N551" t="s" s="2">
+        <v>1308</v>
+      </c>
+      <c r="O551" t="s" s="2">
+        <v>1304</v>
+      </c>
+      <c r="P551" t="s" s="2">
         <v>1305</v>
-      </c>
-      <c r="N551" t="s" s="2">
-        <v>1306</v>
-      </c>
-      <c r="O551" t="s" s="2">
-        <v>1302</v>
-      </c>
-      <c r="P551" t="s" s="2">
-        <v>1303</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63683,7 +63693,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1304</v>
+        <v>1306</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63700,13 +63710,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63732,10 +63742,10 @@
         <v>103</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>1308</v>
+        <v>1310</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1309</v>
+        <v>1311</v>
       </c>
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
@@ -63765,10 +63775,10 @@
         <v>121</v>
       </c>
       <c r="Z552" t="s" s="2">
-        <v>1310</v>
+        <v>1312</v>
       </c>
       <c r="AA552" t="s" s="2">
-        <v>1311</v>
+        <v>1313</v>
       </c>
       <c r="AB552" t="s" s="2">
         <v>23</v>
@@ -63786,7 +63796,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1307</v>
+        <v>1309</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63803,13 +63813,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63832,13 +63842,13 @@
         <v>84</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1313</v>
+        <v>1315</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1314</v>
+        <v>1316</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
@@ -63846,7 +63856,7 @@
         <v>23</v>
       </c>
       <c r="R553" t="s" s="2">
-        <v>1315</v>
+        <v>1317</v>
       </c>
       <c r="S553" t="s" s="2">
         <v>23</v>
@@ -63891,7 +63901,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1312</v>
+        <v>1314</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63908,13 +63918,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63937,13 +63947,13 @@
         <v>84</v>
       </c>
       <c r="L554" t="s" s="2">
-        <v>1291</v>
+        <v>1293</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1317</v>
+        <v>1319</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="O554" s="2"/>
       <c r="P554" s="2"/>
@@ -63994,7 +64004,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1316</v>
+        <v>1318</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64011,13 +64021,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64043,10 +64053,10 @@
         <v>199</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1321</v>
+        <v>1323</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64097,7 +64107,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64114,13 +64124,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64146,10 +64156,10 @@
         <v>199</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1323</v>
+        <v>1325</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1324</v>
+        <v>1326</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64200,7 +64210,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1322</v>
+        <v>1324</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64217,13 +64227,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64249,10 +64259,10 @@
         <v>103</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1326</v>
+        <v>1328</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1327</v>
+        <v>1329</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64283,7 +64293,7 @@
       </c>
       <c r="Z557" s="2"/>
       <c r="AA557" t="s" s="2">
-        <v>1328</v>
+        <v>1330</v>
       </c>
       <c r="AB557" t="s" s="2">
         <v>23</v>
@@ -64301,7 +64311,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1325</v>
+        <v>1327</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64318,13 +64328,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64350,13 +64360,13 @@
         <v>103</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1330</v>
+        <v>1332</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="O558" t="s" s="2">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="P558" s="2"/>
       <c r="Q558" t="s" s="2">
@@ -64386,7 +64396,7 @@
       </c>
       <c r="Z558" s="2"/>
       <c r="AA558" t="s" s="2">
-        <v>1333</v>
+        <v>1335</v>
       </c>
       <c r="AB558" t="s" s="2">
         <v>23</v>
@@ -64404,7 +64414,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1329</v>
+        <v>1331</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64421,13 +64431,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64450,16 +64460,16 @@
         <v>84</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1335</v>
+        <v>1337</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1336</v>
+        <v>1338</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1337</v>
+        <v>1339</v>
       </c>
       <c r="O559" t="s" s="2">
-        <v>1338</v>
+        <v>1340</v>
       </c>
       <c r="P559" s="2"/>
       <c r="Q559" t="s" s="2">
@@ -64509,7 +64519,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1334</v>
+        <v>1336</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64526,13 +64536,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64558,16 +64568,16 @@
         <v>103</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1340</v>
+        <v>1342</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1341</v>
+        <v>1343</v>
       </c>
       <c r="O560" t="s" s="2">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="P560" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="Q560" t="s" s="2">
         <v>23</v>
@@ -64596,7 +64606,7 @@
       </c>
       <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>1344</v>
+        <v>1346</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64614,7 +64624,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1339</v>
+        <v>1341</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64631,13 +64641,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64663,10 +64673,10 @@
         <v>130</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1346</v>
+        <v>1348</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1347</v>
+        <v>1349</v>
       </c>
       <c r="O561" s="2"/>
       <c r="P561" s="2"/>
@@ -64717,7 +64727,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1345</v>
+        <v>1347</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64734,13 +64744,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64766,13 +64776,13 @@
         <v>367</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1349</v>
+        <v>1351</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1350</v>
+        <v>1352</v>
       </c>
       <c r="O562" t="s" s="2">
-        <v>1351</v>
+        <v>1353</v>
       </c>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
@@ -64801,10 +64811,10 @@
         <v>107</v>
       </c>
       <c r="Z562" t="s" s="2">
-        <v>1352</v>
+        <v>1354</v>
       </c>
       <c r="AA562" t="s" s="2">
-        <v>1353</v>
+        <v>1355</v>
       </c>
       <c r="AB562" t="s" s="2">
         <v>23</v>
@@ -64822,7 +64832,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1348</v>
+        <v>1350</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-13T14:40:49+00:00</t>
+    <t>2026-05-15T11:09:11+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18832" uniqueCount="1356">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18866" uniqueCount="1362">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-15T11:09:11+00:00</t>
+    <t>2026-05-22T12:28:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3279,15 +3279,15 @@
     <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medikationdispense-durchgefuehrteAbgabe</t>
   </si>
   <si>
-    <t>AtElgaEmedMedicationRequestDurchgefuehrteAbgabe</t>
+    <t>AtElgaEmedMedicationDispenseDurchgefuehrteAbgabe</t>
   </si>
   <si>
     <t>AT ELGA e-Medikation MedicationDispense Durchgeführte Abgabe</t>
   </si>
   <si>
     <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
-In der durchgeführten Abgabe können Abweichungen hinsichtlich der Dosierung des Medikaments dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Einer mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
+Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
   </si>
   <si>
     <t>MedicationDispense</t>
@@ -3330,13 +3330,33 @@
     <t>MedicationDispense.extension:renderedDosageInstruction</t>
   </si>
   <si>
+    <t>MedicationDispense.extension:recorded</t>
+  </si>
+  <si>
+    <t>recorded</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Extension {http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationDispense.recorded}
+</t>
+  </si>
+  <si>
+    <t>Datum und Uhrzeit, zu denen die Abgabe erfasst wurde. Dies muss nicht unbedingt mit dem Zeitpunkt übereinstimmen, zu dem das Medikament dem Patienten ausgehändigt wurde (z.B. bei Nacherfassung der Abgabe).</t>
+  </si>
+  <si>
+    <t>R5: `MedicationDispense.recorded` (new:dateTime)</t>
+  </si>
+  <si>
+    <t>Element `MedicationDispense.recorded` has a context of MedicationDispense based on following the parent source element upwards and mapping to `MedicationDispense`.
+Element `MedicationDispense.recorded` has no mapping targets in FHIR R4. Typically, this is because the element has been added (is a new element).</t>
+  </si>
+  <si>
     <t>MedicationDispense.modifierExtension</t>
   </si>
   <si>
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID.</t>
+    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -5781,7 +5801,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="179">
@@ -5789,7 +5809,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1175</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="180">
@@ -5805,7 +5825,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1176</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="182">
@@ -5813,7 +5833,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1177</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="183">
@@ -5875,7 +5895,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1178</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="191">
@@ -5911,7 +5931,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1179</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="196">
@@ -5919,7 +5939,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1180</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="197">
@@ -5951,7 +5971,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="201">
@@ -5959,7 +5979,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1246</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="202">
@@ -5975,7 +5995,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1247</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="204">
@@ -5983,7 +6003,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1248</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="205">
@@ -6045,7 +6065,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1248</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="213">
@@ -6081,7 +6101,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1249</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="218">
@@ -6089,7 +6109,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1250</v>
+        <v>1256</v>
       </c>
     </row>
     <row r="219">
@@ -6115,7 +6135,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK562"/>
+  <dimension ref="A1:AK563"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
     <col min="1" max="1" width="46.59375" customWidth="true" bestFit="true"/>
@@ -47983,7 +48003,7 @@
         <v>83</v>
       </c>
       <c r="I401" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J401" t="s" s="2">
         <v>23</v>
@@ -48191,7 +48211,7 @@
         <v>83</v>
       </c>
       <c r="I403" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J403" t="s" s="2">
         <v>23</v>
@@ -54756,7 +54776,7 @@
       </c>
       <c r="F466" s="2"/>
       <c r="G466" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H466" t="s" s="2">
         <v>77</v>
@@ -54956,43 +54976,43 @@
         <v>1049</v>
       </c>
       <c r="C468" t="s" s="2">
-        <v>1049</v>
-      </c>
-      <c r="D468" s="2"/>
+        <v>1047</v>
+      </c>
+      <c r="D468" t="s" s="2">
+        <v>1050</v>
+      </c>
       <c r="E468" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F468" s="2"/>
       <c r="G468" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H468" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I468" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J468" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K468" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L468" t="s" s="2">
-        <v>147</v>
+        <v>1051</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>535</v>
+        <v>1052</v>
       </c>
       <c r="N468" t="s" s="2">
-        <v>536</v>
+        <v>1053</v>
       </c>
       <c r="O468" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P468" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>1054</v>
+      </c>
+      <c r="P468" s="2"/>
       <c r="Q468" t="s" s="2">
         <v>23</v>
       </c>
@@ -55040,7 +55060,7 @@
         <v>23</v>
       </c>
       <c r="AG468" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AH468" t="s" s="2">
         <v>76</v>
@@ -55049,7 +55069,7 @@
         <v>77</v>
       </c>
       <c r="AJ468" t="s" s="2">
-        <v>23</v>
+        <v>740</v>
       </c>
       <c r="AK468" t="s" s="2">
         <v>152</v>
@@ -55060,44 +55080,46 @@
         <v>1031</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1050</v>
+        <v>1055</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F469" s="2"/>
       <c r="G469" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H469" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I469" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J469" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K469" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L469" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1051</v>
+        <v>535</v>
       </c>
       <c r="N469" t="s" s="2">
-        <v>1052</v>
+        <v>536</v>
       </c>
       <c r="O469" t="s" s="2">
-        <v>751</v>
-      </c>
-      <c r="P469" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="P469" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q469" t="s" s="2">
         <v>23</v>
       </c>
@@ -55145,7 +55167,7 @@
         <v>23</v>
       </c>
       <c r="AG469" t="s" s="2">
-        <v>1050</v>
+        <v>537</v>
       </c>
       <c r="AH469" t="s" s="2">
         <v>76</v>
@@ -55157,7 +55179,7 @@
         <v>23</v>
       </c>
       <c r="AK469" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="470">
@@ -55165,10 +55187,10 @@
         <v>1031</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -55191,15 +55213,17 @@
         <v>23</v>
       </c>
       <c r="L470" t="s" s="2">
-        <v>1054</v>
+        <v>112</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1055</v>
+        <v>1057</v>
       </c>
       <c r="N470" t="s" s="2">
-        <v>1056</v>
-      </c>
-      <c r="O470" s="2"/>
+        <v>1058</v>
+      </c>
+      <c r="O470" t="s" s="2">
+        <v>751</v>
+      </c>
       <c r="P470" s="2"/>
       <c r="Q470" t="s" s="2">
         <v>23</v>
@@ -55248,7 +55272,7 @@
         <v>23</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>1053</v>
+        <v>1056</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -55268,10 +55292,10 @@
         <v>1031</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55279,32 +55303,30 @@
       </c>
       <c r="F471" s="2"/>
       <c r="G471" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H471" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I471" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J471" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K471" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L471" t="s" s="2">
-        <v>103</v>
+        <v>1060</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1058</v>
+        <v>1061</v>
       </c>
       <c r="N471" t="s" s="2">
-        <v>1059</v>
-      </c>
-      <c r="O471" t="s" s="2">
-        <v>544</v>
-      </c>
+        <v>1062</v>
+      </c>
+      <c r="O471" s="2"/>
       <c r="P471" s="2"/>
       <c r="Q471" t="s" s="2">
         <v>23</v>
@@ -55329,13 +55351,13 @@
         <v>23</v>
       </c>
       <c r="Y471" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z471" t="s" s="2">
-        <v>1060</v>
+        <v>23</v>
       </c>
       <c r="AA471" t="s" s="2">
-        <v>1061</v>
+        <v>23</v>
       </c>
       <c r="AB471" t="s" s="2">
         <v>23</v>
@@ -55353,13 +55375,13 @@
         <v>23</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1057</v>
+        <v>1059</v>
       </c>
       <c r="AH471" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI471" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ471" t="s" s="2">
         <v>23</v>
@@ -55373,10 +55395,10 @@
         <v>1031</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -55384,30 +55406,32 @@
       </c>
       <c r="F472" s="2"/>
       <c r="G472" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H472" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I472" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J472" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K472" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L472" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1063</v>
+        <v>1064</v>
       </c>
       <c r="N472" t="s" s="2">
-        <v>1064</v>
-      </c>
-      <c r="O472" s="2"/>
+        <v>1065</v>
+      </c>
+      <c r="O472" t="s" s="2">
+        <v>544</v>
+      </c>
       <c r="P472" s="2"/>
       <c r="Q472" t="s" s="2">
         <v>23</v>
@@ -55432,32 +55456,34 @@
         <v>23</v>
       </c>
       <c r="Y472" t="s" s="2">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="Z472" t="s" s="2">
-        <v>1065</v>
+        <v>1066</v>
       </c>
       <c r="AA472" t="s" s="2">
-        <v>1066</v>
+        <v>1067</v>
       </c>
       <c r="AB472" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC472" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AD472" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="AD472" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AE472" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF472" t="s" s="2">
-        <v>169</v>
+        <v>23</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1062</v>
+        <v>1063</v>
       </c>
       <c r="AH472" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI472" t="s" s="2">
         <v>83</v>
@@ -55474,14 +55500,12 @@
         <v>1031</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1067</v>
+        <v>1068</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1062</v>
-      </c>
-      <c r="D473" t="s" s="2">
         <v>1068</v>
       </c>
+      <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
         <v>23</v>
       </c>
@@ -55493,7 +55517,7 @@
         <v>83</v>
       </c>
       <c r="I473" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J473" t="s" s="2">
         <v>23</v>
@@ -55508,7 +55532,7 @@
         <v>1069</v>
       </c>
       <c r="N473" t="s" s="2">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="O473" s="2"/>
       <c r="P473" s="2"/>
@@ -55538,28 +55562,26 @@
         <v>372</v>
       </c>
       <c r="Z473" t="s" s="2">
-        <v>1065</v>
+        <v>1071</v>
       </c>
       <c r="AA473" t="s" s="2">
-        <v>1066</v>
+        <v>1072</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AC473" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD473" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AD473" s="2"/>
       <c r="AE473" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF473" t="s" s="2">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55579,13 +55601,13 @@
         <v>1031</v>
       </c>
       <c r="B474" t="s" s="2">
-        <v>1070</v>
+        <v>1073</v>
       </c>
       <c r="C474" t="s" s="2">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="D474" t="s" s="2">
-        <v>1071</v>
+        <v>1074</v>
       </c>
       <c r="E474" t="s" s="2">
         <v>23</v>
@@ -55595,10 +55617,10 @@
         <v>76</v>
       </c>
       <c r="H474" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I474" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J474" t="s" s="2">
         <v>23</v>
@@ -55607,13 +55629,13 @@
         <v>23</v>
       </c>
       <c r="L474" t="s" s="2">
-        <v>1072</v>
+        <v>367</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1073</v>
+        <v>1075</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1064</v>
+        <v>1070</v>
       </c>
       <c r="O474" s="2"/>
       <c r="P474" s="2"/>
@@ -55640,13 +55662,13 @@
         <v>23</v>
       </c>
       <c r="Y474" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z474" t="s" s="2">
-        <v>23</v>
+        <v>1071</v>
       </c>
       <c r="AA474" t="s" s="2">
-        <v>23</v>
+        <v>1072</v>
       </c>
       <c r="AB474" t="s" s="2">
         <v>23</v>
@@ -55664,7 +55686,7 @@
         <v>23</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1062</v>
+        <v>1068</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -55684,12 +55706,14 @@
         <v>1031</v>
       </c>
       <c r="B475" t="s" s="2">
-        <v>1074</v>
+        <v>1076</v>
       </c>
       <c r="C475" t="s" s="2">
-        <v>1074</v>
-      </c>
-      <c r="D475" s="2"/>
+        <v>1068</v>
+      </c>
+      <c r="D475" t="s" s="2">
+        <v>1077</v>
+      </c>
       <c r="E475" t="s" s="2">
         <v>23</v>
       </c>
@@ -55710,17 +55734,15 @@
         <v>23</v>
       </c>
       <c r="L475" t="s" s="2">
-        <v>367</v>
+        <v>1078</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1075</v>
+        <v>1079</v>
       </c>
       <c r="N475" t="s" s="2">
-        <v>1076</v>
-      </c>
-      <c r="O475" t="s" s="2">
-        <v>1077</v>
-      </c>
+        <v>1070</v>
+      </c>
+      <c r="O475" s="2"/>
       <c r="P475" s="2"/>
       <c r="Q475" t="s" s="2">
         <v>23</v>
@@ -55745,13 +55767,13 @@
         <v>23</v>
       </c>
       <c r="Y475" t="s" s="2">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="Z475" t="s" s="2">
-        <v>1078</v>
+        <v>23</v>
       </c>
       <c r="AA475" t="s" s="2">
-        <v>1079</v>
+        <v>23</v>
       </c>
       <c r="AB475" t="s" s="2">
         <v>23</v>
@@ -55769,7 +55791,7 @@
         <v>23</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1074</v>
+        <v>1068</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -55800,22 +55822,22 @@
       </c>
       <c r="F476" s="2"/>
       <c r="G476" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H476" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I476" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J476" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K476" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L476" t="s" s="2">
-        <v>799</v>
+        <v>367</v>
       </c>
       <c r="M476" t="s" s="2">
         <v>1081</v>
@@ -55850,13 +55872,13 @@
         <v>23</v>
       </c>
       <c r="Y476" t="s" s="2">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Z476" t="s" s="2">
-        <v>23</v>
+        <v>1084</v>
       </c>
       <c r="AA476" t="s" s="2">
-        <v>23</v>
+        <v>1085</v>
       </c>
       <c r="AB476" t="s" s="2">
         <v>23</v>
@@ -55877,7 +55899,7 @@
         <v>1080</v>
       </c>
       <c r="AH476" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI476" t="s" s="2">
         <v>83</v>
@@ -55894,10 +55916,10 @@
         <v>1031</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -55920,16 +55942,16 @@
         <v>84</v>
       </c>
       <c r="L477" t="s" s="2">
-        <v>804</v>
+        <v>799</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1085</v>
+        <v>1087</v>
       </c>
       <c r="N477" t="s" s="2">
-        <v>1086</v>
+        <v>1088</v>
       </c>
       <c r="O477" t="s" s="2">
-        <v>1087</v>
+        <v>1089</v>
       </c>
       <c r="P477" s="2"/>
       <c r="Q477" t="s" s="2">
@@ -55979,10 +56001,10 @@
         <v>23</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1084</v>
+        <v>1086</v>
       </c>
       <c r="AH477" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI477" t="s" s="2">
         <v>83</v>
@@ -55999,10 +56021,10 @@
         <v>1031</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56010,30 +56032,32 @@
       </c>
       <c r="F478" s="2"/>
       <c r="G478" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H478" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I478" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J478" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K478" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>1089</v>
+        <v>804</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1090</v>
+        <v>1091</v>
       </c>
       <c r="N478" t="s" s="2">
-        <v>1091</v>
-      </c>
-      <c r="O478" s="2"/>
+        <v>1092</v>
+      </c>
+      <c r="O478" t="s" s="2">
+        <v>1093</v>
+      </c>
       <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
         <v>23</v>
@@ -56082,7 +56106,7 @@
         <v>23</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1088</v>
+        <v>1090</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>76</v>
@@ -56102,10 +56126,10 @@
         <v>1031</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56128,13 +56152,13 @@
         <v>23</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>813</v>
+        <v>1095</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1093</v>
+        <v>1096</v>
       </c>
       <c r="N479" t="s" s="2">
-        <v>1094</v>
+        <v>1097</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -56185,13 +56209,13 @@
         <v>23</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1092</v>
+        <v>1094</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI479" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ479" t="s" s="2">
         <v>23</v>
@@ -56205,10 +56229,10 @@
         <v>1031</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56216,13 +56240,13 @@
       </c>
       <c r="F480" s="2"/>
       <c r="G480" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H480" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I480" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J480" t="s" s="2">
         <v>23</v>
@@ -56231,13 +56255,13 @@
         <v>23</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>136</v>
+        <v>813</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1096</v>
+        <v>1099</v>
       </c>
       <c r="N480" t="s" s="2">
-        <v>1097</v>
+        <v>1100</v>
       </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
@@ -56288,7 +56312,7 @@
         <v>23</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1095</v>
+        <v>1098</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
@@ -56308,10 +56332,10 @@
         <v>1031</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1098</v>
+        <v>1101</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56319,13 +56343,13 @@
       </c>
       <c r="F481" s="2"/>
       <c r="G481" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H481" t="s" s="2">
         <v>83</v>
       </c>
       <c r="I481" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J481" t="s" s="2">
         <v>23</v>
@@ -56334,13 +56358,13 @@
         <v>23</v>
       </c>
       <c r="L481" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>142</v>
+        <v>1102</v>
       </c>
       <c r="N481" t="s" s="2">
-        <v>143</v>
+        <v>1103</v>
       </c>
       <c r="O481" s="2"/>
       <c r="P481" s="2"/>
@@ -56391,19 +56415,19 @@
         <v>23</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>144</v>
+        <v>1101</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI481" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ481" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK481" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="482">
@@ -56411,21 +56435,21 @@
         <v>1031</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1099</v>
+        <v>1104</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F482" s="2"/>
       <c r="G482" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H482" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I482" t="s" s="2">
         <v>23</v>
@@ -56437,17 +56461,15 @@
         <v>23</v>
       </c>
       <c r="L482" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N482" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O482" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O482" s="2"/>
       <c r="P482" s="2"/>
       <c r="Q482" t="s" s="2">
         <v>23</v>
@@ -56496,19 +56518,19 @@
         <v>23</v>
       </c>
       <c r="AG482" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH482" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI482" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ482" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK482" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="483">
@@ -56516,14 +56538,14 @@
         <v>1031</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1100</v>
+        <v>1105</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F483" s="2"/>
       <c r="G483" t="s" s="2">
@@ -56536,26 +56558,24 @@
         <v>23</v>
       </c>
       <c r="J483" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K483" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L483" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N483" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O483" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P483" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P483" s="2"/>
       <c r="Q483" t="s" s="2">
         <v>23</v>
       </c>
@@ -56603,7 +56623,7 @@
         <v>23</v>
       </c>
       <c r="AG483" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH483" t="s" s="2">
         <v>76</v>
@@ -56623,43 +56643,45 @@
         <v>1031</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1101</v>
+        <v>1106</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F484" s="2"/>
       <c r="G484" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H484" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I484" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J484" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K484" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L484" t="s" s="2">
-        <v>367</v>
+        <v>147</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1102</v>
+        <v>155</v>
       </c>
       <c r="N484" t="s" s="2">
-        <v>1103</v>
-      </c>
-      <c r="O484" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O484" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P484" t="s" s="2">
-        <v>1104</v>
+        <v>157</v>
       </c>
       <c r="Q484" t="s" s="2">
         <v>23</v>
@@ -56684,13 +56706,13 @@
         <v>23</v>
       </c>
       <c r="Y484" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z484" t="s" s="2">
-        <v>1105</v>
+        <v>23</v>
       </c>
       <c r="AA484" t="s" s="2">
-        <v>1106</v>
+        <v>23</v>
       </c>
       <c r="AB484" t="s" s="2">
         <v>23</v>
@@ -56708,19 +56730,19 @@
         <v>23</v>
       </c>
       <c r="AG484" t="s" s="2">
-        <v>1101</v>
+        <v>158</v>
       </c>
       <c r="AH484" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI484" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ484" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK484" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="485">
@@ -56739,13 +56761,13 @@
       </c>
       <c r="F485" s="2"/>
       <c r="G485" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H485" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I485" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J485" t="s" s="2">
         <v>23</v>
@@ -56754,7 +56776,7 @@
         <v>23</v>
       </c>
       <c r="L485" t="s" s="2">
-        <v>820</v>
+        <v>367</v>
       </c>
       <c r="M485" t="s" s="2">
         <v>1108</v>
@@ -56763,7 +56785,9 @@
         <v>1109</v>
       </c>
       <c r="O485" s="2"/>
-      <c r="P485" s="2"/>
+      <c r="P485" t="s" s="2">
+        <v>1110</v>
+      </c>
       <c r="Q485" t="s" s="2">
         <v>23</v>
       </c>
@@ -56787,13 +56811,13 @@
         <v>23</v>
       </c>
       <c r="Y485" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z485" t="s" s="2">
-        <v>23</v>
+        <v>1111</v>
       </c>
       <c r="AA485" t="s" s="2">
-        <v>23</v>
+        <v>1112</v>
       </c>
       <c r="AB485" t="s" s="2">
         <v>23</v>
@@ -56814,7 +56838,7 @@
         <v>1107</v>
       </c>
       <c r="AH485" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI485" t="s" s="2">
         <v>83</v>
@@ -56831,10 +56855,10 @@
         <v>1031</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -56842,13 +56866,13 @@
       </c>
       <c r="F486" s="2"/>
       <c r="G486" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H486" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I486" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J486" t="s" s="2">
         <v>23</v>
@@ -56857,13 +56881,13 @@
         <v>23</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>1111</v>
+        <v>820</v>
       </c>
       <c r="M486" t="s" s="2">
-        <v>1112</v>
+        <v>1114</v>
       </c>
       <c r="N486" t="s" s="2">
-        <v>1113</v>
+        <v>1115</v>
       </c>
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
@@ -56914,10 +56938,10 @@
         <v>23</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1110</v>
+        <v>1113</v>
       </c>
       <c r="AH486" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI486" t="s" s="2">
         <v>83</v>
@@ -56934,10 +56958,10 @@
         <v>1031</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56948,10 +56972,10 @@
         <v>76</v>
       </c>
       <c r="H487" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I487" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J487" t="s" s="2">
         <v>23</v>
@@ -56960,17 +56984,15 @@
         <v>23</v>
       </c>
       <c r="L487" t="s" s="2">
-        <v>950</v>
+        <v>1117</v>
       </c>
       <c r="M487" t="s" s="2">
-        <v>1115</v>
+        <v>1118</v>
       </c>
       <c r="N487" t="s" s="2">
-        <v>1116</v>
-      </c>
-      <c r="O487" t="s" s="2">
-        <v>1117</v>
-      </c>
+        <v>1119</v>
+      </c>
+      <c r="O487" s="2"/>
       <c r="P487" s="2"/>
       <c r="Q487" t="s" s="2">
         <v>23</v>
@@ -57019,13 +57041,13 @@
         <v>23</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1114</v>
+        <v>1116</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI487" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ487" t="s" s="2">
         <v>23</v>
@@ -57039,10 +57061,10 @@
         <v>1031</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1118</v>
+        <v>1120</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -57050,7 +57072,7 @@
       </c>
       <c r="F488" s="2"/>
       <c r="G488" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H488" t="s" s="2">
         <v>83</v>
@@ -57065,15 +57087,17 @@
         <v>23</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>367</v>
+        <v>950</v>
       </c>
       <c r="M488" t="s" s="2">
-        <v>1119</v>
+        <v>1121</v>
       </c>
       <c r="N488" t="s" s="2">
-        <v>1120</v>
-      </c>
-      <c r="O488" s="2"/>
+        <v>1122</v>
+      </c>
+      <c r="O488" t="s" s="2">
+        <v>1123</v>
+      </c>
       <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
         <v>23</v>
@@ -57098,37 +57122,37 @@
         <v>23</v>
       </c>
       <c r="Y488" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF488" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG488" t="s" s="2">
         <v>1120</v>
       </c>
-      <c r="AA488" t="s" s="2">
-        <v>1121</v>
-      </c>
-      <c r="AB488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG488" t="s" s="2">
-        <v>1118</v>
-      </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI488" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ488" t="s" s="2">
         <v>23</v>
@@ -57142,10 +57166,10 @@
         <v>1031</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -57168,13 +57192,13 @@
         <v>23</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1123</v>
+        <v>1125</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>1124</v>
+        <v>1126</v>
       </c>
       <c r="O489" s="2"/>
       <c r="P489" s="2"/>
@@ -57201,13 +57225,13 @@
         <v>23</v>
       </c>
       <c r="Y489" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z489" t="s" s="2">
-        <v>23</v>
+        <v>1126</v>
       </c>
       <c r="AA489" t="s" s="2">
-        <v>23</v>
+        <v>1127</v>
       </c>
       <c r="AB489" t="s" s="2">
         <v>23</v>
@@ -57225,7 +57249,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1122</v>
+        <v>1124</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57245,10 +57269,10 @@
         <v>1031</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -57256,13 +57280,13 @@
       </c>
       <c r="F490" s="2"/>
       <c r="G490" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H490" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I490" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J490" t="s" s="2">
         <v>23</v>
@@ -57274,10 +57298,10 @@
         <v>497</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1126</v>
+        <v>1129</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1127</v>
+        <v>1130</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -57328,7 +57352,7 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1125</v>
+        <v>1128</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -57348,10 +57372,10 @@
         <v>1031</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57371,16 +57395,16 @@
         <v>23</v>
       </c>
       <c r="K491" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>578</v>
+        <v>497</v>
       </c>
       <c r="M491" t="s" s="2">
-        <v>1129</v>
+        <v>1132</v>
       </c>
       <c r="N491" t="s" s="2">
-        <v>1130</v>
+        <v>1133</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -57431,7 +57455,7 @@
         <v>23</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1128</v>
+        <v>1131</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
@@ -57451,10 +57475,10 @@
         <v>1031</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57462,28 +57486,28 @@
       </c>
       <c r="F492" s="2"/>
       <c r="G492" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H492" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I492" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J492" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K492" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="J492" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="K492" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="L492" t="s" s="2">
         <v>578</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1132</v>
+        <v>1135</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1133</v>
+        <v>1136</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57534,7 +57558,7 @@
         <v>23</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1131</v>
+        <v>1134</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57554,10 +57578,10 @@
         <v>1031</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57565,13 +57589,13 @@
       </c>
       <c r="F493" s="2"/>
       <c r="G493" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H493" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I493" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J493" t="s" s="2">
         <v>23</v>
@@ -57580,13 +57604,13 @@
         <v>23</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>1111</v>
+        <v>578</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1135</v>
+        <v>1138</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1136</v>
+        <v>1139</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
@@ -57637,7 +57661,7 @@
         <v>23</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1134</v>
+        <v>1137</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -57657,10 +57681,10 @@
         <v>1031</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57683,13 +57707,13 @@
         <v>23</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1138</v>
+        <v>1117</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1139</v>
+        <v>1141</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1140</v>
+        <v>1142</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
@@ -57740,13 +57764,13 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1137</v>
+        <v>1140</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI494" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ494" t="s" s="2">
         <v>23</v>
@@ -57760,10 +57784,10 @@
         <v>1031</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57774,10 +57798,10 @@
         <v>76</v>
       </c>
       <c r="H495" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I495" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J495" t="s" s="2">
         <v>23</v>
@@ -57786,13 +57810,13 @@
         <v>23</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>598</v>
+        <v>1144</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1142</v>
+        <v>1145</v>
       </c>
       <c r="N495" t="s" s="2">
-        <v>1143</v>
+        <v>1146</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
@@ -57843,7 +57867,7 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1141</v>
+        <v>1143</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
@@ -57863,10 +57887,10 @@
         <v>1031</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -57889,17 +57913,15 @@
         <v>23</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>1145</v>
+        <v>598</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1146</v>
+        <v>1148</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O496" t="s" s="2">
-        <v>1147</v>
-      </c>
+        <v>1149</v>
+      </c>
+      <c r="O496" s="2"/>
       <c r="P496" s="2"/>
       <c r="Q496" t="s" s="2">
         <v>23</v>
@@ -57948,7 +57970,7 @@
         <v>23</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1144</v>
+        <v>1147</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -57968,10 +57990,10 @@
         <v>1031</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -57982,10 +58004,10 @@
         <v>76</v>
       </c>
       <c r="H497" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I497" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J497" t="s" s="2">
         <v>23</v>
@@ -57994,15 +58016,17 @@
         <v>23</v>
       </c>
       <c r="L497" t="s" s="2">
-        <v>136</v>
+        <v>1151</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1149</v>
+        <v>1152</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1150</v>
-      </c>
-      <c r="O497" s="2"/>
+        <v>877</v>
+      </c>
+      <c r="O497" t="s" s="2">
+        <v>1153</v>
+      </c>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
         <v>23</v>
@@ -58051,13 +58075,13 @@
         <v>23</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1148</v>
+        <v>1150</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI497" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ497" t="s" s="2">
         <v>23</v>
@@ -58071,10 +58095,10 @@
         <v>1031</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1151</v>
+        <v>1154</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58085,7 +58109,7 @@
         <v>76</v>
       </c>
       <c r="H498" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I498" t="s" s="2">
         <v>23</v>
@@ -58097,13 +58121,13 @@
         <v>23</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>142</v>
+        <v>1155</v>
       </c>
       <c r="N498" t="s" s="2">
-        <v>143</v>
+        <v>1156</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -58154,7 +58178,7 @@
         <v>23</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>144</v>
+        <v>1154</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -58166,7 +58190,7 @@
         <v>23</v>
       </c>
       <c r="AK498" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="499">
@@ -58174,21 +58198,21 @@
         <v>1031</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1152</v>
+        <v>1157</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F499" s="2"/>
       <c r="G499" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H499" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I499" t="s" s="2">
         <v>23</v>
@@ -58200,17 +58224,15 @@
         <v>23</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O499" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O499" s="2"/>
       <c r="P499" s="2"/>
       <c r="Q499" t="s" s="2">
         <v>23</v>
@@ -58259,19 +58281,19 @@
         <v>23</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI499" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ499" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK499" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="500">
@@ -58279,14 +58301,14 @@
         <v>1031</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1153</v>
+        <v>1158</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
@@ -58299,26 +58321,24 @@
         <v>23</v>
       </c>
       <c r="J500" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K500" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L500" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O500" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P500" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
         <v>23</v>
       </c>
@@ -58366,7 +58386,7 @@
         <v>23</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
@@ -58386,42 +58406,46 @@
         <v>1031</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1154</v>
+        <v>1159</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H501" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I501" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J501" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>385</v>
+        <v>147</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1155</v>
+        <v>155</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>1156</v>
-      </c>
-      <c r="O501" s="2"/>
-      <c r="P501" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O501" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P501" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q501" t="s" s="2">
         <v>23</v>
       </c>
@@ -58469,19 +58493,19 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>1154</v>
+        <v>158</v>
       </c>
       <c r="AH501" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI501" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ501" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK501" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="502">
@@ -58489,10 +58513,10 @@
         <v>1031</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58500,7 +58524,7 @@
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H502" t="s" s="2">
         <v>83</v>
@@ -58515,13 +58539,13 @@
         <v>23</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1158</v>
+        <v>1161</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1159</v>
+        <v>1162</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -58548,34 +58572,34 @@
         <v>23</v>
       </c>
       <c r="Y502" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF502" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG502" t="s" s="2">
         <v>1160</v>
       </c>
-      <c r="AA502" t="s" s="2">
-        <v>943</v>
-      </c>
-      <c r="AB502" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC502" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD502" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE502" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF502" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG502" t="s" s="2">
-        <v>1157</v>
-      </c>
       <c r="AH502" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI502" t="s" s="2">
         <v>83</v>
@@ -58592,10 +58616,10 @@
         <v>1031</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58606,7 +58630,7 @@
         <v>76</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I503" t="s" s="2">
         <v>23</v>
@@ -58621,10 +58645,10 @@
         <v>367</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1162</v>
+        <v>1164</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1163</v>
+        <v>1165</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -58654,10 +58678,10 @@
         <v>372</v>
       </c>
       <c r="Z503" t="s" s="2">
-        <v>947</v>
+        <v>1166</v>
       </c>
       <c r="AA503" t="s" s="2">
-        <v>948</v>
+        <v>943</v>
       </c>
       <c r="AB503" t="s" s="2">
         <v>23</v>
@@ -58675,13 +58699,13 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1161</v>
+        <v>1163</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ503" t="s" s="2">
         <v>23</v>
@@ -58695,10 +58719,10 @@
         <v>1031</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58721,13 +58745,13 @@
         <v>23</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>833</v>
+        <v>367</v>
       </c>
       <c r="M504" t="s" s="2">
-        <v>1165</v>
+        <v>1168</v>
       </c>
       <c r="N504" t="s" s="2">
-        <v>1166</v>
+        <v>1169</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" s="2"/>
@@ -58754,13 +58778,13 @@
         <v>23</v>
       </c>
       <c r="Y504" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z504" t="s" s="2">
-        <v>23</v>
+        <v>947</v>
       </c>
       <c r="AA504" t="s" s="2">
-        <v>23</v>
+        <v>948</v>
       </c>
       <c r="AB504" t="s" s="2">
         <v>23</v>
@@ -58778,7 +58802,7 @@
         <v>23</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1164</v>
+        <v>1167</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -58798,21 +58822,21 @@
         <v>1031</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
-        <v>954</v>
+        <v>23</v>
       </c>
       <c r="F505" s="2"/>
       <c r="G505" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H505" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I505" t="s" s="2">
         <v>23</v>
@@ -58824,17 +58848,15 @@
         <v>23</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>955</v>
+        <v>833</v>
       </c>
       <c r="M505" t="s" s="2">
-        <v>1168</v>
+        <v>1171</v>
       </c>
       <c r="N505" t="s" s="2">
-        <v>1169</v>
-      </c>
-      <c r="O505" t="s" s="2">
-        <v>958</v>
-      </c>
+        <v>1172</v>
+      </c>
+      <c r="O505" s="2"/>
       <c r="P505" s="2"/>
       <c r="Q505" t="s" s="2">
         <v>23</v>
@@ -58883,7 +58905,7 @@
         <v>23</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1167</v>
+        <v>1170</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -58903,14 +58925,14 @@
         <v>1031</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>23</v>
+        <v>954</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
@@ -58929,16 +58951,16 @@
         <v>23</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>960</v>
+        <v>955</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1171</v>
+        <v>1174</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1172</v>
+        <v>1175</v>
       </c>
       <c r="O506" t="s" s="2">
-        <v>1173</v>
+        <v>958</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -58988,7 +59010,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1170</v>
+        <v>1173</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59005,13 +59027,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1174</v>
+        <v>1031</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59022,7 +59044,7 @@
         <v>76</v>
       </c>
       <c r="H507" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I507" t="s" s="2">
         <v>23</v>
@@ -59034,15 +59056,17 @@
         <v>23</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>78</v>
+        <v>960</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1181</v>
+        <v>1177</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1182</v>
-      </c>
-      <c r="O507" s="2"/>
+        <v>1178</v>
+      </c>
+      <c r="O507" t="s" s="2">
+        <v>1179</v>
+      </c>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
         <v>23</v>
@@ -59091,7 +59115,7 @@
         <v>23</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1179</v>
+        <v>1176</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59103,18 +59127,18 @@
         <v>23</v>
       </c>
       <c r="AK507" t="s" s="2">
-        <v>645</v>
+        <v>95</v>
       </c>
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1183</v>
+        <v>1185</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59125,7 +59149,7 @@
         <v>76</v>
       </c>
       <c r="H508" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I508" t="s" s="2">
         <v>23</v>
@@ -59134,20 +59158,18 @@
         <v>23</v>
       </c>
       <c r="K508" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>85</v>
+        <v>78</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>86</v>
+        <v>1187</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>87</v>
-      </c>
-      <c r="O508" t="s" s="2">
-        <v>88</v>
-      </c>
+        <v>1188</v>
+      </c>
+      <c r="O508" s="2"/>
       <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
         <v>23</v>
@@ -59196,30 +59218,30 @@
         <v>23</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>89</v>
+        <v>1185</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI508" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ508" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>23</v>
+        <v>645</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1184</v>
+        <v>1189</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59242,15 +59264,17 @@
         <v>84</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>91</v>
+        <v>85</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>92</v>
+        <v>86</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>93</v>
-      </c>
-      <c r="O509" s="2"/>
+        <v>87</v>
+      </c>
+      <c r="O509" t="s" s="2">
+        <v>88</v>
+      </c>
       <c r="P509" s="2"/>
       <c r="Q509" t="s" s="2">
         <v>23</v>
@@ -59299,7 +59323,7 @@
         <v>23</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>94</v>
+        <v>89</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>76</v>
@@ -59311,18 +59335,18 @@
         <v>23</v>
       </c>
       <c r="AK509" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1185</v>
+        <v>1190</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59339,23 +59363,21 @@
         <v>23</v>
       </c>
       <c r="J510" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K510" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>97</v>
+        <v>91</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>98</v>
+        <v>92</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>99</v>
-      </c>
-      <c r="O510" t="s" s="2">
-        <v>100</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="O510" s="2"/>
       <c r="P510" s="2"/>
       <c r="Q510" t="s" s="2">
         <v>23</v>
@@ -59404,7 +59426,7 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>101</v>
+        <v>94</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
@@ -59421,13 +59443,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1186</v>
+        <v>1191</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59444,22 +59466,22 @@
         <v>23</v>
       </c>
       <c r="J511" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K511" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>103</v>
+        <v>97</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>104</v>
+        <v>98</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>105</v>
+        <v>99</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>106</v>
+        <v>100</v>
       </c>
       <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
@@ -59485,13 +59507,13 @@
         <v>23</v>
       </c>
       <c r="Y511" t="s" s="2">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="Z511" t="s" s="2">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="AA511" t="s" s="2">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="AB511" t="s" s="2">
         <v>23</v>
@@ -59509,7 +59531,7 @@
         <v>23</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>110</v>
+        <v>101</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -59526,17 +59548,17 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1187</v>
+        <v>1192</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
-        <v>519</v>
+        <v>23</v>
       </c>
       <c r="F512" s="2"/>
       <c r="G512" t="s" s="2">
@@ -59555,16 +59577,16 @@
         <v>23</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>520</v>
+        <v>103</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>521</v>
+        <v>104</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>522</v>
+        <v>105</v>
       </c>
       <c r="O512" t="s" s="2">
-        <v>523</v>
+        <v>106</v>
       </c>
       <c r="P512" s="2"/>
       <c r="Q512" t="s" s="2">
@@ -59590,13 +59612,13 @@
         <v>23</v>
       </c>
       <c r="Y512" t="s" s="2">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Z512" t="s" s="2">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="AA512" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="AB512" t="s" s="2">
         <v>23</v>
@@ -59614,7 +59636,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>524</v>
+        <v>110</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -59631,24 +59653,24 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1188</v>
+        <v>1193</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
-        <v>526</v>
+        <v>519</v>
       </c>
       <c r="F513" s="2"/>
       <c r="G513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H513" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I513" t="s" s="2">
         <v>23</v>
@@ -59660,16 +59682,16 @@
         <v>23</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>182</v>
+        <v>520</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>527</v>
+        <v>521</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>528</v>
+        <v>522</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>529</v>
+        <v>523</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -59719,34 +59741,34 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>530</v>
+        <v>524</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI513" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ513" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK513" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1189</v>
+        <v>1194</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
-        <v>146</v>
+        <v>526</v>
       </c>
       <c r="F514" s="2"/>
       <c r="G514" t="s" s="2">
@@ -59765,16 +59787,16 @@
         <v>23</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>148</v>
+        <v>527</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>532</v>
+        <v>528</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>150</v>
+        <v>529</v>
       </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
@@ -59824,7 +59846,7 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>533</v>
+        <v>530</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>76</v>
@@ -59836,18 +59858,18 @@
         <v>23</v>
       </c>
       <c r="AK514" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59864,7 +59886,7 @@
         <v>23</v>
       </c>
       <c r="J515" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K515" t="s" s="2">
         <v>23</v>
@@ -59873,17 +59895,15 @@
         <v>147</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>535</v>
+        <v>148</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>536</v>
+        <v>532</v>
       </c>
       <c r="O515" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P515" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P515" s="2"/>
       <c r="Q515" t="s" s="2">
         <v>23</v>
       </c>
@@ -59931,7 +59951,7 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>537</v>
+        <v>533</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>76</v>
@@ -59948,17 +59968,17 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F516" s="2"/>
       <c r="G516" t="s" s="2">
@@ -59971,24 +59991,26 @@
         <v>23</v>
       </c>
       <c r="J516" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K516" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>1192</v>
+        <v>535</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>1193</v>
+        <v>536</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>1194</v>
-      </c>
-      <c r="P516" s="2"/>
+        <v>150</v>
+      </c>
+      <c r="P516" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q516" t="s" s="2">
         <v>23</v>
       </c>
@@ -60036,7 +60058,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>1191</v>
+        <v>537</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -60048,18 +60070,18 @@
         <v>23</v>
       </c>
       <c r="AK516" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1195</v>
+        <v>1197</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60070,27 +60092,29 @@
         <v>76</v>
       </c>
       <c r="H517" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I517" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J517" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K517" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>103</v>
+        <v>112</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1196</v>
+        <v>1198</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>1197</v>
-      </c>
-      <c r="O517" s="2"/>
+        <v>1199</v>
+      </c>
+      <c r="O517" t="s" s="2">
+        <v>1200</v>
+      </c>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
         <v>23</v>
@@ -60115,37 +60139,37 @@
         <v>23</v>
       </c>
       <c r="Y517" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF517" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG517" t="s" s="2">
         <v>1197</v>
       </c>
-      <c r="AA517" t="s" s="2">
-        <v>1198</v>
-      </c>
-      <c r="AB517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF517" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG517" t="s" s="2">
-        <v>1195</v>
-      </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI517" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ517" t="s" s="2">
         <v>23</v>
@@ -60156,13 +60180,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60173,29 +60197,27 @@
         <v>76</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J518" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K518" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>1201</v>
-      </c>
-      <c r="O518" t="s" s="2">
-        <v>1202</v>
-      </c>
+        <v>1203</v>
+      </c>
+      <c r="O518" s="2"/>
       <c r="P518" s="2"/>
       <c r="Q518" t="s" s="2">
         <v>23</v>
@@ -60220,14 +60242,14 @@
         <v>23</v>
       </c>
       <c r="Y518" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Z518" t="s" s="2">
         <v>1203</v>
       </c>
-      <c r="Z518" t="s" s="2">
+      <c r="AA518" t="s" s="2">
         <v>1204</v>
       </c>
-      <c r="AA518" t="s" s="2">
-        <v>1205</v>
-      </c>
       <c r="AB518" t="s" s="2">
         <v>23</v>
       </c>
@@ -60244,13 +60266,13 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1199</v>
+        <v>1201</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI518" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ518" t="s" s="2">
         <v>23</v>
@@ -60261,13 +60283,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60275,10 +60297,10 @@
       </c>
       <c r="F519" s="2"/>
       <c r="G519" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H519" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I519" t="s" s="2">
         <v>23</v>
@@ -60293,13 +60315,13 @@
         <v>367</v>
       </c>
       <c r="M519" t="s" s="2">
+        <v>1206</v>
+      </c>
+      <c r="N519" t="s" s="2">
         <v>1207</v>
       </c>
-      <c r="N519" t="s" s="2">
+      <c r="O519" t="s" s="2">
         <v>1208</v>
-      </c>
-      <c r="O519" t="s" s="2">
-        <v>1209</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60325,7 +60347,7 @@
         <v>23</v>
       </c>
       <c r="Y519" t="s" s="2">
-        <v>372</v>
+        <v>1209</v>
       </c>
       <c r="Z519" t="s" s="2">
         <v>1210</v>
@@ -60349,13 +60371,13 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1206</v>
+        <v>1205</v>
       </c>
       <c r="AH519" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI519" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ519" t="s" s="2">
         <v>23</v>
@@ -60366,7 +60388,7 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B520" t="s" s="2">
         <v>1212</v>
@@ -60380,7 +60402,7 @@
       </c>
       <c r="F520" s="2"/>
       <c r="G520" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H520" t="s" s="2">
         <v>83</v>
@@ -60395,7 +60417,7 @@
         <v>84</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>141</v>
+        <v>367</v>
       </c>
       <c r="M520" t="s" s="2">
         <v>1213</v>
@@ -60403,7 +60425,9 @@
       <c r="N520" t="s" s="2">
         <v>1214</v>
       </c>
-      <c r="O520" s="2"/>
+      <c r="O520" t="s" s="2">
+        <v>1215</v>
+      </c>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
         <v>23</v>
@@ -60428,13 +60452,13 @@
         <v>23</v>
       </c>
       <c r="Y520" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>23</v>
+        <v>1216</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>23</v>
+        <v>1217</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
@@ -60455,7 +60479,7 @@
         <v>1212</v>
       </c>
       <c r="AH520" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI520" t="s" s="2">
         <v>83</v>
@@ -60469,13 +60493,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1215</v>
+        <v>1218</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60486,7 +60510,7 @@
         <v>76</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I521" t="s" s="2">
         <v>23</v>
@@ -60498,72 +60522,70 @@
         <v>84</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>136</v>
+        <v>141</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1216</v>
+        <v>1219</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1217</v>
+        <v>1220</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R521" t="s" s="2">
+      <c r="R521" s="2"/>
+      <c r="S521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF521" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG521" t="s" s="2">
         <v>1218</v>
       </c>
-      <c r="S521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF521" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG521" t="s" s="2">
-        <v>1215</v>
-      </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI521" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ521" t="s" s="2">
         <v>23</v>
@@ -60574,13 +60596,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1219</v>
+        <v>1221</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60591,7 +60613,7 @@
         <v>76</v>
       </c>
       <c r="H522" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I522" t="s" s="2">
         <v>23</v>
@@ -60600,23 +60622,25 @@
         <v>23</v>
       </c>
       <c r="K522" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>142</v>
+        <v>1222</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>143</v>
+        <v>1223</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R522" s="2"/>
+      <c r="R522" t="s" s="2">
+        <v>1224</v>
+      </c>
       <c r="S522" t="s" s="2">
         <v>23</v>
       </c>
@@ -60660,41 +60684,41 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>144</v>
+        <v>1221</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI522" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ522" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK522" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1220</v>
+        <v>1225</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F523" s="2"/>
       <c r="G523" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H523" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I523" t="s" s="2">
         <v>23</v>
@@ -60706,17 +60730,15 @@
         <v>23</v>
       </c>
       <c r="L523" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O523" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O523" s="2"/>
       <c r="P523" s="2"/>
       <c r="Q523" t="s" s="2">
         <v>23</v>
@@ -60765,34 +60787,34 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI523" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ523" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK523" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1221</v>
+        <v>1226</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F524" s="2"/>
       <c r="G524" t="s" s="2">
@@ -60805,26 +60827,24 @@
         <v>23</v>
       </c>
       <c r="J524" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K524" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L524" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O524" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P524" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
         <v>23</v>
       </c>
@@ -60872,7 +60892,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -60889,45 +60909,49 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1222</v>
+        <v>1227</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F525" s="2"/>
       <c r="G525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H525" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J525" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K525" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>1223</v>
+        <v>155</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>1224</v>
-      </c>
-      <c r="O525" s="2"/>
-      <c r="P525" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O525" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P525" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q525" t="s" s="2">
         <v>23</v>
       </c>
@@ -60975,30 +60999,30 @@
         <v>23</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>1222</v>
+        <v>158</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI525" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK525" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61021,13 +61045,13 @@
         <v>84</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>578</v>
+        <v>112</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1226</v>
+        <v>1229</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1227</v>
+        <v>1230</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" s="2"/>
@@ -61078,7 +61102,7 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1225</v>
+        <v>1228</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61095,13 +61119,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61124,13 +61148,13 @@
         <v>84</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>497</v>
+        <v>578</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1229</v>
+        <v>1232</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -61181,7 +61205,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1228</v>
+        <v>1231</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61198,13 +61222,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61215,7 +61239,7 @@
         <v>76</v>
       </c>
       <c r="H528" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I528" t="s" s="2">
         <v>23</v>
@@ -61227,13 +61251,13 @@
         <v>84</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>136</v>
+        <v>497</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1232</v>
+        <v>1235</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1233</v>
+        <v>1236</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61284,13 +61308,13 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1231</v>
+        <v>1234</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI528" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ528" t="s" s="2">
         <v>23</v>
@@ -61301,13 +61325,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1234</v>
+        <v>1237</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61318,7 +61342,7 @@
         <v>76</v>
       </c>
       <c r="H529" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I529" t="s" s="2">
         <v>23</v>
@@ -61327,16 +61351,16 @@
         <v>23</v>
       </c>
       <c r="K529" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>141</v>
+        <v>136</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>142</v>
+        <v>1238</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>143</v>
+        <v>1239</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61387,41 +61411,41 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>144</v>
+        <v>1237</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI529" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ529" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK529" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1235</v>
+        <v>1240</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F530" s="2"/>
       <c r="G530" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H530" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I530" t="s" s="2">
         <v>23</v>
@@ -61433,17 +61457,15 @@
         <v>23</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O530" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O530" s="2"/>
       <c r="P530" s="2"/>
       <c r="Q530" t="s" s="2">
         <v>23</v>
@@ -61492,34 +61514,34 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI530" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ530" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK530" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1236</v>
+        <v>1241</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F531" s="2"/>
       <c r="G531" t="s" s="2">
@@ -61532,26 +61554,24 @@
         <v>23</v>
       </c>
       <c r="J531" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K531" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L531" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O531" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P531" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P531" s="2"/>
       <c r="Q531" t="s" s="2">
         <v>23</v>
       </c>
@@ -61599,7 +61619,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61616,45 +61636,49 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1237</v>
+        <v>1242</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F532" s="2"/>
       <c r="G532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J532" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K532" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>491</v>
+        <v>147</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>1238</v>
+        <v>155</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>1239</v>
-      </c>
-      <c r="O532" s="2"/>
-      <c r="P532" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O532" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P532" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q532" t="s" s="2">
         <v>23</v>
       </c>
@@ -61702,30 +61726,30 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>1237</v>
+        <v>158</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI532" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1174</v>
+        <v>1180</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61733,7 +61757,7 @@
       </c>
       <c r="F533" s="2"/>
       <c r="G533" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H533" t="s" s="2">
         <v>83</v>
@@ -61748,13 +61772,13 @@
         <v>84</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>1241</v>
+        <v>491</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1242</v>
+        <v>1244</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1243</v>
+        <v>1245</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -61781,13 +61805,13 @@
         <v>23</v>
       </c>
       <c r="Y533" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z533" t="s" s="2">
-        <v>1244</v>
+        <v>23</v>
       </c>
       <c r="AA533" t="s" s="2">
-        <v>1211</v>
+        <v>23</v>
       </c>
       <c r="AB533" t="s" s="2">
         <v>23</v>
@@ -61805,10 +61829,10 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="AH533" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI533" t="s" s="2">
         <v>83</v>
@@ -61822,13 +61846,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1245</v>
+        <v>1180</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61836,10 +61860,10 @@
       </c>
       <c r="F534" s="2"/>
       <c r="G534" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H534" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I534" t="s" s="2">
         <v>23</v>
@@ -61848,20 +61872,18 @@
         <v>23</v>
       </c>
       <c r="K534" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>78</v>
+        <v>1247</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>1251</v>
+        <v>1248</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>1252</v>
-      </c>
-      <c r="O534" t="s" s="2">
-        <v>1253</v>
-      </c>
+        <v>1249</v>
+      </c>
+      <c r="O534" s="2"/>
       <c r="P534" s="2"/>
       <c r="Q534" t="s" s="2">
         <v>23</v>
@@ -61886,13 +61908,13 @@
         <v>23</v>
       </c>
       <c r="Y534" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z534" t="s" s="2">
-        <v>23</v>
+        <v>1250</v>
       </c>
       <c r="AA534" t="s" s="2">
-        <v>23</v>
+        <v>1217</v>
       </c>
       <c r="AB534" t="s" s="2">
         <v>23</v>
@@ -61910,13 +61932,13 @@
         <v>23</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1249</v>
+        <v>1246</v>
       </c>
       <c r="AH534" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI534" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ534" t="s" s="2">
         <v>23</v>
@@ -61927,13 +61949,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -61944,7 +61966,7 @@
         <v>76</v>
       </c>
       <c r="H535" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I535" t="s" s="2">
         <v>23</v>
@@ -61956,15 +61978,17 @@
         <v>23</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>141</v>
+        <v>78</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>142</v>
+        <v>1257</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O535" s="2"/>
+        <v>1258</v>
+      </c>
+      <c r="O535" t="s" s="2">
+        <v>1259</v>
+      </c>
       <c r="P535" s="2"/>
       <c r="Q535" t="s" s="2">
         <v>23</v>
@@ -62013,41 +62037,41 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>144</v>
+        <v>1255</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI535" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ535" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK535" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1255</v>
+        <v>1260</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F536" s="2"/>
       <c r="G536" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H536" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I536" t="s" s="2">
         <v>23</v>
@@ -62059,17 +62083,15 @@
         <v>23</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O536" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O536" s="2"/>
       <c r="P536" s="2"/>
       <c r="Q536" t="s" s="2">
         <v>23</v>
@@ -62106,46 +62128,46 @@
         <v>23</v>
       </c>
       <c r="AC536" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD536" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE536" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF536" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI536" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ536" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK536" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1256</v>
+        <v>1261</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
-        <v>154</v>
+        <v>146</v>
       </c>
       <c r="F537" s="2"/>
       <c r="G537" t="s" s="2">
@@ -62158,26 +62180,24 @@
         <v>23</v>
       </c>
       <c r="J537" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K537" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L537" t="s" s="2">
         <v>147</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>155</v>
+        <v>148</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>156</v>
+        <v>149</v>
       </c>
       <c r="O537" t="s" s="2">
         <v>150</v>
       </c>
-      <c r="P537" t="s" s="2">
-        <v>157</v>
-      </c>
+      <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
         <v>23</v>
       </c>
@@ -62213,19 +62233,19 @@
         <v>23</v>
       </c>
       <c r="AC537" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD537" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE537" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF537" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>158</v>
+        <v>151</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62242,17 +62262,17 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1257</v>
+        <v>1262</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F538" s="2"/>
       <c r="G538" t="s" s="2">
@@ -62262,26 +62282,28 @@
         <v>77</v>
       </c>
       <c r="I538" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J538" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="J538" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="K538" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>578</v>
+        <v>147</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>1258</v>
+        <v>155</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>1259</v>
-      </c>
-      <c r="O538" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O538" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P538" t="s" s="2">
-        <v>1260</v>
+        <v>157</v>
       </c>
       <c r="Q538" t="s" s="2">
         <v>23</v>
@@ -62330,7 +62352,7 @@
         <v>23</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>1257</v>
+        <v>158</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
@@ -62342,18 +62364,18 @@
         <v>23</v>
       </c>
       <c r="AK538" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62364,7 +62386,7 @@
         <v>76</v>
       </c>
       <c r="H539" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I539" t="s" s="2">
         <v>84</v>
@@ -62376,17 +62398,17 @@
         <v>84</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>418</v>
+        <v>578</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1262</v>
+        <v>1264</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1263</v>
+        <v>1265</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" t="s" s="2">
-        <v>1264</v>
+        <v>1266</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>23</v>
@@ -62435,30 +62457,30 @@
         <v>23</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1261</v>
+        <v>1263</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI539" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ539" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK539" t="s" s="2">
-        <v>1265</v>
+        <v>95</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62472,25 +62494,27 @@
         <v>83</v>
       </c>
       <c r="I540" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J540" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K540" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>141</v>
+        <v>418</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>142</v>
+        <v>1268</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>143</v>
+        <v>1269</v>
       </c>
       <c r="O540" s="2"/>
-      <c r="P540" s="2"/>
+      <c r="P540" t="s" s="2">
+        <v>1270</v>
+      </c>
       <c r="Q540" t="s" s="2">
         <v>23</v>
       </c>
@@ -62538,7 +62562,7 @@
         <v>23</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>144</v>
+        <v>1267</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>76</v>
@@ -62550,29 +62574,29 @@
         <v>23</v>
       </c>
       <c r="AK540" t="s" s="2">
-        <v>23</v>
+        <v>1271</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1267</v>
+        <v>1272</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F541" s="2"/>
       <c r="G541" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H541" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I541" t="s" s="2">
         <v>23</v>
@@ -62584,17 +62608,15 @@
         <v>23</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O541" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O541" s="2"/>
       <c r="P541" s="2"/>
       <c r="Q541" t="s" s="2">
         <v>23</v>
@@ -62631,53 +62653,53 @@
         <v>23</v>
       </c>
       <c r="AC541" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD541" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF541" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI541" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK541" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1268</v>
+        <v>1273</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F542" s="2"/>
       <c r="G542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H542" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I542" t="s" s="2">
         <v>23</v>
@@ -62686,18 +62708,20 @@
         <v>23</v>
       </c>
       <c r="K542" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>1269</v>
+        <v>147</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1270</v>
+        <v>148</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1271</v>
-      </c>
-      <c r="O542" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O542" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P542" s="2"/>
       <c r="Q542" t="s" s="2">
         <v>23</v>
@@ -62734,9 +62758,11 @@
         <v>23</v>
       </c>
       <c r="AC542" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AD542" s="2"/>
+        <v>353</v>
+      </c>
+      <c r="AD542" t="s" s="2">
+        <v>354</v>
+      </c>
       <c r="AE542" t="s" s="2">
         <v>23</v>
       </c>
@@ -62744,34 +62770,32 @@
         <v>355</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1268</v>
+        <v>151</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI542" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ542" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK542" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1272</v>
+        <v>1274</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="D543" t="s" s="2">
-        <v>1273</v>
-      </c>
+        <v>1274</v>
+      </c>
+      <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
         <v>23</v>
       </c>
@@ -62792,13 +62816,13 @@
         <v>84</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>903</v>
+        <v>1275</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1270</v>
+        <v>1276</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1271</v>
+        <v>1277</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -62837,19 +62861,17 @@
         <v>23</v>
       </c>
       <c r="AC543" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD543" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AD543" s="2"/>
       <c r="AE543" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF543" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1268</v>
+        <v>1274</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -62866,15 +62888,17 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B544" t="s" s="2">
+        <v>1278</v>
+      </c>
+      <c r="C544" t="s" s="2">
         <v>1274</v>
       </c>
-      <c r="C544" t="s" s="2">
-        <v>1275</v>
-      </c>
-      <c r="D544" s="2"/>
+      <c r="D544" t="s" s="2">
+        <v>1279</v>
+      </c>
       <c r="E544" t="s" s="2">
         <v>23</v>
       </c>
@@ -62892,16 +62916,16 @@
         <v>23</v>
       </c>
       <c r="K544" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>141</v>
+        <v>903</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>142</v>
+        <v>1276</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>143</v>
+        <v>1277</v>
       </c>
       <c r="O544" s="2"/>
       <c r="P544" s="2"/>
@@ -62952,7 +62976,7 @@
         <v>23</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>144</v>
+        <v>1274</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
@@ -62964,29 +62988,29 @@
         <v>23</v>
       </c>
       <c r="AK544" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1276</v>
+        <v>1280</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1277</v>
+        <v>1281</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F545" s="2"/>
       <c r="G545" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H545" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I545" t="s" s="2">
         <v>23</v>
@@ -62998,17 +63022,15 @@
         <v>23</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>148</v>
+        <v>142</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O545" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O545" s="2"/>
       <c r="P545" s="2"/>
       <c r="Q545" t="s" s="2">
         <v>23</v>
@@ -63045,53 +63067,53 @@
         <v>23</v>
       </c>
       <c r="AC545" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD545" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE545" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF545" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>151</v>
+        <v>144</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI545" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ545" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK545" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1278</v>
+        <v>1282</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1279</v>
+        <v>1283</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F546" s="2"/>
       <c r="G546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H546" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I546" t="s" s="2">
         <v>23</v>
@@ -63100,19 +63122,19 @@
         <v>23</v>
       </c>
       <c r="K546" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L546" t="s" s="2">
-        <v>578</v>
+        <v>147</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>1280</v>
+        <v>148</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>1281</v>
+        <v>149</v>
       </c>
       <c r="O546" t="s" s="2">
-        <v>1282</v>
+        <v>150</v>
       </c>
       <c r="P546" s="2"/>
       <c r="Q546" t="s" s="2">
@@ -63150,42 +63172,42 @@
         <v>23</v>
       </c>
       <c r="AC546" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD546" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE546" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF546" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1283</v>
+        <v>151</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI546" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ546" t="s" s="2">
-        <v>1284</v>
+        <v>23</v>
       </c>
       <c r="AK546" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B547" t="s" s="2">
+        <v>1284</v>
+      </c>
+      <c r="C547" t="s" s="2">
         <v>1285</v>
-      </c>
-      <c r="C547" t="s" s="2">
-        <v>1286</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63211,74 +63233,72 @@
         <v>578</v>
       </c>
       <c r="M547" t="s" s="2">
+        <v>1286</v>
+      </c>
+      <c r="N547" t="s" s="2">
         <v>1287</v>
       </c>
-      <c r="N547" t="s" s="2">
+      <c r="O547" t="s" s="2">
         <v>1288</v>
-      </c>
-      <c r="O547" t="s" s="2">
-        <v>1289</v>
       </c>
       <c r="P547" s="2"/>
       <c r="Q547" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R547" t="s" s="2">
+      <c r="R547" s="2"/>
+      <c r="S547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF547" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG547" t="s" s="2">
+        <v>1289</v>
+      </c>
+      <c r="AH547" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI547" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ547" t="s" s="2">
         <v>1290</v>
-      </c>
-      <c r="S547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF547" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG547" t="s" s="2">
-        <v>1291</v>
-      </c>
-      <c r="AH547" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI547" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ547" t="s" s="2">
-        <v>1284</v>
       </c>
       <c r="AK547" t="s" s="2">
         <v>95</v>
@@ -63286,10 +63306,10 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1292</v>
+        <v>1291</v>
       </c>
       <c r="C548" t="s" s="2">
         <v>1292</v>
@@ -63315,69 +63335,69 @@
         <v>84</v>
       </c>
       <c r="L548" t="s" s="2">
+        <v>578</v>
+      </c>
+      <c r="M548" t="s" s="2">
         <v>1293</v>
       </c>
-      <c r="M548" t="s" s="2">
+      <c r="N548" t="s" s="2">
         <v>1294</v>
       </c>
-      <c r="N548" t="s" s="2">
+      <c r="O548" t="s" s="2">
         <v>1295</v>
       </c>
-      <c r="O548" t="s" s="2">
+      <c r="P548" s="2"/>
+      <c r="Q548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R548" t="s" s="2">
         <v>1296</v>
       </c>
-      <c r="P548" t="s" s="2">
+      <c r="S548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG548" t="s" s="2">
         <v>1297</v>
       </c>
-      <c r="Q548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="R548" s="2"/>
-      <c r="S548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG548" t="s" s="2">
-        <v>1292</v>
-      </c>
       <c r="AH548" t="s" s="2">
         <v>76</v>
       </c>
@@ -63385,7 +63405,7 @@
         <v>83</v>
       </c>
       <c r="AJ548" t="s" s="2">
-        <v>23</v>
+        <v>1290</v>
       </c>
       <c r="AK548" t="s" s="2">
         <v>95</v>
@@ -63393,7 +63413,7 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B549" t="s" s="2">
         <v>1298</v>
@@ -63422,16 +63442,20 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1300</v>
-      </c>
-      <c r="O549" s="2"/>
-      <c r="P549" s="2"/>
+        <v>1301</v>
+      </c>
+      <c r="O549" t="s" s="2">
+        <v>1302</v>
+      </c>
+      <c r="P549" t="s" s="2">
+        <v>1303</v>
+      </c>
       <c r="Q549" t="s" s="2">
         <v>23</v>
       </c>
@@ -63496,13 +63520,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63525,20 +63549,16 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>199</v>
+        <v>1299</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1302</v>
+        <v>1305</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1303</v>
-      </c>
-      <c r="O550" t="s" s="2">
-        <v>1304</v>
-      </c>
-      <c r="P550" t="s" s="2">
-        <v>1305</v>
-      </c>
+        <v>1306</v>
+      </c>
+      <c r="O550" s="2"/>
+      <c r="P550" s="2"/>
       <c r="Q550" t="s" s="2">
         <v>23</v>
       </c>
@@ -63586,7 +63606,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1301</v>
+        <v>1304</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63603,13 +63623,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63635,16 +63655,16 @@
         <v>199</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="O551" t="s" s="2">
-        <v>1304</v>
+        <v>1310</v>
       </c>
       <c r="P551" t="s" s="2">
-        <v>1305</v>
+        <v>1311</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63693,7 +63713,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63710,13 +63730,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1309</v>
+        <v>1312</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63739,16 +63759,20 @@
         <v>84</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M552" t="s" s="2">
+        <v>1313</v>
+      </c>
+      <c r="N552" t="s" s="2">
+        <v>1314</v>
+      </c>
+      <c r="O552" t="s" s="2">
         <v>1310</v>
       </c>
-      <c r="N552" t="s" s="2">
+      <c r="P552" t="s" s="2">
         <v>1311</v>
       </c>
-      <c r="O552" s="2"/>
-      <c r="P552" s="2"/>
       <c r="Q552" t="s" s="2">
         <v>23</v>
       </c>
@@ -63772,31 +63796,31 @@
         <v>23</v>
       </c>
       <c r="Y552" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF552" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG552" t="s" s="2">
         <v>1312</v>
-      </c>
-      <c r="AA552" t="s" s="2">
-        <v>1313</v>
-      </c>
-      <c r="AB552" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC552" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD552" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE552" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF552" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG552" t="s" s="2">
-        <v>1309</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63813,13 +63837,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63842,22 +63866,20 @@
         <v>84</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>1293</v>
+        <v>103</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
       <c r="Q553" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R553" t="s" s="2">
-        <v>1317</v>
-      </c>
+      <c r="R553" s="2"/>
       <c r="S553" t="s" s="2">
         <v>23</v>
       </c>
@@ -63877,13 +63899,13 @@
         <v>23</v>
       </c>
       <c r="Y553" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="Z553" t="s" s="2">
-        <v>23</v>
+        <v>1318</v>
       </c>
       <c r="AA553" t="s" s="2">
-        <v>23</v>
+        <v>1319</v>
       </c>
       <c r="AB553" t="s" s="2">
         <v>23</v>
@@ -63901,7 +63923,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63918,13 +63940,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63947,20 +63969,22 @@
         <v>84</v>
       </c>
       <c r="L554" t="s" s="2">
-        <v>1293</v>
+        <v>1299</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1319</v>
+        <v>1321</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1320</v>
+        <v>1322</v>
       </c>
       <c r="O554" s="2"/>
       <c r="P554" s="2"/>
       <c r="Q554" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R554" s="2"/>
+      <c r="R554" t="s" s="2">
+        <v>1323</v>
+      </c>
       <c r="S554" t="s" s="2">
         <v>23</v>
       </c>
@@ -64004,7 +64028,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1318</v>
+        <v>1320</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64021,13 +64045,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64041,7 +64065,7 @@
         <v>83</v>
       </c>
       <c r="I555" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J555" t="s" s="2">
         <v>23</v>
@@ -64050,13 +64074,13 @@
         <v>84</v>
       </c>
       <c r="L555" t="s" s="2">
-        <v>199</v>
+        <v>1299</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1322</v>
+        <v>1325</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1323</v>
+        <v>1326</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64107,7 +64131,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1321</v>
+        <v>1324</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64124,13 +64148,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64144,7 +64168,7 @@
         <v>83</v>
       </c>
       <c r="I556" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J556" t="s" s="2">
         <v>23</v>
@@ -64156,10 +64180,10 @@
         <v>199</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1325</v>
+        <v>1328</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1326</v>
+        <v>1329</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64210,7 +64234,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1324</v>
+        <v>1327</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64227,13 +64251,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1327</v>
+        <v>1330</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64256,13 +64280,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1328</v>
+        <v>1331</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1329</v>
+        <v>1332</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64289,29 +64313,31 @@
         <v>23</v>
       </c>
       <c r="Y557" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z557" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z557" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF557" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG557" t="s" s="2">
         <v>1330</v>
-      </c>
-      <c r="AB557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF557" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG557" t="s" s="2">
-        <v>1327</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64328,13 +64354,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64345,7 +64371,7 @@
         <v>76</v>
       </c>
       <c r="H558" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I558" t="s" s="2">
         <v>23</v>
@@ -64360,14 +64386,12 @@
         <v>103</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1332</v>
+        <v>1334</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1333</v>
-      </c>
-      <c r="O558" t="s" s="2">
-        <v>1334</v>
-      </c>
+        <v>1335</v>
+      </c>
+      <c r="O558" s="2"/>
       <c r="P558" s="2"/>
       <c r="Q558" t="s" s="2">
         <v>23</v>
@@ -64396,7 +64420,7 @@
       </c>
       <c r="Z558" s="2"/>
       <c r="AA558" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="AB558" t="s" s="2">
         <v>23</v>
@@ -64414,13 +64438,13 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1331</v>
+        <v>1333</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI558" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ558" t="s" s="2">
         <v>23</v>
@@ -64431,13 +64455,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64460,7 +64484,7 @@
         <v>84</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>1337</v>
+        <v>103</v>
       </c>
       <c r="M559" t="s" s="2">
         <v>1338</v>
@@ -64495,13 +64519,11 @@
         <v>23</v>
       </c>
       <c r="Y559" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z559" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z559" s="2"/>
       <c r="AA559" t="s" s="2">
-        <v>23</v>
+        <v>1341</v>
       </c>
       <c r="AB559" t="s" s="2">
         <v>23</v>
@@ -64519,7 +64541,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64536,13 +64558,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64556,7 +64578,7 @@
         <v>77</v>
       </c>
       <c r="I560" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J560" t="s" s="2">
         <v>23</v>
@@ -64565,20 +64587,18 @@
         <v>84</v>
       </c>
       <c r="L560" t="s" s="2">
-        <v>103</v>
+        <v>1343</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1342</v>
+        <v>1344</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1343</v>
+        <v>1345</v>
       </c>
       <c r="O560" t="s" s="2">
-        <v>1344</v>
-      </c>
-      <c r="P560" t="s" s="2">
-        <v>1345</v>
-      </c>
+        <v>1346</v>
+      </c>
+      <c r="P560" s="2"/>
       <c r="Q560" t="s" s="2">
         <v>23</v>
       </c>
@@ -64602,11 +64622,13 @@
         <v>23</v>
       </c>
       <c r="Y560" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z560" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z560" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA560" t="s" s="2">
-        <v>1346</v>
+        <v>23</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64624,7 +64646,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64641,7 +64663,7 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B561" t="s" s="2">
         <v>1347</v>
@@ -64658,7 +64680,7 @@
         <v>76</v>
       </c>
       <c r="H561" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I561" t="s" s="2">
         <v>84</v>
@@ -64670,7 +64692,7 @@
         <v>84</v>
       </c>
       <c r="L561" t="s" s="2">
-        <v>130</v>
+        <v>103</v>
       </c>
       <c r="M561" t="s" s="2">
         <v>1348</v>
@@ -64678,8 +64700,12 @@
       <c r="N561" t="s" s="2">
         <v>1349</v>
       </c>
-      <c r="O561" s="2"/>
-      <c r="P561" s="2"/>
+      <c r="O561" t="s" s="2">
+        <v>1350</v>
+      </c>
+      <c r="P561" t="s" s="2">
+        <v>1351</v>
+      </c>
       <c r="Q561" t="s" s="2">
         <v>23</v>
       </c>
@@ -64703,13 +64729,11 @@
         <v>23</v>
       </c>
       <c r="Y561" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z561" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z561" s="2"/>
       <c r="AA561" t="s" s="2">
-        <v>23</v>
+        <v>1352</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64733,7 +64757,7 @@
         <v>76</v>
       </c>
       <c r="AI561" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ561" t="s" s="2">
         <v>23</v>
@@ -64744,13 +64768,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1245</v>
+        <v>1251</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1350</v>
+        <v>1353</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64764,7 +64788,7 @@
         <v>83</v>
       </c>
       <c r="I562" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J562" t="s" s="2">
         <v>23</v>
@@ -64773,17 +64797,15 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>367</v>
+        <v>130</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1351</v>
+        <v>1354</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1352</v>
-      </c>
-      <c r="O562" t="s" s="2">
-        <v>1353</v>
-      </c>
+        <v>1355</v>
+      </c>
+      <c r="O562" s="2"/>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
         <v>23</v>
@@ -64808,42 +64830,147 @@
         <v>23</v>
       </c>
       <c r="Y562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG562" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="AH562" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI562" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ562" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK562" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="563">
+      <c r="A563" t="s" s="2">
+        <v>1251</v>
+      </c>
+      <c r="B563" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="C563" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="D563" s="2"/>
+      <c r="E563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F563" s="2"/>
+      <c r="G563" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H563" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K563" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L563" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M563" t="s" s="2">
+        <v>1357</v>
+      </c>
+      <c r="N563" t="s" s="2">
+        <v>1358</v>
+      </c>
+      <c r="O563" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="P563" s="2"/>
+      <c r="Q563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R563" s="2"/>
+      <c r="S563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y563" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="Z562" t="s" s="2">
-        <v>1354</v>
-      </c>
-      <c r="AA562" t="s" s="2">
-        <v>1355</v>
-      </c>
-      <c r="AB562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG562" t="s" s="2">
-        <v>1350</v>
-      </c>
-      <c r="AH562" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI562" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ562" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK562" t="s" s="2">
+      <c r="Z563" t="s" s="2">
+        <v>1360</v>
+      </c>
+      <c r="AA563" t="s" s="2">
+        <v>1361</v>
+      </c>
+      <c r="AB563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG563" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="AH563" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI563" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK563" t="s" s="2">
         <v>95</v>
       </c>
     </row>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18866" uniqueCount="1362">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18866" uniqueCount="1361">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-22T12:28:16+00:00</t>
+    <t>2026-05-27T13:46:49+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2546,10 +2546,6 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-patient)
-</t>
-  </si>
-  <si>
     <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
@@ -2598,7 +2594,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitioner|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitioner|https://fhir.hl7.at/elga/core/r4/StructureDefinition/at-elga-core-practitionerRole|http://hl7.at/fhir/HL7ATCoreProfiles/4.0.1/StructureDefinition/at-core-organization)
 </t>
   </si>
   <si>
@@ -3287,7 +3283,7 @@
   <si>
     <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
 In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+Sofern eine zugehörige geplante Abgabe vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
   </si>
   <si>
     <t>MedicationDispense</t>
@@ -3555,7 +3551,7 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t>Verpflichtende Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert.</t>
+    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. Planeintrag (MedicationRequest).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -5461,7 +5457,7 @@
         <v>2</v>
       </c>
       <c r="B134" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
     </row>
     <row r="135">
@@ -5469,7 +5465,7 @@
         <v>4</v>
       </c>
       <c r="B135" t="s" s="2">
-        <v>965</v>
+        <v>964</v>
       </c>
     </row>
     <row r="136">
@@ -5485,7 +5481,7 @@
         <v>8</v>
       </c>
       <c r="B137" t="s" s="2">
-        <v>966</v>
+        <v>965</v>
       </c>
     </row>
     <row r="138">
@@ -5493,7 +5489,7 @@
         <v>10</v>
       </c>
       <c r="B138" t="s" s="2">
-        <v>967</v>
+        <v>966</v>
       </c>
     </row>
     <row r="139">
@@ -5555,7 +5551,7 @@
         <v>24</v>
       </c>
       <c r="B146" t="s" s="2">
-        <v>968</v>
+        <v>967</v>
       </c>
     </row>
     <row r="147">
@@ -5631,7 +5627,7 @@
         <v>2</v>
       </c>
       <c r="B156" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
     </row>
     <row r="157">
@@ -5639,7 +5635,7 @@
         <v>4</v>
       </c>
       <c r="B157" t="s" s="2">
-        <v>1032</v>
+        <v>1031</v>
       </c>
     </row>
     <row r="158">
@@ -5655,7 +5651,7 @@
         <v>8</v>
       </c>
       <c r="B159" t="s" s="2">
-        <v>1033</v>
+        <v>1032</v>
       </c>
     </row>
     <row r="160">
@@ -5663,7 +5659,7 @@
         <v>10</v>
       </c>
       <c r="B160" t="s" s="2">
-        <v>1034</v>
+        <v>1033</v>
       </c>
     </row>
     <row r="161">
@@ -5725,7 +5721,7 @@
         <v>24</v>
       </c>
       <c r="B168" t="s" s="2">
-        <v>1035</v>
+        <v>1034</v>
       </c>
     </row>
     <row r="169">
@@ -5761,7 +5757,7 @@
         <v>32</v>
       </c>
       <c r="B173" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
     </row>
     <row r="174">
@@ -5769,7 +5765,7 @@
         <v>34</v>
       </c>
       <c r="B174" t="s" s="2">
-        <v>1037</v>
+        <v>1036</v>
       </c>
     </row>
     <row r="175">
@@ -5801,7 +5797,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
     </row>
     <row r="179">
@@ -5809,7 +5805,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1181</v>
+        <v>1180</v>
       </c>
     </row>
     <row r="180">
@@ -5825,7 +5821,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1182</v>
+        <v>1181</v>
       </c>
     </row>
     <row r="182">
@@ -5833,7 +5829,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1183</v>
+        <v>1182</v>
       </c>
     </row>
     <row r="183">
@@ -5895,7 +5891,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1184</v>
+        <v>1183</v>
       </c>
     </row>
     <row r="191">
@@ -5931,7 +5927,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
     </row>
     <row r="196">
@@ -5939,7 +5935,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1186</v>
+        <v>1185</v>
       </c>
     </row>
     <row r="197">
@@ -5971,7 +5967,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
     </row>
     <row r="201">
@@ -5979,7 +5975,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1252</v>
+        <v>1251</v>
       </c>
     </row>
     <row r="202">
@@ -5995,7 +5991,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1253</v>
+        <v>1252</v>
       </c>
     </row>
     <row r="204">
@@ -6003,7 +5999,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="205">
@@ -6065,7 +6061,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1254</v>
+        <v>1253</v>
       </c>
     </row>
     <row r="213">
@@ -6101,7 +6097,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
     </row>
     <row r="218">
@@ -6109,7 +6105,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1256</v>
+        <v>1255</v>
       </c>
     </row>
     <row r="219">
@@ -41641,16 +41637,16 @@
         <v>84</v>
       </c>
       <c r="L340" t="s" s="2">
+        <v>568</v>
+      </c>
+      <c r="M340" t="s" s="2">
         <v>804</v>
       </c>
-      <c r="M340" t="s" s="2">
+      <c r="N340" t="s" s="2">
         <v>805</v>
       </c>
-      <c r="N340" t="s" s="2">
+      <c r="O340" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="O340" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="P340" s="2"/>
       <c r="Q340" t="s" s="2">
@@ -41720,10 +41716,10 @@
         <v>717</v>
       </c>
       <c r="B341" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C341" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D341" s="2"/>
       <c r="E341" t="s" s="2">
@@ -41749,13 +41745,13 @@
         <v>574</v>
       </c>
       <c r="M341" t="s" s="2">
+        <v>808</v>
+      </c>
+      <c r="N341" t="s" s="2">
         <v>809</v>
       </c>
-      <c r="N341" t="s" s="2">
+      <c r="O341" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="O341" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="P341" s="2"/>
       <c r="Q341" t="s" s="2">
@@ -41805,7 +41801,7 @@
         <v>23</v>
       </c>
       <c r="AG341" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AH341" t="s" s="2">
         <v>76</v>
@@ -41825,10 +41821,10 @@
         <v>717</v>
       </c>
       <c r="B342" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C342" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D342" s="2"/>
       <c r="E342" t="s" s="2">
@@ -41851,13 +41847,13 @@
         <v>23</v>
       </c>
       <c r="L342" t="s" s="2">
+        <v>812</v>
+      </c>
+      <c r="M342" t="s" s="2">
         <v>813</v>
       </c>
-      <c r="M342" t="s" s="2">
+      <c r="N342" t="s" s="2">
         <v>814</v>
-      </c>
-      <c r="N342" t="s" s="2">
-        <v>815</v>
       </c>
       <c r="O342" s="2"/>
       <c r="P342" s="2"/>
@@ -41908,7 +41904,7 @@
         <v>23</v>
       </c>
       <c r="AG342" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AH342" t="s" s="2">
         <v>76</v>
@@ -41928,10 +41924,10 @@
         <v>717</v>
       </c>
       <c r="B343" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C343" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D343" s="2"/>
       <c r="E343" t="s" s="2">
@@ -41957,10 +41953,10 @@
         <v>578</v>
       </c>
       <c r="M343" t="s" s="2">
+        <v>816</v>
+      </c>
+      <c r="N343" t="s" s="2">
         <v>817</v>
-      </c>
-      <c r="N343" t="s" s="2">
-        <v>818</v>
       </c>
       <c r="O343" s="2"/>
       <c r="P343" s="2"/>
@@ -42011,7 +42007,7 @@
         <v>23</v>
       </c>
       <c r="AG343" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AH343" t="s" s="2">
         <v>76</v>
@@ -42031,10 +42027,10 @@
         <v>717</v>
       </c>
       <c r="B344" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C344" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D344" s="2"/>
       <c r="E344" t="s" s="2">
@@ -42057,13 +42053,13 @@
         <v>84</v>
       </c>
       <c r="L344" t="s" s="2">
+        <v>819</v>
+      </c>
+      <c r="M344" t="s" s="2">
         <v>820</v>
       </c>
-      <c r="M344" t="s" s="2">
+      <c r="N344" t="s" s="2">
         <v>821</v>
-      </c>
-      <c r="N344" t="s" s="2">
-        <v>822</v>
       </c>
       <c r="O344" s="2"/>
       <c r="P344" s="2"/>
@@ -42114,7 +42110,7 @@
         <v>23</v>
       </c>
       <c r="AG344" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AH344" t="s" s="2">
         <v>76</v>
@@ -42134,10 +42130,10 @@
         <v>717</v>
       </c>
       <c r="B345" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C345" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D345" s="2"/>
       <c r="E345" t="s" s="2">
@@ -42160,13 +42156,13 @@
         <v>23</v>
       </c>
       <c r="L345" t="s" s="2">
+        <v>823</v>
+      </c>
+      <c r="M345" t="s" s="2">
         <v>824</v>
       </c>
-      <c r="M345" t="s" s="2">
+      <c r="N345" t="s" s="2">
         <v>825</v>
-      </c>
-      <c r="N345" t="s" s="2">
-        <v>826</v>
       </c>
       <c r="O345" s="2"/>
       <c r="P345" s="2"/>
@@ -42217,7 +42213,7 @@
         <v>23</v>
       </c>
       <c r="AG345" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AH345" t="s" s="2">
         <v>76</v>
@@ -42237,10 +42233,10 @@
         <v>717</v>
       </c>
       <c r="B346" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C346" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D346" s="2"/>
       <c r="E346" t="s" s="2">
@@ -42269,10 +42265,10 @@
         <v>796</v>
       </c>
       <c r="N346" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="O346" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="O346" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="P346" s="2"/>
       <c r="Q346" t="s" s="2">
@@ -42301,11 +42297,11 @@
         <v>372</v>
       </c>
       <c r="Z346" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AA346" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="AA346" t="s" s="2">
-        <v>831</v>
-      </c>
       <c r="AB346" t="s" s="2">
         <v>23</v>
       </c>
@@ -42322,7 +42318,7 @@
         <v>23</v>
       </c>
       <c r="AG346" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AH346" t="s" s="2">
         <v>76</v>
@@ -42342,10 +42338,10 @@
         <v>717</v>
       </c>
       <c r="B347" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C347" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D347" s="2"/>
       <c r="E347" t="s" s="2">
@@ -42368,13 +42364,13 @@
         <v>23</v>
       </c>
       <c r="L347" t="s" s="2">
+        <v>832</v>
+      </c>
+      <c r="M347" t="s" s="2">
         <v>833</v>
       </c>
-      <c r="M347" t="s" s="2">
+      <c r="N347" t="s" s="2">
         <v>834</v>
-      </c>
-      <c r="N347" t="s" s="2">
-        <v>835</v>
       </c>
       <c r="O347" s="2"/>
       <c r="P347" s="2"/>
@@ -42425,7 +42421,7 @@
         <v>23</v>
       </c>
       <c r="AG347" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AH347" t="s" s="2">
         <v>76</v>
@@ -42445,10 +42441,10 @@
         <v>717</v>
       </c>
       <c r="B348" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C348" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D348" s="2"/>
       <c r="E348" t="s" s="2">
@@ -42474,13 +42470,13 @@
         <v>367</v>
       </c>
       <c r="M348" t="s" s="2">
+        <v>836</v>
+      </c>
+      <c r="N348" t="s" s="2">
         <v>837</v>
       </c>
-      <c r="N348" t="s" s="2">
+      <c r="O348" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="O348" t="s" s="2">
-        <v>839</v>
       </c>
       <c r="P348" s="2"/>
       <c r="Q348" t="s" s="2">
@@ -42509,11 +42505,11 @@
         <v>372</v>
       </c>
       <c r="Z348" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AA348" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="AA348" t="s" s="2">
-        <v>841</v>
-      </c>
       <c r="AB348" t="s" s="2">
         <v>23</v>
       </c>
@@ -42530,7 +42526,7 @@
         <v>23</v>
       </c>
       <c r="AG348" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AH348" t="s" s="2">
         <v>76</v>
@@ -42550,10 +42546,10 @@
         <v>717</v>
       </c>
       <c r="B349" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C349" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D349" s="2"/>
       <c r="E349" t="s" s="2">
@@ -42576,16 +42572,16 @@
         <v>23</v>
       </c>
       <c r="L349" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="M349" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="M349" t="s" s="2">
+      <c r="N349" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="N349" t="s" s="2">
+      <c r="O349" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="O349" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="P349" s="2"/>
       <c r="Q349" t="s" s="2">
@@ -42635,7 +42631,7 @@
         <v>23</v>
       </c>
       <c r="AG349" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AH349" t="s" s="2">
         <v>76</v>
@@ -42655,10 +42651,10 @@
         <v>717</v>
       </c>
       <c r="B350" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C350" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D350" s="2"/>
       <c r="E350" t="s" s="2">
@@ -42681,13 +42677,13 @@
         <v>84</v>
       </c>
       <c r="L350" t="s" s="2">
+        <v>847</v>
+      </c>
+      <c r="M350" t="s" s="2">
         <v>848</v>
       </c>
-      <c r="M350" t="s" s="2">
+      <c r="N350" t="s" s="2">
         <v>849</v>
-      </c>
-      <c r="N350" t="s" s="2">
-        <v>850</v>
       </c>
       <c r="O350" s="2"/>
       <c r="P350" s="2"/>
@@ -42738,7 +42734,7 @@
         <v>23</v>
       </c>
       <c r="AG350" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AH350" t="s" s="2">
         <v>76</v>
@@ -42758,10 +42754,10 @@
         <v>717</v>
       </c>
       <c r="B351" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C351" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D351" s="2"/>
       <c r="E351" t="s" s="2">
@@ -42787,10 +42783,10 @@
         <v>97</v>
       </c>
       <c r="M351" t="s" s="2">
+        <v>851</v>
+      </c>
+      <c r="N351" t="s" s="2">
         <v>852</v>
-      </c>
-      <c r="N351" t="s" s="2">
-        <v>853</v>
       </c>
       <c r="O351" s="2"/>
       <c r="P351" s="2"/>
@@ -42841,7 +42837,7 @@
         <v>23</v>
       </c>
       <c r="AG351" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AH351" t="s" s="2">
         <v>76</v>
@@ -42861,10 +42857,10 @@
         <v>717</v>
       </c>
       <c r="B352" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C352" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D352" s="2"/>
       <c r="E352" t="s" s="2">
@@ -42890,10 +42886,10 @@
         <v>627</v>
       </c>
       <c r="M352" t="s" s="2">
+        <v>854</v>
+      </c>
+      <c r="N352" t="s" s="2">
         <v>855</v>
-      </c>
-      <c r="N352" t="s" s="2">
-        <v>856</v>
       </c>
       <c r="O352" s="2"/>
       <c r="P352" s="2"/>
@@ -42944,7 +42940,7 @@
         <v>23</v>
       </c>
       <c r="AG352" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AH352" t="s" s="2">
         <v>76</v>
@@ -42964,10 +42960,10 @@
         <v>717</v>
       </c>
       <c r="B353" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C353" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D353" s="2"/>
       <c r="E353" t="s" s="2">
@@ -42993,14 +42989,14 @@
         <v>112</v>
       </c>
       <c r="M353" t="s" s="2">
+        <v>857</v>
+      </c>
+      <c r="N353" t="s" s="2">
         <v>858</v>
-      </c>
-      <c r="N353" t="s" s="2">
-        <v>859</v>
       </c>
       <c r="O353" s="2"/>
       <c r="P353" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="Q353" t="s" s="2">
         <v>23</v>
@@ -43049,7 +43045,7 @@
         <v>23</v>
       </c>
       <c r="AG353" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AH353" t="s" s="2">
         <v>76</v>
@@ -43069,10 +43065,10 @@
         <v>717</v>
       </c>
       <c r="B354" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C354" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D354" s="2"/>
       <c r="E354" t="s" s="2">
@@ -43098,13 +43094,13 @@
         <v>367</v>
       </c>
       <c r="M354" t="s" s="2">
+        <v>861</v>
+      </c>
+      <c r="N354" t="s" s="2">
         <v>862</v>
       </c>
-      <c r="N354" t="s" s="2">
+      <c r="O354" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="O354" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="P354" s="2"/>
       <c r="Q354" t="s" s="2">
@@ -43133,11 +43129,11 @@
         <v>372</v>
       </c>
       <c r="Z354" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AA354" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="AA354" t="s" s="2">
-        <v>866</v>
-      </c>
       <c r="AB354" t="s" s="2">
         <v>23</v>
       </c>
@@ -43154,7 +43150,7 @@
         <v>23</v>
       </c>
       <c r="AG354" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AH354" t="s" s="2">
         <v>76</v>
@@ -43174,10 +43170,10 @@
         <v>717</v>
       </c>
       <c r="B355" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C355" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D355" s="2"/>
       <c r="E355" t="s" s="2">
@@ -43200,13 +43196,13 @@
         <v>23</v>
       </c>
       <c r="L355" t="s" s="2">
+        <v>867</v>
+      </c>
+      <c r="M355" t="s" s="2">
         <v>868</v>
       </c>
-      <c r="M355" t="s" s="2">
+      <c r="N355" t="s" s="2">
         <v>869</v>
-      </c>
-      <c r="N355" t="s" s="2">
-        <v>870</v>
       </c>
       <c r="O355" s="2"/>
       <c r="P355" s="2"/>
@@ -43257,7 +43253,7 @@
         <v>23</v>
       </c>
       <c r="AG355" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AH355" t="s" s="2">
         <v>76</v>
@@ -43277,10 +43273,10 @@
         <v>717</v>
       </c>
       <c r="B356" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C356" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D356" s="2"/>
       <c r="E356" t="s" s="2">
@@ -43306,10 +43302,10 @@
         <v>598</v>
       </c>
       <c r="M356" t="s" s="2">
+        <v>871</v>
+      </c>
+      <c r="N356" t="s" s="2">
         <v>872</v>
-      </c>
-      <c r="N356" t="s" s="2">
-        <v>873</v>
       </c>
       <c r="O356" s="2"/>
       <c r="P356" s="2"/>
@@ -43360,7 +43356,7 @@
         <v>23</v>
       </c>
       <c r="AG356" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AH356" t="s" s="2">
         <v>76</v>
@@ -43380,10 +43376,10 @@
         <v>717</v>
       </c>
       <c r="B357" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C357" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D357" s="2"/>
       <c r="E357" t="s" s="2">
@@ -43406,16 +43402,16 @@
         <v>23</v>
       </c>
       <c r="L357" t="s" s="2">
+        <v>874</v>
+      </c>
+      <c r="M357" t="s" s="2">
         <v>875</v>
       </c>
-      <c r="M357" t="s" s="2">
+      <c r="N357" t="s" s="2">
         <v>876</v>
       </c>
-      <c r="N357" t="s" s="2">
+      <c r="O357" t="s" s="2">
         <v>877</v>
-      </c>
-      <c r="O357" t="s" s="2">
-        <v>878</v>
       </c>
       <c r="P357" s="2"/>
       <c r="Q357" t="s" s="2">
@@ -43465,7 +43461,7 @@
         <v>23</v>
       </c>
       <c r="AG357" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AH357" t="s" s="2">
         <v>76</v>
@@ -43485,10 +43481,10 @@
         <v>717</v>
       </c>
       <c r="B358" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C358" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D358" s="2"/>
       <c r="E358" t="s" s="2">
@@ -43514,10 +43510,10 @@
         <v>136</v>
       </c>
       <c r="M358" t="s" s="2">
+        <v>879</v>
+      </c>
+      <c r="N358" t="s" s="2">
         <v>880</v>
-      </c>
-      <c r="N358" t="s" s="2">
-        <v>881</v>
       </c>
       <c r="O358" s="2"/>
       <c r="P358" s="2"/>
@@ -43568,7 +43564,7 @@
         <v>23</v>
       </c>
       <c r="AG358" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AH358" t="s" s="2">
         <v>76</v>
@@ -43588,10 +43584,10 @@
         <v>717</v>
       </c>
       <c r="B359" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C359" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D359" s="2"/>
       <c r="E359" t="s" s="2">
@@ -43691,10 +43687,10 @@
         <v>717</v>
       </c>
       <c r="B360" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C360" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D360" s="2"/>
       <c r="E360" t="s" s="2">
@@ -43796,10 +43792,10 @@
         <v>717</v>
       </c>
       <c r="B361" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C361" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D361" s="2"/>
       <c r="E361" t="s" s="2">
@@ -43903,10 +43899,10 @@
         <v>717</v>
       </c>
       <c r="B362" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C362" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D362" s="2"/>
       <c r="E362" t="s" s="2">
@@ -43932,13 +43928,13 @@
         <v>136</v>
       </c>
       <c r="M362" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="N362" t="s" s="2">
         <v>886</v>
       </c>
-      <c r="N362" t="s" s="2">
+      <c r="O362" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="O362" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="P362" s="2"/>
       <c r="Q362" t="s" s="2">
@@ -43988,7 +43984,7 @@
         <v>23</v>
       </c>
       <c r="AG362" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AH362" t="s" s="2">
         <v>76</v>
@@ -44008,10 +44004,10 @@
         <v>717</v>
       </c>
       <c r="B363" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C363" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D363" s="2"/>
       <c r="E363" t="s" s="2">
@@ -44111,10 +44107,10 @@
         <v>717</v>
       </c>
       <c r="B364" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C364" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D364" s="2"/>
       <c r="E364" t="s" s="2">
@@ -44216,10 +44212,10 @@
         <v>717</v>
       </c>
       <c r="B365" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C365" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D365" s="2"/>
       <c r="E365" t="s" s="2">
@@ -44323,10 +44319,10 @@
         <v>717</v>
       </c>
       <c r="B366" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C366" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D366" s="2"/>
       <c r="E366" t="s" s="2">
@@ -44352,10 +44348,10 @@
         <v>497</v>
       </c>
       <c r="M366" t="s" s="2">
+        <v>892</v>
+      </c>
+      <c r="N366" t="s" s="2">
         <v>893</v>
-      </c>
-      <c r="N366" t="s" s="2">
-        <v>894</v>
       </c>
       <c r="O366" s="2"/>
       <c r="P366" s="2"/>
@@ -44406,7 +44402,7 @@
         <v>23</v>
       </c>
       <c r="AG366" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AH366" t="s" s="2">
         <v>76</v>
@@ -44426,10 +44422,10 @@
         <v>717</v>
       </c>
       <c r="B367" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C367" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D367" s="2"/>
       <c r="E367" t="s" s="2">
@@ -44452,13 +44448,13 @@
         <v>23</v>
       </c>
       <c r="L367" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="M367" t="s" s="2">
         <v>896</v>
       </c>
-      <c r="M367" t="s" s="2">
+      <c r="N367" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="N367" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="O367" s="2"/>
       <c r="P367" s="2"/>
@@ -44509,7 +44505,7 @@
         <v>23</v>
       </c>
       <c r="AG367" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AH367" t="s" s="2">
         <v>76</v>
@@ -44529,10 +44525,10 @@
         <v>717</v>
       </c>
       <c r="B368" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C368" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D368" s="2"/>
       <c r="E368" t="s" s="2">
@@ -44555,13 +44551,13 @@
         <v>23</v>
       </c>
       <c r="L368" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M368" t="s" s="2">
+        <v>899</v>
+      </c>
+      <c r="N368" t="s" s="2">
         <v>900</v>
-      </c>
-      <c r="N368" t="s" s="2">
-        <v>901</v>
       </c>
       <c r="O368" s="2"/>
       <c r="P368" s="2"/>
@@ -44612,7 +44608,7 @@
         <v>23</v>
       </c>
       <c r="AG368" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="AH368" t="s" s="2">
         <v>76</v>
@@ -44632,10 +44628,10 @@
         <v>717</v>
       </c>
       <c r="B369" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C369" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D369" s="2"/>
       <c r="E369" t="s" s="2">
@@ -44658,19 +44654,19 @@
         <v>23</v>
       </c>
       <c r="L369" t="s" s="2">
+        <v>902</v>
+      </c>
+      <c r="M369" t="s" s="2">
         <v>903</v>
       </c>
-      <c r="M369" t="s" s="2">
+      <c r="N369" t="s" s="2">
         <v>904</v>
       </c>
-      <c r="N369" t="s" s="2">
+      <c r="O369" t="s" s="2">
         <v>905</v>
       </c>
-      <c r="O369" t="s" s="2">
+      <c r="P369" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="P369" t="s" s="2">
-        <v>907</v>
       </c>
       <c r="Q369" t="s" s="2">
         <v>23</v>
@@ -44719,7 +44715,7 @@
         <v>23</v>
       </c>
       <c r="AG369" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AH369" t="s" s="2">
         <v>76</v>
@@ -44739,10 +44735,10 @@
         <v>717</v>
       </c>
       <c r="B370" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C370" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D370" s="2"/>
       <c r="E370" t="s" s="2">
@@ -44768,13 +44764,13 @@
         <v>130</v>
       </c>
       <c r="M370" t="s" s="2">
+        <v>908</v>
+      </c>
+      <c r="N370" t="s" s="2">
         <v>909</v>
       </c>
-      <c r="N370" t="s" s="2">
+      <c r="O370" t="s" s="2">
         <v>910</v>
-      </c>
-      <c r="O370" t="s" s="2">
-        <v>911</v>
       </c>
       <c r="P370" s="2"/>
       <c r="Q370" t="s" s="2">
@@ -44824,7 +44820,7 @@
         <v>23</v>
       </c>
       <c r="AG370" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AH370" t="s" s="2">
         <v>76</v>
@@ -44844,10 +44840,10 @@
         <v>717</v>
       </c>
       <c r="B371" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C371" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D371" s="2"/>
       <c r="E371" t="s" s="2">
@@ -44873,10 +44869,10 @@
         <v>497</v>
       </c>
       <c r="M371" t="s" s="2">
+        <v>912</v>
+      </c>
+      <c r="N371" t="s" s="2">
         <v>913</v>
-      </c>
-      <c r="N371" t="s" s="2">
-        <v>914</v>
       </c>
       <c r="O371" s="2"/>
       <c r="P371" s="2"/>
@@ -44927,7 +44923,7 @@
         <v>23</v>
       </c>
       <c r="AG371" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AH371" t="s" s="2">
         <v>76</v>
@@ -44947,10 +44943,10 @@
         <v>717</v>
       </c>
       <c r="B372" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C372" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D372" s="2"/>
       <c r="E372" t="s" s="2">
@@ -44973,16 +44969,16 @@
         <v>23</v>
       </c>
       <c r="L372" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M372" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="N372" t="s" s="2">
         <v>916</v>
       </c>
-      <c r="N372" t="s" s="2">
+      <c r="O372" t="s" s="2">
         <v>917</v>
-      </c>
-      <c r="O372" t="s" s="2">
-        <v>918</v>
       </c>
       <c r="P372" s="2"/>
       <c r="Q372" t="s" s="2">
@@ -45032,7 +45028,7 @@
         <v>23</v>
       </c>
       <c r="AG372" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AH372" t="s" s="2">
         <v>76</v>
@@ -45052,10 +45048,10 @@
         <v>717</v>
       </c>
       <c r="B373" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="C373" t="s" s="2">
-        <v>919</v>
+        <v>918</v>
       </c>
       <c r="D373" s="2"/>
       <c r="E373" t="s" s="2">
@@ -45155,10 +45151,10 @@
         <v>717</v>
       </c>
       <c r="B374" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="C374" t="s" s="2">
-        <v>920</v>
+        <v>919</v>
       </c>
       <c r="D374" s="2"/>
       <c r="E374" t="s" s="2">
@@ -45260,10 +45256,10 @@
         <v>717</v>
       </c>
       <c r="B375" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="C375" t="s" s="2">
-        <v>921</v>
+        <v>920</v>
       </c>
       <c r="D375" s="2"/>
       <c r="E375" t="s" s="2">
@@ -45289,7 +45285,7 @@
         <v>199</v>
       </c>
       <c r="M375" t="s" s="2">
-        <v>922</v>
+        <v>921</v>
       </c>
       <c r="N375" t="s" s="2">
         <v>450</v>
@@ -45367,10 +45363,10 @@
         <v>717</v>
       </c>
       <c r="B376" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="C376" t="s" s="2">
-        <v>923</v>
+        <v>922</v>
       </c>
       <c r="D376" s="2"/>
       <c r="E376" t="s" s="2">
@@ -45399,7 +45395,7 @@
         <v>456</v>
       </c>
       <c r="N376" t="s" s="2">
-        <v>924</v>
+        <v>923</v>
       </c>
       <c r="O376" s="2"/>
       <c r="P376" t="s" s="2">
@@ -45474,10 +45470,10 @@
         <v>717</v>
       </c>
       <c r="B377" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="C377" t="s" s="2">
-        <v>925</v>
+        <v>924</v>
       </c>
       <c r="D377" s="2"/>
       <c r="E377" t="s" s="2">
@@ -45579,10 +45575,10 @@
         <v>717</v>
       </c>
       <c r="B378" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="C378" t="s" s="2">
-        <v>926</v>
+        <v>925</v>
       </c>
       <c r="D378" s="2"/>
       <c r="E378" t="s" s="2">
@@ -45684,10 +45680,10 @@
         <v>717</v>
       </c>
       <c r="B379" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="C379" t="s" s="2">
-        <v>927</v>
+        <v>926</v>
       </c>
       <c r="D379" s="2"/>
       <c r="E379" t="s" s="2">
@@ -45791,10 +45787,10 @@
         <v>717</v>
       </c>
       <c r="B380" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C380" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D380" s="2"/>
       <c r="E380" t="s" s="2">
@@ -45820,10 +45816,10 @@
         <v>670</v>
       </c>
       <c r="M380" t="s" s="2">
+        <v>928</v>
+      </c>
+      <c r="N380" t="s" s="2">
         <v>929</v>
-      </c>
-      <c r="N380" t="s" s="2">
-        <v>930</v>
       </c>
       <c r="O380" s="2"/>
       <c r="P380" s="2"/>
@@ -45874,7 +45870,7 @@
         <v>23</v>
       </c>
       <c r="AG380" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AH380" t="s" s="2">
         <v>76</v>
@@ -45894,10 +45890,10 @@
         <v>717</v>
       </c>
       <c r="B381" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C381" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D381" s="2"/>
       <c r="E381" t="s" s="2">
@@ -45923,10 +45919,10 @@
         <v>136</v>
       </c>
       <c r="M381" t="s" s="2">
+        <v>931</v>
+      </c>
+      <c r="N381" t="s" s="2">
         <v>932</v>
-      </c>
-      <c r="N381" t="s" s="2">
-        <v>933</v>
       </c>
       <c r="O381" s="2"/>
       <c r="P381" s="2"/>
@@ -45977,7 +45973,7 @@
         <v>23</v>
       </c>
       <c r="AG381" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AH381" t="s" s="2">
         <v>76</v>
@@ -45997,10 +45993,10 @@
         <v>717</v>
       </c>
       <c r="B382" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C382" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D382" s="2"/>
       <c r="E382" t="s" s="2">
@@ -46100,10 +46096,10 @@
         <v>717</v>
       </c>
       <c r="B383" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C383" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D383" s="2"/>
       <c r="E383" t="s" s="2">
@@ -46205,10 +46201,10 @@
         <v>717</v>
       </c>
       <c r="B384" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C384" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D384" s="2"/>
       <c r="E384" t="s" s="2">
@@ -46312,10 +46308,10 @@
         <v>717</v>
       </c>
       <c r="B385" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C385" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D385" s="2"/>
       <c r="E385" t="s" s="2">
@@ -46338,16 +46334,16 @@
         <v>23</v>
       </c>
       <c r="L385" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="M385" t="s" s="2">
         <v>938</v>
       </c>
-      <c r="M385" t="s" s="2">
+      <c r="N385" t="s" s="2">
         <v>939</v>
       </c>
-      <c r="N385" t="s" s="2">
+      <c r="O385" t="s" s="2">
         <v>940</v>
-      </c>
-      <c r="O385" t="s" s="2">
-        <v>941</v>
       </c>
       <c r="P385" s="2"/>
       <c r="Q385" t="s" s="2">
@@ -46376,11 +46372,11 @@
         <v>372</v>
       </c>
       <c r="Z385" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="AA385" t="s" s="2">
         <v>942</v>
       </c>
-      <c r="AA385" t="s" s="2">
-        <v>943</v>
-      </c>
       <c r="AB385" t="s" s="2">
         <v>23</v>
       </c>
@@ -46397,7 +46393,7 @@
         <v>23</v>
       </c>
       <c r="AG385" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AH385" t="s" s="2">
         <v>83</v>
@@ -46417,10 +46413,10 @@
         <v>717</v>
       </c>
       <c r="B386" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C386" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D386" s="2"/>
       <c r="E386" t="s" s="2">
@@ -46446,10 +46442,10 @@
         <v>367</v>
       </c>
       <c r="M386" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="N386" t="s" s="2">
         <v>945</v>
-      </c>
-      <c r="N386" t="s" s="2">
-        <v>946</v>
       </c>
       <c r="O386" s="2"/>
       <c r="P386" s="2"/>
@@ -46479,11 +46475,11 @@
         <v>372</v>
       </c>
       <c r="Z386" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="AA386" t="s" s="2">
         <v>947</v>
       </c>
-      <c r="AA386" t="s" s="2">
-        <v>948</v>
-      </c>
       <c r="AB386" t="s" s="2">
         <v>23</v>
       </c>
@@ -46500,7 +46496,7 @@
         <v>23</v>
       </c>
       <c r="AG386" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AH386" t="s" s="2">
         <v>76</v>
@@ -46520,10 +46516,10 @@
         <v>717</v>
       </c>
       <c r="B387" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C387" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D387" s="2"/>
       <c r="E387" t="s" s="2">
@@ -46546,13 +46542,13 @@
         <v>23</v>
       </c>
       <c r="L387" t="s" s="2">
+        <v>949</v>
+      </c>
+      <c r="M387" t="s" s="2">
         <v>950</v>
       </c>
-      <c r="M387" t="s" s="2">
+      <c r="N387" t="s" s="2">
         <v>951</v>
-      </c>
-      <c r="N387" t="s" s="2">
-        <v>952</v>
       </c>
       <c r="O387" s="2"/>
       <c r="P387" s="2"/>
@@ -46603,7 +46599,7 @@
         <v>23</v>
       </c>
       <c r="AG387" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AH387" t="s" s="2">
         <v>76</v>
@@ -46623,14 +46619,14 @@
         <v>717</v>
       </c>
       <c r="B388" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C388" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D388" s="2"/>
       <c r="E388" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F388" s="2"/>
       <c r="G388" t="s" s="2">
@@ -46649,16 +46645,16 @@
         <v>23</v>
       </c>
       <c r="L388" t="s" s="2">
+        <v>954</v>
+      </c>
+      <c r="M388" t="s" s="2">
         <v>955</v>
       </c>
-      <c r="M388" t="s" s="2">
+      <c r="N388" t="s" s="2">
         <v>956</v>
       </c>
-      <c r="N388" t="s" s="2">
+      <c r="O388" t="s" s="2">
         <v>957</v>
-      </c>
-      <c r="O388" t="s" s="2">
-        <v>958</v>
       </c>
       <c r="P388" s="2"/>
       <c r="Q388" t="s" s="2">
@@ -46708,7 +46704,7 @@
         <v>23</v>
       </c>
       <c r="AG388" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AH388" t="s" s="2">
         <v>76</v>
@@ -46728,10 +46724,10 @@
         <v>717</v>
       </c>
       <c r="B389" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C389" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D389" s="2"/>
       <c r="E389" t="s" s="2">
@@ -46754,16 +46750,16 @@
         <v>23</v>
       </c>
       <c r="L389" t="s" s="2">
+        <v>959</v>
+      </c>
+      <c r="M389" t="s" s="2">
         <v>960</v>
       </c>
-      <c r="M389" t="s" s="2">
+      <c r="N389" t="s" s="2">
         <v>961</v>
       </c>
-      <c r="N389" t="s" s="2">
+      <c r="O389" t="s" s="2">
         <v>962</v>
-      </c>
-      <c r="O389" t="s" s="2">
-        <v>963</v>
       </c>
       <c r="P389" s="2"/>
       <c r="Q389" t="s" s="2">
@@ -46813,7 +46809,7 @@
         <v>23</v>
       </c>
       <c r="AG389" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AH389" t="s" s="2">
         <v>76</v>
@@ -46830,7 +46826,7 @@
     </row>
     <row r="390">
       <c r="A390" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B390" t="s" s="2">
         <v>722</v>
@@ -46933,7 +46929,7 @@
     </row>
     <row r="391">
       <c r="A391" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B391" t="s" s="2">
         <v>725</v>
@@ -47038,7 +47034,7 @@
     </row>
     <row r="392">
       <c r="A392" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B392" t="s" s="2">
         <v>726</v>
@@ -47141,7 +47137,7 @@
     </row>
     <row r="393">
       <c r="A393" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B393" t="s" s="2">
         <v>727</v>
@@ -47246,7 +47242,7 @@
     </row>
     <row r="394">
       <c r="A394" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B394" t="s" s="2">
         <v>728</v>
@@ -47351,7 +47347,7 @@
     </row>
     <row r="395">
       <c r="A395" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B395" t="s" s="2">
         <v>729</v>
@@ -47456,7 +47452,7 @@
     </row>
     <row r="396">
       <c r="A396" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B396" t="s" s="2">
         <v>730</v>
@@ -47561,7 +47557,7 @@
     </row>
     <row r="397">
       <c r="A397" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B397" t="s" s="2">
         <v>731</v>
@@ -47662,7 +47658,7 @@
     </row>
     <row r="398">
       <c r="A398" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B398" t="s" s="2">
         <v>734</v>
@@ -47769,7 +47765,7 @@
     </row>
     <row r="399">
       <c r="A399" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B399" t="s" s="2">
         <v>741</v>
@@ -47876,7 +47872,7 @@
     </row>
     <row r="400">
       <c r="A400" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B400" t="s" s="2">
         <v>747</v>
@@ -47983,7 +47979,7 @@
     </row>
     <row r="401">
       <c r="A401" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B401" t="s" s="2">
         <v>748</v>
@@ -48015,7 +48011,7 @@
         <v>112</v>
       </c>
       <c r="M401" t="s" s="2">
-        <v>969</v>
+        <v>968</v>
       </c>
       <c r="N401" t="s" s="2">
         <v>750</v>
@@ -48088,7 +48084,7 @@
     </row>
     <row r="402">
       <c r="A402" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B402" t="s" s="2">
         <v>752</v>
@@ -48120,7 +48116,7 @@
         <v>103</v>
       </c>
       <c r="M402" t="s" s="2">
-        <v>970</v>
+        <v>969</v>
       </c>
       <c r="N402" t="s" s="2">
         <v>754</v>
@@ -48156,7 +48152,7 @@
       </c>
       <c r="Z402" s="2"/>
       <c r="AA402" t="s" s="2">
-        <v>971</v>
+        <v>970</v>
       </c>
       <c r="AB402" t="s" s="2">
         <v>23</v>
@@ -48191,7 +48187,7 @@
     </row>
     <row r="403">
       <c r="A403" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B403" t="s" s="2">
         <v>756</v>
@@ -48223,7 +48219,7 @@
         <v>367</v>
       </c>
       <c r="M403" t="s" s="2">
-        <v>972</v>
+        <v>971</v>
       </c>
       <c r="N403" t="s" s="2">
         <v>758</v>
@@ -48296,13 +48292,13 @@
     </row>
     <row r="404">
       <c r="A404" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B404" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="C404" t="s" s="2">
-        <v>973</v>
+        <v>972</v>
       </c>
       <c r="D404" s="2"/>
       <c r="E404" t="s" s="2">
@@ -48399,13 +48395,13 @@
     </row>
     <row r="405">
       <c r="A405" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B405" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="C405" t="s" s="2">
-        <v>974</v>
+        <v>973</v>
       </c>
       <c r="D405" s="2"/>
       <c r="E405" t="s" s="2">
@@ -48504,13 +48500,13 @@
     </row>
     <row r="406">
       <c r="A406" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B406" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="C406" t="s" s="2">
-        <v>975</v>
+        <v>974</v>
       </c>
       <c r="D406" s="2"/>
       <c r="E406" t="s" s="2">
@@ -48533,19 +48529,19 @@
         <v>84</v>
       </c>
       <c r="L406" t="s" s="2">
+        <v>975</v>
+      </c>
+      <c r="M406" t="s" s="2">
         <v>976</v>
       </c>
-      <c r="M406" t="s" s="2">
+      <c r="N406" t="s" s="2">
         <v>977</v>
       </c>
-      <c r="N406" t="s" s="2">
+      <c r="O406" t="s" s="2">
         <v>978</v>
       </c>
-      <c r="O406" t="s" s="2">
+      <c r="P406" t="s" s="2">
         <v>979</v>
-      </c>
-      <c r="P406" t="s" s="2">
-        <v>980</v>
       </c>
       <c r="Q406" t="s" s="2">
         <v>23</v>
@@ -48594,7 +48590,7 @@
         <v>23</v>
       </c>
       <c r="AG406" t="s" s="2">
-        <v>981</v>
+        <v>980</v>
       </c>
       <c r="AH406" t="s" s="2">
         <v>76</v>
@@ -48611,13 +48607,13 @@
     </row>
     <row r="407">
       <c r="A407" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B407" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="C407" t="s" s="2">
-        <v>982</v>
+        <v>981</v>
       </c>
       <c r="D407" s="2"/>
       <c r="E407" t="s" s="2">
@@ -48643,16 +48639,16 @@
         <v>141</v>
       </c>
       <c r="M407" t="s" s="2">
+        <v>982</v>
+      </c>
+      <c r="N407" t="s" s="2">
         <v>983</v>
       </c>
-      <c r="N407" t="s" s="2">
+      <c r="O407" t="s" s="2">
         <v>984</v>
       </c>
-      <c r="O407" t="s" s="2">
+      <c r="P407" t="s" s="2">
         <v>985</v>
-      </c>
-      <c r="P407" t="s" s="2">
-        <v>986</v>
       </c>
       <c r="Q407" t="s" s="2">
         <v>23</v>
@@ -48701,7 +48697,7 @@
         <v>23</v>
       </c>
       <c r="AG407" t="s" s="2">
-        <v>987</v>
+        <v>986</v>
       </c>
       <c r="AH407" t="s" s="2">
         <v>76</v>
@@ -48718,7 +48714,7 @@
     </row>
     <row r="408">
       <c r="A408" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B408" t="s" s="2">
         <v>762</v>
@@ -48750,7 +48746,7 @@
         <v>103</v>
       </c>
       <c r="M408" t="s" s="2">
-        <v>988</v>
+        <v>987</v>
       </c>
       <c r="N408" t="s" s="2">
         <v>764</v>
@@ -48823,7 +48819,7 @@
     </row>
     <row r="409">
       <c r="A409" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B409" t="s" s="2">
         <v>769</v>
@@ -48872,7 +48868,7 @@
         <v>23</v>
       </c>
       <c r="T409" t="s" s="2">
-        <v>989</v>
+        <v>988</v>
       </c>
       <c r="U409" t="s" s="2">
         <v>23</v>
@@ -48928,7 +48924,7 @@
     </row>
     <row r="410">
       <c r="A410" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B410" t="s" s="2">
         <v>785</v>
@@ -48960,7 +48956,7 @@
         <v>103</v>
       </c>
       <c r="M410" t="s" s="2">
-        <v>990</v>
+        <v>989</v>
       </c>
       <c r="N410" t="s" s="2">
         <v>787</v>
@@ -49031,7 +49027,7 @@
     </row>
     <row r="411">
       <c r="A411" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B411" t="s" s="2">
         <v>790</v>
@@ -49063,7 +49059,7 @@
         <v>385</v>
       </c>
       <c r="M411" t="s" s="2">
-        <v>991</v>
+        <v>990</v>
       </c>
       <c r="N411" t="s" s="2">
         <v>792</v>
@@ -49136,7 +49132,7 @@
     </row>
     <row r="412">
       <c r="A412" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B412" t="s" s="2">
         <v>794</v>
@@ -49168,7 +49164,7 @@
         <v>385</v>
       </c>
       <c r="M412" t="s" s="2">
-        <v>992</v>
+        <v>991</v>
       </c>
       <c r="N412" t="s" s="2">
         <v>797</v>
@@ -49237,16 +49233,16 @@
     </row>
     <row r="413">
       <c r="A413" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B413" t="s" s="2">
-        <v>993</v>
+        <v>992</v>
       </c>
       <c r="C413" t="s" s="2">
         <v>794</v>
       </c>
       <c r="D413" t="s" s="2">
-        <v>994</v>
+        <v>993</v>
       </c>
       <c r="E413" t="s" s="2">
         <v>23</v>
@@ -49268,10 +49264,10 @@
         <v>84</v>
       </c>
       <c r="L413" t="s" s="2">
+        <v>994</v>
+      </c>
+      <c r="M413" t="s" s="2">
         <v>995</v>
-      </c>
-      <c r="M413" t="s" s="2">
-        <v>996</v>
       </c>
       <c r="N413" t="s" s="2">
         <v>797</v>
@@ -49342,16 +49338,16 @@
     </row>
     <row r="414">
       <c r="A414" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B414" t="s" s="2">
-        <v>997</v>
+        <v>996</v>
       </c>
       <c r="C414" t="s" s="2">
         <v>794</v>
       </c>
       <c r="D414" t="s" s="2">
-        <v>998</v>
+        <v>997</v>
       </c>
       <c r="E414" t="s" s="2">
         <v>23</v>
@@ -49376,7 +49372,7 @@
         <v>385</v>
       </c>
       <c r="M414" t="s" s="2">
-        <v>999</v>
+        <v>998</v>
       </c>
       <c r="N414" t="s" s="2">
         <v>797</v>
@@ -49447,7 +49443,7 @@
     </row>
     <row r="415">
       <c r="A415" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B415" t="s" s="2">
         <v>798</v>
@@ -49479,7 +49475,7 @@
         <v>799</v>
       </c>
       <c r="M415" t="s" s="2">
-        <v>1000</v>
+        <v>999</v>
       </c>
       <c r="N415" t="s" s="2">
         <v>801</v>
@@ -49552,7 +49548,7 @@
     </row>
     <row r="416">
       <c r="A416" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B416" t="s" s="2">
         <v>803</v>
@@ -49581,16 +49577,16 @@
         <v>84</v>
       </c>
       <c r="L416" t="s" s="2">
-        <v>804</v>
+        <v>568</v>
       </c>
       <c r="M416" t="s" s="2">
-        <v>1001</v>
+        <v>1000</v>
       </c>
       <c r="N416" t="s" s="2">
+        <v>805</v>
+      </c>
+      <c r="O416" t="s" s="2">
         <v>806</v>
-      </c>
-      <c r="O416" t="s" s="2">
-        <v>807</v>
       </c>
       <c r="P416" s="2"/>
       <c r="Q416" t="s" s="2">
@@ -49657,13 +49653,13 @@
     </row>
     <row r="417">
       <c r="A417" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B417" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="C417" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="D417" s="2"/>
       <c r="E417" t="s" s="2">
@@ -49689,13 +49685,13 @@
         <v>574</v>
       </c>
       <c r="M417" t="s" s="2">
-        <v>1002</v>
+        <v>1001</v>
       </c>
       <c r="N417" t="s" s="2">
+        <v>809</v>
+      </c>
+      <c r="O417" t="s" s="2">
         <v>810</v>
-      </c>
-      <c r="O417" t="s" s="2">
-        <v>811</v>
       </c>
       <c r="P417" s="2"/>
       <c r="Q417" t="s" s="2">
@@ -49745,7 +49741,7 @@
         <v>23</v>
       </c>
       <c r="AG417" t="s" s="2">
-        <v>808</v>
+        <v>807</v>
       </c>
       <c r="AH417" t="s" s="2">
         <v>76</v>
@@ -49762,13 +49758,13 @@
     </row>
     <row r="418">
       <c r="A418" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B418" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="C418" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="D418" s="2"/>
       <c r="E418" t="s" s="2">
@@ -49791,13 +49787,13 @@
         <v>23</v>
       </c>
       <c r="L418" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M418" t="s" s="2">
-        <v>1003</v>
+        <v>1002</v>
       </c>
       <c r="N418" t="s" s="2">
-        <v>815</v>
+        <v>814</v>
       </c>
       <c r="O418" s="2"/>
       <c r="P418" s="2"/>
@@ -49848,7 +49844,7 @@
         <v>23</v>
       </c>
       <c r="AG418" t="s" s="2">
-        <v>812</v>
+        <v>811</v>
       </c>
       <c r="AH418" t="s" s="2">
         <v>76</v>
@@ -49865,13 +49861,13 @@
     </row>
     <row r="419">
       <c r="A419" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B419" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="C419" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="D419" s="2"/>
       <c r="E419" t="s" s="2">
@@ -49897,10 +49893,10 @@
         <v>578</v>
       </c>
       <c r="M419" t="s" s="2">
-        <v>1004</v>
+        <v>1003</v>
       </c>
       <c r="N419" t="s" s="2">
-        <v>818</v>
+        <v>817</v>
       </c>
       <c r="O419" s="2"/>
       <c r="P419" s="2"/>
@@ -49951,7 +49947,7 @@
         <v>23</v>
       </c>
       <c r="AG419" t="s" s="2">
-        <v>816</v>
+        <v>815</v>
       </c>
       <c r="AH419" t="s" s="2">
         <v>76</v>
@@ -49968,13 +49964,13 @@
     </row>
     <row r="420">
       <c r="A420" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B420" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="C420" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="D420" s="2"/>
       <c r="E420" t="s" s="2">
@@ -49997,13 +49993,13 @@
         <v>84</v>
       </c>
       <c r="L420" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M420" t="s" s="2">
-        <v>1005</v>
+        <v>1004</v>
       </c>
       <c r="N420" t="s" s="2">
-        <v>822</v>
+        <v>821</v>
       </c>
       <c r="O420" s="2"/>
       <c r="P420" s="2"/>
@@ -50054,7 +50050,7 @@
         <v>23</v>
       </c>
       <c r="AG420" t="s" s="2">
-        <v>819</v>
+        <v>818</v>
       </c>
       <c r="AH420" t="s" s="2">
         <v>76</v>
@@ -50071,13 +50067,13 @@
     </row>
     <row r="421">
       <c r="A421" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B421" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="C421" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="D421" s="2"/>
       <c r="E421" t="s" s="2">
@@ -50100,13 +50096,13 @@
         <v>23</v>
       </c>
       <c r="L421" t="s" s="2">
-        <v>824</v>
+        <v>823</v>
       </c>
       <c r="M421" t="s" s="2">
-        <v>1006</v>
+        <v>1005</v>
       </c>
       <c r="N421" t="s" s="2">
-        <v>826</v>
+        <v>825</v>
       </c>
       <c r="O421" s="2"/>
       <c r="P421" s="2"/>
@@ -50157,7 +50153,7 @@
         <v>23</v>
       </c>
       <c r="AG421" t="s" s="2">
-        <v>823</v>
+        <v>822</v>
       </c>
       <c r="AH421" t="s" s="2">
         <v>76</v>
@@ -50174,13 +50170,13 @@
     </row>
     <row r="422">
       <c r="A422" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B422" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="C422" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="D422" s="2"/>
       <c r="E422" t="s" s="2">
@@ -50206,13 +50202,13 @@
         <v>367</v>
       </c>
       <c r="M422" t="s" s="2">
-        <v>1007</v>
+        <v>1006</v>
       </c>
       <c r="N422" t="s" s="2">
+        <v>827</v>
+      </c>
+      <c r="O422" t="s" s="2">
         <v>828</v>
-      </c>
-      <c r="O422" t="s" s="2">
-        <v>829</v>
       </c>
       <c r="P422" s="2"/>
       <c r="Q422" t="s" s="2">
@@ -50241,11 +50237,11 @@
         <v>372</v>
       </c>
       <c r="Z422" t="s" s="2">
+        <v>829</v>
+      </c>
+      <c r="AA422" t="s" s="2">
         <v>830</v>
       </c>
-      <c r="AA422" t="s" s="2">
-        <v>831</v>
-      </c>
       <c r="AB422" t="s" s="2">
         <v>23</v>
       </c>
@@ -50262,7 +50258,7 @@
         <v>23</v>
       </c>
       <c r="AG422" t="s" s="2">
-        <v>827</v>
+        <v>826</v>
       </c>
       <c r="AH422" t="s" s="2">
         <v>76</v>
@@ -50279,13 +50275,13 @@
     </row>
     <row r="423">
       <c r="A423" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B423" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="C423" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="D423" s="2"/>
       <c r="E423" t="s" s="2">
@@ -50308,13 +50304,13 @@
         <v>23</v>
       </c>
       <c r="L423" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M423" t="s" s="2">
-        <v>1008</v>
+        <v>1007</v>
       </c>
       <c r="N423" t="s" s="2">
-        <v>835</v>
+        <v>834</v>
       </c>
       <c r="O423" s="2"/>
       <c r="P423" s="2"/>
@@ -50365,7 +50361,7 @@
         <v>23</v>
       </c>
       <c r="AG423" t="s" s="2">
-        <v>832</v>
+        <v>831</v>
       </c>
       <c r="AH423" t="s" s="2">
         <v>76</v>
@@ -50382,13 +50378,13 @@
     </row>
     <row r="424">
       <c r="A424" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B424" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="C424" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="D424" s="2"/>
       <c r="E424" t="s" s="2">
@@ -50414,13 +50410,13 @@
         <v>367</v>
       </c>
       <c r="M424" t="s" s="2">
-        <v>1009</v>
+        <v>1008</v>
       </c>
       <c r="N424" t="s" s="2">
+        <v>837</v>
+      </c>
+      <c r="O424" t="s" s="2">
         <v>838</v>
-      </c>
-      <c r="O424" t="s" s="2">
-        <v>839</v>
       </c>
       <c r="P424" s="2"/>
       <c r="Q424" t="s" s="2">
@@ -50449,11 +50445,11 @@
         <v>372</v>
       </c>
       <c r="Z424" t="s" s="2">
+        <v>839</v>
+      </c>
+      <c r="AA424" t="s" s="2">
         <v>840</v>
       </c>
-      <c r="AA424" t="s" s="2">
-        <v>841</v>
-      </c>
       <c r="AB424" t="s" s="2">
         <v>23</v>
       </c>
@@ -50470,7 +50466,7 @@
         <v>23</v>
       </c>
       <c r="AG424" t="s" s="2">
-        <v>836</v>
+        <v>835</v>
       </c>
       <c r="AH424" t="s" s="2">
         <v>76</v>
@@ -50487,13 +50483,13 @@
     </row>
     <row r="425">
       <c r="A425" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B425" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="C425" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="D425" s="2"/>
       <c r="E425" t="s" s="2">
@@ -50516,16 +50512,16 @@
         <v>23</v>
       </c>
       <c r="L425" t="s" s="2">
+        <v>842</v>
+      </c>
+      <c r="M425" t="s" s="2">
         <v>843</v>
       </c>
-      <c r="M425" t="s" s="2">
+      <c r="N425" t="s" s="2">
         <v>844</v>
       </c>
-      <c r="N425" t="s" s="2">
+      <c r="O425" t="s" s="2">
         <v>845</v>
-      </c>
-      <c r="O425" t="s" s="2">
-        <v>846</v>
       </c>
       <c r="P425" s="2"/>
       <c r="Q425" t="s" s="2">
@@ -50575,7 +50571,7 @@
         <v>23</v>
       </c>
       <c r="AG425" t="s" s="2">
-        <v>842</v>
+        <v>841</v>
       </c>
       <c r="AH425" t="s" s="2">
         <v>76</v>
@@ -50592,13 +50588,13 @@
     </row>
     <row r="426">
       <c r="A426" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B426" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="C426" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="D426" s="2"/>
       <c r="E426" t="s" s="2">
@@ -50621,13 +50617,13 @@
         <v>84</v>
       </c>
       <c r="L426" t="s" s="2">
-        <v>848</v>
+        <v>847</v>
       </c>
       <c r="M426" t="s" s="2">
-        <v>1010</v>
+        <v>1009</v>
       </c>
       <c r="N426" t="s" s="2">
-        <v>850</v>
+        <v>849</v>
       </c>
       <c r="O426" s="2"/>
       <c r="P426" s="2"/>
@@ -50678,7 +50674,7 @@
         <v>23</v>
       </c>
       <c r="AG426" t="s" s="2">
-        <v>847</v>
+        <v>846</v>
       </c>
       <c r="AH426" t="s" s="2">
         <v>76</v>
@@ -50695,13 +50691,13 @@
     </row>
     <row r="427">
       <c r="A427" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B427" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="C427" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="D427" s="2"/>
       <c r="E427" t="s" s="2">
@@ -50727,10 +50723,10 @@
         <v>97</v>
       </c>
       <c r="M427" t="s" s="2">
-        <v>1011</v>
+        <v>1010</v>
       </c>
       <c r="N427" t="s" s="2">
-        <v>853</v>
+        <v>852</v>
       </c>
       <c r="O427" s="2"/>
       <c r="P427" s="2"/>
@@ -50781,7 +50777,7 @@
         <v>23</v>
       </c>
       <c r="AG427" t="s" s="2">
-        <v>851</v>
+        <v>850</v>
       </c>
       <c r="AH427" t="s" s="2">
         <v>76</v>
@@ -50798,13 +50794,13 @@
     </row>
     <row r="428">
       <c r="A428" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B428" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="C428" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="D428" s="2"/>
       <c r="E428" t="s" s="2">
@@ -50827,13 +50823,13 @@
         <v>84</v>
       </c>
       <c r="L428" t="s" s="2">
+        <v>1011</v>
+      </c>
+      <c r="M428" t="s" s="2">
         <v>1012</v>
       </c>
-      <c r="M428" t="s" s="2">
-        <v>1013</v>
-      </c>
       <c r="N428" t="s" s="2">
-        <v>856</v>
+        <v>855</v>
       </c>
       <c r="O428" s="2"/>
       <c r="P428" s="2"/>
@@ -50884,7 +50880,7 @@
         <v>23</v>
       </c>
       <c r="AG428" t="s" s="2">
-        <v>854</v>
+        <v>853</v>
       </c>
       <c r="AH428" t="s" s="2">
         <v>76</v>
@@ -50901,13 +50897,13 @@
     </row>
     <row r="429">
       <c r="A429" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B429" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="C429" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="D429" s="2"/>
       <c r="E429" t="s" s="2">
@@ -50933,14 +50929,14 @@
         <v>112</v>
       </c>
       <c r="M429" t="s" s="2">
-        <v>1014</v>
+        <v>1013</v>
       </c>
       <c r="N429" t="s" s="2">
-        <v>859</v>
+        <v>858</v>
       </c>
       <c r="O429" s="2"/>
       <c r="P429" t="s" s="2">
-        <v>860</v>
+        <v>859</v>
       </c>
       <c r="Q429" t="s" s="2">
         <v>23</v>
@@ -50989,7 +50985,7 @@
         <v>23</v>
       </c>
       <c r="AG429" t="s" s="2">
-        <v>857</v>
+        <v>856</v>
       </c>
       <c r="AH429" t="s" s="2">
         <v>76</v>
@@ -51006,13 +51002,13 @@
     </row>
     <row r="430">
       <c r="A430" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B430" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="C430" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="D430" s="2"/>
       <c r="E430" t="s" s="2">
@@ -51038,13 +51034,13 @@
         <v>367</v>
       </c>
       <c r="M430" t="s" s="2">
-        <v>1015</v>
+        <v>1014</v>
       </c>
       <c r="N430" t="s" s="2">
+        <v>862</v>
+      </c>
+      <c r="O430" t="s" s="2">
         <v>863</v>
-      </c>
-      <c r="O430" t="s" s="2">
-        <v>864</v>
       </c>
       <c r="P430" s="2"/>
       <c r="Q430" t="s" s="2">
@@ -51073,11 +51069,11 @@
         <v>372</v>
       </c>
       <c r="Z430" t="s" s="2">
+        <v>864</v>
+      </c>
+      <c r="AA430" t="s" s="2">
         <v>865</v>
       </c>
-      <c r="AA430" t="s" s="2">
-        <v>866</v>
-      </c>
       <c r="AB430" t="s" s="2">
         <v>23</v>
       </c>
@@ -51094,7 +51090,7 @@
         <v>23</v>
       </c>
       <c r="AG430" t="s" s="2">
-        <v>861</v>
+        <v>860</v>
       </c>
       <c r="AH430" t="s" s="2">
         <v>76</v>
@@ -51111,13 +51107,13 @@
     </row>
     <row r="431">
       <c r="A431" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B431" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="C431" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="D431" s="2"/>
       <c r="E431" t="s" s="2">
@@ -51140,13 +51136,13 @@
         <v>23</v>
       </c>
       <c r="L431" t="s" s="2">
-        <v>868</v>
+        <v>867</v>
       </c>
       <c r="M431" t="s" s="2">
-        <v>1013</v>
+        <v>1012</v>
       </c>
       <c r="N431" t="s" s="2">
-        <v>870</v>
+        <v>869</v>
       </c>
       <c r="O431" s="2"/>
       <c r="P431" s="2"/>
@@ -51197,7 +51193,7 @@
         <v>23</v>
       </c>
       <c r="AG431" t="s" s="2">
-        <v>867</v>
+        <v>866</v>
       </c>
       <c r="AH431" t="s" s="2">
         <v>76</v>
@@ -51214,13 +51210,13 @@
     </row>
     <row r="432">
       <c r="A432" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B432" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="C432" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="D432" s="2"/>
       <c r="E432" t="s" s="2">
@@ -51246,10 +51242,10 @@
         <v>598</v>
       </c>
       <c r="M432" t="s" s="2">
-        <v>1016</v>
+        <v>1015</v>
       </c>
       <c r="N432" t="s" s="2">
-        <v>873</v>
+        <v>872</v>
       </c>
       <c r="O432" s="2"/>
       <c r="P432" s="2"/>
@@ -51300,7 +51296,7 @@
         <v>23</v>
       </c>
       <c r="AG432" t="s" s="2">
-        <v>871</v>
+        <v>870</v>
       </c>
       <c r="AH432" t="s" s="2">
         <v>76</v>
@@ -51317,13 +51313,13 @@
     </row>
     <row r="433">
       <c r="A433" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B433" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="C433" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="D433" s="2"/>
       <c r="E433" t="s" s="2">
@@ -51346,16 +51342,16 @@
         <v>23</v>
       </c>
       <c r="L433" t="s" s="2">
-        <v>875</v>
+        <v>874</v>
       </c>
       <c r="M433" t="s" s="2">
-        <v>1017</v>
+        <v>1016</v>
       </c>
       <c r="N433" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="O433" t="s" s="2">
         <v>877</v>
-      </c>
-      <c r="O433" t="s" s="2">
-        <v>878</v>
       </c>
       <c r="P433" s="2"/>
       <c r="Q433" t="s" s="2">
@@ -51405,7 +51401,7 @@
         <v>23</v>
       </c>
       <c r="AG433" t="s" s="2">
-        <v>874</v>
+        <v>873</v>
       </c>
       <c r="AH433" t="s" s="2">
         <v>76</v>
@@ -51422,13 +51418,13 @@
     </row>
     <row r="434">
       <c r="A434" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B434" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="C434" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="D434" s="2"/>
       <c r="E434" t="s" s="2">
@@ -51454,10 +51450,10 @@
         <v>136</v>
       </c>
       <c r="M434" t="s" s="2">
-        <v>1018</v>
+        <v>1017</v>
       </c>
       <c r="N434" t="s" s="2">
-        <v>881</v>
+        <v>880</v>
       </c>
       <c r="O434" s="2"/>
       <c r="P434" s="2"/>
@@ -51508,7 +51504,7 @@
         <v>23</v>
       </c>
       <c r="AG434" t="s" s="2">
-        <v>879</v>
+        <v>878</v>
       </c>
       <c r="AH434" t="s" s="2">
         <v>76</v>
@@ -51525,13 +51521,13 @@
     </row>
     <row r="435">
       <c r="A435" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B435" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="C435" t="s" s="2">
-        <v>882</v>
+        <v>881</v>
       </c>
       <c r="D435" s="2"/>
       <c r="E435" t="s" s="2">
@@ -51628,13 +51624,13 @@
     </row>
     <row r="436">
       <c r="A436" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B436" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="C436" t="s" s="2">
-        <v>883</v>
+        <v>882</v>
       </c>
       <c r="D436" s="2"/>
       <c r="E436" t="s" s="2">
@@ -51733,13 +51729,13 @@
     </row>
     <row r="437">
       <c r="A437" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B437" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="C437" t="s" s="2">
-        <v>884</v>
+        <v>883</v>
       </c>
       <c r="D437" s="2"/>
       <c r="E437" t="s" s="2">
@@ -51840,13 +51836,13 @@
     </row>
     <row r="438">
       <c r="A438" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B438" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="C438" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="D438" s="2"/>
       <c r="E438" t="s" s="2">
@@ -51872,13 +51868,13 @@
         <v>136</v>
       </c>
       <c r="M438" t="s" s="2">
+        <v>885</v>
+      </c>
+      <c r="N438" t="s" s="2">
         <v>886</v>
       </c>
-      <c r="N438" t="s" s="2">
+      <c r="O438" t="s" s="2">
         <v>887</v>
-      </c>
-      <c r="O438" t="s" s="2">
-        <v>888</v>
       </c>
       <c r="P438" s="2"/>
       <c r="Q438" t="s" s="2">
@@ -51928,7 +51924,7 @@
         <v>23</v>
       </c>
       <c r="AG438" t="s" s="2">
-        <v>885</v>
+        <v>884</v>
       </c>
       <c r="AH438" t="s" s="2">
         <v>76</v>
@@ -51945,13 +51941,13 @@
     </row>
     <row r="439">
       <c r="A439" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B439" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="C439" t="s" s="2">
-        <v>889</v>
+        <v>888</v>
       </c>
       <c r="D439" s="2"/>
       <c r="E439" t="s" s="2">
@@ -52048,13 +52044,13 @@
     </row>
     <row r="440">
       <c r="A440" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B440" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="C440" t="s" s="2">
-        <v>890</v>
+        <v>889</v>
       </c>
       <c r="D440" s="2"/>
       <c r="E440" t="s" s="2">
@@ -52153,13 +52149,13 @@
     </row>
     <row r="441">
       <c r="A441" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B441" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="C441" t="s" s="2">
-        <v>891</v>
+        <v>890</v>
       </c>
       <c r="D441" s="2"/>
       <c r="E441" t="s" s="2">
@@ -52260,13 +52256,13 @@
     </row>
     <row r="442">
       <c r="A442" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B442" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="C442" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="D442" s="2"/>
       <c r="E442" t="s" s="2">
@@ -52292,10 +52288,10 @@
         <v>497</v>
       </c>
       <c r="M442" t="s" s="2">
-        <v>1019</v>
+        <v>1018</v>
       </c>
       <c r="N442" t="s" s="2">
-        <v>894</v>
+        <v>893</v>
       </c>
       <c r="O442" s="2"/>
       <c r="P442" s="2"/>
@@ -52346,7 +52342,7 @@
         <v>23</v>
       </c>
       <c r="AG442" t="s" s="2">
-        <v>892</v>
+        <v>891</v>
       </c>
       <c r="AH442" t="s" s="2">
         <v>76</v>
@@ -52363,13 +52359,13 @@
     </row>
     <row r="443">
       <c r="A443" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B443" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="C443" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="D443" s="2"/>
       <c r="E443" t="s" s="2">
@@ -52392,13 +52388,13 @@
         <v>23</v>
       </c>
       <c r="L443" t="s" s="2">
+        <v>895</v>
+      </c>
+      <c r="M443" t="s" s="2">
         <v>896</v>
       </c>
-      <c r="M443" t="s" s="2">
+      <c r="N443" t="s" s="2">
         <v>897</v>
-      </c>
-      <c r="N443" t="s" s="2">
-        <v>898</v>
       </c>
       <c r="O443" s="2"/>
       <c r="P443" s="2"/>
@@ -52449,7 +52445,7 @@
         <v>23</v>
       </c>
       <c r="AG443" t="s" s="2">
-        <v>895</v>
+        <v>894</v>
       </c>
       <c r="AH443" t="s" s="2">
         <v>76</v>
@@ -52466,13 +52462,13 @@
     </row>
     <row r="444">
       <c r="A444" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B444" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="C444" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="D444" s="2"/>
       <c r="E444" t="s" s="2">
@@ -52495,13 +52491,13 @@
         <v>23</v>
       </c>
       <c r="L444" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M444" t="s" s="2">
-        <v>1020</v>
+        <v>1019</v>
       </c>
       <c r="N444" t="s" s="2">
-        <v>901</v>
+        <v>900</v>
       </c>
       <c r="O444" s="2"/>
       <c r="P444" s="2"/>
@@ -52552,7 +52548,7 @@
         <v>23</v>
       </c>
       <c r="AG444" t="s" s="2">
-        <v>899</v>
+        <v>898</v>
       </c>
       <c r="AH444" t="s" s="2">
         <v>76</v>
@@ -52569,13 +52565,13 @@
     </row>
     <row r="445">
       <c r="A445" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B445" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="C445" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="D445" s="2"/>
       <c r="E445" t="s" s="2">
@@ -52598,19 +52594,19 @@
         <v>23</v>
       </c>
       <c r="L445" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="M445" t="s" s="2">
+        <v>1020</v>
+      </c>
+      <c r="N445" t="s" s="2">
         <v>1021</v>
       </c>
-      <c r="N445" t="s" s="2">
-        <v>1022</v>
-      </c>
       <c r="O445" t="s" s="2">
+        <v>905</v>
+      </c>
+      <c r="P445" t="s" s="2">
         <v>906</v>
-      </c>
-      <c r="P445" t="s" s="2">
-        <v>907</v>
       </c>
       <c r="Q445" t="s" s="2">
         <v>23</v>
@@ -52659,7 +52655,7 @@
         <v>23</v>
       </c>
       <c r="AG445" t="s" s="2">
-        <v>902</v>
+        <v>901</v>
       </c>
       <c r="AH445" t="s" s="2">
         <v>76</v>
@@ -52676,13 +52672,13 @@
     </row>
     <row r="446">
       <c r="A446" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B446" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="C446" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="D446" s="2"/>
       <c r="E446" t="s" s="2">
@@ -52708,13 +52704,13 @@
         <v>130</v>
       </c>
       <c r="M446" t="s" s="2">
+        <v>1022</v>
+      </c>
+      <c r="N446" t="s" s="2">
         <v>1023</v>
       </c>
-      <c r="N446" t="s" s="2">
-        <v>1024</v>
-      </c>
       <c r="O446" t="s" s="2">
-        <v>911</v>
+        <v>910</v>
       </c>
       <c r="P446" s="2"/>
       <c r="Q446" t="s" s="2">
@@ -52764,7 +52760,7 @@
         <v>23</v>
       </c>
       <c r="AG446" t="s" s="2">
-        <v>908</v>
+        <v>907</v>
       </c>
       <c r="AH446" t="s" s="2">
         <v>76</v>
@@ -52781,13 +52777,13 @@
     </row>
     <row r="447">
       <c r="A447" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B447" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="C447" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="D447" s="2"/>
       <c r="E447" t="s" s="2">
@@ -52813,10 +52809,10 @@
         <v>497</v>
       </c>
       <c r="M447" t="s" s="2">
-        <v>1025</v>
+        <v>1024</v>
       </c>
       <c r="N447" t="s" s="2">
-        <v>914</v>
+        <v>913</v>
       </c>
       <c r="O447" s="2"/>
       <c r="P447" s="2"/>
@@ -52867,7 +52863,7 @@
         <v>23</v>
       </c>
       <c r="AG447" t="s" s="2">
-        <v>912</v>
+        <v>911</v>
       </c>
       <c r="AH447" t="s" s="2">
         <v>76</v>
@@ -52884,13 +52880,13 @@
     </row>
     <row r="448">
       <c r="A448" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B448" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="C448" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="D448" s="2"/>
       <c r="E448" t="s" s="2">
@@ -52913,16 +52909,16 @@
         <v>23</v>
       </c>
       <c r="L448" t="s" s="2">
-        <v>896</v>
+        <v>895</v>
       </c>
       <c r="M448" t="s" s="2">
+        <v>915</v>
+      </c>
+      <c r="N448" t="s" s="2">
         <v>916</v>
       </c>
-      <c r="N448" t="s" s="2">
+      <c r="O448" t="s" s="2">
         <v>917</v>
-      </c>
-      <c r="O448" t="s" s="2">
-        <v>918</v>
       </c>
       <c r="P448" s="2"/>
       <c r="Q448" t="s" s="2">
@@ -52972,7 +52968,7 @@
         <v>23</v>
       </c>
       <c r="AG448" t="s" s="2">
-        <v>915</v>
+        <v>914</v>
       </c>
       <c r="AH448" t="s" s="2">
         <v>76</v>
@@ -52989,13 +52985,13 @@
     </row>
     <row r="449">
       <c r="A449" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B449" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="C449" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="D449" s="2"/>
       <c r="E449" t="s" s="2">
@@ -53021,10 +53017,10 @@
         <v>670</v>
       </c>
       <c r="M449" t="s" s="2">
-        <v>1026</v>
+        <v>1025</v>
       </c>
       <c r="N449" t="s" s="2">
-        <v>930</v>
+        <v>929</v>
       </c>
       <c r="O449" s="2"/>
       <c r="P449" s="2"/>
@@ -53075,7 +53071,7 @@
         <v>23</v>
       </c>
       <c r="AG449" t="s" s="2">
-        <v>928</v>
+        <v>927</v>
       </c>
       <c r="AH449" t="s" s="2">
         <v>76</v>
@@ -53092,13 +53088,13 @@
     </row>
     <row r="450">
       <c r="A450" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B450" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="C450" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="D450" s="2"/>
       <c r="E450" t="s" s="2">
@@ -53124,10 +53120,10 @@
         <v>136</v>
       </c>
       <c r="M450" t="s" s="2">
-        <v>1027</v>
+        <v>1026</v>
       </c>
       <c r="N450" t="s" s="2">
-        <v>933</v>
+        <v>932</v>
       </c>
       <c r="O450" s="2"/>
       <c r="P450" s="2"/>
@@ -53178,7 +53174,7 @@
         <v>23</v>
       </c>
       <c r="AG450" t="s" s="2">
-        <v>931</v>
+        <v>930</v>
       </c>
       <c r="AH450" t="s" s="2">
         <v>76</v>
@@ -53195,13 +53191,13 @@
     </row>
     <row r="451">
       <c r="A451" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B451" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="C451" t="s" s="2">
-        <v>934</v>
+        <v>933</v>
       </c>
       <c r="D451" s="2"/>
       <c r="E451" t="s" s="2">
@@ -53298,13 +53294,13 @@
     </row>
     <row r="452">
       <c r="A452" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B452" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="C452" t="s" s="2">
-        <v>935</v>
+        <v>934</v>
       </c>
       <c r="D452" s="2"/>
       <c r="E452" t="s" s="2">
@@ -53403,13 +53399,13 @@
     </row>
     <row r="453">
       <c r="A453" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B453" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="C453" t="s" s="2">
-        <v>936</v>
+        <v>935</v>
       </c>
       <c r="D453" s="2"/>
       <c r="E453" t="s" s="2">
@@ -53510,13 +53506,13 @@
     </row>
     <row r="454">
       <c r="A454" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B454" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="C454" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="D454" s="2"/>
       <c r="E454" t="s" s="2">
@@ -53539,16 +53535,16 @@
         <v>23</v>
       </c>
       <c r="L454" t="s" s="2">
+        <v>937</v>
+      </c>
+      <c r="M454" t="s" s="2">
         <v>938</v>
       </c>
-      <c r="M454" t="s" s="2">
+      <c r="N454" t="s" s="2">
         <v>939</v>
       </c>
-      <c r="N454" t="s" s="2">
+      <c r="O454" t="s" s="2">
         <v>940</v>
-      </c>
-      <c r="O454" t="s" s="2">
-        <v>941</v>
       </c>
       <c r="P454" s="2"/>
       <c r="Q454" t="s" s="2">
@@ -53577,11 +53573,11 @@
         <v>372</v>
       </c>
       <c r="Z454" t="s" s="2">
+        <v>941</v>
+      </c>
+      <c r="AA454" t="s" s="2">
         <v>942</v>
       </c>
-      <c r="AA454" t="s" s="2">
-        <v>943</v>
-      </c>
       <c r="AB454" t="s" s="2">
         <v>23</v>
       </c>
@@ -53598,7 +53594,7 @@
         <v>23</v>
       </c>
       <c r="AG454" t="s" s="2">
-        <v>937</v>
+        <v>936</v>
       </c>
       <c r="AH454" t="s" s="2">
         <v>83</v>
@@ -53615,13 +53611,13 @@
     </row>
     <row r="455">
       <c r="A455" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -53647,10 +53643,10 @@
         <v>367</v>
       </c>
       <c r="M455" t="s" s="2">
+        <v>944</v>
+      </c>
+      <c r="N455" t="s" s="2">
         <v>945</v>
-      </c>
-      <c r="N455" t="s" s="2">
-        <v>946</v>
       </c>
       <c r="O455" s="2"/>
       <c r="P455" s="2"/>
@@ -53680,11 +53676,11 @@
         <v>372</v>
       </c>
       <c r="Z455" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="AA455" t="s" s="2">
         <v>947</v>
       </c>
-      <c r="AA455" t="s" s="2">
-        <v>948</v>
-      </c>
       <c r="AB455" t="s" s="2">
         <v>23</v>
       </c>
@@ -53701,7 +53697,7 @@
         <v>23</v>
       </c>
       <c r="AG455" t="s" s="2">
-        <v>944</v>
+        <v>943</v>
       </c>
       <c r="AH455" t="s" s="2">
         <v>76</v>
@@ -53718,13 +53714,13 @@
     </row>
     <row r="456">
       <c r="A456" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -53747,13 +53743,13 @@
         <v>23</v>
       </c>
       <c r="L456" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="M456" t="s" s="2">
-        <v>1028</v>
+        <v>1027</v>
       </c>
       <c r="N456" t="s" s="2">
-        <v>952</v>
+        <v>951</v>
       </c>
       <c r="O456" s="2"/>
       <c r="P456" s="2"/>
@@ -53804,7 +53800,7 @@
         <v>23</v>
       </c>
       <c r="AG456" t="s" s="2">
-        <v>949</v>
+        <v>948</v>
       </c>
       <c r="AH456" t="s" s="2">
         <v>76</v>
@@ -53821,17 +53817,17 @@
     </row>
     <row r="457">
       <c r="A457" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F457" s="2"/>
       <c r="G457" t="s" s="2">
@@ -53850,16 +53846,16 @@
         <v>23</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1029</v>
+        <v>1028</v>
       </c>
       <c r="N457" t="s" s="2">
+        <v>956</v>
+      </c>
+      <c r="O457" t="s" s="2">
         <v>957</v>
-      </c>
-      <c r="O457" t="s" s="2">
-        <v>958</v>
       </c>
       <c r="P457" s="2"/>
       <c r="Q457" t="s" s="2">
@@ -53909,7 +53905,7 @@
         <v>23</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>953</v>
+        <v>952</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>76</v>
@@ -53926,13 +53922,13 @@
     </row>
     <row r="458">
       <c r="A458" t="s" s="2">
-        <v>964</v>
+        <v>963</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -53955,16 +53951,16 @@
         <v>23</v>
       </c>
       <c r="L458" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>1030</v>
+        <v>1029</v>
       </c>
       <c r="N458" t="s" s="2">
+        <v>961</v>
+      </c>
+      <c r="O458" t="s" s="2">
         <v>962</v>
-      </c>
-      <c r="O458" t="s" s="2">
-        <v>963</v>
       </c>
       <c r="P458" s="2"/>
       <c r="Q458" t="s" s="2">
@@ -54014,7 +54010,7 @@
         <v>23</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>959</v>
+        <v>958</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>76</v>
@@ -54031,13 +54027,13 @@
     </row>
     <row r="459">
       <c r="A459" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B459" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="C459" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="D459" s="2"/>
       <c r="E459" t="s" s="2">
@@ -54063,10 +54059,10 @@
         <v>78</v>
       </c>
       <c r="M459" t="s" s="2">
+        <v>1037</v>
+      </c>
+      <c r="N459" t="s" s="2">
         <v>1038</v>
-      </c>
-      <c r="N459" t="s" s="2">
-        <v>1039</v>
       </c>
       <c r="O459" s="2"/>
       <c r="P459" s="2"/>
@@ -54117,7 +54113,7 @@
         <v>23</v>
       </c>
       <c r="AG459" t="s" s="2">
-        <v>1036</v>
+        <v>1035</v>
       </c>
       <c r="AH459" t="s" s="2">
         <v>76</v>
@@ -54129,18 +54125,18 @@
         <v>23</v>
       </c>
       <c r="AK459" t="s" s="2">
-        <v>1040</v>
+        <v>1039</v>
       </c>
     </row>
     <row r="460">
       <c r="A460" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B460" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="C460" t="s" s="2">
-        <v>1041</v>
+        <v>1040</v>
       </c>
       <c r="D460" s="2"/>
       <c r="E460" t="s" s="2">
@@ -54239,13 +54235,13 @@
     </row>
     <row r="461">
       <c r="A461" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B461" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="C461" t="s" s="2">
-        <v>1042</v>
+        <v>1041</v>
       </c>
       <c r="D461" s="2"/>
       <c r="E461" t="s" s="2">
@@ -54342,13 +54338,13 @@
     </row>
     <row r="462">
       <c r="A462" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B462" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="C462" t="s" s="2">
-        <v>1043</v>
+        <v>1042</v>
       </c>
       <c r="D462" s="2"/>
       <c r="E462" t="s" s="2">
@@ -54447,13 +54443,13 @@
     </row>
     <row r="463">
       <c r="A463" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B463" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="C463" t="s" s="2">
-        <v>1044</v>
+        <v>1043</v>
       </c>
       <c r="D463" s="2"/>
       <c r="E463" t="s" s="2">
@@ -54552,13 +54548,13 @@
     </row>
     <row r="464">
       <c r="A464" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="C464" t="s" s="2">
-        <v>1045</v>
+        <v>1044</v>
       </c>
       <c r="D464" s="2"/>
       <c r="E464" t="s" s="2">
@@ -54657,13 +54653,13 @@
     </row>
     <row r="465">
       <c r="A465" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="C465" t="s" s="2">
-        <v>1046</v>
+        <v>1045</v>
       </c>
       <c r="D465" s="2"/>
       <c r="E465" t="s" s="2">
@@ -54762,13 +54758,13 @@
     </row>
     <row r="466">
       <c r="A466" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B466" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="C466" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D466" s="2"/>
       <c r="E466" t="s" s="2">
@@ -54863,13 +54859,13 @@
     </row>
     <row r="467">
       <c r="A467" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B467" t="s" s="2">
-        <v>1048</v>
+        <v>1047</v>
       </c>
       <c r="C467" t="s" s="2">
-        <v>1047</v>
+        <v>1046</v>
       </c>
       <c r="D467" t="s" s="2">
         <v>742</v>
@@ -54970,16 +54966,16 @@
     </row>
     <row r="468">
       <c r="A468" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B468" t="s" s="2">
+        <v>1048</v>
+      </c>
+      <c r="C468" t="s" s="2">
+        <v>1046</v>
+      </c>
+      <c r="D468" t="s" s="2">
         <v>1049</v>
-      </c>
-      <c r="C468" t="s" s="2">
-        <v>1047</v>
-      </c>
-      <c r="D468" t="s" s="2">
-        <v>1050</v>
       </c>
       <c r="E468" t="s" s="2">
         <v>23</v>
@@ -55001,16 +54997,16 @@
         <v>23</v>
       </c>
       <c r="L468" t="s" s="2">
+        <v>1050</v>
+      </c>
+      <c r="M468" t="s" s="2">
         <v>1051</v>
       </c>
-      <c r="M468" t="s" s="2">
+      <c r="N468" t="s" s="2">
         <v>1052</v>
       </c>
-      <c r="N468" t="s" s="2">
+      <c r="O468" t="s" s="2">
         <v>1053</v>
-      </c>
-      <c r="O468" t="s" s="2">
-        <v>1054</v>
       </c>
       <c r="P468" s="2"/>
       <c r="Q468" t="s" s="2">
@@ -55077,13 +55073,13 @@
     </row>
     <row r="469">
       <c r="A469" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B469" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="C469" t="s" s="2">
-        <v>1055</v>
+        <v>1054</v>
       </c>
       <c r="D469" s="2"/>
       <c r="E469" t="s" s="2">
@@ -55184,13 +55180,13 @@
     </row>
     <row r="470">
       <c r="A470" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B470" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="C470" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="D470" s="2"/>
       <c r="E470" t="s" s="2">
@@ -55216,10 +55212,10 @@
         <v>112</v>
       </c>
       <c r="M470" t="s" s="2">
+        <v>1056</v>
+      </c>
+      <c r="N470" t="s" s="2">
         <v>1057</v>
-      </c>
-      <c r="N470" t="s" s="2">
-        <v>1058</v>
       </c>
       <c r="O470" t="s" s="2">
         <v>751</v>
@@ -55272,7 +55268,7 @@
         <v>23</v>
       </c>
       <c r="AG470" t="s" s="2">
-        <v>1056</v>
+        <v>1055</v>
       </c>
       <c r="AH470" t="s" s="2">
         <v>76</v>
@@ -55289,13 +55285,13 @@
     </row>
     <row r="471">
       <c r="A471" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B471" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="C471" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="D471" s="2"/>
       <c r="E471" t="s" s="2">
@@ -55318,13 +55314,13 @@
         <v>23</v>
       </c>
       <c r="L471" t="s" s="2">
+        <v>1059</v>
+      </c>
+      <c r="M471" t="s" s="2">
         <v>1060</v>
       </c>
-      <c r="M471" t="s" s="2">
+      <c r="N471" t="s" s="2">
         <v>1061</v>
-      </c>
-      <c r="N471" t="s" s="2">
-        <v>1062</v>
       </c>
       <c r="O471" s="2"/>
       <c r="P471" s="2"/>
@@ -55375,7 +55371,7 @@
         <v>23</v>
       </c>
       <c r="AG471" t="s" s="2">
-        <v>1059</v>
+        <v>1058</v>
       </c>
       <c r="AH471" t="s" s="2">
         <v>76</v>
@@ -55392,13 +55388,13 @@
     </row>
     <row r="472">
       <c r="A472" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B472" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="C472" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="D472" s="2"/>
       <c r="E472" t="s" s="2">
@@ -55424,10 +55420,10 @@
         <v>103</v>
       </c>
       <c r="M472" t="s" s="2">
+        <v>1063</v>
+      </c>
+      <c r="N472" t="s" s="2">
         <v>1064</v>
-      </c>
-      <c r="N472" t="s" s="2">
-        <v>1065</v>
       </c>
       <c r="O472" t="s" s="2">
         <v>544</v>
@@ -55459,11 +55455,11 @@
         <v>121</v>
       </c>
       <c r="Z472" t="s" s="2">
+        <v>1065</v>
+      </c>
+      <c r="AA472" t="s" s="2">
         <v>1066</v>
       </c>
-      <c r="AA472" t="s" s="2">
-        <v>1067</v>
-      </c>
       <c r="AB472" t="s" s="2">
         <v>23</v>
       </c>
@@ -55480,7 +55476,7 @@
         <v>23</v>
       </c>
       <c r="AG472" t="s" s="2">
-        <v>1063</v>
+        <v>1062</v>
       </c>
       <c r="AH472" t="s" s="2">
         <v>83</v>
@@ -55497,13 +55493,13 @@
     </row>
     <row r="473">
       <c r="A473" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B473" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="C473" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="D473" s="2"/>
       <c r="E473" t="s" s="2">
@@ -55529,10 +55525,10 @@
         <v>367</v>
       </c>
       <c r="M473" t="s" s="2">
+        <v>1068</v>
+      </c>
+      <c r="N473" t="s" s="2">
         <v>1069</v>
-      </c>
-      <c r="N473" t="s" s="2">
-        <v>1070</v>
       </c>
       <c r="O473" s="2"/>
       <c r="P473" s="2"/>
@@ -55562,10 +55558,10 @@
         <v>372</v>
       </c>
       <c r="Z473" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="AA473" t="s" s="2">
         <v>1071</v>
-      </c>
-      <c r="AA473" t="s" s="2">
-        <v>1072</v>
       </c>
       <c r="AB473" t="s" s="2">
         <v>23</v>
@@ -55581,7 +55577,7 @@
         <v>169</v>
       </c>
       <c r="AG473" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AH473" t="s" s="2">
         <v>76</v>
@@ -55598,16 +55594,16 @@
     </row>
     <row r="474">
       <c r="A474" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B474" t="s" s="2">
+        <v>1072</v>
+      </c>
+      <c r="C474" t="s" s="2">
+        <v>1067</v>
+      </c>
+      <c r="D474" t="s" s="2">
         <v>1073</v>
-      </c>
-      <c r="C474" t="s" s="2">
-        <v>1068</v>
-      </c>
-      <c r="D474" t="s" s="2">
-        <v>1074</v>
       </c>
       <c r="E474" t="s" s="2">
         <v>23</v>
@@ -55632,10 +55628,10 @@
         <v>367</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1075</v>
+        <v>1074</v>
       </c>
       <c r="N474" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="O474" s="2"/>
       <c r="P474" s="2"/>
@@ -55665,11 +55661,11 @@
         <v>372</v>
       </c>
       <c r="Z474" t="s" s="2">
+        <v>1070</v>
+      </c>
+      <c r="AA474" t="s" s="2">
         <v>1071</v>
       </c>
-      <c r="AA474" t="s" s="2">
-        <v>1072</v>
-      </c>
       <c r="AB474" t="s" s="2">
         <v>23</v>
       </c>
@@ -55686,7 +55682,7 @@
         <v>23</v>
       </c>
       <c r="AG474" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AH474" t="s" s="2">
         <v>76</v>
@@ -55703,16 +55699,16 @@
     </row>
     <row r="475">
       <c r="A475" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B475" t="s" s="2">
+        <v>1075</v>
+      </c>
+      <c r="C475" t="s" s="2">
+        <v>1067</v>
+      </c>
+      <c r="D475" t="s" s="2">
         <v>1076</v>
-      </c>
-      <c r="C475" t="s" s="2">
-        <v>1068</v>
-      </c>
-      <c r="D475" t="s" s="2">
-        <v>1077</v>
       </c>
       <c r="E475" t="s" s="2">
         <v>23</v>
@@ -55734,13 +55730,13 @@
         <v>23</v>
       </c>
       <c r="L475" t="s" s="2">
+        <v>1077</v>
+      </c>
+      <c r="M475" t="s" s="2">
         <v>1078</v>
       </c>
-      <c r="M475" t="s" s="2">
-        <v>1079</v>
-      </c>
       <c r="N475" t="s" s="2">
-        <v>1070</v>
+        <v>1069</v>
       </c>
       <c r="O475" s="2"/>
       <c r="P475" s="2"/>
@@ -55791,7 +55787,7 @@
         <v>23</v>
       </c>
       <c r="AG475" t="s" s="2">
-        <v>1068</v>
+        <v>1067</v>
       </c>
       <c r="AH475" t="s" s="2">
         <v>76</v>
@@ -55808,13 +55804,13 @@
     </row>
     <row r="476">
       <c r="A476" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B476" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="C476" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="D476" s="2"/>
       <c r="E476" t="s" s="2">
@@ -55840,13 +55836,13 @@
         <v>367</v>
       </c>
       <c r="M476" t="s" s="2">
+        <v>1080</v>
+      </c>
+      <c r="N476" t="s" s="2">
         <v>1081</v>
       </c>
-      <c r="N476" t="s" s="2">
+      <c r="O476" t="s" s="2">
         <v>1082</v>
-      </c>
-      <c r="O476" t="s" s="2">
-        <v>1083</v>
       </c>
       <c r="P476" s="2"/>
       <c r="Q476" t="s" s="2">
@@ -55875,11 +55871,11 @@
         <v>107</v>
       </c>
       <c r="Z476" t="s" s="2">
+        <v>1083</v>
+      </c>
+      <c r="AA476" t="s" s="2">
         <v>1084</v>
       </c>
-      <c r="AA476" t="s" s="2">
-        <v>1085</v>
-      </c>
       <c r="AB476" t="s" s="2">
         <v>23</v>
       </c>
@@ -55896,7 +55892,7 @@
         <v>23</v>
       </c>
       <c r="AG476" t="s" s="2">
-        <v>1080</v>
+        <v>1079</v>
       </c>
       <c r="AH476" t="s" s="2">
         <v>76</v>
@@ -55913,13 +55909,13 @@
     </row>
     <row r="477">
       <c r="A477" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B477" t="s" s="2">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="C477" t="s" s="2">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="D477" s="2"/>
       <c r="E477" t="s" s="2">
@@ -55945,13 +55941,13 @@
         <v>799</v>
       </c>
       <c r="M477" t="s" s="2">
+        <v>1086</v>
+      </c>
+      <c r="N477" t="s" s="2">
         <v>1087</v>
       </c>
-      <c r="N477" t="s" s="2">
+      <c r="O477" t="s" s="2">
         <v>1088</v>
-      </c>
-      <c r="O477" t="s" s="2">
-        <v>1089</v>
       </c>
       <c r="P477" s="2"/>
       <c r="Q477" t="s" s="2">
@@ -56001,7 +55997,7 @@
         <v>23</v>
       </c>
       <c r="AG477" t="s" s="2">
-        <v>1086</v>
+        <v>1085</v>
       </c>
       <c r="AH477" t="s" s="2">
         <v>83</v>
@@ -56018,13 +56014,13 @@
     </row>
     <row r="478">
       <c r="A478" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B478" t="s" s="2">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="C478" t="s" s="2">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="D478" s="2"/>
       <c r="E478" t="s" s="2">
@@ -56047,16 +56043,16 @@
         <v>84</v>
       </c>
       <c r="L478" t="s" s="2">
-        <v>804</v>
+        <v>568</v>
       </c>
       <c r="M478" t="s" s="2">
+        <v>1090</v>
+      </c>
+      <c r="N478" t="s" s="2">
         <v>1091</v>
       </c>
-      <c r="N478" t="s" s="2">
+      <c r="O478" t="s" s="2">
         <v>1092</v>
-      </c>
-      <c r="O478" t="s" s="2">
-        <v>1093</v>
       </c>
       <c r="P478" s="2"/>
       <c r="Q478" t="s" s="2">
@@ -56106,7 +56102,7 @@
         <v>23</v>
       </c>
       <c r="AG478" t="s" s="2">
-        <v>1090</v>
+        <v>1089</v>
       </c>
       <c r="AH478" t="s" s="2">
         <v>76</v>
@@ -56123,13 +56119,13 @@
     </row>
     <row r="479">
       <c r="A479" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B479" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="C479" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="D479" s="2"/>
       <c r="E479" t="s" s="2">
@@ -56152,13 +56148,13 @@
         <v>23</v>
       </c>
       <c r="L479" t="s" s="2">
+        <v>1094</v>
+      </c>
+      <c r="M479" t="s" s="2">
         <v>1095</v>
       </c>
-      <c r="M479" t="s" s="2">
+      <c r="N479" t="s" s="2">
         <v>1096</v>
-      </c>
-      <c r="N479" t="s" s="2">
-        <v>1097</v>
       </c>
       <c r="O479" s="2"/>
       <c r="P479" s="2"/>
@@ -56209,7 +56205,7 @@
         <v>23</v>
       </c>
       <c r="AG479" t="s" s="2">
-        <v>1094</v>
+        <v>1093</v>
       </c>
       <c r="AH479" t="s" s="2">
         <v>76</v>
@@ -56226,13 +56222,13 @@
     </row>
     <row r="480">
       <c r="A480" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B480" t="s" s="2">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="C480" t="s" s="2">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="D480" s="2"/>
       <c r="E480" t="s" s="2">
@@ -56255,13 +56251,13 @@
         <v>23</v>
       </c>
       <c r="L480" t="s" s="2">
-        <v>813</v>
+        <v>812</v>
       </c>
       <c r="M480" t="s" s="2">
+        <v>1098</v>
+      </c>
+      <c r="N480" t="s" s="2">
         <v>1099</v>
-      </c>
-      <c r="N480" t="s" s="2">
-        <v>1100</v>
       </c>
       <c r="O480" s="2"/>
       <c r="P480" s="2"/>
@@ -56312,7 +56308,7 @@
         <v>23</v>
       </c>
       <c r="AG480" t="s" s="2">
-        <v>1098</v>
+        <v>1097</v>
       </c>
       <c r="AH480" t="s" s="2">
         <v>76</v>
@@ -56329,13 +56325,13 @@
     </row>
     <row r="481">
       <c r="A481" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B481" t="s" s="2">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="C481" t="s" s="2">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="D481" s="2"/>
       <c r="E481" t="s" s="2">
@@ -56361,10 +56357,10 @@
         <v>136</v>
       </c>
       <c r="M481" t="s" s="2">
+        <v>1101</v>
+      </c>
+      <c r="N481" t="s" s="2">
         <v>1102</v>
-      </c>
-      <c r="N481" t="s" s="2">
-        <v>1103</v>
       </c>
       <c r="O481" s="2"/>
       <c r="P481" s="2"/>
@@ -56415,7 +56411,7 @@
         <v>23</v>
       </c>
       <c r="AG481" t="s" s="2">
-        <v>1101</v>
+        <v>1100</v>
       </c>
       <c r="AH481" t="s" s="2">
         <v>76</v>
@@ -56432,13 +56428,13 @@
     </row>
     <row r="482">
       <c r="A482" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B482" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="C482" t="s" s="2">
-        <v>1104</v>
+        <v>1103</v>
       </c>
       <c r="D482" s="2"/>
       <c r="E482" t="s" s="2">
@@ -56535,13 +56531,13 @@
     </row>
     <row r="483">
       <c r="A483" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B483" t="s" s="2">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="C483" t="s" s="2">
-        <v>1105</v>
+        <v>1104</v>
       </c>
       <c r="D483" s="2"/>
       <c r="E483" t="s" s="2">
@@ -56640,13 +56636,13 @@
     </row>
     <row r="484">
       <c r="A484" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B484" t="s" s="2">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="C484" t="s" s="2">
-        <v>1106</v>
+        <v>1105</v>
       </c>
       <c r="D484" s="2"/>
       <c r="E484" t="s" s="2">
@@ -56747,13 +56743,13 @@
     </row>
     <row r="485">
       <c r="A485" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B485" t="s" s="2">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="C485" t="s" s="2">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="D485" s="2"/>
       <c r="E485" t="s" s="2">
@@ -56779,14 +56775,14 @@
         <v>367</v>
       </c>
       <c r="M485" t="s" s="2">
+        <v>1107</v>
+      </c>
+      <c r="N485" t="s" s="2">
         <v>1108</v>
-      </c>
-      <c r="N485" t="s" s="2">
-        <v>1109</v>
       </c>
       <c r="O485" s="2"/>
       <c r="P485" t="s" s="2">
-        <v>1110</v>
+        <v>1109</v>
       </c>
       <c r="Q485" t="s" s="2">
         <v>23</v>
@@ -56814,11 +56810,11 @@
         <v>372</v>
       </c>
       <c r="Z485" t="s" s="2">
+        <v>1110</v>
+      </c>
+      <c r="AA485" t="s" s="2">
         <v>1111</v>
       </c>
-      <c r="AA485" t="s" s="2">
-        <v>1112</v>
-      </c>
       <c r="AB485" t="s" s="2">
         <v>23</v>
       </c>
@@ -56835,7 +56831,7 @@
         <v>23</v>
       </c>
       <c r="AG485" t="s" s="2">
-        <v>1107</v>
+        <v>1106</v>
       </c>
       <c r="AH485" t="s" s="2">
         <v>76</v>
@@ -56852,13 +56848,13 @@
     </row>
     <row r="486">
       <c r="A486" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B486" t="s" s="2">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="C486" t="s" s="2">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="D486" s="2"/>
       <c r="E486" t="s" s="2">
@@ -56881,13 +56877,13 @@
         <v>23</v>
       </c>
       <c r="L486" t="s" s="2">
-        <v>820</v>
+        <v>819</v>
       </c>
       <c r="M486" t="s" s="2">
+        <v>1113</v>
+      </c>
+      <c r="N486" t="s" s="2">
         <v>1114</v>
-      </c>
-      <c r="N486" t="s" s="2">
-        <v>1115</v>
       </c>
       <c r="O486" s="2"/>
       <c r="P486" s="2"/>
@@ -56938,7 +56934,7 @@
         <v>23</v>
       </c>
       <c r="AG486" t="s" s="2">
-        <v>1113</v>
+        <v>1112</v>
       </c>
       <c r="AH486" t="s" s="2">
         <v>83</v>
@@ -56955,13 +56951,13 @@
     </row>
     <row r="487">
       <c r="A487" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B487" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="C487" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="D487" s="2"/>
       <c r="E487" t="s" s="2">
@@ -56984,13 +56980,13 @@
         <v>23</v>
       </c>
       <c r="L487" t="s" s="2">
+        <v>1116</v>
+      </c>
+      <c r="M487" t="s" s="2">
         <v>1117</v>
       </c>
-      <c r="M487" t="s" s="2">
+      <c r="N487" t="s" s="2">
         <v>1118</v>
-      </c>
-      <c r="N487" t="s" s="2">
-        <v>1119</v>
       </c>
       <c r="O487" s="2"/>
       <c r="P487" s="2"/>
@@ -57041,7 +57037,7 @@
         <v>23</v>
       </c>
       <c r="AG487" t="s" s="2">
-        <v>1116</v>
+        <v>1115</v>
       </c>
       <c r="AH487" t="s" s="2">
         <v>76</v>
@@ -57058,13 +57054,13 @@
     </row>
     <row r="488">
       <c r="A488" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B488" t="s" s="2">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="C488" t="s" s="2">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="D488" s="2"/>
       <c r="E488" t="s" s="2">
@@ -57075,7 +57071,7 @@
         <v>76</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>83</v>
+        <v>770</v>
       </c>
       <c r="I488" t="s" s="2">
         <v>84</v>
@@ -57087,16 +57083,16 @@
         <v>23</v>
       </c>
       <c r="L488" t="s" s="2">
-        <v>950</v>
+        <v>949</v>
       </c>
       <c r="M488" t="s" s="2">
+        <v>1120</v>
+      </c>
+      <c r="N488" t="s" s="2">
         <v>1121</v>
       </c>
-      <c r="N488" t="s" s="2">
+      <c r="O488" t="s" s="2">
         <v>1122</v>
-      </c>
-      <c r="O488" t="s" s="2">
-        <v>1123</v>
       </c>
       <c r="P488" s="2"/>
       <c r="Q488" t="s" s="2">
@@ -57146,7 +57142,7 @@
         <v>23</v>
       </c>
       <c r="AG488" t="s" s="2">
-        <v>1120</v>
+        <v>1119</v>
       </c>
       <c r="AH488" t="s" s="2">
         <v>76</v>
@@ -57163,13 +57159,13 @@
     </row>
     <row r="489">
       <c r="A489" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="D489" s="2"/>
       <c r="E489" t="s" s="2">
@@ -57195,10 +57191,10 @@
         <v>367</v>
       </c>
       <c r="M489" t="s" s="2">
+        <v>1124</v>
+      </c>
+      <c r="N489" t="s" s="2">
         <v>1125</v>
-      </c>
-      <c r="N489" t="s" s="2">
-        <v>1126</v>
       </c>
       <c r="O489" s="2"/>
       <c r="P489" s="2"/>
@@ -57228,11 +57224,11 @@
         <v>372</v>
       </c>
       <c r="Z489" t="s" s="2">
+        <v>1125</v>
+      </c>
+      <c r="AA489" t="s" s="2">
         <v>1126</v>
       </c>
-      <c r="AA489" t="s" s="2">
-        <v>1127</v>
-      </c>
       <c r="AB489" t="s" s="2">
         <v>23</v>
       </c>
@@ -57249,7 +57245,7 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1124</v>
+        <v>1123</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
@@ -57266,13 +57262,13 @@
     </row>
     <row r="490">
       <c r="A490" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="D490" s="2"/>
       <c r="E490" t="s" s="2">
@@ -57298,10 +57294,10 @@
         <v>497</v>
       </c>
       <c r="M490" t="s" s="2">
+        <v>1128</v>
+      </c>
+      <c r="N490" t="s" s="2">
         <v>1129</v>
-      </c>
-      <c r="N490" t="s" s="2">
-        <v>1130</v>
       </c>
       <c r="O490" s="2"/>
       <c r="P490" s="2"/>
@@ -57352,7 +57348,7 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
@@ -57369,13 +57365,13 @@
     </row>
     <row r="491">
       <c r="A491" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B491" t="s" s="2">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="C491" t="s" s="2">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="D491" s="2"/>
       <c r="E491" t="s" s="2">
@@ -57401,10 +57397,10 @@
         <v>497</v>
       </c>
       <c r="M491" t="s" s="2">
+        <v>1131</v>
+      </c>
+      <c r="N491" t="s" s="2">
         <v>1132</v>
-      </c>
-      <c r="N491" t="s" s="2">
-        <v>1133</v>
       </c>
       <c r="O491" s="2"/>
       <c r="P491" s="2"/>
@@ -57455,7 +57451,7 @@
         <v>23</v>
       </c>
       <c r="AG491" t="s" s="2">
-        <v>1131</v>
+        <v>1130</v>
       </c>
       <c r="AH491" t="s" s="2">
         <v>76</v>
@@ -57472,13 +57468,13 @@
     </row>
     <row r="492">
       <c r="A492" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57504,10 +57500,10 @@
         <v>578</v>
       </c>
       <c r="M492" t="s" s="2">
+        <v>1134</v>
+      </c>
+      <c r="N492" t="s" s="2">
         <v>1135</v>
-      </c>
-      <c r="N492" t="s" s="2">
-        <v>1136</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57558,7 +57554,7 @@
         <v>23</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1134</v>
+        <v>1133</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57575,13 +57571,13 @@
     </row>
     <row r="493">
       <c r="A493" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57607,10 +57603,10 @@
         <v>578</v>
       </c>
       <c r="M493" t="s" s="2">
+        <v>1137</v>
+      </c>
+      <c r="N493" t="s" s="2">
         <v>1138</v>
-      </c>
-      <c r="N493" t="s" s="2">
-        <v>1139</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
@@ -57661,7 +57657,7 @@
         <v>23</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1137</v>
+        <v>1136</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -57678,13 +57674,13 @@
     </row>
     <row r="494">
       <c r="A494" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57707,13 +57703,13 @@
         <v>23</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1117</v>
+        <v>1116</v>
       </c>
       <c r="M494" t="s" s="2">
+        <v>1140</v>
+      </c>
+      <c r="N494" t="s" s="2">
         <v>1141</v>
-      </c>
-      <c r="N494" t="s" s="2">
-        <v>1142</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
@@ -57764,7 +57760,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1140</v>
+        <v>1139</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -57781,13 +57777,13 @@
     </row>
     <row r="495">
       <c r="A495" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57810,13 +57806,13 @@
         <v>23</v>
       </c>
       <c r="L495" t="s" s="2">
+        <v>1143</v>
+      </c>
+      <c r="M495" t="s" s="2">
         <v>1144</v>
       </c>
-      <c r="M495" t="s" s="2">
+      <c r="N495" t="s" s="2">
         <v>1145</v>
-      </c>
-      <c r="N495" t="s" s="2">
-        <v>1146</v>
       </c>
       <c r="O495" s="2"/>
       <c r="P495" s="2"/>
@@ -57867,7 +57863,7 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1143</v>
+        <v>1142</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
@@ -57884,13 +57880,13 @@
     </row>
     <row r="496">
       <c r="A496" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B496" t="s" s="2">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="C496" t="s" s="2">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="D496" s="2"/>
       <c r="E496" t="s" s="2">
@@ -57916,10 +57912,10 @@
         <v>598</v>
       </c>
       <c r="M496" t="s" s="2">
+        <v>1147</v>
+      </c>
+      <c r="N496" t="s" s="2">
         <v>1148</v>
-      </c>
-      <c r="N496" t="s" s="2">
-        <v>1149</v>
       </c>
       <c r="O496" s="2"/>
       <c r="P496" s="2"/>
@@ -57970,7 +57966,7 @@
         <v>23</v>
       </c>
       <c r="AG496" t="s" s="2">
-        <v>1147</v>
+        <v>1146</v>
       </c>
       <c r="AH496" t="s" s="2">
         <v>76</v>
@@ -57987,13 +57983,13 @@
     </row>
     <row r="497">
       <c r="A497" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B497" t="s" s="2">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="C497" t="s" s="2">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="D497" s="2"/>
       <c r="E497" t="s" s="2">
@@ -58016,16 +58012,16 @@
         <v>23</v>
       </c>
       <c r="L497" t="s" s="2">
+        <v>1150</v>
+      </c>
+      <c r="M497" t="s" s="2">
         <v>1151</v>
       </c>
-      <c r="M497" t="s" s="2">
+      <c r="N497" t="s" s="2">
+        <v>876</v>
+      </c>
+      <c r="O497" t="s" s="2">
         <v>1152</v>
-      </c>
-      <c r="N497" t="s" s="2">
-        <v>877</v>
-      </c>
-      <c r="O497" t="s" s="2">
-        <v>1153</v>
       </c>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
@@ -58075,7 +58071,7 @@
         <v>23</v>
       </c>
       <c r="AG497" t="s" s="2">
-        <v>1150</v>
+        <v>1149</v>
       </c>
       <c r="AH497" t="s" s="2">
         <v>76</v>
@@ -58092,13 +58088,13 @@
     </row>
     <row r="498">
       <c r="A498" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B498" t="s" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="C498" t="s" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="D498" s="2"/>
       <c r="E498" t="s" s="2">
@@ -58124,10 +58120,10 @@
         <v>136</v>
       </c>
       <c r="M498" t="s" s="2">
+        <v>1154</v>
+      </c>
+      <c r="N498" t="s" s="2">
         <v>1155</v>
-      </c>
-      <c r="N498" t="s" s="2">
-        <v>1156</v>
       </c>
       <c r="O498" s="2"/>
       <c r="P498" s="2"/>
@@ -58178,7 +58174,7 @@
         <v>23</v>
       </c>
       <c r="AG498" t="s" s="2">
-        <v>1154</v>
+        <v>1153</v>
       </c>
       <c r="AH498" t="s" s="2">
         <v>76</v>
@@ -58195,13 +58191,13 @@
     </row>
     <row r="499">
       <c r="A499" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B499" t="s" s="2">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="C499" t="s" s="2">
-        <v>1157</v>
+        <v>1156</v>
       </c>
       <c r="D499" s="2"/>
       <c r="E499" t="s" s="2">
@@ -58298,13 +58294,13 @@
     </row>
     <row r="500">
       <c r="A500" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1158</v>
+        <v>1157</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
@@ -58403,13 +58399,13 @@
     </row>
     <row r="501">
       <c r="A501" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1159</v>
+        <v>1158</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
@@ -58510,13 +58506,13 @@
     </row>
     <row r="502">
       <c r="A502" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
@@ -58542,10 +58538,10 @@
         <v>385</v>
       </c>
       <c r="M502" t="s" s="2">
+        <v>1160</v>
+      </c>
+      <c r="N502" t="s" s="2">
         <v>1161</v>
-      </c>
-      <c r="N502" t="s" s="2">
-        <v>1162</v>
       </c>
       <c r="O502" s="2"/>
       <c r="P502" s="2"/>
@@ -58596,7 +58592,7 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1160</v>
+        <v>1159</v>
       </c>
       <c r="AH502" t="s" s="2">
         <v>83</v>
@@ -58613,13 +58609,13 @@
     </row>
     <row r="503">
       <c r="A503" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
@@ -58645,10 +58641,10 @@
         <v>367</v>
       </c>
       <c r="M503" t="s" s="2">
+        <v>1163</v>
+      </c>
+      <c r="N503" t="s" s="2">
         <v>1164</v>
-      </c>
-      <c r="N503" t="s" s="2">
-        <v>1165</v>
       </c>
       <c r="O503" s="2"/>
       <c r="P503" s="2"/>
@@ -58678,10 +58674,10 @@
         <v>372</v>
       </c>
       <c r="Z503" t="s" s="2">
-        <v>1166</v>
+        <v>1165</v>
       </c>
       <c r="AA503" t="s" s="2">
-        <v>943</v>
+        <v>942</v>
       </c>
       <c r="AB503" t="s" s="2">
         <v>23</v>
@@ -58699,7 +58695,7 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1163</v>
+        <v>1162</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
@@ -58716,13 +58712,13 @@
     </row>
     <row r="504">
       <c r="A504" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B504" t="s" s="2">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="C504" t="s" s="2">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="D504" s="2"/>
       <c r="E504" t="s" s="2">
@@ -58748,10 +58744,10 @@
         <v>367</v>
       </c>
       <c r="M504" t="s" s="2">
+        <v>1167</v>
+      </c>
+      <c r="N504" t="s" s="2">
         <v>1168</v>
-      </c>
-      <c r="N504" t="s" s="2">
-        <v>1169</v>
       </c>
       <c r="O504" s="2"/>
       <c r="P504" s="2"/>
@@ -58781,11 +58777,11 @@
         <v>372</v>
       </c>
       <c r="Z504" t="s" s="2">
+        <v>946</v>
+      </c>
+      <c r="AA504" t="s" s="2">
         <v>947</v>
       </c>
-      <c r="AA504" t="s" s="2">
-        <v>948</v>
-      </c>
       <c r="AB504" t="s" s="2">
         <v>23</v>
       </c>
@@ -58802,7 +58798,7 @@
         <v>23</v>
       </c>
       <c r="AG504" t="s" s="2">
-        <v>1167</v>
+        <v>1166</v>
       </c>
       <c r="AH504" t="s" s="2">
         <v>76</v>
@@ -58819,13 +58815,13 @@
     </row>
     <row r="505">
       <c r="A505" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B505" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="C505" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="D505" s="2"/>
       <c r="E505" t="s" s="2">
@@ -58848,13 +58844,13 @@
         <v>23</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>833</v>
+        <v>832</v>
       </c>
       <c r="M505" t="s" s="2">
+        <v>1170</v>
+      </c>
+      <c r="N505" t="s" s="2">
         <v>1171</v>
-      </c>
-      <c r="N505" t="s" s="2">
-        <v>1172</v>
       </c>
       <c r="O505" s="2"/>
       <c r="P505" s="2"/>
@@ -58905,7 +58901,7 @@
         <v>23</v>
       </c>
       <c r="AG505" t="s" s="2">
-        <v>1170</v>
+        <v>1169</v>
       </c>
       <c r="AH505" t="s" s="2">
         <v>76</v>
@@ -58922,17 +58918,17 @@
     </row>
     <row r="506">
       <c r="A506" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>954</v>
+        <v>953</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
@@ -58951,16 +58947,16 @@
         <v>23</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>955</v>
+        <v>954</v>
       </c>
       <c r="M506" t="s" s="2">
+        <v>1173</v>
+      </c>
+      <c r="N506" t="s" s="2">
         <v>1174</v>
       </c>
-      <c r="N506" t="s" s="2">
-        <v>1175</v>
-      </c>
       <c r="O506" t="s" s="2">
-        <v>958</v>
+        <v>957</v>
       </c>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
@@ -59010,7 +59006,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1173</v>
+        <v>1172</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59027,13 +59023,13 @@
     </row>
     <row r="507">
       <c r="A507" t="s" s="2">
-        <v>1031</v>
+        <v>1030</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59056,16 +59052,16 @@
         <v>23</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>960</v>
+        <v>959</v>
       </c>
       <c r="M507" t="s" s="2">
+        <v>1176</v>
+      </c>
+      <c r="N507" t="s" s="2">
         <v>1177</v>
       </c>
-      <c r="N507" t="s" s="2">
+      <c r="O507" t="s" s="2">
         <v>1178</v>
-      </c>
-      <c r="O507" t="s" s="2">
-        <v>1179</v>
       </c>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
@@ -59115,7 +59111,7 @@
         <v>23</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1176</v>
+        <v>1175</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59132,13 +59128,13 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B508" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="C508" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
@@ -59164,10 +59160,10 @@
         <v>78</v>
       </c>
       <c r="M508" t="s" s="2">
+        <v>1186</v>
+      </c>
+      <c r="N508" t="s" s="2">
         <v>1187</v>
-      </c>
-      <c r="N508" t="s" s="2">
-        <v>1188</v>
       </c>
       <c r="O508" s="2"/>
       <c r="P508" s="2"/>
@@ -59218,7 +59214,7 @@
         <v>23</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1185</v>
+        <v>1184</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
@@ -59235,13 +59231,13 @@
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1189</v>
+        <v>1188</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59340,13 +59336,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1190</v>
+        <v>1189</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59443,13 +59439,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1191</v>
+        <v>1190</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59548,13 +59544,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1192</v>
+        <v>1191</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59653,13 +59649,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1193</v>
+        <v>1192</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59758,13 +59754,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1194</v>
+        <v>1193</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59863,13 +59859,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1195</v>
+        <v>1194</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59968,13 +59964,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1196</v>
+        <v>1195</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -60075,13 +60071,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60107,13 +60103,13 @@
         <v>112</v>
       </c>
       <c r="M517" t="s" s="2">
+        <v>1197</v>
+      </c>
+      <c r="N517" t="s" s="2">
         <v>1198</v>
       </c>
-      <c r="N517" t="s" s="2">
+      <c r="O517" t="s" s="2">
         <v>1199</v>
-      </c>
-      <c r="O517" t="s" s="2">
-        <v>1200</v>
       </c>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
@@ -60163,7 +60159,7 @@
         <v>23</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1197</v>
+        <v>1196</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
@@ -60180,13 +60176,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60212,10 +60208,10 @@
         <v>103</v>
       </c>
       <c r="M518" t="s" s="2">
+        <v>1201</v>
+      </c>
+      <c r="N518" t="s" s="2">
         <v>1202</v>
-      </c>
-      <c r="N518" t="s" s="2">
-        <v>1203</v>
       </c>
       <c r="O518" s="2"/>
       <c r="P518" s="2"/>
@@ -60245,11 +60241,11 @@
         <v>121</v>
       </c>
       <c r="Z518" t="s" s="2">
+        <v>1202</v>
+      </c>
+      <c r="AA518" t="s" s="2">
         <v>1203</v>
       </c>
-      <c r="AA518" t="s" s="2">
-        <v>1204</v>
-      </c>
       <c r="AB518" t="s" s="2">
         <v>23</v>
       </c>
@@ -60266,7 +60262,7 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1201</v>
+        <v>1200</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
@@ -60283,13 +60279,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60315,13 +60311,13 @@
         <v>367</v>
       </c>
       <c r="M519" t="s" s="2">
+        <v>1205</v>
+      </c>
+      <c r="N519" t="s" s="2">
         <v>1206</v>
       </c>
-      <c r="N519" t="s" s="2">
+      <c r="O519" t="s" s="2">
         <v>1207</v>
-      </c>
-      <c r="O519" t="s" s="2">
-        <v>1208</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60347,14 +60343,14 @@
         <v>23</v>
       </c>
       <c r="Y519" t="s" s="2">
+        <v>1208</v>
+      </c>
+      <c r="Z519" t="s" s="2">
         <v>1209</v>
       </c>
-      <c r="Z519" t="s" s="2">
+      <c r="AA519" t="s" s="2">
         <v>1210</v>
       </c>
-      <c r="AA519" t="s" s="2">
-        <v>1211</v>
-      </c>
       <c r="AB519" t="s" s="2">
         <v>23</v>
       </c>
@@ -60371,7 +60367,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1205</v>
+        <v>1204</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
@@ -60388,13 +60384,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60420,13 +60416,13 @@
         <v>367</v>
       </c>
       <c r="M520" t="s" s="2">
+        <v>1212</v>
+      </c>
+      <c r="N520" t="s" s="2">
         <v>1213</v>
       </c>
-      <c r="N520" t="s" s="2">
+      <c r="O520" t="s" s="2">
         <v>1214</v>
-      </c>
-      <c r="O520" t="s" s="2">
-        <v>1215</v>
       </c>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
@@ -60455,11 +60451,11 @@
         <v>372</v>
       </c>
       <c r="Z520" t="s" s="2">
+        <v>1215</v>
+      </c>
+      <c r="AA520" t="s" s="2">
         <v>1216</v>
       </c>
-      <c r="AA520" t="s" s="2">
-        <v>1217</v>
-      </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
       </c>
@@ -60476,7 +60472,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1212</v>
+        <v>1211</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>83</v>
@@ -60493,13 +60489,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60525,10 +60521,10 @@
         <v>141</v>
       </c>
       <c r="M521" t="s" s="2">
+        <v>1218</v>
+      </c>
+      <c r="N521" t="s" s="2">
         <v>1219</v>
-      </c>
-      <c r="N521" t="s" s="2">
-        <v>1220</v>
       </c>
       <c r="O521" s="2"/>
       <c r="P521" s="2"/>
@@ -60579,7 +60575,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1218</v>
+        <v>1217</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -60596,13 +60592,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60628,10 +60624,10 @@
         <v>136</v>
       </c>
       <c r="M522" t="s" s="2">
+        <v>1221</v>
+      </c>
+      <c r="N522" t="s" s="2">
         <v>1222</v>
-      </c>
-      <c r="N522" t="s" s="2">
-        <v>1223</v>
       </c>
       <c r="O522" s="2"/>
       <c r="P522" s="2"/>
@@ -60639,7 +60635,7 @@
         <v>23</v>
       </c>
       <c r="R522" t="s" s="2">
-        <v>1224</v>
+        <v>1223</v>
       </c>
       <c r="S522" t="s" s="2">
         <v>23</v>
@@ -60684,7 +60680,7 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1221</v>
+        <v>1220</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>76</v>
@@ -60701,13 +60697,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1225</v>
+        <v>1224</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60804,13 +60800,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1226</v>
+        <v>1225</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60909,13 +60905,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1227</v>
+        <v>1226</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61016,13 +61012,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61048,10 +61044,10 @@
         <v>112</v>
       </c>
       <c r="M526" t="s" s="2">
+        <v>1228</v>
+      </c>
+      <c r="N526" t="s" s="2">
         <v>1229</v>
-      </c>
-      <c r="N526" t="s" s="2">
-        <v>1230</v>
       </c>
       <c r="O526" s="2"/>
       <c r="P526" s="2"/>
@@ -61102,7 +61098,7 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1228</v>
+        <v>1227</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
@@ -61119,13 +61115,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61151,10 +61147,10 @@
         <v>578</v>
       </c>
       <c r="M527" t="s" s="2">
+        <v>1231</v>
+      </c>
+      <c r="N527" t="s" s="2">
         <v>1232</v>
-      </c>
-      <c r="N527" t="s" s="2">
-        <v>1233</v>
       </c>
       <c r="O527" s="2"/>
       <c r="P527" s="2"/>
@@ -61205,7 +61201,7 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1231</v>
+        <v>1230</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
@@ -61222,13 +61218,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61254,10 +61250,10 @@
         <v>497</v>
       </c>
       <c r="M528" t="s" s="2">
+        <v>1234</v>
+      </c>
+      <c r="N528" t="s" s="2">
         <v>1235</v>
-      </c>
-      <c r="N528" t="s" s="2">
-        <v>1236</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61308,7 +61304,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1234</v>
+        <v>1233</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61325,13 +61321,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61357,10 +61353,10 @@
         <v>136</v>
       </c>
       <c r="M529" t="s" s="2">
+        <v>1237</v>
+      </c>
+      <c r="N529" t="s" s="2">
         <v>1238</v>
-      </c>
-      <c r="N529" t="s" s="2">
-        <v>1239</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61411,7 +61407,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1237</v>
+        <v>1236</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61428,13 +61424,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1240</v>
+        <v>1239</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61531,13 +61527,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1241</v>
+        <v>1240</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61636,13 +61632,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1242</v>
+        <v>1241</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61743,13 +61739,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61775,10 +61771,10 @@
         <v>491</v>
       </c>
       <c r="M533" t="s" s="2">
+        <v>1243</v>
+      </c>
+      <c r="N533" t="s" s="2">
         <v>1244</v>
-      </c>
-      <c r="N533" t="s" s="2">
-        <v>1245</v>
       </c>
       <c r="O533" s="2"/>
       <c r="P533" s="2"/>
@@ -61829,7 +61825,7 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1243</v>
+        <v>1242</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>76</v>
@@ -61846,13 +61842,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1180</v>
+        <v>1179</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61875,13 +61871,13 @@
         <v>84</v>
       </c>
       <c r="L534" t="s" s="2">
+        <v>1246</v>
+      </c>
+      <c r="M534" t="s" s="2">
         <v>1247</v>
       </c>
-      <c r="M534" t="s" s="2">
+      <c r="N534" t="s" s="2">
         <v>1248</v>
-      </c>
-      <c r="N534" t="s" s="2">
-        <v>1249</v>
       </c>
       <c r="O534" s="2"/>
       <c r="P534" s="2"/>
@@ -61911,10 +61907,10 @@
         <v>372</v>
       </c>
       <c r="Z534" t="s" s="2">
-        <v>1250</v>
+        <v>1249</v>
       </c>
       <c r="AA534" t="s" s="2">
-        <v>1217</v>
+        <v>1216</v>
       </c>
       <c r="AB534" t="s" s="2">
         <v>23</v>
@@ -61932,7 +61928,7 @@
         <v>23</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1246</v>
+        <v>1245</v>
       </c>
       <c r="AH534" t="s" s="2">
         <v>83</v>
@@ -61949,13 +61945,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -61981,13 +61977,13 @@
         <v>78</v>
       </c>
       <c r="M535" t="s" s="2">
+        <v>1256</v>
+      </c>
+      <c r="N535" t="s" s="2">
         <v>1257</v>
       </c>
-      <c r="N535" t="s" s="2">
+      <c r="O535" t="s" s="2">
         <v>1258</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>1259</v>
       </c>
       <c r="P535" s="2"/>
       <c r="Q535" t="s" s="2">
@@ -62037,7 +62033,7 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1255</v>
+        <v>1254</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -62054,13 +62050,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1260</v>
+        <v>1259</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62157,13 +62153,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1261</v>
+        <v>1260</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62262,13 +62258,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1262</v>
+        <v>1261</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62369,13 +62365,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62401,14 +62397,14 @@
         <v>578</v>
       </c>
       <c r="M539" t="s" s="2">
+        <v>1263</v>
+      </c>
+      <c r="N539" t="s" s="2">
         <v>1264</v>
-      </c>
-      <c r="N539" t="s" s="2">
-        <v>1265</v>
       </c>
       <c r="O539" s="2"/>
       <c r="P539" t="s" s="2">
-        <v>1266</v>
+        <v>1265</v>
       </c>
       <c r="Q539" t="s" s="2">
         <v>23</v>
@@ -62457,7 +62453,7 @@
         <v>23</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1263</v>
+        <v>1262</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
@@ -62474,13 +62470,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62506,14 +62502,14 @@
         <v>418</v>
       </c>
       <c r="M540" t="s" s="2">
+        <v>1267</v>
+      </c>
+      <c r="N540" t="s" s="2">
         <v>1268</v>
-      </c>
-      <c r="N540" t="s" s="2">
-        <v>1269</v>
       </c>
       <c r="O540" s="2"/>
       <c r="P540" t="s" s="2">
-        <v>1270</v>
+        <v>1269</v>
       </c>
       <c r="Q540" t="s" s="2">
         <v>23</v>
@@ -62562,7 +62558,7 @@
         <v>23</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1267</v>
+        <v>1266</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>76</v>
@@ -62574,18 +62570,18 @@
         <v>23</v>
       </c>
       <c r="AK540" t="s" s="2">
-        <v>1271</v>
+        <v>1270</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1272</v>
+        <v>1271</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62682,13 +62678,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1273</v>
+        <v>1272</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62787,13 +62783,13 @@
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62816,13 +62812,13 @@
         <v>84</v>
       </c>
       <c r="L543" t="s" s="2">
+        <v>1274</v>
+      </c>
+      <c r="M543" t="s" s="2">
         <v>1275</v>
       </c>
-      <c r="M543" t="s" s="2">
+      <c r="N543" t="s" s="2">
         <v>1276</v>
-      </c>
-      <c r="N543" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -62871,7 +62867,7 @@
         <v>355</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -62888,16 +62884,16 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B544" t="s" s="2">
+        <v>1277</v>
+      </c>
+      <c r="C544" t="s" s="2">
+        <v>1273</v>
+      </c>
+      <c r="D544" t="s" s="2">
         <v>1278</v>
-      </c>
-      <c r="C544" t="s" s="2">
-        <v>1274</v>
-      </c>
-      <c r="D544" t="s" s="2">
-        <v>1279</v>
       </c>
       <c r="E544" t="s" s="2">
         <v>23</v>
@@ -62919,13 +62915,13 @@
         <v>84</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>903</v>
+        <v>902</v>
       </c>
       <c r="M544" t="s" s="2">
+        <v>1275</v>
+      </c>
+      <c r="N544" t="s" s="2">
         <v>1276</v>
-      </c>
-      <c r="N544" t="s" s="2">
-        <v>1277</v>
       </c>
       <c r="O544" s="2"/>
       <c r="P544" s="2"/>
@@ -62976,7 +62972,7 @@
         <v>23</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1274</v>
+        <v>1273</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
@@ -62993,13 +62989,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B545" t="s" s="2">
+        <v>1279</v>
+      </c>
+      <c r="C545" t="s" s="2">
         <v>1280</v>
-      </c>
-      <c r="C545" t="s" s="2">
-        <v>1281</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63096,13 +63092,13 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B546" t="s" s="2">
+        <v>1281</v>
+      </c>
+      <c r="C546" t="s" s="2">
         <v>1282</v>
-      </c>
-      <c r="C546" t="s" s="2">
-        <v>1283</v>
       </c>
       <c r="D546" s="2"/>
       <c r="E546" t="s" s="2">
@@ -63201,13 +63197,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B547" t="s" s="2">
+        <v>1283</v>
+      </c>
+      <c r="C547" t="s" s="2">
         <v>1284</v>
-      </c>
-      <c r="C547" t="s" s="2">
-        <v>1285</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63233,13 +63229,13 @@
         <v>578</v>
       </c>
       <c r="M547" t="s" s="2">
+        <v>1285</v>
+      </c>
+      <c r="N547" t="s" s="2">
         <v>1286</v>
       </c>
-      <c r="N547" t="s" s="2">
+      <c r="O547" t="s" s="2">
         <v>1287</v>
-      </c>
-      <c r="O547" t="s" s="2">
-        <v>1288</v>
       </c>
       <c r="P547" s="2"/>
       <c r="Q547" t="s" s="2">
@@ -63289,16 +63285,16 @@
         <v>23</v>
       </c>
       <c r="AG547" t="s" s="2">
+        <v>1288</v>
+      </c>
+      <c r="AH547" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI547" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ547" t="s" s="2">
         <v>1289</v>
-      </c>
-      <c r="AH547" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI547" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ547" t="s" s="2">
-        <v>1290</v>
       </c>
       <c r="AK547" t="s" s="2">
         <v>95</v>
@@ -63306,13 +63302,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B548" t="s" s="2">
+        <v>1290</v>
+      </c>
+      <c r="C548" t="s" s="2">
         <v>1291</v>
-      </c>
-      <c r="C548" t="s" s="2">
-        <v>1292</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63338,66 +63334,66 @@
         <v>578</v>
       </c>
       <c r="M548" t="s" s="2">
+        <v>1292</v>
+      </c>
+      <c r="N548" t="s" s="2">
         <v>1293</v>
       </c>
-      <c r="N548" t="s" s="2">
+      <c r="O548" t="s" s="2">
         <v>1294</v>
-      </c>
-      <c r="O548" t="s" s="2">
-        <v>1295</v>
       </c>
       <c r="P548" s="2"/>
       <c r="Q548" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R548" t="s" s="2">
+        <v>1295</v>
+      </c>
+      <c r="S548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF548" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG548" t="s" s="2">
         <v>1296</v>
       </c>
-      <c r="S548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AB548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF548" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG548" t="s" s="2">
-        <v>1297</v>
-      </c>
       <c r="AH548" t="s" s="2">
         <v>76</v>
       </c>
@@ -63405,7 +63401,7 @@
         <v>83</v>
       </c>
       <c r="AJ548" t="s" s="2">
-        <v>1290</v>
+        <v>1289</v>
       </c>
       <c r="AK548" t="s" s="2">
         <v>95</v>
@@ -63413,13 +63409,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63442,19 +63438,19 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
+        <v>1298</v>
+      </c>
+      <c r="M549" t="s" s="2">
         <v>1299</v>
       </c>
-      <c r="M549" t="s" s="2">
+      <c r="N549" t="s" s="2">
         <v>1300</v>
       </c>
-      <c r="N549" t="s" s="2">
+      <c r="O549" t="s" s="2">
         <v>1301</v>
       </c>
-      <c r="O549" t="s" s="2">
+      <c r="P549" t="s" s="2">
         <v>1302</v>
-      </c>
-      <c r="P549" t="s" s="2">
-        <v>1303</v>
       </c>
       <c r="Q549" t="s" s="2">
         <v>23</v>
@@ -63503,7 +63499,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1298</v>
+        <v>1297</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63520,13 +63516,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63549,13 +63545,13 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="M550" t="s" s="2">
+        <v>1304</v>
+      </c>
+      <c r="N550" t="s" s="2">
         <v>1305</v>
-      </c>
-      <c r="N550" t="s" s="2">
-        <v>1306</v>
       </c>
       <c r="O550" s="2"/>
       <c r="P550" s="2"/>
@@ -63606,7 +63602,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1304</v>
+        <v>1303</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63623,13 +63619,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63655,16 +63651,16 @@
         <v>199</v>
       </c>
       <c r="M551" t="s" s="2">
+        <v>1307</v>
+      </c>
+      <c r="N551" t="s" s="2">
         <v>1308</v>
       </c>
-      <c r="N551" t="s" s="2">
+      <c r="O551" t="s" s="2">
         <v>1309</v>
       </c>
-      <c r="O551" t="s" s="2">
+      <c r="P551" t="s" s="2">
         <v>1310</v>
-      </c>
-      <c r="P551" t="s" s="2">
-        <v>1311</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63713,7 +63709,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1307</v>
+        <v>1306</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63730,13 +63726,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63762,16 +63758,16 @@
         <v>199</v>
       </c>
       <c r="M552" t="s" s="2">
+        <v>1312</v>
+      </c>
+      <c r="N552" t="s" s="2">
         <v>1313</v>
       </c>
-      <c r="N552" t="s" s="2">
-        <v>1314</v>
-      </c>
       <c r="O552" t="s" s="2">
+        <v>1309</v>
+      </c>
+      <c r="P552" t="s" s="2">
         <v>1310</v>
-      </c>
-      <c r="P552" t="s" s="2">
-        <v>1311</v>
       </c>
       <c r="Q552" t="s" s="2">
         <v>23</v>
@@ -63820,7 +63816,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1312</v>
+        <v>1311</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63837,13 +63833,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63869,10 +63865,10 @@
         <v>103</v>
       </c>
       <c r="M553" t="s" s="2">
+        <v>1315</v>
+      </c>
+      <c r="N553" t="s" s="2">
         <v>1316</v>
-      </c>
-      <c r="N553" t="s" s="2">
-        <v>1317</v>
       </c>
       <c r="O553" s="2"/>
       <c r="P553" s="2"/>
@@ -63902,11 +63898,11 @@
         <v>121</v>
       </c>
       <c r="Z553" t="s" s="2">
+        <v>1317</v>
+      </c>
+      <c r="AA553" t="s" s="2">
         <v>1318</v>
       </c>
-      <c r="AA553" t="s" s="2">
-        <v>1319</v>
-      </c>
       <c r="AB553" t="s" s="2">
         <v>23</v>
       </c>
@@ -63923,7 +63919,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1315</v>
+        <v>1314</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63940,13 +63936,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63969,13 +63965,13 @@
         <v>84</v>
       </c>
       <c r="L554" t="s" s="2">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="M554" t="s" s="2">
+        <v>1320</v>
+      </c>
+      <c r="N554" t="s" s="2">
         <v>1321</v>
-      </c>
-      <c r="N554" t="s" s="2">
-        <v>1322</v>
       </c>
       <c r="O554" s="2"/>
       <c r="P554" s="2"/>
@@ -63983,7 +63979,7 @@
         <v>23</v>
       </c>
       <c r="R554" t="s" s="2">
-        <v>1323</v>
+        <v>1322</v>
       </c>
       <c r="S554" t="s" s="2">
         <v>23</v>
@@ -64028,7 +64024,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1320</v>
+        <v>1319</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64045,13 +64041,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64074,13 +64070,13 @@
         <v>84</v>
       </c>
       <c r="L555" t="s" s="2">
-        <v>1299</v>
+        <v>1298</v>
       </c>
       <c r="M555" t="s" s="2">
+        <v>1324</v>
+      </c>
+      <c r="N555" t="s" s="2">
         <v>1325</v>
-      </c>
-      <c r="N555" t="s" s="2">
-        <v>1326</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64131,7 +64127,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1324</v>
+        <v>1323</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64148,13 +64144,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64180,10 +64176,10 @@
         <v>199</v>
       </c>
       <c r="M556" t="s" s="2">
+        <v>1327</v>
+      </c>
+      <c r="N556" t="s" s="2">
         <v>1328</v>
-      </c>
-      <c r="N556" t="s" s="2">
-        <v>1329</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64234,7 +64230,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1327</v>
+        <v>1326</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64251,13 +64247,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64283,10 +64279,10 @@
         <v>199</v>
       </c>
       <c r="M557" t="s" s="2">
+        <v>1330</v>
+      </c>
+      <c r="N557" t="s" s="2">
         <v>1331</v>
-      </c>
-      <c r="N557" t="s" s="2">
-        <v>1332</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64337,7 +64333,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1330</v>
+        <v>1329</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64354,13 +64350,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64386,10 +64382,10 @@
         <v>103</v>
       </c>
       <c r="M558" t="s" s="2">
+        <v>1333</v>
+      </c>
+      <c r="N558" t="s" s="2">
         <v>1334</v>
-      </c>
-      <c r="N558" t="s" s="2">
-        <v>1335</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
@@ -64420,7 +64416,7 @@
       </c>
       <c r="Z558" s="2"/>
       <c r="AA558" t="s" s="2">
-        <v>1336</v>
+        <v>1335</v>
       </c>
       <c r="AB558" t="s" s="2">
         <v>23</v>
@@ -64438,7 +64434,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1333</v>
+        <v>1332</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64455,13 +64451,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64487,13 +64483,13 @@
         <v>103</v>
       </c>
       <c r="M559" t="s" s="2">
+        <v>1337</v>
+      </c>
+      <c r="N559" t="s" s="2">
         <v>1338</v>
       </c>
-      <c r="N559" t="s" s="2">
+      <c r="O559" t="s" s="2">
         <v>1339</v>
-      </c>
-      <c r="O559" t="s" s="2">
-        <v>1340</v>
       </c>
       <c r="P559" s="2"/>
       <c r="Q559" t="s" s="2">
@@ -64523,7 +64519,7 @@
       </c>
       <c r="Z559" s="2"/>
       <c r="AA559" t="s" s="2">
-        <v>1341</v>
+        <v>1340</v>
       </c>
       <c r="AB559" t="s" s="2">
         <v>23</v>
@@ -64541,7 +64537,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1337</v>
+        <v>1336</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64558,13 +64554,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64587,16 +64583,16 @@
         <v>84</v>
       </c>
       <c r="L560" t="s" s="2">
+        <v>1342</v>
+      </c>
+      <c r="M560" t="s" s="2">
         <v>1343</v>
       </c>
-      <c r="M560" t="s" s="2">
+      <c r="N560" t="s" s="2">
         <v>1344</v>
       </c>
-      <c r="N560" t="s" s="2">
+      <c r="O560" t="s" s="2">
         <v>1345</v>
-      </c>
-      <c r="O560" t="s" s="2">
-        <v>1346</v>
       </c>
       <c r="P560" s="2"/>
       <c r="Q560" t="s" s="2">
@@ -64646,7 +64642,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1342</v>
+        <v>1341</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64663,13 +64659,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64695,16 +64691,16 @@
         <v>103</v>
       </c>
       <c r="M561" t="s" s="2">
+        <v>1347</v>
+      </c>
+      <c r="N561" t="s" s="2">
         <v>1348</v>
       </c>
-      <c r="N561" t="s" s="2">
+      <c r="O561" t="s" s="2">
         <v>1349</v>
       </c>
-      <c r="O561" t="s" s="2">
+      <c r="P561" t="s" s="2">
         <v>1350</v>
-      </c>
-      <c r="P561" t="s" s="2">
-        <v>1351</v>
       </c>
       <c r="Q561" t="s" s="2">
         <v>23</v>
@@ -64733,7 +64729,7 @@
       </c>
       <c r="Z561" s="2"/>
       <c r="AA561" t="s" s="2">
-        <v>1352</v>
+        <v>1351</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64751,7 +64747,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1347</v>
+        <v>1346</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64768,13 +64764,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64800,10 +64796,10 @@
         <v>130</v>
       </c>
       <c r="M562" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="N562" t="s" s="2">
         <v>1354</v>
-      </c>
-      <c r="N562" t="s" s="2">
-        <v>1355</v>
       </c>
       <c r="O562" s="2"/>
       <c r="P562" s="2"/>
@@ -64854,7 +64850,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1353</v>
+        <v>1352</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -64871,13 +64867,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1251</v>
+        <v>1250</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -64903,13 +64899,13 @@
         <v>367</v>
       </c>
       <c r="M563" t="s" s="2">
+        <v>1356</v>
+      </c>
+      <c r="N563" t="s" s="2">
         <v>1357</v>
       </c>
-      <c r="N563" t="s" s="2">
+      <c r="O563" t="s" s="2">
         <v>1358</v>
-      </c>
-      <c r="O563" t="s" s="2">
-        <v>1359</v>
       </c>
       <c r="P563" s="2"/>
       <c r="Q563" t="s" s="2">
@@ -64938,11 +64934,11 @@
         <v>107</v>
       </c>
       <c r="Z563" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="AA563" t="s" s="2">
         <v>1360</v>
       </c>
-      <c r="AA563" t="s" s="2">
-        <v>1361</v>
-      </c>
       <c r="AB563" t="s" s="2">
         <v>23</v>
       </c>
@@ -64959,7 +64955,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1356</v>
+        <v>1355</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-27T13:46:49+00:00</t>
+    <t>2026-05-28T11:16:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18866" uniqueCount="1361">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18933" uniqueCount="1368">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-05-28T11:16:16+00:00</t>
+    <t>2026-06-01T11:23:56+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1204,7 +1204,7 @@
     <t>Dosage.timing</t>
   </si>
   <si>
-    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing-zeiten}
+    <t xml:space="preserve">Timing {https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing}
 </t>
   </si>
   <si>
@@ -2175,7 +2175,7 @@
   </si>
   <si>
     <t>CodeableConcept
-Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-substanz) &lt;&lt;contained&gt;&gt;</t>
+Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;</t>
   </si>
   <si>
     <t>The actual ingredient or content</t>
@@ -2199,7 +2199,7 @@
     <t>itemReference</t>
   </si>
   <si>
-    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-substanz) &lt;&lt;contained&gt;&gt;
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff) &lt;&lt;contained&gt;&gt;
 </t>
   </si>
   <si>
@@ -3269,10 +3269,10 @@
     <t>Referenz auf Provenance-Ressourcen, die verschiedene relevante Versionen dieser Ressource dokumentieren. Keine Verwendung im Medikationsplaneintrag.</t>
   </si>
   <si>
-    <t>at-elga-emed-medikationdispense-durchgefuehrteAbgabe</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medikationdispense-durchgefuehrteAbgabe</t>
+    <t>at-elga-emed-medikationdispense-durchgefuehrteabgabe</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medikationdispense-durchgefuehrteabgabe</t>
   </si>
   <si>
     <t>AtElgaEmedMedicationDispenseDurchgefuehrteAbgabe</t>
@@ -3551,13 +3551,38 @@
     <t>MedicationDispense.authorizingPrescription</t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. Planeintrag (MedicationRequest).</t>
+    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
+Planeintrag (MedicationRequest). Es muss nicht zwingend eine geplante Abgabe referenziert werden, da es auch durchgeführte 
+Abgaben ohne geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
   </si>
   <si>
     <t>Maps to basedOn in Event logical model.</t>
+  </si>
+  <si>
+    <t xml:space="preserve">value:reference.ofType(MedicationRequest).category}
+</t>
+  </si>
+  <si>
+    <t>MedicationDispense.authorizingPrescription:geplanteAbgabe</t>
+  </si>
+  <si>
+    <t>geplanteAbgabe</t>
+  </si>
+  <si>
+    <t xml:space="preserve">Reference(https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-medicationrequest-geplanteabgabe)
+</t>
+  </si>
+  <si>
+    <t>Medication order that authorizes the dispense</t>
+  </si>
+  <si>
+    <t>MedicationDispense.authorizingPrescription:planeintrag</t>
+  </si>
+  <si>
+    <t>planeintrag</t>
   </si>
   <si>
     <t>MedicationDispense.type</t>
@@ -3733,19 +3758,19 @@
     <t>This might not include provenances for all versions of the request – only those deemed “relevant” or important. This SHALL NOT include the Provenance associated with this current version of the resource. (If that provenance is deemed to be a “relevant” change, it will need to be added as part of a later update. Until then, it can be queried directly as the Provenance that points to this version using _revinclude All Provenances should have some historical version of this Request as their subject.).</t>
   </si>
   <si>
-    <t>at-elga-emed-substance-substanz</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-substanz</t>
-  </si>
-  <si>
-    <t>AtElgaEmedSubstanceSubstanz</t>
-  </si>
-  <si>
-    <t>At ELGA e-Medikation Substance Substanz</t>
-  </si>
-  <si>
-    <t>Dokumentation der Substanz eines Inhaltsstoffes eines Arzneimittels in der ELGA e-Medikation, sofern es nicht kodiert vorliegt.</t>
+    <t>at-elga-emed-substance-wirkstoff</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-substance-wirkstoff</t>
+  </si>
+  <si>
+    <t>AtElgaEmedSubstanceWirkstoff</t>
+  </si>
+  <si>
+    <t>At ELGA e-Medikation Substance Wirkstoff</t>
+  </si>
+  <si>
+    <t>Dokumentation des Wirkstoffs eines Arzneimittels in der ELGA e-Medikation, sofern es nicht kodiert vorliegt.</t>
   </si>
   <si>
     <t>Substance</t>
@@ -3947,16 +3972,16 @@
     <t>Substance Ingredient codes.</t>
   </si>
   <si>
-    <t>at-elga-emed-timing-zeiten</t>
-  </si>
-  <si>
-    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing-zeiten</t>
-  </si>
-  <si>
-    <t>AtElgaEmedTimingZeiten</t>
-  </si>
-  <si>
-    <t>AT ELGA e-Medikation Timing Zeiten</t>
+    <t>at-elga-emed-timing</t>
+  </si>
+  <si>
+    <t>https://fhir.hl7.at/elga/emed/r4/StructureDefinition/at-elga-emed-timing</t>
+  </si>
+  <si>
+    <t>AtElgaEmedTiming</t>
+  </si>
+  <si>
+    <t>AT ELGA e-Medikation Timing</t>
   </si>
   <si>
     <t>Timing</t>
@@ -5797,7 +5822,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
     </row>
     <row r="179">
@@ -5805,7 +5830,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1180</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="180">
@@ -5821,7 +5846,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1181</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="182">
@@ -5829,7 +5854,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1182</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="183">
@@ -5891,7 +5916,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1183</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="191">
@@ -5927,7 +5952,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1184</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="196">
@@ -5935,7 +5960,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1185</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="197">
@@ -5967,7 +5992,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
     </row>
     <row r="201">
@@ -5975,7 +6000,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1251</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="202">
@@ -5991,7 +6016,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1252</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="204">
@@ -5999,7 +6024,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1253</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="205">
@@ -6061,7 +6086,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1253</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="213">
@@ -6097,7 +6122,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1254</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="218">
@@ -6105,7 +6130,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1255</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="219">
@@ -6131,10 +6156,10 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <dimension ref="A1:AK563"/>
+  <dimension ref="A1:AK565"/>
   <sheetFormatPr defaultRowHeight="15.0"/>
   <cols>
-    <col min="1" max="1" width="46.59375" customWidth="true" bestFit="true"/>
+    <col min="1" max="1" width="46.48046875" customWidth="true" bestFit="true"/>
     <col min="2" max="2" width="59.5390625" customWidth="true" bestFit="true"/>
     <col min="3" max="3" width="59.5390625" customWidth="true" bestFit="true" hidden="true"/>
     <col min="4" max="4" width="25.4140625" customWidth="true" bestFit="true" hidden="true"/>
@@ -6162,7 +6187,7 @@
     <col min="26" max="26" width="169.7734375" customWidth="true" bestFit="true"/>
     <col min="27" max="27" width="61.125" customWidth="true" bestFit="true"/>
     <col min="28" max="28" width="5.44140625" customWidth="true" bestFit="true"/>
-    <col min="29" max="29" width="19.4765625" customWidth="true" bestFit="true"/>
+    <col min="29" max="29" width="43.8828125" customWidth="true" bestFit="true"/>
     <col min="30" max="30" width="36.0390625" customWidth="true" bestFit="true"/>
     <col min="31" max="31" width="14.7578125" customWidth="true" bestFit="true" hidden="true"/>
     <col min="32" max="32" width="12.359375" customWidth="true" bestFit="true" hidden="true"/>
@@ -57071,10 +57096,10 @@
         <v>76</v>
       </c>
       <c r="H488" t="s" s="2">
-        <v>770</v>
+        <v>77</v>
       </c>
       <c r="I488" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J488" t="s" s="2">
         <v>23</v>
@@ -57130,16 +57155,14 @@
         <v>23</v>
       </c>
       <c r="AC488" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD488" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>1123</v>
+      </c>
+      <c r="AD488" s="2"/>
       <c r="AE488" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF488" t="s" s="2">
-        <v>23</v>
+        <v>169</v>
       </c>
       <c r="AG488" t="s" s="2">
         <v>1119</v>
@@ -57162,18 +57185,20 @@
         <v>1030</v>
       </c>
       <c r="B489" t="s" s="2">
-        <v>1123</v>
+        <v>1124</v>
       </c>
       <c r="C489" t="s" s="2">
-        <v>1123</v>
-      </c>
-      <c r="D489" s="2"/>
+        <v>1119</v>
+      </c>
+      <c r="D489" t="s" s="2">
+        <v>1125</v>
+      </c>
       <c r="E489" t="s" s="2">
         <v>23</v>
       </c>
       <c r="F489" s="2"/>
       <c r="G489" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H489" t="s" s="2">
         <v>83</v>
@@ -57188,15 +57213,17 @@
         <v>23</v>
       </c>
       <c r="L489" t="s" s="2">
-        <v>367</v>
+        <v>1126</v>
       </c>
       <c r="M489" t="s" s="2">
-        <v>1124</v>
+        <v>1127</v>
       </c>
       <c r="N489" t="s" s="2">
-        <v>1125</v>
-      </c>
-      <c r="O489" s="2"/>
+        <v>1121</v>
+      </c>
+      <c r="O489" t="s" s="2">
+        <v>1122</v>
+      </c>
       <c r="P489" s="2"/>
       <c r="Q489" t="s" s="2">
         <v>23</v>
@@ -57221,13 +57248,13 @@
         <v>23</v>
       </c>
       <c r="Y489" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z489" t="s" s="2">
-        <v>1125</v>
+        <v>23</v>
       </c>
       <c r="AA489" t="s" s="2">
-        <v>1126</v>
+        <v>23</v>
       </c>
       <c r="AB489" t="s" s="2">
         <v>23</v>
@@ -57245,13 +57272,13 @@
         <v>23</v>
       </c>
       <c r="AG489" t="s" s="2">
-        <v>1123</v>
+        <v>1119</v>
       </c>
       <c r="AH489" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI489" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ489" t="s" s="2">
         <v>23</v>
@@ -57265,18 +57292,20 @@
         <v>1030</v>
       </c>
       <c r="B490" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="C490" t="s" s="2">
-        <v>1127</v>
-      </c>
-      <c r="D490" s="2"/>
+        <v>1119</v>
+      </c>
+      <c r="D490" t="s" s="2">
+        <v>1129</v>
+      </c>
       <c r="E490" t="s" s="2">
         <v>23</v>
       </c>
       <c r="F490" s="2"/>
       <c r="G490" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H490" t="s" s="2">
         <v>83</v>
@@ -57291,15 +57320,17 @@
         <v>23</v>
       </c>
       <c r="L490" t="s" s="2">
-        <v>497</v>
+        <v>627</v>
       </c>
       <c r="M490" t="s" s="2">
-        <v>1128</v>
+        <v>1127</v>
       </c>
       <c r="N490" t="s" s="2">
-        <v>1129</v>
-      </c>
-      <c r="O490" s="2"/>
+        <v>1121</v>
+      </c>
+      <c r="O490" t="s" s="2">
+        <v>1122</v>
+      </c>
       <c r="P490" s="2"/>
       <c r="Q490" t="s" s="2">
         <v>23</v>
@@ -57348,13 +57379,13 @@
         <v>23</v>
       </c>
       <c r="AG490" t="s" s="2">
-        <v>1127</v>
+        <v>1119</v>
       </c>
       <c r="AH490" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI490" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ490" t="s" s="2">
         <v>23</v>
@@ -57379,13 +57410,13 @@
       </c>
       <c r="F491" s="2"/>
       <c r="G491" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H491" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I491" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J491" t="s" s="2">
         <v>23</v>
@@ -57394,7 +57425,7 @@
         <v>23</v>
       </c>
       <c r="L491" t="s" s="2">
-        <v>497</v>
+        <v>367</v>
       </c>
       <c r="M491" t="s" s="2">
         <v>1131</v>
@@ -57427,13 +57458,13 @@
         <v>23</v>
       </c>
       <c r="Y491" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z491" t="s" s="2">
-        <v>23</v>
+        <v>1132</v>
       </c>
       <c r="AA491" t="s" s="2">
-        <v>23</v>
+        <v>1133</v>
       </c>
       <c r="AB491" t="s" s="2">
         <v>23</v>
@@ -57471,10 +57502,10 @@
         <v>1030</v>
       </c>
       <c r="B492" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="C492" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="D492" s="2"/>
       <c r="E492" t="s" s="2">
@@ -57482,28 +57513,28 @@
       </c>
       <c r="F492" s="2"/>
       <c r="G492" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H492" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I492" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J492" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K492" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L492" t="s" s="2">
-        <v>578</v>
+        <v>497</v>
       </c>
       <c r="M492" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="N492" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="O492" s="2"/>
       <c r="P492" s="2"/>
@@ -57554,7 +57585,7 @@
         <v>23</v>
       </c>
       <c r="AG492" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="AH492" t="s" s="2">
         <v>76</v>
@@ -57574,10 +57605,10 @@
         <v>1030</v>
       </c>
       <c r="B493" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="C493" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="D493" s="2"/>
       <c r="E493" t="s" s="2">
@@ -57585,13 +57616,13 @@
       </c>
       <c r="F493" s="2"/>
       <c r="G493" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H493" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I493" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J493" t="s" s="2">
         <v>23</v>
@@ -57600,13 +57631,13 @@
         <v>23</v>
       </c>
       <c r="L493" t="s" s="2">
-        <v>578</v>
+        <v>497</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="N493" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="O493" s="2"/>
       <c r="P493" s="2"/>
@@ -57657,7 +57688,7 @@
         <v>23</v>
       </c>
       <c r="AG493" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AH493" t="s" s="2">
         <v>76</v>
@@ -57677,10 +57708,10 @@
         <v>1030</v>
       </c>
       <c r="B494" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="C494" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="D494" s="2"/>
       <c r="E494" t="s" s="2">
@@ -57700,16 +57731,16 @@
         <v>23</v>
       </c>
       <c r="K494" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L494" t="s" s="2">
-        <v>1116</v>
+        <v>578</v>
       </c>
       <c r="M494" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="N494" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="O494" s="2"/>
       <c r="P494" s="2"/>
@@ -57760,7 +57791,7 @@
         <v>23</v>
       </c>
       <c r="AG494" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="AH494" t="s" s="2">
         <v>76</v>
@@ -57780,10 +57811,10 @@
         <v>1030</v>
       </c>
       <c r="B495" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="C495" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="D495" s="2"/>
       <c r="E495" t="s" s="2">
@@ -57791,13 +57822,13 @@
       </c>
       <c r="F495" s="2"/>
       <c r="G495" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H495" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I495" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J495" t="s" s="2">
         <v>23</v>
@@ -57806,7 +57837,7 @@
         <v>23</v>
       </c>
       <c r="L495" t="s" s="2">
-        <v>1143</v>
+        <v>578</v>
       </c>
       <c r="M495" t="s" s="2">
         <v>1144</v>
@@ -57863,13 +57894,13 @@
         <v>23</v>
       </c>
       <c r="AG495" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AH495" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI495" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ495" t="s" s="2">
         <v>23</v>
@@ -57897,10 +57928,10 @@
         <v>76</v>
       </c>
       <c r="H496" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I496" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J496" t="s" s="2">
         <v>23</v>
@@ -57909,7 +57940,7 @@
         <v>23</v>
       </c>
       <c r="L496" t="s" s="2">
-        <v>598</v>
+        <v>1116</v>
       </c>
       <c r="M496" t="s" s="2">
         <v>1147</v>
@@ -57972,7 +58003,7 @@
         <v>76</v>
       </c>
       <c r="AI496" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ496" t="s" s="2">
         <v>23</v>
@@ -58000,10 +58031,10 @@
         <v>76</v>
       </c>
       <c r="H497" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I497" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J497" t="s" s="2">
         <v>23</v>
@@ -58018,11 +58049,9 @@
         <v>1151</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>876</v>
-      </c>
-      <c r="O497" t="s" s="2">
         <v>1152</v>
       </c>
+      <c r="O497" s="2"/>
       <c r="P497" s="2"/>
       <c r="Q497" t="s" s="2">
         <v>23</v>
@@ -58105,10 +58134,10 @@
         <v>76</v>
       </c>
       <c r="H498" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I498" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J498" t="s" s="2">
         <v>23</v>
@@ -58117,7 +58146,7 @@
         <v>23</v>
       </c>
       <c r="L498" t="s" s="2">
-        <v>136</v>
+        <v>598</v>
       </c>
       <c r="M498" t="s" s="2">
         <v>1154</v>
@@ -58180,7 +58209,7 @@
         <v>76</v>
       </c>
       <c r="AI498" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ498" t="s" s="2">
         <v>23</v>
@@ -58208,10 +58237,10 @@
         <v>76</v>
       </c>
       <c r="H499" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I499" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J499" t="s" s="2">
         <v>23</v>
@@ -58220,15 +58249,17 @@
         <v>23</v>
       </c>
       <c r="L499" t="s" s="2">
-        <v>141</v>
+        <v>1157</v>
       </c>
       <c r="M499" t="s" s="2">
-        <v>142</v>
+        <v>1158</v>
       </c>
       <c r="N499" t="s" s="2">
-        <v>143</v>
-      </c>
-      <c r="O499" s="2"/>
+        <v>876</v>
+      </c>
+      <c r="O499" t="s" s="2">
+        <v>1159</v>
+      </c>
       <c r="P499" s="2"/>
       <c r="Q499" t="s" s="2">
         <v>23</v>
@@ -58277,19 +58308,19 @@
         <v>23</v>
       </c>
       <c r="AG499" t="s" s="2">
-        <v>144</v>
+        <v>1156</v>
       </c>
       <c r="AH499" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI499" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ499" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK499" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="500">
@@ -58297,21 +58328,21 @@
         <v>1030</v>
       </c>
       <c r="B500" t="s" s="2">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="C500" t="s" s="2">
-        <v>1157</v>
+        <v>1160</v>
       </c>
       <c r="D500" s="2"/>
       <c r="E500" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F500" s="2"/>
       <c r="G500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H500" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I500" t="s" s="2">
         <v>23</v>
@@ -58323,17 +58354,15 @@
         <v>23</v>
       </c>
       <c r="L500" t="s" s="2">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>148</v>
+        <v>1161</v>
       </c>
       <c r="N500" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O500" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1162</v>
+      </c>
+      <c r="O500" s="2"/>
       <c r="P500" s="2"/>
       <c r="Q500" t="s" s="2">
         <v>23</v>
@@ -58382,19 +58411,19 @@
         <v>23</v>
       </c>
       <c r="AG500" t="s" s="2">
-        <v>151</v>
+        <v>1160</v>
       </c>
       <c r="AH500" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI500" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ500" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK500" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="501">
@@ -58402,46 +58431,42 @@
         <v>1030</v>
       </c>
       <c r="B501" t="s" s="2">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="C501" t="s" s="2">
-        <v>1158</v>
+        <v>1163</v>
       </c>
       <c r="D501" s="2"/>
       <c r="E501" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F501" s="2"/>
       <c r="G501" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H501" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I501" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J501" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K501" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L501" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N501" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O501" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P501" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O501" s="2"/>
+      <c r="P501" s="2"/>
       <c r="Q501" t="s" s="2">
         <v>23</v>
       </c>
@@ -58489,19 +58514,19 @@
         <v>23</v>
       </c>
       <c r="AG501" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AH501" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI501" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ501" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK501" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="502">
@@ -58509,21 +58534,21 @@
         <v>1030</v>
       </c>
       <c r="B502" t="s" s="2">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="C502" t="s" s="2">
-        <v>1159</v>
+        <v>1164</v>
       </c>
       <c r="D502" s="2"/>
       <c r="E502" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F502" s="2"/>
       <c r="G502" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H502" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I502" t="s" s="2">
         <v>23</v>
@@ -58535,15 +58560,17 @@
         <v>23</v>
       </c>
       <c r="L502" t="s" s="2">
-        <v>385</v>
+        <v>147</v>
       </c>
       <c r="M502" t="s" s="2">
-        <v>1160</v>
+        <v>148</v>
       </c>
       <c r="N502" t="s" s="2">
-        <v>1161</v>
-      </c>
-      <c r="O502" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O502" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P502" s="2"/>
       <c r="Q502" t="s" s="2">
         <v>23</v>
@@ -58592,19 +58619,19 @@
         <v>23</v>
       </c>
       <c r="AG502" t="s" s="2">
-        <v>1159</v>
+        <v>151</v>
       </c>
       <c r="AH502" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI502" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ502" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK502" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="503">
@@ -58612,42 +58639,46 @@
         <v>1030</v>
       </c>
       <c r="B503" t="s" s="2">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="C503" t="s" s="2">
-        <v>1162</v>
+        <v>1165</v>
       </c>
       <c r="D503" s="2"/>
       <c r="E503" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F503" s="2"/>
       <c r="G503" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H503" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I503" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J503" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K503" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L503" t="s" s="2">
-        <v>367</v>
+        <v>147</v>
       </c>
       <c r="M503" t="s" s="2">
-        <v>1163</v>
+        <v>155</v>
       </c>
       <c r="N503" t="s" s="2">
-        <v>1164</v>
-      </c>
-      <c r="O503" s="2"/>
-      <c r="P503" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O503" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P503" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q503" t="s" s="2">
         <v>23</v>
       </c>
@@ -58671,13 +58702,13 @@
         <v>23</v>
       </c>
       <c r="Y503" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z503" t="s" s="2">
-        <v>1165</v>
+        <v>23</v>
       </c>
       <c r="AA503" t="s" s="2">
-        <v>942</v>
+        <v>23</v>
       </c>
       <c r="AB503" t="s" s="2">
         <v>23</v>
@@ -58695,19 +58726,19 @@
         <v>23</v>
       </c>
       <c r="AG503" t="s" s="2">
-        <v>1162</v>
+        <v>158</v>
       </c>
       <c r="AH503" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI503" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ503" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK503" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="504">
@@ -58726,10 +58757,10 @@
       </c>
       <c r="F504" s="2"/>
       <c r="G504" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H504" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I504" t="s" s="2">
         <v>23</v>
@@ -58741,7 +58772,7 @@
         <v>23</v>
       </c>
       <c r="L504" t="s" s="2">
-        <v>367</v>
+        <v>385</v>
       </c>
       <c r="M504" t="s" s="2">
         <v>1167</v>
@@ -58774,13 +58805,13 @@
         <v>23</v>
       </c>
       <c r="Y504" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z504" t="s" s="2">
-        <v>946</v>
+        <v>23</v>
       </c>
       <c r="AA504" t="s" s="2">
-        <v>947</v>
+        <v>23</v>
       </c>
       <c r="AB504" t="s" s="2">
         <v>23</v>
@@ -58801,10 +58832,10 @@
         <v>1166</v>
       </c>
       <c r="AH504" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI504" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ504" t="s" s="2">
         <v>23</v>
@@ -58832,7 +58863,7 @@
         <v>76</v>
       </c>
       <c r="H505" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I505" t="s" s="2">
         <v>23</v>
@@ -58844,7 +58875,7 @@
         <v>23</v>
       </c>
       <c r="L505" t="s" s="2">
-        <v>832</v>
+        <v>367</v>
       </c>
       <c r="M505" t="s" s="2">
         <v>1170</v>
@@ -58877,13 +58908,13 @@
         <v>23</v>
       </c>
       <c r="Y505" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z505" t="s" s="2">
-        <v>23</v>
+        <v>1172</v>
       </c>
       <c r="AA505" t="s" s="2">
-        <v>23</v>
+        <v>942</v>
       </c>
       <c r="AB505" t="s" s="2">
         <v>23</v>
@@ -58907,7 +58938,7 @@
         <v>76</v>
       </c>
       <c r="AI505" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ505" t="s" s="2">
         <v>23</v>
@@ -58921,21 +58952,21 @@
         <v>1030</v>
       </c>
       <c r="B506" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="C506" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="D506" s="2"/>
       <c r="E506" t="s" s="2">
-        <v>953</v>
+        <v>23</v>
       </c>
       <c r="F506" s="2"/>
       <c r="G506" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H506" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I506" t="s" s="2">
         <v>23</v>
@@ -58947,17 +58978,15 @@
         <v>23</v>
       </c>
       <c r="L506" t="s" s="2">
-        <v>954</v>
+        <v>367</v>
       </c>
       <c r="M506" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N506" t="s" s="2">
-        <v>1174</v>
-      </c>
-      <c r="O506" t="s" s="2">
-        <v>957</v>
-      </c>
+        <v>1175</v>
+      </c>
+      <c r="O506" s="2"/>
       <c r="P506" s="2"/>
       <c r="Q506" t="s" s="2">
         <v>23</v>
@@ -58982,13 +59011,13 @@
         <v>23</v>
       </c>
       <c r="Y506" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z506" t="s" s="2">
-        <v>23</v>
+        <v>946</v>
       </c>
       <c r="AA506" t="s" s="2">
-        <v>23</v>
+        <v>947</v>
       </c>
       <c r="AB506" t="s" s="2">
         <v>23</v>
@@ -59006,7 +59035,7 @@
         <v>23</v>
       </c>
       <c r="AG506" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="AH506" t="s" s="2">
         <v>76</v>
@@ -59026,10 +59055,10 @@
         <v>1030</v>
       </c>
       <c r="B507" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="C507" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="D507" s="2"/>
       <c r="E507" t="s" s="2">
@@ -59040,7 +59069,7 @@
         <v>76</v>
       </c>
       <c r="H507" t="s" s="2">
-        <v>76</v>
+        <v>77</v>
       </c>
       <c r="I507" t="s" s="2">
         <v>23</v>
@@ -59052,17 +59081,15 @@
         <v>23</v>
       </c>
       <c r="L507" t="s" s="2">
-        <v>959</v>
+        <v>832</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N507" t="s" s="2">
-        <v>1177</v>
-      </c>
-      <c r="O507" t="s" s="2">
         <v>1178</v>
       </c>
+      <c r="O507" s="2"/>
       <c r="P507" s="2"/>
       <c r="Q507" t="s" s="2">
         <v>23</v>
@@ -59111,7 +59138,7 @@
         <v>23</v>
       </c>
       <c r="AG507" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="AH507" t="s" s="2">
         <v>76</v>
@@ -59128,24 +59155,24 @@
     </row>
     <row r="508">
       <c r="A508" t="s" s="2">
+        <v>1030</v>
+      </c>
+      <c r="B508" t="s" s="2">
         <v>1179</v>
       </c>
-      <c r="B508" t="s" s="2">
-        <v>1184</v>
-      </c>
       <c r="C508" t="s" s="2">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="D508" s="2"/>
       <c r="E508" t="s" s="2">
-        <v>23</v>
+        <v>953</v>
       </c>
       <c r="F508" s="2"/>
       <c r="G508" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H508" t="s" s="2">
-        <v>77</v>
+        <v>76</v>
       </c>
       <c r="I508" t="s" s="2">
         <v>23</v>
@@ -59157,15 +59184,17 @@
         <v>23</v>
       </c>
       <c r="L508" t="s" s="2">
-        <v>78</v>
+        <v>954</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1186</v>
+        <v>1180</v>
       </c>
       <c r="N508" t="s" s="2">
-        <v>1187</v>
-      </c>
-      <c r="O508" s="2"/>
+        <v>1181</v>
+      </c>
+      <c r="O508" t="s" s="2">
+        <v>957</v>
+      </c>
       <c r="P508" s="2"/>
       <c r="Q508" t="s" s="2">
         <v>23</v>
@@ -59214,7 +59243,7 @@
         <v>23</v>
       </c>
       <c r="AG508" t="s" s="2">
-        <v>1184</v>
+        <v>1179</v>
       </c>
       <c r="AH508" t="s" s="2">
         <v>76</v>
@@ -59226,18 +59255,18 @@
         <v>23</v>
       </c>
       <c r="AK508" t="s" s="2">
-        <v>645</v>
+        <v>95</v>
       </c>
     </row>
     <row r="509">
       <c r="A509" t="s" s="2">
-        <v>1179</v>
+        <v>1030</v>
       </c>
       <c r="B509" t="s" s="2">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="C509" t="s" s="2">
-        <v>1188</v>
+        <v>1182</v>
       </c>
       <c r="D509" s="2"/>
       <c r="E509" t="s" s="2">
@@ -59248,7 +59277,7 @@
         <v>76</v>
       </c>
       <c r="H509" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="I509" t="s" s="2">
         <v>23</v>
@@ -59257,19 +59286,19 @@
         <v>23</v>
       </c>
       <c r="K509" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L509" t="s" s="2">
-        <v>85</v>
+        <v>959</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>86</v>
+        <v>1183</v>
       </c>
       <c r="N509" t="s" s="2">
-        <v>87</v>
+        <v>1184</v>
       </c>
       <c r="O509" t="s" s="2">
-        <v>88</v>
+        <v>1185</v>
       </c>
       <c r="P509" s="2"/>
       <c r="Q509" t="s" s="2">
@@ -59319,30 +59348,30 @@
         <v>23</v>
       </c>
       <c r="AG509" t="s" s="2">
-        <v>89</v>
+        <v>1182</v>
       </c>
       <c r="AH509" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI509" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ509" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK509" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1189</v>
+        <v>1191</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59353,7 +59382,7 @@
         <v>76</v>
       </c>
       <c r="H510" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I510" t="s" s="2">
         <v>23</v>
@@ -59362,16 +59391,16 @@
         <v>23</v>
       </c>
       <c r="K510" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L510" t="s" s="2">
-        <v>91</v>
+        <v>78</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>92</v>
+        <v>1193</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>93</v>
+        <v>1194</v>
       </c>
       <c r="O510" s="2"/>
       <c r="P510" s="2"/>
@@ -59422,30 +59451,30 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>94</v>
+        <v>1191</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI510" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ510" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK510" t="s" s="2">
-        <v>95</v>
+        <v>645</v>
       </c>
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1190</v>
+        <v>1195</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59462,22 +59491,22 @@
         <v>23</v>
       </c>
       <c r="J511" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K511" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L511" t="s" s="2">
-        <v>97</v>
+        <v>85</v>
       </c>
       <c r="M511" t="s" s="2">
-        <v>98</v>
+        <v>86</v>
       </c>
       <c r="N511" t="s" s="2">
-        <v>99</v>
+        <v>87</v>
       </c>
       <c r="O511" t="s" s="2">
-        <v>100</v>
+        <v>88</v>
       </c>
       <c r="P511" s="2"/>
       <c r="Q511" t="s" s="2">
@@ -59527,7 +59556,7 @@
         <v>23</v>
       </c>
       <c r="AG511" t="s" s="2">
-        <v>101</v>
+        <v>89</v>
       </c>
       <c r="AH511" t="s" s="2">
         <v>76</v>
@@ -59539,18 +59568,18 @@
         <v>23</v>
       </c>
       <c r="AK511" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1191</v>
+        <v>1196</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59570,20 +59599,18 @@
         <v>23</v>
       </c>
       <c r="K512" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L512" t="s" s="2">
-        <v>103</v>
+        <v>91</v>
       </c>
       <c r="M512" t="s" s="2">
-        <v>104</v>
+        <v>92</v>
       </c>
       <c r="N512" t="s" s="2">
-        <v>105</v>
-      </c>
-      <c r="O512" t="s" s="2">
-        <v>106</v>
-      </c>
+        <v>93</v>
+      </c>
+      <c r="O512" s="2"/>
       <c r="P512" s="2"/>
       <c r="Q512" t="s" s="2">
         <v>23</v>
@@ -59608,13 +59635,13 @@
         <v>23</v>
       </c>
       <c r="Y512" t="s" s="2">
-        <v>107</v>
+        <v>23</v>
       </c>
       <c r="Z512" t="s" s="2">
-        <v>108</v>
+        <v>23</v>
       </c>
       <c r="AA512" t="s" s="2">
-        <v>109</v>
+        <v>23</v>
       </c>
       <c r="AB512" t="s" s="2">
         <v>23</v>
@@ -59632,7 +59659,7 @@
         <v>23</v>
       </c>
       <c r="AG512" t="s" s="2">
-        <v>110</v>
+        <v>94</v>
       </c>
       <c r="AH512" t="s" s="2">
         <v>76</v>
@@ -59649,17 +59676,17 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1192</v>
+        <v>1197</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
-        <v>519</v>
+        <v>23</v>
       </c>
       <c r="F513" s="2"/>
       <c r="G513" t="s" s="2">
@@ -59672,22 +59699,22 @@
         <v>23</v>
       </c>
       <c r="J513" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K513" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L513" t="s" s="2">
-        <v>520</v>
+        <v>97</v>
       </c>
       <c r="M513" t="s" s="2">
-        <v>521</v>
+        <v>98</v>
       </c>
       <c r="N513" t="s" s="2">
-        <v>522</v>
+        <v>99</v>
       </c>
       <c r="O513" t="s" s="2">
-        <v>523</v>
+        <v>100</v>
       </c>
       <c r="P513" s="2"/>
       <c r="Q513" t="s" s="2">
@@ -59737,7 +59764,7 @@
         <v>23</v>
       </c>
       <c r="AG513" t="s" s="2">
-        <v>524</v>
+        <v>101</v>
       </c>
       <c r="AH513" t="s" s="2">
         <v>76</v>
@@ -59754,24 +59781,24 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1193</v>
+        <v>1198</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
-        <v>526</v>
+        <v>23</v>
       </c>
       <c r="F514" s="2"/>
       <c r="G514" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H514" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I514" t="s" s="2">
         <v>23</v>
@@ -59783,16 +59810,16 @@
         <v>23</v>
       </c>
       <c r="L514" t="s" s="2">
-        <v>182</v>
+        <v>103</v>
       </c>
       <c r="M514" t="s" s="2">
-        <v>527</v>
+        <v>104</v>
       </c>
       <c r="N514" t="s" s="2">
-        <v>528</v>
+        <v>105</v>
       </c>
       <c r="O514" t="s" s="2">
-        <v>529</v>
+        <v>106</v>
       </c>
       <c r="P514" s="2"/>
       <c r="Q514" t="s" s="2">
@@ -59818,13 +59845,13 @@
         <v>23</v>
       </c>
       <c r="Y514" t="s" s="2">
-        <v>23</v>
+        <v>107</v>
       </c>
       <c r="Z514" t="s" s="2">
-        <v>23</v>
+        <v>108</v>
       </c>
       <c r="AA514" t="s" s="2">
-        <v>23</v>
+        <v>109</v>
       </c>
       <c r="AB514" t="s" s="2">
         <v>23</v>
@@ -59842,41 +59869,41 @@
         <v>23</v>
       </c>
       <c r="AG514" t="s" s="2">
-        <v>530</v>
+        <v>110</v>
       </c>
       <c r="AH514" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI514" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ514" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK514" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1194</v>
+        <v>1199</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
-        <v>146</v>
+        <v>519</v>
       </c>
       <c r="F515" s="2"/>
       <c r="G515" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H515" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I515" t="s" s="2">
         <v>23</v>
@@ -59888,16 +59915,16 @@
         <v>23</v>
       </c>
       <c r="L515" t="s" s="2">
-        <v>147</v>
+        <v>520</v>
       </c>
       <c r="M515" t="s" s="2">
-        <v>148</v>
+        <v>521</v>
       </c>
       <c r="N515" t="s" s="2">
-        <v>532</v>
+        <v>522</v>
       </c>
       <c r="O515" t="s" s="2">
-        <v>150</v>
+        <v>523</v>
       </c>
       <c r="P515" s="2"/>
       <c r="Q515" t="s" s="2">
@@ -59947,34 +59974,34 @@
         <v>23</v>
       </c>
       <c r="AG515" t="s" s="2">
-        <v>533</v>
+        <v>524</v>
       </c>
       <c r="AH515" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI515" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ515" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK515" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1195</v>
+        <v>1200</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
-        <v>146</v>
+        <v>526</v>
       </c>
       <c r="F516" s="2"/>
       <c r="G516" t="s" s="2">
@@ -59987,26 +60014,24 @@
         <v>23</v>
       </c>
       <c r="J516" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K516" t="s" s="2">
         <v>23</v>
       </c>
       <c r="L516" t="s" s="2">
-        <v>147</v>
+        <v>182</v>
       </c>
       <c r="M516" t="s" s="2">
-        <v>535</v>
+        <v>527</v>
       </c>
       <c r="N516" t="s" s="2">
-        <v>536</v>
+        <v>528</v>
       </c>
       <c r="O516" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P516" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>529</v>
+      </c>
+      <c r="P516" s="2"/>
       <c r="Q516" t="s" s="2">
         <v>23</v>
       </c>
@@ -60054,7 +60079,7 @@
         <v>23</v>
       </c>
       <c r="AG516" t="s" s="2">
-        <v>537</v>
+        <v>530</v>
       </c>
       <c r="AH516" t="s" s="2">
         <v>76</v>
@@ -60066,22 +60091,22 @@
         <v>23</v>
       </c>
       <c r="AK516" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1196</v>
+        <v>1201</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F517" s="2"/>
       <c r="G517" t="s" s="2">
@@ -60097,19 +60122,19 @@
         <v>23</v>
       </c>
       <c r="K517" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L517" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M517" t="s" s="2">
-        <v>1197</v>
+        <v>148</v>
       </c>
       <c r="N517" t="s" s="2">
-        <v>1198</v>
+        <v>532</v>
       </c>
       <c r="O517" t="s" s="2">
-        <v>1199</v>
+        <v>150</v>
       </c>
       <c r="P517" s="2"/>
       <c r="Q517" t="s" s="2">
@@ -60159,7 +60184,7 @@
         <v>23</v>
       </c>
       <c r="AG517" t="s" s="2">
-        <v>1196</v>
+        <v>533</v>
       </c>
       <c r="AH517" t="s" s="2">
         <v>76</v>
@@ -60171,29 +60196,29 @@
         <v>23</v>
       </c>
       <c r="AK517" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1200</v>
+        <v>1202</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F518" s="2"/>
       <c r="G518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H518" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I518" t="s" s="2">
         <v>23</v>
@@ -60202,19 +60227,23 @@
         <v>84</v>
       </c>
       <c r="K518" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L518" t="s" s="2">
-        <v>103</v>
+        <v>147</v>
       </c>
       <c r="M518" t="s" s="2">
-        <v>1201</v>
+        <v>535</v>
       </c>
       <c r="N518" t="s" s="2">
-        <v>1202</v>
-      </c>
-      <c r="O518" s="2"/>
-      <c r="P518" s="2"/>
+        <v>536</v>
+      </c>
+      <c r="O518" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P518" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q518" t="s" s="2">
         <v>23</v>
       </c>
@@ -60238,13 +60267,13 @@
         <v>23</v>
       </c>
       <c r="Y518" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z518" t="s" s="2">
-        <v>1202</v>
+        <v>23</v>
       </c>
       <c r="AA518" t="s" s="2">
-        <v>1203</v>
+        <v>23</v>
       </c>
       <c r="AB518" t="s" s="2">
         <v>23</v>
@@ -60262,30 +60291,30 @@
         <v>23</v>
       </c>
       <c r="AG518" t="s" s="2">
-        <v>1200</v>
+        <v>537</v>
       </c>
       <c r="AH518" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI518" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ518" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK518" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60308,16 +60337,16 @@
         <v>84</v>
       </c>
       <c r="L519" t="s" s="2">
-        <v>367</v>
+        <v>112</v>
       </c>
       <c r="M519" t="s" s="2">
+        <v>1204</v>
+      </c>
+      <c r="N519" t="s" s="2">
         <v>1205</v>
       </c>
-      <c r="N519" t="s" s="2">
+      <c r="O519" t="s" s="2">
         <v>1206</v>
-      </c>
-      <c r="O519" t="s" s="2">
-        <v>1207</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60343,13 +60372,13 @@
         <v>23</v>
       </c>
       <c r="Y519" t="s" s="2">
-        <v>1208</v>
+        <v>23</v>
       </c>
       <c r="Z519" t="s" s="2">
-        <v>1209</v>
+        <v>23</v>
       </c>
       <c r="AA519" t="s" s="2">
-        <v>1210</v>
+        <v>23</v>
       </c>
       <c r="AB519" t="s" s="2">
         <v>23</v>
@@ -60367,7 +60396,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1204</v>
+        <v>1203</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
@@ -60384,13 +60413,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60398,7 +60427,7 @@
       </c>
       <c r="F520" s="2"/>
       <c r="G520" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H520" t="s" s="2">
         <v>83</v>
@@ -60407,23 +60436,21 @@
         <v>23</v>
       </c>
       <c r="J520" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K520" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L520" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1212</v>
+        <v>1208</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1213</v>
-      </c>
-      <c r="O520" t="s" s="2">
-        <v>1214</v>
-      </c>
+        <v>1209</v>
+      </c>
+      <c r="O520" s="2"/>
       <c r="P520" s="2"/>
       <c r="Q520" t="s" s="2">
         <v>23</v>
@@ -60448,13 +60475,13 @@
         <v>23</v>
       </c>
       <c r="Y520" t="s" s="2">
-        <v>372</v>
+        <v>121</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>1215</v>
+        <v>1209</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>1216</v>
+        <v>1210</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
@@ -60472,10 +60499,10 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1211</v>
+        <v>1207</v>
       </c>
       <c r="AH520" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI520" t="s" s="2">
         <v>83</v>
@@ -60489,13 +60516,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60506,7 +60533,7 @@
         <v>76</v>
       </c>
       <c r="H521" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I521" t="s" s="2">
         <v>23</v>
@@ -60518,15 +60545,17 @@
         <v>84</v>
       </c>
       <c r="L521" t="s" s="2">
-        <v>141</v>
+        <v>367</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1218</v>
+        <v>1212</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1219</v>
-      </c>
-      <c r="O521" s="2"/>
+        <v>1213</v>
+      </c>
+      <c r="O521" t="s" s="2">
+        <v>1214</v>
+      </c>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
         <v>23</v>
@@ -60551,13 +60580,13 @@
         <v>23</v>
       </c>
       <c r="Y521" t="s" s="2">
-        <v>23</v>
+        <v>1215</v>
       </c>
       <c r="Z521" t="s" s="2">
-        <v>23</v>
+        <v>1216</v>
       </c>
       <c r="AA521" t="s" s="2">
-        <v>23</v>
+        <v>1217</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>23</v>
@@ -60575,13 +60604,13 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1217</v>
+        <v>1211</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI521" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ521" t="s" s="2">
         <v>23</v>
@@ -60592,13 +60621,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60606,10 +60635,10 @@
       </c>
       <c r="F522" s="2"/>
       <c r="G522" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H522" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I522" t="s" s="2">
         <v>23</v>
@@ -60621,49 +60650,49 @@
         <v>84</v>
       </c>
       <c r="L522" t="s" s="2">
-        <v>136</v>
+        <v>367</v>
       </c>
       <c r="M522" t="s" s="2">
+        <v>1219</v>
+      </c>
+      <c r="N522" t="s" s="2">
+        <v>1220</v>
+      </c>
+      <c r="O522" t="s" s="2">
         <v>1221</v>
       </c>
-      <c r="N522" t="s" s="2">
-        <v>1222</v>
-      </c>
-      <c r="O522" s="2"/>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R522" t="s" s="2">
+      <c r="R522" s="2"/>
+      <c r="S522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X522" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y522" t="s" s="2">
+        <v>372</v>
+      </c>
+      <c r="Z522" t="s" s="2">
+        <v>1222</v>
+      </c>
+      <c r="AA522" t="s" s="2">
         <v>1223</v>
       </c>
-      <c r="S522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="T522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="U522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="V522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="W522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="X522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Y522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z522" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AA522" t="s" s="2">
-        <v>23</v>
-      </c>
       <c r="AB522" t="s" s="2">
         <v>23</v>
       </c>
@@ -60680,13 +60709,13 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1220</v>
+        <v>1218</v>
       </c>
       <c r="AH522" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI522" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ522" t="s" s="2">
         <v>23</v>
@@ -60697,7 +60726,7 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B523" t="s" s="2">
         <v>1224</v>
@@ -60723,16 +60752,16 @@
         <v>23</v>
       </c>
       <c r="K523" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L523" t="s" s="2">
         <v>141</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>142</v>
+        <v>1225</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>143</v>
+        <v>1226</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -60783,7 +60812,7 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>144</v>
+        <v>1224</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
@@ -60795,22 +60824,22 @@
         <v>23</v>
       </c>
       <c r="AK523" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1225</v>
+        <v>1227</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F524" s="2"/>
       <c r="G524" t="s" s="2">
@@ -60826,25 +60855,25 @@
         <v>23</v>
       </c>
       <c r="K524" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L524" t="s" s="2">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>148</v>
+        <v>1228</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O524" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1229</v>
+      </c>
+      <c r="O524" s="2"/>
       <c r="P524" s="2"/>
       <c r="Q524" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R524" s="2"/>
+      <c r="R524" t="s" s="2">
+        <v>1230</v>
+      </c>
       <c r="S524" t="s" s="2">
         <v>23</v>
       </c>
@@ -60888,7 +60917,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>151</v>
+        <v>1227</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -60900,54 +60929,50 @@
         <v>23</v>
       </c>
       <c r="AK524" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1226</v>
+        <v>1231</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F525" s="2"/>
       <c r="G525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H525" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J525" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K525" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L525" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M525" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N525" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O525" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P525" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O525" s="2"/>
+      <c r="P525" s="2"/>
       <c r="Q525" t="s" s="2">
         <v>23</v>
       </c>
@@ -60995,41 +61020,41 @@
         <v>23</v>
       </c>
       <c r="AG525" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AH525" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI525" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ525" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK525" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1227</v>
+        <v>1232</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F526" s="2"/>
       <c r="G526" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H526" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I526" t="s" s="2">
         <v>23</v>
@@ -61038,18 +61063,20 @@
         <v>23</v>
       </c>
       <c r="K526" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L526" t="s" s="2">
-        <v>112</v>
+        <v>147</v>
       </c>
       <c r="M526" t="s" s="2">
-        <v>1228</v>
+        <v>148</v>
       </c>
       <c r="N526" t="s" s="2">
-        <v>1229</v>
-      </c>
-      <c r="O526" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O526" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P526" s="2"/>
       <c r="Q526" t="s" s="2">
         <v>23</v>
@@ -61098,62 +61125,66 @@
         <v>23</v>
       </c>
       <c r="AG526" t="s" s="2">
-        <v>1227</v>
+        <v>151</v>
       </c>
       <c r="AH526" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI526" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ526" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK526" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1230</v>
+        <v>1233</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F527" s="2"/>
       <c r="G527" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H527" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I527" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J527" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K527" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L527" t="s" s="2">
-        <v>578</v>
+        <v>147</v>
       </c>
       <c r="M527" t="s" s="2">
-        <v>1231</v>
+        <v>155</v>
       </c>
       <c r="N527" t="s" s="2">
-        <v>1232</v>
-      </c>
-      <c r="O527" s="2"/>
-      <c r="P527" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O527" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P527" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q527" t="s" s="2">
         <v>23</v>
       </c>
@@ -61201,30 +61232,30 @@
         <v>23</v>
       </c>
       <c r="AG527" t="s" s="2">
-        <v>1230</v>
+        <v>158</v>
       </c>
       <c r="AH527" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI527" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ527" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK527" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61247,13 +61278,13 @@
         <v>84</v>
       </c>
       <c r="L528" t="s" s="2">
-        <v>497</v>
+        <v>112</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61304,7 +61335,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61321,13 +61352,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61338,7 +61369,7 @@
         <v>76</v>
       </c>
       <c r="H529" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I529" t="s" s="2">
         <v>23</v>
@@ -61350,13 +61381,13 @@
         <v>84</v>
       </c>
       <c r="L529" t="s" s="2">
-        <v>136</v>
+        <v>578</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61407,13 +61438,13 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI529" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ529" t="s" s="2">
         <v>23</v>
@@ -61424,13 +61455,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61450,16 +61481,16 @@
         <v>23</v>
       </c>
       <c r="K530" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L530" t="s" s="2">
-        <v>141</v>
+        <v>497</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>142</v>
+        <v>1241</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>143</v>
+        <v>1242</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -61510,7 +61541,7 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>144</v>
+        <v>1240</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
@@ -61522,22 +61553,22 @@
         <v>23</v>
       </c>
       <c r="AK530" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1240</v>
+        <v>1243</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F531" s="2"/>
       <c r="G531" t="s" s="2">
@@ -61553,20 +61584,18 @@
         <v>23</v>
       </c>
       <c r="K531" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L531" t="s" s="2">
-        <v>147</v>
+        <v>136</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>148</v>
+        <v>1244</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O531" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1245</v>
+      </c>
+      <c r="O531" s="2"/>
       <c r="P531" s="2"/>
       <c r="Q531" t="s" s="2">
         <v>23</v>
@@ -61615,7 +61644,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>151</v>
+        <v>1243</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61627,54 +61656,50 @@
         <v>23</v>
       </c>
       <c r="AK531" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1241</v>
+        <v>1246</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F532" s="2"/>
       <c r="G532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H532" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J532" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K532" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L532" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M532" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N532" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O532" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P532" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O532" s="2"/>
+      <c r="P532" s="2"/>
       <c r="Q532" t="s" s="2">
         <v>23</v>
       </c>
@@ -61722,41 +61747,41 @@
         <v>23</v>
       </c>
       <c r="AG532" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AH532" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI532" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ532" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK532" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1242</v>
+        <v>1247</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F533" s="2"/>
       <c r="G533" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H533" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I533" t="s" s="2">
         <v>23</v>
@@ -61765,18 +61790,20 @@
         <v>23</v>
       </c>
       <c r="K533" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L533" t="s" s="2">
-        <v>491</v>
+        <v>147</v>
       </c>
       <c r="M533" t="s" s="2">
-        <v>1243</v>
+        <v>148</v>
       </c>
       <c r="N533" t="s" s="2">
-        <v>1244</v>
-      </c>
-      <c r="O533" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O533" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P533" s="2"/>
       <c r="Q533" t="s" s="2">
         <v>23</v>
@@ -61825,62 +61852,66 @@
         <v>23</v>
       </c>
       <c r="AG533" t="s" s="2">
-        <v>1242</v>
+        <v>151</v>
       </c>
       <c r="AH533" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI533" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ533" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK533" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1179</v>
+        <v>1186</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1245</v>
+        <v>1248</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F534" s="2"/>
       <c r="G534" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="H534" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I534" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J534" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="K534" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L534" t="s" s="2">
-        <v>1246</v>
+        <v>147</v>
       </c>
       <c r="M534" t="s" s="2">
-        <v>1247</v>
+        <v>155</v>
       </c>
       <c r="N534" t="s" s="2">
-        <v>1248</v>
-      </c>
-      <c r="O534" s="2"/>
-      <c r="P534" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O534" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P534" t="s" s="2">
+        <v>157</v>
+      </c>
       <c r="Q534" t="s" s="2">
         <v>23</v>
       </c>
@@ -61904,13 +61935,13 @@
         <v>23</v>
       </c>
       <c r="Y534" t="s" s="2">
-        <v>372</v>
+        <v>23</v>
       </c>
       <c r="Z534" t="s" s="2">
-        <v>1249</v>
+        <v>23</v>
       </c>
       <c r="AA534" t="s" s="2">
-        <v>1216</v>
+        <v>23</v>
       </c>
       <c r="AB534" t="s" s="2">
         <v>23</v>
@@ -61928,30 +61959,30 @@
         <v>23</v>
       </c>
       <c r="AG534" t="s" s="2">
-        <v>1245</v>
+        <v>158</v>
       </c>
       <c r="AH534" t="s" s="2">
-        <v>83</v>
+        <v>76</v>
       </c>
       <c r="AI534" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ534" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK534" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1250</v>
+        <v>1186</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -61962,7 +61993,7 @@
         <v>76</v>
       </c>
       <c r="H535" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I535" t="s" s="2">
         <v>23</v>
@@ -61971,20 +62002,18 @@
         <v>23</v>
       </c>
       <c r="K535" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L535" t="s" s="2">
-        <v>78</v>
+        <v>491</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1256</v>
+        <v>1250</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1257</v>
-      </c>
-      <c r="O535" t="s" s="2">
-        <v>1258</v>
-      </c>
+        <v>1251</v>
+      </c>
+      <c r="O535" s="2"/>
       <c r="P535" s="2"/>
       <c r="Q535" t="s" s="2">
         <v>23</v>
@@ -62033,13 +62062,13 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1254</v>
+        <v>1249</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI535" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ535" t="s" s="2">
         <v>23</v>
@@ -62050,13 +62079,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1250</v>
+        <v>1186</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1259</v>
+        <v>1252</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62064,7 +62093,7 @@
       </c>
       <c r="F536" s="2"/>
       <c r="G536" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H536" t="s" s="2">
         <v>83</v>
@@ -62076,16 +62105,16 @@
         <v>23</v>
       </c>
       <c r="K536" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>141</v>
+        <v>1253</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>142</v>
+        <v>1254</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>143</v>
+        <v>1255</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -62112,13 +62141,13 @@
         <v>23</v>
       </c>
       <c r="Y536" t="s" s="2">
-        <v>23</v>
+        <v>372</v>
       </c>
       <c r="Z536" t="s" s="2">
-        <v>23</v>
+        <v>1256</v>
       </c>
       <c r="AA536" t="s" s="2">
-        <v>23</v>
+        <v>1223</v>
       </c>
       <c r="AB536" t="s" s="2">
         <v>23</v>
@@ -62136,10 +62165,10 @@
         <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>144</v>
+        <v>1252</v>
       </c>
       <c r="AH536" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="AI536" t="s" s="2">
         <v>83</v>
@@ -62148,22 +62177,22 @@
         <v>23</v>
       </c>
       <c r="AK536" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F537" s="2"/>
       <c r="G537" t="s" s="2">
@@ -62182,16 +62211,16 @@
         <v>23</v>
       </c>
       <c r="L537" t="s" s="2">
-        <v>147</v>
+        <v>78</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>148</v>
+        <v>1263</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>149</v>
+        <v>1264</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>150</v>
+        <v>1265</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
@@ -62229,19 +62258,19 @@
         <v>23</v>
       </c>
       <c r="AC537" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD537" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE537" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF537" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>151</v>
+        <v>1261</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62253,54 +62282,50 @@
         <v>23</v>
       </c>
       <c r="AK537" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1261</v>
+        <v>1266</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
-        <v>154</v>
+        <v>23</v>
       </c>
       <c r="F538" s="2"/>
       <c r="G538" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H538" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I538" t="s" s="2">
         <v>23</v>
       </c>
       <c r="J538" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="K538" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L538" t="s" s="2">
-        <v>147</v>
+        <v>141</v>
       </c>
       <c r="M538" t="s" s="2">
-        <v>155</v>
+        <v>142</v>
       </c>
       <c r="N538" t="s" s="2">
-        <v>156</v>
-      </c>
-      <c r="O538" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P538" t="s" s="2">
-        <v>157</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O538" s="2"/>
+      <c r="P538" s="2"/>
       <c r="Q538" t="s" s="2">
         <v>23</v>
       </c>
@@ -62348,34 +62373,34 @@
         <v>23</v>
       </c>
       <c r="AG538" t="s" s="2">
-        <v>158</v>
+        <v>144</v>
       </c>
       <c r="AH538" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI538" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ538" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK538" t="s" s="2">
-        <v>152</v>
+        <v>23</v>
       </c>
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1262</v>
+        <v>1267</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F539" s="2"/>
       <c r="G539" t="s" s="2">
@@ -62385,27 +62410,27 @@
         <v>77</v>
       </c>
       <c r="I539" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J539" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K539" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L539" t="s" s="2">
-        <v>578</v>
+        <v>147</v>
       </c>
       <c r="M539" t="s" s="2">
-        <v>1263</v>
+        <v>148</v>
       </c>
       <c r="N539" t="s" s="2">
-        <v>1264</v>
-      </c>
-      <c r="O539" s="2"/>
-      <c r="P539" t="s" s="2">
-        <v>1265</v>
-      </c>
+        <v>149</v>
+      </c>
+      <c r="O539" t="s" s="2">
+        <v>150</v>
+      </c>
+      <c r="P539" s="2"/>
       <c r="Q539" t="s" s="2">
         <v>23</v>
       </c>
@@ -62441,19 +62466,19 @@
         <v>23</v>
       </c>
       <c r="AC539" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD539" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE539" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF539" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG539" t="s" s="2">
-        <v>1262</v>
+        <v>151</v>
       </c>
       <c r="AH539" t="s" s="2">
         <v>76</v>
@@ -62465,51 +62490,53 @@
         <v>23</v>
       </c>
       <c r="AK539" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1266</v>
+        <v>1268</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
-        <v>23</v>
+        <v>154</v>
       </c>
       <c r="F540" s="2"/>
       <c r="G540" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H540" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I540" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J540" t="s" s="2">
         <v>84</v>
-      </c>
-      <c r="J540" t="s" s="2">
-        <v>23</v>
       </c>
       <c r="K540" t="s" s="2">
         <v>84</v>
       </c>
       <c r="L540" t="s" s="2">
-        <v>418</v>
+        <v>147</v>
       </c>
       <c r="M540" t="s" s="2">
-        <v>1267</v>
+        <v>155</v>
       </c>
       <c r="N540" t="s" s="2">
-        <v>1268</v>
-      </c>
-      <c r="O540" s="2"/>
+        <v>156</v>
+      </c>
+      <c r="O540" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P540" t="s" s="2">
-        <v>1269</v>
+        <v>157</v>
       </c>
       <c r="Q540" t="s" s="2">
         <v>23</v>
@@ -62558,30 +62585,30 @@
         <v>23</v>
       </c>
       <c r="AG540" t="s" s="2">
-        <v>1266</v>
+        <v>158</v>
       </c>
       <c r="AH540" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI540" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ540" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK540" t="s" s="2">
-        <v>1270</v>
+        <v>152</v>
       </c>
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1271</v>
+        <v>1269</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62592,28 +62619,30 @@
         <v>76</v>
       </c>
       <c r="H541" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I541" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K541" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L541" t="s" s="2">
-        <v>141</v>
+        <v>578</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>142</v>
+        <v>1270</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>143</v>
+        <v>1271</v>
       </c>
       <c r="O541" s="2"/>
-      <c r="P541" s="2"/>
+      <c r="P541" t="s" s="2">
+        <v>1272</v>
+      </c>
       <c r="Q541" t="s" s="2">
         <v>23</v>
       </c>
@@ -62661,64 +62690,64 @@
         <v>23</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>144</v>
+        <v>1269</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI541" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ541" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK541" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F542" s="2"/>
       <c r="G542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H542" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I542" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J542" t="s" s="2">
         <v>23</v>
       </c>
       <c r="K542" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L542" t="s" s="2">
-        <v>147</v>
+        <v>418</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>148</v>
+        <v>1274</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O542" t="s" s="2">
-        <v>150</v>
-      </c>
-      <c r="P542" s="2"/>
+        <v>1275</v>
+      </c>
+      <c r="O542" s="2"/>
+      <c r="P542" t="s" s="2">
+        <v>1276</v>
+      </c>
       <c r="Q542" t="s" s="2">
         <v>23</v>
       </c>
@@ -62754,42 +62783,42 @@
         <v>23</v>
       </c>
       <c r="AC542" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD542" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE542" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF542" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>151</v>
+        <v>1273</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI542" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ542" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK542" t="s" s="2">
-        <v>152</v>
+        <v>1277</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1273</v>
+        <v>1278</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62809,16 +62838,16 @@
         <v>23</v>
       </c>
       <c r="K543" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L543" t="s" s="2">
-        <v>1274</v>
+        <v>141</v>
       </c>
       <c r="M543" t="s" s="2">
-        <v>1275</v>
+        <v>142</v>
       </c>
       <c r="N543" t="s" s="2">
-        <v>1276</v>
+        <v>143</v>
       </c>
       <c r="O543" s="2"/>
       <c r="P543" s="2"/>
@@ -62857,17 +62886,19 @@
         <v>23</v>
       </c>
       <c r="AC543" t="s" s="2">
-        <v>391</v>
-      </c>
-      <c r="AD543" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="AD543" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AE543" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF543" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG543" t="s" s="2">
-        <v>1273</v>
+        <v>144</v>
       </c>
       <c r="AH543" t="s" s="2">
         <v>76</v>
@@ -62879,31 +62910,29 @@
         <v>23</v>
       </c>
       <c r="AK543" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1277</v>
+        <v>1279</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1273</v>
-      </c>
-      <c r="D544" t="s" s="2">
-        <v>1278</v>
-      </c>
+        <v>1279</v>
+      </c>
+      <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F544" s="2"/>
       <c r="G544" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H544" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I544" t="s" s="2">
         <v>23</v>
@@ -62912,18 +62941,20 @@
         <v>23</v>
       </c>
       <c r="K544" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L544" t="s" s="2">
-        <v>902</v>
+        <v>147</v>
       </c>
       <c r="M544" t="s" s="2">
-        <v>1275</v>
+        <v>148</v>
       </c>
       <c r="N544" t="s" s="2">
-        <v>1276</v>
-      </c>
-      <c r="O544" s="2"/>
+        <v>149</v>
+      </c>
+      <c r="O544" t="s" s="2">
+        <v>150</v>
+      </c>
       <c r="P544" s="2"/>
       <c r="Q544" t="s" s="2">
         <v>23</v>
@@ -62960,39 +62991,39 @@
         <v>23</v>
       </c>
       <c r="AC544" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD544" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE544" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF544" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG544" t="s" s="2">
-        <v>1273</v>
+        <v>151</v>
       </c>
       <c r="AH544" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI544" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ544" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK544" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C545" t="s" s="2">
         <v>1280</v>
@@ -63015,16 +63046,16 @@
         <v>23</v>
       </c>
       <c r="K545" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>141</v>
+        <v>1281</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>142</v>
+        <v>1282</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>143</v>
+        <v>1283</v>
       </c>
       <c r="O545" s="2"/>
       <c r="P545" s="2"/>
@@ -63063,19 +63094,17 @@
         <v>23</v>
       </c>
       <c r="AC545" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD545" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>391</v>
+      </c>
+      <c r="AD545" s="2"/>
       <c r="AE545" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF545" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>144</v>
+        <v>1280</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63087,29 +63116,31 @@
         <v>23</v>
       </c>
       <c r="AK545" t="s" s="2">
-        <v>23</v>
+        <v>95</v>
       </c>
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1281</v>
+        <v>1284</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1282</v>
-      </c>
-      <c r="D546" s="2"/>
+        <v>1280</v>
+      </c>
+      <c r="D546" t="s" s="2">
+        <v>1285</v>
+      </c>
       <c r="E546" t="s" s="2">
-        <v>146</v>
+        <v>23</v>
       </c>
       <c r="F546" s="2"/>
       <c r="G546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H546" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I546" t="s" s="2">
         <v>23</v>
@@ -63118,20 +63149,18 @@
         <v>23</v>
       </c>
       <c r="K546" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="L546" t="s" s="2">
-        <v>147</v>
+        <v>902</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>148</v>
+        <v>1282</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>149</v>
-      </c>
-      <c r="O546" t="s" s="2">
-        <v>150</v>
-      </c>
+        <v>1283</v>
+      </c>
+      <c r="O546" s="2"/>
       <c r="P546" s="2"/>
       <c r="Q546" t="s" s="2">
         <v>23</v>
@@ -63168,42 +63197,42 @@
         <v>23</v>
       </c>
       <c r="AC546" t="s" s="2">
-        <v>353</v>
+        <v>23</v>
       </c>
       <c r="AD546" t="s" s="2">
-        <v>354</v>
+        <v>23</v>
       </c>
       <c r="AE546" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF546" t="s" s="2">
-        <v>355</v>
+        <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>151</v>
+        <v>1280</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI546" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ546" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AK546" t="s" s="2">
-        <v>152</v>
+        <v>95</v>
       </c>
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1283</v>
+        <v>1286</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1284</v>
+        <v>1287</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63223,20 +63252,18 @@
         <v>23</v>
       </c>
       <c r="K547" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L547" t="s" s="2">
-        <v>578</v>
+        <v>141</v>
       </c>
       <c r="M547" t="s" s="2">
-        <v>1285</v>
+        <v>142</v>
       </c>
       <c r="N547" t="s" s="2">
-        <v>1286</v>
-      </c>
-      <c r="O547" t="s" s="2">
-        <v>1287</v>
-      </c>
+        <v>143</v>
+      </c>
+      <c r="O547" s="2"/>
       <c r="P547" s="2"/>
       <c r="Q547" t="s" s="2">
         <v>23</v>
@@ -63285,7 +63312,7 @@
         <v>23</v>
       </c>
       <c r="AG547" t="s" s="2">
-        <v>1288</v>
+        <v>144</v>
       </c>
       <c r="AH547" t="s" s="2">
         <v>76</v>
@@ -63294,32 +63321,32 @@
         <v>83</v>
       </c>
       <c r="AJ547" t="s" s="2">
-        <v>1289</v>
+        <v>23</v>
       </c>
       <c r="AK547" t="s" s="2">
-        <v>95</v>
+        <v>23</v>
       </c>
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1290</v>
+        <v>1288</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1291</v>
+        <v>1289</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
-        <v>23</v>
+        <v>146</v>
       </c>
       <c r="F548" s="2"/>
       <c r="G548" t="s" s="2">
         <v>76</v>
       </c>
       <c r="H548" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I548" t="s" s="2">
         <v>23</v>
@@ -63328,27 +63355,25 @@
         <v>23</v>
       </c>
       <c r="K548" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="L548" t="s" s="2">
-        <v>578</v>
+        <v>147</v>
       </c>
       <c r="M548" t="s" s="2">
-        <v>1292</v>
+        <v>148</v>
       </c>
       <c r="N548" t="s" s="2">
-        <v>1293</v>
+        <v>149</v>
       </c>
       <c r="O548" t="s" s="2">
-        <v>1294</v>
+        <v>150</v>
       </c>
       <c r="P548" s="2"/>
       <c r="Q548" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R548" t="s" s="2">
-        <v>1295</v>
-      </c>
+      <c r="R548" s="2"/>
       <c r="S548" t="s" s="2">
         <v>23</v>
       </c>
@@ -63380,42 +63405,42 @@
         <v>23</v>
       </c>
       <c r="AC548" t="s" s="2">
-        <v>23</v>
+        <v>353</v>
       </c>
       <c r="AD548" t="s" s="2">
-        <v>23</v>
+        <v>354</v>
       </c>
       <c r="AE548" t="s" s="2">
         <v>23</v>
       </c>
       <c r="AF548" t="s" s="2">
-        <v>23</v>
+        <v>355</v>
       </c>
       <c r="AG548" t="s" s="2">
-        <v>1296</v>
+        <v>151</v>
       </c>
       <c r="AH548" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI548" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ548" t="s" s="2">
-        <v>1289</v>
+        <v>23</v>
       </c>
       <c r="AK548" t="s" s="2">
-        <v>95</v>
+        <v>152</v>
       </c>
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1297</v>
+        <v>1290</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1297</v>
+        <v>1291</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63438,20 +63463,18 @@
         <v>84</v>
       </c>
       <c r="L549" t="s" s="2">
-        <v>1298</v>
+        <v>578</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1299</v>
+        <v>1292</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1300</v>
+        <v>1293</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>1301</v>
-      </c>
-      <c r="P549" t="s" s="2">
-        <v>1302</v>
-      </c>
+        <v>1294</v>
+      </c>
+      <c r="P549" s="2"/>
       <c r="Q549" t="s" s="2">
         <v>23</v>
       </c>
@@ -63499,7 +63522,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1297</v>
+        <v>1295</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63508,7 +63531,7 @@
         <v>83</v>
       </c>
       <c r="AJ549" t="s" s="2">
-        <v>23</v>
+        <v>1296</v>
       </c>
       <c r="AK549" t="s" s="2">
         <v>95</v>
@@ -63516,13 +63539,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1303</v>
+        <v>1297</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1303</v>
+        <v>1298</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63545,20 +63568,24 @@
         <v>84</v>
       </c>
       <c r="L550" t="s" s="2">
-        <v>1298</v>
+        <v>578</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1304</v>
+        <v>1299</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1305</v>
-      </c>
-      <c r="O550" s="2"/>
+        <v>1300</v>
+      </c>
+      <c r="O550" t="s" s="2">
+        <v>1301</v>
+      </c>
       <c r="P550" s="2"/>
       <c r="Q550" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R550" s="2"/>
+      <c r="R550" t="s" s="2">
+        <v>1302</v>
+      </c>
       <c r="S550" t="s" s="2">
         <v>23</v>
       </c>
@@ -63611,7 +63638,7 @@
         <v>83</v>
       </c>
       <c r="AJ550" t="s" s="2">
-        <v>23</v>
+        <v>1296</v>
       </c>
       <c r="AK550" t="s" s="2">
         <v>95</v>
@@ -63619,13 +63646,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63648,19 +63675,19 @@
         <v>84</v>
       </c>
       <c r="L551" t="s" s="2">
-        <v>199</v>
+        <v>1305</v>
       </c>
       <c r="M551" t="s" s="2">
+        <v>1306</v>
+      </c>
+      <c r="N551" t="s" s="2">
         <v>1307</v>
       </c>
-      <c r="N551" t="s" s="2">
+      <c r="O551" t="s" s="2">
         <v>1308</v>
       </c>
-      <c r="O551" t="s" s="2">
+      <c r="P551" t="s" s="2">
         <v>1309</v>
-      </c>
-      <c r="P551" t="s" s="2">
-        <v>1310</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63709,7 +63736,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1306</v>
+        <v>1304</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63726,13 +63753,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63755,20 +63782,16 @@
         <v>84</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>199</v>
+        <v>1305</v>
       </c>
       <c r="M552" t="s" s="2">
+        <v>1311</v>
+      </c>
+      <c r="N552" t="s" s="2">
         <v>1312</v>
       </c>
-      <c r="N552" t="s" s="2">
-        <v>1313</v>
-      </c>
-      <c r="O552" t="s" s="2">
-        <v>1309</v>
-      </c>
-      <c r="P552" t="s" s="2">
-        <v>1310</v>
-      </c>
+      <c r="O552" s="2"/>
+      <c r="P552" s="2"/>
       <c r="Q552" t="s" s="2">
         <v>23</v>
       </c>
@@ -63816,7 +63839,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1311</v>
+        <v>1310</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63833,13 +63856,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63862,16 +63885,20 @@
         <v>84</v>
       </c>
       <c r="L553" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M553" t="s" s="2">
+        <v>1314</v>
+      </c>
+      <c r="N553" t="s" s="2">
         <v>1315</v>
       </c>
-      <c r="N553" t="s" s="2">
+      <c r="O553" t="s" s="2">
         <v>1316</v>
       </c>
-      <c r="O553" s="2"/>
-      <c r="P553" s="2"/>
+      <c r="P553" t="s" s="2">
+        <v>1317</v>
+      </c>
       <c r="Q553" t="s" s="2">
         <v>23</v>
       </c>
@@ -63895,13 +63922,13 @@
         <v>23</v>
       </c>
       <c r="Y553" t="s" s="2">
-        <v>121</v>
+        <v>23</v>
       </c>
       <c r="Z553" t="s" s="2">
-        <v>1317</v>
+        <v>23</v>
       </c>
       <c r="AA553" t="s" s="2">
-        <v>1318</v>
+        <v>23</v>
       </c>
       <c r="AB553" t="s" s="2">
         <v>23</v>
@@ -63919,7 +63946,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1314</v>
+        <v>1313</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63936,13 +63963,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63965,22 +63992,24 @@
         <v>84</v>
       </c>
       <c r="L554" t="s" s="2">
-        <v>1298</v>
+        <v>199</v>
       </c>
       <c r="M554" t="s" s="2">
+        <v>1319</v>
+      </c>
+      <c r="N554" t="s" s="2">
         <v>1320</v>
       </c>
-      <c r="N554" t="s" s="2">
-        <v>1321</v>
-      </c>
-      <c r="O554" s="2"/>
-      <c r="P554" s="2"/>
+      <c r="O554" t="s" s="2">
+        <v>1316</v>
+      </c>
+      <c r="P554" t="s" s="2">
+        <v>1317</v>
+      </c>
       <c r="Q554" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R554" t="s" s="2">
-        <v>1322</v>
-      </c>
+      <c r="R554" s="2"/>
       <c r="S554" t="s" s="2">
         <v>23</v>
       </c>
@@ -64024,7 +64053,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1319</v>
+        <v>1318</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64041,13 +64070,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64070,13 +64099,13 @@
         <v>84</v>
       </c>
       <c r="L555" t="s" s="2">
-        <v>1298</v>
+        <v>103</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1324</v>
+        <v>1322</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1325</v>
+        <v>1323</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64103,13 +64132,13 @@
         <v>23</v>
       </c>
       <c r="Y555" t="s" s="2">
-        <v>23</v>
+        <v>121</v>
       </c>
       <c r="Z555" t="s" s="2">
-        <v>23</v>
+        <v>1324</v>
       </c>
       <c r="AA555" t="s" s="2">
-        <v>23</v>
+        <v>1325</v>
       </c>
       <c r="AB555" t="s" s="2">
         <v>23</v>
@@ -64127,7 +64156,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1323</v>
+        <v>1321</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64144,7 +64173,7 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B556" t="s" s="2">
         <v>1326</v>
@@ -64164,7 +64193,7 @@
         <v>83</v>
       </c>
       <c r="I556" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J556" t="s" s="2">
         <v>23</v>
@@ -64173,7 +64202,7 @@
         <v>84</v>
       </c>
       <c r="L556" t="s" s="2">
-        <v>199</v>
+        <v>1305</v>
       </c>
       <c r="M556" t="s" s="2">
         <v>1327</v>
@@ -64186,7 +64215,9 @@
       <c r="Q556" t="s" s="2">
         <v>23</v>
       </c>
-      <c r="R556" s="2"/>
+      <c r="R556" t="s" s="2">
+        <v>1329</v>
+      </c>
       <c r="S556" t="s" s="2">
         <v>23</v>
       </c>
@@ -64247,13 +64278,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64276,13 +64307,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>199</v>
+        <v>1305</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64333,7 +64364,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64350,13 +64381,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64370,7 +64401,7 @@
         <v>83</v>
       </c>
       <c r="I558" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J558" t="s" s="2">
         <v>23</v>
@@ -64379,13 +64410,13 @@
         <v>84</v>
       </c>
       <c r="L558" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
@@ -64412,11 +64443,13 @@
         <v>23</v>
       </c>
       <c r="Y558" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z558" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z558" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA558" t="s" s="2">
-        <v>1335</v>
+        <v>23</v>
       </c>
       <c r="AB558" t="s" s="2">
         <v>23</v>
@@ -64434,7 +64467,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64451,7 +64484,7 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B559" t="s" s="2">
         <v>1336</v>
@@ -64468,7 +64501,7 @@
         <v>76</v>
       </c>
       <c r="H559" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I559" t="s" s="2">
         <v>23</v>
@@ -64480,7 +64513,7 @@
         <v>84</v>
       </c>
       <c r="L559" t="s" s="2">
-        <v>103</v>
+        <v>199</v>
       </c>
       <c r="M559" t="s" s="2">
         <v>1337</v>
@@ -64488,9 +64521,7 @@
       <c r="N559" t="s" s="2">
         <v>1338</v>
       </c>
-      <c r="O559" t="s" s="2">
-        <v>1339</v>
-      </c>
+      <c r="O559" s="2"/>
       <c r="P559" s="2"/>
       <c r="Q559" t="s" s="2">
         <v>23</v>
@@ -64515,11 +64546,13 @@
         <v>23</v>
       </c>
       <c r="Y559" t="s" s="2">
-        <v>121</v>
-      </c>
-      <c r="Z559" s="2"/>
+        <v>23</v>
+      </c>
+      <c r="Z559" t="s" s="2">
+        <v>23</v>
+      </c>
       <c r="AA559" t="s" s="2">
-        <v>1340</v>
+        <v>23</v>
       </c>
       <c r="AB559" t="s" s="2">
         <v>23</v>
@@ -64543,7 +64576,7 @@
         <v>76</v>
       </c>
       <c r="AI559" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ559" t="s" s="2">
         <v>23</v>
@@ -64554,13 +64587,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64571,7 +64604,7 @@
         <v>76</v>
       </c>
       <c r="H560" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="I560" t="s" s="2">
         <v>23</v>
@@ -64583,17 +64616,15 @@
         <v>84</v>
       </c>
       <c r="L560" t="s" s="2">
-        <v>1342</v>
+        <v>103</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1343</v>
+        <v>1340</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1344</v>
-      </c>
-      <c r="O560" t="s" s="2">
-        <v>1345</v>
-      </c>
+        <v>1341</v>
+      </c>
+      <c r="O560" s="2"/>
       <c r="P560" s="2"/>
       <c r="Q560" t="s" s="2">
         <v>23</v>
@@ -64618,13 +64649,11 @@
         <v>23</v>
       </c>
       <c r="Y560" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="Z560" t="s" s="2">
-        <v>23</v>
-      </c>
+        <v>121</v>
+      </c>
+      <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>23</v>
+        <v>1342</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64642,13 +64671,13 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1341</v>
+        <v>1339</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI560" t="s" s="2">
-        <v>77</v>
+        <v>83</v>
       </c>
       <c r="AJ560" t="s" s="2">
         <v>23</v>
@@ -64659,13 +64688,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64679,7 +64708,7 @@
         <v>77</v>
       </c>
       <c r="I561" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J561" t="s" s="2">
         <v>23</v>
@@ -64691,17 +64720,15 @@
         <v>103</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1347</v>
+        <v>1344</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1348</v>
+        <v>1345</v>
       </c>
       <c r="O561" t="s" s="2">
-        <v>1349</v>
-      </c>
-      <c r="P561" t="s" s="2">
-        <v>1350</v>
-      </c>
+        <v>1346</v>
+      </c>
+      <c r="P561" s="2"/>
       <c r="Q561" t="s" s="2">
         <v>23</v>
       </c>
@@ -64729,7 +64756,7 @@
       </c>
       <c r="Z561" s="2"/>
       <c r="AA561" t="s" s="2">
-        <v>1351</v>
+        <v>1347</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64747,7 +64774,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1346</v>
+        <v>1343</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64764,13 +64791,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64781,10 +64808,10 @@
         <v>76</v>
       </c>
       <c r="H562" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I562" t="s" s="2">
-        <v>84</v>
+        <v>23</v>
       </c>
       <c r="J562" t="s" s="2">
         <v>23</v>
@@ -64793,15 +64820,17 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>130</v>
+        <v>1349</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1353</v>
+        <v>1350</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1354</v>
-      </c>
-      <c r="O562" s="2"/>
+        <v>1351</v>
+      </c>
+      <c r="O562" t="s" s="2">
+        <v>1352</v>
+      </c>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
         <v>23</v>
@@ -64850,13 +64879,13 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1352</v>
+        <v>1348</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
       </c>
       <c r="AI562" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="AJ562" t="s" s="2">
         <v>23</v>
@@ -64867,13 +64896,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1250</v>
+        <v>1257</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1355</v>
+        <v>1353</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -64884,10 +64913,10 @@
         <v>76</v>
       </c>
       <c r="H563" t="s" s="2">
-        <v>83</v>
+        <v>77</v>
       </c>
       <c r="I563" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J563" t="s" s="2">
         <v>23</v>
@@ -64896,18 +64925,20 @@
         <v>84</v>
       </c>
       <c r="L563" t="s" s="2">
-        <v>367</v>
+        <v>103</v>
       </c>
       <c r="M563" t="s" s="2">
+        <v>1354</v>
+      </c>
+      <c r="N563" t="s" s="2">
+        <v>1355</v>
+      </c>
+      <c r="O563" t="s" s="2">
         <v>1356</v>
       </c>
-      <c r="N563" t="s" s="2">
+      <c r="P563" t="s" s="2">
         <v>1357</v>
       </c>
-      <c r="O563" t="s" s="2">
-        <v>1358</v>
-      </c>
-      <c r="P563" s="2"/>
       <c r="Q563" t="s" s="2">
         <v>23</v>
       </c>
@@ -64931,42 +64962,248 @@
         <v>23</v>
       </c>
       <c r="Y563" t="s" s="2">
+        <v>121</v>
+      </c>
+      <c r="Z563" s="2"/>
+      <c r="AA563" t="s" s="2">
+        <v>1358</v>
+      </c>
+      <c r="AB563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG563" t="s" s="2">
+        <v>1353</v>
+      </c>
+      <c r="AH563" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI563" t="s" s="2">
+        <v>77</v>
+      </c>
+      <c r="AJ563" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK563" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="564">
+      <c r="A564" t="s" s="2">
+        <v>1257</v>
+      </c>
+      <c r="B564" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="C564" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="D564" s="2"/>
+      <c r="E564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F564" s="2"/>
+      <c r="G564" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H564" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I564" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="J564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K564" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L564" t="s" s="2">
+        <v>130</v>
+      </c>
+      <c r="M564" t="s" s="2">
+        <v>1360</v>
+      </c>
+      <c r="N564" t="s" s="2">
+        <v>1361</v>
+      </c>
+      <c r="O564" s="2"/>
+      <c r="P564" s="2"/>
+      <c r="Q564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R564" s="2"/>
+      <c r="S564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Z564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AA564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AB564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG564" t="s" s="2">
+        <v>1359</v>
+      </c>
+      <c r="AH564" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI564" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ564" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK564" t="s" s="2">
+        <v>95</v>
+      </c>
+    </row>
+    <row r="565">
+      <c r="A565" t="s" s="2">
+        <v>1257</v>
+      </c>
+      <c r="B565" t="s" s="2">
+        <v>1362</v>
+      </c>
+      <c r="C565" t="s" s="2">
+        <v>1362</v>
+      </c>
+      <c r="D565" s="2"/>
+      <c r="E565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="F565" s="2"/>
+      <c r="G565" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="H565" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="I565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="J565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="K565" t="s" s="2">
+        <v>84</v>
+      </c>
+      <c r="L565" t="s" s="2">
+        <v>367</v>
+      </c>
+      <c r="M565" t="s" s="2">
+        <v>1363</v>
+      </c>
+      <c r="N565" t="s" s="2">
+        <v>1364</v>
+      </c>
+      <c r="O565" t="s" s="2">
+        <v>1365</v>
+      </c>
+      <c r="P565" s="2"/>
+      <c r="Q565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="R565" s="2"/>
+      <c r="S565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="T565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="U565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="V565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="W565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="X565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="Y565" t="s" s="2">
         <v>107</v>
       </c>
-      <c r="Z563" t="s" s="2">
-        <v>1359</v>
-      </c>
-      <c r="AA563" t="s" s="2">
-        <v>1360</v>
-      </c>
-      <c r="AB563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AC563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AD563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AE563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AF563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AG563" t="s" s="2">
-        <v>1355</v>
-      </c>
-      <c r="AH563" t="s" s="2">
-        <v>76</v>
-      </c>
-      <c r="AI563" t="s" s="2">
-        <v>83</v>
-      </c>
-      <c r="AJ563" t="s" s="2">
-        <v>23</v>
-      </c>
-      <c r="AK563" t="s" s="2">
+      <c r="Z565" t="s" s="2">
+        <v>1366</v>
+      </c>
+      <c r="AA565" t="s" s="2">
+        <v>1367</v>
+      </c>
+      <c r="AB565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AC565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AD565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AE565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AF565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AG565" t="s" s="2">
+        <v>1362</v>
+      </c>
+      <c r="AH565" t="s" s="2">
+        <v>76</v>
+      </c>
+      <c r="AI565" t="s" s="2">
+        <v>83</v>
+      </c>
+      <c r="AJ565" t="s" s="2">
+        <v>23</v>
+      </c>
+      <c r="AK565" t="s" s="2">
         <v>95</v>
       </c>
     </row>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:23:56+00:00</t>
+    <t>2026-06-01T11:34:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-01T11:34:34+00:00</t>
+    <t>2026-06-02T13:07:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-02T13:07:12+00:00</t>
+    <t>2026-06-09T15:23:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-09T15:23:07+00:00</t>
+    <t>2026-06-10T09:53:12+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -90,9 +90,10 @@
     <t>Description</t>
   </si>
   <si>
-    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan bestehend aus: 
+    <t>Das Bundle vom Typ Transaction dient dem schreibenden Zugriff auf den ELGA Medikationsplan (Aktualisierung aller enthaltenen Ressourcen) und besteht aus: 
 - 1..1 Medikationsplan (List): Liste mit Referenzen auf Medikationsplaneinträge und zur Abbildung von Reihenfolge und Änderungsstatus 
-- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung</t>
+- 0..* Medikationsplaneinträge (MedicationRequests): Medikation und Dosierung
+Alle neuen bzw. geänderten und zu entfernenden Medikationsplaneinträge müssen inline im Bundle enthalten sein, alle unveränderten Ressourcen werden referenziert.</t>
   </si>
   <si>
     <t>Purpose</t>
@@ -2276,9 +2277,10 @@
     <t>At ELGA e-Medikation MedicationRequest Geplante Abgabe</t>
   </si>
   <si>
-    <t>Bildet eine geplante Abgabe eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource).
-Sie enthält das verordnete Arzneimittel und dessen Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation.
-Werden mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer'). Verwendet R5 Backport Extensions.</t>
+    <t>Bildet eine "Geplante Abgabe" eines Arzneimittels aus dem zugrundeliegenden Medikationsplaneintrag des ELGA-Teilnehmers ab ("MedicationRequest"-Ressource mit Kategorie "Geplante Abgabe"):
+Sie enthält die verordnete Medikation und deren Dosierung und spielgelt die Inhalte des e-Rezepts wider. Geplante Abgaben dienen somit der Nachvollziehbarkeit der rezeptierten Arzneimittel in der e-Medikation. 
+Werden mehrere Medikamente gleichzeitig verordnet und sollen demselben e-Rezept zugeordnet sein, wird für jedes Medikament eine "Geplante Abgabe" mit demselben "e-Med GroupIdentifier" erstellt (bildet 'Rezept-Klammer'). 
+Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>MedicationRequest</t>
@@ -3281,9 +3283,11 @@
     <t>AT ELGA e-Medikation MedicationDispense Durchgeführte Abgabe</t>
   </si>
   <si>
-    <t>Dokumentiert eine durchgeführte Abgabe eines Arzneimittels ("MedicationDispense"-Ressource). 
-In der durchgeführten Abgabe können Abweichungen hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
-Sofern eine zugehörige geplante Abgabe vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige geplante Abgabe, ersichtlich.</t>
+    <t>Dokumentiert eine "Durchgeführte Abgabe" eines Arzneimittels ("MedicationDispense"-Ressource). 
+Die "Durchgeführte Abgabe" enthält die abgegebene Medikation und deren Dosierung und dient somit der Nachvollziehbarkeit der abgegebenen Arzneimittel in der e-Medikation. 
+Es können Abweichungen zur "Geplanten Abgabe" hinsichtlich des Medikaments und dessen Dosierung dokumentiert werden.
+Sofern eine zugehörige "Geplanten Abgabe" vorliegt, muss diese mit dem zugehörigen Planeintrag referenziert werden. Eine mögliche Substitution des Medikaments ist implizit, durch die Referenz auf die zugehörige "Geplante Abgabe", ersichtlich.
+Der aktuelle Status einer "Durchgeführten Abgabe" wird mittels "status"- und "type"-Element dokumentiert. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>MedicationDispense</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T09:53:12+00:00</t>
+    <t>2026-06-10T11:38:54+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-10T11:38:54+00:00</t>
+    <t>2026-06-12T12:35:19+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3073,7 +3073,7 @@
   <si>
     <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
 Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
-Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer geplanten Abgabe dienen. Es werden R5-Backport-Extensions verwendet.</t>
+Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
   </si>
   <si>
     <t>Medikationsplaneintrag-ID.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-12T12:35:19+00:00</t>
+    <t>2026-06-15T08:37:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T08:37:42+00:00</t>
+    <t>2026-06-15T17:37:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-15T21:20:33+00:00</t>
+    <t>2026-06-16T10:30:24+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T10:30:24+00:00</t>
+    <t>2026-06-16T16:59:26+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-16T16:59:26+00:00</t>
+    <t>2026-06-17T13:25:59+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-17T13:25:59+00:00</t>
+    <t>2026-06-19T14:53:34+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-19T14:53:34+00:00</t>
+    <t>2026-06-22T08:46:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2027,7 +2027,7 @@
     <t>AT ELGA e-Medikation Medication Medikation</t>
   </si>
   <si>
-    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, geplante Abgabe und durchgeführte Abgabe.</t>
+    <t>Bildet ein Arzneimittel in der "Medication"-Ressource ab. Wird grundsätzlich verwendet in Planeintrag, Geplanter Abgabe und Durchgeführter Abgabe.</t>
   </si>
   <si>
     <t>Medication</t>
@@ -2377,7 +2377,7 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -2393,7 +2393,7 @@
 </t>
   </si>
   <si>
-    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Auslösendes Ereignis (Referenz auf Procedure-Ressource). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The procedure that trigger the dispense.</t>
@@ -2402,7 +2402,7 @@
     <t>MedicationDispense.status</t>
   </si>
   <si>
-    <t>Status der durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
+    <t>Status der Durchgeführten Abgabe. Mögliche Ausprägungen: [completed | entered-in-error | stopped] Bedeutung: completed: Die Durchgeführte Abgabe ist abgeschlossen. | entered-in-error: Die Durchgeführte Abgabe wird aufgrund falscher Eingabe storniert. | stopped: Die Abgabe wird nicht durchgeführt (Medikament wird abgesetzt).</t>
   </si>
   <si>
     <t>A code specifying the state of the set of dispense events.</t>
@@ -2448,13 +2448,13 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf DetectedIssue-Ressource. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>MedicationDispense.category</t>
   </si>
   <si>
-    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Angabe, wo das abgegebene Medikament voraussichtlich eingenommen oder verabreicht wird (z.B. stationär oder ambulant). Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the type of medication dispense (for example, where the medication is expected to be consumed or administered (i.e. inpatient or outpatient)).</t>
@@ -2489,7 +2489,7 @@
     <t>MedicationDispense.subject</t>
   </si>
   <si>
-    <t>Patient, für den die durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Durchgeführte Abgabe ausgestellt wird (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or the group to whom the medication will be given.</t>
@@ -2505,7 +2505,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz auf Encounter oder EpisodeOfCare. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>The encounter or episode of care that establishes the context for this event.</t>
@@ -2518,7 +2518,7 @@
 </t>
   </si>
   <si>
-    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Referenz (Any) auf zusätzliche Informationen, die die Abgabe des Medikaments unterstützen. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Additional information that supports the medication being dispensed.</t>
@@ -2545,7 +2545,7 @@
     <t>MedicationDispense.performer.function</t>
   </si>
   <si>
-    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der durchgeführten Abgabe.</t>
+    <t>Rolle der Person, die die Abgabe durchgeführt hat. Keine Verwendung in der Durchgeführten Abgabe.</t>
   </si>
   <si>
     <t>Distinguishes the type of performer in the dispense.  For example, date enterer, packager, final checker.</t>
@@ -2568,7 +2568,7 @@
   </si>
   <si>
     <t>Refrenz auf Practitioner, PractitionerRole, Organization, 
-der/die die durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
+der/die die Durchgeführte Abgabe erstellt hat und für den Inhalt verantwortlich ist (identifiziert über den GDA-Index und berechtigt 
 auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -2595,9 +2595,9 @@
 </t>
   </si>
   <si>
-    <t>Referenz auf zugehörige geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
-Planeintrag (MedicationRequest). Es muss nicht zwingend eine geplante Abgabe referenziert werden, da es auch durchgeführte 
-Abgaben ohne geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
+    <t>Referenz auf zugehörige Geplante Abgabe (MedicationRequest), sofern diese existiert bzw. 
+Planeintrag (MedicationRequest). Es muss nicht zwingend eine Geplante Abgabe referenziert werden, da es auch durchgeführte 
+Abgaben ohne Geplante Abgabe geben kann (z.B. Notfall oder OTC-Medikation).</t>
   </si>
   <si>
     <t>Indicates the medication order that is being dispensed against.</t>
@@ -2919,7 +2919,7 @@
     <t>MedicationRequest.status</t>
   </si>
   <si>
-    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, geplante Abgabe | completed: geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
+    <t>Status der geplanten Abgabe. Mögliche Ausprägung: [active | completed | entered-in-error | stopped]. Bedeutung: active: offene, Geplante Abgabe | completed: Geplante Abgabe abgeschlossen | entered-in-error: nach fehlerhafter Eingabe; Storno nur möglich, wenn noch keine zugehörige Abgabe durchgeführt wurde | stopped: Verwendung zu prüfen (Status soll analog zu e-Rezept abgebildet werden)</t>
   </si>
   <si>
     <t>A code specifying the current state of the order.  Generally, this will be active or completed state.</t>
@@ -2949,7 +2949,7 @@
     <t>MedicationRequest.intent</t>
   </si>
   <si>
-    <t>Die geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
+    <t>Die Geplante Abgabe stellt einen Auftrag zur Durchführung und eine Autorisierung des Verfassers dar; daher ist intent immer "order".</t>
   </si>
   <si>
     <t>Whether the request is a proposal, plan, or an original order.</t>
@@ -3044,7 +3044,7 @@
     <t>MedicationRequest.doNotPerform</t>
   </si>
   <si>
-    <t>Gibt an, ob die geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob die Geplante Abgabe untersagt ist. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>If true indicates that the provider is asking for the medication request not to occur.</t>
@@ -3082,7 +3082,7 @@
     <t>MedicationRequest.subject</t>
   </si>
   <si>
-    <t>Patient, für den die geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
+    <t>Patient, für den die Geplante Abgabe ausgestellt werden soll (über Zentralen Patientenindex identifiziert und Teilnehmer von ELGA e-Medikation).</t>
   </si>
   <si>
     <t>A link to a resource representing the person or set of individuals to whom the medication will be given.</t>
@@ -3094,7 +3094,7 @@
     <t>MedicationRequest.encounter</t>
   </si>
   <si>
-    <t>Aufenthalt/Begegnung, während dessen die geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Aufenthalt/Begegnung, während dessen die Geplante Abgabe erstellt wurde. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>The Encounter during which this [x] was created or to which the creation of this record is tightly associated.</t>
@@ -3126,7 +3126,7 @@
     <t>MedicationRequest.requester</t>
   </si>
   <si>
-    <t>Der Arzt oder die Ärztin, die die geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
+    <t>Der Arzt oder die Ärztin, die die Geplante Abgabe erstellt hat und für den Inhalt verantwortlich ist 
 (eindeutig identifiziert über den GDA-Index und berechtigt auf die ELGA e-Medikation des Patienten zuzugreifen).</t>
   </si>
   <si>
@@ -3231,7 +3231,7 @@
     <t>MedicationRequest.basedOn</t>
   </si>
   <si>
-    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese geplante Abgabe basiert.</t>
+    <t>Referenz auf die (aktuelle) Version des zugrundeliegenden Medikationsplaneintrags, auf dem diese Geplante Abgabe basiert.</t>
   </si>
   <si>
     <t>A plan or request that is fulfilled in whole or in part by this medication request.</t>
@@ -3242,7 +3242,7 @@
   <si>
     <t>Als groupIdentifier dient die eMED-ID, die auch im e-Rezept mitgeführt wird. 
 Werden von einem:r Arzt:Ärtztin mehrere Arzneimittel gleichzeitig verordnet, wird für jedes Arzneimittel eine 
-geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
+Geplante Abgabe mit demselben groupIdentifier erstellt (bildet 'Rezept-Klammer').</t>
   </si>
   <si>
     <t>A shared identifier common to all requests that were authorized more or less simultaneously by a single author, representing the identifier of the requisition or prescription.</t>
@@ -3381,10 +3381,10 @@
 </t>
   </si>
   <si>
-    <t>Gültigkeitszeitraum einer geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
-  </si>
-  <si>
-    <t>Zeitraum in dem die geplante Abgabe eingelöst werden kann.
+    <t>Gültigkeitszeitraum einer Geplante Abgabe (abhängig von Rezeptart): Kassenrezept: ab Erstelldatum 1 Monat, bei Teilabgabe verlängert sich Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess). Privatrezept: ab Erstelldatum max. 365 Tage, die Gültigkeitsdauer kann vom Arzt definiert werden. Substitutionsrezept: Max. Gültigkeitsdauer 12 Monate.</t>
+  </si>
+  <si>
+    <t>Zeitraum in dem die Geplante Abgabe eingelöst werden kann.
 Der Gültigkeitszeitraum ist abhängig von der **Rezeptart**: 
 * **Kassenrezept**: ab Erstelldatum einen Monat gültig (vom Ausstellungszeitpunkt bis zum gleichen Tag des Folgemonats 23:59 Uhr); validityPeriod.start kein Datum in der Zukunft; bei einer Teilabgabe verlängert sich die gesamte Gültigkeitsdauer auf 3 Monate („Besorger“-Prozess).
 * **Privatrezept**: ab Erstelldatum maximal 365 Tage gültig, wenn die erste Einlösung innerhalb von 1 Monat ab Erstelldatum erfolgt (sonst Status abgelaufen). validityPeriod.start kein Datum in der Zukunft; Die Gültigkeitsdauer (validityPeriod.end) kann vom Arzt definiert werden.
@@ -3465,7 +3465,7 @@
     <t>MedicationRequest.dispenseRequest.performer</t>
   </si>
   <si>
-    <t>Apotheke oder andere Einrichtung, die die geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Apotheke oder andere Einrichtung, die die Geplante Abgabe einlösen soll. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates the intended dispensing Organization specified by the prescriber.</t>
@@ -3474,7 +3474,7 @@
     <t>MedicationRequest.substitution</t>
   </si>
   <si>
-    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Gibt an, ob das Arzneimittel substituiert werden darf (Absicht des Arztes, der die Geplante Abgabe erstellt). Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>Indicates whether or not substitution can or should be part of the dispense. In some cases, substitution must happen, in other cases substitution must not happen. This block explains the prescriber's intent. If nothing is specified substitution may be done.</t>
@@ -3520,7 +3520,7 @@
     <t>MedicationRequest.priorPrescription</t>
   </si>
   <si>
-    <t>Im Falle einer Änderung wird auf die ersetzte geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
+    <t>Im Falle einer Änderung wird auf die ersetzte Geplante Abgabe verwiesen. Keine Verwendung in der geplanten Abgabe.</t>
   </si>
   <si>
     <t>A link to a resource representing an earlier order related order or prescription.</t>
@@ -3625,7 +3625,7 @@
     <t>CodeableConcept.text</t>
   </si>
   <si>
-    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
+    <t>Ein Medikationsplaneintrag ist eine autorisierte ärztliche Anordnung und stellt eine verbindliche Einnahmeanweisung für den Patienten dar, auf dessen Basis eine Geplante Abgabe erstellt werden kann. Fixer Wert: "order". (req) proposal | plan | order | original-order | reflex-order | filler-order | instance-order | option. https://hl7.org/fhir/R4/valueset-medicationrequest-intent.html</t>
   </si>
   <si>
     <t>&lt;valueCodeableConcept xmlns="http://hl7.org/fhir"&gt;

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T08:46:55+00:00</t>
+    <t>2026-06-22T09:33:42+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-22T09:33:42+00:00</t>
+    <t>2026-06-26T11:41:48+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-26T11:41:48+00:00</t>
+    <t>2026-06-30T14:26:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-06-30T14:26:32+00:00</t>
+    <t>2026-07-01T15:59:29+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-01T15:59:29+00:00</t>
+    <t>2026-07-06T05:37:07+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T05:37:07+00:00</t>
+    <t>2026-07-06T12:58:40+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T12:58:40+00:00</t>
+    <t>2026-07-06T16:22:02+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -2377,7 +2377,7 @@
     <t>MedicationDispense.identifier</t>
   </si>
   <si>
-    <t>Durchgeführte-Abgabe-ID. Keine Verwendung in der Durchgeführten Abgabe.</t>
+    <t>Verpflichtende Angabe des 'e-Med Groupidentifiers' der Geplanten Abgabe, sofern diese existiert.</t>
   </si>
   <si>
     <t>Identifiers associated with this Medication Dispense that are defined by business processes and/or used to refer to it when a direct URL reference to the resource itself is not appropriate. They are business identifiers assigned to this resource by the performer or other systems and remain constant as the resource is updated and propagates from server to server.</t>
@@ -40505,10 +40505,10 @@
         <v>76</v>
       </c>
       <c r="H329" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="I329" t="s" s="2">
-        <v>23</v>
+        <v>84</v>
       </c>
       <c r="J329" t="s" s="2">
         <v>23</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-06T16:22:02+00:00</t>
+    <t>2026-07-08T18:47:08+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T18:47:08+00:00</t>
+    <t>2026-07-08T22:06:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-08T22:06:32+00:00</t>
+    <t>2026-07-09T09:27:37+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T09:27:37+00:00</t>
+    <t>2026-07-09T10:22:28+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T10:22:28+00:00</t>
+    <t>2026-07-09T13:13:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T13:13:16+00:00</t>
+    <t>2026-07-09T17:30:16+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-09T17:30:16+00:00</t>
+    <t>2026-07-10T13:02:50+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -42,7 +42,7 @@
     <t>Name</t>
   </si>
   <si>
-    <t>AtEmedBundleMedikationsplan</t>
+    <t>AtElgaEmedBundleMedikationsplan</t>
   </si>
   <si>
     <t>Title</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-10T13:02:50+00:00</t>
+    <t>2026-07-13T07:52:05+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -1613,7 +1613,7 @@
   </si>
   <si>
     <t>Der Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine List-Ressource abgebildet. 
-Diese enthält 0..* Einträge (List.entry), wobei jedes Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
+Diese enthält 0..* Einträge (List.entry), wobei jeder Entry genau eine Referenz auf einen Medikationsplaneintrag (MedicationRequest) in List.entry.item beinhaltet.
 Die Reihenfolge der Einträge kann durch den GDA festgelegt werden. Jeder Listeneintrag enthält im Element List.entry.flag den Änderungsstatus des jeweiligen Medikationsplaneintrags.</t>
   </si>
   <si>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-13T07:52:05+00:00</t>
+    <t>2026-07-14T09:15:46+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3665,7 +3665,7 @@
     <t>reportedBoolean</t>
   </si>
   <si>
-    <t>TRUE im Falle der Dokumentation von Fremdmedikation (ein anderer Arzt hat das Medikament ursprünglich verordnet), sonst FALSE.</t>
+    <t>Quelle der Information. Bedeutung: false: Verordnung durch den Planeintrag erstellenden GDA | true: Fremdmedikation oder Eigenmedikation des Patienten.</t>
   </si>
   <si>
     <t>Das Arzneimittel wird immer in einer contained Medication Ressource dokumentiert, damit Arzneimittel mit und ohne PZN einheitlich dokumentiert werden können.</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-14T09:15:46+00:00</t>
+    <t>2026-07-17T15:29:52+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-17T15:29:52+00:00</t>
+    <t>2026-07-27T22:31:32+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-27T22:31:32+00:00</t>
+    <t>2026-07-28T00:05:30+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -13,7 +13,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18933" uniqueCount="1368">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="18933" uniqueCount="1369">
   <si>
     <t>Property</t>
   </si>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-28T00:05:30+00:00</t>
+    <t>2026-07-29T17:39:31+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
@@ -3565,6 +3565,10 @@
     <t>Ein Medikationsplaneintrag im Medikationsplan eines ELGA-Teilnehmers bzw. einer ELGA-Teilnehmerin wird durch eine "MedicationRequest"-Ressource abgebildet.
 Die Ressource enthält genau ein Medikament mit der zugehörigen Dosierung, wobei das Medikament verpflichtend in einer contained Medication-Ressource (inline, d.h. innerhalb der Ressource), dokumentiert wird.
 Der Medikationsplaneintrag kann in weiterer Folge als Grundlage für die Erstellung einer "Geplanten Abgabe" dienen. Es werden R5-Backport-Extensions verwendet.</t>
+  </si>
+  <si>
+    <t>dom-2:If the resource is contained in another resource, it SHALL NOT contain nested Resources {contained.contained.empty()}
+dom-3:If the resource is contained in another resource, it SHALL be referred to from elsewhere in the resource or SHALL refer to the containing resource {contained.where((('#'+id in (%resource.descendants().reference | %resource.descendants().as(canonical) | %resource.descendants().as(uri) | %resource.descendants().as(url))) or descendants().where(reference = '#').exists() or descendants().where(as(canonical) = '#').exists() or descendants().where(as(canonical) = '#').exists()).not()).trace('unmatched', id).empty()}dom-4:If a resource is contained in another resource, it SHALL NOT have a meta.versionId or a meta.lastUpdated {contained.meta.versionId.empty() and contained.meta.lastUpdated.empty()}dom-5:If a resource is contained in another resource, it SHALL NOT have a security label {contained.meta.security.empty()}dom-6:A resource should have narrative for robust management {text.`div`.exists()}e-med-continuous-medication-effectiveDosePeriod:Eine Dauermedikation (courseOfTherapyType = #continuous) darf kein Enddatum besitzen. {courseOfTherapyType.where(coding.code='continuous' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists().not()}e-med-acute-medication-effectiveDosePeriod:Eine Akutmedikation (courseOfTherapyType = #acute) muss ein Enddatum besitzen. {courseOfTherapyType.where(coding.code='acute' and coding.system = 'http://terminology.hl7.org/CodeSystem/medicationrequest-course-of-therapy').exists() implies extension.where(url = 'http://hl7.org/fhir/5.0/StructureDefinition/extension-MedicationRequest.effectiveDosePeriod').value.ofType(Period).end.exists()}</t>
   </si>
   <si>
     <t>Medikationsplaneintrag-ID.</t>
@@ -5826,7 +5830,7 @@
         <v>2</v>
       </c>
       <c r="B178" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
     </row>
     <row r="179">
@@ -5834,7 +5838,7 @@
         <v>4</v>
       </c>
       <c r="B179" t="s" s="2">
-        <v>1187</v>
+        <v>1188</v>
       </c>
     </row>
     <row r="180">
@@ -5850,7 +5854,7 @@
         <v>8</v>
       </c>
       <c r="B181" t="s" s="2">
-        <v>1188</v>
+        <v>1189</v>
       </c>
     </row>
     <row r="182">
@@ -5858,7 +5862,7 @@
         <v>10</v>
       </c>
       <c r="B182" t="s" s="2">
-        <v>1189</v>
+        <v>1190</v>
       </c>
     </row>
     <row r="183">
@@ -5920,7 +5924,7 @@
         <v>24</v>
       </c>
       <c r="B190" t="s" s="2">
-        <v>1190</v>
+        <v>1191</v>
       </c>
     </row>
     <row r="191">
@@ -5956,7 +5960,7 @@
         <v>32</v>
       </c>
       <c r="B195" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
     </row>
     <row r="196">
@@ -5964,7 +5968,7 @@
         <v>34</v>
       </c>
       <c r="B196" t="s" s="2">
-        <v>1192</v>
+        <v>1193</v>
       </c>
     </row>
     <row r="197">
@@ -5996,7 +6000,7 @@
         <v>2</v>
       </c>
       <c r="B200" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
     </row>
     <row r="201">
@@ -6004,7 +6008,7 @@
         <v>4</v>
       </c>
       <c r="B201" t="s" s="2">
-        <v>1258</v>
+        <v>1259</v>
       </c>
     </row>
     <row r="202">
@@ -6020,7 +6024,7 @@
         <v>8</v>
       </c>
       <c r="B203" t="s" s="2">
-        <v>1259</v>
+        <v>1260</v>
       </c>
     </row>
     <row r="204">
@@ -6028,7 +6032,7 @@
         <v>10</v>
       </c>
       <c r="B204" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="205">
@@ -6090,7 +6094,7 @@
         <v>24</v>
       </c>
       <c r="B212" t="s" s="2">
-        <v>1260</v>
+        <v>1261</v>
       </c>
     </row>
     <row r="213">
@@ -6126,7 +6130,7 @@
         <v>32</v>
       </c>
       <c r="B217" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
     </row>
     <row r="218">
@@ -6134,7 +6138,7 @@
         <v>34</v>
       </c>
       <c r="B218" t="s" s="2">
-        <v>1262</v>
+        <v>1263</v>
       </c>
     </row>
     <row r="219">
@@ -52266,7 +52270,7 @@
         <v>23</v>
       </c>
       <c r="AK441" t="s" s="2">
-        <v>645</v>
+        <v>1124</v>
       </c>
     </row>
     <row r="442">
@@ -52913,7 +52917,7 @@
       </c>
       <c r="F448" s="2"/>
       <c r="G448" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H448" t="s" s="2">
         <v>77</v>
@@ -53016,7 +53020,7 @@
       </c>
       <c r="F449" s="2"/>
       <c r="G449" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H449" t="s" s="2">
         <v>83</v>
@@ -53353,7 +53357,7 @@
         <v>112</v>
       </c>
       <c r="M452" t="s" s="2">
-        <v>1124</v>
+        <v>1125</v>
       </c>
       <c r="N452" t="s" s="2">
         <v>920</v>
@@ -53458,7 +53462,7 @@
         <v>103</v>
       </c>
       <c r="M453" t="s" s="2">
-        <v>1125</v>
+        <v>1126</v>
       </c>
       <c r="N453" t="s" s="2">
         <v>923</v>
@@ -53494,7 +53498,7 @@
       </c>
       <c r="Z453" s="2"/>
       <c r="AA453" t="s" s="2">
-        <v>1126</v>
+        <v>1127</v>
       </c>
       <c r="AB453" t="s" s="2">
         <v>23</v>
@@ -53561,7 +53565,7 @@
         <v>367</v>
       </c>
       <c r="M454" t="s" s="2">
-        <v>1127</v>
+        <v>1128</v>
       </c>
       <c r="N454" t="s" s="2">
         <v>927</v>
@@ -53637,10 +53641,10 @@
         <v>1119</v>
       </c>
       <c r="B455" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="C455" t="s" s="2">
-        <v>1128</v>
+        <v>1129</v>
       </c>
       <c r="D455" s="2"/>
       <c r="E455" t="s" s="2">
@@ -53740,10 +53744,10 @@
         <v>1119</v>
       </c>
       <c r="B456" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="C456" t="s" s="2">
-        <v>1129</v>
+        <v>1130</v>
       </c>
       <c r="D456" s="2"/>
       <c r="E456" t="s" s="2">
@@ -53845,10 +53849,10 @@
         <v>1119</v>
       </c>
       <c r="B457" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="C457" t="s" s="2">
-        <v>1130</v>
+        <v>1131</v>
       </c>
       <c r="D457" s="2"/>
       <c r="E457" t="s" s="2">
@@ -53871,19 +53875,19 @@
         <v>84</v>
       </c>
       <c r="L457" t="s" s="2">
-        <v>1131</v>
+        <v>1132</v>
       </c>
       <c r="M457" t="s" s="2">
-        <v>1132</v>
+        <v>1133</v>
       </c>
       <c r="N457" t="s" s="2">
-        <v>1133</v>
+        <v>1134</v>
       </c>
       <c r="O457" t="s" s="2">
-        <v>1134</v>
+        <v>1135</v>
       </c>
       <c r="P457" t="s" s="2">
-        <v>1135</v>
+        <v>1136</v>
       </c>
       <c r="Q457" t="s" s="2">
         <v>23</v>
@@ -53932,7 +53936,7 @@
         <v>23</v>
       </c>
       <c r="AG457" t="s" s="2">
-        <v>1136</v>
+        <v>1137</v>
       </c>
       <c r="AH457" t="s" s="2">
         <v>76</v>
@@ -53952,10 +53956,10 @@
         <v>1119</v>
       </c>
       <c r="B458" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="C458" t="s" s="2">
-        <v>1137</v>
+        <v>1138</v>
       </c>
       <c r="D458" s="2"/>
       <c r="E458" t="s" s="2">
@@ -53981,16 +53985,16 @@
         <v>141</v>
       </c>
       <c r="M458" t="s" s="2">
-        <v>1138</v>
+        <v>1139</v>
       </c>
       <c r="N458" t="s" s="2">
-        <v>1139</v>
+        <v>1140</v>
       </c>
       <c r="O458" t="s" s="2">
-        <v>1140</v>
+        <v>1141</v>
       </c>
       <c r="P458" t="s" s="2">
-        <v>1141</v>
+        <v>1142</v>
       </c>
       <c r="Q458" t="s" s="2">
         <v>23</v>
@@ -54039,7 +54043,7 @@
         <v>23</v>
       </c>
       <c r="AG458" t="s" s="2">
-        <v>1142</v>
+        <v>1143</v>
       </c>
       <c r="AH458" t="s" s="2">
         <v>76</v>
@@ -54088,7 +54092,7 @@
         <v>103</v>
       </c>
       <c r="M459" t="s" s="2">
-        <v>1143</v>
+        <v>1144</v>
       </c>
       <c r="N459" t="s" s="2">
         <v>933</v>
@@ -54210,7 +54214,7 @@
         <v>23</v>
       </c>
       <c r="T460" t="s" s="2">
-        <v>1144</v>
+        <v>1145</v>
       </c>
       <c r="U460" t="s" s="2">
         <v>23</v>
@@ -54298,7 +54302,7 @@
         <v>103</v>
       </c>
       <c r="M461" t="s" s="2">
-        <v>1145</v>
+        <v>1146</v>
       </c>
       <c r="N461" t="s" s="2">
         <v>956</v>
@@ -54401,7 +54405,7 @@
         <v>385</v>
       </c>
       <c r="M462" t="s" s="2">
-        <v>1146</v>
+        <v>1147</v>
       </c>
       <c r="N462" t="s" s="2">
         <v>961</v>
@@ -54506,7 +54510,7 @@
         <v>385</v>
       </c>
       <c r="M463" t="s" s="2">
-        <v>1147</v>
+        <v>1148</v>
       </c>
       <c r="N463" t="s" s="2">
         <v>966</v>
@@ -54578,13 +54582,13 @@
         <v>1119</v>
       </c>
       <c r="B464" t="s" s="2">
-        <v>1148</v>
+        <v>1149</v>
       </c>
       <c r="C464" t="s" s="2">
         <v>963</v>
       </c>
       <c r="D464" t="s" s="2">
-        <v>1149</v>
+        <v>1150</v>
       </c>
       <c r="E464" t="s" s="2">
         <v>23</v>
@@ -54606,10 +54610,10 @@
         <v>84</v>
       </c>
       <c r="L464" t="s" s="2">
-        <v>1150</v>
+        <v>1151</v>
       </c>
       <c r="M464" t="s" s="2">
-        <v>1151</v>
+        <v>1152</v>
       </c>
       <c r="N464" t="s" s="2">
         <v>966</v>
@@ -54683,13 +54687,13 @@
         <v>1119</v>
       </c>
       <c r="B465" t="s" s="2">
-        <v>1152</v>
+        <v>1153</v>
       </c>
       <c r="C465" t="s" s="2">
         <v>963</v>
       </c>
       <c r="D465" t="s" s="2">
-        <v>1153</v>
+        <v>1154</v>
       </c>
       <c r="E465" t="s" s="2">
         <v>23</v>
@@ -54714,7 +54718,7 @@
         <v>385</v>
       </c>
       <c r="M465" t="s" s="2">
-        <v>1154</v>
+        <v>1155</v>
       </c>
       <c r="N465" t="s" s="2">
         <v>966</v>
@@ -54817,7 +54821,7 @@
         <v>782</v>
       </c>
       <c r="M466" t="s" s="2">
-        <v>1155</v>
+        <v>1156</v>
       </c>
       <c r="N466" t="s" s="2">
         <v>969</v>
@@ -54922,7 +54926,7 @@
         <v>568</v>
       </c>
       <c r="M467" t="s" s="2">
-        <v>1156</v>
+        <v>1157</v>
       </c>
       <c r="N467" t="s" s="2">
         <v>973</v>
@@ -55027,7 +55031,7 @@
         <v>574</v>
       </c>
       <c r="M468" t="s" s="2">
-        <v>1157</v>
+        <v>1158</v>
       </c>
       <c r="N468" t="s" s="2">
         <v>977</v>
@@ -55132,7 +55136,7 @@
         <v>795</v>
       </c>
       <c r="M469" t="s" s="2">
-        <v>1158</v>
+        <v>1159</v>
       </c>
       <c r="N469" t="s" s="2">
         <v>981</v>
@@ -55235,7 +55239,7 @@
         <v>578</v>
       </c>
       <c r="M470" t="s" s="2">
-        <v>1159</v>
+        <v>1160</v>
       </c>
       <c r="N470" t="s" s="2">
         <v>984</v>
@@ -55338,7 +55342,7 @@
         <v>811</v>
       </c>
       <c r="M471" t="s" s="2">
-        <v>1160</v>
+        <v>1161</v>
       </c>
       <c r="N471" t="s" s="2">
         <v>987</v>
@@ -55441,7 +55445,7 @@
         <v>989</v>
       </c>
       <c r="M472" t="s" s="2">
-        <v>1161</v>
+        <v>1162</v>
       </c>
       <c r="N472" t="s" s="2">
         <v>991</v>
@@ -55544,7 +55548,7 @@
         <v>367</v>
       </c>
       <c r="M473" t="s" s="2">
-        <v>1162</v>
+        <v>1163</v>
       </c>
       <c r="N473" t="s" s="2">
         <v>993</v>
@@ -55649,7 +55653,7 @@
         <v>881</v>
       </c>
       <c r="M474" t="s" s="2">
-        <v>1163</v>
+        <v>1164</v>
       </c>
       <c r="N474" t="s" s="2">
         <v>999</v>
@@ -55752,7 +55756,7 @@
         <v>367</v>
       </c>
       <c r="M475" t="s" s="2">
-        <v>1164</v>
+        <v>1165</v>
       </c>
       <c r="N475" t="s" s="2">
         <v>1002</v>
@@ -55962,7 +55966,7 @@
         <v>1012</v>
       </c>
       <c r="M477" t="s" s="2">
-        <v>1165</v>
+        <v>1166</v>
       </c>
       <c r="N477" t="s" s="2">
         <v>1014</v>
@@ -56065,7 +56069,7 @@
         <v>97</v>
       </c>
       <c r="M478" t="s" s="2">
-        <v>1166</v>
+        <v>1167</v>
       </c>
       <c r="N478" t="s" s="2">
         <v>1017</v>
@@ -56165,10 +56169,10 @@
         <v>84</v>
       </c>
       <c r="L479" t="s" s="2">
-        <v>1167</v>
+        <v>1168</v>
       </c>
       <c r="M479" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N479" t="s" s="2">
         <v>1020</v>
@@ -56271,7 +56275,7 @@
         <v>112</v>
       </c>
       <c r="M480" t="s" s="2">
-        <v>1169</v>
+        <v>1170</v>
       </c>
       <c r="N480" t="s" s="2">
         <v>1023</v>
@@ -56358,7 +56362,7 @@
       </c>
       <c r="F481" s="2"/>
       <c r="G481" t="s" s="2">
-        <v>76</v>
+        <v>83</v>
       </c>
       <c r="H481" t="s" s="2">
         <v>83</v>
@@ -56376,7 +56380,7 @@
         <v>367</v>
       </c>
       <c r="M481" t="s" s="2">
-        <v>1170</v>
+        <v>1171</v>
       </c>
       <c r="N481" t="s" s="2">
         <v>1027</v>
@@ -56481,7 +56485,7 @@
         <v>1032</v>
       </c>
       <c r="M482" t="s" s="2">
-        <v>1168</v>
+        <v>1169</v>
       </c>
       <c r="N482" t="s" s="2">
         <v>1034</v>
@@ -56584,7 +56588,7 @@
         <v>598</v>
       </c>
       <c r="M483" t="s" s="2">
-        <v>1171</v>
+        <v>1172</v>
       </c>
       <c r="N483" t="s" s="2">
         <v>1037</v>
@@ -56687,7 +56691,7 @@
         <v>1039</v>
       </c>
       <c r="M484" t="s" s="2">
-        <v>1172</v>
+        <v>1173</v>
       </c>
       <c r="N484" t="s" s="2">
         <v>859</v>
@@ -56792,7 +56796,7 @@
         <v>136</v>
       </c>
       <c r="M485" t="s" s="2">
-        <v>1173</v>
+        <v>1174</v>
       </c>
       <c r="N485" t="s" s="2">
         <v>1044</v>
@@ -57630,7 +57634,7 @@
         <v>497</v>
       </c>
       <c r="M493" t="s" s="2">
-        <v>1174</v>
+        <v>1175</v>
       </c>
       <c r="N493" t="s" s="2">
         <v>1057</v>
@@ -57836,7 +57840,7 @@
         <v>1059</v>
       </c>
       <c r="M495" t="s" s="2">
-        <v>1175</v>
+        <v>1176</v>
       </c>
       <c r="N495" t="s" s="2">
         <v>1064</v>
@@ -57939,10 +57943,10 @@
         <v>1066</v>
       </c>
       <c r="M496" t="s" s="2">
-        <v>1176</v>
+        <v>1177</v>
       </c>
       <c r="N496" t="s" s="2">
-        <v>1177</v>
+        <v>1178</v>
       </c>
       <c r="O496" t="s" s="2">
         <v>1069</v>
@@ -58046,10 +58050,10 @@
         <v>130</v>
       </c>
       <c r="M497" t="s" s="2">
-        <v>1178</v>
+        <v>1179</v>
       </c>
       <c r="N497" t="s" s="2">
-        <v>1179</v>
+        <v>1180</v>
       </c>
       <c r="O497" t="s" s="2">
         <v>1074</v>
@@ -58151,7 +58155,7 @@
         <v>497</v>
       </c>
       <c r="M498" t="s" s="2">
-        <v>1180</v>
+        <v>1181</v>
       </c>
       <c r="N498" t="s" s="2">
         <v>1077</v>
@@ -58359,7 +58363,7 @@
         <v>670</v>
       </c>
       <c r="M500" t="s" s="2">
-        <v>1181</v>
+        <v>1182</v>
       </c>
       <c r="N500" t="s" s="2">
         <v>1093</v>
@@ -58462,7 +58466,7 @@
         <v>136</v>
       </c>
       <c r="M501" t="s" s="2">
-        <v>1182</v>
+        <v>1183</v>
       </c>
       <c r="N501" t="s" s="2">
         <v>1096</v>
@@ -59088,7 +59092,7 @@
         <v>819</v>
       </c>
       <c r="M507" t="s" s="2">
-        <v>1183</v>
+        <v>1184</v>
       </c>
       <c r="N507" t="s" s="2">
         <v>1111</v>
@@ -59191,7 +59195,7 @@
         <v>886</v>
       </c>
       <c r="M508" t="s" s="2">
-        <v>1184</v>
+        <v>1185</v>
       </c>
       <c r="N508" t="s" s="2">
         <v>1114</v>
@@ -59296,7 +59300,7 @@
         <v>891</v>
       </c>
       <c r="M509" t="s" s="2">
-        <v>1185</v>
+        <v>1186</v>
       </c>
       <c r="N509" t="s" s="2">
         <v>1117</v>
@@ -59369,13 +59373,13 @@
     </row>
     <row r="510">
       <c r="A510" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B510" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="C510" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="D510" s="2"/>
       <c r="E510" t="s" s="2">
@@ -59401,10 +59405,10 @@
         <v>78</v>
       </c>
       <c r="M510" t="s" s="2">
-        <v>1193</v>
+        <v>1194</v>
       </c>
       <c r="N510" t="s" s="2">
-        <v>1194</v>
+        <v>1195</v>
       </c>
       <c r="O510" s="2"/>
       <c r="P510" s="2"/>
@@ -59455,7 +59459,7 @@
         <v>23</v>
       </c>
       <c r="AG510" t="s" s="2">
-        <v>1191</v>
+        <v>1192</v>
       </c>
       <c r="AH510" t="s" s="2">
         <v>76</v>
@@ -59472,13 +59476,13 @@
     </row>
     <row r="511">
       <c r="A511" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B511" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="C511" t="s" s="2">
-        <v>1195</v>
+        <v>1196</v>
       </c>
       <c r="D511" s="2"/>
       <c r="E511" t="s" s="2">
@@ -59577,13 +59581,13 @@
     </row>
     <row r="512">
       <c r="A512" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B512" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="C512" t="s" s="2">
-        <v>1196</v>
+        <v>1197</v>
       </c>
       <c r="D512" s="2"/>
       <c r="E512" t="s" s="2">
@@ -59680,13 +59684,13 @@
     </row>
     <row r="513">
       <c r="A513" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B513" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="C513" t="s" s="2">
-        <v>1197</v>
+        <v>1198</v>
       </c>
       <c r="D513" s="2"/>
       <c r="E513" t="s" s="2">
@@ -59785,13 +59789,13 @@
     </row>
     <row r="514">
       <c r="A514" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B514" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="C514" t="s" s="2">
-        <v>1198</v>
+        <v>1199</v>
       </c>
       <c r="D514" s="2"/>
       <c r="E514" t="s" s="2">
@@ -59890,13 +59894,13 @@
     </row>
     <row r="515">
       <c r="A515" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B515" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="C515" t="s" s="2">
-        <v>1199</v>
+        <v>1200</v>
       </c>
       <c r="D515" s="2"/>
       <c r="E515" t="s" s="2">
@@ -59995,13 +59999,13 @@
     </row>
     <row r="516">
       <c r="A516" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B516" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="C516" t="s" s="2">
-        <v>1200</v>
+        <v>1201</v>
       </c>
       <c r="D516" s="2"/>
       <c r="E516" t="s" s="2">
@@ -60100,13 +60104,13 @@
     </row>
     <row r="517">
       <c r="A517" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B517" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="C517" t="s" s="2">
-        <v>1201</v>
+        <v>1202</v>
       </c>
       <c r="D517" s="2"/>
       <c r="E517" t="s" s="2">
@@ -60205,13 +60209,13 @@
     </row>
     <row r="518">
       <c r="A518" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B518" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="C518" t="s" s="2">
-        <v>1202</v>
+        <v>1203</v>
       </c>
       <c r="D518" s="2"/>
       <c r="E518" t="s" s="2">
@@ -60312,13 +60316,13 @@
     </row>
     <row r="519">
       <c r="A519" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B519" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="C519" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="D519" s="2"/>
       <c r="E519" t="s" s="2">
@@ -60344,13 +60348,13 @@
         <v>112</v>
       </c>
       <c r="M519" t="s" s="2">
-        <v>1204</v>
+        <v>1205</v>
       </c>
       <c r="N519" t="s" s="2">
-        <v>1205</v>
+        <v>1206</v>
       </c>
       <c r="O519" t="s" s="2">
-        <v>1206</v>
+        <v>1207</v>
       </c>
       <c r="P519" s="2"/>
       <c r="Q519" t="s" s="2">
@@ -60400,7 +60404,7 @@
         <v>23</v>
       </c>
       <c r="AG519" t="s" s="2">
-        <v>1203</v>
+        <v>1204</v>
       </c>
       <c r="AH519" t="s" s="2">
         <v>76</v>
@@ -60417,13 +60421,13 @@
     </row>
     <row r="520">
       <c r="A520" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B520" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="C520" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="D520" s="2"/>
       <c r="E520" t="s" s="2">
@@ -60449,10 +60453,10 @@
         <v>103</v>
       </c>
       <c r="M520" t="s" s="2">
-        <v>1208</v>
+        <v>1209</v>
       </c>
       <c r="N520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="O520" s="2"/>
       <c r="P520" s="2"/>
@@ -60482,10 +60486,10 @@
         <v>121</v>
       </c>
       <c r="Z520" t="s" s="2">
-        <v>1209</v>
+        <v>1210</v>
       </c>
       <c r="AA520" t="s" s="2">
-        <v>1210</v>
+        <v>1211</v>
       </c>
       <c r="AB520" t="s" s="2">
         <v>23</v>
@@ -60503,7 +60507,7 @@
         <v>23</v>
       </c>
       <c r="AG520" t="s" s="2">
-        <v>1207</v>
+        <v>1208</v>
       </c>
       <c r="AH520" t="s" s="2">
         <v>76</v>
@@ -60520,13 +60524,13 @@
     </row>
     <row r="521">
       <c r="A521" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B521" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="C521" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="D521" s="2"/>
       <c r="E521" t="s" s="2">
@@ -60552,13 +60556,13 @@
         <v>367</v>
       </c>
       <c r="M521" t="s" s="2">
-        <v>1212</v>
+        <v>1213</v>
       </c>
       <c r="N521" t="s" s="2">
-        <v>1213</v>
+        <v>1214</v>
       </c>
       <c r="O521" t="s" s="2">
-        <v>1214</v>
+        <v>1215</v>
       </c>
       <c r="P521" s="2"/>
       <c r="Q521" t="s" s="2">
@@ -60584,13 +60588,13 @@
         <v>23</v>
       </c>
       <c r="Y521" t="s" s="2">
-        <v>1215</v>
+        <v>1216</v>
       </c>
       <c r="Z521" t="s" s="2">
-        <v>1216</v>
+        <v>1217</v>
       </c>
       <c r="AA521" t="s" s="2">
-        <v>1217</v>
+        <v>1218</v>
       </c>
       <c r="AB521" t="s" s="2">
         <v>23</v>
@@ -60608,7 +60612,7 @@
         <v>23</v>
       </c>
       <c r="AG521" t="s" s="2">
-        <v>1211</v>
+        <v>1212</v>
       </c>
       <c r="AH521" t="s" s="2">
         <v>76</v>
@@ -60625,13 +60629,13 @@
     </row>
     <row r="522">
       <c r="A522" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B522" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="C522" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="D522" s="2"/>
       <c r="E522" t="s" s="2">
@@ -60657,13 +60661,13 @@
         <v>367</v>
       </c>
       <c r="M522" t="s" s="2">
-        <v>1219</v>
+        <v>1220</v>
       </c>
       <c r="N522" t="s" s="2">
-        <v>1220</v>
+        <v>1221</v>
       </c>
       <c r="O522" t="s" s="2">
-        <v>1221</v>
+        <v>1222</v>
       </c>
       <c r="P522" s="2"/>
       <c r="Q522" t="s" s="2">
@@ -60692,10 +60696,10 @@
         <v>372</v>
       </c>
       <c r="Z522" t="s" s="2">
-        <v>1222</v>
+        <v>1223</v>
       </c>
       <c r="AA522" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="AB522" t="s" s="2">
         <v>23</v>
@@ -60713,7 +60717,7 @@
         <v>23</v>
       </c>
       <c r="AG522" t="s" s="2">
-        <v>1218</v>
+        <v>1219</v>
       </c>
       <c r="AH522" t="s" s="2">
         <v>83</v>
@@ -60730,13 +60734,13 @@
     </row>
     <row r="523">
       <c r="A523" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B523" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="C523" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="D523" s="2"/>
       <c r="E523" t="s" s="2">
@@ -60762,10 +60766,10 @@
         <v>141</v>
       </c>
       <c r="M523" t="s" s="2">
-        <v>1225</v>
+        <v>1226</v>
       </c>
       <c r="N523" t="s" s="2">
-        <v>1226</v>
+        <v>1227</v>
       </c>
       <c r="O523" s="2"/>
       <c r="P523" s="2"/>
@@ -60816,7 +60820,7 @@
         <v>23</v>
       </c>
       <c r="AG523" t="s" s="2">
-        <v>1224</v>
+        <v>1225</v>
       </c>
       <c r="AH523" t="s" s="2">
         <v>76</v>
@@ -60833,13 +60837,13 @@
     </row>
     <row r="524">
       <c r="A524" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B524" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="C524" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="D524" s="2"/>
       <c r="E524" t="s" s="2">
@@ -60865,10 +60869,10 @@
         <v>136</v>
       </c>
       <c r="M524" t="s" s="2">
-        <v>1228</v>
+        <v>1229</v>
       </c>
       <c r="N524" t="s" s="2">
-        <v>1229</v>
+        <v>1230</v>
       </c>
       <c r="O524" s="2"/>
       <c r="P524" s="2"/>
@@ -60876,7 +60880,7 @@
         <v>23</v>
       </c>
       <c r="R524" t="s" s="2">
-        <v>1230</v>
+        <v>1231</v>
       </c>
       <c r="S524" t="s" s="2">
         <v>23</v>
@@ -60921,7 +60925,7 @@
         <v>23</v>
       </c>
       <c r="AG524" t="s" s="2">
-        <v>1227</v>
+        <v>1228</v>
       </c>
       <c r="AH524" t="s" s="2">
         <v>76</v>
@@ -60938,13 +60942,13 @@
     </row>
     <row r="525">
       <c r="A525" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B525" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="C525" t="s" s="2">
-        <v>1231</v>
+        <v>1232</v>
       </c>
       <c r="D525" s="2"/>
       <c r="E525" t="s" s="2">
@@ -61041,13 +61045,13 @@
     </row>
     <row r="526">
       <c r="A526" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B526" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="C526" t="s" s="2">
-        <v>1232</v>
+        <v>1233</v>
       </c>
       <c r="D526" s="2"/>
       <c r="E526" t="s" s="2">
@@ -61146,13 +61150,13 @@
     </row>
     <row r="527">
       <c r="A527" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B527" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="C527" t="s" s="2">
-        <v>1233</v>
+        <v>1234</v>
       </c>
       <c r="D527" s="2"/>
       <c r="E527" t="s" s="2">
@@ -61253,13 +61257,13 @@
     </row>
     <row r="528">
       <c r="A528" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B528" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="C528" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="D528" s="2"/>
       <c r="E528" t="s" s="2">
@@ -61285,10 +61289,10 @@
         <v>112</v>
       </c>
       <c r="M528" t="s" s="2">
-        <v>1235</v>
+        <v>1236</v>
       </c>
       <c r="N528" t="s" s="2">
-        <v>1236</v>
+        <v>1237</v>
       </c>
       <c r="O528" s="2"/>
       <c r="P528" s="2"/>
@@ -61339,7 +61343,7 @@
         <v>23</v>
       </c>
       <c r="AG528" t="s" s="2">
-        <v>1234</v>
+        <v>1235</v>
       </c>
       <c r="AH528" t="s" s="2">
         <v>76</v>
@@ -61356,13 +61360,13 @@
     </row>
     <row r="529">
       <c r="A529" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B529" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="C529" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="D529" s="2"/>
       <c r="E529" t="s" s="2">
@@ -61388,10 +61392,10 @@
         <v>578</v>
       </c>
       <c r="M529" t="s" s="2">
-        <v>1238</v>
+        <v>1239</v>
       </c>
       <c r="N529" t="s" s="2">
-        <v>1239</v>
+        <v>1240</v>
       </c>
       <c r="O529" s="2"/>
       <c r="P529" s="2"/>
@@ -61442,7 +61446,7 @@
         <v>23</v>
       </c>
       <c r="AG529" t="s" s="2">
-        <v>1237</v>
+        <v>1238</v>
       </c>
       <c r="AH529" t="s" s="2">
         <v>76</v>
@@ -61459,13 +61463,13 @@
     </row>
     <row r="530">
       <c r="A530" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B530" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="C530" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="D530" s="2"/>
       <c r="E530" t="s" s="2">
@@ -61491,10 +61495,10 @@
         <v>497</v>
       </c>
       <c r="M530" t="s" s="2">
-        <v>1241</v>
+        <v>1242</v>
       </c>
       <c r="N530" t="s" s="2">
-        <v>1242</v>
+        <v>1243</v>
       </c>
       <c r="O530" s="2"/>
       <c r="P530" s="2"/>
@@ -61545,7 +61549,7 @@
         <v>23</v>
       </c>
       <c r="AG530" t="s" s="2">
-        <v>1240</v>
+        <v>1241</v>
       </c>
       <c r="AH530" t="s" s="2">
         <v>76</v>
@@ -61562,13 +61566,13 @@
     </row>
     <row r="531">
       <c r="A531" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B531" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="C531" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="D531" s="2"/>
       <c r="E531" t="s" s="2">
@@ -61594,10 +61598,10 @@
         <v>136</v>
       </c>
       <c r="M531" t="s" s="2">
-        <v>1244</v>
+        <v>1245</v>
       </c>
       <c r="N531" t="s" s="2">
-        <v>1245</v>
+        <v>1246</v>
       </c>
       <c r="O531" s="2"/>
       <c r="P531" s="2"/>
@@ -61648,7 +61652,7 @@
         <v>23</v>
       </c>
       <c r="AG531" t="s" s="2">
-        <v>1243</v>
+        <v>1244</v>
       </c>
       <c r="AH531" t="s" s="2">
         <v>76</v>
@@ -61665,13 +61669,13 @@
     </row>
     <row r="532">
       <c r="A532" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B532" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="C532" t="s" s="2">
-        <v>1246</v>
+        <v>1247</v>
       </c>
       <c r="D532" s="2"/>
       <c r="E532" t="s" s="2">
@@ -61768,13 +61772,13 @@
     </row>
     <row r="533">
       <c r="A533" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B533" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="C533" t="s" s="2">
-        <v>1247</v>
+        <v>1248</v>
       </c>
       <c r="D533" s="2"/>
       <c r="E533" t="s" s="2">
@@ -61873,13 +61877,13 @@
     </row>
     <row r="534">
       <c r="A534" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B534" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="C534" t="s" s="2">
-        <v>1248</v>
+        <v>1249</v>
       </c>
       <c r="D534" s="2"/>
       <c r="E534" t="s" s="2">
@@ -61980,13 +61984,13 @@
     </row>
     <row r="535">
       <c r="A535" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B535" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="C535" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="D535" s="2"/>
       <c r="E535" t="s" s="2">
@@ -62012,10 +62016,10 @@
         <v>491</v>
       </c>
       <c r="M535" t="s" s="2">
-        <v>1250</v>
+        <v>1251</v>
       </c>
       <c r="N535" t="s" s="2">
-        <v>1251</v>
+        <v>1252</v>
       </c>
       <c r="O535" s="2"/>
       <c r="P535" s="2"/>
@@ -62066,7 +62070,7 @@
         <v>23</v>
       </c>
       <c r="AG535" t="s" s="2">
-        <v>1249</v>
+        <v>1250</v>
       </c>
       <c r="AH535" t="s" s="2">
         <v>76</v>
@@ -62083,13 +62087,13 @@
     </row>
     <row r="536">
       <c r="A536" t="s" s="2">
-        <v>1186</v>
+        <v>1187</v>
       </c>
       <c r="B536" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="C536" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="D536" s="2"/>
       <c r="E536" t="s" s="2">
@@ -62112,13 +62116,13 @@
         <v>84</v>
       </c>
       <c r="L536" t="s" s="2">
-        <v>1253</v>
+        <v>1254</v>
       </c>
       <c r="M536" t="s" s="2">
-        <v>1254</v>
+        <v>1255</v>
       </c>
       <c r="N536" t="s" s="2">
-        <v>1255</v>
+        <v>1256</v>
       </c>
       <c r="O536" s="2"/>
       <c r="P536" s="2"/>
@@ -62148,10 +62152,10 @@
         <v>372</v>
       </c>
       <c r="Z536" t="s" s="2">
-        <v>1256</v>
+        <v>1257</v>
       </c>
       <c r="AA536" t="s" s="2">
-        <v>1223</v>
+        <v>1224</v>
       </c>
       <c r="AB536" t="s" s="2">
         <v>23</v>
@@ -62169,7 +62173,7 @@
         <v>23</v>
       </c>
       <c r="AG536" t="s" s="2">
-        <v>1252</v>
+        <v>1253</v>
       </c>
       <c r="AH536" t="s" s="2">
         <v>83</v>
@@ -62186,13 +62190,13 @@
     </row>
     <row r="537">
       <c r="A537" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B537" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="C537" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="D537" s="2"/>
       <c r="E537" t="s" s="2">
@@ -62218,13 +62222,13 @@
         <v>78</v>
       </c>
       <c r="M537" t="s" s="2">
-        <v>1263</v>
+        <v>1264</v>
       </c>
       <c r="N537" t="s" s="2">
-        <v>1264</v>
+        <v>1265</v>
       </c>
       <c r="O537" t="s" s="2">
-        <v>1265</v>
+        <v>1266</v>
       </c>
       <c r="P537" s="2"/>
       <c r="Q537" t="s" s="2">
@@ -62274,7 +62278,7 @@
         <v>23</v>
       </c>
       <c r="AG537" t="s" s="2">
-        <v>1261</v>
+        <v>1262</v>
       </c>
       <c r="AH537" t="s" s="2">
         <v>76</v>
@@ -62291,13 +62295,13 @@
     </row>
     <row r="538">
       <c r="A538" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B538" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="C538" t="s" s="2">
-        <v>1266</v>
+        <v>1267</v>
       </c>
       <c r="D538" s="2"/>
       <c r="E538" t="s" s="2">
@@ -62394,13 +62398,13 @@
     </row>
     <row r="539">
       <c r="A539" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B539" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="C539" t="s" s="2">
-        <v>1267</v>
+        <v>1268</v>
       </c>
       <c r="D539" s="2"/>
       <c r="E539" t="s" s="2">
@@ -62499,13 +62503,13 @@
     </row>
     <row r="540">
       <c r="A540" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B540" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="C540" t="s" s="2">
-        <v>1268</v>
+        <v>1269</v>
       </c>
       <c r="D540" s="2"/>
       <c r="E540" t="s" s="2">
@@ -62606,13 +62610,13 @@
     </row>
     <row r="541">
       <c r="A541" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B541" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="C541" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="D541" s="2"/>
       <c r="E541" t="s" s="2">
@@ -62638,14 +62642,14 @@
         <v>578</v>
       </c>
       <c r="M541" t="s" s="2">
-        <v>1270</v>
+        <v>1271</v>
       </c>
       <c r="N541" t="s" s="2">
-        <v>1271</v>
+        <v>1272</v>
       </c>
       <c r="O541" s="2"/>
       <c r="P541" t="s" s="2">
-        <v>1272</v>
+        <v>1273</v>
       </c>
       <c r="Q541" t="s" s="2">
         <v>23</v>
@@ -62694,7 +62698,7 @@
         <v>23</v>
       </c>
       <c r="AG541" t="s" s="2">
-        <v>1269</v>
+        <v>1270</v>
       </c>
       <c r="AH541" t="s" s="2">
         <v>76</v>
@@ -62711,13 +62715,13 @@
     </row>
     <row r="542">
       <c r="A542" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B542" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="C542" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="D542" s="2"/>
       <c r="E542" t="s" s="2">
@@ -62743,14 +62747,14 @@
         <v>418</v>
       </c>
       <c r="M542" t="s" s="2">
-        <v>1274</v>
+        <v>1275</v>
       </c>
       <c r="N542" t="s" s="2">
-        <v>1275</v>
+        <v>1276</v>
       </c>
       <c r="O542" s="2"/>
       <c r="P542" t="s" s="2">
-        <v>1276</v>
+        <v>1277</v>
       </c>
       <c r="Q542" t="s" s="2">
         <v>23</v>
@@ -62799,7 +62803,7 @@
         <v>23</v>
       </c>
       <c r="AG542" t="s" s="2">
-        <v>1273</v>
+        <v>1274</v>
       </c>
       <c r="AH542" t="s" s="2">
         <v>76</v>
@@ -62811,18 +62815,18 @@
         <v>23</v>
       </c>
       <c r="AK542" t="s" s="2">
-        <v>1277</v>
+        <v>1278</v>
       </c>
     </row>
     <row r="543">
       <c r="A543" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B543" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="C543" t="s" s="2">
-        <v>1278</v>
+        <v>1279</v>
       </c>
       <c r="D543" s="2"/>
       <c r="E543" t="s" s="2">
@@ -62919,13 +62923,13 @@
     </row>
     <row r="544">
       <c r="A544" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B544" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="C544" t="s" s="2">
-        <v>1279</v>
+        <v>1280</v>
       </c>
       <c r="D544" s="2"/>
       <c r="E544" t="s" s="2">
@@ -63024,13 +63028,13 @@
     </row>
     <row r="545">
       <c r="A545" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="C545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D545" s="2"/>
       <c r="E545" t="s" s="2">
@@ -63053,13 +63057,13 @@
         <v>84</v>
       </c>
       <c r="L545" t="s" s="2">
-        <v>1281</v>
+        <v>1282</v>
       </c>
       <c r="M545" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N545" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O545" s="2"/>
       <c r="P545" s="2"/>
@@ -63108,7 +63112,7 @@
         <v>355</v>
       </c>
       <c r="AG545" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="AH545" t="s" s="2">
         <v>76</v>
@@ -63125,16 +63129,16 @@
     </row>
     <row r="546">
       <c r="A546" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B546" t="s" s="2">
-        <v>1284</v>
+        <v>1285</v>
       </c>
       <c r="C546" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="D546" t="s" s="2">
-        <v>1285</v>
+        <v>1286</v>
       </c>
       <c r="E546" t="s" s="2">
         <v>23</v>
@@ -63159,10 +63163,10 @@
         <v>1066</v>
       </c>
       <c r="M546" t="s" s="2">
-        <v>1282</v>
+        <v>1283</v>
       </c>
       <c r="N546" t="s" s="2">
-        <v>1283</v>
+        <v>1284</v>
       </c>
       <c r="O546" s="2"/>
       <c r="P546" s="2"/>
@@ -63213,7 +63217,7 @@
         <v>23</v>
       </c>
       <c r="AG546" t="s" s="2">
-        <v>1280</v>
+        <v>1281</v>
       </c>
       <c r="AH546" t="s" s="2">
         <v>76</v>
@@ -63230,13 +63234,13 @@
     </row>
     <row r="547">
       <c r="A547" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B547" t="s" s="2">
-        <v>1286</v>
+        <v>1287</v>
       </c>
       <c r="C547" t="s" s="2">
-        <v>1287</v>
+        <v>1288</v>
       </c>
       <c r="D547" s="2"/>
       <c r="E547" t="s" s="2">
@@ -63333,13 +63337,13 @@
     </row>
     <row r="548">
       <c r="A548" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B548" t="s" s="2">
-        <v>1288</v>
+        <v>1289</v>
       </c>
       <c r="C548" t="s" s="2">
-        <v>1289</v>
+        <v>1290</v>
       </c>
       <c r="D548" s="2"/>
       <c r="E548" t="s" s="2">
@@ -63438,13 +63442,13 @@
     </row>
     <row r="549">
       <c r="A549" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B549" t="s" s="2">
-        <v>1290</v>
+        <v>1291</v>
       </c>
       <c r="C549" t="s" s="2">
-        <v>1291</v>
+        <v>1292</v>
       </c>
       <c r="D549" s="2"/>
       <c r="E549" t="s" s="2">
@@ -63470,13 +63474,13 @@
         <v>578</v>
       </c>
       <c r="M549" t="s" s="2">
-        <v>1292</v>
+        <v>1293</v>
       </c>
       <c r="N549" t="s" s="2">
-        <v>1293</v>
+        <v>1294</v>
       </c>
       <c r="O549" t="s" s="2">
-        <v>1294</v>
+        <v>1295</v>
       </c>
       <c r="P549" s="2"/>
       <c r="Q549" t="s" s="2">
@@ -63526,7 +63530,7 @@
         <v>23</v>
       </c>
       <c r="AG549" t="s" s="2">
-        <v>1295</v>
+        <v>1296</v>
       </c>
       <c r="AH549" t="s" s="2">
         <v>76</v>
@@ -63535,7 +63539,7 @@
         <v>83</v>
       </c>
       <c r="AJ549" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="AK549" t="s" s="2">
         <v>95</v>
@@ -63543,13 +63547,13 @@
     </row>
     <row r="550">
       <c r="A550" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B550" t="s" s="2">
-        <v>1297</v>
+        <v>1298</v>
       </c>
       <c r="C550" t="s" s="2">
-        <v>1298</v>
+        <v>1299</v>
       </c>
       <c r="D550" s="2"/>
       <c r="E550" t="s" s="2">
@@ -63575,20 +63579,20 @@
         <v>578</v>
       </c>
       <c r="M550" t="s" s="2">
-        <v>1299</v>
+        <v>1300</v>
       </c>
       <c r="N550" t="s" s="2">
-        <v>1300</v>
+        <v>1301</v>
       </c>
       <c r="O550" t="s" s="2">
-        <v>1301</v>
+        <v>1302</v>
       </c>
       <c r="P550" s="2"/>
       <c r="Q550" t="s" s="2">
         <v>23</v>
       </c>
       <c r="R550" t="s" s="2">
-        <v>1302</v>
+        <v>1303</v>
       </c>
       <c r="S550" t="s" s="2">
         <v>23</v>
@@ -63633,7 +63637,7 @@
         <v>23</v>
       </c>
       <c r="AG550" t="s" s="2">
-        <v>1303</v>
+        <v>1304</v>
       </c>
       <c r="AH550" t="s" s="2">
         <v>76</v>
@@ -63642,7 +63646,7 @@
         <v>83</v>
       </c>
       <c r="AJ550" t="s" s="2">
-        <v>1296</v>
+        <v>1297</v>
       </c>
       <c r="AK550" t="s" s="2">
         <v>95</v>
@@ -63650,13 +63654,13 @@
     </row>
     <row r="551">
       <c r="A551" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B551" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="C551" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="D551" s="2"/>
       <c r="E551" t="s" s="2">
@@ -63679,19 +63683,19 @@
         <v>84</v>
       </c>
       <c r="L551" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="M551" t="s" s="2">
-        <v>1306</v>
+        <v>1307</v>
       </c>
       <c r="N551" t="s" s="2">
-        <v>1307</v>
+        <v>1308</v>
       </c>
       <c r="O551" t="s" s="2">
-        <v>1308</v>
+        <v>1309</v>
       </c>
       <c r="P551" t="s" s="2">
-        <v>1309</v>
+        <v>1310</v>
       </c>
       <c r="Q551" t="s" s="2">
         <v>23</v>
@@ -63740,7 +63744,7 @@
         <v>23</v>
       </c>
       <c r="AG551" t="s" s="2">
-        <v>1304</v>
+        <v>1305</v>
       </c>
       <c r="AH551" t="s" s="2">
         <v>76</v>
@@ -63757,13 +63761,13 @@
     </row>
     <row r="552">
       <c r="A552" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B552" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="C552" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="D552" s="2"/>
       <c r="E552" t="s" s="2">
@@ -63786,13 +63790,13 @@
         <v>84</v>
       </c>
       <c r="L552" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="M552" t="s" s="2">
-        <v>1311</v>
+        <v>1312</v>
       </c>
       <c r="N552" t="s" s="2">
-        <v>1312</v>
+        <v>1313</v>
       </c>
       <c r="O552" s="2"/>
       <c r="P552" s="2"/>
@@ -63843,7 +63847,7 @@
         <v>23</v>
       </c>
       <c r="AG552" t="s" s="2">
-        <v>1310</v>
+        <v>1311</v>
       </c>
       <c r="AH552" t="s" s="2">
         <v>76</v>
@@ -63860,13 +63864,13 @@
     </row>
     <row r="553">
       <c r="A553" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B553" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="C553" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="D553" s="2"/>
       <c r="E553" t="s" s="2">
@@ -63892,16 +63896,16 @@
         <v>199</v>
       </c>
       <c r="M553" t="s" s="2">
-        <v>1314</v>
+        <v>1315</v>
       </c>
       <c r="N553" t="s" s="2">
-        <v>1315</v>
+        <v>1316</v>
       </c>
       <c r="O553" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="P553" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="Q553" t="s" s="2">
         <v>23</v>
@@ -63950,7 +63954,7 @@
         <v>23</v>
       </c>
       <c r="AG553" t="s" s="2">
-        <v>1313</v>
+        <v>1314</v>
       </c>
       <c r="AH553" t="s" s="2">
         <v>76</v>
@@ -63967,13 +63971,13 @@
     </row>
     <row r="554">
       <c r="A554" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B554" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="C554" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="D554" s="2"/>
       <c r="E554" t="s" s="2">
@@ -63999,16 +64003,16 @@
         <v>199</v>
       </c>
       <c r="M554" t="s" s="2">
-        <v>1319</v>
+        <v>1320</v>
       </c>
       <c r="N554" t="s" s="2">
-        <v>1320</v>
+        <v>1321</v>
       </c>
       <c r="O554" t="s" s="2">
-        <v>1316</v>
+        <v>1317</v>
       </c>
       <c r="P554" t="s" s="2">
-        <v>1317</v>
+        <v>1318</v>
       </c>
       <c r="Q554" t="s" s="2">
         <v>23</v>
@@ -64057,7 +64061,7 @@
         <v>23</v>
       </c>
       <c r="AG554" t="s" s="2">
-        <v>1318</v>
+        <v>1319</v>
       </c>
       <c r="AH554" t="s" s="2">
         <v>76</v>
@@ -64074,13 +64078,13 @@
     </row>
     <row r="555">
       <c r="A555" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B555" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="C555" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="D555" s="2"/>
       <c r="E555" t="s" s="2">
@@ -64106,10 +64110,10 @@
         <v>103</v>
       </c>
       <c r="M555" t="s" s="2">
-        <v>1322</v>
+        <v>1323</v>
       </c>
       <c r="N555" t="s" s="2">
-        <v>1323</v>
+        <v>1324</v>
       </c>
       <c r="O555" s="2"/>
       <c r="P555" s="2"/>
@@ -64139,10 +64143,10 @@
         <v>121</v>
       </c>
       <c r="Z555" t="s" s="2">
-        <v>1324</v>
+        <v>1325</v>
       </c>
       <c r="AA555" t="s" s="2">
-        <v>1325</v>
+        <v>1326</v>
       </c>
       <c r="AB555" t="s" s="2">
         <v>23</v>
@@ -64160,7 +64164,7 @@
         <v>23</v>
       </c>
       <c r="AG555" t="s" s="2">
-        <v>1321</v>
+        <v>1322</v>
       </c>
       <c r="AH555" t="s" s="2">
         <v>76</v>
@@ -64177,13 +64181,13 @@
     </row>
     <row r="556">
       <c r="A556" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B556" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="C556" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="D556" s="2"/>
       <c r="E556" t="s" s="2">
@@ -64206,13 +64210,13 @@
         <v>84</v>
       </c>
       <c r="L556" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="M556" t="s" s="2">
-        <v>1327</v>
+        <v>1328</v>
       </c>
       <c r="N556" t="s" s="2">
-        <v>1328</v>
+        <v>1329</v>
       </c>
       <c r="O556" s="2"/>
       <c r="P556" s="2"/>
@@ -64220,7 +64224,7 @@
         <v>23</v>
       </c>
       <c r="R556" t="s" s="2">
-        <v>1329</v>
+        <v>1330</v>
       </c>
       <c r="S556" t="s" s="2">
         <v>23</v>
@@ -64265,7 +64269,7 @@
         <v>23</v>
       </c>
       <c r="AG556" t="s" s="2">
-        <v>1326</v>
+        <v>1327</v>
       </c>
       <c r="AH556" t="s" s="2">
         <v>76</v>
@@ -64282,13 +64286,13 @@
     </row>
     <row r="557">
       <c r="A557" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="C557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="D557" s="2"/>
       <c r="E557" t="s" s="2">
@@ -64311,13 +64315,13 @@
         <v>84</v>
       </c>
       <c r="L557" t="s" s="2">
-        <v>1305</v>
+        <v>1306</v>
       </c>
       <c r="M557" t="s" s="2">
-        <v>1331</v>
+        <v>1332</v>
       </c>
       <c r="N557" t="s" s="2">
-        <v>1332</v>
+        <v>1333</v>
       </c>
       <c r="O557" s="2"/>
       <c r="P557" s="2"/>
@@ -64368,7 +64372,7 @@
         <v>23</v>
       </c>
       <c r="AG557" t="s" s="2">
-        <v>1330</v>
+        <v>1331</v>
       </c>
       <c r="AH557" t="s" s="2">
         <v>76</v>
@@ -64385,13 +64389,13 @@
     </row>
     <row r="558">
       <c r="A558" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="C558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="D558" s="2"/>
       <c r="E558" t="s" s="2">
@@ -64417,10 +64421,10 @@
         <v>199</v>
       </c>
       <c r="M558" t="s" s="2">
-        <v>1334</v>
+        <v>1335</v>
       </c>
       <c r="N558" t="s" s="2">
-        <v>1335</v>
+        <v>1336</v>
       </c>
       <c r="O558" s="2"/>
       <c r="P558" s="2"/>
@@ -64471,7 +64475,7 @@
         <v>23</v>
       </c>
       <c r="AG558" t="s" s="2">
-        <v>1333</v>
+        <v>1334</v>
       </c>
       <c r="AH558" t="s" s="2">
         <v>76</v>
@@ -64488,13 +64492,13 @@
     </row>
     <row r="559">
       <c r="A559" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="C559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="D559" s="2"/>
       <c r="E559" t="s" s="2">
@@ -64520,10 +64524,10 @@
         <v>199</v>
       </c>
       <c r="M559" t="s" s="2">
-        <v>1337</v>
+        <v>1338</v>
       </c>
       <c r="N559" t="s" s="2">
-        <v>1338</v>
+        <v>1339</v>
       </c>
       <c r="O559" s="2"/>
       <c r="P559" s="2"/>
@@ -64574,7 +64578,7 @@
         <v>23</v>
       </c>
       <c r="AG559" t="s" s="2">
-        <v>1336</v>
+        <v>1337</v>
       </c>
       <c r="AH559" t="s" s="2">
         <v>76</v>
@@ -64591,13 +64595,13 @@
     </row>
     <row r="560">
       <c r="A560" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="C560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="D560" s="2"/>
       <c r="E560" t="s" s="2">
@@ -64623,10 +64627,10 @@
         <v>103</v>
       </c>
       <c r="M560" t="s" s="2">
-        <v>1340</v>
+        <v>1341</v>
       </c>
       <c r="N560" t="s" s="2">
-        <v>1341</v>
+        <v>1342</v>
       </c>
       <c r="O560" s="2"/>
       <c r="P560" s="2"/>
@@ -64657,7 +64661,7 @@
       </c>
       <c r="Z560" s="2"/>
       <c r="AA560" t="s" s="2">
-        <v>1342</v>
+        <v>1343</v>
       </c>
       <c r="AB560" t="s" s="2">
         <v>23</v>
@@ -64675,7 +64679,7 @@
         <v>23</v>
       </c>
       <c r="AG560" t="s" s="2">
-        <v>1339</v>
+        <v>1340</v>
       </c>
       <c r="AH560" t="s" s="2">
         <v>76</v>
@@ -64692,13 +64696,13 @@
     </row>
     <row r="561">
       <c r="A561" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B561" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="C561" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="D561" s="2"/>
       <c r="E561" t="s" s="2">
@@ -64724,13 +64728,13 @@
         <v>103</v>
       </c>
       <c r="M561" t="s" s="2">
-        <v>1344</v>
+        <v>1345</v>
       </c>
       <c r="N561" t="s" s="2">
-        <v>1345</v>
+        <v>1346</v>
       </c>
       <c r="O561" t="s" s="2">
-        <v>1346</v>
+        <v>1347</v>
       </c>
       <c r="P561" s="2"/>
       <c r="Q561" t="s" s="2">
@@ -64760,7 +64764,7 @@
       </c>
       <c r="Z561" s="2"/>
       <c r="AA561" t="s" s="2">
-        <v>1347</v>
+        <v>1348</v>
       </c>
       <c r="AB561" t="s" s="2">
         <v>23</v>
@@ -64778,7 +64782,7 @@
         <v>23</v>
       </c>
       <c r="AG561" t="s" s="2">
-        <v>1343</v>
+        <v>1344</v>
       </c>
       <c r="AH561" t="s" s="2">
         <v>76</v>
@@ -64795,13 +64799,13 @@
     </row>
     <row r="562">
       <c r="A562" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B562" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="C562" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="D562" s="2"/>
       <c r="E562" t="s" s="2">
@@ -64824,16 +64828,16 @@
         <v>84</v>
       </c>
       <c r="L562" t="s" s="2">
-        <v>1349</v>
+        <v>1350</v>
       </c>
       <c r="M562" t="s" s="2">
-        <v>1350</v>
+        <v>1351</v>
       </c>
       <c r="N562" t="s" s="2">
-        <v>1351</v>
+        <v>1352</v>
       </c>
       <c r="O562" t="s" s="2">
-        <v>1352</v>
+        <v>1353</v>
       </c>
       <c r="P562" s="2"/>
       <c r="Q562" t="s" s="2">
@@ -64883,7 +64887,7 @@
         <v>23</v>
       </c>
       <c r="AG562" t="s" s="2">
-        <v>1348</v>
+        <v>1349</v>
       </c>
       <c r="AH562" t="s" s="2">
         <v>76</v>
@@ -64900,13 +64904,13 @@
     </row>
     <row r="563">
       <c r="A563" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B563" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="C563" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="D563" s="2"/>
       <c r="E563" t="s" s="2">
@@ -64932,16 +64936,16 @@
         <v>103</v>
       </c>
       <c r="M563" t="s" s="2">
-        <v>1354</v>
+        <v>1355</v>
       </c>
       <c r="N563" t="s" s="2">
-        <v>1355</v>
+        <v>1356</v>
       </c>
       <c r="O563" t="s" s="2">
-        <v>1356</v>
+        <v>1357</v>
       </c>
       <c r="P563" t="s" s="2">
-        <v>1357</v>
+        <v>1358</v>
       </c>
       <c r="Q563" t="s" s="2">
         <v>23</v>
@@ -64970,7 +64974,7 @@
       </c>
       <c r="Z563" s="2"/>
       <c r="AA563" t="s" s="2">
-        <v>1358</v>
+        <v>1359</v>
       </c>
       <c r="AB563" t="s" s="2">
         <v>23</v>
@@ -64988,7 +64992,7 @@
         <v>23</v>
       </c>
       <c r="AG563" t="s" s="2">
-        <v>1353</v>
+        <v>1354</v>
       </c>
       <c r="AH563" t="s" s="2">
         <v>76</v>
@@ -65005,13 +65009,13 @@
     </row>
     <row r="564">
       <c r="A564" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B564" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="C564" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="D564" s="2"/>
       <c r="E564" t="s" s="2">
@@ -65037,10 +65041,10 @@
         <v>130</v>
       </c>
       <c r="M564" t="s" s="2">
-        <v>1360</v>
+        <v>1361</v>
       </c>
       <c r="N564" t="s" s="2">
-        <v>1361</v>
+        <v>1362</v>
       </c>
       <c r="O564" s="2"/>
       <c r="P564" s="2"/>
@@ -65091,7 +65095,7 @@
         <v>23</v>
       </c>
       <c r="AG564" t="s" s="2">
-        <v>1359</v>
+        <v>1360</v>
       </c>
       <c r="AH564" t="s" s="2">
         <v>76</v>
@@ -65108,13 +65112,13 @@
     </row>
     <row r="565">
       <c r="A565" t="s" s="2">
-        <v>1257</v>
+        <v>1258</v>
       </c>
       <c r="B565" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="C565" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="D565" s="2"/>
       <c r="E565" t="s" s="2">
@@ -65140,13 +65144,13 @@
         <v>367</v>
       </c>
       <c r="M565" t="s" s="2">
-        <v>1363</v>
+        <v>1364</v>
       </c>
       <c r="N565" t="s" s="2">
-        <v>1364</v>
+        <v>1365</v>
       </c>
       <c r="O565" t="s" s="2">
-        <v>1365</v>
+        <v>1366</v>
       </c>
       <c r="P565" s="2"/>
       <c r="Q565" t="s" s="2">
@@ -65175,10 +65179,10 @@
         <v>107</v>
       </c>
       <c r="Z565" t="s" s="2">
-        <v>1366</v>
+        <v>1367</v>
       </c>
       <c r="AA565" t="s" s="2">
-        <v>1367</v>
+        <v>1368</v>
       </c>
       <c r="AB565" t="s" s="2">
         <v>23</v>
@@ -65196,7 +65200,7 @@
         <v>23</v>
       </c>
       <c r="AG565" t="s" s="2">
-        <v>1362</v>
+        <v>1363</v>
       </c>
       <c r="AH565" t="s" s="2">
         <v>76</v>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-07-29T17:39:31+00:00</t>
+    <t>2026-08-26T12:53:55+00:00</t>
   </si>
   <si>
     <t>Publisher</t>

--- a/r4-ELGA-e-Medikation-main/all-profiles.xlsx
+++ b/r4-ELGA-e-Medikation-main/all-profiles.xlsx
@@ -48,7 +48,7 @@
     <t>Title</t>
   </si>
   <si>
-    <t>AT ELGA e-Medikation Collection Bundle Medikationsplan</t>
+    <t>AT ELGA e-Medikation Medikationsplan-Searchset-Bundle Medikationsplan</t>
   </si>
   <si>
     <t>Status</t>
@@ -63,7 +63,7 @@
     <t>Date</t>
   </si>
   <si>
-    <t>2026-08-26T12:53:55+00:00</t>
+    <t>2026-08-27T15:34:15+00:00</t>
   </si>
   <si>
     <t>Publisher</t>
